--- a/cypress/fixtures/run-log.xlsx
+++ b/cypress/fixtures/run-log.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AD6"/>
+  <dimension ref="A1:AD32"/>
   <sheetData>
     <row r="1" xml:space="preserve">
       <c r="A1" t="str" xml:space="preserve">
@@ -888,9 +888,2011 @@
         <v>Yes</v>
       </c>
     </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>(243)</v>
+      </c>
+      <c r="B7" t="str">
+        <v>(1) Viet Nga Group, (2) Việt Nga Group-THT HKD Thanh Mai</v>
+      </c>
+      <c r="C7" t="str">
+        <v>73399</v>
+      </c>
+      <c r="D7" t="str">
+        <v>388673145</v>
+      </c>
+      <c r="E7" t="str">
+        <v>NGUYỄN VĂN DƯỜNG</v>
+      </c>
+      <c r="F7" t="str">
+        <v>HỘ KINH DOANH THANH MAI</v>
+      </c>
+      <c r="J7" t="str">
+        <v>Intensive rice production // Trồng lúa thâm canh</v>
+      </c>
+      <c r="K7" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="L7" t="str">
+        <v>Male // Nam</v>
+      </c>
+      <c r="M7" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="N7" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O7" t="str">
+        <v>0</v>
+      </c>
+      <c r="P7" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="str">
+        <v>0</v>
+      </c>
+      <c r="R7" t="str">
+        <v>0</v>
+      </c>
+      <c r="S7" t="str">
+        <v>0</v>
+      </c>
+      <c r="T7" t="str">
+        <v>0</v>
+      </c>
+      <c r="U7" t="str">
+        <v>4</v>
+      </c>
+      <c r="V7" t="str">
+        <v>0</v>
+      </c>
+      <c r="W7" t="str">
+        <v>3</v>
+      </c>
+      <c r="X7" t="str">
+        <v>4/6/26</v>
+      </c>
+      <c r="Y7" t="str">
+        <v>7/10/26</v>
+      </c>
+      <c r="Z7" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="AB7" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="AD7" t="str">
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>(245)</v>
+      </c>
+      <c r="B8" t="str">
+        <v>(1) Viet Nga Group, (2) Việt Nga Group-THT HKD Thanh Mai</v>
+      </c>
+      <c r="C8" t="str">
+        <v>73401</v>
+      </c>
+      <c r="D8" t="str">
+        <v>359757527</v>
+      </c>
+      <c r="E8" t="str">
+        <v>NGUYỄN THANH NHÀN</v>
+      </c>
+      <c r="F8" t="str">
+        <v>HỘ KINH DOANH THANH MAI</v>
+      </c>
+      <c r="J8" t="str">
+        <v>Intensive rice production // Trồng lúa thâm canh</v>
+      </c>
+      <c r="K8" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="L8" t="str">
+        <v>Female // Nữ</v>
+      </c>
+      <c r="M8" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="N8" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O8" t="str">
+        <v>1</v>
+      </c>
+      <c r="P8" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="str">
+        <v>0</v>
+      </c>
+      <c r="R8" t="str">
+        <v>0</v>
+      </c>
+      <c r="S8" t="str">
+        <v>0</v>
+      </c>
+      <c r="T8" t="str">
+        <v>0</v>
+      </c>
+      <c r="U8" t="str">
+        <v>4</v>
+      </c>
+      <c r="V8" t="str">
+        <v>0</v>
+      </c>
+      <c r="W8" t="str">
+        <v>3</v>
+      </c>
+      <c r="X8" t="str">
+        <v>4/6/26</v>
+      </c>
+      <c r="Y8" t="str">
+        <v>7/10/26</v>
+      </c>
+      <c r="Z8" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="AB8" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="AD8" t="str">
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>(246)</v>
+      </c>
+      <c r="B9" t="str">
+        <v>(1) Viet Nga Group, (2) Việt Nga Group-THT HKD Thanh Mai</v>
+      </c>
+      <c r="C9" t="str">
+        <v>73402</v>
+      </c>
+      <c r="D9" t="str">
+        <v>382211425</v>
+      </c>
+      <c r="E9" t="str">
+        <v>HUỲNH HOÀNG DŨNG</v>
+      </c>
+      <c r="F9" t="str">
+        <v>HỘ KINH DOANH THANH MAI</v>
+      </c>
+      <c r="J9" t="str">
+        <v>Intensive rice production // Trồng lúa thâm canh</v>
+      </c>
+      <c r="K9" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="L9" t="str">
+        <v>Male // Nam</v>
+      </c>
+      <c r="M9" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="N9" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O9" t="str">
+        <v>1</v>
+      </c>
+      <c r="P9" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="str">
+        <v>0</v>
+      </c>
+      <c r="R9" t="str">
+        <v>0</v>
+      </c>
+      <c r="S9" t="str">
+        <v>0</v>
+      </c>
+      <c r="T9" t="str">
+        <v>0</v>
+      </c>
+      <c r="U9" t="str">
+        <v>3</v>
+      </c>
+      <c r="V9" t="str">
+        <v>0</v>
+      </c>
+      <c r="W9" t="str">
+        <v>2</v>
+      </c>
+      <c r="X9" t="str">
+        <v>4/6/26</v>
+      </c>
+      <c r="Y9" t="str">
+        <v>7/10/26</v>
+      </c>
+      <c r="Z9" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="AB9" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="AD9" t="str">
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>(247)</v>
+      </c>
+      <c r="B10" t="str">
+        <v>(1) Viet Nga Group, (2) Việt Nga Group-THT HKD Thanh Mai</v>
+      </c>
+      <c r="C10" t="str">
+        <v>73403</v>
+      </c>
+      <c r="D10" t="str">
+        <v>913613458</v>
+      </c>
+      <c r="E10" t="str">
+        <v>ĐINH THÀNH NGUYÊN</v>
+      </c>
+      <c r="F10" t="str">
+        <v>HỘ KINH DOANH THANH MAI</v>
+      </c>
+      <c r="J10" t="str">
+        <v>Intensive rice production // Trồng lúa thâm canh</v>
+      </c>
+      <c r="K10" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="L10" t="str">
+        <v>Male // Nam</v>
+      </c>
+      <c r="M10" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="N10" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O10" t="str">
+        <v>0</v>
+      </c>
+      <c r="P10" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="str">
+        <v>0</v>
+      </c>
+      <c r="R10" t="str">
+        <v>0</v>
+      </c>
+      <c r="S10" t="str">
+        <v>0</v>
+      </c>
+      <c r="T10" t="str">
+        <v>0</v>
+      </c>
+      <c r="U10" t="str">
+        <v>2</v>
+      </c>
+      <c r="V10" t="str">
+        <v>0</v>
+      </c>
+      <c r="W10" t="str">
+        <v>1</v>
+      </c>
+      <c r="X10" t="str">
+        <v>4/6/26</v>
+      </c>
+      <c r="Y10" t="str">
+        <v>7/10/26</v>
+      </c>
+      <c r="Z10" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="AB10" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="AD10" t="str">
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>(249)</v>
+      </c>
+      <c r="B11" t="str">
+        <v>(1) Viet Nga Group, (2) Việt Nga Group-THT HKD Thanh Mai</v>
+      </c>
+      <c r="C11" t="str">
+        <v>73405</v>
+      </c>
+      <c r="D11" t="str">
+        <v>834994432</v>
+      </c>
+      <c r="E11" t="str">
+        <v>NGUYỄN VĂN NHÁNH</v>
+      </c>
+      <c r="F11" t="str">
+        <v>HỘ KINH DOANH THANH MAI</v>
+      </c>
+      <c r="J11" t="str">
+        <v>Intensive rice production // Trồng lúa thâm canh</v>
+      </c>
+      <c r="K11" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="L11" t="str">
+        <v>Male // Nam</v>
+      </c>
+      <c r="M11" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="N11" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O11" t="str">
+        <v>0</v>
+      </c>
+      <c r="P11" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="str">
+        <v>0</v>
+      </c>
+      <c r="R11" t="str">
+        <v>0</v>
+      </c>
+      <c r="S11" t="str">
+        <v>0</v>
+      </c>
+      <c r="T11" t="str">
+        <v>0</v>
+      </c>
+      <c r="U11" t="str">
+        <v>4</v>
+      </c>
+      <c r="V11" t="str">
+        <v>0</v>
+      </c>
+      <c r="W11" t="str">
+        <v>3</v>
+      </c>
+      <c r="X11" t="str">
+        <v>4/6/26</v>
+      </c>
+      <c r="Y11" t="str">
+        <v>7/10/26</v>
+      </c>
+      <c r="Z11" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="AB11" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="AD11" t="str">
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>(250)</v>
+      </c>
+      <c r="B12" t="str">
+        <v>(1) Viet Nga Group, (2) Việt Nga Group-THT HKD Thanh Mai</v>
+      </c>
+      <c r="C12" t="str">
+        <v>73406</v>
+      </c>
+      <c r="D12" t="str">
+        <v>936735077</v>
+      </c>
+      <c r="E12" t="str">
+        <v>NGUYỄN MINH TRƯỜNG</v>
+      </c>
+      <c r="F12" t="str">
+        <v>HỘ KINH DOANH THANH MAI</v>
+      </c>
+      <c r="J12" t="str">
+        <v>Intensive rice production // Trồng lúa thâm canh</v>
+      </c>
+      <c r="K12" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="L12" t="str">
+        <v>Male // Nam</v>
+      </c>
+      <c r="M12" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="N12" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O12" t="str">
+        <v>1</v>
+      </c>
+      <c r="P12" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q12" t="str">
+        <v>0</v>
+      </c>
+      <c r="R12" t="str">
+        <v>0</v>
+      </c>
+      <c r="S12" t="str">
+        <v>0</v>
+      </c>
+      <c r="T12" t="str">
+        <v>0</v>
+      </c>
+      <c r="U12" t="str">
+        <v>3</v>
+      </c>
+      <c r="V12" t="str">
+        <v>0</v>
+      </c>
+      <c r="W12" t="str">
+        <v>2</v>
+      </c>
+      <c r="X12" t="str">
+        <v>4/6/26</v>
+      </c>
+      <c r="Y12" t="str">
+        <v>7/10/26</v>
+      </c>
+      <c r="Z12" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="AB12" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="AD12" t="str">
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>(251)</v>
+      </c>
+      <c r="B13" t="str">
+        <v>(1) Viet Nga Group, (2) Việt Nga Group-THT HKD Thanh Mai</v>
+      </c>
+      <c r="C13" t="str">
+        <v>73407</v>
+      </c>
+      <c r="D13" t="str">
+        <v>356309142</v>
+      </c>
+      <c r="E13" t="str">
+        <v>TRẦN VĂN VĨNH</v>
+      </c>
+      <c r="F13" t="str">
+        <v>HỘ KINH DOANH THANH MAI</v>
+      </c>
+      <c r="J13" t="str">
+        <v>Intensive rice production // Trồng lúa thâm canh</v>
+      </c>
+      <c r="K13" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="L13" t="str">
+        <v>Male // Nam</v>
+      </c>
+      <c r="M13" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="N13" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O13" t="str">
+        <v>0</v>
+      </c>
+      <c r="P13" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="str">
+        <v>0</v>
+      </c>
+      <c r="R13" t="str">
+        <v>0</v>
+      </c>
+      <c r="S13" t="str">
+        <v>0</v>
+      </c>
+      <c r="T13" t="str">
+        <v>0</v>
+      </c>
+      <c r="U13" t="str">
+        <v>2</v>
+      </c>
+      <c r="V13" t="str">
+        <v>0</v>
+      </c>
+      <c r="W13" t="str">
+        <v>1</v>
+      </c>
+      <c r="X13" t="str">
+        <v>4/6/26</v>
+      </c>
+      <c r="Y13" t="str">
+        <v>7/10/26</v>
+      </c>
+      <c r="Z13" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="AB13" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="AD13" t="str">
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>(256)</v>
+      </c>
+      <c r="B14" t="str">
+        <v>(1) Viet Nga Group, (2) Việt Nga Group-THT HKD Thanh Mai</v>
+      </c>
+      <c r="C14" t="str">
+        <v>73412</v>
+      </c>
+      <c r="D14" t="str">
+        <v>388443780</v>
+      </c>
+      <c r="E14" t="str">
+        <v>PHAN VĂN BE</v>
+      </c>
+      <c r="F14" t="str">
+        <v>HỘ KINH DOANH THANH MAI</v>
+      </c>
+      <c r="J14" t="str">
+        <v>Intensive rice production // Trồng lúa thâm canh</v>
+      </c>
+      <c r="K14" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="L14" t="str">
+        <v>Male // Nam</v>
+      </c>
+      <c r="M14" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="N14" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O14" t="str">
+        <v>0</v>
+      </c>
+      <c r="P14" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q14" t="str">
+        <v>0</v>
+      </c>
+      <c r="R14" t="str">
+        <v>0</v>
+      </c>
+      <c r="S14" t="str">
+        <v>0</v>
+      </c>
+      <c r="T14" t="str">
+        <v>0</v>
+      </c>
+      <c r="U14" t="str">
+        <v>4</v>
+      </c>
+      <c r="V14" t="str">
+        <v>0</v>
+      </c>
+      <c r="W14" t="str">
+        <v>3</v>
+      </c>
+      <c r="X14" t="str">
+        <v>4/6/26</v>
+      </c>
+      <c r="Y14" t="str">
+        <v>7/10/26</v>
+      </c>
+      <c r="Z14" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="AB14" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="AD14" t="str">
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>(243)</v>
+      </c>
+      <c r="B15" t="str">
+        <v>(1) Viet Nga Group, (2) Việt Nga Group-THT HKD Thanh Mai</v>
+      </c>
+      <c r="C15" t="str">
+        <v>73399</v>
+      </c>
+      <c r="D15" t="str">
+        <v>388673145</v>
+      </c>
+      <c r="E15" t="str">
+        <v>NGUYỄN VĂN DƯỜNG</v>
+      </c>
+      <c r="F15" t="str">
+        <v>HỘ KINH DOANH THANH MAI</v>
+      </c>
+      <c r="J15" t="str">
+        <v>Intensive rice production // Trồng lúa thâm canh</v>
+      </c>
+      <c r="K15" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="L15" t="str">
+        <v>Male // Nam</v>
+      </c>
+      <c r="M15" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="N15" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O15" t="str">
+        <v>0</v>
+      </c>
+      <c r="P15" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q15" t="str">
+        <v>0</v>
+      </c>
+      <c r="R15" t="str">
+        <v>0</v>
+      </c>
+      <c r="S15" t="str">
+        <v>0</v>
+      </c>
+      <c r="T15" t="str">
+        <v>0</v>
+      </c>
+      <c r="U15" t="str">
+        <v>4</v>
+      </c>
+      <c r="V15" t="str">
+        <v>0</v>
+      </c>
+      <c r="W15" t="str">
+        <v>3</v>
+      </c>
+      <c r="X15" t="str">
+        <v>4/6/26</v>
+      </c>
+      <c r="Y15" t="str">
+        <v>7/10/26</v>
+      </c>
+      <c r="Z15" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="AB15" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="AD15" t="str">
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>(245)</v>
+      </c>
+      <c r="B16" t="str">
+        <v>(1) Viet Nga Group, (2) Việt Nga Group-THT HKD Thanh Mai</v>
+      </c>
+      <c r="C16" t="str">
+        <v>73401</v>
+      </c>
+      <c r="D16" t="str">
+        <v>359757527</v>
+      </c>
+      <c r="E16" t="str">
+        <v>NGUYỄN THANH NHÀN</v>
+      </c>
+      <c r="F16" t="str">
+        <v>HỘ KINH DOANH THANH MAI</v>
+      </c>
+      <c r="J16" t="str">
+        <v>Intensive rice production // Trồng lúa thâm canh</v>
+      </c>
+      <c r="K16" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="L16" t="str">
+        <v>Female // Nữ</v>
+      </c>
+      <c r="M16" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="N16" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O16" t="str">
+        <v>1</v>
+      </c>
+      <c r="P16" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q16" t="str">
+        <v>0</v>
+      </c>
+      <c r="R16" t="str">
+        <v>0</v>
+      </c>
+      <c r="S16" t="str">
+        <v>0</v>
+      </c>
+      <c r="T16" t="str">
+        <v>0</v>
+      </c>
+      <c r="U16" t="str">
+        <v>4</v>
+      </c>
+      <c r="V16" t="str">
+        <v>0</v>
+      </c>
+      <c r="W16" t="str">
+        <v>3</v>
+      </c>
+      <c r="X16" t="str">
+        <v>4/6/26</v>
+      </c>
+      <c r="Y16" t="str">
+        <v>7/10/26</v>
+      </c>
+      <c r="Z16" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="AB16" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="AD16" t="str">
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>(246)</v>
+      </c>
+      <c r="B17" t="str">
+        <v>(1) Viet Nga Group, (2) Việt Nga Group-THT HKD Thanh Mai</v>
+      </c>
+      <c r="C17" t="str">
+        <v>73402</v>
+      </c>
+      <c r="D17" t="str">
+        <v>382211425</v>
+      </c>
+      <c r="E17" t="str">
+        <v>HUỲNH HOÀNG DŨNG</v>
+      </c>
+      <c r="F17" t="str">
+        <v>HỘ KINH DOANH THANH MAI</v>
+      </c>
+      <c r="J17" t="str">
+        <v>Intensive rice production // Trồng lúa thâm canh</v>
+      </c>
+      <c r="K17" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="L17" t="str">
+        <v>Male // Nam</v>
+      </c>
+      <c r="M17" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="N17" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O17" t="str">
+        <v>1</v>
+      </c>
+      <c r="P17" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="str">
+        <v>0</v>
+      </c>
+      <c r="R17" t="str">
+        <v>0</v>
+      </c>
+      <c r="S17" t="str">
+        <v>0</v>
+      </c>
+      <c r="T17" t="str">
+        <v>0</v>
+      </c>
+      <c r="U17" t="str">
+        <v>3</v>
+      </c>
+      <c r="V17" t="str">
+        <v>0</v>
+      </c>
+      <c r="W17" t="str">
+        <v>2</v>
+      </c>
+      <c r="X17" t="str">
+        <v>4/6/26</v>
+      </c>
+      <c r="Y17" t="str">
+        <v>7/10/26</v>
+      </c>
+      <c r="Z17" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="AB17" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="AD17" t="str">
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>(247)</v>
+      </c>
+      <c r="B18" t="str">
+        <v>(1) Viet Nga Group, (2) Việt Nga Group-THT HKD Thanh Mai</v>
+      </c>
+      <c r="C18" t="str">
+        <v>73403</v>
+      </c>
+      <c r="D18" t="str">
+        <v>913613458</v>
+      </c>
+      <c r="E18" t="str">
+        <v>ĐINH THÀNH NGUYÊN</v>
+      </c>
+      <c r="F18" t="str">
+        <v>HỘ KINH DOANH THANH MAI</v>
+      </c>
+      <c r="J18" t="str">
+        <v>Intensive rice production // Trồng lúa thâm canh</v>
+      </c>
+      <c r="K18" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="L18" t="str">
+        <v>Male // Nam</v>
+      </c>
+      <c r="M18" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="N18" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O18" t="str">
+        <v>0</v>
+      </c>
+      <c r="P18" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q18" t="str">
+        <v>0</v>
+      </c>
+      <c r="R18" t="str">
+        <v>0</v>
+      </c>
+      <c r="S18" t="str">
+        <v>0</v>
+      </c>
+      <c r="T18" t="str">
+        <v>0</v>
+      </c>
+      <c r="U18" t="str">
+        <v>2</v>
+      </c>
+      <c r="V18" t="str">
+        <v>0</v>
+      </c>
+      <c r="W18" t="str">
+        <v>1</v>
+      </c>
+      <c r="X18" t="str">
+        <v>4/6/26</v>
+      </c>
+      <c r="Y18" t="str">
+        <v>7/10/26</v>
+      </c>
+      <c r="Z18" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="AB18" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="AD18" t="str">
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>(249)</v>
+      </c>
+      <c r="B19" t="str">
+        <v>(1) Viet Nga Group, (2) Việt Nga Group-THT HKD Thanh Mai</v>
+      </c>
+      <c r="C19" t="str">
+        <v>73405</v>
+      </c>
+      <c r="D19" t="str">
+        <v>834994432</v>
+      </c>
+      <c r="E19" t="str">
+        <v>NGUYỄN VĂN NHÁNH</v>
+      </c>
+      <c r="F19" t="str">
+        <v>HỘ KINH DOANH THANH MAI</v>
+      </c>
+      <c r="J19" t="str">
+        <v>Intensive rice production // Trồng lúa thâm canh</v>
+      </c>
+      <c r="K19" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="L19" t="str">
+        <v>Male // Nam</v>
+      </c>
+      <c r="M19" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="N19" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O19" t="str">
+        <v>0</v>
+      </c>
+      <c r="P19" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q19" t="str">
+        <v>0</v>
+      </c>
+      <c r="R19" t="str">
+        <v>0</v>
+      </c>
+      <c r="S19" t="str">
+        <v>0</v>
+      </c>
+      <c r="T19" t="str">
+        <v>0</v>
+      </c>
+      <c r="U19" t="str">
+        <v>4</v>
+      </c>
+      <c r="V19" t="str">
+        <v>0</v>
+      </c>
+      <c r="W19" t="str">
+        <v>3</v>
+      </c>
+      <c r="X19" t="str">
+        <v>4/6/26</v>
+      </c>
+      <c r="Y19" t="str">
+        <v>7/10/26</v>
+      </c>
+      <c r="Z19" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="AB19" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="AD19" t="str">
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>(250)</v>
+      </c>
+      <c r="B20" t="str">
+        <v>(1) Viet Nga Group, (2) Việt Nga Group-THT HKD Thanh Mai</v>
+      </c>
+      <c r="C20" t="str">
+        <v>73406</v>
+      </c>
+      <c r="D20" t="str">
+        <v>936735077</v>
+      </c>
+      <c r="E20" t="str">
+        <v>NGUYỄN MINH TRƯỜNG</v>
+      </c>
+      <c r="F20" t="str">
+        <v>HỘ KINH DOANH THANH MAI</v>
+      </c>
+      <c r="J20" t="str">
+        <v>Intensive rice production // Trồng lúa thâm canh</v>
+      </c>
+      <c r="K20" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="L20" t="str">
+        <v>Male // Nam</v>
+      </c>
+      <c r="M20" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="N20" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O20" t="str">
+        <v>1</v>
+      </c>
+      <c r="P20" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q20" t="str">
+        <v>0</v>
+      </c>
+      <c r="R20" t="str">
+        <v>0</v>
+      </c>
+      <c r="S20" t="str">
+        <v>0</v>
+      </c>
+      <c r="T20" t="str">
+        <v>0</v>
+      </c>
+      <c r="U20" t="str">
+        <v>3</v>
+      </c>
+      <c r="V20" t="str">
+        <v>0</v>
+      </c>
+      <c r="W20" t="str">
+        <v>2</v>
+      </c>
+      <c r="X20" t="str">
+        <v>4/6/26</v>
+      </c>
+      <c r="Y20" t="str">
+        <v>7/10/26</v>
+      </c>
+      <c r="Z20" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="AB20" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="AD20" t="str">
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="str">
+        <v>(251)</v>
+      </c>
+      <c r="B21" t="str">
+        <v>(1) Viet Nga Group, (2) Việt Nga Group-THT HKD Thanh Mai</v>
+      </c>
+      <c r="C21" t="str">
+        <v>73407</v>
+      </c>
+      <c r="D21" t="str">
+        <v>356309142</v>
+      </c>
+      <c r="E21" t="str">
+        <v>TRẦN VĂN VĨNH</v>
+      </c>
+      <c r="F21" t="str">
+        <v>HỘ KINH DOANH THANH MAI</v>
+      </c>
+      <c r="J21" t="str">
+        <v>Intensive rice production // Trồng lúa thâm canh</v>
+      </c>
+      <c r="K21" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="L21" t="str">
+        <v>Male // Nam</v>
+      </c>
+      <c r="M21" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="N21" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O21" t="str">
+        <v>0</v>
+      </c>
+      <c r="P21" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q21" t="str">
+        <v>0</v>
+      </c>
+      <c r="R21" t="str">
+        <v>0</v>
+      </c>
+      <c r="S21" t="str">
+        <v>0</v>
+      </c>
+      <c r="T21" t="str">
+        <v>0</v>
+      </c>
+      <c r="U21" t="str">
+        <v>2</v>
+      </c>
+      <c r="V21" t="str">
+        <v>0</v>
+      </c>
+      <c r="W21" t="str">
+        <v>1</v>
+      </c>
+      <c r="X21" t="str">
+        <v>4/6/26</v>
+      </c>
+      <c r="Y21" t="str">
+        <v>7/10/26</v>
+      </c>
+      <c r="Z21" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="AB21" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="AD21" t="str">
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="str">
+        <v>(256)</v>
+      </c>
+      <c r="B22" t="str">
+        <v>(1) Viet Nga Group, (2) Việt Nga Group-THT HKD Thanh Mai</v>
+      </c>
+      <c r="C22" t="str">
+        <v>73412</v>
+      </c>
+      <c r="D22" t="str">
+        <v>388443780</v>
+      </c>
+      <c r="E22" t="str">
+        <v>PHAN VĂN BE</v>
+      </c>
+      <c r="F22" t="str">
+        <v>HỘ KINH DOANH THANH MAI</v>
+      </c>
+      <c r="J22" t="str">
+        <v>Intensive rice production // Trồng lúa thâm canh</v>
+      </c>
+      <c r="K22" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="L22" t="str">
+        <v>Male // Nam</v>
+      </c>
+      <c r="M22" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="N22" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O22" t="str">
+        <v>0</v>
+      </c>
+      <c r="P22" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q22" t="str">
+        <v>0</v>
+      </c>
+      <c r="R22" t="str">
+        <v>0</v>
+      </c>
+      <c r="S22" t="str">
+        <v>0</v>
+      </c>
+      <c r="T22" t="str">
+        <v>0</v>
+      </c>
+      <c r="U22" t="str">
+        <v>4</v>
+      </c>
+      <c r="V22" t="str">
+        <v>0</v>
+      </c>
+      <c r="W22" t="str">
+        <v>3</v>
+      </c>
+      <c r="X22" t="str">
+        <v>4/6/26</v>
+      </c>
+      <c r="Y22" t="str">
+        <v>7/10/26</v>
+      </c>
+      <c r="Z22" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="AB22" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="AD22" t="str">
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="str">
+        <v>(243)</v>
+      </c>
+      <c r="B23" t="str">
+        <v>(1) Viet Nga Group, (2) Việt Nga Group-THT HKD Thanh Mai</v>
+      </c>
+      <c r="C23" t="str">
+        <v>73399</v>
+      </c>
+      <c r="D23" t="str">
+        <v>388673145</v>
+      </c>
+      <c r="E23" t="str">
+        <v>NGUYỄN VĂN DƯỜNG</v>
+      </c>
+      <c r="F23" t="str">
+        <v>HỘ KINH DOANH THANH MAI</v>
+      </c>
+      <c r="J23" t="str">
+        <v>Intensive rice production // Trồng lúa thâm canh</v>
+      </c>
+      <c r="K23" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="L23" t="str">
+        <v>Male // Nam</v>
+      </c>
+      <c r="M23" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="N23" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O23" t="str">
+        <v>0</v>
+      </c>
+      <c r="P23" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q23" t="str">
+        <v>0</v>
+      </c>
+      <c r="R23" t="str">
+        <v>0</v>
+      </c>
+      <c r="S23" t="str">
+        <v>0</v>
+      </c>
+      <c r="T23" t="str">
+        <v>0</v>
+      </c>
+      <c r="U23" t="str">
+        <v>4</v>
+      </c>
+      <c r="V23" t="str">
+        <v>0</v>
+      </c>
+      <c r="W23" t="str">
+        <v>3</v>
+      </c>
+      <c r="X23" t="str">
+        <v>4/6/26</v>
+      </c>
+      <c r="Y23" t="str">
+        <v>7/10/26</v>
+      </c>
+      <c r="Z23" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="AB23" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="AD23" t="str">
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="str">
+        <v>(245)</v>
+      </c>
+      <c r="B24" t="str">
+        <v>(1) Viet Nga Group, (2) Việt Nga Group-THT HKD Thanh Mai</v>
+      </c>
+      <c r="C24" t="str">
+        <v>73401</v>
+      </c>
+      <c r="D24" t="str">
+        <v>359757527</v>
+      </c>
+      <c r="E24" t="str">
+        <v>NGUYỄN THANH NHÀN</v>
+      </c>
+      <c r="F24" t="str">
+        <v>HỘ KINH DOANH THANH MAI</v>
+      </c>
+      <c r="J24" t="str">
+        <v>Intensive rice production // Trồng lúa thâm canh</v>
+      </c>
+      <c r="K24" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="L24" t="str">
+        <v>Female // Nữ</v>
+      </c>
+      <c r="M24" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="N24" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O24" t="str">
+        <v>1</v>
+      </c>
+      <c r="P24" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q24" t="str">
+        <v>0</v>
+      </c>
+      <c r="R24" t="str">
+        <v>0</v>
+      </c>
+      <c r="S24" t="str">
+        <v>0</v>
+      </c>
+      <c r="T24" t="str">
+        <v>0</v>
+      </c>
+      <c r="U24" t="str">
+        <v>4</v>
+      </c>
+      <c r="V24" t="str">
+        <v>0</v>
+      </c>
+      <c r="W24" t="str">
+        <v>3</v>
+      </c>
+      <c r="X24" t="str">
+        <v>4/6/26</v>
+      </c>
+      <c r="Y24" t="str">
+        <v>7/10/26</v>
+      </c>
+      <c r="Z24" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="AB24" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="AD24" t="str">
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="str">
+        <v>(246)</v>
+      </c>
+      <c r="B25" t="str">
+        <v>(1) Viet Nga Group, (2) Việt Nga Group-THT HKD Thanh Mai</v>
+      </c>
+      <c r="C25" t="str">
+        <v>73402</v>
+      </c>
+      <c r="D25" t="str">
+        <v>382211425</v>
+      </c>
+      <c r="E25" t="str">
+        <v>HUỲNH HOÀNG DŨNG</v>
+      </c>
+      <c r="F25" t="str">
+        <v>HỘ KINH DOANH THANH MAI</v>
+      </c>
+      <c r="J25" t="str">
+        <v>Intensive rice production // Trồng lúa thâm canh</v>
+      </c>
+      <c r="K25" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="L25" t="str">
+        <v>Male // Nam</v>
+      </c>
+      <c r="M25" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="N25" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O25" t="str">
+        <v>1</v>
+      </c>
+      <c r="P25" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q25" t="str">
+        <v>0</v>
+      </c>
+      <c r="R25" t="str">
+        <v>0</v>
+      </c>
+      <c r="S25" t="str">
+        <v>0</v>
+      </c>
+      <c r="T25" t="str">
+        <v>0</v>
+      </c>
+      <c r="U25" t="str">
+        <v>3</v>
+      </c>
+      <c r="V25" t="str">
+        <v>0</v>
+      </c>
+      <c r="W25" t="str">
+        <v>2</v>
+      </c>
+      <c r="X25" t="str">
+        <v>4/6/26</v>
+      </c>
+      <c r="Y25" t="str">
+        <v>7/10/26</v>
+      </c>
+      <c r="Z25" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="AB25" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="AD25" t="str">
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="str">
+        <v>(247)</v>
+      </c>
+      <c r="B26" t="str">
+        <v>(1) Viet Nga Group, (2) Việt Nga Group-THT HKD Thanh Mai</v>
+      </c>
+      <c r="C26" t="str">
+        <v>73403</v>
+      </c>
+      <c r="D26" t="str">
+        <v>913613458</v>
+      </c>
+      <c r="E26" t="str">
+        <v>ĐINH THÀNH NGUYÊN</v>
+      </c>
+      <c r="F26" t="str">
+        <v>HỘ KINH DOANH THANH MAI</v>
+      </c>
+      <c r="J26" t="str">
+        <v>Intensive rice production // Trồng lúa thâm canh</v>
+      </c>
+      <c r="K26" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="L26" t="str">
+        <v>Male // Nam</v>
+      </c>
+      <c r="M26" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="N26" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O26" t="str">
+        <v>0</v>
+      </c>
+      <c r="P26" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q26" t="str">
+        <v>0</v>
+      </c>
+      <c r="R26" t="str">
+        <v>0</v>
+      </c>
+      <c r="S26" t="str">
+        <v>0</v>
+      </c>
+      <c r="T26" t="str">
+        <v>0</v>
+      </c>
+      <c r="U26" t="str">
+        <v>2</v>
+      </c>
+      <c r="V26" t="str">
+        <v>0</v>
+      </c>
+      <c r="W26" t="str">
+        <v>1</v>
+      </c>
+      <c r="X26" t="str">
+        <v>4/6/26</v>
+      </c>
+      <c r="Y26" t="str">
+        <v>7/10/26</v>
+      </c>
+      <c r="Z26" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="AB26" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="AD26" t="str">
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="str">
+        <v>(249)</v>
+      </c>
+      <c r="B27" t="str">
+        <v>(1) Viet Nga Group, (2) Việt Nga Group-THT HKD Thanh Mai</v>
+      </c>
+      <c r="C27" t="str">
+        <v>73405</v>
+      </c>
+      <c r="D27" t="str">
+        <v>834994432</v>
+      </c>
+      <c r="E27" t="str">
+        <v>NGUYỄN VĂN NHÁNH</v>
+      </c>
+      <c r="F27" t="str">
+        <v>HỘ KINH DOANH THANH MAI</v>
+      </c>
+      <c r="J27" t="str">
+        <v>Intensive rice production // Trồng lúa thâm canh</v>
+      </c>
+      <c r="K27" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="L27" t="str">
+        <v>Male // Nam</v>
+      </c>
+      <c r="M27" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="N27" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O27" t="str">
+        <v>0</v>
+      </c>
+      <c r="P27" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q27" t="str">
+        <v>0</v>
+      </c>
+      <c r="R27" t="str">
+        <v>0</v>
+      </c>
+      <c r="S27" t="str">
+        <v>0</v>
+      </c>
+      <c r="T27" t="str">
+        <v>0</v>
+      </c>
+      <c r="U27" t="str">
+        <v>4</v>
+      </c>
+      <c r="V27" t="str">
+        <v>0</v>
+      </c>
+      <c r="W27" t="str">
+        <v>3</v>
+      </c>
+      <c r="X27" t="str">
+        <v>4/6/26</v>
+      </c>
+      <c r="Y27" t="str">
+        <v>7/10/26</v>
+      </c>
+      <c r="Z27" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="AB27" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="AD27" t="str">
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="str">
+        <v>(250)</v>
+      </c>
+      <c r="B28" t="str">
+        <v>(1) Viet Nga Group, (2) Việt Nga Group-THT HKD Thanh Mai</v>
+      </c>
+      <c r="C28" t="str">
+        <v>73406</v>
+      </c>
+      <c r="D28" t="str">
+        <v>936735077</v>
+      </c>
+      <c r="E28" t="str">
+        <v>NGUYỄN MINH TRƯỜNG</v>
+      </c>
+      <c r="F28" t="str">
+        <v>HỘ KINH DOANH THANH MAI</v>
+      </c>
+      <c r="J28" t="str">
+        <v>Intensive rice production // Trồng lúa thâm canh</v>
+      </c>
+      <c r="K28" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="L28" t="str">
+        <v>Male // Nam</v>
+      </c>
+      <c r="M28" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="N28" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O28" t="str">
+        <v>1</v>
+      </c>
+      <c r="P28" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q28" t="str">
+        <v>0</v>
+      </c>
+      <c r="R28" t="str">
+        <v>0</v>
+      </c>
+      <c r="S28" t="str">
+        <v>0</v>
+      </c>
+      <c r="T28" t="str">
+        <v>0</v>
+      </c>
+      <c r="U28" t="str">
+        <v>3</v>
+      </c>
+      <c r="V28" t="str">
+        <v>0</v>
+      </c>
+      <c r="W28" t="str">
+        <v>2</v>
+      </c>
+      <c r="X28" t="str">
+        <v>4/6/26</v>
+      </c>
+      <c r="Y28" t="str">
+        <v>7/10/26</v>
+      </c>
+      <c r="Z28" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="AB28" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="AD28" t="str">
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="str">
+        <v>(251)</v>
+      </c>
+      <c r="B29" t="str">
+        <v>(1) Viet Nga Group, (2) Việt Nga Group-THT HKD Thanh Mai</v>
+      </c>
+      <c r="C29" t="str">
+        <v>73407</v>
+      </c>
+      <c r="D29" t="str">
+        <v>356309142</v>
+      </c>
+      <c r="E29" t="str">
+        <v>TRẦN VĂN VĨNH</v>
+      </c>
+      <c r="F29" t="str">
+        <v>HỘ KINH DOANH THANH MAI</v>
+      </c>
+      <c r="J29" t="str">
+        <v>Intensive rice production // Trồng lúa thâm canh</v>
+      </c>
+      <c r="K29" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="L29" t="str">
+        <v>Male // Nam</v>
+      </c>
+      <c r="M29" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="N29" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O29" t="str">
+        <v>0</v>
+      </c>
+      <c r="P29" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q29" t="str">
+        <v>0</v>
+      </c>
+      <c r="R29" t="str">
+        <v>0</v>
+      </c>
+      <c r="S29" t="str">
+        <v>0</v>
+      </c>
+      <c r="T29" t="str">
+        <v>0</v>
+      </c>
+      <c r="U29" t="str">
+        <v>2</v>
+      </c>
+      <c r="V29" t="str">
+        <v>0</v>
+      </c>
+      <c r="W29" t="str">
+        <v>1</v>
+      </c>
+      <c r="X29" t="str">
+        <v>4/6/26</v>
+      </c>
+      <c r="Y29" t="str">
+        <v>7/10/26</v>
+      </c>
+      <c r="Z29" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="AB29" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="AD29" t="str">
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="str">
+        <v>(256)</v>
+      </c>
+      <c r="B30" t="str">
+        <v>(1) Viet Nga Group, (2) Việt Nga Group-THT HKD Thanh Mai</v>
+      </c>
+      <c r="C30" t="str">
+        <v>73412</v>
+      </c>
+      <c r="D30" t="str">
+        <v>388443780</v>
+      </c>
+      <c r="E30" t="str">
+        <v>PHAN VĂN BE</v>
+      </c>
+      <c r="F30" t="str">
+        <v>HỘ KINH DOANH THANH MAI</v>
+      </c>
+      <c r="J30" t="str">
+        <v>Intensive rice production // Trồng lúa thâm canh</v>
+      </c>
+      <c r="K30" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="L30" t="str">
+        <v>Male // Nam</v>
+      </c>
+      <c r="M30" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="N30" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O30" t="str">
+        <v>0</v>
+      </c>
+      <c r="P30" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q30" t="str">
+        <v>0</v>
+      </c>
+      <c r="R30" t="str">
+        <v>0</v>
+      </c>
+      <c r="S30" t="str">
+        <v>0</v>
+      </c>
+      <c r="T30" t="str">
+        <v>0</v>
+      </c>
+      <c r="U30" t="str">
+        <v>4</v>
+      </c>
+      <c r="V30" t="str">
+        <v>0</v>
+      </c>
+      <c r="W30" t="str">
+        <v>3</v>
+      </c>
+      <c r="X30" t="str">
+        <v>4/6/26</v>
+      </c>
+      <c r="Y30" t="str">
+        <v>7/10/26</v>
+      </c>
+      <c r="Z30" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="AB30" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="AD30" t="str">
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="str">
+        <v>(243)</v>
+      </c>
+      <c r="B31" t="str">
+        <v>(1) Viet Nga Group, (2) Việt Nga Group-THT HKD Thanh Mai</v>
+      </c>
+      <c r="C31" t="str">
+        <v>73399</v>
+      </c>
+      <c r="D31" t="str">
+        <v>388673145</v>
+      </c>
+      <c r="E31" t="str">
+        <v>NGUYỄN VĂN DƯỜNG</v>
+      </c>
+      <c r="F31" t="str">
+        <v>HỘ KINH DOANH THANH MAI</v>
+      </c>
+      <c r="J31" t="str">
+        <v>Intensive rice production // Trồng lúa thâm canh</v>
+      </c>
+      <c r="K31" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="L31" t="str">
+        <v>Male // Nam</v>
+      </c>
+      <c r="M31" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="N31" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O31" t="str">
+        <v>0</v>
+      </c>
+      <c r="P31" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q31" t="str">
+        <v>0</v>
+      </c>
+      <c r="R31" t="str">
+        <v>0</v>
+      </c>
+      <c r="S31" t="str">
+        <v>0</v>
+      </c>
+      <c r="T31" t="str">
+        <v>0</v>
+      </c>
+      <c r="U31" t="str">
+        <v>4</v>
+      </c>
+      <c r="V31" t="str">
+        <v>0</v>
+      </c>
+      <c r="W31" t="str">
+        <v>3</v>
+      </c>
+      <c r="X31" t="str">
+        <v>4/6/26</v>
+      </c>
+      <c r="Y31" t="str">
+        <v>7/10/26</v>
+      </c>
+      <c r="Z31" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="AB31" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="AD31" t="str">
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="str">
+        <v>(245)</v>
+      </c>
+      <c r="B32" t="str">
+        <v>(1) Viet Nga Group, (2) Việt Nga Group-THT HKD Thanh Mai</v>
+      </c>
+      <c r="C32" t="str">
+        <v>73401</v>
+      </c>
+      <c r="D32" t="str">
+        <v>359757527</v>
+      </c>
+      <c r="E32" t="str">
+        <v>NGUYỄN THANH NHÀN</v>
+      </c>
+      <c r="F32" t="str">
+        <v>HỘ KINH DOANH THANH MAI</v>
+      </c>
+      <c r="J32" t="str">
+        <v>Intensive rice production // Trồng lúa thâm canh</v>
+      </c>
+      <c r="K32" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="L32" t="str">
+        <v>Female // Nữ</v>
+      </c>
+      <c r="M32" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="N32" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O32" t="str">
+        <v>1</v>
+      </c>
+      <c r="P32" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q32" t="str">
+        <v>0</v>
+      </c>
+      <c r="R32" t="str">
+        <v>0</v>
+      </c>
+      <c r="S32" t="str">
+        <v>0</v>
+      </c>
+      <c r="T32" t="str">
+        <v>0</v>
+      </c>
+      <c r="U32" t="str">
+        <v>4</v>
+      </c>
+      <c r="V32" t="str">
+        <v>0</v>
+      </c>
+      <c r="W32" t="str">
+        <v>3</v>
+      </c>
+      <c r="X32" t="str">
+        <v>4/6/26</v>
+      </c>
+      <c r="Y32" t="str">
+        <v>7/10/26</v>
+      </c>
+      <c r="Z32" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="AB32" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="AD32" t="str">
+        <v>Yes</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:AD6"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:AD32"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/cypress/fixtures/run-log.xlsx
+++ b/cypress/fixtures/run-log.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AD32"/>
+  <dimension ref="A1:AD63"/>
   <sheetData>
     <row r="1" xml:space="preserve">
       <c r="A1" t="str" xml:space="preserve">
@@ -2890,9 +2890,2396 @@
         <v>Yes</v>
       </c>
     </row>
+    <row r="33">
+      <c r="A33" t="str">
+        <v>(246)</v>
+      </c>
+      <c r="B33" t="str">
+        <v>(1) Viet Nga Group, (2) Việt Nga Group-THT HKD Thanh Mai</v>
+      </c>
+      <c r="C33" t="str">
+        <v>73402</v>
+      </c>
+      <c r="D33" t="str">
+        <v>382211425</v>
+      </c>
+      <c r="E33" t="str">
+        <v>HUỲNH HOÀNG DŨNG</v>
+      </c>
+      <c r="F33" t="str">
+        <v>HỘ KINH DOANH THANH MAI</v>
+      </c>
+      <c r="J33" t="str">
+        <v>Intensive rice production // Trồng lúa thâm canh</v>
+      </c>
+      <c r="K33" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="L33" t="str">
+        <v>Male // Nam</v>
+      </c>
+      <c r="M33" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="N33" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O33" t="str">
+        <v>1</v>
+      </c>
+      <c r="P33" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q33" t="str">
+        <v>0</v>
+      </c>
+      <c r="R33" t="str">
+        <v>0</v>
+      </c>
+      <c r="S33" t="str">
+        <v>0</v>
+      </c>
+      <c r="T33" t="str">
+        <v>0</v>
+      </c>
+      <c r="U33" t="str">
+        <v>3</v>
+      </c>
+      <c r="V33" t="str">
+        <v>0</v>
+      </c>
+      <c r="W33" t="str">
+        <v>2</v>
+      </c>
+      <c r="X33" t="str">
+        <v>4/6/26</v>
+      </c>
+      <c r="Y33" t="str">
+        <v>7/10/26</v>
+      </c>
+      <c r="Z33" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="AB33" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="AD33" t="str">
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="str">
+        <v>(247)</v>
+      </c>
+      <c r="B34" t="str">
+        <v>(1) Viet Nga Group, (2) Việt Nga Group-THT HKD Thanh Mai</v>
+      </c>
+      <c r="C34" t="str">
+        <v>73403</v>
+      </c>
+      <c r="D34" t="str">
+        <v>913613458</v>
+      </c>
+      <c r="E34" t="str">
+        <v>ĐINH THÀNH NGUYÊN</v>
+      </c>
+      <c r="F34" t="str">
+        <v>HỘ KINH DOANH THANH MAI</v>
+      </c>
+      <c r="J34" t="str">
+        <v>Intensive rice production // Trồng lúa thâm canh</v>
+      </c>
+      <c r="K34" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="L34" t="str">
+        <v>Male // Nam</v>
+      </c>
+      <c r="M34" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="N34" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O34" t="str">
+        <v>0</v>
+      </c>
+      <c r="P34" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q34" t="str">
+        <v>0</v>
+      </c>
+      <c r="R34" t="str">
+        <v>0</v>
+      </c>
+      <c r="S34" t="str">
+        <v>0</v>
+      </c>
+      <c r="T34" t="str">
+        <v>0</v>
+      </c>
+      <c r="U34" t="str">
+        <v>2</v>
+      </c>
+      <c r="V34" t="str">
+        <v>0</v>
+      </c>
+      <c r="W34" t="str">
+        <v>1</v>
+      </c>
+      <c r="X34" t="str">
+        <v>4/6/26</v>
+      </c>
+      <c r="Y34" t="str">
+        <v>7/10/26</v>
+      </c>
+      <c r="Z34" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="AB34" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="AD34" t="str">
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="str">
+        <v>(249)</v>
+      </c>
+      <c r="B35" t="str">
+        <v>(1) Viet Nga Group, (2) Việt Nga Group-THT HKD Thanh Mai</v>
+      </c>
+      <c r="C35" t="str">
+        <v>73405</v>
+      </c>
+      <c r="D35" t="str">
+        <v>834994432</v>
+      </c>
+      <c r="E35" t="str">
+        <v>NGUYỄN VĂN NHÁNH</v>
+      </c>
+      <c r="F35" t="str">
+        <v>HỘ KINH DOANH THANH MAI</v>
+      </c>
+      <c r="J35" t="str">
+        <v>Intensive rice production // Trồng lúa thâm canh</v>
+      </c>
+      <c r="K35" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="L35" t="str">
+        <v>Male // Nam</v>
+      </c>
+      <c r="M35" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="N35" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O35" t="str">
+        <v>0</v>
+      </c>
+      <c r="P35" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q35" t="str">
+        <v>0</v>
+      </c>
+      <c r="R35" t="str">
+        <v>0</v>
+      </c>
+      <c r="S35" t="str">
+        <v>0</v>
+      </c>
+      <c r="T35" t="str">
+        <v>0</v>
+      </c>
+      <c r="U35" t="str">
+        <v>4</v>
+      </c>
+      <c r="V35" t="str">
+        <v>0</v>
+      </c>
+      <c r="W35" t="str">
+        <v>3</v>
+      </c>
+      <c r="X35" t="str">
+        <v>4/6/26</v>
+      </c>
+      <c r="Y35" t="str">
+        <v>7/10/26</v>
+      </c>
+      <c r="Z35" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="AB35" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="AD35" t="str">
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="str">
+        <v>(250)</v>
+      </c>
+      <c r="B36" t="str">
+        <v>(1) Viet Nga Group, (2) Việt Nga Group-THT HKD Thanh Mai</v>
+      </c>
+      <c r="C36" t="str">
+        <v>73406</v>
+      </c>
+      <c r="D36" t="str">
+        <v>936735077</v>
+      </c>
+      <c r="E36" t="str">
+        <v>NGUYỄN MINH TRƯỜNG</v>
+      </c>
+      <c r="F36" t="str">
+        <v>HỘ KINH DOANH THANH MAI</v>
+      </c>
+      <c r="J36" t="str">
+        <v>Intensive rice production // Trồng lúa thâm canh</v>
+      </c>
+      <c r="K36" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="L36" t="str">
+        <v>Male // Nam</v>
+      </c>
+      <c r="M36" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="N36" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O36" t="str">
+        <v>1</v>
+      </c>
+      <c r="P36" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q36" t="str">
+        <v>0</v>
+      </c>
+      <c r="R36" t="str">
+        <v>0</v>
+      </c>
+      <c r="S36" t="str">
+        <v>0</v>
+      </c>
+      <c r="T36" t="str">
+        <v>0</v>
+      </c>
+      <c r="U36" t="str">
+        <v>3</v>
+      </c>
+      <c r="V36" t="str">
+        <v>0</v>
+      </c>
+      <c r="W36" t="str">
+        <v>2</v>
+      </c>
+      <c r="X36" t="str">
+        <v>4/6/26</v>
+      </c>
+      <c r="Y36" t="str">
+        <v>7/10/26</v>
+      </c>
+      <c r="Z36" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="AB36" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="AD36" t="str">
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="str">
+        <v>(251)</v>
+      </c>
+      <c r="B37" t="str">
+        <v>(1) Viet Nga Group, (2) Việt Nga Group-THT HKD Thanh Mai</v>
+      </c>
+      <c r="C37" t="str">
+        <v>73407</v>
+      </c>
+      <c r="D37" t="str">
+        <v>356309142</v>
+      </c>
+      <c r="E37" t="str">
+        <v>TRẦN VĂN VĨNH</v>
+      </c>
+      <c r="F37" t="str">
+        <v>HỘ KINH DOANH THANH MAI</v>
+      </c>
+      <c r="J37" t="str">
+        <v>Intensive rice production // Trồng lúa thâm canh</v>
+      </c>
+      <c r="K37" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="L37" t="str">
+        <v>Male // Nam</v>
+      </c>
+      <c r="M37" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="N37" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O37" t="str">
+        <v>0</v>
+      </c>
+      <c r="P37" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q37" t="str">
+        <v>0</v>
+      </c>
+      <c r="R37" t="str">
+        <v>0</v>
+      </c>
+      <c r="S37" t="str">
+        <v>0</v>
+      </c>
+      <c r="T37" t="str">
+        <v>0</v>
+      </c>
+      <c r="U37" t="str">
+        <v>2</v>
+      </c>
+      <c r="V37" t="str">
+        <v>0</v>
+      </c>
+      <c r="W37" t="str">
+        <v>1</v>
+      </c>
+      <c r="X37" t="str">
+        <v>4/6/26</v>
+      </c>
+      <c r="Y37" t="str">
+        <v>7/10/26</v>
+      </c>
+      <c r="Z37" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="AB37" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="AD37" t="str">
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="str">
+        <v>(256)</v>
+      </c>
+      <c r="B38" t="str">
+        <v>(1) Viet Nga Group, (2) Việt Nga Group-THT HKD Thanh Mai</v>
+      </c>
+      <c r="C38" t="str">
+        <v>73412</v>
+      </c>
+      <c r="D38" t="str">
+        <v>388443780</v>
+      </c>
+      <c r="E38" t="str">
+        <v>PHAN VĂN BE</v>
+      </c>
+      <c r="F38" t="str">
+        <v>HỘ KINH DOANH THANH MAI</v>
+      </c>
+      <c r="J38" t="str">
+        <v>Intensive rice production // Trồng lúa thâm canh</v>
+      </c>
+      <c r="K38" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="L38" t="str">
+        <v>Male // Nam</v>
+      </c>
+      <c r="M38" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="N38" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O38" t="str">
+        <v>0</v>
+      </c>
+      <c r="P38" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q38" t="str">
+        <v>0</v>
+      </c>
+      <c r="R38" t="str">
+        <v>0</v>
+      </c>
+      <c r="S38" t="str">
+        <v>0</v>
+      </c>
+      <c r="T38" t="str">
+        <v>0</v>
+      </c>
+      <c r="U38" t="str">
+        <v>4</v>
+      </c>
+      <c r="V38" t="str">
+        <v>0</v>
+      </c>
+      <c r="W38" t="str">
+        <v>3</v>
+      </c>
+      <c r="X38" t="str">
+        <v>4/6/26</v>
+      </c>
+      <c r="Y38" t="str">
+        <v>7/10/26</v>
+      </c>
+      <c r="Z38" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="AB38" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="AD38" t="str">
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="str">
+        <v>(243)</v>
+      </c>
+      <c r="B39" t="str">
+        <v>(1) Viet Nga Group, (2) Việt Nga Group-THT HKD Thanh Mai</v>
+      </c>
+      <c r="C39" t="str">
+        <v>73399</v>
+      </c>
+      <c r="D39" t="str">
+        <v>388673145</v>
+      </c>
+      <c r="E39" t="str">
+        <v>NGUYỄN VĂN DƯỜNG</v>
+      </c>
+      <c r="F39" t="str">
+        <v>HỘ KINH DOANH THANH MAI</v>
+      </c>
+      <c r="J39" t="str">
+        <v>Intensive rice production // Trồng lúa thâm canh</v>
+      </c>
+      <c r="K39" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="L39" t="str">
+        <v>Male // Nam</v>
+      </c>
+      <c r="M39" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="N39" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O39" t="str">
+        <v>0</v>
+      </c>
+      <c r="P39" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q39" t="str">
+        <v>0</v>
+      </c>
+      <c r="R39" t="str">
+        <v>0</v>
+      </c>
+      <c r="S39" t="str">
+        <v>0</v>
+      </c>
+      <c r="T39" t="str">
+        <v>0</v>
+      </c>
+      <c r="U39" t="str">
+        <v>4</v>
+      </c>
+      <c r="V39" t="str">
+        <v>0</v>
+      </c>
+      <c r="W39" t="str">
+        <v>3</v>
+      </c>
+      <c r="X39" t="str">
+        <v>4/6/26</v>
+      </c>
+      <c r="Y39" t="str">
+        <v>7/10/26</v>
+      </c>
+      <c r="Z39" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="AB39" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="AD39" t="str">
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="str">
+        <v>(245)</v>
+      </c>
+      <c r="B40" t="str">
+        <v>(1) Viet Nga Group, (2) Việt Nga Group-THT HKD Thanh Mai</v>
+      </c>
+      <c r="C40" t="str">
+        <v>73401</v>
+      </c>
+      <c r="D40" t="str">
+        <v>359757527</v>
+      </c>
+      <c r="E40" t="str">
+        <v>NGUYỄN THANH NHÀN</v>
+      </c>
+      <c r="F40" t="str">
+        <v>HỘ KINH DOANH THANH MAI</v>
+      </c>
+      <c r="J40" t="str">
+        <v>Intensive rice production // Trồng lúa thâm canh</v>
+      </c>
+      <c r="K40" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="L40" t="str">
+        <v>Female // Nữ</v>
+      </c>
+      <c r="M40" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="N40" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O40" t="str">
+        <v>1</v>
+      </c>
+      <c r="P40" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q40" t="str">
+        <v>0</v>
+      </c>
+      <c r="R40" t="str">
+        <v>0</v>
+      </c>
+      <c r="S40" t="str">
+        <v>0</v>
+      </c>
+      <c r="T40" t="str">
+        <v>0</v>
+      </c>
+      <c r="U40" t="str">
+        <v>4</v>
+      </c>
+      <c r="V40" t="str">
+        <v>0</v>
+      </c>
+      <c r="W40" t="str">
+        <v>3</v>
+      </c>
+      <c r="X40" t="str">
+        <v>4/6/26</v>
+      </c>
+      <c r="Y40" t="str">
+        <v>7/10/26</v>
+      </c>
+      <c r="Z40" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="AB40" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="AD40" t="str">
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="str">
+        <v>(246)</v>
+      </c>
+      <c r="B41" t="str">
+        <v>(1) Viet Nga Group, (2) Việt Nga Group-THT HKD Thanh Mai</v>
+      </c>
+      <c r="C41" t="str">
+        <v>73402</v>
+      </c>
+      <c r="D41" t="str">
+        <v>382211425</v>
+      </c>
+      <c r="E41" t="str">
+        <v>HUỲNH HOÀNG DŨNG</v>
+      </c>
+      <c r="F41" t="str">
+        <v>HỘ KINH DOANH THANH MAI</v>
+      </c>
+      <c r="J41" t="str">
+        <v>Intensive rice production // Trồng lúa thâm canh</v>
+      </c>
+      <c r="K41" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="L41" t="str">
+        <v>Male // Nam</v>
+      </c>
+      <c r="M41" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="N41" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O41" t="str">
+        <v>1</v>
+      </c>
+      <c r="P41" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q41" t="str">
+        <v>0</v>
+      </c>
+      <c r="R41" t="str">
+        <v>0</v>
+      </c>
+      <c r="S41" t="str">
+        <v>0</v>
+      </c>
+      <c r="T41" t="str">
+        <v>0</v>
+      </c>
+      <c r="U41" t="str">
+        <v>3</v>
+      </c>
+      <c r="V41" t="str">
+        <v>0</v>
+      </c>
+      <c r="W41" t="str">
+        <v>2</v>
+      </c>
+      <c r="X41" t="str">
+        <v>4/6/26</v>
+      </c>
+      <c r="Y41" t="str">
+        <v>7/10/26</v>
+      </c>
+      <c r="Z41" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="AB41" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="AD41" t="str">
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="str">
+        <v>(247)</v>
+      </c>
+      <c r="B42" t="str">
+        <v>(1) Viet Nga Group, (2) Việt Nga Group-THT HKD Thanh Mai</v>
+      </c>
+      <c r="C42" t="str">
+        <v>73403</v>
+      </c>
+      <c r="D42" t="str">
+        <v>913613458</v>
+      </c>
+      <c r="E42" t="str">
+        <v>ĐINH THÀNH NGUYÊN</v>
+      </c>
+      <c r="F42" t="str">
+        <v>HỘ KINH DOANH THANH MAI</v>
+      </c>
+      <c r="J42" t="str">
+        <v>Intensive rice production // Trồng lúa thâm canh</v>
+      </c>
+      <c r="K42" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="L42" t="str">
+        <v>Male // Nam</v>
+      </c>
+      <c r="M42" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="N42" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O42" t="str">
+        <v>0</v>
+      </c>
+      <c r="P42" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q42" t="str">
+        <v>0</v>
+      </c>
+      <c r="R42" t="str">
+        <v>0</v>
+      </c>
+      <c r="S42" t="str">
+        <v>0</v>
+      </c>
+      <c r="T42" t="str">
+        <v>0</v>
+      </c>
+      <c r="U42" t="str">
+        <v>2</v>
+      </c>
+      <c r="V42" t="str">
+        <v>0</v>
+      </c>
+      <c r="W42" t="str">
+        <v>1</v>
+      </c>
+      <c r="X42" t="str">
+        <v>4/6/26</v>
+      </c>
+      <c r="Y42" t="str">
+        <v>7/10/26</v>
+      </c>
+      <c r="Z42" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="AB42" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="AD42" t="str">
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="str">
+        <v>(249)</v>
+      </c>
+      <c r="B43" t="str">
+        <v>(1) Viet Nga Group, (2) Việt Nga Group-THT HKD Thanh Mai</v>
+      </c>
+      <c r="C43" t="str">
+        <v>73405</v>
+      </c>
+      <c r="D43" t="str">
+        <v>834994432</v>
+      </c>
+      <c r="E43" t="str">
+        <v>NGUYỄN VĂN NHÁNH</v>
+      </c>
+      <c r="F43" t="str">
+        <v>HỘ KINH DOANH THANH MAI</v>
+      </c>
+      <c r="J43" t="str">
+        <v>Intensive rice production // Trồng lúa thâm canh</v>
+      </c>
+      <c r="K43" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="L43" t="str">
+        <v>Male // Nam</v>
+      </c>
+      <c r="M43" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="N43" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O43" t="str">
+        <v>0</v>
+      </c>
+      <c r="P43" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q43" t="str">
+        <v>0</v>
+      </c>
+      <c r="R43" t="str">
+        <v>0</v>
+      </c>
+      <c r="S43" t="str">
+        <v>0</v>
+      </c>
+      <c r="T43" t="str">
+        <v>0</v>
+      </c>
+      <c r="U43" t="str">
+        <v>4</v>
+      </c>
+      <c r="V43" t="str">
+        <v>0</v>
+      </c>
+      <c r="W43" t="str">
+        <v>3</v>
+      </c>
+      <c r="X43" t="str">
+        <v>4/6/26</v>
+      </c>
+      <c r="Y43" t="str">
+        <v>7/10/26</v>
+      </c>
+      <c r="Z43" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="AB43" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="AD43" t="str">
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="str">
+        <v>(250)</v>
+      </c>
+      <c r="B44" t="str">
+        <v>(1) Viet Nga Group, (2) Việt Nga Group-THT HKD Thanh Mai</v>
+      </c>
+      <c r="C44" t="str">
+        <v>73406</v>
+      </c>
+      <c r="D44" t="str">
+        <v>936735077</v>
+      </c>
+      <c r="E44" t="str">
+        <v>NGUYỄN MINH TRƯỜNG</v>
+      </c>
+      <c r="F44" t="str">
+        <v>HỘ KINH DOANH THANH MAI</v>
+      </c>
+      <c r="J44" t="str">
+        <v>Intensive rice production // Trồng lúa thâm canh</v>
+      </c>
+      <c r="K44" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="L44" t="str">
+        <v>Male // Nam</v>
+      </c>
+      <c r="M44" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="N44" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O44" t="str">
+        <v>1</v>
+      </c>
+      <c r="P44" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q44" t="str">
+        <v>0</v>
+      </c>
+      <c r="R44" t="str">
+        <v>0</v>
+      </c>
+      <c r="S44" t="str">
+        <v>0</v>
+      </c>
+      <c r="T44" t="str">
+        <v>0</v>
+      </c>
+      <c r="U44" t="str">
+        <v>3</v>
+      </c>
+      <c r="V44" t="str">
+        <v>0</v>
+      </c>
+      <c r="W44" t="str">
+        <v>2</v>
+      </c>
+      <c r="X44" t="str">
+        <v>4/6/26</v>
+      </c>
+      <c r="Y44" t="str">
+        <v>7/10/26</v>
+      </c>
+      <c r="Z44" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="AB44" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="AD44" t="str">
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="str">
+        <v>(251)</v>
+      </c>
+      <c r="B45" t="str">
+        <v>(1) Viet Nga Group, (2) Việt Nga Group-THT HKD Thanh Mai</v>
+      </c>
+      <c r="C45" t="str">
+        <v>73407</v>
+      </c>
+      <c r="D45" t="str">
+        <v>356309142</v>
+      </c>
+      <c r="E45" t="str">
+        <v>TRẦN VĂN VĨNH</v>
+      </c>
+      <c r="F45" t="str">
+        <v>HỘ KINH DOANH THANH MAI</v>
+      </c>
+      <c r="J45" t="str">
+        <v>Intensive rice production // Trồng lúa thâm canh</v>
+      </c>
+      <c r="K45" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="L45" t="str">
+        <v>Male // Nam</v>
+      </c>
+      <c r="M45" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="N45" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O45" t="str">
+        <v>0</v>
+      </c>
+      <c r="P45" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q45" t="str">
+        <v>0</v>
+      </c>
+      <c r="R45" t="str">
+        <v>0</v>
+      </c>
+      <c r="S45" t="str">
+        <v>0</v>
+      </c>
+      <c r="T45" t="str">
+        <v>0</v>
+      </c>
+      <c r="U45" t="str">
+        <v>2</v>
+      </c>
+      <c r="V45" t="str">
+        <v>0</v>
+      </c>
+      <c r="W45" t="str">
+        <v>1</v>
+      </c>
+      <c r="X45" t="str">
+        <v>4/6/26</v>
+      </c>
+      <c r="Y45" t="str">
+        <v>7/10/26</v>
+      </c>
+      <c r="Z45" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="AB45" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="AD45" t="str">
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="str">
+        <v>(256)</v>
+      </c>
+      <c r="B46" t="str">
+        <v>(1) Viet Nga Group, (2) Việt Nga Group-THT HKD Thanh Mai</v>
+      </c>
+      <c r="C46" t="str">
+        <v>73412</v>
+      </c>
+      <c r="D46" t="str">
+        <v>388443780</v>
+      </c>
+      <c r="E46" t="str">
+        <v>PHAN VĂN BE</v>
+      </c>
+      <c r="F46" t="str">
+        <v>HỘ KINH DOANH THANH MAI</v>
+      </c>
+      <c r="J46" t="str">
+        <v>Intensive rice production // Trồng lúa thâm canh</v>
+      </c>
+      <c r="K46" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="L46" t="str">
+        <v>Male // Nam</v>
+      </c>
+      <c r="M46" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="N46" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O46" t="str">
+        <v>0</v>
+      </c>
+      <c r="P46" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q46" t="str">
+        <v>0</v>
+      </c>
+      <c r="R46" t="str">
+        <v>0</v>
+      </c>
+      <c r="S46" t="str">
+        <v>0</v>
+      </c>
+      <c r="T46" t="str">
+        <v>0</v>
+      </c>
+      <c r="U46" t="str">
+        <v>4</v>
+      </c>
+      <c r="V46" t="str">
+        <v>0</v>
+      </c>
+      <c r="W46" t="str">
+        <v>3</v>
+      </c>
+      <c r="X46" t="str">
+        <v>4/6/26</v>
+      </c>
+      <c r="Y46" t="str">
+        <v>7/10/26</v>
+      </c>
+      <c r="Z46" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="AB46" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="AD46" t="str">
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="str">
+        <v>(243)</v>
+      </c>
+      <c r="B47" t="str">
+        <v>(1) Viet Nga Group, (2) Việt Nga Group-THT HKD Thanh Mai</v>
+      </c>
+      <c r="C47" t="str">
+        <v>73399</v>
+      </c>
+      <c r="D47" t="str">
+        <v>388673145</v>
+      </c>
+      <c r="E47" t="str">
+        <v>NGUYỄN VĂN DƯỜNG</v>
+      </c>
+      <c r="F47" t="str">
+        <v>HỘ KINH DOANH THANH MAI</v>
+      </c>
+      <c r="J47" t="str">
+        <v>Intensive rice production // Trồng lúa thâm canh</v>
+      </c>
+      <c r="K47" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="L47" t="str">
+        <v>Male // Nam</v>
+      </c>
+      <c r="M47" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="N47" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O47" t="str">
+        <v>0</v>
+      </c>
+      <c r="P47" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q47" t="str">
+        <v>0</v>
+      </c>
+      <c r="R47" t="str">
+        <v>0</v>
+      </c>
+      <c r="S47" t="str">
+        <v>0</v>
+      </c>
+      <c r="T47" t="str">
+        <v>0</v>
+      </c>
+      <c r="U47" t="str">
+        <v>4</v>
+      </c>
+      <c r="V47" t="str">
+        <v>0</v>
+      </c>
+      <c r="W47" t="str">
+        <v>3</v>
+      </c>
+      <c r="X47" t="str">
+        <v>4/6/26</v>
+      </c>
+      <c r="Y47" t="str">
+        <v>7/10/26</v>
+      </c>
+      <c r="Z47" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="AB47" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="AD47" t="str">
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="str">
+        <v>(243)</v>
+      </c>
+      <c r="B48" t="str">
+        <v>(1) Viet Nga Group, (2) Việt Nga Group-THT HKD Thanh Mai</v>
+      </c>
+      <c r="C48" t="str">
+        <v>73399</v>
+      </c>
+      <c r="D48" t="str">
+        <v>388673145</v>
+      </c>
+      <c r="E48" t="str">
+        <v>NGUYỄN VĂN DƯỜNG</v>
+      </c>
+      <c r="F48" t="str">
+        <v>HỘ KINH DOANH THANH MAI</v>
+      </c>
+      <c r="J48" t="str">
+        <v>Intensive rice production // Trồng lúa thâm canh</v>
+      </c>
+      <c r="K48" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="L48" t="str">
+        <v>Male // Nam</v>
+      </c>
+      <c r="M48" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="N48" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O48" t="str">
+        <v>0</v>
+      </c>
+      <c r="P48" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q48" t="str">
+        <v>0</v>
+      </c>
+      <c r="R48" t="str">
+        <v>0</v>
+      </c>
+      <c r="S48" t="str">
+        <v>0</v>
+      </c>
+      <c r="T48" t="str">
+        <v>0</v>
+      </c>
+      <c r="U48" t="str">
+        <v>4</v>
+      </c>
+      <c r="V48" t="str">
+        <v>0</v>
+      </c>
+      <c r="W48" t="str">
+        <v>3</v>
+      </c>
+      <c r="X48" t="str">
+        <v>4/6/26</v>
+      </c>
+      <c r="Y48" t="str">
+        <v>7/10/26</v>
+      </c>
+      <c r="Z48" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="AB48" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="AD48" t="str">
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="str">
+        <v>(245)</v>
+      </c>
+      <c r="B49" t="str">
+        <v>(1) Viet Nga Group, (2) Việt Nga Group-THT HKD Thanh Mai</v>
+      </c>
+      <c r="C49" t="str">
+        <v>73401</v>
+      </c>
+      <c r="D49" t="str">
+        <v>359757527</v>
+      </c>
+      <c r="E49" t="str">
+        <v>NGUYỄN THANH NHÀN</v>
+      </c>
+      <c r="F49" t="str">
+        <v>HỘ KINH DOANH THANH MAI</v>
+      </c>
+      <c r="J49" t="str">
+        <v>Intensive rice production // Trồng lúa thâm canh</v>
+      </c>
+      <c r="K49" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="L49" t="str">
+        <v>Female // Nữ</v>
+      </c>
+      <c r="M49" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="N49" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O49" t="str">
+        <v>1</v>
+      </c>
+      <c r="P49" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q49" t="str">
+        <v>0</v>
+      </c>
+      <c r="R49" t="str">
+        <v>0</v>
+      </c>
+      <c r="S49" t="str">
+        <v>0</v>
+      </c>
+      <c r="T49" t="str">
+        <v>0</v>
+      </c>
+      <c r="U49" t="str">
+        <v>4</v>
+      </c>
+      <c r="V49" t="str">
+        <v>0</v>
+      </c>
+      <c r="W49" t="str">
+        <v>3</v>
+      </c>
+      <c r="X49" t="str">
+        <v>4/6/26</v>
+      </c>
+      <c r="Y49" t="str">
+        <v>7/10/26</v>
+      </c>
+      <c r="Z49" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="AB49" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="AD49" t="str">
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="str">
+        <v>(246)</v>
+      </c>
+      <c r="B50" t="str">
+        <v>(1) Viet Nga Group, (2) Việt Nga Group-THT HKD Thanh Mai</v>
+      </c>
+      <c r="C50" t="str">
+        <v>73402</v>
+      </c>
+      <c r="D50" t="str">
+        <v>382211425</v>
+      </c>
+      <c r="E50" t="str">
+        <v>HUỲNH HOÀNG DŨNG</v>
+      </c>
+      <c r="F50" t="str">
+        <v>HỘ KINH DOANH THANH MAI</v>
+      </c>
+      <c r="J50" t="str">
+        <v>Intensive rice production // Trồng lúa thâm canh</v>
+      </c>
+      <c r="K50" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="L50" t="str">
+        <v>Male // Nam</v>
+      </c>
+      <c r="M50" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="N50" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O50" t="str">
+        <v>1</v>
+      </c>
+      <c r="P50" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q50" t="str">
+        <v>0</v>
+      </c>
+      <c r="R50" t="str">
+        <v>0</v>
+      </c>
+      <c r="S50" t="str">
+        <v>0</v>
+      </c>
+      <c r="T50" t="str">
+        <v>0</v>
+      </c>
+      <c r="U50" t="str">
+        <v>3</v>
+      </c>
+      <c r="V50" t="str">
+        <v>0</v>
+      </c>
+      <c r="W50" t="str">
+        <v>2</v>
+      </c>
+      <c r="X50" t="str">
+        <v>4/6/26</v>
+      </c>
+      <c r="Y50" t="str">
+        <v>7/10/26</v>
+      </c>
+      <c r="Z50" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="AB50" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="AD50" t="str">
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="str">
+        <v>(247)</v>
+      </c>
+      <c r="B51" t="str">
+        <v>(1) Viet Nga Group, (2) Việt Nga Group-THT HKD Thanh Mai</v>
+      </c>
+      <c r="C51" t="str">
+        <v>73403</v>
+      </c>
+      <c r="D51" t="str">
+        <v>913613458</v>
+      </c>
+      <c r="E51" t="str">
+        <v>ĐINH THÀNH NGUYÊN</v>
+      </c>
+      <c r="F51" t="str">
+        <v>HỘ KINH DOANH THANH MAI</v>
+      </c>
+      <c r="J51" t="str">
+        <v>Intensive rice production // Trồng lúa thâm canh</v>
+      </c>
+      <c r="K51" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="L51" t="str">
+        <v>Male // Nam</v>
+      </c>
+      <c r="M51" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="N51" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O51" t="str">
+        <v>0</v>
+      </c>
+      <c r="P51" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q51" t="str">
+        <v>0</v>
+      </c>
+      <c r="R51" t="str">
+        <v>0</v>
+      </c>
+      <c r="S51" t="str">
+        <v>0</v>
+      </c>
+      <c r="T51" t="str">
+        <v>0</v>
+      </c>
+      <c r="U51" t="str">
+        <v>2</v>
+      </c>
+      <c r="V51" t="str">
+        <v>0</v>
+      </c>
+      <c r="W51" t="str">
+        <v>1</v>
+      </c>
+      <c r="X51" t="str">
+        <v>4/6/26</v>
+      </c>
+      <c r="Y51" t="str">
+        <v>7/10/26</v>
+      </c>
+      <c r="Z51" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="AB51" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="AD51" t="str">
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="str">
+        <v>(249)</v>
+      </c>
+      <c r="B52" t="str">
+        <v>(1) Viet Nga Group, (2) Việt Nga Group-THT HKD Thanh Mai</v>
+      </c>
+      <c r="C52" t="str">
+        <v>73405</v>
+      </c>
+      <c r="D52" t="str">
+        <v>834994432</v>
+      </c>
+      <c r="E52" t="str">
+        <v>NGUYỄN VĂN NHÁNH</v>
+      </c>
+      <c r="F52" t="str">
+        <v>HỘ KINH DOANH THANH MAI</v>
+      </c>
+      <c r="J52" t="str">
+        <v>Intensive rice production // Trồng lúa thâm canh</v>
+      </c>
+      <c r="K52" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="L52" t="str">
+        <v>Male // Nam</v>
+      </c>
+      <c r="M52" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="N52" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O52" t="str">
+        <v>0</v>
+      </c>
+      <c r="P52" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q52" t="str">
+        <v>0</v>
+      </c>
+      <c r="R52" t="str">
+        <v>0</v>
+      </c>
+      <c r="S52" t="str">
+        <v>0</v>
+      </c>
+      <c r="T52" t="str">
+        <v>0</v>
+      </c>
+      <c r="U52" t="str">
+        <v>4</v>
+      </c>
+      <c r="V52" t="str">
+        <v>0</v>
+      </c>
+      <c r="W52" t="str">
+        <v>3</v>
+      </c>
+      <c r="X52" t="str">
+        <v>4/6/26</v>
+      </c>
+      <c r="Y52" t="str">
+        <v>7/10/26</v>
+      </c>
+      <c r="Z52" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="AB52" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="AD52" t="str">
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="str">
+        <v>(250)</v>
+      </c>
+      <c r="B53" t="str">
+        <v>(1) Viet Nga Group, (2) Việt Nga Group-THT HKD Thanh Mai</v>
+      </c>
+      <c r="C53" t="str">
+        <v>73406</v>
+      </c>
+      <c r="D53" t="str">
+        <v>936735077</v>
+      </c>
+      <c r="E53" t="str">
+        <v>NGUYỄN MINH TRƯỜNG</v>
+      </c>
+      <c r="F53" t="str">
+        <v>HỘ KINH DOANH THANH MAI</v>
+      </c>
+      <c r="J53" t="str">
+        <v>Intensive rice production // Trồng lúa thâm canh</v>
+      </c>
+      <c r="K53" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="L53" t="str">
+        <v>Male // Nam</v>
+      </c>
+      <c r="M53" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="N53" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O53" t="str">
+        <v>1</v>
+      </c>
+      <c r="P53" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q53" t="str">
+        <v>0</v>
+      </c>
+      <c r="R53" t="str">
+        <v>0</v>
+      </c>
+      <c r="S53" t="str">
+        <v>0</v>
+      </c>
+      <c r="T53" t="str">
+        <v>0</v>
+      </c>
+      <c r="U53" t="str">
+        <v>3</v>
+      </c>
+      <c r="V53" t="str">
+        <v>0</v>
+      </c>
+      <c r="W53" t="str">
+        <v>2</v>
+      </c>
+      <c r="X53" t="str">
+        <v>4/6/26</v>
+      </c>
+      <c r="Y53" t="str">
+        <v>7/10/26</v>
+      </c>
+      <c r="Z53" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="AB53" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="AD53" t="str">
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="str">
+        <v>(251)</v>
+      </c>
+      <c r="B54" t="str">
+        <v>(1) Viet Nga Group, (2) Việt Nga Group-THT HKD Thanh Mai</v>
+      </c>
+      <c r="C54" t="str">
+        <v>73407</v>
+      </c>
+      <c r="D54" t="str">
+        <v>356309142</v>
+      </c>
+      <c r="E54" t="str">
+        <v>TRẦN VĂN VĨNH</v>
+      </c>
+      <c r="F54" t="str">
+        <v>HỘ KINH DOANH THANH MAI</v>
+      </c>
+      <c r="J54" t="str">
+        <v>Intensive rice production // Trồng lúa thâm canh</v>
+      </c>
+      <c r="K54" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="L54" t="str">
+        <v>Male // Nam</v>
+      </c>
+      <c r="M54" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="N54" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O54" t="str">
+        <v>0</v>
+      </c>
+      <c r="P54" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q54" t="str">
+        <v>0</v>
+      </c>
+      <c r="R54" t="str">
+        <v>0</v>
+      </c>
+      <c r="S54" t="str">
+        <v>0</v>
+      </c>
+      <c r="T54" t="str">
+        <v>0</v>
+      </c>
+      <c r="U54" t="str">
+        <v>2</v>
+      </c>
+      <c r="V54" t="str">
+        <v>0</v>
+      </c>
+      <c r="W54" t="str">
+        <v>1</v>
+      </c>
+      <c r="X54" t="str">
+        <v>4/6/26</v>
+      </c>
+      <c r="Y54" t="str">
+        <v>7/10/26</v>
+      </c>
+      <c r="Z54" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="AB54" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="AD54" t="str">
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="str">
+        <v>(256)</v>
+      </c>
+      <c r="B55" t="str">
+        <v>(1) Viet Nga Group, (2) Việt Nga Group-THT HKD Thanh Mai</v>
+      </c>
+      <c r="C55" t="str">
+        <v>73412</v>
+      </c>
+      <c r="D55" t="str">
+        <v>388443780</v>
+      </c>
+      <c r="E55" t="str">
+        <v>PHAN VĂN BE</v>
+      </c>
+      <c r="F55" t="str">
+        <v>HỘ KINH DOANH THANH MAI</v>
+      </c>
+      <c r="J55" t="str">
+        <v>Intensive rice production // Trồng lúa thâm canh</v>
+      </c>
+      <c r="K55" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="L55" t="str">
+        <v>Male // Nam</v>
+      </c>
+      <c r="M55" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="N55" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O55" t="str">
+        <v>0</v>
+      </c>
+      <c r="P55" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q55" t="str">
+        <v>0</v>
+      </c>
+      <c r="R55" t="str">
+        <v>0</v>
+      </c>
+      <c r="S55" t="str">
+        <v>0</v>
+      </c>
+      <c r="T55" t="str">
+        <v>0</v>
+      </c>
+      <c r="U55" t="str">
+        <v>4</v>
+      </c>
+      <c r="V55" t="str">
+        <v>0</v>
+      </c>
+      <c r="W55" t="str">
+        <v>3</v>
+      </c>
+      <c r="X55" t="str">
+        <v>4/6/26</v>
+      </c>
+      <c r="Y55" t="str">
+        <v>7/10/26</v>
+      </c>
+      <c r="Z55" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="AB55" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="AD55" t="str">
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="str">
+        <v>(243)</v>
+      </c>
+      <c r="B56" t="str">
+        <v>(1) Viet Nga Group, (2) Việt Nga Group-THT HKD Thanh Mai</v>
+      </c>
+      <c r="C56" t="str">
+        <v>73399</v>
+      </c>
+      <c r="D56" t="str">
+        <v>388673145</v>
+      </c>
+      <c r="E56" t="str">
+        <v>NGUYỄN VĂN DƯỜNG</v>
+      </c>
+      <c r="F56" t="str">
+        <v>HỘ KINH DOANH THANH MAI</v>
+      </c>
+      <c r="J56" t="str">
+        <v>Intensive rice production // Trồng lúa thâm canh</v>
+      </c>
+      <c r="K56" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="L56" t="str">
+        <v>Male // Nam</v>
+      </c>
+      <c r="M56" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="N56" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O56" t="str">
+        <v>0</v>
+      </c>
+      <c r="P56" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q56" t="str">
+        <v>0</v>
+      </c>
+      <c r="R56" t="str">
+        <v>0</v>
+      </c>
+      <c r="S56" t="str">
+        <v>0</v>
+      </c>
+      <c r="T56" t="str">
+        <v>0</v>
+      </c>
+      <c r="U56" t="str">
+        <v>4</v>
+      </c>
+      <c r="V56" t="str">
+        <v>0</v>
+      </c>
+      <c r="W56" t="str">
+        <v>3</v>
+      </c>
+      <c r="X56" t="str">
+        <v>4/6/26</v>
+      </c>
+      <c r="Y56" t="str">
+        <v>7/10/26</v>
+      </c>
+      <c r="Z56" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="AB56" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="AD56" t="str">
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="str">
+        <v>(245)</v>
+      </c>
+      <c r="B57" t="str">
+        <v>(1) Viet Nga Group, (2) Việt Nga Group-THT HKD Thanh Mai</v>
+      </c>
+      <c r="C57" t="str">
+        <v>73401</v>
+      </c>
+      <c r="D57" t="str">
+        <v>359757527</v>
+      </c>
+      <c r="E57" t="str">
+        <v>NGUYỄN THANH NHÀN</v>
+      </c>
+      <c r="F57" t="str">
+        <v>HỘ KINH DOANH THANH MAI</v>
+      </c>
+      <c r="J57" t="str">
+        <v>Intensive rice production // Trồng lúa thâm canh</v>
+      </c>
+      <c r="K57" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="L57" t="str">
+        <v>Female // Nữ</v>
+      </c>
+      <c r="M57" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="N57" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O57" t="str">
+        <v>1</v>
+      </c>
+      <c r="P57" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q57" t="str">
+        <v>0</v>
+      </c>
+      <c r="R57" t="str">
+        <v>0</v>
+      </c>
+      <c r="S57" t="str">
+        <v>0</v>
+      </c>
+      <c r="T57" t="str">
+        <v>0</v>
+      </c>
+      <c r="U57" t="str">
+        <v>4</v>
+      </c>
+      <c r="V57" t="str">
+        <v>0</v>
+      </c>
+      <c r="W57" t="str">
+        <v>3</v>
+      </c>
+      <c r="X57" t="str">
+        <v>4/6/26</v>
+      </c>
+      <c r="Y57" t="str">
+        <v>7/10/26</v>
+      </c>
+      <c r="Z57" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="AB57" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="AD57" t="str">
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="str">
+        <v>(246)</v>
+      </c>
+      <c r="B58" t="str">
+        <v>(1) Viet Nga Group, (2) Việt Nga Group-THT HKD Thanh Mai</v>
+      </c>
+      <c r="C58" t="str">
+        <v>73402</v>
+      </c>
+      <c r="D58" t="str">
+        <v>382211425</v>
+      </c>
+      <c r="E58" t="str">
+        <v>HUỲNH HOÀNG DŨNG</v>
+      </c>
+      <c r="F58" t="str">
+        <v>HỘ KINH DOANH THANH MAI</v>
+      </c>
+      <c r="J58" t="str">
+        <v>Intensive rice production // Trồng lúa thâm canh</v>
+      </c>
+      <c r="K58" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="L58" t="str">
+        <v>Male // Nam</v>
+      </c>
+      <c r="M58" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="N58" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O58" t="str">
+        <v>1</v>
+      </c>
+      <c r="P58" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q58" t="str">
+        <v>0</v>
+      </c>
+      <c r="R58" t="str">
+        <v>0</v>
+      </c>
+      <c r="S58" t="str">
+        <v>0</v>
+      </c>
+      <c r="T58" t="str">
+        <v>0</v>
+      </c>
+      <c r="U58" t="str">
+        <v>3</v>
+      </c>
+      <c r="V58" t="str">
+        <v>0</v>
+      </c>
+      <c r="W58" t="str">
+        <v>2</v>
+      </c>
+      <c r="X58" t="str">
+        <v>4/6/26</v>
+      </c>
+      <c r="Y58" t="str">
+        <v>7/10/26</v>
+      </c>
+      <c r="Z58" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="AB58" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="AD58" t="str">
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="str">
+        <v>(247)</v>
+      </c>
+      <c r="B59" t="str">
+        <v>(1) Viet Nga Group, (2) Việt Nga Group-THT HKD Thanh Mai</v>
+      </c>
+      <c r="C59" t="str">
+        <v>73403</v>
+      </c>
+      <c r="D59" t="str">
+        <v>913613458</v>
+      </c>
+      <c r="E59" t="str">
+        <v>ĐINH THÀNH NGUYÊN</v>
+      </c>
+      <c r="F59" t="str">
+        <v>HỘ KINH DOANH THANH MAI</v>
+      </c>
+      <c r="J59" t="str">
+        <v>Intensive rice production // Trồng lúa thâm canh</v>
+      </c>
+      <c r="K59" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="L59" t="str">
+        <v>Male // Nam</v>
+      </c>
+      <c r="M59" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="N59" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O59" t="str">
+        <v>0</v>
+      </c>
+      <c r="P59" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q59" t="str">
+        <v>0</v>
+      </c>
+      <c r="R59" t="str">
+        <v>0</v>
+      </c>
+      <c r="S59" t="str">
+        <v>0</v>
+      </c>
+      <c r="T59" t="str">
+        <v>0</v>
+      </c>
+      <c r="U59" t="str">
+        <v>2</v>
+      </c>
+      <c r="V59" t="str">
+        <v>0</v>
+      </c>
+      <c r="W59" t="str">
+        <v>1</v>
+      </c>
+      <c r="X59" t="str">
+        <v>4/6/26</v>
+      </c>
+      <c r="Y59" t="str">
+        <v>7/10/26</v>
+      </c>
+      <c r="Z59" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="AB59" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="AD59" t="str">
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="str">
+        <v>(249)</v>
+      </c>
+      <c r="B60" t="str">
+        <v>(1) Viet Nga Group, (2) Việt Nga Group-THT HKD Thanh Mai</v>
+      </c>
+      <c r="C60" t="str">
+        <v>73405</v>
+      </c>
+      <c r="D60" t="str">
+        <v>834994432</v>
+      </c>
+      <c r="E60" t="str">
+        <v>NGUYỄN VĂN NHÁNH</v>
+      </c>
+      <c r="F60" t="str">
+        <v>HỘ KINH DOANH THANH MAI</v>
+      </c>
+      <c r="J60" t="str">
+        <v>Intensive rice production // Trồng lúa thâm canh</v>
+      </c>
+      <c r="K60" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="L60" t="str">
+        <v>Male // Nam</v>
+      </c>
+      <c r="M60" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="N60" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O60" t="str">
+        <v>0</v>
+      </c>
+      <c r="P60" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q60" t="str">
+        <v>0</v>
+      </c>
+      <c r="R60" t="str">
+        <v>0</v>
+      </c>
+      <c r="S60" t="str">
+        <v>0</v>
+      </c>
+      <c r="T60" t="str">
+        <v>0</v>
+      </c>
+      <c r="U60" t="str">
+        <v>4</v>
+      </c>
+      <c r="V60" t="str">
+        <v>0</v>
+      </c>
+      <c r="W60" t="str">
+        <v>3</v>
+      </c>
+      <c r="X60" t="str">
+        <v>4/6/26</v>
+      </c>
+      <c r="Y60" t="str">
+        <v>7/10/26</v>
+      </c>
+      <c r="Z60" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="AB60" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="AD60" t="str">
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="str">
+        <v>(250)</v>
+      </c>
+      <c r="B61" t="str">
+        <v>(1) Viet Nga Group, (2) Việt Nga Group-THT HKD Thanh Mai</v>
+      </c>
+      <c r="C61" t="str">
+        <v>73406</v>
+      </c>
+      <c r="D61" t="str">
+        <v>936735077</v>
+      </c>
+      <c r="E61" t="str">
+        <v>NGUYỄN MINH TRƯỜNG</v>
+      </c>
+      <c r="F61" t="str">
+        <v>HỘ KINH DOANH THANH MAI</v>
+      </c>
+      <c r="J61" t="str">
+        <v>Intensive rice production // Trồng lúa thâm canh</v>
+      </c>
+      <c r="K61" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="L61" t="str">
+        <v>Male // Nam</v>
+      </c>
+      <c r="M61" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="N61" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O61" t="str">
+        <v>1</v>
+      </c>
+      <c r="P61" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q61" t="str">
+        <v>0</v>
+      </c>
+      <c r="R61" t="str">
+        <v>0</v>
+      </c>
+      <c r="S61" t="str">
+        <v>0</v>
+      </c>
+      <c r="T61" t="str">
+        <v>0</v>
+      </c>
+      <c r="U61" t="str">
+        <v>3</v>
+      </c>
+      <c r="V61" t="str">
+        <v>0</v>
+      </c>
+      <c r="W61" t="str">
+        <v>2</v>
+      </c>
+      <c r="X61" t="str">
+        <v>4/6/26</v>
+      </c>
+      <c r="Y61" t="str">
+        <v>7/10/26</v>
+      </c>
+      <c r="Z61" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="AB61" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="AD61" t="str">
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="str">
+        <v>(251)</v>
+      </c>
+      <c r="B62" t="str">
+        <v>(1) Viet Nga Group, (2) Việt Nga Group-THT HKD Thanh Mai</v>
+      </c>
+      <c r="C62" t="str">
+        <v>73407</v>
+      </c>
+      <c r="D62" t="str">
+        <v>356309142</v>
+      </c>
+      <c r="E62" t="str">
+        <v>TRẦN VĂN VĨNH</v>
+      </c>
+      <c r="F62" t="str">
+        <v>HỘ KINH DOANH THANH MAI</v>
+      </c>
+      <c r="J62" t="str">
+        <v>Intensive rice production // Trồng lúa thâm canh</v>
+      </c>
+      <c r="K62" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="L62" t="str">
+        <v>Male // Nam</v>
+      </c>
+      <c r="M62" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="N62" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O62" t="str">
+        <v>0</v>
+      </c>
+      <c r="P62" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q62" t="str">
+        <v>0</v>
+      </c>
+      <c r="R62" t="str">
+        <v>0</v>
+      </c>
+      <c r="S62" t="str">
+        <v>0</v>
+      </c>
+      <c r="T62" t="str">
+        <v>0</v>
+      </c>
+      <c r="U62" t="str">
+        <v>2</v>
+      </c>
+      <c r="V62" t="str">
+        <v>0</v>
+      </c>
+      <c r="W62" t="str">
+        <v>1</v>
+      </c>
+      <c r="X62" t="str">
+        <v>4/6/26</v>
+      </c>
+      <c r="Y62" t="str">
+        <v>7/10/26</v>
+      </c>
+      <c r="Z62" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="AB62" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="AD62" t="str">
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="str">
+        <v>(256)</v>
+      </c>
+      <c r="B63" t="str">
+        <v>(1) Viet Nga Group, (2) Việt Nga Group-THT HKD Thanh Mai</v>
+      </c>
+      <c r="C63" t="str">
+        <v>73412</v>
+      </c>
+      <c r="D63" t="str">
+        <v>388443780</v>
+      </c>
+      <c r="E63" t="str">
+        <v>PHAN VĂN BE</v>
+      </c>
+      <c r="F63" t="str">
+        <v>HỘ KINH DOANH THANH MAI</v>
+      </c>
+      <c r="J63" t="str">
+        <v>Intensive rice production // Trồng lúa thâm canh</v>
+      </c>
+      <c r="K63" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="L63" t="str">
+        <v>Male // Nam</v>
+      </c>
+      <c r="M63" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="N63" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O63" t="str">
+        <v>0</v>
+      </c>
+      <c r="P63" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q63" t="str">
+        <v>0</v>
+      </c>
+      <c r="R63" t="str">
+        <v>0</v>
+      </c>
+      <c r="S63" t="str">
+        <v>0</v>
+      </c>
+      <c r="T63" t="str">
+        <v>0</v>
+      </c>
+      <c r="U63" t="str">
+        <v>4</v>
+      </c>
+      <c r="V63" t="str">
+        <v>0</v>
+      </c>
+      <c r="W63" t="str">
+        <v>3</v>
+      </c>
+      <c r="X63" t="str">
+        <v>4/6/26</v>
+      </c>
+      <c r="Y63" t="str">
+        <v>7/10/26</v>
+      </c>
+      <c r="Z63" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="AB63" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="AD63" t="str">
+        <v>Yes</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:AD32"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:AD63"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/cypress/fixtures/run-log.xlsx
+++ b/cypress/fixtures/run-log.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AD63"/>
+  <dimension ref="A1:AD187"/>
   <sheetData>
     <row r="1" xml:space="preserve">
       <c r="A1" t="str" xml:space="preserve">
@@ -5277,9 +5277,9557 @@
         <v>Yes</v>
       </c>
     </row>
+    <row r="64">
+      <c r="A64" t="str">
+        <v>(243)</v>
+      </c>
+      <c r="B64" t="str">
+        <v>(1) Viet Nga Group, (2) Việt Nga Group-THT HKD Thanh Mai</v>
+      </c>
+      <c r="C64" t="str">
+        <v>73399</v>
+      </c>
+      <c r="D64" t="str">
+        <v>388673145</v>
+      </c>
+      <c r="E64" t="str">
+        <v>NGUYỄN VĂN DƯỜNG</v>
+      </c>
+      <c r="F64" t="str">
+        <v>HỘ KINH DOANH THANH MAI</v>
+      </c>
+      <c r="J64" t="str">
+        <v>Intensive rice production // Trồng lúa thâm canh</v>
+      </c>
+      <c r="K64" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="L64" t="str">
+        <v>Male // Nam</v>
+      </c>
+      <c r="M64" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="N64" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O64" t="str">
+        <v>0</v>
+      </c>
+      <c r="P64" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q64" t="str">
+        <v>0</v>
+      </c>
+      <c r="R64" t="str">
+        <v>0</v>
+      </c>
+      <c r="S64" t="str">
+        <v>0</v>
+      </c>
+      <c r="T64" t="str">
+        <v>0</v>
+      </c>
+      <c r="U64" t="str">
+        <v>4</v>
+      </c>
+      <c r="V64" t="str">
+        <v>0</v>
+      </c>
+      <c r="W64" t="str">
+        <v>3</v>
+      </c>
+      <c r="X64" t="str">
+        <v>4/6/26</v>
+      </c>
+      <c r="Y64" t="str">
+        <v>7/10/26</v>
+      </c>
+      <c r="Z64" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="AB64" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="AD64" t="str">
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="str">
+        <v>(245)</v>
+      </c>
+      <c r="B65" t="str">
+        <v>(1) Viet Nga Group, (2) Việt Nga Group-THT HKD Thanh Mai</v>
+      </c>
+      <c r="C65" t="str">
+        <v>73401</v>
+      </c>
+      <c r="D65" t="str">
+        <v>359757527</v>
+      </c>
+      <c r="E65" t="str">
+        <v>NGUYỄN THANH NHÀN</v>
+      </c>
+      <c r="F65" t="str">
+        <v>HỘ KINH DOANH THANH MAI</v>
+      </c>
+      <c r="J65" t="str">
+        <v>Intensive rice production // Trồng lúa thâm canh</v>
+      </c>
+      <c r="K65" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="L65" t="str">
+        <v>Female // Nữ</v>
+      </c>
+      <c r="M65" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="N65" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O65" t="str">
+        <v>1</v>
+      </c>
+      <c r="P65" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q65" t="str">
+        <v>0</v>
+      </c>
+      <c r="R65" t="str">
+        <v>0</v>
+      </c>
+      <c r="S65" t="str">
+        <v>0</v>
+      </c>
+      <c r="T65" t="str">
+        <v>0</v>
+      </c>
+      <c r="U65" t="str">
+        <v>4</v>
+      </c>
+      <c r="V65" t="str">
+        <v>0</v>
+      </c>
+      <c r="W65" t="str">
+        <v>3</v>
+      </c>
+      <c r="X65" t="str">
+        <v>4/6/26</v>
+      </c>
+      <c r="Y65" t="str">
+        <v>7/10/26</v>
+      </c>
+      <c r="Z65" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="AB65" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="AD65" t="str">
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="str">
+        <v>(246)</v>
+      </c>
+      <c r="B66" t="str">
+        <v>(1) Viet Nga Group, (2) Việt Nga Group-THT HKD Thanh Mai</v>
+      </c>
+      <c r="C66" t="str">
+        <v>73402</v>
+      </c>
+      <c r="D66" t="str">
+        <v>382211425</v>
+      </c>
+      <c r="E66" t="str">
+        <v>HUỲNH HOÀNG DŨNG</v>
+      </c>
+      <c r="F66" t="str">
+        <v>HỘ KINH DOANH THANH MAI</v>
+      </c>
+      <c r="J66" t="str">
+        <v>Intensive rice production // Trồng lúa thâm canh</v>
+      </c>
+      <c r="K66" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="L66" t="str">
+        <v>Male // Nam</v>
+      </c>
+      <c r="M66" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="N66" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O66" t="str">
+        <v>1</v>
+      </c>
+      <c r="P66" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q66" t="str">
+        <v>0</v>
+      </c>
+      <c r="R66" t="str">
+        <v>0</v>
+      </c>
+      <c r="S66" t="str">
+        <v>0</v>
+      </c>
+      <c r="T66" t="str">
+        <v>0</v>
+      </c>
+      <c r="U66" t="str">
+        <v>3</v>
+      </c>
+      <c r="V66" t="str">
+        <v>0</v>
+      </c>
+      <c r="W66" t="str">
+        <v>2</v>
+      </c>
+      <c r="X66" t="str">
+        <v>4/6/26</v>
+      </c>
+      <c r="Y66" t="str">
+        <v>7/10/26</v>
+      </c>
+      <c r="Z66" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="AB66" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="AD66" t="str">
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="str">
+        <v>(247)</v>
+      </c>
+      <c r="B67" t="str">
+        <v>(1) Viet Nga Group, (2) Việt Nga Group-THT HKD Thanh Mai</v>
+      </c>
+      <c r="C67" t="str">
+        <v>73403</v>
+      </c>
+      <c r="D67" t="str">
+        <v>913613458</v>
+      </c>
+      <c r="E67" t="str">
+        <v>ĐINH THÀNH NGUYÊN</v>
+      </c>
+      <c r="F67" t="str">
+        <v>HỘ KINH DOANH THANH MAI</v>
+      </c>
+      <c r="J67" t="str">
+        <v>Intensive rice production // Trồng lúa thâm canh</v>
+      </c>
+      <c r="K67" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="L67" t="str">
+        <v>Male // Nam</v>
+      </c>
+      <c r="M67" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="N67" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O67" t="str">
+        <v>0</v>
+      </c>
+      <c r="P67" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q67" t="str">
+        <v>0</v>
+      </c>
+      <c r="R67" t="str">
+        <v>0</v>
+      </c>
+      <c r="S67" t="str">
+        <v>0</v>
+      </c>
+      <c r="T67" t="str">
+        <v>0</v>
+      </c>
+      <c r="U67" t="str">
+        <v>2</v>
+      </c>
+      <c r="V67" t="str">
+        <v>0</v>
+      </c>
+      <c r="W67" t="str">
+        <v>1</v>
+      </c>
+      <c r="X67" t="str">
+        <v>4/6/26</v>
+      </c>
+      <c r="Y67" t="str">
+        <v>7/10/26</v>
+      </c>
+      <c r="Z67" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="AB67" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="AD67" t="str">
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="str">
+        <v>(249)</v>
+      </c>
+      <c r="B68" t="str">
+        <v>(1) Viet Nga Group, (2) Việt Nga Group-THT HKD Thanh Mai</v>
+      </c>
+      <c r="C68" t="str">
+        <v>73405</v>
+      </c>
+      <c r="D68" t="str">
+        <v>834994432</v>
+      </c>
+      <c r="E68" t="str">
+        <v>NGUYỄN VĂN NHÁNH</v>
+      </c>
+      <c r="F68" t="str">
+        <v>HỘ KINH DOANH THANH MAI</v>
+      </c>
+      <c r="J68" t="str">
+        <v>Intensive rice production // Trồng lúa thâm canh</v>
+      </c>
+      <c r="K68" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="L68" t="str">
+        <v>Male // Nam</v>
+      </c>
+      <c r="M68" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="N68" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O68" t="str">
+        <v>0</v>
+      </c>
+      <c r="P68" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q68" t="str">
+        <v>0</v>
+      </c>
+      <c r="R68" t="str">
+        <v>0</v>
+      </c>
+      <c r="S68" t="str">
+        <v>0</v>
+      </c>
+      <c r="T68" t="str">
+        <v>0</v>
+      </c>
+      <c r="U68" t="str">
+        <v>4</v>
+      </c>
+      <c r="V68" t="str">
+        <v>0</v>
+      </c>
+      <c r="W68" t="str">
+        <v>3</v>
+      </c>
+      <c r="X68" t="str">
+        <v>4/6/26</v>
+      </c>
+      <c r="Y68" t="str">
+        <v>7/10/26</v>
+      </c>
+      <c r="Z68" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="AB68" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="AD68" t="str">
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="str">
+        <v>(250)</v>
+      </c>
+      <c r="B69" t="str">
+        <v>(1) Viet Nga Group, (2) Việt Nga Group-THT HKD Thanh Mai</v>
+      </c>
+      <c r="C69" t="str">
+        <v>73406</v>
+      </c>
+      <c r="D69" t="str">
+        <v>936735077</v>
+      </c>
+      <c r="E69" t="str">
+        <v>NGUYỄN MINH TRƯỜNG</v>
+      </c>
+      <c r="F69" t="str">
+        <v>HỘ KINH DOANH THANH MAI</v>
+      </c>
+      <c r="J69" t="str">
+        <v>Intensive rice production // Trồng lúa thâm canh</v>
+      </c>
+      <c r="K69" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="L69" t="str">
+        <v>Male // Nam</v>
+      </c>
+      <c r="M69" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="N69" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O69" t="str">
+        <v>1</v>
+      </c>
+      <c r="P69" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q69" t="str">
+        <v>0</v>
+      </c>
+      <c r="R69" t="str">
+        <v>0</v>
+      </c>
+      <c r="S69" t="str">
+        <v>0</v>
+      </c>
+      <c r="T69" t="str">
+        <v>0</v>
+      </c>
+      <c r="U69" t="str">
+        <v>3</v>
+      </c>
+      <c r="V69" t="str">
+        <v>0</v>
+      </c>
+      <c r="W69" t="str">
+        <v>2</v>
+      </c>
+      <c r="X69" t="str">
+        <v>4/6/26</v>
+      </c>
+      <c r="Y69" t="str">
+        <v>7/10/26</v>
+      </c>
+      <c r="Z69" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="AB69" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="AD69" t="str">
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="str">
+        <v>(251)</v>
+      </c>
+      <c r="B70" t="str">
+        <v>(1) Viet Nga Group, (2) Việt Nga Group-THT HKD Thanh Mai</v>
+      </c>
+      <c r="C70" t="str">
+        <v>73407</v>
+      </c>
+      <c r="D70" t="str">
+        <v>356309142</v>
+      </c>
+      <c r="E70" t="str">
+        <v>TRẦN VĂN VĨNH</v>
+      </c>
+      <c r="F70" t="str">
+        <v>HỘ KINH DOANH THANH MAI</v>
+      </c>
+      <c r="J70" t="str">
+        <v>Intensive rice production // Trồng lúa thâm canh</v>
+      </c>
+      <c r="K70" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="L70" t="str">
+        <v>Male // Nam</v>
+      </c>
+      <c r="M70" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="N70" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O70" t="str">
+        <v>0</v>
+      </c>
+      <c r="P70" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q70" t="str">
+        <v>0</v>
+      </c>
+      <c r="R70" t="str">
+        <v>0</v>
+      </c>
+      <c r="S70" t="str">
+        <v>0</v>
+      </c>
+      <c r="T70" t="str">
+        <v>0</v>
+      </c>
+      <c r="U70" t="str">
+        <v>2</v>
+      </c>
+      <c r="V70" t="str">
+        <v>0</v>
+      </c>
+      <c r="W70" t="str">
+        <v>1</v>
+      </c>
+      <c r="X70" t="str">
+        <v>4/6/26</v>
+      </c>
+      <c r="Y70" t="str">
+        <v>7/10/26</v>
+      </c>
+      <c r="Z70" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="AB70" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="AD70" t="str">
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="str">
+        <v>(256)</v>
+      </c>
+      <c r="B71" t="str">
+        <v>(1) Viet Nga Group, (2) Việt Nga Group-THT HKD Thanh Mai</v>
+      </c>
+      <c r="C71" t="str">
+        <v>73412</v>
+      </c>
+      <c r="D71" t="str">
+        <v>388443780</v>
+      </c>
+      <c r="E71" t="str">
+        <v>PHAN VĂN BE</v>
+      </c>
+      <c r="F71" t="str">
+        <v>HỘ KINH DOANH THANH MAI</v>
+      </c>
+      <c r="J71" t="str">
+        <v>Intensive rice production // Trồng lúa thâm canh</v>
+      </c>
+      <c r="K71" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="L71" t="str">
+        <v>Male // Nam</v>
+      </c>
+      <c r="M71" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="N71" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O71" t="str">
+        <v>0</v>
+      </c>
+      <c r="P71" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q71" t="str">
+        <v>0</v>
+      </c>
+      <c r="R71" t="str">
+        <v>0</v>
+      </c>
+      <c r="S71" t="str">
+        <v>0</v>
+      </c>
+      <c r="T71" t="str">
+        <v>0</v>
+      </c>
+      <c r="U71" t="str">
+        <v>4</v>
+      </c>
+      <c r="V71" t="str">
+        <v>0</v>
+      </c>
+      <c r="W71" t="str">
+        <v>3</v>
+      </c>
+      <c r="X71" t="str">
+        <v>4/6/26</v>
+      </c>
+      <c r="Y71" t="str">
+        <v>7/10/26</v>
+      </c>
+      <c r="Z71" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="AB71" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="AD71" t="str">
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="str">
+        <v>(258)</v>
+      </c>
+      <c r="B72" t="str">
+        <v>(1) Viet Nga Group, (2) Việt Nga Group-THT HKD Thanh Mai</v>
+      </c>
+      <c r="C72" t="str">
+        <v>73414</v>
+      </c>
+      <c r="D72" t="str">
+        <v>339640487</v>
+      </c>
+      <c r="E72" t="str">
+        <v>NGUYỄN VĂN SƠN</v>
+      </c>
+      <c r="F72" t="str">
+        <v>HỘ KINH DOANH THANH MAI</v>
+      </c>
+      <c r="J72" t="str">
+        <v>Intensive rice production // Trồng lúa thâm canh</v>
+      </c>
+      <c r="K72" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="L72" t="str">
+        <v>Male // Nam</v>
+      </c>
+      <c r="M72" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="N72" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O72" t="str">
+        <v>1</v>
+      </c>
+      <c r="P72" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q72" t="str">
+        <v>0</v>
+      </c>
+      <c r="R72" t="str">
+        <v>0</v>
+      </c>
+      <c r="S72" t="str">
+        <v>0</v>
+      </c>
+      <c r="T72" t="str">
+        <v>0</v>
+      </c>
+      <c r="U72" t="str">
+        <v>2</v>
+      </c>
+      <c r="V72" t="str">
+        <v>0</v>
+      </c>
+      <c r="W72" t="str">
+        <v>1</v>
+      </c>
+      <c r="X72" t="str">
+        <v>4/6/26</v>
+      </c>
+      <c r="Y72" t="str">
+        <v>7/10/26</v>
+      </c>
+      <c r="Z72" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="AB72" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="AD72" t="str">
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="str">
+        <v>(259)</v>
+      </c>
+      <c r="B73" t="str">
+        <v>(1) Viet Nga Group, (2) Việt Nga Group-THT HKD Thanh Mai</v>
+      </c>
+      <c r="C73" t="str">
+        <v>73415</v>
+      </c>
+      <c r="D73" t="str">
+        <v>374465404</v>
+      </c>
+      <c r="E73" t="str">
+        <v>NGÔ THANH TUẤN</v>
+      </c>
+      <c r="F73" t="str">
+        <v>HỘ KINH DOANH THANH MAI</v>
+      </c>
+      <c r="J73" t="str">
+        <v>Intensive rice production // Trồng lúa thâm canh</v>
+      </c>
+      <c r="K73" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="L73" t="str">
+        <v>Male // Nam</v>
+      </c>
+      <c r="M73" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="N73" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O73" t="str">
+        <v>0</v>
+      </c>
+      <c r="P73" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q73" t="str">
+        <v>0</v>
+      </c>
+      <c r="R73" t="str">
+        <v>0</v>
+      </c>
+      <c r="S73" t="str">
+        <v>0</v>
+      </c>
+      <c r="T73" t="str">
+        <v>0</v>
+      </c>
+      <c r="U73" t="str">
+        <v>2</v>
+      </c>
+      <c r="V73" t="str">
+        <v>0</v>
+      </c>
+      <c r="W73" t="str">
+        <v>1</v>
+      </c>
+      <c r="X73" t="str">
+        <v>4/6/26</v>
+      </c>
+      <c r="Y73" t="str">
+        <v>7/10/26</v>
+      </c>
+      <c r="Z73" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="AB73" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="AD73" t="str">
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="str">
+        <v>(261)</v>
+      </c>
+      <c r="B74" t="str">
+        <v>(1) Viet Nga Group, (2) Việt Nga Group-THT HKD Thanh Mai</v>
+      </c>
+      <c r="C74" t="str">
+        <v>73417</v>
+      </c>
+      <c r="D74" t="str">
+        <v>977098292</v>
+      </c>
+      <c r="E74" t="str">
+        <v>NGUYỄN THANH SANG</v>
+      </c>
+      <c r="F74" t="str">
+        <v>HỘ KINH DOANH THANH MAI</v>
+      </c>
+      <c r="J74" t="str">
+        <v>Intensive rice production // Trồng lúa thâm canh</v>
+      </c>
+      <c r="K74" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="L74" t="str">
+        <v>Female // Nữ</v>
+      </c>
+      <c r="M74" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="N74" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O74" t="str">
+        <v>1</v>
+      </c>
+      <c r="P74" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q74" t="str">
+        <v>0</v>
+      </c>
+      <c r="R74" t="str">
+        <v>0</v>
+      </c>
+      <c r="S74" t="str">
+        <v>0</v>
+      </c>
+      <c r="T74" t="str">
+        <v>0</v>
+      </c>
+      <c r="U74" t="str">
+        <v>4</v>
+      </c>
+      <c r="V74" t="str">
+        <v>0</v>
+      </c>
+      <c r="W74" t="str">
+        <v>3</v>
+      </c>
+      <c r="X74" t="str">
+        <v>4/6/26</v>
+      </c>
+      <c r="Y74" t="str">
+        <v>7/10/26</v>
+      </c>
+      <c r="Z74" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="AB74" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="AD74" t="str">
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="str">
+        <v>(308)</v>
+      </c>
+      <c r="B75" t="str">
+        <v>(1) Viet Nga Group, (2) Việt Nga Group-HTX DVNN Bình Hiệp B</v>
+      </c>
+      <c r="C75" t="str">
+        <v>73798</v>
+      </c>
+      <c r="D75" t="str">
+        <v>375625234</v>
+      </c>
+      <c r="E75" t="str">
+        <v>LÊ VĂN SON</v>
+      </c>
+      <c r="F75" t="str">
+        <v>HỢP TÁC XÃ DỊCH VỤ NÔNG NGHIỆP BÌNH HIỆP B</v>
+      </c>
+      <c r="J75" t="str">
+        <v>Intensive rice production // Trồng lúa thâm canh</v>
+      </c>
+      <c r="K75" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="L75" t="str">
+        <v>Male // Nam</v>
+      </c>
+      <c r="M75" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="N75" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O75" t="str">
+        <v>0</v>
+      </c>
+      <c r="P75" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q75" t="str">
+        <v>0</v>
+      </c>
+      <c r="R75" t="str">
+        <v>0</v>
+      </c>
+      <c r="S75" t="str">
+        <v>0</v>
+      </c>
+      <c r="T75" t="str">
+        <v>0</v>
+      </c>
+      <c r="U75" t="str">
+        <v>3</v>
+      </c>
+      <c r="V75" t="str">
+        <v>0</v>
+      </c>
+      <c r="W75" t="str">
+        <v>2</v>
+      </c>
+      <c r="X75" t="str">
+        <v>4/10/26</v>
+      </c>
+      <c r="Y75" t="str">
+        <v>7/14/26</v>
+      </c>
+      <c r="Z75" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="AB75" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="AD75" t="str">
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="str">
+        <v>(309)</v>
+      </c>
+      <c r="B76" t="str">
+        <v>(1) Viet Nga Group, (2) Việt Nga Group-HTX DVNN Bình Hiệp B</v>
+      </c>
+      <c r="C76" t="str">
+        <v>73799</v>
+      </c>
+      <c r="D76" t="str">
+        <v>862256519</v>
+      </c>
+      <c r="E76" t="str">
+        <v>NGUYỄN VĂN VŨ</v>
+      </c>
+      <c r="F76" t="str">
+        <v>HỢP TÁC XÃ DỊCH VỤ NÔNG NGHIỆP BÌNH HIỆP B</v>
+      </c>
+      <c r="J76" t="str">
+        <v>Intensive rice production // Trồng lúa thâm canh</v>
+      </c>
+      <c r="K76" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="L76" t="str">
+        <v>Male // Nam</v>
+      </c>
+      <c r="M76" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="N76" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O76" t="str">
+        <v>0</v>
+      </c>
+      <c r="P76" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q76" t="str">
+        <v>0</v>
+      </c>
+      <c r="R76" t="str">
+        <v>0</v>
+      </c>
+      <c r="S76" t="str">
+        <v>0</v>
+      </c>
+      <c r="T76" t="str">
+        <v>0</v>
+      </c>
+      <c r="U76" t="str">
+        <v>3</v>
+      </c>
+      <c r="V76" t="str">
+        <v>0</v>
+      </c>
+      <c r="W76" t="str">
+        <v>2</v>
+      </c>
+      <c r="X76" t="str">
+        <v>4/10/26</v>
+      </c>
+      <c r="Y76" t="str">
+        <v>7/14/26</v>
+      </c>
+      <c r="Z76" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="AB76" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="AD76" t="str">
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="str">
+        <v>(310)</v>
+      </c>
+      <c r="B77" t="str">
+        <v>(1) Viet Nga Group, (2) Việt Nga Group-HTX DVNN Bình Hiệp B</v>
+      </c>
+      <c r="C77" t="str">
+        <v>73800</v>
+      </c>
+      <c r="D77" t="str">
+        <v>973345487</v>
+      </c>
+      <c r="E77" t="str">
+        <v>NGUYỄN VĂN SÁU</v>
+      </c>
+      <c r="F77" t="str">
+        <v>HỢP TÁC XÃ DỊCH VỤ NÔNG NGHIỆP BÌNH HIỆP B</v>
+      </c>
+      <c r="J77" t="str">
+        <v>Intensive rice production // Trồng lúa thâm canh</v>
+      </c>
+      <c r="K77" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="L77" t="str">
+        <v>Male // Nam</v>
+      </c>
+      <c r="M77" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="N77" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O77" t="str">
+        <v>0</v>
+      </c>
+      <c r="P77" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q77" t="str">
+        <v>0</v>
+      </c>
+      <c r="R77" t="str">
+        <v>0</v>
+      </c>
+      <c r="S77" t="str">
+        <v>0</v>
+      </c>
+      <c r="T77" t="str">
+        <v>0</v>
+      </c>
+      <c r="U77" t="str">
+        <v>4</v>
+      </c>
+      <c r="V77" t="str">
+        <v>0</v>
+      </c>
+      <c r="W77" t="str">
+        <v>2</v>
+      </c>
+      <c r="X77" t="str">
+        <v>4/10/26</v>
+      </c>
+      <c r="Y77" t="str">
+        <v>7/14/26</v>
+      </c>
+      <c r="Z77" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="AB77" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="AD77" t="str">
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="str">
+        <v>(311)</v>
+      </c>
+      <c r="B78" t="str">
+        <v>(1) Viet Nga Group, (2) Việt Nga Group-HTX DVNN Bình Hiệp B</v>
+      </c>
+      <c r="C78" t="str">
+        <v>73801</v>
+      </c>
+      <c r="D78" t="str">
+        <v>949611220</v>
+      </c>
+      <c r="E78" t="str">
+        <v>PHẠM VĂN LUÔNG</v>
+      </c>
+      <c r="F78" t="str">
+        <v>HỢP TÁC XÃ DỊCH VỤ NÔNG NGHIỆP BÌNH HIỆP B</v>
+      </c>
+      <c r="J78" t="str">
+        <v>Intensive rice production // Trồng lúa thâm canh</v>
+      </c>
+      <c r="K78" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="L78" t="str">
+        <v>Male // Nam</v>
+      </c>
+      <c r="M78" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="N78" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O78" t="str">
+        <v>0</v>
+      </c>
+      <c r="P78" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q78" t="str">
+        <v>0</v>
+      </c>
+      <c r="R78" t="str">
+        <v>0</v>
+      </c>
+      <c r="S78" t="str">
+        <v>0</v>
+      </c>
+      <c r="T78" t="str">
+        <v>0</v>
+      </c>
+      <c r="U78" t="str">
+        <v>5</v>
+      </c>
+      <c r="V78" t="str">
+        <v>0</v>
+      </c>
+      <c r="W78" t="str">
+        <v>2</v>
+      </c>
+      <c r="X78" t="str">
+        <v>4/10/26</v>
+      </c>
+      <c r="Y78" t="str">
+        <v>7/14/26</v>
+      </c>
+      <c r="Z78" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="AB78" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="AD78" t="str">
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="str">
+        <v>(312)</v>
+      </c>
+      <c r="B79" t="str">
+        <v>(1) Viet Nga Group, (2) Việt Nga Group-HTX DVNN Bình Hiệp B</v>
+      </c>
+      <c r="C79" t="str">
+        <v>73802</v>
+      </c>
+      <c r="D79" t="str">
+        <v>939354864</v>
+      </c>
+      <c r="E79" t="str">
+        <v>PHẠM VĂN MỘNG</v>
+      </c>
+      <c r="F79" t="str">
+        <v>HỢP TÁC XÃ DỊCH VỤ NÔNG NGHIỆP BÌNH HIỆP B</v>
+      </c>
+      <c r="J79" t="str">
+        <v>Intensive rice production // Trồng lúa thâm canh</v>
+      </c>
+      <c r="K79" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="L79" t="str">
+        <v>Male // Nam</v>
+      </c>
+      <c r="M79" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="N79" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O79" t="str">
+        <v>0</v>
+      </c>
+      <c r="P79" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q79" t="str">
+        <v>0</v>
+      </c>
+      <c r="R79" t="str">
+        <v>0</v>
+      </c>
+      <c r="S79" t="str">
+        <v>0</v>
+      </c>
+      <c r="T79" t="str">
+        <v>0</v>
+      </c>
+      <c r="U79" t="str">
+        <v>4</v>
+      </c>
+      <c r="V79" t="str">
+        <v>0</v>
+      </c>
+      <c r="W79" t="str">
+        <v>3</v>
+      </c>
+      <c r="X79" t="str">
+        <v>4/10/26</v>
+      </c>
+      <c r="Y79" t="str">
+        <v>7/14/26</v>
+      </c>
+      <c r="Z79" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="AB79" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="AD79" t="str">
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="str">
+        <v>(314)</v>
+      </c>
+      <c r="B80" t="str">
+        <v>(1) Viet Nga Group, (2) Việt Nga Group-HTX DVNN Bình Hiệp B</v>
+      </c>
+      <c r="C80" t="str">
+        <v>73804</v>
+      </c>
+      <c r="D80" t="str">
+        <v>386363522</v>
+      </c>
+      <c r="E80" t="str">
+        <v>NGUYỄN VĂN NGON</v>
+      </c>
+      <c r="F80" t="str">
+        <v>HỢP TÁC XÃ DỊCH VỤ NÔNG NGHIỆP BÌNH HIỆP B</v>
+      </c>
+      <c r="J80" t="str">
+        <v>Intensive rice production // Trồng lúa thâm canh</v>
+      </c>
+      <c r="K80" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="L80" t="str">
+        <v>Male // Nam</v>
+      </c>
+      <c r="M80" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="N80" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O80" t="str">
+        <v>0</v>
+      </c>
+      <c r="P80" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q80" t="str">
+        <v>0</v>
+      </c>
+      <c r="R80" t="str">
+        <v>0</v>
+      </c>
+      <c r="S80" t="str">
+        <v>0</v>
+      </c>
+      <c r="T80" t="str">
+        <v>0</v>
+      </c>
+      <c r="U80" t="str">
+        <v>4</v>
+      </c>
+      <c r="V80" t="str">
+        <v>0</v>
+      </c>
+      <c r="W80" t="str">
+        <v>3</v>
+      </c>
+      <c r="X80" t="str">
+        <v>4/10/26</v>
+      </c>
+      <c r="Y80" t="str">
+        <v>7/14/26</v>
+      </c>
+      <c r="Z80" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="AB80" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="AD80" t="str">
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="str">
+        <v>(319)</v>
+      </c>
+      <c r="B81" t="str">
+        <v>(1) Viet Nga Group, (2) Việt Nga Group-HTX DVNN Bình Hiệp B</v>
+      </c>
+      <c r="C81" t="str">
+        <v>73809</v>
+      </c>
+      <c r="D81" t="str">
+        <v>388744749</v>
+      </c>
+      <c r="E81" t="str">
+        <v>HUỲNH TẤN KIỆT</v>
+      </c>
+      <c r="F81" t="str">
+        <v>HỢP TÁC XÃ DỊCH VỤ NÔNG NGHIỆP BÌNH HIỆP B</v>
+      </c>
+      <c r="J81" t="str">
+        <v>Intensive rice production // Trồng lúa thâm canh</v>
+      </c>
+      <c r="K81" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="L81" t="str">
+        <v>Male // Nam</v>
+      </c>
+      <c r="M81" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="N81" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O81" t="str">
+        <v>0</v>
+      </c>
+      <c r="P81" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q81" t="str">
+        <v>0</v>
+      </c>
+      <c r="R81" t="str">
+        <v>0</v>
+      </c>
+      <c r="S81" t="str">
+        <v>0</v>
+      </c>
+      <c r="T81" t="str">
+        <v>0</v>
+      </c>
+      <c r="U81" t="str">
+        <v>4</v>
+      </c>
+      <c r="V81" t="str">
+        <v>0</v>
+      </c>
+      <c r="W81" t="str">
+        <v>3</v>
+      </c>
+      <c r="X81" t="str">
+        <v>4/10/26</v>
+      </c>
+      <c r="Y81" t="str">
+        <v>7/14/26</v>
+      </c>
+      <c r="Z81" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="AB81" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="AD81" t="str">
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="str">
+        <v>(320)</v>
+      </c>
+      <c r="B82" t="str">
+        <v>(1) Viet Nga Group, (2) Việt Nga Group-HTX DVNN Bình Hiệp B</v>
+      </c>
+      <c r="C82" t="str">
+        <v>73810</v>
+      </c>
+      <c r="D82" t="str">
+        <v>834367845</v>
+      </c>
+      <c r="E82" t="str">
+        <v>HỒ VĂN CÒN</v>
+      </c>
+      <c r="F82" t="str">
+        <v>HỢP TÁC XÃ DỊCH VỤ NÔNG NGHIỆP BÌNH HIỆP B</v>
+      </c>
+      <c r="J82" t="str">
+        <v>Intensive rice production // Trồng lúa thâm canh</v>
+      </c>
+      <c r="K82" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="L82" t="str">
+        <v>Male // Nam</v>
+      </c>
+      <c r="M82" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="N82" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O82" t="str">
+        <v>0</v>
+      </c>
+      <c r="P82" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q82" t="str">
+        <v>0</v>
+      </c>
+      <c r="R82" t="str">
+        <v>0</v>
+      </c>
+      <c r="S82" t="str">
+        <v>0</v>
+      </c>
+      <c r="T82" t="str">
+        <v>0</v>
+      </c>
+      <c r="U82" t="str">
+        <v>5</v>
+      </c>
+      <c r="V82" t="str">
+        <v>0</v>
+      </c>
+      <c r="W82" t="str">
+        <v>4</v>
+      </c>
+      <c r="X82" t="str">
+        <v>4/10/26</v>
+      </c>
+      <c r="Y82" t="str">
+        <v>7/14/26</v>
+      </c>
+      <c r="Z82" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="AB82" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="AD82" t="str">
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="str">
+        <v>(322)</v>
+      </c>
+      <c r="B83" t="str">
+        <v>(1) Viet Nga Group, (2) Việt Nga Group-HTX DVNN Bình Hiệp B</v>
+      </c>
+      <c r="C83" t="str">
+        <v>73812</v>
+      </c>
+      <c r="D83" t="str">
+        <v>374515291</v>
+      </c>
+      <c r="E83" t="str">
+        <v>PHẠM VĂN TIỂNG</v>
+      </c>
+      <c r="F83" t="str">
+        <v>HỢP TÁC XÃ DỊCH VỤ NÔNG NGHIỆP BÌNH HIỆP B</v>
+      </c>
+      <c r="J83" t="str">
+        <v>Intensive rice production // Trồng lúa thâm canh</v>
+      </c>
+      <c r="K83" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="L83" t="str">
+        <v>Male // Nam</v>
+      </c>
+      <c r="M83" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="N83" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O83" t="str">
+        <v>0</v>
+      </c>
+      <c r="P83" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q83" t="str">
+        <v>0</v>
+      </c>
+      <c r="R83" t="str">
+        <v>0</v>
+      </c>
+      <c r="S83" t="str">
+        <v>0</v>
+      </c>
+      <c r="T83" t="str">
+        <v>0</v>
+      </c>
+      <c r="U83" t="str">
+        <v>4</v>
+      </c>
+      <c r="V83" t="str">
+        <v>0</v>
+      </c>
+      <c r="W83" t="str">
+        <v>3</v>
+      </c>
+      <c r="X83" t="str">
+        <v>4/10/26</v>
+      </c>
+      <c r="Y83" t="str">
+        <v>7/14/26</v>
+      </c>
+      <c r="Z83" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="AB83" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="AD83" t="str">
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="str">
+        <v>(324)</v>
+      </c>
+      <c r="B84" t="str">
+        <v>(1) Viet Nga Group, (2) Việt Nga Group-HTX DVNN Bình Hiệp B</v>
+      </c>
+      <c r="C84" t="str">
+        <v>73814</v>
+      </c>
+      <c r="D84" t="str">
+        <v>384965513</v>
+      </c>
+      <c r="E84" t="str">
+        <v>NGUYỄN VĂN BỰC</v>
+      </c>
+      <c r="F84" t="str">
+        <v>HỢP TÁC XÃ DỊCH VỤ NÔNG NGHIỆP BÌNH HIỆP B</v>
+      </c>
+      <c r="J84" t="str">
+        <v>Intensive rice production // Trồng lúa thâm canh</v>
+      </c>
+      <c r="K84" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="L84" t="str">
+        <v>Male // Nam</v>
+      </c>
+      <c r="M84" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="N84" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O84" t="str">
+        <v>0</v>
+      </c>
+      <c r="P84" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q84" t="str">
+        <v>0</v>
+      </c>
+      <c r="R84" t="str">
+        <v>0</v>
+      </c>
+      <c r="S84" t="str">
+        <v>0</v>
+      </c>
+      <c r="T84" t="str">
+        <v>0</v>
+      </c>
+      <c r="U84" t="str">
+        <v>3</v>
+      </c>
+      <c r="V84" t="str">
+        <v>0</v>
+      </c>
+      <c r="W84" t="str">
+        <v>2</v>
+      </c>
+      <c r="X84" t="str">
+        <v>4/10/26</v>
+      </c>
+      <c r="Y84" t="str">
+        <v>7/14/26</v>
+      </c>
+      <c r="Z84" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="AB84" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="AD84" t="str">
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="str">
+        <v>(325)</v>
+      </c>
+      <c r="B85" t="str">
+        <v>(1) Viet Nga Group, (2) Việt Nga Group-HTX DVNN Bình Hiệp B</v>
+      </c>
+      <c r="C85" t="str">
+        <v>73815</v>
+      </c>
+      <c r="D85" t="str">
+        <v>984622189</v>
+      </c>
+      <c r="E85" t="str">
+        <v>NGUYỄN VĂN TÍCH</v>
+      </c>
+      <c r="F85" t="str">
+        <v>HỢP TÁC XÃ DỊCH VỤ NÔNG NGHIỆP BÌNH HIỆP B</v>
+      </c>
+      <c r="J85" t="str">
+        <v>Intensive rice production // Trồng lúa thâm canh</v>
+      </c>
+      <c r="K85" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="L85" t="str">
+        <v>Male // Nam</v>
+      </c>
+      <c r="M85" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="N85" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O85" t="str">
+        <v>0</v>
+      </c>
+      <c r="P85" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q85" t="str">
+        <v>0</v>
+      </c>
+      <c r="R85" t="str">
+        <v>0</v>
+      </c>
+      <c r="S85" t="str">
+        <v>0</v>
+      </c>
+      <c r="T85" t="str">
+        <v>0</v>
+      </c>
+      <c r="U85" t="str">
+        <v>3</v>
+      </c>
+      <c r="V85" t="str">
+        <v>0</v>
+      </c>
+      <c r="W85" t="str">
+        <v>2</v>
+      </c>
+      <c r="X85" t="str">
+        <v>4/10/26</v>
+      </c>
+      <c r="Y85" t="str">
+        <v>7/14/26</v>
+      </c>
+      <c r="Z85" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="AB85" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="AD85" t="str">
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="str">
+        <v>(327)</v>
+      </c>
+      <c r="B86" t="str">
+        <v>(1) Viet Nga Group, (2) Việt Nga Group-HTX DVNN Bình Hiệp B</v>
+      </c>
+      <c r="C86" t="str">
+        <v>73817</v>
+      </c>
+      <c r="D86" t="str">
+        <v>386049296</v>
+      </c>
+      <c r="E86" t="str">
+        <v>NGUYỄN VĂN GÚP</v>
+      </c>
+      <c r="F86" t="str">
+        <v>HỢP TÁC XÃ DỊCH VỤ NÔNG NGHIỆP BÌNH HIỆP B</v>
+      </c>
+      <c r="J86" t="str">
+        <v>Intensive rice production // Trồng lúa thâm canh</v>
+      </c>
+      <c r="K86" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="L86" t="str">
+        <v>Male // Nam</v>
+      </c>
+      <c r="M86" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="N86" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O86" t="str">
+        <v>0</v>
+      </c>
+      <c r="P86" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q86" t="str">
+        <v>0</v>
+      </c>
+      <c r="R86" t="str">
+        <v>0</v>
+      </c>
+      <c r="S86" t="str">
+        <v>0</v>
+      </c>
+      <c r="T86" t="str">
+        <v>0</v>
+      </c>
+      <c r="U86" t="str">
+        <v>5</v>
+      </c>
+      <c r="V86" t="str">
+        <v>0</v>
+      </c>
+      <c r="W86" t="str">
+        <v>4</v>
+      </c>
+      <c r="X86" t="str">
+        <v>4/10/26</v>
+      </c>
+      <c r="Y86" t="str">
+        <v>7/14/26</v>
+      </c>
+      <c r="Z86" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="AB86" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="AD86" t="str">
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="str">
+        <v>(328)</v>
+      </c>
+      <c r="B87" t="str">
+        <v>(1) Viet Nga Group, (2) Việt Nga Group-HTX DVNN Bình Hiệp B</v>
+      </c>
+      <c r="C87" t="str">
+        <v>73818</v>
+      </c>
+      <c r="D87" t="str">
+        <v>939250405</v>
+      </c>
+      <c r="E87" t="str">
+        <v>NGUYỄN THANH TUẤN</v>
+      </c>
+      <c r="F87" t="str">
+        <v>HỢP TÁC XÃ DỊCH VỤ NÔNG NGHIỆP BÌNH HIỆP B</v>
+      </c>
+      <c r="J87" t="str">
+        <v>Intensive rice production // Trồng lúa thâm canh</v>
+      </c>
+      <c r="K87" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="L87" t="str">
+        <v>Male // Nam</v>
+      </c>
+      <c r="M87" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="N87" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O87" t="str">
+        <v>0</v>
+      </c>
+      <c r="P87" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q87" t="str">
+        <v>0</v>
+      </c>
+      <c r="R87" t="str">
+        <v>0</v>
+      </c>
+      <c r="S87" t="str">
+        <v>0</v>
+      </c>
+      <c r="T87" t="str">
+        <v>0</v>
+      </c>
+      <c r="U87" t="str">
+        <v>4</v>
+      </c>
+      <c r="V87" t="str">
+        <v>0</v>
+      </c>
+      <c r="W87" t="str">
+        <v>3</v>
+      </c>
+      <c r="X87" t="str">
+        <v>4/10/26</v>
+      </c>
+      <c r="Y87" t="str">
+        <v>7/14/26</v>
+      </c>
+      <c r="Z87" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="AB87" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="AD87" t="str">
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="str">
+        <v>(331)</v>
+      </c>
+      <c r="B88" t="str">
+        <v>(1) Viet Nga Group, (2) Việt Nga Group-HTX DVNN Bình Hiệp B</v>
+      </c>
+      <c r="C88" t="str">
+        <v>73821</v>
+      </c>
+      <c r="D88" t="str">
+        <v>386658846</v>
+      </c>
+      <c r="E88" t="str">
+        <v>LƯƠNG TẤN XUÂN</v>
+      </c>
+      <c r="F88" t="str">
+        <v>HỢP TÁC XÃ DỊCH VỤ NÔNG NGHIỆP BÌNH HIỆP B</v>
+      </c>
+      <c r="J88" t="str">
+        <v>Intensive rice production // Trồng lúa thâm canh</v>
+      </c>
+      <c r="K88" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="L88" t="str">
+        <v>Male // Nam</v>
+      </c>
+      <c r="M88" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="N88" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O88" t="str">
+        <v>0</v>
+      </c>
+      <c r="P88" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q88" t="str">
+        <v>0</v>
+      </c>
+      <c r="R88" t="str">
+        <v>0</v>
+      </c>
+      <c r="S88" t="str">
+        <v>0</v>
+      </c>
+      <c r="T88" t="str">
+        <v>0</v>
+      </c>
+      <c r="U88" t="str">
+        <v>3</v>
+      </c>
+      <c r="V88" t="str">
+        <v>0</v>
+      </c>
+      <c r="W88" t="str">
+        <v>2</v>
+      </c>
+      <c r="X88" t="str">
+        <v>4/10/26</v>
+      </c>
+      <c r="Y88" t="str">
+        <v>7/14/26</v>
+      </c>
+      <c r="Z88" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="AB88" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="AD88" t="str">
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="str">
+        <v>(333)</v>
+      </c>
+      <c r="B89" t="str">
+        <v>(1) Viet Nga Group, (2) Việt Nga Group-HTX DVNN Bình Hiệp B</v>
+      </c>
+      <c r="C89" t="str">
+        <v>73823</v>
+      </c>
+      <c r="D89" t="str">
+        <v>336348881</v>
+      </c>
+      <c r="E89" t="str">
+        <v>ĐOÀN VĂN HAI</v>
+      </c>
+      <c r="F89" t="str">
+        <v>HỢP TÁC XÃ DỊCH VỤ NÔNG NGHIỆP BÌNH HIỆP B</v>
+      </c>
+      <c r="J89" t="str">
+        <v>Intensive rice production // Trồng lúa thâm canh</v>
+      </c>
+      <c r="K89" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="L89" t="str">
+        <v>Male // Nam</v>
+      </c>
+      <c r="M89" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="N89" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O89" t="str">
+        <v>0</v>
+      </c>
+      <c r="P89" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q89" t="str">
+        <v>0</v>
+      </c>
+      <c r="R89" t="str">
+        <v>0</v>
+      </c>
+      <c r="S89" t="str">
+        <v>0</v>
+      </c>
+      <c r="T89" t="str">
+        <v>0</v>
+      </c>
+      <c r="U89" t="str">
+        <v>3</v>
+      </c>
+      <c r="V89" t="str">
+        <v>0</v>
+      </c>
+      <c r="W89" t="str">
+        <v>2</v>
+      </c>
+      <c r="X89" t="str">
+        <v>4/10/26</v>
+      </c>
+      <c r="Y89" t="str">
+        <v>7/14/26</v>
+      </c>
+      <c r="Z89" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="AB89" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="AD89" t="str">
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="str">
+        <v>(334)</v>
+      </c>
+      <c r="B90" t="str">
+        <v>(1) Viet Nga Group, (2) Việt Nga Group-HTX DVNN Bình Hiệp B</v>
+      </c>
+      <c r="C90" t="str">
+        <v>73824</v>
+      </c>
+      <c r="D90" t="str">
+        <v>388218751</v>
+      </c>
+      <c r="E90" t="str">
+        <v>NGUYỄN VĂN LẮM</v>
+      </c>
+      <c r="F90" t="str">
+        <v>HỢP TÁC XÃ DỊCH VỤ NÔNG NGHIỆP BÌNH HIỆP B</v>
+      </c>
+      <c r="J90" t="str">
+        <v>Intensive rice production // Trồng lúa thâm canh</v>
+      </c>
+      <c r="K90" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="L90" t="str">
+        <v>Male // Nam</v>
+      </c>
+      <c r="M90" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="N90" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O90" t="str">
+        <v>0</v>
+      </c>
+      <c r="P90" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q90" t="str">
+        <v>0</v>
+      </c>
+      <c r="R90" t="str">
+        <v>0</v>
+      </c>
+      <c r="S90" t="str">
+        <v>0</v>
+      </c>
+      <c r="T90" t="str">
+        <v>0</v>
+      </c>
+      <c r="U90" t="str">
+        <v>4</v>
+      </c>
+      <c r="V90" t="str">
+        <v>0</v>
+      </c>
+      <c r="W90" t="str">
+        <v>2</v>
+      </c>
+      <c r="X90" t="str">
+        <v>4/10/26</v>
+      </c>
+      <c r="Y90" t="str">
+        <v>7/14/26</v>
+      </c>
+      <c r="Z90" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="AB90" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="AD90" t="str">
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="str">
+        <v>(335)</v>
+      </c>
+      <c r="B91" t="str">
+        <v>(1) Viet Nga Group, (2) Việt Nga Group-HTX DVNN Bình Hiệp B</v>
+      </c>
+      <c r="C91" t="str">
+        <v>73825</v>
+      </c>
+      <c r="D91" t="str">
+        <v>919320157</v>
+      </c>
+      <c r="E91" t="str">
+        <v>NGUYỄN HỮU ĐỨC</v>
+      </c>
+      <c r="F91" t="str">
+        <v>HỢP TÁC XÃ DỊCH VỤ NÔNG NGHIỆP BÌNH HIỆP B</v>
+      </c>
+      <c r="J91" t="str">
+        <v>Intensive rice production // Trồng lúa thâm canh</v>
+      </c>
+      <c r="K91" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="L91" t="str">
+        <v>Male // Nam</v>
+      </c>
+      <c r="M91" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="N91" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O91" t="str">
+        <v>0</v>
+      </c>
+      <c r="P91" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q91" t="str">
+        <v>0</v>
+      </c>
+      <c r="R91" t="str">
+        <v>0</v>
+      </c>
+      <c r="S91" t="str">
+        <v>0</v>
+      </c>
+      <c r="T91" t="str">
+        <v>0</v>
+      </c>
+      <c r="U91" t="str">
+        <v>4</v>
+      </c>
+      <c r="V91" t="str">
+        <v>0</v>
+      </c>
+      <c r="W91" t="str">
+        <v>3</v>
+      </c>
+      <c r="X91" t="str">
+        <v>4/10/26</v>
+      </c>
+      <c r="Y91" t="str">
+        <v>7/14/26</v>
+      </c>
+      <c r="Z91" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="AB91" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="AD91" t="str">
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="str">
+        <v>(336)</v>
+      </c>
+      <c r="B92" t="str">
+        <v>(1) Viet Nga Group, (2) Việt Nga Group-HTX DVNN Bình Hiệp B</v>
+      </c>
+      <c r="C92" t="str">
+        <v>73826</v>
+      </c>
+      <c r="D92" t="str">
+        <v>919705659</v>
+      </c>
+      <c r="E92" t="str">
+        <v>LÊ VĂN ÚT</v>
+      </c>
+      <c r="F92" t="str">
+        <v>HỢP TÁC XÃ DỊCH VỤ NÔNG NGHIỆP BÌNH HIỆP B</v>
+      </c>
+      <c r="J92" t="str">
+        <v>Intensive rice production // Trồng lúa thâm canh</v>
+      </c>
+      <c r="K92" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="L92" t="str">
+        <v>Male // Nam</v>
+      </c>
+      <c r="M92" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="N92" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O92" t="str">
+        <v>0</v>
+      </c>
+      <c r="P92" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q92" t="str">
+        <v>0</v>
+      </c>
+      <c r="R92" t="str">
+        <v>0</v>
+      </c>
+      <c r="S92" t="str">
+        <v>0</v>
+      </c>
+      <c r="T92" t="str">
+        <v>0</v>
+      </c>
+      <c r="U92" t="str">
+        <v>4</v>
+      </c>
+      <c r="V92" t="str">
+        <v>0</v>
+      </c>
+      <c r="W92" t="str">
+        <v>3</v>
+      </c>
+      <c r="X92" t="str">
+        <v>4/10/26</v>
+      </c>
+      <c r="Y92" t="str">
+        <v>7/14/26</v>
+      </c>
+      <c r="Z92" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="AB92" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="AD92" t="str">
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="str">
+        <v>(337)</v>
+      </c>
+      <c r="B93" t="str">
+        <v>(1) Viet Nga Group, (2) Việt Nga Group-HTX DVNN Bình Hiệp B</v>
+      </c>
+      <c r="C93" t="str">
+        <v>73827</v>
+      </c>
+      <c r="D93" t="str">
+        <v>372108598</v>
+      </c>
+      <c r="E93" t="str">
+        <v>NGUYỄN VĂN ÚT</v>
+      </c>
+      <c r="F93" t="str">
+        <v>HỢP TÁC XÃ DỊCH VỤ NÔNG NGHIỆP BÌNH HIỆP B</v>
+      </c>
+      <c r="J93" t="str">
+        <v>Intensive rice production // Trồng lúa thâm canh</v>
+      </c>
+      <c r="K93" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="L93" t="str">
+        <v>Male // Nam</v>
+      </c>
+      <c r="M93" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="N93" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O93" t="str">
+        <v>0</v>
+      </c>
+      <c r="P93" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q93" t="str">
+        <v>0</v>
+      </c>
+      <c r="R93" t="str">
+        <v>0</v>
+      </c>
+      <c r="S93" t="str">
+        <v>0</v>
+      </c>
+      <c r="T93" t="str">
+        <v>0</v>
+      </c>
+      <c r="U93" t="str">
+        <v>4</v>
+      </c>
+      <c r="V93" t="str">
+        <v>0</v>
+      </c>
+      <c r="W93" t="str">
+        <v>3</v>
+      </c>
+      <c r="X93" t="str">
+        <v>4/10/26</v>
+      </c>
+      <c r="Y93" t="str">
+        <v>7/14/26</v>
+      </c>
+      <c r="Z93" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="AB93" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="AD93" t="str">
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="str">
+        <v>(338)</v>
+      </c>
+      <c r="B94" t="str">
+        <v>(1) Viet Nga Group, (2) Việt Nga Group-HTX DVNN Bình Hiệp B</v>
+      </c>
+      <c r="C94" t="str">
+        <v>73828</v>
+      </c>
+      <c r="D94" t="str">
+        <v>783858306</v>
+      </c>
+      <c r="E94" t="str">
+        <v>HOÀNG HOA THÁM</v>
+      </c>
+      <c r="F94" t="str">
+        <v>HỢP TÁC XÃ DỊCH VỤ NÔNG NGHIỆP BÌNH HIỆP B</v>
+      </c>
+      <c r="J94" t="str">
+        <v>Intensive rice production // Trồng lúa thâm canh</v>
+      </c>
+      <c r="K94" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="L94" t="str">
+        <v>Male // Nam</v>
+      </c>
+      <c r="M94" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="N94" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O94" t="str">
+        <v>0</v>
+      </c>
+      <c r="P94" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q94" t="str">
+        <v>0</v>
+      </c>
+      <c r="R94" t="str">
+        <v>0</v>
+      </c>
+      <c r="S94" t="str">
+        <v>0</v>
+      </c>
+      <c r="T94" t="str">
+        <v>0</v>
+      </c>
+      <c r="U94" t="str">
+        <v>4</v>
+      </c>
+      <c r="V94" t="str">
+        <v>0</v>
+      </c>
+      <c r="W94" t="str">
+        <v>3</v>
+      </c>
+      <c r="X94" t="str">
+        <v>4/10/26</v>
+      </c>
+      <c r="Y94" t="str">
+        <v>7/14/26</v>
+      </c>
+      <c r="Z94" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="AB94" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="AD94" t="str">
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="str">
+        <v>(339)</v>
+      </c>
+      <c r="B95" t="str">
+        <v>(1) Viet Nga Group, (2) Việt Nga Group-HTX DVNN Bình Hiệp B</v>
+      </c>
+      <c r="C95" t="str">
+        <v>73829</v>
+      </c>
+      <c r="D95" t="str">
+        <v>329301571</v>
+      </c>
+      <c r="E95" t="str">
+        <v>ĐOÀN TẤN VÂN</v>
+      </c>
+      <c r="F95" t="str">
+        <v>HỢP TÁC XÃ DỊCH VỤ NÔNG NGHIỆP BÌNH HIỆP B</v>
+      </c>
+      <c r="J95" t="str">
+        <v>Intensive rice production // Trồng lúa thâm canh</v>
+      </c>
+      <c r="K95" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="L95" t="str">
+        <v>Male // Nam</v>
+      </c>
+      <c r="M95" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="N95" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O95" t="str">
+        <v>0</v>
+      </c>
+      <c r="P95" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q95" t="str">
+        <v>0</v>
+      </c>
+      <c r="R95" t="str">
+        <v>0</v>
+      </c>
+      <c r="S95" t="str">
+        <v>0</v>
+      </c>
+      <c r="T95" t="str">
+        <v>0</v>
+      </c>
+      <c r="U95" t="str">
+        <v>5</v>
+      </c>
+      <c r="V95" t="str">
+        <v>0</v>
+      </c>
+      <c r="W95" t="str">
+        <v>4</v>
+      </c>
+      <c r="X95" t="str">
+        <v>4/10/26</v>
+      </c>
+      <c r="Y95" t="str">
+        <v>7/14/26</v>
+      </c>
+      <c r="Z95" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="AB95" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="AD95" t="str">
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="str">
+        <v>(421)</v>
+      </c>
+      <c r="B96" t="str">
+        <v>(1) Viet Nga Group, (2) Việt Nga Group-HTX DVNN Bình Hiệp B</v>
+      </c>
+      <c r="C96" t="str">
+        <v>74933</v>
+      </c>
+      <c r="D96" t="str">
+        <v>397378799</v>
+      </c>
+      <c r="E96" t="str">
+        <v>NGUYỄN TRUNG TẤN</v>
+      </c>
+      <c r="F96" t="str">
+        <v>HỢP TÁC XÃ DỊCH VỤ NÔNG NGHIỆP BÌNH HIỆP B</v>
+      </c>
+      <c r="J96" t="str">
+        <v>Intensive rice production // Trồng lúa thâm canh</v>
+      </c>
+      <c r="K96" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="L96" t="str">
+        <v>Male // Nam</v>
+      </c>
+      <c r="M96" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="N96" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O96" t="str">
+        <v>0</v>
+      </c>
+      <c r="P96" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q96" t="str">
+        <v>0</v>
+      </c>
+      <c r="R96" t="str">
+        <v>0</v>
+      </c>
+      <c r="S96" t="str">
+        <v>0</v>
+      </c>
+      <c r="T96" t="str">
+        <v>0</v>
+      </c>
+      <c r="U96" t="str">
+        <v>3</v>
+      </c>
+      <c r="V96" t="str">
+        <v>0</v>
+      </c>
+      <c r="W96" t="str">
+        <v>2</v>
+      </c>
+      <c r="X96" t="str">
+        <v>4/10/26</v>
+      </c>
+      <c r="Y96" t="str">
+        <v>7/14/26</v>
+      </c>
+      <c r="Z96" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="AB96" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="AD96" t="str">
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="str">
+        <v>(421)</v>
+      </c>
+      <c r="B97" t="str">
+        <v>(1) Viet Nga Group, (2) Việt Nga Group-HTX DVNN Bình Hiệp B</v>
+      </c>
+      <c r="C97" t="str">
+        <v>74933</v>
+      </c>
+      <c r="D97" t="str">
+        <v>397378799</v>
+      </c>
+      <c r="E97" t="str">
+        <v>NGUYỄN TRUNG TẤN</v>
+      </c>
+      <c r="F97" t="str">
+        <v>HỢP TÁC XÃ DỊCH VỤ NÔNG NGHIỆP BÌNH HIỆP B</v>
+      </c>
+      <c r="J97" t="str">
+        <v>Intensive rice production // Trồng lúa thâm canh</v>
+      </c>
+      <c r="K97" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="L97" t="str">
+        <v>Male // Nam</v>
+      </c>
+      <c r="M97" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="N97" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O97" t="str">
+        <v>0</v>
+      </c>
+      <c r="P97" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q97" t="str">
+        <v>0</v>
+      </c>
+      <c r="R97" t="str">
+        <v>0</v>
+      </c>
+      <c r="S97" t="str">
+        <v>0</v>
+      </c>
+      <c r="T97" t="str">
+        <v>0</v>
+      </c>
+      <c r="U97" t="str">
+        <v>3</v>
+      </c>
+      <c r="V97" t="str">
+        <v>0</v>
+      </c>
+      <c r="W97" t="str">
+        <v>2</v>
+      </c>
+      <c r="X97" t="str">
+        <v>4/10/26</v>
+      </c>
+      <c r="Y97" t="str">
+        <v>7/14/26</v>
+      </c>
+      <c r="Z97" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="AB97" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="AD97" t="str">
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="str">
+        <v>(308)</v>
+      </c>
+      <c r="B98" t="str">
+        <v>(1) Viet Nga Group, (2) Việt Nga Group-HTX DVNN Bình Hiệp B</v>
+      </c>
+      <c r="C98" t="str">
+        <v>73798</v>
+      </c>
+      <c r="D98" t="str">
+        <v>375625234</v>
+      </c>
+      <c r="E98" t="str">
+        <v>LÊ VĂN SON</v>
+      </c>
+      <c r="F98" t="str">
+        <v>HỢP TÁC XÃ DỊCH VỤ NÔNG NGHIỆP BÌNH HIỆP B</v>
+      </c>
+      <c r="J98" t="str">
+        <v>Intensive rice production // Trồng lúa thâm canh</v>
+      </c>
+      <c r="K98" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="L98" t="str">
+        <v>Male // Nam</v>
+      </c>
+      <c r="M98" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="N98" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O98" t="str">
+        <v>0</v>
+      </c>
+      <c r="P98" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q98" t="str">
+        <v>0</v>
+      </c>
+      <c r="R98" t="str">
+        <v>0</v>
+      </c>
+      <c r="S98" t="str">
+        <v>0</v>
+      </c>
+      <c r="T98" t="str">
+        <v>0</v>
+      </c>
+      <c r="U98" t="str">
+        <v>3</v>
+      </c>
+      <c r="V98" t="str">
+        <v>0</v>
+      </c>
+      <c r="W98" t="str">
+        <v>2</v>
+      </c>
+      <c r="X98" t="str">
+        <v>4/10/26</v>
+      </c>
+      <c r="Y98" t="str">
+        <v>7/14/26</v>
+      </c>
+      <c r="Z98" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="AB98" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="AD98" t="str">
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="str">
+        <v>(309)</v>
+      </c>
+      <c r="B99" t="str">
+        <v>(1) Viet Nga Group, (2) Việt Nga Group-HTX DVNN Bình Hiệp B</v>
+      </c>
+      <c r="C99" t="str">
+        <v>73799</v>
+      </c>
+      <c r="D99" t="str">
+        <v>862256519</v>
+      </c>
+      <c r="E99" t="str">
+        <v>NGUYỄN VĂN VŨ</v>
+      </c>
+      <c r="F99" t="str">
+        <v>HỢP TÁC XÃ DỊCH VỤ NÔNG NGHIỆP BÌNH HIỆP B</v>
+      </c>
+      <c r="J99" t="str">
+        <v>Intensive rice production // Trồng lúa thâm canh</v>
+      </c>
+      <c r="K99" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="L99" t="str">
+        <v>Male // Nam</v>
+      </c>
+      <c r="M99" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="N99" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O99" t="str">
+        <v>0</v>
+      </c>
+      <c r="P99" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q99" t="str">
+        <v>0</v>
+      </c>
+      <c r="R99" t="str">
+        <v>0</v>
+      </c>
+      <c r="S99" t="str">
+        <v>0</v>
+      </c>
+      <c r="T99" t="str">
+        <v>0</v>
+      </c>
+      <c r="U99" t="str">
+        <v>3</v>
+      </c>
+      <c r="V99" t="str">
+        <v>0</v>
+      </c>
+      <c r="W99" t="str">
+        <v>2</v>
+      </c>
+      <c r="X99" t="str">
+        <v>4/10/26</v>
+      </c>
+      <c r="Y99" t="str">
+        <v>7/14/26</v>
+      </c>
+      <c r="Z99" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="AB99" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="AD99" t="str">
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="str">
+        <v>(310)</v>
+      </c>
+      <c r="B100" t="str">
+        <v>(1) Viet Nga Group, (2) Việt Nga Group-HTX DVNN Bình Hiệp B</v>
+      </c>
+      <c r="C100" t="str">
+        <v>73800</v>
+      </c>
+      <c r="D100" t="str">
+        <v>973345487</v>
+      </c>
+      <c r="E100" t="str">
+        <v>NGUYỄN VĂN SÁU</v>
+      </c>
+      <c r="F100" t="str">
+        <v>HỢP TÁC XÃ DỊCH VỤ NÔNG NGHIỆP BÌNH HIỆP B</v>
+      </c>
+      <c r="J100" t="str">
+        <v>Intensive rice production // Trồng lúa thâm canh</v>
+      </c>
+      <c r="K100" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="L100" t="str">
+        <v>Male // Nam</v>
+      </c>
+      <c r="M100" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="N100" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O100" t="str">
+        <v>0</v>
+      </c>
+      <c r="P100" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q100" t="str">
+        <v>0</v>
+      </c>
+      <c r="R100" t="str">
+        <v>0</v>
+      </c>
+      <c r="S100" t="str">
+        <v>0</v>
+      </c>
+      <c r="T100" t="str">
+        <v>0</v>
+      </c>
+      <c r="U100" t="str">
+        <v>4</v>
+      </c>
+      <c r="V100" t="str">
+        <v>0</v>
+      </c>
+      <c r="W100" t="str">
+        <v>2</v>
+      </c>
+      <c r="X100" t="str">
+        <v>4/10/26</v>
+      </c>
+      <c r="Y100" t="str">
+        <v>7/14/26</v>
+      </c>
+      <c r="Z100" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="AB100" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="AD100" t="str">
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="str">
+        <v>(311)</v>
+      </c>
+      <c r="B101" t="str">
+        <v>(1) Viet Nga Group, (2) Việt Nga Group-HTX DVNN Bình Hiệp B</v>
+      </c>
+      <c r="C101" t="str">
+        <v>73801</v>
+      </c>
+      <c r="D101" t="str">
+        <v>949611220</v>
+      </c>
+      <c r="E101" t="str">
+        <v>PHẠM VĂN LUÔNG</v>
+      </c>
+      <c r="F101" t="str">
+        <v>HỢP TÁC XÃ DỊCH VỤ NÔNG NGHIỆP BÌNH HIỆP B</v>
+      </c>
+      <c r="J101" t="str">
+        <v>Intensive rice production // Trồng lúa thâm canh</v>
+      </c>
+      <c r="K101" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="L101" t="str">
+        <v>Male // Nam</v>
+      </c>
+      <c r="M101" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="N101" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O101" t="str">
+        <v>0</v>
+      </c>
+      <c r="P101" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q101" t="str">
+        <v>0</v>
+      </c>
+      <c r="R101" t="str">
+        <v>0</v>
+      </c>
+      <c r="S101" t="str">
+        <v>0</v>
+      </c>
+      <c r="T101" t="str">
+        <v>0</v>
+      </c>
+      <c r="U101" t="str">
+        <v>5</v>
+      </c>
+      <c r="V101" t="str">
+        <v>0</v>
+      </c>
+      <c r="W101" t="str">
+        <v>2</v>
+      </c>
+      <c r="X101" t="str">
+        <v>4/10/26</v>
+      </c>
+      <c r="Y101" t="str">
+        <v>7/14/26</v>
+      </c>
+      <c r="Z101" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="AB101" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="AD101" t="str">
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="str">
+        <v>(312)</v>
+      </c>
+      <c r="B102" t="str">
+        <v>(1) Viet Nga Group, (2) Việt Nga Group-HTX DVNN Bình Hiệp B</v>
+      </c>
+      <c r="C102" t="str">
+        <v>73802</v>
+      </c>
+      <c r="D102" t="str">
+        <v>939354864</v>
+      </c>
+      <c r="E102" t="str">
+        <v>PHẠM VĂN MỘNG</v>
+      </c>
+      <c r="F102" t="str">
+        <v>HỢP TÁC XÃ DỊCH VỤ NÔNG NGHIỆP BÌNH HIỆP B</v>
+      </c>
+      <c r="J102" t="str">
+        <v>Intensive rice production // Trồng lúa thâm canh</v>
+      </c>
+      <c r="K102" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="L102" t="str">
+        <v>Male // Nam</v>
+      </c>
+      <c r="M102" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="N102" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O102" t="str">
+        <v>0</v>
+      </c>
+      <c r="P102" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q102" t="str">
+        <v>0</v>
+      </c>
+      <c r="R102" t="str">
+        <v>0</v>
+      </c>
+      <c r="S102" t="str">
+        <v>0</v>
+      </c>
+      <c r="T102" t="str">
+        <v>0</v>
+      </c>
+      <c r="U102" t="str">
+        <v>4</v>
+      </c>
+      <c r="V102" t="str">
+        <v>0</v>
+      </c>
+      <c r="W102" t="str">
+        <v>3</v>
+      </c>
+      <c r="X102" t="str">
+        <v>4/10/26</v>
+      </c>
+      <c r="Y102" t="str">
+        <v>7/14/26</v>
+      </c>
+      <c r="Z102" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="AB102" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="AD102" t="str">
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="str">
+        <v>(314)</v>
+      </c>
+      <c r="B103" t="str">
+        <v>(1) Viet Nga Group, (2) Việt Nga Group-HTX DVNN Bình Hiệp B</v>
+      </c>
+      <c r="C103" t="str">
+        <v>73804</v>
+      </c>
+      <c r="D103" t="str">
+        <v>386363522</v>
+      </c>
+      <c r="E103" t="str">
+        <v>NGUYỄN VĂN NGON</v>
+      </c>
+      <c r="F103" t="str">
+        <v>HỢP TÁC XÃ DỊCH VỤ NÔNG NGHIỆP BÌNH HIỆP B</v>
+      </c>
+      <c r="J103" t="str">
+        <v>Intensive rice production // Trồng lúa thâm canh</v>
+      </c>
+      <c r="K103" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="L103" t="str">
+        <v>Male // Nam</v>
+      </c>
+      <c r="M103" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="N103" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O103" t="str">
+        <v>0</v>
+      </c>
+      <c r="P103" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q103" t="str">
+        <v>0</v>
+      </c>
+      <c r="R103" t="str">
+        <v>0</v>
+      </c>
+      <c r="S103" t="str">
+        <v>0</v>
+      </c>
+      <c r="T103" t="str">
+        <v>0</v>
+      </c>
+      <c r="U103" t="str">
+        <v>4</v>
+      </c>
+      <c r="V103" t="str">
+        <v>0</v>
+      </c>
+      <c r="W103" t="str">
+        <v>3</v>
+      </c>
+      <c r="X103" t="str">
+        <v>4/10/26</v>
+      </c>
+      <c r="Y103" t="str">
+        <v>7/14/26</v>
+      </c>
+      <c r="Z103" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="AB103" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="AD103" t="str">
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="str">
+        <v>(319)</v>
+      </c>
+      <c r="B104" t="str">
+        <v>(1) Viet Nga Group, (2) Việt Nga Group-HTX DVNN Bình Hiệp B</v>
+      </c>
+      <c r="C104" t="str">
+        <v>73809</v>
+      </c>
+      <c r="D104" t="str">
+        <v>388744749</v>
+      </c>
+      <c r="E104" t="str">
+        <v>HUỲNH TẤN KIỆT</v>
+      </c>
+      <c r="F104" t="str">
+        <v>HỢP TÁC XÃ DỊCH VỤ NÔNG NGHIỆP BÌNH HIỆP B</v>
+      </c>
+      <c r="J104" t="str">
+        <v>Intensive rice production // Trồng lúa thâm canh</v>
+      </c>
+      <c r="K104" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="L104" t="str">
+        <v>Male // Nam</v>
+      </c>
+      <c r="M104" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="N104" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O104" t="str">
+        <v>0</v>
+      </c>
+      <c r="P104" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q104" t="str">
+        <v>0</v>
+      </c>
+      <c r="R104" t="str">
+        <v>0</v>
+      </c>
+      <c r="S104" t="str">
+        <v>0</v>
+      </c>
+      <c r="T104" t="str">
+        <v>0</v>
+      </c>
+      <c r="U104" t="str">
+        <v>4</v>
+      </c>
+      <c r="V104" t="str">
+        <v>0</v>
+      </c>
+      <c r="W104" t="str">
+        <v>3</v>
+      </c>
+      <c r="X104" t="str">
+        <v>4/10/26</v>
+      </c>
+      <c r="Y104" t="str">
+        <v>7/14/26</v>
+      </c>
+      <c r="Z104" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="AB104" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="AD104" t="str">
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="str">
+        <v>(320)</v>
+      </c>
+      <c r="B105" t="str">
+        <v>(1) Viet Nga Group, (2) Việt Nga Group-HTX DVNN Bình Hiệp B</v>
+      </c>
+      <c r="C105" t="str">
+        <v>73810</v>
+      </c>
+      <c r="D105" t="str">
+        <v>834367845</v>
+      </c>
+      <c r="E105" t="str">
+        <v>HỒ VĂN CÒN</v>
+      </c>
+      <c r="F105" t="str">
+        <v>HỢP TÁC XÃ DỊCH VỤ NÔNG NGHIỆP BÌNH HIỆP B</v>
+      </c>
+      <c r="J105" t="str">
+        <v>Intensive rice production // Trồng lúa thâm canh</v>
+      </c>
+      <c r="K105" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="L105" t="str">
+        <v>Male // Nam</v>
+      </c>
+      <c r="M105" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="N105" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O105" t="str">
+        <v>0</v>
+      </c>
+      <c r="P105" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q105" t="str">
+        <v>0</v>
+      </c>
+      <c r="R105" t="str">
+        <v>0</v>
+      </c>
+      <c r="S105" t="str">
+        <v>0</v>
+      </c>
+      <c r="T105" t="str">
+        <v>0</v>
+      </c>
+      <c r="U105" t="str">
+        <v>5</v>
+      </c>
+      <c r="V105" t="str">
+        <v>0</v>
+      </c>
+      <c r="W105" t="str">
+        <v>4</v>
+      </c>
+      <c r="X105" t="str">
+        <v>4/10/26</v>
+      </c>
+      <c r="Y105" t="str">
+        <v>7/14/26</v>
+      </c>
+      <c r="Z105" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="AB105" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="AD105" t="str">
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="str">
+        <v>(322)</v>
+      </c>
+      <c r="B106" t="str">
+        <v>(1) Viet Nga Group, (2) Việt Nga Group-HTX DVNN Bình Hiệp B</v>
+      </c>
+      <c r="C106" t="str">
+        <v>73812</v>
+      </c>
+      <c r="D106" t="str">
+        <v>374515291</v>
+      </c>
+      <c r="E106" t="str">
+        <v>PHẠM VĂN TIỂNG</v>
+      </c>
+      <c r="F106" t="str">
+        <v>HỢP TÁC XÃ DỊCH VỤ NÔNG NGHIỆP BÌNH HIỆP B</v>
+      </c>
+      <c r="J106" t="str">
+        <v>Intensive rice production // Trồng lúa thâm canh</v>
+      </c>
+      <c r="K106" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="L106" t="str">
+        <v>Male // Nam</v>
+      </c>
+      <c r="M106" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="N106" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O106" t="str">
+        <v>0</v>
+      </c>
+      <c r="P106" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q106" t="str">
+        <v>0</v>
+      </c>
+      <c r="R106" t="str">
+        <v>0</v>
+      </c>
+      <c r="S106" t="str">
+        <v>0</v>
+      </c>
+      <c r="T106" t="str">
+        <v>0</v>
+      </c>
+      <c r="U106" t="str">
+        <v>4</v>
+      </c>
+      <c r="V106" t="str">
+        <v>0</v>
+      </c>
+      <c r="W106" t="str">
+        <v>3</v>
+      </c>
+      <c r="X106" t="str">
+        <v>4/10/26</v>
+      </c>
+      <c r="Y106" t="str">
+        <v>7/14/26</v>
+      </c>
+      <c r="Z106" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="AB106" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="AD106" t="str">
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="str">
+        <v>(324)</v>
+      </c>
+      <c r="B107" t="str">
+        <v>(1) Viet Nga Group, (2) Việt Nga Group-HTX DVNN Bình Hiệp B</v>
+      </c>
+      <c r="C107" t="str">
+        <v>73814</v>
+      </c>
+      <c r="D107" t="str">
+        <v>384965513</v>
+      </c>
+      <c r="E107" t="str">
+        <v>NGUYỄN VĂN BỰC</v>
+      </c>
+      <c r="F107" t="str">
+        <v>HỢP TÁC XÃ DỊCH VỤ NÔNG NGHIỆP BÌNH HIỆP B</v>
+      </c>
+      <c r="J107" t="str">
+        <v>Intensive rice production // Trồng lúa thâm canh</v>
+      </c>
+      <c r="K107" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="L107" t="str">
+        <v>Male // Nam</v>
+      </c>
+      <c r="M107" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="N107" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O107" t="str">
+        <v>0</v>
+      </c>
+      <c r="P107" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q107" t="str">
+        <v>0</v>
+      </c>
+      <c r="R107" t="str">
+        <v>0</v>
+      </c>
+      <c r="S107" t="str">
+        <v>0</v>
+      </c>
+      <c r="T107" t="str">
+        <v>0</v>
+      </c>
+      <c r="U107" t="str">
+        <v>3</v>
+      </c>
+      <c r="V107" t="str">
+        <v>0</v>
+      </c>
+      <c r="W107" t="str">
+        <v>2</v>
+      </c>
+      <c r="X107" t="str">
+        <v>4/10/26</v>
+      </c>
+      <c r="Y107" t="str">
+        <v>7/14/26</v>
+      </c>
+      <c r="Z107" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="AB107" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="AD107" t="str">
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="str">
+        <v>(325)</v>
+      </c>
+      <c r="B108" t="str">
+        <v>(1) Viet Nga Group, (2) Việt Nga Group-HTX DVNN Bình Hiệp B</v>
+      </c>
+      <c r="C108" t="str">
+        <v>73815</v>
+      </c>
+      <c r="D108" t="str">
+        <v>984622189</v>
+      </c>
+      <c r="E108" t="str">
+        <v>NGUYỄN VĂN TÍCH</v>
+      </c>
+      <c r="F108" t="str">
+        <v>HỢP TÁC XÃ DỊCH VỤ NÔNG NGHIỆP BÌNH HIỆP B</v>
+      </c>
+      <c r="J108" t="str">
+        <v>Intensive rice production // Trồng lúa thâm canh</v>
+      </c>
+      <c r="K108" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="L108" t="str">
+        <v>Male // Nam</v>
+      </c>
+      <c r="M108" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="N108" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O108" t="str">
+        <v>0</v>
+      </c>
+      <c r="P108" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q108" t="str">
+        <v>0</v>
+      </c>
+      <c r="R108" t="str">
+        <v>0</v>
+      </c>
+      <c r="S108" t="str">
+        <v>0</v>
+      </c>
+      <c r="T108" t="str">
+        <v>0</v>
+      </c>
+      <c r="U108" t="str">
+        <v>3</v>
+      </c>
+      <c r="V108" t="str">
+        <v>0</v>
+      </c>
+      <c r="W108" t="str">
+        <v>2</v>
+      </c>
+      <c r="X108" t="str">
+        <v>4/10/26</v>
+      </c>
+      <c r="Y108" t="str">
+        <v>7/14/26</v>
+      </c>
+      <c r="Z108" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="AB108" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="AD108" t="str">
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="str">
+        <v>(327)</v>
+      </c>
+      <c r="B109" t="str">
+        <v>(1) Viet Nga Group, (2) Việt Nga Group-HTX DVNN Bình Hiệp B</v>
+      </c>
+      <c r="C109" t="str">
+        <v>73817</v>
+      </c>
+      <c r="D109" t="str">
+        <v>386049296</v>
+      </c>
+      <c r="E109" t="str">
+        <v>NGUYỄN VĂN GÚP</v>
+      </c>
+      <c r="F109" t="str">
+        <v>HỢP TÁC XÃ DỊCH VỤ NÔNG NGHIỆP BÌNH HIỆP B</v>
+      </c>
+      <c r="J109" t="str">
+        <v>Intensive rice production // Trồng lúa thâm canh</v>
+      </c>
+      <c r="K109" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="L109" t="str">
+        <v>Male // Nam</v>
+      </c>
+      <c r="M109" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="N109" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O109" t="str">
+        <v>0</v>
+      </c>
+      <c r="P109" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q109" t="str">
+        <v>0</v>
+      </c>
+      <c r="R109" t="str">
+        <v>0</v>
+      </c>
+      <c r="S109" t="str">
+        <v>0</v>
+      </c>
+      <c r="T109" t="str">
+        <v>0</v>
+      </c>
+      <c r="U109" t="str">
+        <v>5</v>
+      </c>
+      <c r="V109" t="str">
+        <v>0</v>
+      </c>
+      <c r="W109" t="str">
+        <v>4</v>
+      </c>
+      <c r="X109" t="str">
+        <v>4/10/26</v>
+      </c>
+      <c r="Y109" t="str">
+        <v>7/14/26</v>
+      </c>
+      <c r="Z109" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="AB109" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="AD109" t="str">
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="str">
+        <v>(328)</v>
+      </c>
+      <c r="B110" t="str">
+        <v>(1) Viet Nga Group, (2) Việt Nga Group-HTX DVNN Bình Hiệp B</v>
+      </c>
+      <c r="C110" t="str">
+        <v>73818</v>
+      </c>
+      <c r="D110" t="str">
+        <v>939250405</v>
+      </c>
+      <c r="E110" t="str">
+        <v>NGUYỄN THANH TUẤN</v>
+      </c>
+      <c r="F110" t="str">
+        <v>HỢP TÁC XÃ DỊCH VỤ NÔNG NGHIỆP BÌNH HIỆP B</v>
+      </c>
+      <c r="J110" t="str">
+        <v>Intensive rice production // Trồng lúa thâm canh</v>
+      </c>
+      <c r="K110" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="L110" t="str">
+        <v>Male // Nam</v>
+      </c>
+      <c r="M110" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="N110" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O110" t="str">
+        <v>0</v>
+      </c>
+      <c r="P110" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q110" t="str">
+        <v>0</v>
+      </c>
+      <c r="R110" t="str">
+        <v>0</v>
+      </c>
+      <c r="S110" t="str">
+        <v>0</v>
+      </c>
+      <c r="T110" t="str">
+        <v>0</v>
+      </c>
+      <c r="U110" t="str">
+        <v>4</v>
+      </c>
+      <c r="V110" t="str">
+        <v>0</v>
+      </c>
+      <c r="W110" t="str">
+        <v>3</v>
+      </c>
+      <c r="X110" t="str">
+        <v>4/10/26</v>
+      </c>
+      <c r="Y110" t="str">
+        <v>7/14/26</v>
+      </c>
+      <c r="Z110" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="AB110" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="AD110" t="str">
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="str">
+        <v>(331)</v>
+      </c>
+      <c r="B111" t="str">
+        <v>(1) Viet Nga Group, (2) Việt Nga Group-HTX DVNN Bình Hiệp B</v>
+      </c>
+      <c r="C111" t="str">
+        <v>73821</v>
+      </c>
+      <c r="D111" t="str">
+        <v>386658846</v>
+      </c>
+      <c r="E111" t="str">
+        <v>LƯƠNG TẤN XUÂN</v>
+      </c>
+      <c r="F111" t="str">
+        <v>HỢP TÁC XÃ DỊCH VỤ NÔNG NGHIỆP BÌNH HIỆP B</v>
+      </c>
+      <c r="J111" t="str">
+        <v>Intensive rice production // Trồng lúa thâm canh</v>
+      </c>
+      <c r="K111" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="L111" t="str">
+        <v>Male // Nam</v>
+      </c>
+      <c r="M111" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="N111" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O111" t="str">
+        <v>0</v>
+      </c>
+      <c r="P111" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q111" t="str">
+        <v>0</v>
+      </c>
+      <c r="R111" t="str">
+        <v>0</v>
+      </c>
+      <c r="S111" t="str">
+        <v>0</v>
+      </c>
+      <c r="T111" t="str">
+        <v>0</v>
+      </c>
+      <c r="U111" t="str">
+        <v>3</v>
+      </c>
+      <c r="V111" t="str">
+        <v>0</v>
+      </c>
+      <c r="W111" t="str">
+        <v>2</v>
+      </c>
+      <c r="X111" t="str">
+        <v>4/10/26</v>
+      </c>
+      <c r="Y111" t="str">
+        <v>7/14/26</v>
+      </c>
+      <c r="Z111" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="AB111" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="AD111" t="str">
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="str">
+        <v>(333)</v>
+      </c>
+      <c r="B112" t="str">
+        <v>(1) Viet Nga Group, (2) Việt Nga Group-HTX DVNN Bình Hiệp B</v>
+      </c>
+      <c r="C112" t="str">
+        <v>73823</v>
+      </c>
+      <c r="D112" t="str">
+        <v>336348881</v>
+      </c>
+      <c r="E112" t="str">
+        <v>ĐOÀN VĂN HAI</v>
+      </c>
+      <c r="F112" t="str">
+        <v>HỢP TÁC XÃ DỊCH VỤ NÔNG NGHIỆP BÌNH HIỆP B</v>
+      </c>
+      <c r="J112" t="str">
+        <v>Intensive rice production // Trồng lúa thâm canh</v>
+      </c>
+      <c r="K112" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="L112" t="str">
+        <v>Male // Nam</v>
+      </c>
+      <c r="M112" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="N112" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O112" t="str">
+        <v>0</v>
+      </c>
+      <c r="P112" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q112" t="str">
+        <v>0</v>
+      </c>
+      <c r="R112" t="str">
+        <v>0</v>
+      </c>
+      <c r="S112" t="str">
+        <v>0</v>
+      </c>
+      <c r="T112" t="str">
+        <v>0</v>
+      </c>
+      <c r="U112" t="str">
+        <v>3</v>
+      </c>
+      <c r="V112" t="str">
+        <v>0</v>
+      </c>
+      <c r="W112" t="str">
+        <v>2</v>
+      </c>
+      <c r="X112" t="str">
+        <v>4/10/26</v>
+      </c>
+      <c r="Y112" t="str">
+        <v>7/14/26</v>
+      </c>
+      <c r="Z112" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="AB112" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="AD112" t="str">
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="str">
+        <v>(334)</v>
+      </c>
+      <c r="B113" t="str">
+        <v>(1) Viet Nga Group, (2) Việt Nga Group-HTX DVNN Bình Hiệp B</v>
+      </c>
+      <c r="C113" t="str">
+        <v>73824</v>
+      </c>
+      <c r="D113" t="str">
+        <v>388218751</v>
+      </c>
+      <c r="E113" t="str">
+        <v>NGUYỄN VĂN LẮM</v>
+      </c>
+      <c r="F113" t="str">
+        <v>HỢP TÁC XÃ DỊCH VỤ NÔNG NGHIỆP BÌNH HIỆP B</v>
+      </c>
+      <c r="J113" t="str">
+        <v>Intensive rice production // Trồng lúa thâm canh</v>
+      </c>
+      <c r="K113" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="L113" t="str">
+        <v>Male // Nam</v>
+      </c>
+      <c r="M113" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="N113" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O113" t="str">
+        <v>0</v>
+      </c>
+      <c r="P113" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q113" t="str">
+        <v>0</v>
+      </c>
+      <c r="R113" t="str">
+        <v>0</v>
+      </c>
+      <c r="S113" t="str">
+        <v>0</v>
+      </c>
+      <c r="T113" t="str">
+        <v>0</v>
+      </c>
+      <c r="U113" t="str">
+        <v>4</v>
+      </c>
+      <c r="V113" t="str">
+        <v>0</v>
+      </c>
+      <c r="W113" t="str">
+        <v>2</v>
+      </c>
+      <c r="X113" t="str">
+        <v>4/10/26</v>
+      </c>
+      <c r="Y113" t="str">
+        <v>7/14/26</v>
+      </c>
+      <c r="Z113" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="AB113" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="AD113" t="str">
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="str">
+        <v>(335)</v>
+      </c>
+      <c r="B114" t="str">
+        <v>(1) Viet Nga Group, (2) Việt Nga Group-HTX DVNN Bình Hiệp B</v>
+      </c>
+      <c r="C114" t="str">
+        <v>73825</v>
+      </c>
+      <c r="D114" t="str">
+        <v>919320157</v>
+      </c>
+      <c r="E114" t="str">
+        <v>NGUYỄN HỮU ĐỨC</v>
+      </c>
+      <c r="F114" t="str">
+        <v>HỢP TÁC XÃ DỊCH VỤ NÔNG NGHIỆP BÌNH HIỆP B</v>
+      </c>
+      <c r="J114" t="str">
+        <v>Intensive rice production // Trồng lúa thâm canh</v>
+      </c>
+      <c r="K114" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="L114" t="str">
+        <v>Male // Nam</v>
+      </c>
+      <c r="M114" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="N114" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O114" t="str">
+        <v>0</v>
+      </c>
+      <c r="P114" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q114" t="str">
+        <v>0</v>
+      </c>
+      <c r="R114" t="str">
+        <v>0</v>
+      </c>
+      <c r="S114" t="str">
+        <v>0</v>
+      </c>
+      <c r="T114" t="str">
+        <v>0</v>
+      </c>
+      <c r="U114" t="str">
+        <v>4</v>
+      </c>
+      <c r="V114" t="str">
+        <v>0</v>
+      </c>
+      <c r="W114" t="str">
+        <v>3</v>
+      </c>
+      <c r="X114" t="str">
+        <v>4/10/26</v>
+      </c>
+      <c r="Y114" t="str">
+        <v>7/14/26</v>
+      </c>
+      <c r="Z114" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="AB114" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="AD114" t="str">
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="str">
+        <v>(336)</v>
+      </c>
+      <c r="B115" t="str">
+        <v>(1) Viet Nga Group, (2) Việt Nga Group-HTX DVNN Bình Hiệp B</v>
+      </c>
+      <c r="C115" t="str">
+        <v>73826</v>
+      </c>
+      <c r="D115" t="str">
+        <v>919705659</v>
+      </c>
+      <c r="E115" t="str">
+        <v>LÊ VĂN ÚT</v>
+      </c>
+      <c r="F115" t="str">
+        <v>HỢP TÁC XÃ DỊCH VỤ NÔNG NGHIỆP BÌNH HIỆP B</v>
+      </c>
+      <c r="J115" t="str">
+        <v>Intensive rice production // Trồng lúa thâm canh</v>
+      </c>
+      <c r="K115" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="L115" t="str">
+        <v>Male // Nam</v>
+      </c>
+      <c r="M115" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="N115" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O115" t="str">
+        <v>0</v>
+      </c>
+      <c r="P115" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q115" t="str">
+        <v>0</v>
+      </c>
+      <c r="R115" t="str">
+        <v>0</v>
+      </c>
+      <c r="S115" t="str">
+        <v>0</v>
+      </c>
+      <c r="T115" t="str">
+        <v>0</v>
+      </c>
+      <c r="U115" t="str">
+        <v>4</v>
+      </c>
+      <c r="V115" t="str">
+        <v>0</v>
+      </c>
+      <c r="W115" t="str">
+        <v>3</v>
+      </c>
+      <c r="X115" t="str">
+        <v>4/10/26</v>
+      </c>
+      <c r="Y115" t="str">
+        <v>7/14/26</v>
+      </c>
+      <c r="Z115" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="AB115" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="AD115" t="str">
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="str">
+        <v>(337)</v>
+      </c>
+      <c r="B116" t="str">
+        <v>(1) Viet Nga Group, (2) Việt Nga Group-HTX DVNN Bình Hiệp B</v>
+      </c>
+      <c r="C116" t="str">
+        <v>73827</v>
+      </c>
+      <c r="D116" t="str">
+        <v>372108598</v>
+      </c>
+      <c r="E116" t="str">
+        <v>NGUYỄN VĂN ÚT</v>
+      </c>
+      <c r="F116" t="str">
+        <v>HỢP TÁC XÃ DỊCH VỤ NÔNG NGHIỆP BÌNH HIỆP B</v>
+      </c>
+      <c r="J116" t="str">
+        <v>Intensive rice production // Trồng lúa thâm canh</v>
+      </c>
+      <c r="K116" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="L116" t="str">
+        <v>Male // Nam</v>
+      </c>
+      <c r="M116" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="N116" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O116" t="str">
+        <v>0</v>
+      </c>
+      <c r="P116" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q116" t="str">
+        <v>0</v>
+      </c>
+      <c r="R116" t="str">
+        <v>0</v>
+      </c>
+      <c r="S116" t="str">
+        <v>0</v>
+      </c>
+      <c r="T116" t="str">
+        <v>0</v>
+      </c>
+      <c r="U116" t="str">
+        <v>4</v>
+      </c>
+      <c r="V116" t="str">
+        <v>0</v>
+      </c>
+      <c r="W116" t="str">
+        <v>3</v>
+      </c>
+      <c r="X116" t="str">
+        <v>4/10/26</v>
+      </c>
+      <c r="Y116" t="str">
+        <v>7/14/26</v>
+      </c>
+      <c r="Z116" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="AB116" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="AD116" t="str">
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="str">
+        <v>(338)</v>
+      </c>
+      <c r="B117" t="str">
+        <v>(1) Viet Nga Group, (2) Việt Nga Group-HTX DVNN Bình Hiệp B</v>
+      </c>
+      <c r="C117" t="str">
+        <v>73828</v>
+      </c>
+      <c r="D117" t="str">
+        <v>783858306</v>
+      </c>
+      <c r="E117" t="str">
+        <v>HOÀNG HOA THÁM</v>
+      </c>
+      <c r="F117" t="str">
+        <v>HỢP TÁC XÃ DỊCH VỤ NÔNG NGHIỆP BÌNH HIỆP B</v>
+      </c>
+      <c r="J117" t="str">
+        <v>Intensive rice production // Trồng lúa thâm canh</v>
+      </c>
+      <c r="K117" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="L117" t="str">
+        <v>Male // Nam</v>
+      </c>
+      <c r="M117" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="N117" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O117" t="str">
+        <v>0</v>
+      </c>
+      <c r="P117" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q117" t="str">
+        <v>0</v>
+      </c>
+      <c r="R117" t="str">
+        <v>0</v>
+      </c>
+      <c r="S117" t="str">
+        <v>0</v>
+      </c>
+      <c r="T117" t="str">
+        <v>0</v>
+      </c>
+      <c r="U117" t="str">
+        <v>4</v>
+      </c>
+      <c r="V117" t="str">
+        <v>0</v>
+      </c>
+      <c r="W117" t="str">
+        <v>3</v>
+      </c>
+      <c r="X117" t="str">
+        <v>4/10/26</v>
+      </c>
+      <c r="Y117" t="str">
+        <v>7/14/26</v>
+      </c>
+      <c r="Z117" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="AB117" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="AD117" t="str">
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="str">
+        <v>(339)</v>
+      </c>
+      <c r="B118" t="str">
+        <v>(1) Viet Nga Group, (2) Việt Nga Group-HTX DVNN Bình Hiệp B</v>
+      </c>
+      <c r="C118" t="str">
+        <v>73829</v>
+      </c>
+      <c r="D118" t="str">
+        <v>329301571</v>
+      </c>
+      <c r="E118" t="str">
+        <v>ĐOÀN TẤN VÂN</v>
+      </c>
+      <c r="F118" t="str">
+        <v>HỢP TÁC XÃ DỊCH VỤ NÔNG NGHIỆP BÌNH HIỆP B</v>
+      </c>
+      <c r="J118" t="str">
+        <v>Intensive rice production // Trồng lúa thâm canh</v>
+      </c>
+      <c r="K118" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="L118" t="str">
+        <v>Male // Nam</v>
+      </c>
+      <c r="M118" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="N118" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O118" t="str">
+        <v>0</v>
+      </c>
+      <c r="P118" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q118" t="str">
+        <v>0</v>
+      </c>
+      <c r="R118" t="str">
+        <v>0</v>
+      </c>
+      <c r="S118" t="str">
+        <v>0</v>
+      </c>
+      <c r="T118" t="str">
+        <v>0</v>
+      </c>
+      <c r="U118" t="str">
+        <v>5</v>
+      </c>
+      <c r="V118" t="str">
+        <v>0</v>
+      </c>
+      <c r="W118" t="str">
+        <v>4</v>
+      </c>
+      <c r="X118" t="str">
+        <v>4/10/26</v>
+      </c>
+      <c r="Y118" t="str">
+        <v>7/14/26</v>
+      </c>
+      <c r="Z118" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="AB118" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="AD118" t="str">
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="str">
+        <v>(340)</v>
+      </c>
+      <c r="B119" t="str">
+        <v>(1) Viet Nga Group, (2) Việt Nga Group-HTX DVNN Bình Hiệp B</v>
+      </c>
+      <c r="C119" t="str">
+        <v>74852</v>
+      </c>
+      <c r="D119" t="str">
+        <v>784448070</v>
+      </c>
+      <c r="E119" t="str">
+        <v>LÊ THANH TÙNG</v>
+      </c>
+      <c r="F119" t="str">
+        <v>HỢP TÁC XÃ DỊCH VỤ NÔNG NGHIỆP BÌNH HIỆP B</v>
+      </c>
+      <c r="J119" t="str">
+        <v>Intensive rice production // Trồng lúa thâm canh</v>
+      </c>
+      <c r="K119" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="L119" t="str">
+        <v>Male // Nam</v>
+      </c>
+      <c r="M119" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="N119" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O119" t="str">
+        <v>0</v>
+      </c>
+      <c r="P119" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q119" t="str">
+        <v>0</v>
+      </c>
+      <c r="R119" t="str">
+        <v>0</v>
+      </c>
+      <c r="S119" t="str">
+        <v>0</v>
+      </c>
+      <c r="T119" t="str">
+        <v>0</v>
+      </c>
+      <c r="U119" t="str">
+        <v>3</v>
+      </c>
+      <c r="V119" t="str">
+        <v>0</v>
+      </c>
+      <c r="W119" t="str">
+        <v>2</v>
+      </c>
+      <c r="X119" t="str">
+        <v>4/10/26</v>
+      </c>
+      <c r="Y119" t="str">
+        <v>7/14/26</v>
+      </c>
+      <c r="Z119" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="AB119" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="AD119" t="str">
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="str">
+        <v>(341)</v>
+      </c>
+      <c r="B120" t="str">
+        <v>(1) Viet Nga Group, (2) Việt Nga Group-HTX DVNN Bình Hiệp B</v>
+      </c>
+      <c r="C120" t="str">
+        <v>74853</v>
+      </c>
+      <c r="D120" t="str">
+        <v>939269691</v>
+      </c>
+      <c r="E120" t="str">
+        <v>MAI VĂN SUÔL</v>
+      </c>
+      <c r="F120" t="str">
+        <v>HỢP TÁC XÃ DỊCH VỤ NÔNG NGHIỆP BÌNH HIỆP B</v>
+      </c>
+      <c r="J120" t="str">
+        <v>Intensive rice production // Trồng lúa thâm canh</v>
+      </c>
+      <c r="K120" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="L120" t="str">
+        <v>Male // Nam</v>
+      </c>
+      <c r="M120" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="N120" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O120" t="str">
+        <v>0</v>
+      </c>
+      <c r="P120" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q120" t="str">
+        <v>0</v>
+      </c>
+      <c r="R120" t="str">
+        <v>0</v>
+      </c>
+      <c r="S120" t="str">
+        <v>0</v>
+      </c>
+      <c r="T120" t="str">
+        <v>0</v>
+      </c>
+      <c r="U120" t="str">
+        <v>4</v>
+      </c>
+      <c r="V120" t="str">
+        <v>0</v>
+      </c>
+      <c r="W120" t="str">
+        <v>3</v>
+      </c>
+      <c r="X120" t="str">
+        <v>4/10/26</v>
+      </c>
+      <c r="Y120" t="str">
+        <v>7/14/26</v>
+      </c>
+      <c r="Z120" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="AB120" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="AD120" t="str">
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="str">
+        <v>(342)</v>
+      </c>
+      <c r="B121" t="str">
+        <v>(1) Viet Nga Group, (2) Việt Nga Group-HTX DVNN Bình Hiệp B</v>
+      </c>
+      <c r="C121" t="str">
+        <v>74854</v>
+      </c>
+      <c r="D121" t="str">
+        <v>326466713</v>
+      </c>
+      <c r="E121" t="str">
+        <v>HUỲNH VĂN DỰA</v>
+      </c>
+      <c r="F121" t="str">
+        <v>HỢP TÁC XÃ DỊCH VỤ NÔNG NGHIỆP BÌNH HIỆP B</v>
+      </c>
+      <c r="J121" t="str">
+        <v>Intensive rice production // Trồng lúa thâm canh</v>
+      </c>
+      <c r="K121" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="L121" t="str">
+        <v>Male // Nam</v>
+      </c>
+      <c r="M121" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="N121" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O121" t="str">
+        <v>0</v>
+      </c>
+      <c r="P121" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q121" t="str">
+        <v>0</v>
+      </c>
+      <c r="R121" t="str">
+        <v>0</v>
+      </c>
+      <c r="S121" t="str">
+        <v>0</v>
+      </c>
+      <c r="T121" t="str">
+        <v>0</v>
+      </c>
+      <c r="U121" t="str">
+        <v>3</v>
+      </c>
+      <c r="V121" t="str">
+        <v>0</v>
+      </c>
+      <c r="W121" t="str">
+        <v>2</v>
+      </c>
+      <c r="X121" t="str">
+        <v>4/10/26</v>
+      </c>
+      <c r="Y121" t="str">
+        <v>7/14/26</v>
+      </c>
+      <c r="Z121" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="AB121" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="AD121" t="str">
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="str">
+        <v>(344)</v>
+      </c>
+      <c r="B122" t="str">
+        <v>(1) Viet Nga Group, (2) Việt Nga Group-HTX DVNN Bình Hiệp B</v>
+      </c>
+      <c r="C122" t="str">
+        <v>74856</v>
+      </c>
+      <c r="D122" t="str">
+        <v>939308990</v>
+      </c>
+      <c r="E122" t="str">
+        <v>LÊ THANH DƯƠNG</v>
+      </c>
+      <c r="F122" t="str">
+        <v>HỢP TÁC XÃ DỊCH VỤ NÔNG NGHIỆP BÌNH HIỆP B</v>
+      </c>
+      <c r="J122" t="str">
+        <v>Intensive rice production // Trồng lúa thâm canh</v>
+      </c>
+      <c r="K122" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="L122" t="str">
+        <v>Male // Nam</v>
+      </c>
+      <c r="M122" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="N122" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O122" t="str">
+        <v>0</v>
+      </c>
+      <c r="P122" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q122" t="str">
+        <v>0</v>
+      </c>
+      <c r="R122" t="str">
+        <v>0</v>
+      </c>
+      <c r="S122" t="str">
+        <v>0</v>
+      </c>
+      <c r="T122" t="str">
+        <v>0</v>
+      </c>
+      <c r="U122" t="str">
+        <v>4</v>
+      </c>
+      <c r="V122" t="str">
+        <v>0</v>
+      </c>
+      <c r="W122" t="str">
+        <v>3</v>
+      </c>
+      <c r="X122" t="str">
+        <v>4/10/26</v>
+      </c>
+      <c r="Y122" t="str">
+        <v>7/14/26</v>
+      </c>
+      <c r="Z122" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="AB122" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="AD122" t="str">
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="str">
+        <v>(345)</v>
+      </c>
+      <c r="B123" t="str">
+        <v>(1) Viet Nga Group, (2) Việt Nga Group-HTX DVNN Bình Hiệp B</v>
+      </c>
+      <c r="C123" t="str">
+        <v>74857</v>
+      </c>
+      <c r="D123" t="str">
+        <v>398161268</v>
+      </c>
+      <c r="E123" t="str">
+        <v>NGÔ VĂN NGHIÊM</v>
+      </c>
+      <c r="F123" t="str">
+        <v>HỢP TÁC XÃ DỊCH VỤ NÔNG NGHIỆP BÌNH HIỆP B</v>
+      </c>
+      <c r="J123" t="str">
+        <v>Intensive rice production // Trồng lúa thâm canh</v>
+      </c>
+      <c r="K123" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="L123" t="str">
+        <v>Male // Nam</v>
+      </c>
+      <c r="M123" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="N123" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O123" t="str">
+        <v>0</v>
+      </c>
+      <c r="P123" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q123" t="str">
+        <v>0</v>
+      </c>
+      <c r="R123" t="str">
+        <v>0</v>
+      </c>
+      <c r="S123" t="str">
+        <v>0</v>
+      </c>
+      <c r="T123" t="str">
+        <v>0</v>
+      </c>
+      <c r="U123" t="str">
+        <v>3</v>
+      </c>
+      <c r="V123" t="str">
+        <v>0</v>
+      </c>
+      <c r="W123" t="str">
+        <v>2</v>
+      </c>
+      <c r="X123" t="str">
+        <v>4/10/26</v>
+      </c>
+      <c r="Y123" t="str">
+        <v>7/14/26</v>
+      </c>
+      <c r="Z123" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="AB123" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="AD123" t="str">
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="str">
+        <v>(346)</v>
+      </c>
+      <c r="B124" t="str">
+        <v>(1) Viet Nga Group, (2) Việt Nga Group-HTX DVNN Bình Hiệp B</v>
+      </c>
+      <c r="C124" t="str">
+        <v>74858</v>
+      </c>
+      <c r="D124" t="str">
+        <v>975990998</v>
+      </c>
+      <c r="E124" t="str">
+        <v>TRẦN PHƯỚC KHANG</v>
+      </c>
+      <c r="F124" t="str">
+        <v>HỢP TÁC XÃ DỊCH VỤ NÔNG NGHIỆP BÌNH HIỆP B</v>
+      </c>
+      <c r="J124" t="str">
+        <v>Intensive rice production // Trồng lúa thâm canh</v>
+      </c>
+      <c r="K124" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="L124" t="str">
+        <v>Male // Nam</v>
+      </c>
+      <c r="M124" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="N124" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O124" t="str">
+        <v>0</v>
+      </c>
+      <c r="P124" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q124" t="str">
+        <v>0</v>
+      </c>
+      <c r="R124" t="str">
+        <v>0</v>
+      </c>
+      <c r="S124" t="str">
+        <v>0</v>
+      </c>
+      <c r="T124" t="str">
+        <v>0</v>
+      </c>
+      <c r="U124" t="str">
+        <v>4</v>
+      </c>
+      <c r="V124" t="str">
+        <v>0</v>
+      </c>
+      <c r="W124" t="str">
+        <v>3</v>
+      </c>
+      <c r="X124" t="str">
+        <v>4/10/26</v>
+      </c>
+      <c r="Y124" t="str">
+        <v>7/14/26</v>
+      </c>
+      <c r="Z124" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="AB124" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="AD124" t="str">
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="str">
+        <v>(349)</v>
+      </c>
+      <c r="B125" t="str">
+        <v>(1) Viet Nga Group, (2) Việt Nga Group-HTX DVNN Bình Hiệp B</v>
+      </c>
+      <c r="C125" t="str">
+        <v>74861</v>
+      </c>
+      <c r="D125" t="str">
+        <v>919429426</v>
+      </c>
+      <c r="E125" t="str">
+        <v>NGUYỄN VĂN LÀ</v>
+      </c>
+      <c r="F125" t="str">
+        <v>HỢP TÁC XÃ DỊCH VỤ NÔNG NGHIỆP BÌNH HIỆP B</v>
+      </c>
+      <c r="J125" t="str">
+        <v>Intensive rice production // Trồng lúa thâm canh</v>
+      </c>
+      <c r="K125" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="L125" t="str">
+        <v>Male // Nam</v>
+      </c>
+      <c r="M125" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="N125" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O125" t="str">
+        <v>0</v>
+      </c>
+      <c r="P125" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q125" t="str">
+        <v>0</v>
+      </c>
+      <c r="R125" t="str">
+        <v>0</v>
+      </c>
+      <c r="S125" t="str">
+        <v>0</v>
+      </c>
+      <c r="T125" t="str">
+        <v>0</v>
+      </c>
+      <c r="U125" t="str">
+        <v>4</v>
+      </c>
+      <c r="V125" t="str">
+        <v>0</v>
+      </c>
+      <c r="W125" t="str">
+        <v>3</v>
+      </c>
+      <c r="X125" t="str">
+        <v>4/10/26</v>
+      </c>
+      <c r="Y125" t="str">
+        <v>7/14/26</v>
+      </c>
+      <c r="Z125" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="AB125" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="AD125" t="str">
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="str">
+        <v>(350)</v>
+      </c>
+      <c r="B126" t="str">
+        <v>(1) Viet Nga Group, (2) Việt Nga Group-HTX DVNN Bình Hiệp B</v>
+      </c>
+      <c r="C126" t="str">
+        <v>74862</v>
+      </c>
+      <c r="D126" t="str">
+        <v>704971727</v>
+      </c>
+      <c r="E126" t="str">
+        <v>NGUYỄN THANH SƠN</v>
+      </c>
+      <c r="F126" t="str">
+        <v>HỢP TÁC XÃ DỊCH VỤ NÔNG NGHIỆP BÌNH HIỆP B</v>
+      </c>
+      <c r="J126" t="str">
+        <v>Intensive rice production // Trồng lúa thâm canh</v>
+      </c>
+      <c r="K126" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="L126" t="str">
+        <v>Male // Nam</v>
+      </c>
+      <c r="M126" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="N126" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O126" t="str">
+        <v>0</v>
+      </c>
+      <c r="P126" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q126" t="str">
+        <v>0</v>
+      </c>
+      <c r="R126" t="str">
+        <v>0</v>
+      </c>
+      <c r="S126" t="str">
+        <v>0</v>
+      </c>
+      <c r="T126" t="str">
+        <v>0</v>
+      </c>
+      <c r="U126" t="str">
+        <v>3</v>
+      </c>
+      <c r="V126" t="str">
+        <v>0</v>
+      </c>
+      <c r="W126" t="str">
+        <v>2</v>
+      </c>
+      <c r="X126" t="str">
+        <v>4/10/26</v>
+      </c>
+      <c r="Y126" t="str">
+        <v>7/14/26</v>
+      </c>
+      <c r="Z126" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="AB126" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="AD126" t="str">
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="str">
+        <v>(351)</v>
+      </c>
+      <c r="B127" t="str">
+        <v>(1) Viet Nga Group, (2) Việt Nga Group-HTX DVNN Bình Hiệp B</v>
+      </c>
+      <c r="C127" t="str">
+        <v>74863</v>
+      </c>
+      <c r="D127" t="str">
+        <v>772176771</v>
+      </c>
+      <c r="E127" t="str">
+        <v>TỪ VĂN LIẾP</v>
+      </c>
+      <c r="F127" t="str">
+        <v>HỢP TÁC XÃ DỊCH VỤ NÔNG NGHIỆP BÌNH HIỆP B</v>
+      </c>
+      <c r="J127" t="str">
+        <v>Intensive rice production // Trồng lúa thâm canh</v>
+      </c>
+      <c r="K127" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="L127" t="str">
+        <v>Male // Nam</v>
+      </c>
+      <c r="M127" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="N127" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O127" t="str">
+        <v>0</v>
+      </c>
+      <c r="P127" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q127" t="str">
+        <v>0</v>
+      </c>
+      <c r="R127" t="str">
+        <v>0</v>
+      </c>
+      <c r="S127" t="str">
+        <v>0</v>
+      </c>
+      <c r="T127" t="str">
+        <v>0</v>
+      </c>
+      <c r="U127" t="str">
+        <v>3</v>
+      </c>
+      <c r="V127" t="str">
+        <v>0</v>
+      </c>
+      <c r="W127" t="str">
+        <v>2</v>
+      </c>
+      <c r="X127" t="str">
+        <v>4/10/26</v>
+      </c>
+      <c r="Y127" t="str">
+        <v>7/14/26</v>
+      </c>
+      <c r="Z127" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="AB127" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="AD127" t="str">
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="str">
+        <v>(352)</v>
+      </c>
+      <c r="B128" t="str">
+        <v>(1) Viet Nga Group, (2) Việt Nga Group-HTX DVNN Bình Hiệp B</v>
+      </c>
+      <c r="C128" t="str">
+        <v>74864</v>
+      </c>
+      <c r="D128" t="str">
+        <v>355126008</v>
+      </c>
+      <c r="E128" t="str">
+        <v>VÕ THANH VŨ</v>
+      </c>
+      <c r="F128" t="str">
+        <v>HỢP TÁC XÃ DỊCH VỤ NÔNG NGHIỆP BÌNH HIỆP B</v>
+      </c>
+      <c r="J128" t="str">
+        <v>Intensive rice production // Trồng lúa thâm canh</v>
+      </c>
+      <c r="K128" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="L128" t="str">
+        <v>Male // Nam</v>
+      </c>
+      <c r="M128" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="N128" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O128" t="str">
+        <v>0</v>
+      </c>
+      <c r="P128" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q128" t="str">
+        <v>0</v>
+      </c>
+      <c r="R128" t="str">
+        <v>0</v>
+      </c>
+      <c r="S128" t="str">
+        <v>0</v>
+      </c>
+      <c r="T128" t="str">
+        <v>0</v>
+      </c>
+      <c r="U128" t="str">
+        <v>3</v>
+      </c>
+      <c r="V128" t="str">
+        <v>0</v>
+      </c>
+      <c r="W128" t="str">
+        <v>2</v>
+      </c>
+      <c r="X128" t="str">
+        <v>4/10/26</v>
+      </c>
+      <c r="Y128" t="str">
+        <v>7/14/26</v>
+      </c>
+      <c r="Z128" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="AB128" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="AD128" t="str">
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="str">
+        <v>(353)</v>
+      </c>
+      <c r="B129" t="str">
+        <v>(1) Viet Nga Group, (2) Việt Nga Group-HTX DVNN Bình Hiệp B</v>
+      </c>
+      <c r="C129" t="str">
+        <v>74865</v>
+      </c>
+      <c r="D129" t="str">
+        <v>795865683</v>
+      </c>
+      <c r="E129" t="str">
+        <v>TRƯƠNG THANH BÌNH</v>
+      </c>
+      <c r="F129" t="str">
+        <v>HỢP TÁC XÃ DỊCH VỤ NÔNG NGHIỆP BÌNH HIỆP B</v>
+      </c>
+      <c r="J129" t="str">
+        <v>Intensive rice production // Trồng lúa thâm canh</v>
+      </c>
+      <c r="K129" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="L129" t="str">
+        <v>Male // Nam</v>
+      </c>
+      <c r="M129" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="N129" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O129" t="str">
+        <v>0</v>
+      </c>
+      <c r="P129" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q129" t="str">
+        <v>0</v>
+      </c>
+      <c r="R129" t="str">
+        <v>0</v>
+      </c>
+      <c r="S129" t="str">
+        <v>0</v>
+      </c>
+      <c r="T129" t="str">
+        <v>0</v>
+      </c>
+      <c r="U129" t="str">
+        <v>4</v>
+      </c>
+      <c r="V129" t="str">
+        <v>0</v>
+      </c>
+      <c r="W129" t="str">
+        <v>3</v>
+      </c>
+      <c r="X129" t="str">
+        <v>4/10/26</v>
+      </c>
+      <c r="Y129" t="str">
+        <v>7/14/26</v>
+      </c>
+      <c r="Z129" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="AB129" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="AD129" t="str">
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="str">
+        <v>(355)</v>
+      </c>
+      <c r="B130" t="str">
+        <v>(1) Viet Nga Group, (2) Việt Nga Group-HTX DVNN Bình Hiệp B</v>
+      </c>
+      <c r="C130" t="str">
+        <v>74867</v>
+      </c>
+      <c r="D130" t="str">
+        <v>939898955</v>
+      </c>
+      <c r="E130" t="str">
+        <v>TRẦN VĂN MỐC</v>
+      </c>
+      <c r="F130" t="str">
+        <v>HỢP TÁC XÃ DỊCH VỤ NÔNG NGHIỆP BÌNH HIỆP B</v>
+      </c>
+      <c r="J130" t="str">
+        <v>Intensive rice production // Trồng lúa thâm canh</v>
+      </c>
+      <c r="K130" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="L130" t="str">
+        <v>Male // Nam</v>
+      </c>
+      <c r="M130" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="N130" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O130" t="str">
+        <v>0</v>
+      </c>
+      <c r="P130" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q130" t="str">
+        <v>0</v>
+      </c>
+      <c r="R130" t="str">
+        <v>0</v>
+      </c>
+      <c r="S130" t="str">
+        <v>0</v>
+      </c>
+      <c r="T130" t="str">
+        <v>0</v>
+      </c>
+      <c r="U130" t="str">
+        <v>3</v>
+      </c>
+      <c r="V130" t="str">
+        <v>0</v>
+      </c>
+      <c r="W130" t="str">
+        <v>2</v>
+      </c>
+      <c r="X130" t="str">
+        <v>4/10/26</v>
+      </c>
+      <c r="Y130" t="str">
+        <v>7/14/26</v>
+      </c>
+      <c r="Z130" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="AB130" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="AD130" t="str">
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="str">
+        <v>(358)</v>
+      </c>
+      <c r="B131" t="str">
+        <v>(1) Viet Nga Group, (2) Việt Nga Group-HTX DVNN Bình Hiệp B</v>
+      </c>
+      <c r="C131" t="str">
+        <v>74870</v>
+      </c>
+      <c r="D131" t="str">
+        <v>397478550</v>
+      </c>
+      <c r="E131" t="str">
+        <v>NGUYỄN THANH TUẤN</v>
+      </c>
+      <c r="F131" t="str">
+        <v>HỢP TÁC XÃ DỊCH VỤ NÔNG NGHIỆP BÌNH HIỆP B</v>
+      </c>
+      <c r="J131" t="str">
+        <v>Intensive rice production // Trồng lúa thâm canh</v>
+      </c>
+      <c r="K131" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="L131" t="str">
+        <v>Male // Nam</v>
+      </c>
+      <c r="M131" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="N131" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O131" t="str">
+        <v>0</v>
+      </c>
+      <c r="P131" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q131" t="str">
+        <v>0</v>
+      </c>
+      <c r="R131" t="str">
+        <v>0</v>
+      </c>
+      <c r="S131" t="str">
+        <v>0</v>
+      </c>
+      <c r="T131" t="str">
+        <v>0</v>
+      </c>
+      <c r="U131" t="str">
+        <v>3</v>
+      </c>
+      <c r="V131" t="str">
+        <v>0</v>
+      </c>
+      <c r="W131" t="str">
+        <v>2</v>
+      </c>
+      <c r="X131" t="str">
+        <v>4/10/26</v>
+      </c>
+      <c r="Y131" t="str">
+        <v>7/14/26</v>
+      </c>
+      <c r="Z131" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="AB131" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="AD131" t="str">
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="str">
+        <v>(359)</v>
+      </c>
+      <c r="B132" t="str">
+        <v>(1) Viet Nga Group, (2) Việt Nga Group-HTX DVNN Bình Hiệp B</v>
+      </c>
+      <c r="C132" t="str">
+        <v>74871</v>
+      </c>
+      <c r="D132" t="str">
+        <v>362126594</v>
+      </c>
+      <c r="E132" t="str">
+        <v>HỒ VĂN ÚT</v>
+      </c>
+      <c r="F132" t="str">
+        <v>HỢP TÁC XÃ DỊCH VỤ NÔNG NGHIỆP BÌNH HIỆP B</v>
+      </c>
+      <c r="J132" t="str">
+        <v>Intensive rice production // Trồng lúa thâm canh</v>
+      </c>
+      <c r="K132" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="L132" t="str">
+        <v>Male // Nam</v>
+      </c>
+      <c r="M132" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="N132" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O132" t="str">
+        <v>0</v>
+      </c>
+      <c r="P132" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q132" t="str">
+        <v>0</v>
+      </c>
+      <c r="R132" t="str">
+        <v>0</v>
+      </c>
+      <c r="S132" t="str">
+        <v>0</v>
+      </c>
+      <c r="T132" t="str">
+        <v>0</v>
+      </c>
+      <c r="U132" t="str">
+        <v>3</v>
+      </c>
+      <c r="V132" t="str">
+        <v>0</v>
+      </c>
+      <c r="W132" t="str">
+        <v>2</v>
+      </c>
+      <c r="X132" t="str">
+        <v>4/10/26</v>
+      </c>
+      <c r="Y132" t="str">
+        <v>7/14/26</v>
+      </c>
+      <c r="Z132" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="AB132" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="AD132" t="str">
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="str">
+        <v>(363)</v>
+      </c>
+      <c r="B133" t="str">
+        <v>(1) Viet Nga Group, (2) Việt Nga Group-HTX DVNN Bình Hiệp B</v>
+      </c>
+      <c r="C133" t="str">
+        <v>74875</v>
+      </c>
+      <c r="D133" t="str">
+        <v>383889900</v>
+      </c>
+      <c r="E133" t="str">
+        <v>TRẦN VĂN HẬU</v>
+      </c>
+      <c r="F133" t="str">
+        <v>HỢP TÁC XÃ DỊCH VỤ NÔNG NGHIỆP BÌNH HIỆP B</v>
+      </c>
+      <c r="J133" t="str">
+        <v>Intensive rice production // Trồng lúa thâm canh</v>
+      </c>
+      <c r="K133" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="L133" t="str">
+        <v>Male // Nam</v>
+      </c>
+      <c r="M133" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="N133" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O133" t="str">
+        <v>0</v>
+      </c>
+      <c r="P133" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q133" t="str">
+        <v>0</v>
+      </c>
+      <c r="R133" t="str">
+        <v>0</v>
+      </c>
+      <c r="S133" t="str">
+        <v>0</v>
+      </c>
+      <c r="T133" t="str">
+        <v>0</v>
+      </c>
+      <c r="U133" t="str">
+        <v>3</v>
+      </c>
+      <c r="V133" t="str">
+        <v>0</v>
+      </c>
+      <c r="W133" t="str">
+        <v>2</v>
+      </c>
+      <c r="X133" t="str">
+        <v>4/10/26</v>
+      </c>
+      <c r="Y133" t="str">
+        <v>7/14/26</v>
+      </c>
+      <c r="Z133" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="AB133" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="AD133" t="str">
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="str">
+        <v>(367)</v>
+      </c>
+      <c r="B134" t="str">
+        <v>(1) Viet Nga Group, (2) Việt Nga Group-HTX DVNN Bình Hiệp B</v>
+      </c>
+      <c r="C134" t="str">
+        <v>74879</v>
+      </c>
+      <c r="D134" t="str">
+        <v>939269451</v>
+      </c>
+      <c r="E134" t="str">
+        <v>TRẦN VĂN BÌNH</v>
+      </c>
+      <c r="F134" t="str">
+        <v>HỢP TÁC XÃ DỊCH VỤ NÔNG NGHIỆP BÌNH HIỆP B</v>
+      </c>
+      <c r="J134" t="str">
+        <v>Intensive rice production // Trồng lúa thâm canh</v>
+      </c>
+      <c r="K134" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="L134" t="str">
+        <v>Male // Nam</v>
+      </c>
+      <c r="M134" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="N134" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O134" t="str">
+        <v>0</v>
+      </c>
+      <c r="P134" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q134" t="str">
+        <v>0</v>
+      </c>
+      <c r="R134" t="str">
+        <v>0</v>
+      </c>
+      <c r="S134" t="str">
+        <v>0</v>
+      </c>
+      <c r="T134" t="str">
+        <v>0</v>
+      </c>
+      <c r="U134" t="str">
+        <v>3</v>
+      </c>
+      <c r="V134" t="str">
+        <v>0</v>
+      </c>
+      <c r="W134" t="str">
+        <v>2</v>
+      </c>
+      <c r="X134" t="str">
+        <v>4/10/26</v>
+      </c>
+      <c r="Y134" t="str">
+        <v>7/14/26</v>
+      </c>
+      <c r="Z134" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="AB134" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="AD134" t="str">
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="str">
+        <v>(372)</v>
+      </c>
+      <c r="B135" t="str">
+        <v>(1) Viet Nga Group, (2) Việt Nga Group-HTX DVNN Bình Hiệp B</v>
+      </c>
+      <c r="C135" t="str">
+        <v>74883</v>
+      </c>
+      <c r="D135" t="str">
+        <v>338401528</v>
+      </c>
+      <c r="E135" t="str">
+        <v>LÊ VĂN NGỢI</v>
+      </c>
+      <c r="F135" t="str">
+        <v>HỢP TÁC XÃ DỊCH VỤ NÔNG NGHIỆP BÌNH HIỆP B</v>
+      </c>
+      <c r="J135" t="str">
+        <v>Intensive rice production // Trồng lúa thâm canh</v>
+      </c>
+      <c r="K135" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="L135" t="str">
+        <v>Male // Nam</v>
+      </c>
+      <c r="M135" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="N135" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O135" t="str">
+        <v>0</v>
+      </c>
+      <c r="P135" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q135" t="str">
+        <v>0</v>
+      </c>
+      <c r="R135" t="str">
+        <v>0</v>
+      </c>
+      <c r="S135" t="str">
+        <v>0</v>
+      </c>
+      <c r="T135" t="str">
+        <v>0</v>
+      </c>
+      <c r="U135" t="str">
+        <v>4</v>
+      </c>
+      <c r="V135" t="str">
+        <v>0</v>
+      </c>
+      <c r="W135" t="str">
+        <v>3</v>
+      </c>
+      <c r="X135" t="str">
+        <v>4/10/26</v>
+      </c>
+      <c r="Y135" t="str">
+        <v>7/14/26</v>
+      </c>
+      <c r="Z135" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="AB135" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="AD135" t="str">
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="str">
+        <v>(374)</v>
+      </c>
+      <c r="B136" t="str">
+        <v>(1) Viet Nga Group, (2) Việt Nga Group-HTX DVNN Bình Hiệp B</v>
+      </c>
+      <c r="C136" t="str">
+        <v>74885</v>
+      </c>
+      <c r="D136" t="str">
+        <v>983702182</v>
+      </c>
+      <c r="E136" t="str">
+        <v>NGUYỄN VĂN LONG</v>
+      </c>
+      <c r="F136" t="str">
+        <v>HỢP TÁC XÃ DỊCH VỤ NÔNG NGHIỆP BÌNH HIỆP B</v>
+      </c>
+      <c r="J136" t="str">
+        <v>Intensive rice production // Trồng lúa thâm canh</v>
+      </c>
+      <c r="K136" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="L136" t="str">
+        <v>Male // Nam</v>
+      </c>
+      <c r="M136" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="N136" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O136" t="str">
+        <v>0</v>
+      </c>
+      <c r="P136" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q136" t="str">
+        <v>0</v>
+      </c>
+      <c r="R136" t="str">
+        <v>0</v>
+      </c>
+      <c r="S136" t="str">
+        <v>0</v>
+      </c>
+      <c r="T136" t="str">
+        <v>0</v>
+      </c>
+      <c r="U136" t="str">
+        <v>4</v>
+      </c>
+      <c r="V136" t="str">
+        <v>0</v>
+      </c>
+      <c r="W136" t="str">
+        <v>3</v>
+      </c>
+      <c r="X136" t="str">
+        <v>4/10/26</v>
+      </c>
+      <c r="Y136" t="str">
+        <v>7/14/26</v>
+      </c>
+      <c r="Z136" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="AB136" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="AD136" t="str">
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="str">
+        <v>(376)</v>
+      </c>
+      <c r="B137" t="str">
+        <v>(1) Viet Nga Group, (2) Việt Nga Group-HTX DVNN Bình Hiệp B</v>
+      </c>
+      <c r="C137" t="str">
+        <v>74887</v>
+      </c>
+      <c r="D137" t="str">
+        <v>356634518</v>
+      </c>
+      <c r="E137" t="str">
+        <v>NGUYỄN VĂN ĐÀNH</v>
+      </c>
+      <c r="F137" t="str">
+        <v>HỢP TÁC XÃ DỊCH VỤ NÔNG NGHIỆP BÌNH HIỆP B</v>
+      </c>
+      <c r="J137" t="str">
+        <v>Intensive rice production // Trồng lúa thâm canh</v>
+      </c>
+      <c r="K137" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="L137" t="str">
+        <v>Male // Nam</v>
+      </c>
+      <c r="M137" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="N137" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O137" t="str">
+        <v>0</v>
+      </c>
+      <c r="P137" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q137" t="str">
+        <v>0</v>
+      </c>
+      <c r="R137" t="str">
+        <v>0</v>
+      </c>
+      <c r="S137" t="str">
+        <v>0</v>
+      </c>
+      <c r="T137" t="str">
+        <v>0</v>
+      </c>
+      <c r="U137" t="str">
+        <v>4</v>
+      </c>
+      <c r="V137" t="str">
+        <v>0</v>
+      </c>
+      <c r="W137" t="str">
+        <v>3</v>
+      </c>
+      <c r="X137" t="str">
+        <v>4/10/26</v>
+      </c>
+      <c r="Y137" t="str">
+        <v>7/14/26</v>
+      </c>
+      <c r="Z137" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="AB137" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="AD137" t="str">
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="str">
+        <v>(377)</v>
+      </c>
+      <c r="B138" t="str">
+        <v>(1) Viet Nga Group, (2) Việt Nga Group-HTX DVNN Bình Hiệp B</v>
+      </c>
+      <c r="C138" t="str">
+        <v>74888</v>
+      </c>
+      <c r="D138" t="str">
+        <v>987052029</v>
+      </c>
+      <c r="E138" t="str">
+        <v>NGUYỄN THỊ DIỄM</v>
+      </c>
+      <c r="F138" t="str">
+        <v>HỢP TÁC XÃ DỊCH VỤ NÔNG NGHIỆP BÌNH HIỆP B</v>
+      </c>
+      <c r="J138" t="str">
+        <v>Intensive rice production // Trồng lúa thâm canh</v>
+      </c>
+      <c r="K138" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="L138" t="str">
+        <v>Female // Nữ</v>
+      </c>
+      <c r="M138" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="N138" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O138" t="str">
+        <v>1</v>
+      </c>
+      <c r="P138" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q138" t="str">
+        <v>0</v>
+      </c>
+      <c r="R138" t="str">
+        <v>0</v>
+      </c>
+      <c r="S138" t="str">
+        <v>0</v>
+      </c>
+      <c r="T138" t="str">
+        <v>0</v>
+      </c>
+      <c r="U138" t="str">
+        <v>3</v>
+      </c>
+      <c r="V138" t="str">
+        <v>0</v>
+      </c>
+      <c r="W138" t="str">
+        <v>1</v>
+      </c>
+      <c r="X138" t="str">
+        <v>4/10/26</v>
+      </c>
+      <c r="Y138" t="str">
+        <v>7/14/26</v>
+      </c>
+      <c r="Z138" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="AB138" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="AD138" t="str">
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="str">
+        <v>(380)</v>
+      </c>
+      <c r="B139" t="str">
+        <v>(1) Viet Nga Group, (2) Việt Nga Group-HTX DVNN Bình Hiệp B</v>
+      </c>
+      <c r="C139" t="str">
+        <v>74891</v>
+      </c>
+      <c r="D139" t="str">
+        <v>338659732</v>
+      </c>
+      <c r="E139" t="str">
+        <v>NGUYỄN VĂN HIẾU</v>
+      </c>
+      <c r="F139" t="str">
+        <v>HỢP TÁC XÃ DỊCH VỤ NÔNG NGHIỆP BÌNH HIỆP B</v>
+      </c>
+      <c r="J139" t="str">
+        <v>Intensive rice production // Trồng lúa thâm canh</v>
+      </c>
+      <c r="K139" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="L139" t="str">
+        <v>Male // Nam</v>
+      </c>
+      <c r="M139" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="N139" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O139" t="str">
+        <v>0</v>
+      </c>
+      <c r="P139" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q139" t="str">
+        <v>0</v>
+      </c>
+      <c r="R139" t="str">
+        <v>0</v>
+      </c>
+      <c r="S139" t="str">
+        <v>0</v>
+      </c>
+      <c r="T139" t="str">
+        <v>0</v>
+      </c>
+      <c r="U139" t="str">
+        <v>5</v>
+      </c>
+      <c r="V139" t="str">
+        <v>0</v>
+      </c>
+      <c r="W139" t="str">
+        <v>2</v>
+      </c>
+      <c r="X139" t="str">
+        <v>4/10/26</v>
+      </c>
+      <c r="Y139" t="str">
+        <v>7/14/26</v>
+      </c>
+      <c r="Z139" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="AB139" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="AD139" t="str">
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="str">
+        <v>(381)</v>
+      </c>
+      <c r="B140" t="str">
+        <v>(1) Viet Nga Group, (2) Việt Nga Group-HTX DVNN Bình Hiệp B</v>
+      </c>
+      <c r="C140" t="str">
+        <v>74892</v>
+      </c>
+      <c r="D140" t="str">
+        <v>934030306</v>
+      </c>
+      <c r="E140" t="str">
+        <v>LÊ VĂN HỢP</v>
+      </c>
+      <c r="F140" t="str">
+        <v>HỢP TÁC XÃ DỊCH VỤ NÔNG NGHIỆP BÌNH HIỆP B</v>
+      </c>
+      <c r="J140" t="str">
+        <v>Intensive rice production // Trồng lúa thâm canh</v>
+      </c>
+      <c r="K140" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="L140" t="str">
+        <v>Male // Nam</v>
+      </c>
+      <c r="M140" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="N140" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O140" t="str">
+        <v>0</v>
+      </c>
+      <c r="P140" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q140" t="str">
+        <v>0</v>
+      </c>
+      <c r="R140" t="str">
+        <v>0</v>
+      </c>
+      <c r="S140" t="str">
+        <v>0</v>
+      </c>
+      <c r="T140" t="str">
+        <v>0</v>
+      </c>
+      <c r="U140" t="str">
+        <v>5</v>
+      </c>
+      <c r="V140" t="str">
+        <v>0</v>
+      </c>
+      <c r="W140" t="str">
+        <v>4</v>
+      </c>
+      <c r="X140" t="str">
+        <v>4/10/26</v>
+      </c>
+      <c r="Y140" t="str">
+        <v>7/14/26</v>
+      </c>
+      <c r="Z140" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="AB140" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="AD140" t="str">
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="str">
+        <v>(387)</v>
+      </c>
+      <c r="B141" t="str">
+        <v>(1) Viet Nga Group, (2) Việt Nga Group-HTX DVNN Bình Hiệp B</v>
+      </c>
+      <c r="C141" t="str">
+        <v>74898</v>
+      </c>
+      <c r="D141" t="str">
+        <v>905586404</v>
+      </c>
+      <c r="E141" t="str">
+        <v>NGUYỄN VĂN CHÍNH</v>
+      </c>
+      <c r="F141" t="str">
+        <v>HỢP TÁC XÃ DỊCH VỤ NÔNG NGHIỆP BÌNH HIỆP B</v>
+      </c>
+      <c r="J141" t="str">
+        <v>Intensive rice production // Trồng lúa thâm canh</v>
+      </c>
+      <c r="K141" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="L141" t="str">
+        <v>Male // Nam</v>
+      </c>
+      <c r="M141" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="N141" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O141" t="str">
+        <v>0</v>
+      </c>
+      <c r="P141" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q141" t="str">
+        <v>0</v>
+      </c>
+      <c r="R141" t="str">
+        <v>0</v>
+      </c>
+      <c r="S141" t="str">
+        <v>0</v>
+      </c>
+      <c r="T141" t="str">
+        <v>0</v>
+      </c>
+      <c r="U141" t="str">
+        <v>5</v>
+      </c>
+      <c r="V141" t="str">
+        <v>0</v>
+      </c>
+      <c r="W141" t="str">
+        <v>4</v>
+      </c>
+      <c r="X141" t="str">
+        <v>4/10/26</v>
+      </c>
+      <c r="Y141" t="str">
+        <v>7/14/26</v>
+      </c>
+      <c r="Z141" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="AB141" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="AD141" t="str">
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="str">
+        <v>(388)</v>
+      </c>
+      <c r="B142" t="str">
+        <v>(1) Viet Nga Group, (2) Việt Nga Group-HTX DVNN Bình Hiệp B</v>
+      </c>
+      <c r="C142" t="str">
+        <v>74899</v>
+      </c>
+      <c r="D142" t="str">
+        <v>929318437</v>
+      </c>
+      <c r="E142" t="str">
+        <v>LÂM VĂN PHỤNG</v>
+      </c>
+      <c r="F142" t="str">
+        <v>HỢP TÁC XÃ DỊCH VỤ NÔNG NGHIỆP BÌNH HIỆP B</v>
+      </c>
+      <c r="J142" t="str">
+        <v>Intensive rice production // Trồng lúa thâm canh</v>
+      </c>
+      <c r="K142" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="L142" t="str">
+        <v>Male // Nam</v>
+      </c>
+      <c r="M142" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="N142" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O142" t="str">
+        <v>0</v>
+      </c>
+      <c r="P142" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q142" t="str">
+        <v>0</v>
+      </c>
+      <c r="R142" t="str">
+        <v>0</v>
+      </c>
+      <c r="S142" t="str">
+        <v>0</v>
+      </c>
+      <c r="T142" t="str">
+        <v>0</v>
+      </c>
+      <c r="U142" t="str">
+        <v>3</v>
+      </c>
+      <c r="V142" t="str">
+        <v>0</v>
+      </c>
+      <c r="W142" t="str">
+        <v>2</v>
+      </c>
+      <c r="X142" t="str">
+        <v>4/10/26</v>
+      </c>
+      <c r="Y142" t="str">
+        <v>7/14/26</v>
+      </c>
+      <c r="Z142" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="AB142" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="AD142" t="str">
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="str">
+        <v>(389)</v>
+      </c>
+      <c r="B143" t="str">
+        <v>(1) Viet Nga Group, (2) Việt Nga Group-HTX DVNN Bình Hiệp B</v>
+      </c>
+      <c r="C143" t="str">
+        <v>74900</v>
+      </c>
+      <c r="D143" t="str">
+        <v>383006807</v>
+      </c>
+      <c r="E143" t="str">
+        <v>PHẠM HỮU LỢI</v>
+      </c>
+      <c r="F143" t="str">
+        <v>HỢP TÁC XÃ DỊCH VỤ NÔNG NGHIỆP BÌNH HIỆP B</v>
+      </c>
+      <c r="J143" t="str">
+        <v>Intensive rice production // Trồng lúa thâm canh</v>
+      </c>
+      <c r="K143" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="L143" t="str">
+        <v>Male // Nam</v>
+      </c>
+      <c r="M143" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="N143" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O143" t="str">
+        <v>0</v>
+      </c>
+      <c r="P143" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q143" t="str">
+        <v>0</v>
+      </c>
+      <c r="R143" t="str">
+        <v>0</v>
+      </c>
+      <c r="S143" t="str">
+        <v>0</v>
+      </c>
+      <c r="T143" t="str">
+        <v>0</v>
+      </c>
+      <c r="U143" t="str">
+        <v>3</v>
+      </c>
+      <c r="V143" t="str">
+        <v>0</v>
+      </c>
+      <c r="W143" t="str">
+        <v>2</v>
+      </c>
+      <c r="X143" t="str">
+        <v>4/10/26</v>
+      </c>
+      <c r="Y143" t="str">
+        <v>7/14/26</v>
+      </c>
+      <c r="Z143" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="AB143" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="AD143" t="str">
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="str">
+        <v>(393)</v>
+      </c>
+      <c r="B144" t="str">
+        <v>(1) Viet Nga Group, (2) Việt Nga Group-HTX DVNN Bình Hiệp B</v>
+      </c>
+      <c r="C144" t="str">
+        <v>74905</v>
+      </c>
+      <c r="D144" t="str">
+        <v>337961917</v>
+      </c>
+      <c r="E144" t="str">
+        <v>PHẠM THANH NHÂN</v>
+      </c>
+      <c r="F144" t="str">
+        <v>HỢP TÁC XÃ DỊCH VỤ NÔNG NGHIỆP BÌNH HIỆP B</v>
+      </c>
+      <c r="J144" t="str">
+        <v>Intensive rice production // Trồng lúa thâm canh</v>
+      </c>
+      <c r="K144" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="L144" t="str">
+        <v>Male // Nam</v>
+      </c>
+      <c r="M144" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="N144" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O144" t="str">
+        <v>0</v>
+      </c>
+      <c r="P144" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q144" t="str">
+        <v>0</v>
+      </c>
+      <c r="R144" t="str">
+        <v>0</v>
+      </c>
+      <c r="S144" t="str">
+        <v>0</v>
+      </c>
+      <c r="T144" t="str">
+        <v>0</v>
+      </c>
+      <c r="U144" t="str">
+        <v>4</v>
+      </c>
+      <c r="V144" t="str">
+        <v>0</v>
+      </c>
+      <c r="W144" t="str">
+        <v>3</v>
+      </c>
+      <c r="X144" t="str">
+        <v>4/10/26</v>
+      </c>
+      <c r="Y144" t="str">
+        <v>7/14/26</v>
+      </c>
+      <c r="Z144" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="AB144" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="AD144" t="str">
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="str">
+        <v>(401)</v>
+      </c>
+      <c r="B145" t="str">
+        <v>(1) Viet Nga Group, (2) Việt Nga Group-HTX DVNN Bình Hiệp B</v>
+      </c>
+      <c r="C145" t="str">
+        <v>74913</v>
+      </c>
+      <c r="D145" t="str">
+        <v>825525367</v>
+      </c>
+      <c r="E145" t="str">
+        <v>NGUYỄN VĂN KHỠI</v>
+      </c>
+      <c r="F145" t="str">
+        <v>HỢP TÁC XÃ DỊCH VỤ NÔNG NGHIỆP BÌNH HIỆP B</v>
+      </c>
+      <c r="J145" t="str">
+        <v>Intensive rice production // Trồng lúa thâm canh</v>
+      </c>
+      <c r="K145" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="L145" t="str">
+        <v>Male // Nam</v>
+      </c>
+      <c r="M145" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="N145" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O145" t="str">
+        <v>0</v>
+      </c>
+      <c r="P145" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q145" t="str">
+        <v>0</v>
+      </c>
+      <c r="R145" t="str">
+        <v>0</v>
+      </c>
+      <c r="S145" t="str">
+        <v>0</v>
+      </c>
+      <c r="T145" t="str">
+        <v>0</v>
+      </c>
+      <c r="U145" t="str">
+        <v>5</v>
+      </c>
+      <c r="V145" t="str">
+        <v>0</v>
+      </c>
+      <c r="W145" t="str">
+        <v>4</v>
+      </c>
+      <c r="X145" t="str">
+        <v>4/10/26</v>
+      </c>
+      <c r="Y145" t="str">
+        <v>7/14/26</v>
+      </c>
+      <c r="Z145" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="AB145" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="AD145" t="str">
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="str">
+        <v>(402)</v>
+      </c>
+      <c r="B146" t="str">
+        <v>(1) Viet Nga Group, (2) Việt Nga Group-HTX DVNN Bình Hiệp B</v>
+      </c>
+      <c r="C146" t="str">
+        <v>74914</v>
+      </c>
+      <c r="D146" t="str">
+        <v>983848841</v>
+      </c>
+      <c r="E146" t="str">
+        <v>HUỲNH NGỌC DŨNG</v>
+      </c>
+      <c r="F146" t="str">
+        <v>HỢP TÁC XÃ DỊCH VỤ NÔNG NGHIỆP BÌNH HIỆP B</v>
+      </c>
+      <c r="J146" t="str">
+        <v>Intensive rice production // Trồng lúa thâm canh</v>
+      </c>
+      <c r="K146" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="L146" t="str">
+        <v>Male // Nam</v>
+      </c>
+      <c r="M146" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="N146" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O146" t="str">
+        <v>0</v>
+      </c>
+      <c r="P146" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q146" t="str">
+        <v>0</v>
+      </c>
+      <c r="R146" t="str">
+        <v>0</v>
+      </c>
+      <c r="S146" t="str">
+        <v>0</v>
+      </c>
+      <c r="T146" t="str">
+        <v>0</v>
+      </c>
+      <c r="U146" t="str">
+        <v>6</v>
+      </c>
+      <c r="V146" t="str">
+        <v>0</v>
+      </c>
+      <c r="W146" t="str">
+        <v>5</v>
+      </c>
+      <c r="X146" t="str">
+        <v>4/10/26</v>
+      </c>
+      <c r="Y146" t="str">
+        <v>7/14/26</v>
+      </c>
+      <c r="Z146" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="AB146" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="AD146" t="str">
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="str">
+        <v>(410)</v>
+      </c>
+      <c r="B147" t="str">
+        <v>(1) Viet Nga Group, (2) Việt Nga Group-HTX DVNN Bình Hiệp B</v>
+      </c>
+      <c r="C147" t="str">
+        <v>74922</v>
+      </c>
+      <c r="D147" t="str">
+        <v>345567224</v>
+      </c>
+      <c r="E147" t="str">
+        <v>HUỲNH NGỌC ẪN</v>
+      </c>
+      <c r="F147" t="str">
+        <v>HỢP TÁC XÃ DỊCH VỤ NÔNG NGHIỆP BÌNH HIỆP B</v>
+      </c>
+      <c r="J147" t="str">
+        <v>Intensive rice production // Trồng lúa thâm canh</v>
+      </c>
+      <c r="K147" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="L147" t="str">
+        <v>Male // Nam</v>
+      </c>
+      <c r="M147" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="N147" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O147" t="str">
+        <v>0</v>
+      </c>
+      <c r="P147" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q147" t="str">
+        <v>0</v>
+      </c>
+      <c r="R147" t="str">
+        <v>0</v>
+      </c>
+      <c r="S147" t="str">
+        <v>0</v>
+      </c>
+      <c r="T147" t="str">
+        <v>0</v>
+      </c>
+      <c r="U147" t="str">
+        <v>5</v>
+      </c>
+      <c r="V147" t="str">
+        <v>0</v>
+      </c>
+      <c r="W147" t="str">
+        <v>3</v>
+      </c>
+      <c r="X147" t="str">
+        <v>4/10/26</v>
+      </c>
+      <c r="Y147" t="str">
+        <v>7/14/26</v>
+      </c>
+      <c r="Z147" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="AB147" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="AD147" t="str">
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="str">
+        <v>(352)</v>
+      </c>
+      <c r="B148" t="str">
+        <v>(1) Viet Nga Group, (2) Việt Nga Group-HTX DVNN Bình Hiệp B</v>
+      </c>
+      <c r="C148" t="str">
+        <v>74864</v>
+      </c>
+      <c r="D148" t="str">
+        <v>355126008</v>
+      </c>
+      <c r="E148" t="str">
+        <v>VÕ THANH VŨ</v>
+      </c>
+      <c r="F148" t="str">
+        <v>HỢP TÁC XÃ DỊCH VỤ NÔNG NGHIỆP BÌNH HIỆP B</v>
+      </c>
+      <c r="J148" t="str">
+        <v>Intensive rice production // Trồng lúa thâm canh</v>
+      </c>
+      <c r="K148" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="L148" t="str">
+        <v>Male // Nam</v>
+      </c>
+      <c r="M148" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="N148" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O148" t="str">
+        <v>0</v>
+      </c>
+      <c r="P148" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q148" t="str">
+        <v>0</v>
+      </c>
+      <c r="R148" t="str">
+        <v>0</v>
+      </c>
+      <c r="S148" t="str">
+        <v>0</v>
+      </c>
+      <c r="T148" t="str">
+        <v>0</v>
+      </c>
+      <c r="U148" t="str">
+        <v>3</v>
+      </c>
+      <c r="V148" t="str">
+        <v>0</v>
+      </c>
+      <c r="W148" t="str">
+        <v>2</v>
+      </c>
+      <c r="X148" t="str">
+        <v>4/10/26</v>
+      </c>
+      <c r="Y148" t="str">
+        <v>7/14/26</v>
+      </c>
+      <c r="Z148" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="AB148" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="AD148" t="str">
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="str">
+        <v>(353)</v>
+      </c>
+      <c r="B149" t="str">
+        <v>(1) Viet Nga Group, (2) Việt Nga Group-HTX DVNN Bình Hiệp B</v>
+      </c>
+      <c r="C149" t="str">
+        <v>74865</v>
+      </c>
+      <c r="D149" t="str">
+        <v>795865683</v>
+      </c>
+      <c r="E149" t="str">
+        <v>TRƯƠNG THANH BÌNH</v>
+      </c>
+      <c r="F149" t="str">
+        <v>HỢP TÁC XÃ DỊCH VỤ NÔNG NGHIỆP BÌNH HIỆP B</v>
+      </c>
+      <c r="J149" t="str">
+        <v>Intensive rice production // Trồng lúa thâm canh</v>
+      </c>
+      <c r="K149" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="L149" t="str">
+        <v>Male // Nam</v>
+      </c>
+      <c r="M149" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="N149" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O149" t="str">
+        <v>0</v>
+      </c>
+      <c r="P149" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q149" t="str">
+        <v>0</v>
+      </c>
+      <c r="R149" t="str">
+        <v>0</v>
+      </c>
+      <c r="S149" t="str">
+        <v>0</v>
+      </c>
+      <c r="T149" t="str">
+        <v>0</v>
+      </c>
+      <c r="U149" t="str">
+        <v>4</v>
+      </c>
+      <c r="V149" t="str">
+        <v>0</v>
+      </c>
+      <c r="W149" t="str">
+        <v>3</v>
+      </c>
+      <c r="X149" t="str">
+        <v>4/10/26</v>
+      </c>
+      <c r="Y149" t="str">
+        <v>7/14/26</v>
+      </c>
+      <c r="Z149" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="AB149" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="AD149" t="str">
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="str">
+        <v>(355)</v>
+      </c>
+      <c r="B150" t="str">
+        <v>(1) Viet Nga Group, (2) Việt Nga Group-HTX DVNN Bình Hiệp B</v>
+      </c>
+      <c r="C150" t="str">
+        <v>74867</v>
+      </c>
+      <c r="D150" t="str">
+        <v>939898955</v>
+      </c>
+      <c r="E150" t="str">
+        <v>TRẦN VĂN MỐC</v>
+      </c>
+      <c r="F150" t="str">
+        <v>HỢP TÁC XÃ DỊCH VỤ NÔNG NGHIỆP BÌNH HIỆP B</v>
+      </c>
+      <c r="J150" t="str">
+        <v>Intensive rice production // Trồng lúa thâm canh</v>
+      </c>
+      <c r="K150" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="L150" t="str">
+        <v>Male // Nam</v>
+      </c>
+      <c r="M150" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="N150" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O150" t="str">
+        <v>0</v>
+      </c>
+      <c r="P150" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q150" t="str">
+        <v>0</v>
+      </c>
+      <c r="R150" t="str">
+        <v>0</v>
+      </c>
+      <c r="S150" t="str">
+        <v>0</v>
+      </c>
+      <c r="T150" t="str">
+        <v>0</v>
+      </c>
+      <c r="U150" t="str">
+        <v>3</v>
+      </c>
+      <c r="V150" t="str">
+        <v>0</v>
+      </c>
+      <c r="W150" t="str">
+        <v>2</v>
+      </c>
+      <c r="X150" t="str">
+        <v>4/10/26</v>
+      </c>
+      <c r="Y150" t="str">
+        <v>7/14/26</v>
+      </c>
+      <c r="Z150" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="AB150" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="AD150" t="str">
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="str">
+        <v>(358)</v>
+      </c>
+      <c r="B151" t="str">
+        <v>(1) Viet Nga Group, (2) Việt Nga Group-HTX DVNN Bình Hiệp B</v>
+      </c>
+      <c r="C151" t="str">
+        <v>74870</v>
+      </c>
+      <c r="D151" t="str">
+        <v>397478550</v>
+      </c>
+      <c r="E151" t="str">
+        <v>NGUYỄN THANH TUẤN</v>
+      </c>
+      <c r="F151" t="str">
+        <v>HỢP TÁC XÃ DỊCH VỤ NÔNG NGHIỆP BÌNH HIỆP B</v>
+      </c>
+      <c r="J151" t="str">
+        <v>Intensive rice production // Trồng lúa thâm canh</v>
+      </c>
+      <c r="K151" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="L151" t="str">
+        <v>Male // Nam</v>
+      </c>
+      <c r="M151" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="N151" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O151" t="str">
+        <v>0</v>
+      </c>
+      <c r="P151" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q151" t="str">
+        <v>0</v>
+      </c>
+      <c r="R151" t="str">
+        <v>0</v>
+      </c>
+      <c r="S151" t="str">
+        <v>0</v>
+      </c>
+      <c r="T151" t="str">
+        <v>0</v>
+      </c>
+      <c r="U151" t="str">
+        <v>3</v>
+      </c>
+      <c r="V151" t="str">
+        <v>0</v>
+      </c>
+      <c r="W151" t="str">
+        <v>2</v>
+      </c>
+      <c r="X151" t="str">
+        <v>4/10/26</v>
+      </c>
+      <c r="Y151" t="str">
+        <v>7/14/26</v>
+      </c>
+      <c r="Z151" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="AB151" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="AD151" t="str">
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="str">
+        <v>(359)</v>
+      </c>
+      <c r="B152" t="str">
+        <v>(1) Viet Nga Group, (2) Việt Nga Group-HTX DVNN Bình Hiệp B</v>
+      </c>
+      <c r="C152" t="str">
+        <v>74871</v>
+      </c>
+      <c r="D152" t="str">
+        <v>362126594</v>
+      </c>
+      <c r="E152" t="str">
+        <v>HỒ VĂN ÚT</v>
+      </c>
+      <c r="F152" t="str">
+        <v>HỢP TÁC XÃ DỊCH VỤ NÔNG NGHIỆP BÌNH HIỆP B</v>
+      </c>
+      <c r="J152" t="str">
+        <v>Intensive rice production // Trồng lúa thâm canh</v>
+      </c>
+      <c r="K152" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="L152" t="str">
+        <v>Male // Nam</v>
+      </c>
+      <c r="M152" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="N152" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O152" t="str">
+        <v>0</v>
+      </c>
+      <c r="P152" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q152" t="str">
+        <v>0</v>
+      </c>
+      <c r="R152" t="str">
+        <v>0</v>
+      </c>
+      <c r="S152" t="str">
+        <v>0</v>
+      </c>
+      <c r="T152" t="str">
+        <v>0</v>
+      </c>
+      <c r="U152" t="str">
+        <v>3</v>
+      </c>
+      <c r="V152" t="str">
+        <v>0</v>
+      </c>
+      <c r="W152" t="str">
+        <v>2</v>
+      </c>
+      <c r="X152" t="str">
+        <v>4/10/26</v>
+      </c>
+      <c r="Y152" t="str">
+        <v>7/14/26</v>
+      </c>
+      <c r="Z152" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="AB152" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="AD152" t="str">
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="str">
+        <v>(363)</v>
+      </c>
+      <c r="B153" t="str">
+        <v>(1) Viet Nga Group, (2) Việt Nga Group-HTX DVNN Bình Hiệp B</v>
+      </c>
+      <c r="C153" t="str">
+        <v>74875</v>
+      </c>
+      <c r="D153" t="str">
+        <v>383889900</v>
+      </c>
+      <c r="E153" t="str">
+        <v>TRẦN VĂN HẬU</v>
+      </c>
+      <c r="F153" t="str">
+        <v>HỢP TÁC XÃ DỊCH VỤ NÔNG NGHIỆP BÌNH HIỆP B</v>
+      </c>
+      <c r="J153" t="str">
+        <v>Intensive rice production // Trồng lúa thâm canh</v>
+      </c>
+      <c r="K153" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="L153" t="str">
+        <v>Male // Nam</v>
+      </c>
+      <c r="M153" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="N153" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O153" t="str">
+        <v>0</v>
+      </c>
+      <c r="P153" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q153" t="str">
+        <v>0</v>
+      </c>
+      <c r="R153" t="str">
+        <v>0</v>
+      </c>
+      <c r="S153" t="str">
+        <v>0</v>
+      </c>
+      <c r="T153" t="str">
+        <v>0</v>
+      </c>
+      <c r="U153" t="str">
+        <v>3</v>
+      </c>
+      <c r="V153" t="str">
+        <v>0</v>
+      </c>
+      <c r="W153" t="str">
+        <v>2</v>
+      </c>
+      <c r="X153" t="str">
+        <v>4/10/26</v>
+      </c>
+      <c r="Y153" t="str">
+        <v>7/14/26</v>
+      </c>
+      <c r="Z153" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="AB153" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="AD153" t="str">
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="str">
+        <v>(367)</v>
+      </c>
+      <c r="B154" t="str">
+        <v>(1) Viet Nga Group, (2) Việt Nga Group-HTX DVNN Bình Hiệp B</v>
+      </c>
+      <c r="C154" t="str">
+        <v>74879</v>
+      </c>
+      <c r="D154" t="str">
+        <v>939269451</v>
+      </c>
+      <c r="E154" t="str">
+        <v>TRẦN VĂN BÌNH</v>
+      </c>
+      <c r="F154" t="str">
+        <v>HỢP TÁC XÃ DỊCH VỤ NÔNG NGHIỆP BÌNH HIỆP B</v>
+      </c>
+      <c r="J154" t="str">
+        <v>Intensive rice production // Trồng lúa thâm canh</v>
+      </c>
+      <c r="K154" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="L154" t="str">
+        <v>Male // Nam</v>
+      </c>
+      <c r="M154" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="N154" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O154" t="str">
+        <v>0</v>
+      </c>
+      <c r="P154" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q154" t="str">
+        <v>0</v>
+      </c>
+      <c r="R154" t="str">
+        <v>0</v>
+      </c>
+      <c r="S154" t="str">
+        <v>0</v>
+      </c>
+      <c r="T154" t="str">
+        <v>0</v>
+      </c>
+      <c r="U154" t="str">
+        <v>3</v>
+      </c>
+      <c r="V154" t="str">
+        <v>0</v>
+      </c>
+      <c r="W154" t="str">
+        <v>2</v>
+      </c>
+      <c r="X154" t="str">
+        <v>4/10/26</v>
+      </c>
+      <c r="Y154" t="str">
+        <v>7/14/26</v>
+      </c>
+      <c r="Z154" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="AB154" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="AD154" t="str">
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="str">
+        <v>(372)</v>
+      </c>
+      <c r="B155" t="str">
+        <v>(1) Viet Nga Group, (2) Việt Nga Group-HTX DVNN Bình Hiệp B</v>
+      </c>
+      <c r="C155" t="str">
+        <v>74883</v>
+      </c>
+      <c r="D155" t="str">
+        <v>338401528</v>
+      </c>
+      <c r="E155" t="str">
+        <v>LÊ VĂN NGỢI</v>
+      </c>
+      <c r="F155" t="str">
+        <v>HỢP TÁC XÃ DỊCH VỤ NÔNG NGHIỆP BÌNH HIỆP B</v>
+      </c>
+      <c r="J155" t="str">
+        <v>Intensive rice production // Trồng lúa thâm canh</v>
+      </c>
+      <c r="K155" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="L155" t="str">
+        <v>Male // Nam</v>
+      </c>
+      <c r="M155" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="N155" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O155" t="str">
+        <v>0</v>
+      </c>
+      <c r="P155" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q155" t="str">
+        <v>0</v>
+      </c>
+      <c r="R155" t="str">
+        <v>0</v>
+      </c>
+      <c r="S155" t="str">
+        <v>0</v>
+      </c>
+      <c r="T155" t="str">
+        <v>0</v>
+      </c>
+      <c r="U155" t="str">
+        <v>4</v>
+      </c>
+      <c r="V155" t="str">
+        <v>0</v>
+      </c>
+      <c r="W155" t="str">
+        <v>3</v>
+      </c>
+      <c r="X155" t="str">
+        <v>4/10/26</v>
+      </c>
+      <c r="Y155" t="str">
+        <v>7/14/26</v>
+      </c>
+      <c r="Z155" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="AB155" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="AD155" t="str">
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="str">
+        <v>(374)</v>
+      </c>
+      <c r="B156" t="str">
+        <v>(1) Viet Nga Group, (2) Việt Nga Group-HTX DVNN Bình Hiệp B</v>
+      </c>
+      <c r="C156" t="str">
+        <v>74885</v>
+      </c>
+      <c r="D156" t="str">
+        <v>983702182</v>
+      </c>
+      <c r="E156" t="str">
+        <v>NGUYỄN VĂN LONG</v>
+      </c>
+      <c r="F156" t="str">
+        <v>HỢP TÁC XÃ DỊCH VỤ NÔNG NGHIỆP BÌNH HIỆP B</v>
+      </c>
+      <c r="J156" t="str">
+        <v>Intensive rice production // Trồng lúa thâm canh</v>
+      </c>
+      <c r="K156" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="L156" t="str">
+        <v>Male // Nam</v>
+      </c>
+      <c r="M156" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="N156" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O156" t="str">
+        <v>0</v>
+      </c>
+      <c r="P156" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q156" t="str">
+        <v>0</v>
+      </c>
+      <c r="R156" t="str">
+        <v>0</v>
+      </c>
+      <c r="S156" t="str">
+        <v>0</v>
+      </c>
+      <c r="T156" t="str">
+        <v>0</v>
+      </c>
+      <c r="U156" t="str">
+        <v>4</v>
+      </c>
+      <c r="V156" t="str">
+        <v>0</v>
+      </c>
+      <c r="W156" t="str">
+        <v>3</v>
+      </c>
+      <c r="X156" t="str">
+        <v>4/10/26</v>
+      </c>
+      <c r="Y156" t="str">
+        <v>7/14/26</v>
+      </c>
+      <c r="Z156" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="AB156" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="AD156" t="str">
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="str">
+        <v>(376)</v>
+      </c>
+      <c r="B157" t="str">
+        <v>(1) Viet Nga Group, (2) Việt Nga Group-HTX DVNN Bình Hiệp B</v>
+      </c>
+      <c r="C157" t="str">
+        <v>74887</v>
+      </c>
+      <c r="D157" t="str">
+        <v>356634518</v>
+      </c>
+      <c r="E157" t="str">
+        <v>NGUYỄN VĂN ĐÀNH</v>
+      </c>
+      <c r="F157" t="str">
+        <v>HỢP TÁC XÃ DỊCH VỤ NÔNG NGHIỆP BÌNH HIỆP B</v>
+      </c>
+      <c r="J157" t="str">
+        <v>Intensive rice production // Trồng lúa thâm canh</v>
+      </c>
+      <c r="K157" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="L157" t="str">
+        <v>Male // Nam</v>
+      </c>
+      <c r="M157" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="N157" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O157" t="str">
+        <v>0</v>
+      </c>
+      <c r="P157" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q157" t="str">
+        <v>0</v>
+      </c>
+      <c r="R157" t="str">
+        <v>0</v>
+      </c>
+      <c r="S157" t="str">
+        <v>0</v>
+      </c>
+      <c r="T157" t="str">
+        <v>0</v>
+      </c>
+      <c r="U157" t="str">
+        <v>4</v>
+      </c>
+      <c r="V157" t="str">
+        <v>0</v>
+      </c>
+      <c r="W157" t="str">
+        <v>3</v>
+      </c>
+      <c r="X157" t="str">
+        <v>4/10/26</v>
+      </c>
+      <c r="Y157" t="str">
+        <v>7/14/26</v>
+      </c>
+      <c r="Z157" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="AB157" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="AD157" t="str">
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="str">
+        <v>(377)</v>
+      </c>
+      <c r="B158" t="str">
+        <v>(1) Viet Nga Group, (2) Việt Nga Group-HTX DVNN Bình Hiệp B</v>
+      </c>
+      <c r="C158" t="str">
+        <v>74888</v>
+      </c>
+      <c r="D158" t="str">
+        <v>987052029</v>
+      </c>
+      <c r="E158" t="str">
+        <v>NGUYỄN THỊ DIỄM</v>
+      </c>
+      <c r="F158" t="str">
+        <v>HỢP TÁC XÃ DỊCH VỤ NÔNG NGHIỆP BÌNH HIỆP B</v>
+      </c>
+      <c r="J158" t="str">
+        <v>Intensive rice production // Trồng lúa thâm canh</v>
+      </c>
+      <c r="K158" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="L158" t="str">
+        <v>Female // Nữ</v>
+      </c>
+      <c r="M158" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="N158" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O158" t="str">
+        <v>1</v>
+      </c>
+      <c r="P158" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q158" t="str">
+        <v>0</v>
+      </c>
+      <c r="R158" t="str">
+        <v>0</v>
+      </c>
+      <c r="S158" t="str">
+        <v>0</v>
+      </c>
+      <c r="T158" t="str">
+        <v>0</v>
+      </c>
+      <c r="U158" t="str">
+        <v>3</v>
+      </c>
+      <c r="V158" t="str">
+        <v>0</v>
+      </c>
+      <c r="W158" t="str">
+        <v>1</v>
+      </c>
+      <c r="X158" t="str">
+        <v>4/10/26</v>
+      </c>
+      <c r="Y158" t="str">
+        <v>7/14/26</v>
+      </c>
+      <c r="Z158" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="AB158" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="AD158" t="str">
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="str">
+        <v>(380)</v>
+      </c>
+      <c r="B159" t="str">
+        <v>(1) Viet Nga Group, (2) Việt Nga Group-HTX DVNN Bình Hiệp B</v>
+      </c>
+      <c r="C159" t="str">
+        <v>74891</v>
+      </c>
+      <c r="D159" t="str">
+        <v>338659732</v>
+      </c>
+      <c r="E159" t="str">
+        <v>NGUYỄN VĂN HIẾU</v>
+      </c>
+      <c r="F159" t="str">
+        <v>HỢP TÁC XÃ DỊCH VỤ NÔNG NGHIỆP BÌNH HIỆP B</v>
+      </c>
+      <c r="J159" t="str">
+        <v>Intensive rice production // Trồng lúa thâm canh</v>
+      </c>
+      <c r="K159" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="L159" t="str">
+        <v>Male // Nam</v>
+      </c>
+      <c r="M159" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="N159" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O159" t="str">
+        <v>0</v>
+      </c>
+      <c r="P159" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q159" t="str">
+        <v>0</v>
+      </c>
+      <c r="R159" t="str">
+        <v>0</v>
+      </c>
+      <c r="S159" t="str">
+        <v>0</v>
+      </c>
+      <c r="T159" t="str">
+        <v>0</v>
+      </c>
+      <c r="U159" t="str">
+        <v>5</v>
+      </c>
+      <c r="V159" t="str">
+        <v>0</v>
+      </c>
+      <c r="W159" t="str">
+        <v>2</v>
+      </c>
+      <c r="X159" t="str">
+        <v>4/10/26</v>
+      </c>
+      <c r="Y159" t="str">
+        <v>7/14/26</v>
+      </c>
+      <c r="Z159" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="AB159" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="AD159" t="str">
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="str">
+        <v>(381)</v>
+      </c>
+      <c r="B160" t="str">
+        <v>(1) Viet Nga Group, (2) Việt Nga Group-HTX DVNN Bình Hiệp B</v>
+      </c>
+      <c r="C160" t="str">
+        <v>74892</v>
+      </c>
+      <c r="D160" t="str">
+        <v>934030306</v>
+      </c>
+      <c r="E160" t="str">
+        <v>LÊ VĂN HỢP</v>
+      </c>
+      <c r="F160" t="str">
+        <v>HỢP TÁC XÃ DỊCH VỤ NÔNG NGHIỆP BÌNH HIỆP B</v>
+      </c>
+      <c r="J160" t="str">
+        <v>Intensive rice production // Trồng lúa thâm canh</v>
+      </c>
+      <c r="K160" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="L160" t="str">
+        <v>Male // Nam</v>
+      </c>
+      <c r="M160" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="N160" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O160" t="str">
+        <v>0</v>
+      </c>
+      <c r="P160" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q160" t="str">
+        <v>0</v>
+      </c>
+      <c r="R160" t="str">
+        <v>0</v>
+      </c>
+      <c r="S160" t="str">
+        <v>0</v>
+      </c>
+      <c r="T160" t="str">
+        <v>0</v>
+      </c>
+      <c r="U160" t="str">
+        <v>5</v>
+      </c>
+      <c r="V160" t="str">
+        <v>0</v>
+      </c>
+      <c r="W160" t="str">
+        <v>4</v>
+      </c>
+      <c r="X160" t="str">
+        <v>4/10/26</v>
+      </c>
+      <c r="Y160" t="str">
+        <v>7/14/26</v>
+      </c>
+      <c r="Z160" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="AB160" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="AD160" t="str">
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="str">
+        <v>(387)</v>
+      </c>
+      <c r="B161" t="str">
+        <v>(1) Viet Nga Group, (2) Việt Nga Group-HTX DVNN Bình Hiệp B</v>
+      </c>
+      <c r="C161" t="str">
+        <v>74898</v>
+      </c>
+      <c r="D161" t="str">
+        <v>905586404</v>
+      </c>
+      <c r="E161" t="str">
+        <v>NGUYỄN VĂN CHÍNH</v>
+      </c>
+      <c r="F161" t="str">
+        <v>HỢP TÁC XÃ DỊCH VỤ NÔNG NGHIỆP BÌNH HIỆP B</v>
+      </c>
+      <c r="J161" t="str">
+        <v>Intensive rice production // Trồng lúa thâm canh</v>
+      </c>
+      <c r="K161" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="L161" t="str">
+        <v>Male // Nam</v>
+      </c>
+      <c r="M161" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="N161" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O161" t="str">
+        <v>0</v>
+      </c>
+      <c r="P161" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q161" t="str">
+        <v>0</v>
+      </c>
+      <c r="R161" t="str">
+        <v>0</v>
+      </c>
+      <c r="S161" t="str">
+        <v>0</v>
+      </c>
+      <c r="T161" t="str">
+        <v>0</v>
+      </c>
+      <c r="U161" t="str">
+        <v>5</v>
+      </c>
+      <c r="V161" t="str">
+        <v>0</v>
+      </c>
+      <c r="W161" t="str">
+        <v>4</v>
+      </c>
+      <c r="X161" t="str">
+        <v>4/10/26</v>
+      </c>
+      <c r="Y161" t="str">
+        <v>7/14/26</v>
+      </c>
+      <c r="Z161" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="AB161" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="AD161" t="str">
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="str">
+        <v>(388)</v>
+      </c>
+      <c r="B162" t="str">
+        <v>(1) Viet Nga Group, (2) Việt Nga Group-HTX DVNN Bình Hiệp B</v>
+      </c>
+      <c r="C162" t="str">
+        <v>74899</v>
+      </c>
+      <c r="D162" t="str">
+        <v>929318437</v>
+      </c>
+      <c r="E162" t="str">
+        <v>LÂM VĂN PHỤNG</v>
+      </c>
+      <c r="F162" t="str">
+        <v>HỢP TÁC XÃ DỊCH VỤ NÔNG NGHIỆP BÌNH HIỆP B</v>
+      </c>
+      <c r="J162" t="str">
+        <v>Intensive rice production // Trồng lúa thâm canh</v>
+      </c>
+      <c r="K162" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="L162" t="str">
+        <v>Male // Nam</v>
+      </c>
+      <c r="M162" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="N162" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O162" t="str">
+        <v>0</v>
+      </c>
+      <c r="P162" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q162" t="str">
+        <v>0</v>
+      </c>
+      <c r="R162" t="str">
+        <v>0</v>
+      </c>
+      <c r="S162" t="str">
+        <v>0</v>
+      </c>
+      <c r="T162" t="str">
+        <v>0</v>
+      </c>
+      <c r="U162" t="str">
+        <v>3</v>
+      </c>
+      <c r="V162" t="str">
+        <v>0</v>
+      </c>
+      <c r="W162" t="str">
+        <v>2</v>
+      </c>
+      <c r="X162" t="str">
+        <v>4/10/26</v>
+      </c>
+      <c r="Y162" t="str">
+        <v>7/14/26</v>
+      </c>
+      <c r="Z162" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="AB162" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="AD162" t="str">
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="str">
+        <v>(389)</v>
+      </c>
+      <c r="B163" t="str">
+        <v>(1) Viet Nga Group, (2) Việt Nga Group-HTX DVNN Bình Hiệp B</v>
+      </c>
+      <c r="C163" t="str">
+        <v>74900</v>
+      </c>
+      <c r="D163" t="str">
+        <v>383006807</v>
+      </c>
+      <c r="E163" t="str">
+        <v>PHẠM HỮU LỢI</v>
+      </c>
+      <c r="F163" t="str">
+        <v>HỢP TÁC XÃ DỊCH VỤ NÔNG NGHIỆP BÌNH HIỆP B</v>
+      </c>
+      <c r="J163" t="str">
+        <v>Intensive rice production // Trồng lúa thâm canh</v>
+      </c>
+      <c r="K163" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="L163" t="str">
+        <v>Male // Nam</v>
+      </c>
+      <c r="M163" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="N163" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O163" t="str">
+        <v>0</v>
+      </c>
+      <c r="P163" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q163" t="str">
+        <v>0</v>
+      </c>
+      <c r="R163" t="str">
+        <v>0</v>
+      </c>
+      <c r="S163" t="str">
+        <v>0</v>
+      </c>
+      <c r="T163" t="str">
+        <v>0</v>
+      </c>
+      <c r="U163" t="str">
+        <v>3</v>
+      </c>
+      <c r="V163" t="str">
+        <v>0</v>
+      </c>
+      <c r="W163" t="str">
+        <v>2</v>
+      </c>
+      <c r="X163" t="str">
+        <v>4/10/26</v>
+      </c>
+      <c r="Y163" t="str">
+        <v>7/14/26</v>
+      </c>
+      <c r="Z163" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="AB163" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="AD163" t="str">
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="str">
+        <v>(393)</v>
+      </c>
+      <c r="B164" t="str">
+        <v>(1) Viet Nga Group, (2) Việt Nga Group-HTX DVNN Bình Hiệp B</v>
+      </c>
+      <c r="C164" t="str">
+        <v>74905</v>
+      </c>
+      <c r="D164" t="str">
+        <v>337961917</v>
+      </c>
+      <c r="E164" t="str">
+        <v>PHẠM THANH NHÂN</v>
+      </c>
+      <c r="F164" t="str">
+        <v>HỢP TÁC XÃ DỊCH VỤ NÔNG NGHIỆP BÌNH HIỆP B</v>
+      </c>
+      <c r="J164" t="str">
+        <v>Intensive rice production // Trồng lúa thâm canh</v>
+      </c>
+      <c r="K164" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="L164" t="str">
+        <v>Male // Nam</v>
+      </c>
+      <c r="M164" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="N164" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O164" t="str">
+        <v>0</v>
+      </c>
+      <c r="P164" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q164" t="str">
+        <v>0</v>
+      </c>
+      <c r="R164" t="str">
+        <v>0</v>
+      </c>
+      <c r="S164" t="str">
+        <v>0</v>
+      </c>
+      <c r="T164" t="str">
+        <v>0</v>
+      </c>
+      <c r="U164" t="str">
+        <v>4</v>
+      </c>
+      <c r="V164" t="str">
+        <v>0</v>
+      </c>
+      <c r="W164" t="str">
+        <v>3</v>
+      </c>
+      <c r="X164" t="str">
+        <v>4/10/26</v>
+      </c>
+      <c r="Y164" t="str">
+        <v>7/14/26</v>
+      </c>
+      <c r="Z164" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="AB164" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="AD164" t="str">
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="str">
+        <v>(401)</v>
+      </c>
+      <c r="B165" t="str">
+        <v>(1) Viet Nga Group, (2) Việt Nga Group-HTX DVNN Bình Hiệp B</v>
+      </c>
+      <c r="C165" t="str">
+        <v>74913</v>
+      </c>
+      <c r="D165" t="str">
+        <v>825525367</v>
+      </c>
+      <c r="E165" t="str">
+        <v>NGUYỄN VĂN KHỠI</v>
+      </c>
+      <c r="F165" t="str">
+        <v>HỢP TÁC XÃ DỊCH VỤ NÔNG NGHIỆP BÌNH HIỆP B</v>
+      </c>
+      <c r="J165" t="str">
+        <v>Intensive rice production // Trồng lúa thâm canh</v>
+      </c>
+      <c r="K165" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="L165" t="str">
+        <v>Male // Nam</v>
+      </c>
+      <c r="M165" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="N165" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O165" t="str">
+        <v>0</v>
+      </c>
+      <c r="P165" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q165" t="str">
+        <v>0</v>
+      </c>
+      <c r="R165" t="str">
+        <v>0</v>
+      </c>
+      <c r="S165" t="str">
+        <v>0</v>
+      </c>
+      <c r="T165" t="str">
+        <v>0</v>
+      </c>
+      <c r="U165" t="str">
+        <v>5</v>
+      </c>
+      <c r="V165" t="str">
+        <v>0</v>
+      </c>
+      <c r="W165" t="str">
+        <v>4</v>
+      </c>
+      <c r="X165" t="str">
+        <v>4/10/26</v>
+      </c>
+      <c r="Y165" t="str">
+        <v>7/14/26</v>
+      </c>
+      <c r="Z165" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="AB165" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="AD165" t="str">
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="str">
+        <v>(402)</v>
+      </c>
+      <c r="B166" t="str">
+        <v>(1) Viet Nga Group, (2) Việt Nga Group-HTX DVNN Bình Hiệp B</v>
+      </c>
+      <c r="C166" t="str">
+        <v>74914</v>
+      </c>
+      <c r="D166" t="str">
+        <v>983848841</v>
+      </c>
+      <c r="E166" t="str">
+        <v>HUỲNH NGỌC DŨNG</v>
+      </c>
+      <c r="F166" t="str">
+        <v>HỢP TÁC XÃ DỊCH VỤ NÔNG NGHIỆP BÌNH HIỆP B</v>
+      </c>
+      <c r="J166" t="str">
+        <v>Intensive rice production // Trồng lúa thâm canh</v>
+      </c>
+      <c r="K166" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="L166" t="str">
+        <v>Male // Nam</v>
+      </c>
+      <c r="M166" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="N166" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O166" t="str">
+        <v>0</v>
+      </c>
+      <c r="P166" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q166" t="str">
+        <v>0</v>
+      </c>
+      <c r="R166" t="str">
+        <v>0</v>
+      </c>
+      <c r="S166" t="str">
+        <v>0</v>
+      </c>
+      <c r="T166" t="str">
+        <v>0</v>
+      </c>
+      <c r="U166" t="str">
+        <v>6</v>
+      </c>
+      <c r="V166" t="str">
+        <v>0</v>
+      </c>
+      <c r="W166" t="str">
+        <v>5</v>
+      </c>
+      <c r="X166" t="str">
+        <v>4/10/26</v>
+      </c>
+      <c r="Y166" t="str">
+        <v>7/14/26</v>
+      </c>
+      <c r="Z166" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="AB166" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="AD166" t="str">
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="str">
+        <v>(410)</v>
+      </c>
+      <c r="B167" t="str">
+        <v>(1) Viet Nga Group, (2) Việt Nga Group-HTX DVNN Bình Hiệp B</v>
+      </c>
+      <c r="C167" t="str">
+        <v>74922</v>
+      </c>
+      <c r="D167" t="str">
+        <v>345567224</v>
+      </c>
+      <c r="E167" t="str">
+        <v>HUỲNH NGỌC ẪN</v>
+      </c>
+      <c r="F167" t="str">
+        <v>HỢP TÁC XÃ DỊCH VỤ NÔNG NGHIỆP BÌNH HIỆP B</v>
+      </c>
+      <c r="J167" t="str">
+        <v>Intensive rice production // Trồng lúa thâm canh</v>
+      </c>
+      <c r="K167" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="L167" t="str">
+        <v>Male // Nam</v>
+      </c>
+      <c r="M167" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="N167" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O167" t="str">
+        <v>0</v>
+      </c>
+      <c r="P167" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q167" t="str">
+        <v>0</v>
+      </c>
+      <c r="R167" t="str">
+        <v>0</v>
+      </c>
+      <c r="S167" t="str">
+        <v>0</v>
+      </c>
+      <c r="T167" t="str">
+        <v>0</v>
+      </c>
+      <c r="U167" t="str">
+        <v>5</v>
+      </c>
+      <c r="V167" t="str">
+        <v>0</v>
+      </c>
+      <c r="W167" t="str">
+        <v>3</v>
+      </c>
+      <c r="X167" t="str">
+        <v>4/10/26</v>
+      </c>
+      <c r="Y167" t="str">
+        <v>7/14/26</v>
+      </c>
+      <c r="Z167" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="AB167" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="AD167" t="str">
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="str">
+        <v>(352)</v>
+      </c>
+      <c r="B168" t="str">
+        <v>(1) Viet Nga Group, (2) Việt Nga Group-HTX DVNN Bình Hiệp B</v>
+      </c>
+      <c r="C168" t="str">
+        <v>74864</v>
+      </c>
+      <c r="D168" t="str">
+        <v>355126008</v>
+      </c>
+      <c r="E168" t="str">
+        <v>VÕ THANH VŨ</v>
+      </c>
+      <c r="F168" t="str">
+        <v>HỢP TÁC XÃ DỊCH VỤ NÔNG NGHIỆP BÌNH HIỆP B</v>
+      </c>
+      <c r="J168" t="str">
+        <v>Intensive rice production // Trồng lúa thâm canh</v>
+      </c>
+      <c r="K168" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="L168" t="str">
+        <v>Male // Nam</v>
+      </c>
+      <c r="M168" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="N168" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O168" t="str">
+        <v>0</v>
+      </c>
+      <c r="P168" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q168" t="str">
+        <v>0</v>
+      </c>
+      <c r="R168" t="str">
+        <v>0</v>
+      </c>
+      <c r="S168" t="str">
+        <v>0</v>
+      </c>
+      <c r="T168" t="str">
+        <v>0</v>
+      </c>
+      <c r="U168" t="str">
+        <v>3</v>
+      </c>
+      <c r="V168" t="str">
+        <v>0</v>
+      </c>
+      <c r="W168" t="str">
+        <v>2</v>
+      </c>
+      <c r="X168" t="str">
+        <v>4/10/26</v>
+      </c>
+      <c r="Y168" t="str">
+        <v>7/14/26</v>
+      </c>
+      <c r="Z168" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="AB168" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="AD168" t="str">
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="str">
+        <v>(353)</v>
+      </c>
+      <c r="B169" t="str">
+        <v>(1) Viet Nga Group, (2) Việt Nga Group-HTX DVNN Bình Hiệp B</v>
+      </c>
+      <c r="C169" t="str">
+        <v>74865</v>
+      </c>
+      <c r="D169" t="str">
+        <v>795865683</v>
+      </c>
+      <c r="E169" t="str">
+        <v>TRƯƠNG THANH BÌNH</v>
+      </c>
+      <c r="F169" t="str">
+        <v>HỢP TÁC XÃ DỊCH VỤ NÔNG NGHIỆP BÌNH HIỆP B</v>
+      </c>
+      <c r="J169" t="str">
+        <v>Intensive rice production // Trồng lúa thâm canh</v>
+      </c>
+      <c r="K169" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="L169" t="str">
+        <v>Male // Nam</v>
+      </c>
+      <c r="M169" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="N169" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O169" t="str">
+        <v>0</v>
+      </c>
+      <c r="P169" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q169" t="str">
+        <v>0</v>
+      </c>
+      <c r="R169" t="str">
+        <v>0</v>
+      </c>
+      <c r="S169" t="str">
+        <v>0</v>
+      </c>
+      <c r="T169" t="str">
+        <v>0</v>
+      </c>
+      <c r="U169" t="str">
+        <v>4</v>
+      </c>
+      <c r="V169" t="str">
+        <v>0</v>
+      </c>
+      <c r="W169" t="str">
+        <v>3</v>
+      </c>
+      <c r="X169" t="str">
+        <v>4/10/26</v>
+      </c>
+      <c r="Y169" t="str">
+        <v>7/14/26</v>
+      </c>
+      <c r="Z169" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="AB169" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="AD169" t="str">
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="str">
+        <v>(355)</v>
+      </c>
+      <c r="B170" t="str">
+        <v>(1) Viet Nga Group, (2) Việt Nga Group-HTX DVNN Bình Hiệp B</v>
+      </c>
+      <c r="C170" t="str">
+        <v>74867</v>
+      </c>
+      <c r="D170" t="str">
+        <v>939898955</v>
+      </c>
+      <c r="E170" t="str">
+        <v>TRẦN VĂN MỐC</v>
+      </c>
+      <c r="F170" t="str">
+        <v>HỢP TÁC XÃ DỊCH VỤ NÔNG NGHIỆP BÌNH HIỆP B</v>
+      </c>
+      <c r="J170" t="str">
+        <v>Intensive rice production // Trồng lúa thâm canh</v>
+      </c>
+      <c r="K170" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="L170" t="str">
+        <v>Male // Nam</v>
+      </c>
+      <c r="M170" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="N170" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O170" t="str">
+        <v>0</v>
+      </c>
+      <c r="P170" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q170" t="str">
+        <v>0</v>
+      </c>
+      <c r="R170" t="str">
+        <v>0</v>
+      </c>
+      <c r="S170" t="str">
+        <v>0</v>
+      </c>
+      <c r="T170" t="str">
+        <v>0</v>
+      </c>
+      <c r="U170" t="str">
+        <v>3</v>
+      </c>
+      <c r="V170" t="str">
+        <v>0</v>
+      </c>
+      <c r="W170" t="str">
+        <v>2</v>
+      </c>
+      <c r="X170" t="str">
+        <v>4/10/26</v>
+      </c>
+      <c r="Y170" t="str">
+        <v>7/14/26</v>
+      </c>
+      <c r="Z170" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="AB170" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="AD170" t="str">
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="str">
+        <v>(358)</v>
+      </c>
+      <c r="B171" t="str">
+        <v>(1) Viet Nga Group, (2) Việt Nga Group-HTX DVNN Bình Hiệp B</v>
+      </c>
+      <c r="C171" t="str">
+        <v>74870</v>
+      </c>
+      <c r="D171" t="str">
+        <v>397478550</v>
+      </c>
+      <c r="E171" t="str">
+        <v>NGUYỄN THANH TUẤN</v>
+      </c>
+      <c r="F171" t="str">
+        <v>HỢP TÁC XÃ DỊCH VỤ NÔNG NGHIỆP BÌNH HIỆP B</v>
+      </c>
+      <c r="J171" t="str">
+        <v>Intensive rice production // Trồng lúa thâm canh</v>
+      </c>
+      <c r="K171" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="L171" t="str">
+        <v>Male // Nam</v>
+      </c>
+      <c r="M171" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="N171" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O171" t="str">
+        <v>0</v>
+      </c>
+      <c r="P171" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q171" t="str">
+        <v>0</v>
+      </c>
+      <c r="R171" t="str">
+        <v>0</v>
+      </c>
+      <c r="S171" t="str">
+        <v>0</v>
+      </c>
+      <c r="T171" t="str">
+        <v>0</v>
+      </c>
+      <c r="U171" t="str">
+        <v>3</v>
+      </c>
+      <c r="V171" t="str">
+        <v>0</v>
+      </c>
+      <c r="W171" t="str">
+        <v>2</v>
+      </c>
+      <c r="X171" t="str">
+        <v>4/10/26</v>
+      </c>
+      <c r="Y171" t="str">
+        <v>7/14/26</v>
+      </c>
+      <c r="Z171" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="AB171" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="AD171" t="str">
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="str">
+        <v>(359)</v>
+      </c>
+      <c r="B172" t="str">
+        <v>(1) Viet Nga Group, (2) Việt Nga Group-HTX DVNN Bình Hiệp B</v>
+      </c>
+      <c r="C172" t="str">
+        <v>74871</v>
+      </c>
+      <c r="D172" t="str">
+        <v>362126594</v>
+      </c>
+      <c r="E172" t="str">
+        <v>HỒ VĂN ÚT</v>
+      </c>
+      <c r="F172" t="str">
+        <v>HỢP TÁC XÃ DỊCH VỤ NÔNG NGHIỆP BÌNH HIỆP B</v>
+      </c>
+      <c r="J172" t="str">
+        <v>Intensive rice production // Trồng lúa thâm canh</v>
+      </c>
+      <c r="K172" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="L172" t="str">
+        <v>Male // Nam</v>
+      </c>
+      <c r="M172" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="N172" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O172" t="str">
+        <v>0</v>
+      </c>
+      <c r="P172" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q172" t="str">
+        <v>0</v>
+      </c>
+      <c r="R172" t="str">
+        <v>0</v>
+      </c>
+      <c r="S172" t="str">
+        <v>0</v>
+      </c>
+      <c r="T172" t="str">
+        <v>0</v>
+      </c>
+      <c r="U172" t="str">
+        <v>3</v>
+      </c>
+      <c r="V172" t="str">
+        <v>0</v>
+      </c>
+      <c r="W172" t="str">
+        <v>2</v>
+      </c>
+      <c r="X172" t="str">
+        <v>4/10/26</v>
+      </c>
+      <c r="Y172" t="str">
+        <v>7/14/26</v>
+      </c>
+      <c r="Z172" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="AB172" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="AD172" t="str">
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="str">
+        <v>(363)</v>
+      </c>
+      <c r="B173" t="str">
+        <v>(1) Viet Nga Group, (2) Việt Nga Group-HTX DVNN Bình Hiệp B</v>
+      </c>
+      <c r="C173" t="str">
+        <v>74875</v>
+      </c>
+      <c r="D173" t="str">
+        <v>383889900</v>
+      </c>
+      <c r="E173" t="str">
+        <v>TRẦN VĂN HẬU</v>
+      </c>
+      <c r="F173" t="str">
+        <v>HỢP TÁC XÃ DỊCH VỤ NÔNG NGHIỆP BÌNH HIỆP B</v>
+      </c>
+      <c r="J173" t="str">
+        <v>Intensive rice production // Trồng lúa thâm canh</v>
+      </c>
+      <c r="K173" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="L173" t="str">
+        <v>Male // Nam</v>
+      </c>
+      <c r="M173" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="N173" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O173" t="str">
+        <v>0</v>
+      </c>
+      <c r="P173" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q173" t="str">
+        <v>0</v>
+      </c>
+      <c r="R173" t="str">
+        <v>0</v>
+      </c>
+      <c r="S173" t="str">
+        <v>0</v>
+      </c>
+      <c r="T173" t="str">
+        <v>0</v>
+      </c>
+      <c r="U173" t="str">
+        <v>3</v>
+      </c>
+      <c r="V173" t="str">
+        <v>0</v>
+      </c>
+      <c r="W173" t="str">
+        <v>2</v>
+      </c>
+      <c r="X173" t="str">
+        <v>4/10/26</v>
+      </c>
+      <c r="Y173" t="str">
+        <v>7/14/26</v>
+      </c>
+      <c r="Z173" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="AB173" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="AD173" t="str">
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="str">
+        <v>(367)</v>
+      </c>
+      <c r="B174" t="str">
+        <v>(1) Viet Nga Group, (2) Việt Nga Group-HTX DVNN Bình Hiệp B</v>
+      </c>
+      <c r="C174" t="str">
+        <v>74879</v>
+      </c>
+      <c r="D174" t="str">
+        <v>939269451</v>
+      </c>
+      <c r="E174" t="str">
+        <v>TRẦN VĂN BÌNH</v>
+      </c>
+      <c r="F174" t="str">
+        <v>HỢP TÁC XÃ DỊCH VỤ NÔNG NGHIỆP BÌNH HIỆP B</v>
+      </c>
+      <c r="J174" t="str">
+        <v>Intensive rice production // Trồng lúa thâm canh</v>
+      </c>
+      <c r="K174" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="L174" t="str">
+        <v>Male // Nam</v>
+      </c>
+      <c r="M174" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="N174" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O174" t="str">
+        <v>0</v>
+      </c>
+      <c r="P174" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q174" t="str">
+        <v>0</v>
+      </c>
+      <c r="R174" t="str">
+        <v>0</v>
+      </c>
+      <c r="S174" t="str">
+        <v>0</v>
+      </c>
+      <c r="T174" t="str">
+        <v>0</v>
+      </c>
+      <c r="U174" t="str">
+        <v>3</v>
+      </c>
+      <c r="V174" t="str">
+        <v>0</v>
+      </c>
+      <c r="W174" t="str">
+        <v>2</v>
+      </c>
+      <c r="X174" t="str">
+        <v>4/10/26</v>
+      </c>
+      <c r="Y174" t="str">
+        <v>7/14/26</v>
+      </c>
+      <c r="Z174" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="AB174" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="AD174" t="str">
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="str">
+        <v>(372)</v>
+      </c>
+      <c r="B175" t="str">
+        <v>(1) Viet Nga Group, (2) Việt Nga Group-HTX DVNN Bình Hiệp B</v>
+      </c>
+      <c r="C175" t="str">
+        <v>74883</v>
+      </c>
+      <c r="D175" t="str">
+        <v>338401528</v>
+      </c>
+      <c r="E175" t="str">
+        <v>LÊ VĂN NGỢI</v>
+      </c>
+      <c r="F175" t="str">
+        <v>HỢP TÁC XÃ DỊCH VỤ NÔNG NGHIỆP BÌNH HIỆP B</v>
+      </c>
+      <c r="J175" t="str">
+        <v>Intensive rice production // Trồng lúa thâm canh</v>
+      </c>
+      <c r="K175" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="L175" t="str">
+        <v>Male // Nam</v>
+      </c>
+      <c r="M175" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="N175" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O175" t="str">
+        <v>0</v>
+      </c>
+      <c r="P175" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q175" t="str">
+        <v>0</v>
+      </c>
+      <c r="R175" t="str">
+        <v>0</v>
+      </c>
+      <c r="S175" t="str">
+        <v>0</v>
+      </c>
+      <c r="T175" t="str">
+        <v>0</v>
+      </c>
+      <c r="U175" t="str">
+        <v>4</v>
+      </c>
+      <c r="V175" t="str">
+        <v>0</v>
+      </c>
+      <c r="W175" t="str">
+        <v>3</v>
+      </c>
+      <c r="X175" t="str">
+        <v>4/10/26</v>
+      </c>
+      <c r="Y175" t="str">
+        <v>7/14/26</v>
+      </c>
+      <c r="Z175" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="AB175" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="AD175" t="str">
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="str">
+        <v>(374)</v>
+      </c>
+      <c r="B176" t="str">
+        <v>(1) Viet Nga Group, (2) Việt Nga Group-HTX DVNN Bình Hiệp B</v>
+      </c>
+      <c r="C176" t="str">
+        <v>74885</v>
+      </c>
+      <c r="D176" t="str">
+        <v>983702182</v>
+      </c>
+      <c r="E176" t="str">
+        <v>NGUYỄN VĂN LONG</v>
+      </c>
+      <c r="F176" t="str">
+        <v>HỢP TÁC XÃ DỊCH VỤ NÔNG NGHIỆP BÌNH HIỆP B</v>
+      </c>
+      <c r="J176" t="str">
+        <v>Intensive rice production // Trồng lúa thâm canh</v>
+      </c>
+      <c r="K176" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="L176" t="str">
+        <v>Male // Nam</v>
+      </c>
+      <c r="M176" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="N176" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O176" t="str">
+        <v>0</v>
+      </c>
+      <c r="P176" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q176" t="str">
+        <v>0</v>
+      </c>
+      <c r="R176" t="str">
+        <v>0</v>
+      </c>
+      <c r="S176" t="str">
+        <v>0</v>
+      </c>
+      <c r="T176" t="str">
+        <v>0</v>
+      </c>
+      <c r="U176" t="str">
+        <v>4</v>
+      </c>
+      <c r="V176" t="str">
+        <v>0</v>
+      </c>
+      <c r="W176" t="str">
+        <v>3</v>
+      </c>
+      <c r="X176" t="str">
+        <v>4/10/26</v>
+      </c>
+      <c r="Y176" t="str">
+        <v>7/14/26</v>
+      </c>
+      <c r="Z176" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="AB176" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="AD176" t="str">
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="str">
+        <v>(376)</v>
+      </c>
+      <c r="B177" t="str">
+        <v>(1) Viet Nga Group, (2) Việt Nga Group-HTX DVNN Bình Hiệp B</v>
+      </c>
+      <c r="C177" t="str">
+        <v>74887</v>
+      </c>
+      <c r="D177" t="str">
+        <v>356634518</v>
+      </c>
+      <c r="E177" t="str">
+        <v>NGUYỄN VĂN ĐÀNH</v>
+      </c>
+      <c r="F177" t="str">
+        <v>HỢP TÁC XÃ DỊCH VỤ NÔNG NGHIỆP BÌNH HIỆP B</v>
+      </c>
+      <c r="J177" t="str">
+        <v>Intensive rice production // Trồng lúa thâm canh</v>
+      </c>
+      <c r="K177" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="L177" t="str">
+        <v>Male // Nam</v>
+      </c>
+      <c r="M177" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="N177" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O177" t="str">
+        <v>0</v>
+      </c>
+      <c r="P177" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q177" t="str">
+        <v>0</v>
+      </c>
+      <c r="R177" t="str">
+        <v>0</v>
+      </c>
+      <c r="S177" t="str">
+        <v>0</v>
+      </c>
+      <c r="T177" t="str">
+        <v>0</v>
+      </c>
+      <c r="U177" t="str">
+        <v>4</v>
+      </c>
+      <c r="V177" t="str">
+        <v>0</v>
+      </c>
+      <c r="W177" t="str">
+        <v>3</v>
+      </c>
+      <c r="X177" t="str">
+        <v>4/10/26</v>
+      </c>
+      <c r="Y177" t="str">
+        <v>7/14/26</v>
+      </c>
+      <c r="Z177" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="AB177" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="AD177" t="str">
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="str">
+        <v>(377)</v>
+      </c>
+      <c r="B178" t="str">
+        <v>(1) Viet Nga Group, (2) Việt Nga Group-HTX DVNN Bình Hiệp B</v>
+      </c>
+      <c r="C178" t="str">
+        <v>74888</v>
+      </c>
+      <c r="D178" t="str">
+        <v>987052029</v>
+      </c>
+      <c r="E178" t="str">
+        <v>NGUYỄN THỊ DIỄM</v>
+      </c>
+      <c r="F178" t="str">
+        <v>HỢP TÁC XÃ DỊCH VỤ NÔNG NGHIỆP BÌNH HIỆP B</v>
+      </c>
+      <c r="J178" t="str">
+        <v>Intensive rice production // Trồng lúa thâm canh</v>
+      </c>
+      <c r="K178" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="L178" t="str">
+        <v>Female // Nữ</v>
+      </c>
+      <c r="M178" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="N178" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O178" t="str">
+        <v>1</v>
+      </c>
+      <c r="P178" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q178" t="str">
+        <v>0</v>
+      </c>
+      <c r="R178" t="str">
+        <v>0</v>
+      </c>
+      <c r="S178" t="str">
+        <v>0</v>
+      </c>
+      <c r="T178" t="str">
+        <v>0</v>
+      </c>
+      <c r="U178" t="str">
+        <v>3</v>
+      </c>
+      <c r="V178" t="str">
+        <v>0</v>
+      </c>
+      <c r="W178" t="str">
+        <v>1</v>
+      </c>
+      <c r="X178" t="str">
+        <v>4/10/26</v>
+      </c>
+      <c r="Y178" t="str">
+        <v>7/14/26</v>
+      </c>
+      <c r="Z178" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="AB178" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="AD178" t="str">
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="str">
+        <v>(380)</v>
+      </c>
+      <c r="B179" t="str">
+        <v>(1) Viet Nga Group, (2) Việt Nga Group-HTX DVNN Bình Hiệp B</v>
+      </c>
+      <c r="C179" t="str">
+        <v>74891</v>
+      </c>
+      <c r="D179" t="str">
+        <v>338659732</v>
+      </c>
+      <c r="E179" t="str">
+        <v>NGUYỄN VĂN HIẾU</v>
+      </c>
+      <c r="F179" t="str">
+        <v>HỢP TÁC XÃ DỊCH VỤ NÔNG NGHIỆP BÌNH HIỆP B</v>
+      </c>
+      <c r="J179" t="str">
+        <v>Intensive rice production // Trồng lúa thâm canh</v>
+      </c>
+      <c r="K179" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="L179" t="str">
+        <v>Male // Nam</v>
+      </c>
+      <c r="M179" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="N179" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O179" t="str">
+        <v>0</v>
+      </c>
+      <c r="P179" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q179" t="str">
+        <v>0</v>
+      </c>
+      <c r="R179" t="str">
+        <v>0</v>
+      </c>
+      <c r="S179" t="str">
+        <v>0</v>
+      </c>
+      <c r="T179" t="str">
+        <v>0</v>
+      </c>
+      <c r="U179" t="str">
+        <v>5</v>
+      </c>
+      <c r="V179" t="str">
+        <v>0</v>
+      </c>
+      <c r="W179" t="str">
+        <v>2</v>
+      </c>
+      <c r="X179" t="str">
+        <v>4/10/26</v>
+      </c>
+      <c r="Y179" t="str">
+        <v>7/14/26</v>
+      </c>
+      <c r="Z179" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="AB179" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="AD179" t="str">
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="str">
+        <v>(381)</v>
+      </c>
+      <c r="B180" t="str">
+        <v>(1) Viet Nga Group, (2) Việt Nga Group-HTX DVNN Bình Hiệp B</v>
+      </c>
+      <c r="C180" t="str">
+        <v>74892</v>
+      </c>
+      <c r="D180" t="str">
+        <v>934030306</v>
+      </c>
+      <c r="E180" t="str">
+        <v>LÊ VĂN HỢP</v>
+      </c>
+      <c r="F180" t="str">
+        <v>HỢP TÁC XÃ DỊCH VỤ NÔNG NGHIỆP BÌNH HIỆP B</v>
+      </c>
+      <c r="J180" t="str">
+        <v>Intensive rice production // Trồng lúa thâm canh</v>
+      </c>
+      <c r="K180" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="L180" t="str">
+        <v>Male // Nam</v>
+      </c>
+      <c r="M180" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="N180" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O180" t="str">
+        <v>0</v>
+      </c>
+      <c r="P180" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q180" t="str">
+        <v>0</v>
+      </c>
+      <c r="R180" t="str">
+        <v>0</v>
+      </c>
+      <c r="S180" t="str">
+        <v>0</v>
+      </c>
+      <c r="T180" t="str">
+        <v>0</v>
+      </c>
+      <c r="U180" t="str">
+        <v>5</v>
+      </c>
+      <c r="V180" t="str">
+        <v>0</v>
+      </c>
+      <c r="W180" t="str">
+        <v>4</v>
+      </c>
+      <c r="X180" t="str">
+        <v>4/10/26</v>
+      </c>
+      <c r="Y180" t="str">
+        <v>7/14/26</v>
+      </c>
+      <c r="Z180" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="AB180" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="AD180" t="str">
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="str">
+        <v>(387)</v>
+      </c>
+      <c r="B181" t="str">
+        <v>(1) Viet Nga Group, (2) Việt Nga Group-HTX DVNN Bình Hiệp B</v>
+      </c>
+      <c r="C181" t="str">
+        <v>74898</v>
+      </c>
+      <c r="D181" t="str">
+        <v>905586404</v>
+      </c>
+      <c r="E181" t="str">
+        <v>NGUYỄN VĂN CHÍNH</v>
+      </c>
+      <c r="F181" t="str">
+        <v>HỢP TÁC XÃ DỊCH VỤ NÔNG NGHIỆP BÌNH HIỆP B</v>
+      </c>
+      <c r="J181" t="str">
+        <v>Intensive rice production // Trồng lúa thâm canh</v>
+      </c>
+      <c r="K181" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="L181" t="str">
+        <v>Male // Nam</v>
+      </c>
+      <c r="M181" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="N181" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O181" t="str">
+        <v>0</v>
+      </c>
+      <c r="P181" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q181" t="str">
+        <v>0</v>
+      </c>
+      <c r="R181" t="str">
+        <v>0</v>
+      </c>
+      <c r="S181" t="str">
+        <v>0</v>
+      </c>
+      <c r="T181" t="str">
+        <v>0</v>
+      </c>
+      <c r="U181" t="str">
+        <v>5</v>
+      </c>
+      <c r="V181" t="str">
+        <v>0</v>
+      </c>
+      <c r="W181" t="str">
+        <v>4</v>
+      </c>
+      <c r="X181" t="str">
+        <v>4/10/26</v>
+      </c>
+      <c r="Y181" t="str">
+        <v>7/14/26</v>
+      </c>
+      <c r="Z181" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="AB181" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="AD181" t="str">
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="str">
+        <v>(388)</v>
+      </c>
+      <c r="B182" t="str">
+        <v>(1) Viet Nga Group, (2) Việt Nga Group-HTX DVNN Bình Hiệp B</v>
+      </c>
+      <c r="C182" t="str">
+        <v>74899</v>
+      </c>
+      <c r="D182" t="str">
+        <v>929318437</v>
+      </c>
+      <c r="E182" t="str">
+        <v>LÂM VĂN PHỤNG</v>
+      </c>
+      <c r="F182" t="str">
+        <v>HỢP TÁC XÃ DỊCH VỤ NÔNG NGHIỆP BÌNH HIỆP B</v>
+      </c>
+      <c r="J182" t="str">
+        <v>Intensive rice production // Trồng lúa thâm canh</v>
+      </c>
+      <c r="K182" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="L182" t="str">
+        <v>Male // Nam</v>
+      </c>
+      <c r="M182" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="N182" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O182" t="str">
+        <v>0</v>
+      </c>
+      <c r="P182" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q182" t="str">
+        <v>0</v>
+      </c>
+      <c r="R182" t="str">
+        <v>0</v>
+      </c>
+      <c r="S182" t="str">
+        <v>0</v>
+      </c>
+      <c r="T182" t="str">
+        <v>0</v>
+      </c>
+      <c r="U182" t="str">
+        <v>3</v>
+      </c>
+      <c r="V182" t="str">
+        <v>0</v>
+      </c>
+      <c r="W182" t="str">
+        <v>2</v>
+      </c>
+      <c r="X182" t="str">
+        <v>4/10/26</v>
+      </c>
+      <c r="Y182" t="str">
+        <v>7/14/26</v>
+      </c>
+      <c r="Z182" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="AB182" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="AD182" t="str">
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="str">
+        <v>(389)</v>
+      </c>
+      <c r="B183" t="str">
+        <v>(1) Viet Nga Group, (2) Việt Nga Group-HTX DVNN Bình Hiệp B</v>
+      </c>
+      <c r="C183" t="str">
+        <v>74900</v>
+      </c>
+      <c r="D183" t="str">
+        <v>383006807</v>
+      </c>
+      <c r="E183" t="str">
+        <v>PHẠM HỮU LỢI</v>
+      </c>
+      <c r="F183" t="str">
+        <v>HỢP TÁC XÃ DỊCH VỤ NÔNG NGHIỆP BÌNH HIỆP B</v>
+      </c>
+      <c r="J183" t="str">
+        <v>Intensive rice production // Trồng lúa thâm canh</v>
+      </c>
+      <c r="K183" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="L183" t="str">
+        <v>Male // Nam</v>
+      </c>
+      <c r="M183" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="N183" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O183" t="str">
+        <v>0</v>
+      </c>
+      <c r="P183" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q183" t="str">
+        <v>0</v>
+      </c>
+      <c r="R183" t="str">
+        <v>0</v>
+      </c>
+      <c r="S183" t="str">
+        <v>0</v>
+      </c>
+      <c r="T183" t="str">
+        <v>0</v>
+      </c>
+      <c r="U183" t="str">
+        <v>3</v>
+      </c>
+      <c r="V183" t="str">
+        <v>0</v>
+      </c>
+      <c r="W183" t="str">
+        <v>2</v>
+      </c>
+      <c r="X183" t="str">
+        <v>4/10/26</v>
+      </c>
+      <c r="Y183" t="str">
+        <v>7/14/26</v>
+      </c>
+      <c r="Z183" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="AB183" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="AD183" t="str">
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="str">
+        <v>(393)</v>
+      </c>
+      <c r="B184" t="str">
+        <v>(1) Viet Nga Group, (2) Việt Nga Group-HTX DVNN Bình Hiệp B</v>
+      </c>
+      <c r="C184" t="str">
+        <v>74905</v>
+      </c>
+      <c r="D184" t="str">
+        <v>337961917</v>
+      </c>
+      <c r="E184" t="str">
+        <v>PHẠM THANH NHÂN</v>
+      </c>
+      <c r="F184" t="str">
+        <v>HỢP TÁC XÃ DỊCH VỤ NÔNG NGHIỆP BÌNH HIỆP B</v>
+      </c>
+      <c r="J184" t="str">
+        <v>Intensive rice production // Trồng lúa thâm canh</v>
+      </c>
+      <c r="K184" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="L184" t="str">
+        <v>Male // Nam</v>
+      </c>
+      <c r="M184" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="N184" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O184" t="str">
+        <v>0</v>
+      </c>
+      <c r="P184" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q184" t="str">
+        <v>0</v>
+      </c>
+      <c r="R184" t="str">
+        <v>0</v>
+      </c>
+      <c r="S184" t="str">
+        <v>0</v>
+      </c>
+      <c r="T184" t="str">
+        <v>0</v>
+      </c>
+      <c r="U184" t="str">
+        <v>4</v>
+      </c>
+      <c r="V184" t="str">
+        <v>0</v>
+      </c>
+      <c r="W184" t="str">
+        <v>3</v>
+      </c>
+      <c r="X184" t="str">
+        <v>4/10/26</v>
+      </c>
+      <c r="Y184" t="str">
+        <v>7/14/26</v>
+      </c>
+      <c r="Z184" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="AB184" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="AD184" t="str">
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="str">
+        <v>(401)</v>
+      </c>
+      <c r="B185" t="str">
+        <v>(1) Viet Nga Group, (2) Việt Nga Group-HTX DVNN Bình Hiệp B</v>
+      </c>
+      <c r="C185" t="str">
+        <v>74913</v>
+      </c>
+      <c r="D185" t="str">
+        <v>825525367</v>
+      </c>
+      <c r="E185" t="str">
+        <v>NGUYỄN VĂN KHỠI</v>
+      </c>
+      <c r="F185" t="str">
+        <v>HỢP TÁC XÃ DỊCH VỤ NÔNG NGHIỆP BÌNH HIỆP B</v>
+      </c>
+      <c r="J185" t="str">
+        <v>Intensive rice production // Trồng lúa thâm canh</v>
+      </c>
+      <c r="K185" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="L185" t="str">
+        <v>Male // Nam</v>
+      </c>
+      <c r="M185" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="N185" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O185" t="str">
+        <v>0</v>
+      </c>
+      <c r="P185" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q185" t="str">
+        <v>0</v>
+      </c>
+      <c r="R185" t="str">
+        <v>0</v>
+      </c>
+      <c r="S185" t="str">
+        <v>0</v>
+      </c>
+      <c r="T185" t="str">
+        <v>0</v>
+      </c>
+      <c r="U185" t="str">
+        <v>5</v>
+      </c>
+      <c r="V185" t="str">
+        <v>0</v>
+      </c>
+      <c r="W185" t="str">
+        <v>4</v>
+      </c>
+      <c r="X185" t="str">
+        <v>4/10/26</v>
+      </c>
+      <c r="Y185" t="str">
+        <v>7/14/26</v>
+      </c>
+      <c r="Z185" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="AB185" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="AD185" t="str">
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="str">
+        <v>(402)</v>
+      </c>
+      <c r="B186" t="str">
+        <v>(1) Viet Nga Group, (2) Việt Nga Group-HTX DVNN Bình Hiệp B</v>
+      </c>
+      <c r="C186" t="str">
+        <v>74914</v>
+      </c>
+      <c r="D186" t="str">
+        <v>983848841</v>
+      </c>
+      <c r="E186" t="str">
+        <v>HUỲNH NGỌC DŨNG</v>
+      </c>
+      <c r="F186" t="str">
+        <v>HỢP TÁC XÃ DỊCH VỤ NÔNG NGHIỆP BÌNH HIỆP B</v>
+      </c>
+      <c r="J186" t="str">
+        <v>Intensive rice production // Trồng lúa thâm canh</v>
+      </c>
+      <c r="K186" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="L186" t="str">
+        <v>Male // Nam</v>
+      </c>
+      <c r="M186" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="N186" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O186" t="str">
+        <v>0</v>
+      </c>
+      <c r="P186" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q186" t="str">
+        <v>0</v>
+      </c>
+      <c r="R186" t="str">
+        <v>0</v>
+      </c>
+      <c r="S186" t="str">
+        <v>0</v>
+      </c>
+      <c r="T186" t="str">
+        <v>0</v>
+      </c>
+      <c r="U186" t="str">
+        <v>6</v>
+      </c>
+      <c r="V186" t="str">
+        <v>0</v>
+      </c>
+      <c r="W186" t="str">
+        <v>5</v>
+      </c>
+      <c r="X186" t="str">
+        <v>4/10/26</v>
+      </c>
+      <c r="Y186" t="str">
+        <v>7/14/26</v>
+      </c>
+      <c r="Z186" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="AB186" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="AD186" t="str">
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="str">
+        <v>(410)</v>
+      </c>
+      <c r="B187" t="str">
+        <v>(1) Viet Nga Group, (2) Việt Nga Group-HTX DVNN Bình Hiệp B</v>
+      </c>
+      <c r="C187" t="str">
+        <v>74922</v>
+      </c>
+      <c r="D187" t="str">
+        <v>345567224</v>
+      </c>
+      <c r="E187" t="str">
+        <v>HUỲNH NGỌC ẪN</v>
+      </c>
+      <c r="F187" t="str">
+        <v>HỢP TÁC XÃ DỊCH VỤ NÔNG NGHIỆP BÌNH HIỆP B</v>
+      </c>
+      <c r="J187" t="str">
+        <v>Intensive rice production // Trồng lúa thâm canh</v>
+      </c>
+      <c r="K187" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="L187" t="str">
+        <v>Male // Nam</v>
+      </c>
+      <c r="M187" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="N187" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O187" t="str">
+        <v>0</v>
+      </c>
+      <c r="P187" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q187" t="str">
+        <v>0</v>
+      </c>
+      <c r="R187" t="str">
+        <v>0</v>
+      </c>
+      <c r="S187" t="str">
+        <v>0</v>
+      </c>
+      <c r="T187" t="str">
+        <v>0</v>
+      </c>
+      <c r="U187" t="str">
+        <v>5</v>
+      </c>
+      <c r="V187" t="str">
+        <v>0</v>
+      </c>
+      <c r="W187" t="str">
+        <v>3</v>
+      </c>
+      <c r="X187" t="str">
+        <v>4/10/26</v>
+      </c>
+      <c r="Y187" t="str">
+        <v>7/14/26</v>
+      </c>
+      <c r="Z187" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="AB187" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="AD187" t="str">
+        <v>Yes</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:AD63"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:AD187"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/cypress/fixtures/run-log.xlsx
+++ b/cypress/fixtures/run-log.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AD187"/>
+  <dimension ref="A1:AD224"/>
   <sheetData>
     <row r="1" xml:space="preserve">
       <c r="A1" t="str" xml:space="preserve">
@@ -14825,9 +14825,2858 @@
         <v>Yes</v>
       </c>
     </row>
+    <row r="188">
+      <c r="A188" t="str">
+        <v>(352)</v>
+      </c>
+      <c r="B188" t="str">
+        <v>(1) Viet Nga Group, (2) Việt Nga Group-HTX DVNN Bình Hiệp B</v>
+      </c>
+      <c r="C188" t="str">
+        <v>74864</v>
+      </c>
+      <c r="D188" t="str">
+        <v>355126008</v>
+      </c>
+      <c r="E188" t="str">
+        <v>VÕ THANH VŨ</v>
+      </c>
+      <c r="F188" t="str">
+        <v>HỢP TÁC XÃ DỊCH VỤ NÔNG NGHIỆP BÌNH HIỆP B</v>
+      </c>
+      <c r="J188" t="str">
+        <v>Intensive rice production // Trồng lúa thâm canh</v>
+      </c>
+      <c r="K188" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="L188" t="str">
+        <v>Male // Nam</v>
+      </c>
+      <c r="M188" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="N188" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O188" t="str">
+        <v>0</v>
+      </c>
+      <c r="P188" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q188" t="str">
+        <v>0</v>
+      </c>
+      <c r="R188" t="str">
+        <v>0</v>
+      </c>
+      <c r="S188" t="str">
+        <v>0</v>
+      </c>
+      <c r="T188" t="str">
+        <v>0</v>
+      </c>
+      <c r="U188" t="str">
+        <v>3</v>
+      </c>
+      <c r="V188" t="str">
+        <v>0</v>
+      </c>
+      <c r="W188" t="str">
+        <v>2</v>
+      </c>
+      <c r="X188" t="str">
+        <v>4/10/26</v>
+      </c>
+      <c r="Y188" t="str">
+        <v>7/14/26</v>
+      </c>
+      <c r="Z188" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="AB188" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="AD188" t="str">
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="str">
+        <v>(353)</v>
+      </c>
+      <c r="B189" t="str">
+        <v>(1) Viet Nga Group, (2) Việt Nga Group-HTX DVNN Bình Hiệp B</v>
+      </c>
+      <c r="C189" t="str">
+        <v>74865</v>
+      </c>
+      <c r="D189" t="str">
+        <v>795865683</v>
+      </c>
+      <c r="E189" t="str">
+        <v>TRƯƠNG THANH BÌNH</v>
+      </c>
+      <c r="F189" t="str">
+        <v>HỢP TÁC XÃ DỊCH VỤ NÔNG NGHIỆP BÌNH HIỆP B</v>
+      </c>
+      <c r="J189" t="str">
+        <v>Intensive rice production // Trồng lúa thâm canh</v>
+      </c>
+      <c r="K189" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="L189" t="str">
+        <v>Male // Nam</v>
+      </c>
+      <c r="M189" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="N189" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O189" t="str">
+        <v>0</v>
+      </c>
+      <c r="P189" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q189" t="str">
+        <v>0</v>
+      </c>
+      <c r="R189" t="str">
+        <v>0</v>
+      </c>
+      <c r="S189" t="str">
+        <v>0</v>
+      </c>
+      <c r="T189" t="str">
+        <v>0</v>
+      </c>
+      <c r="U189" t="str">
+        <v>4</v>
+      </c>
+      <c r="V189" t="str">
+        <v>0</v>
+      </c>
+      <c r="W189" t="str">
+        <v>3</v>
+      </c>
+      <c r="X189" t="str">
+        <v>4/10/26</v>
+      </c>
+      <c r="Y189" t="str">
+        <v>7/14/26</v>
+      </c>
+      <c r="Z189" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="AB189" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="AD189" t="str">
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="str">
+        <v>(355)</v>
+      </c>
+      <c r="B190" t="str">
+        <v>(1) Viet Nga Group, (2) Việt Nga Group-HTX DVNN Bình Hiệp B</v>
+      </c>
+      <c r="C190" t="str">
+        <v>74867</v>
+      </c>
+      <c r="D190" t="str">
+        <v>939898955</v>
+      </c>
+      <c r="E190" t="str">
+        <v>TRẦN VĂN MỐC</v>
+      </c>
+      <c r="F190" t="str">
+        <v>HỢP TÁC XÃ DỊCH VỤ NÔNG NGHIỆP BÌNH HIỆP B</v>
+      </c>
+      <c r="J190" t="str">
+        <v>Intensive rice production // Trồng lúa thâm canh</v>
+      </c>
+      <c r="K190" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="L190" t="str">
+        <v>Male // Nam</v>
+      </c>
+      <c r="M190" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="N190" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O190" t="str">
+        <v>0</v>
+      </c>
+      <c r="P190" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q190" t="str">
+        <v>0</v>
+      </c>
+      <c r="R190" t="str">
+        <v>0</v>
+      </c>
+      <c r="S190" t="str">
+        <v>0</v>
+      </c>
+      <c r="T190" t="str">
+        <v>0</v>
+      </c>
+      <c r="U190" t="str">
+        <v>3</v>
+      </c>
+      <c r="V190" t="str">
+        <v>0</v>
+      </c>
+      <c r="W190" t="str">
+        <v>2</v>
+      </c>
+      <c r="X190" t="str">
+        <v>4/10/26</v>
+      </c>
+      <c r="Y190" t="str">
+        <v>7/14/26</v>
+      </c>
+      <c r="Z190" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="AB190" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="AD190" t="str">
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="str">
+        <v>(358)</v>
+      </c>
+      <c r="B191" t="str">
+        <v>(1) Viet Nga Group, (2) Việt Nga Group-HTX DVNN Bình Hiệp B</v>
+      </c>
+      <c r="C191" t="str">
+        <v>74870</v>
+      </c>
+      <c r="D191" t="str">
+        <v>397478550</v>
+      </c>
+      <c r="E191" t="str">
+        <v>NGUYỄN THANH TUẤN</v>
+      </c>
+      <c r="F191" t="str">
+        <v>HỢP TÁC XÃ DỊCH VỤ NÔNG NGHIỆP BÌNH HIỆP B</v>
+      </c>
+      <c r="J191" t="str">
+        <v>Intensive rice production // Trồng lúa thâm canh</v>
+      </c>
+      <c r="K191" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="L191" t="str">
+        <v>Male // Nam</v>
+      </c>
+      <c r="M191" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="N191" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O191" t="str">
+        <v>0</v>
+      </c>
+      <c r="P191" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q191" t="str">
+        <v>0</v>
+      </c>
+      <c r="R191" t="str">
+        <v>0</v>
+      </c>
+      <c r="S191" t="str">
+        <v>0</v>
+      </c>
+      <c r="T191" t="str">
+        <v>0</v>
+      </c>
+      <c r="U191" t="str">
+        <v>3</v>
+      </c>
+      <c r="V191" t="str">
+        <v>0</v>
+      </c>
+      <c r="W191" t="str">
+        <v>2</v>
+      </c>
+      <c r="X191" t="str">
+        <v>4/10/26</v>
+      </c>
+      <c r="Y191" t="str">
+        <v>7/14/26</v>
+      </c>
+      <c r="Z191" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="AB191" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="AD191" t="str">
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="str">
+        <v>(359)</v>
+      </c>
+      <c r="B192" t="str">
+        <v>(1) Viet Nga Group, (2) Việt Nga Group-HTX DVNN Bình Hiệp B</v>
+      </c>
+      <c r="C192" t="str">
+        <v>74871</v>
+      </c>
+      <c r="D192" t="str">
+        <v>362126594</v>
+      </c>
+      <c r="E192" t="str">
+        <v>HỒ VĂN ÚT</v>
+      </c>
+      <c r="F192" t="str">
+        <v>HỢP TÁC XÃ DỊCH VỤ NÔNG NGHIỆP BÌNH HIỆP B</v>
+      </c>
+      <c r="J192" t="str">
+        <v>Intensive rice production // Trồng lúa thâm canh</v>
+      </c>
+      <c r="K192" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="L192" t="str">
+        <v>Male // Nam</v>
+      </c>
+      <c r="M192" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="N192" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O192" t="str">
+        <v>0</v>
+      </c>
+      <c r="P192" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q192" t="str">
+        <v>0</v>
+      </c>
+      <c r="R192" t="str">
+        <v>0</v>
+      </c>
+      <c r="S192" t="str">
+        <v>0</v>
+      </c>
+      <c r="T192" t="str">
+        <v>0</v>
+      </c>
+      <c r="U192" t="str">
+        <v>3</v>
+      </c>
+      <c r="V192" t="str">
+        <v>0</v>
+      </c>
+      <c r="W192" t="str">
+        <v>2</v>
+      </c>
+      <c r="X192" t="str">
+        <v>4/10/26</v>
+      </c>
+      <c r="Y192" t="str">
+        <v>7/14/26</v>
+      </c>
+      <c r="Z192" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="AB192" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="AD192" t="str">
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="str">
+        <v>(352)</v>
+      </c>
+      <c r="B193" t="str">
+        <v>(1) Viet Nga Group, (2) Việt Nga Group-HTX DVNN Bình Hiệp B</v>
+      </c>
+      <c r="C193" t="str">
+        <v>74864</v>
+      </c>
+      <c r="D193" t="str">
+        <v>355126008</v>
+      </c>
+      <c r="E193" t="str">
+        <v>VÕ THANH VŨ</v>
+      </c>
+      <c r="F193" t="str">
+        <v>HỢP TÁC XÃ DỊCH VỤ NÔNG NGHIỆP BÌNH HIỆP B</v>
+      </c>
+      <c r="J193" t="str">
+        <v>Intensive rice production // Trồng lúa thâm canh</v>
+      </c>
+      <c r="K193" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="L193" t="str">
+        <v>Male // Nam</v>
+      </c>
+      <c r="M193" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="N193" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O193" t="str">
+        <v>0</v>
+      </c>
+      <c r="P193" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q193" t="str">
+        <v>0</v>
+      </c>
+      <c r="R193" t="str">
+        <v>0</v>
+      </c>
+      <c r="S193" t="str">
+        <v>0</v>
+      </c>
+      <c r="T193" t="str">
+        <v>0</v>
+      </c>
+      <c r="U193" t="str">
+        <v>3</v>
+      </c>
+      <c r="V193" t="str">
+        <v>0</v>
+      </c>
+      <c r="W193" t="str">
+        <v>2</v>
+      </c>
+      <c r="X193" t="str">
+        <v>4/10/26</v>
+      </c>
+      <c r="Y193" t="str">
+        <v>7/14/26</v>
+      </c>
+      <c r="Z193" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="AB193" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="AD193" t="str">
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="str">
+        <v>(353)</v>
+      </c>
+      <c r="B194" t="str">
+        <v>(1) Viet Nga Group, (2) Việt Nga Group-HTX DVNN Bình Hiệp B</v>
+      </c>
+      <c r="C194" t="str">
+        <v>74865</v>
+      </c>
+      <c r="D194" t="str">
+        <v>795865683</v>
+      </c>
+      <c r="E194" t="str">
+        <v>TRƯƠNG THANH BÌNH</v>
+      </c>
+      <c r="F194" t="str">
+        <v>HỢP TÁC XÃ DỊCH VỤ NÔNG NGHIỆP BÌNH HIỆP B</v>
+      </c>
+      <c r="J194" t="str">
+        <v>Intensive rice production // Trồng lúa thâm canh</v>
+      </c>
+      <c r="K194" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="L194" t="str">
+        <v>Male // Nam</v>
+      </c>
+      <c r="M194" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="N194" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O194" t="str">
+        <v>0</v>
+      </c>
+      <c r="P194" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q194" t="str">
+        <v>0</v>
+      </c>
+      <c r="R194" t="str">
+        <v>0</v>
+      </c>
+      <c r="S194" t="str">
+        <v>0</v>
+      </c>
+      <c r="T194" t="str">
+        <v>0</v>
+      </c>
+      <c r="U194" t="str">
+        <v>4</v>
+      </c>
+      <c r="V194" t="str">
+        <v>0</v>
+      </c>
+      <c r="W194" t="str">
+        <v>3</v>
+      </c>
+      <c r="X194" t="str">
+        <v>4/10/26</v>
+      </c>
+      <c r="Y194" t="str">
+        <v>7/14/26</v>
+      </c>
+      <c r="Z194" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="AB194" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="AD194" t="str">
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="str">
+        <v>(355)</v>
+      </c>
+      <c r="B195" t="str">
+        <v>(1) Viet Nga Group, (2) Việt Nga Group-HTX DVNN Bình Hiệp B</v>
+      </c>
+      <c r="C195" t="str">
+        <v>74867</v>
+      </c>
+      <c r="D195" t="str">
+        <v>939898955</v>
+      </c>
+      <c r="E195" t="str">
+        <v>TRẦN VĂN MỐC</v>
+      </c>
+      <c r="F195" t="str">
+        <v>HỢP TÁC XÃ DỊCH VỤ NÔNG NGHIỆP BÌNH HIỆP B</v>
+      </c>
+      <c r="J195" t="str">
+        <v>Intensive rice production // Trồng lúa thâm canh</v>
+      </c>
+      <c r="K195" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="L195" t="str">
+        <v>Male // Nam</v>
+      </c>
+      <c r="M195" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="N195" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O195" t="str">
+        <v>0</v>
+      </c>
+      <c r="P195" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q195" t="str">
+        <v>0</v>
+      </c>
+      <c r="R195" t="str">
+        <v>0</v>
+      </c>
+      <c r="S195" t="str">
+        <v>0</v>
+      </c>
+      <c r="T195" t="str">
+        <v>0</v>
+      </c>
+      <c r="U195" t="str">
+        <v>3</v>
+      </c>
+      <c r="V195" t="str">
+        <v>0</v>
+      </c>
+      <c r="W195" t="str">
+        <v>2</v>
+      </c>
+      <c r="X195" t="str">
+        <v>4/10/26</v>
+      </c>
+      <c r="Y195" t="str">
+        <v>7/14/26</v>
+      </c>
+      <c r="Z195" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="AB195" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="AD195" t="str">
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="str">
+        <v>(358)</v>
+      </c>
+      <c r="B196" t="str">
+        <v>(1) Viet Nga Group, (2) Việt Nga Group-HTX DVNN Bình Hiệp B</v>
+      </c>
+      <c r="C196" t="str">
+        <v>74870</v>
+      </c>
+      <c r="D196" t="str">
+        <v>397478550</v>
+      </c>
+      <c r="E196" t="str">
+        <v>NGUYỄN THANH TUẤN</v>
+      </c>
+      <c r="F196" t="str">
+        <v>HỢP TÁC XÃ DỊCH VỤ NÔNG NGHIỆP BÌNH HIỆP B</v>
+      </c>
+      <c r="J196" t="str">
+        <v>Intensive rice production // Trồng lúa thâm canh</v>
+      </c>
+      <c r="K196" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="L196" t="str">
+        <v>Male // Nam</v>
+      </c>
+      <c r="M196" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="N196" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O196" t="str">
+        <v>0</v>
+      </c>
+      <c r="P196" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q196" t="str">
+        <v>0</v>
+      </c>
+      <c r="R196" t="str">
+        <v>0</v>
+      </c>
+      <c r="S196" t="str">
+        <v>0</v>
+      </c>
+      <c r="T196" t="str">
+        <v>0</v>
+      </c>
+      <c r="U196" t="str">
+        <v>3</v>
+      </c>
+      <c r="V196" t="str">
+        <v>0</v>
+      </c>
+      <c r="W196" t="str">
+        <v>2</v>
+      </c>
+      <c r="X196" t="str">
+        <v>4/10/26</v>
+      </c>
+      <c r="Y196" t="str">
+        <v>7/14/26</v>
+      </c>
+      <c r="Z196" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="AB196" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="AD196" t="str">
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="str">
+        <v>(359)</v>
+      </c>
+      <c r="B197" t="str">
+        <v>(1) Viet Nga Group, (2) Việt Nga Group-HTX DVNN Bình Hiệp B</v>
+      </c>
+      <c r="C197" t="str">
+        <v>74871</v>
+      </c>
+      <c r="D197" t="str">
+        <v>362126594</v>
+      </c>
+      <c r="E197" t="str">
+        <v>HỒ VĂN ÚT</v>
+      </c>
+      <c r="F197" t="str">
+        <v>HỢP TÁC XÃ DỊCH VỤ NÔNG NGHIỆP BÌNH HIỆP B</v>
+      </c>
+      <c r="J197" t="str">
+        <v>Intensive rice production // Trồng lúa thâm canh</v>
+      </c>
+      <c r="K197" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="L197" t="str">
+        <v>Male // Nam</v>
+      </c>
+      <c r="M197" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="N197" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O197" t="str">
+        <v>0</v>
+      </c>
+      <c r="P197" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q197" t="str">
+        <v>0</v>
+      </c>
+      <c r="R197" t="str">
+        <v>0</v>
+      </c>
+      <c r="S197" t="str">
+        <v>0</v>
+      </c>
+      <c r="T197" t="str">
+        <v>0</v>
+      </c>
+      <c r="U197" t="str">
+        <v>3</v>
+      </c>
+      <c r="V197" t="str">
+        <v>0</v>
+      </c>
+      <c r="W197" t="str">
+        <v>2</v>
+      </c>
+      <c r="X197" t="str">
+        <v>4/10/26</v>
+      </c>
+      <c r="Y197" t="str">
+        <v>7/14/26</v>
+      </c>
+      <c r="Z197" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="AB197" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="AD197" t="str">
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="str">
+        <v>(363)</v>
+      </c>
+      <c r="B198" t="str">
+        <v>(1) Viet Nga Group, (2) Việt Nga Group-HTX DVNN Bình Hiệp B</v>
+      </c>
+      <c r="C198" t="str">
+        <v>74875</v>
+      </c>
+      <c r="D198" t="str">
+        <v>383889900</v>
+      </c>
+      <c r="E198" t="str">
+        <v>TRẦN VĂN HẬU</v>
+      </c>
+      <c r="F198" t="str">
+        <v>HỢP TÁC XÃ DỊCH VỤ NÔNG NGHIỆP BÌNH HIỆP B</v>
+      </c>
+      <c r="J198" t="str">
+        <v>Intensive rice production // Trồng lúa thâm canh</v>
+      </c>
+      <c r="K198" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="L198" t="str">
+        <v>Male // Nam</v>
+      </c>
+      <c r="M198" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="N198" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O198" t="str">
+        <v>0</v>
+      </c>
+      <c r="P198" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q198" t="str">
+        <v>0</v>
+      </c>
+      <c r="R198" t="str">
+        <v>0</v>
+      </c>
+      <c r="S198" t="str">
+        <v>0</v>
+      </c>
+      <c r="T198" t="str">
+        <v>0</v>
+      </c>
+      <c r="U198" t="str">
+        <v>3</v>
+      </c>
+      <c r="V198" t="str">
+        <v>0</v>
+      </c>
+      <c r="W198" t="str">
+        <v>2</v>
+      </c>
+      <c r="X198" t="str">
+        <v>4/10/26</v>
+      </c>
+      <c r="Y198" t="str">
+        <v>7/14/26</v>
+      </c>
+      <c r="Z198" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="AB198" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="AD198" t="str">
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="str">
+        <v>(367)</v>
+      </c>
+      <c r="B199" t="str">
+        <v>(1) Viet Nga Group, (2) Việt Nga Group-HTX DVNN Bình Hiệp B</v>
+      </c>
+      <c r="C199" t="str">
+        <v>74879</v>
+      </c>
+      <c r="D199" t="str">
+        <v>939269451</v>
+      </c>
+      <c r="E199" t="str">
+        <v>TRẦN VĂN BÌNH</v>
+      </c>
+      <c r="F199" t="str">
+        <v>HỢP TÁC XÃ DỊCH VỤ NÔNG NGHIỆP BÌNH HIỆP B</v>
+      </c>
+      <c r="J199" t="str">
+        <v>Intensive rice production // Trồng lúa thâm canh</v>
+      </c>
+      <c r="K199" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="L199" t="str">
+        <v>Male // Nam</v>
+      </c>
+      <c r="M199" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="N199" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O199" t="str">
+        <v>0</v>
+      </c>
+      <c r="P199" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q199" t="str">
+        <v>0</v>
+      </c>
+      <c r="R199" t="str">
+        <v>0</v>
+      </c>
+      <c r="S199" t="str">
+        <v>0</v>
+      </c>
+      <c r="T199" t="str">
+        <v>0</v>
+      </c>
+      <c r="U199" t="str">
+        <v>3</v>
+      </c>
+      <c r="V199" t="str">
+        <v>0</v>
+      </c>
+      <c r="W199" t="str">
+        <v>2</v>
+      </c>
+      <c r="X199" t="str">
+        <v>4/10/26</v>
+      </c>
+      <c r="Y199" t="str">
+        <v>7/14/26</v>
+      </c>
+      <c r="Z199" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="AB199" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="AD199" t="str">
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="str">
+        <v>(372)</v>
+      </c>
+      <c r="B200" t="str">
+        <v>(1) Viet Nga Group, (2) Việt Nga Group-HTX DVNN Bình Hiệp B</v>
+      </c>
+      <c r="C200" t="str">
+        <v>74883</v>
+      </c>
+      <c r="D200" t="str">
+        <v>338401528</v>
+      </c>
+      <c r="E200" t="str">
+        <v>LÊ VĂN NGỢI</v>
+      </c>
+      <c r="F200" t="str">
+        <v>HỢP TÁC XÃ DỊCH VỤ NÔNG NGHIỆP BÌNH HIỆP B</v>
+      </c>
+      <c r="J200" t="str">
+        <v>Intensive rice production // Trồng lúa thâm canh</v>
+      </c>
+      <c r="K200" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="L200" t="str">
+        <v>Male // Nam</v>
+      </c>
+      <c r="M200" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="N200" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O200" t="str">
+        <v>0</v>
+      </c>
+      <c r="P200" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q200" t="str">
+        <v>0</v>
+      </c>
+      <c r="R200" t="str">
+        <v>0</v>
+      </c>
+      <c r="S200" t="str">
+        <v>0</v>
+      </c>
+      <c r="T200" t="str">
+        <v>0</v>
+      </c>
+      <c r="U200" t="str">
+        <v>4</v>
+      </c>
+      <c r="V200" t="str">
+        <v>0</v>
+      </c>
+      <c r="W200" t="str">
+        <v>3</v>
+      </c>
+      <c r="X200" t="str">
+        <v>4/10/26</v>
+      </c>
+      <c r="Y200" t="str">
+        <v>7/14/26</v>
+      </c>
+      <c r="Z200" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="AB200" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="AD200" t="str">
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="str">
+        <v>(374)</v>
+      </c>
+      <c r="B201" t="str">
+        <v>(1) Viet Nga Group, (2) Việt Nga Group-HTX DVNN Bình Hiệp B</v>
+      </c>
+      <c r="C201" t="str">
+        <v>74885</v>
+      </c>
+      <c r="D201" t="str">
+        <v>983702182</v>
+      </c>
+      <c r="E201" t="str">
+        <v>NGUYỄN VĂN LONG</v>
+      </c>
+      <c r="F201" t="str">
+        <v>HỢP TÁC XÃ DỊCH VỤ NÔNG NGHIỆP BÌNH HIỆP B</v>
+      </c>
+      <c r="J201" t="str">
+        <v>Intensive rice production // Trồng lúa thâm canh</v>
+      </c>
+      <c r="K201" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="L201" t="str">
+        <v>Male // Nam</v>
+      </c>
+      <c r="M201" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="N201" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O201" t="str">
+        <v>0</v>
+      </c>
+      <c r="P201" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q201" t="str">
+        <v>0</v>
+      </c>
+      <c r="R201" t="str">
+        <v>0</v>
+      </c>
+      <c r="S201" t="str">
+        <v>0</v>
+      </c>
+      <c r="T201" t="str">
+        <v>0</v>
+      </c>
+      <c r="U201" t="str">
+        <v>4</v>
+      </c>
+      <c r="V201" t="str">
+        <v>0</v>
+      </c>
+      <c r="W201" t="str">
+        <v>3</v>
+      </c>
+      <c r="X201" t="str">
+        <v>4/10/26</v>
+      </c>
+      <c r="Y201" t="str">
+        <v>7/14/26</v>
+      </c>
+      <c r="Z201" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="AB201" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="AD201" t="str">
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="str">
+        <v>(376)</v>
+      </c>
+      <c r="B202" t="str">
+        <v>(1) Viet Nga Group, (2) Việt Nga Group-HTX DVNN Bình Hiệp B</v>
+      </c>
+      <c r="C202" t="str">
+        <v>74887</v>
+      </c>
+      <c r="D202" t="str">
+        <v>356634518</v>
+      </c>
+      <c r="E202" t="str">
+        <v>NGUYỄN VĂN ĐÀNH</v>
+      </c>
+      <c r="F202" t="str">
+        <v>HỢP TÁC XÃ DỊCH VỤ NÔNG NGHIỆP BÌNH HIỆP B</v>
+      </c>
+      <c r="J202" t="str">
+        <v>Intensive rice production // Trồng lúa thâm canh</v>
+      </c>
+      <c r="K202" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="L202" t="str">
+        <v>Male // Nam</v>
+      </c>
+      <c r="M202" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="N202" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O202" t="str">
+        <v>0</v>
+      </c>
+      <c r="P202" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q202" t="str">
+        <v>0</v>
+      </c>
+      <c r="R202" t="str">
+        <v>0</v>
+      </c>
+      <c r="S202" t="str">
+        <v>0</v>
+      </c>
+      <c r="T202" t="str">
+        <v>0</v>
+      </c>
+      <c r="U202" t="str">
+        <v>4</v>
+      </c>
+      <c r="V202" t="str">
+        <v>0</v>
+      </c>
+      <c r="W202" t="str">
+        <v>3</v>
+      </c>
+      <c r="X202" t="str">
+        <v>4/10/26</v>
+      </c>
+      <c r="Y202" t="str">
+        <v>7/14/26</v>
+      </c>
+      <c r="Z202" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="AB202" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="AD202" t="str">
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="str">
+        <v>(377)</v>
+      </c>
+      <c r="B203" t="str">
+        <v>(1) Viet Nga Group, (2) Việt Nga Group-HTX DVNN Bình Hiệp B</v>
+      </c>
+      <c r="C203" t="str">
+        <v>74888</v>
+      </c>
+      <c r="D203" t="str">
+        <v>987052029</v>
+      </c>
+      <c r="E203" t="str">
+        <v>NGUYỄN THỊ DIỄM</v>
+      </c>
+      <c r="F203" t="str">
+        <v>HỢP TÁC XÃ DỊCH VỤ NÔNG NGHIỆP BÌNH HIỆP B</v>
+      </c>
+      <c r="J203" t="str">
+        <v>Intensive rice production // Trồng lúa thâm canh</v>
+      </c>
+      <c r="K203" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="L203" t="str">
+        <v>Female // Nữ</v>
+      </c>
+      <c r="M203" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="N203" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O203" t="str">
+        <v>1</v>
+      </c>
+      <c r="P203" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q203" t="str">
+        <v>0</v>
+      </c>
+      <c r="R203" t="str">
+        <v>0</v>
+      </c>
+      <c r="S203" t="str">
+        <v>0</v>
+      </c>
+      <c r="T203" t="str">
+        <v>0</v>
+      </c>
+      <c r="U203" t="str">
+        <v>3</v>
+      </c>
+      <c r="V203" t="str">
+        <v>0</v>
+      </c>
+      <c r="W203" t="str">
+        <v>1</v>
+      </c>
+      <c r="X203" t="str">
+        <v>4/10/26</v>
+      </c>
+      <c r="Y203" t="str">
+        <v>7/14/26</v>
+      </c>
+      <c r="Z203" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="AB203" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="AD203" t="str">
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="str">
+        <v>(380)</v>
+      </c>
+      <c r="B204" t="str">
+        <v>(1) Viet Nga Group, (2) Việt Nga Group-HTX DVNN Bình Hiệp B</v>
+      </c>
+      <c r="C204" t="str">
+        <v>74891</v>
+      </c>
+      <c r="D204" t="str">
+        <v>338659732</v>
+      </c>
+      <c r="E204" t="str">
+        <v>NGUYỄN VĂN HIẾU</v>
+      </c>
+      <c r="F204" t="str">
+        <v>HỢP TÁC XÃ DỊCH VỤ NÔNG NGHIỆP BÌNH HIỆP B</v>
+      </c>
+      <c r="J204" t="str">
+        <v>Intensive rice production // Trồng lúa thâm canh</v>
+      </c>
+      <c r="K204" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="L204" t="str">
+        <v>Male // Nam</v>
+      </c>
+      <c r="M204" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="N204" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O204" t="str">
+        <v>0</v>
+      </c>
+      <c r="P204" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q204" t="str">
+        <v>0</v>
+      </c>
+      <c r="R204" t="str">
+        <v>0</v>
+      </c>
+      <c r="S204" t="str">
+        <v>0</v>
+      </c>
+      <c r="T204" t="str">
+        <v>0</v>
+      </c>
+      <c r="U204" t="str">
+        <v>5</v>
+      </c>
+      <c r="V204" t="str">
+        <v>0</v>
+      </c>
+      <c r="W204" t="str">
+        <v>2</v>
+      </c>
+      <c r="X204" t="str">
+        <v>4/10/26</v>
+      </c>
+      <c r="Y204" t="str">
+        <v>7/14/26</v>
+      </c>
+      <c r="Z204" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="AB204" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="AD204" t="str">
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="str">
+        <v>(381)</v>
+      </c>
+      <c r="B205" t="str">
+        <v>(1) Viet Nga Group, (2) Việt Nga Group-HTX DVNN Bình Hiệp B</v>
+      </c>
+      <c r="C205" t="str">
+        <v>74892</v>
+      </c>
+      <c r="D205" t="str">
+        <v>934030306</v>
+      </c>
+      <c r="E205" t="str">
+        <v>LÊ VĂN HỢP</v>
+      </c>
+      <c r="F205" t="str">
+        <v>HỢP TÁC XÃ DỊCH VỤ NÔNG NGHIỆP BÌNH HIỆP B</v>
+      </c>
+      <c r="J205" t="str">
+        <v>Intensive rice production // Trồng lúa thâm canh</v>
+      </c>
+      <c r="K205" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="L205" t="str">
+        <v>Male // Nam</v>
+      </c>
+      <c r="M205" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="N205" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O205" t="str">
+        <v>0</v>
+      </c>
+      <c r="P205" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q205" t="str">
+        <v>0</v>
+      </c>
+      <c r="R205" t="str">
+        <v>0</v>
+      </c>
+      <c r="S205" t="str">
+        <v>0</v>
+      </c>
+      <c r="T205" t="str">
+        <v>0</v>
+      </c>
+      <c r="U205" t="str">
+        <v>5</v>
+      </c>
+      <c r="V205" t="str">
+        <v>0</v>
+      </c>
+      <c r="W205" t="str">
+        <v>4</v>
+      </c>
+      <c r="X205" t="str">
+        <v>4/10/26</v>
+      </c>
+      <c r="Y205" t="str">
+        <v>7/14/26</v>
+      </c>
+      <c r="Z205" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="AB205" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="AD205" t="str">
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="str">
+        <v>(387)</v>
+      </c>
+      <c r="B206" t="str">
+        <v>(1) Viet Nga Group, (2) Việt Nga Group-HTX DVNN Bình Hiệp B</v>
+      </c>
+      <c r="C206" t="str">
+        <v>74898</v>
+      </c>
+      <c r="D206" t="str">
+        <v>905586404</v>
+      </c>
+      <c r="E206" t="str">
+        <v>NGUYỄN VĂN CHÍNH</v>
+      </c>
+      <c r="F206" t="str">
+        <v>HỢP TÁC XÃ DỊCH VỤ NÔNG NGHIỆP BÌNH HIỆP B</v>
+      </c>
+      <c r="J206" t="str">
+        <v>Intensive rice production // Trồng lúa thâm canh</v>
+      </c>
+      <c r="K206" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="L206" t="str">
+        <v>Male // Nam</v>
+      </c>
+      <c r="M206" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="N206" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O206" t="str">
+        <v>0</v>
+      </c>
+      <c r="P206" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q206" t="str">
+        <v>0</v>
+      </c>
+      <c r="R206" t="str">
+        <v>0</v>
+      </c>
+      <c r="S206" t="str">
+        <v>0</v>
+      </c>
+      <c r="T206" t="str">
+        <v>0</v>
+      </c>
+      <c r="U206" t="str">
+        <v>5</v>
+      </c>
+      <c r="V206" t="str">
+        <v>0</v>
+      </c>
+      <c r="W206" t="str">
+        <v>4</v>
+      </c>
+      <c r="X206" t="str">
+        <v>4/10/26</v>
+      </c>
+      <c r="Y206" t="str">
+        <v>7/14/26</v>
+      </c>
+      <c r="Z206" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="AB206" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="AD206" t="str">
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="str">
+        <v>(388)</v>
+      </c>
+      <c r="B207" t="str">
+        <v>(1) Viet Nga Group, (2) Việt Nga Group-HTX DVNN Bình Hiệp B</v>
+      </c>
+      <c r="C207" t="str">
+        <v>74899</v>
+      </c>
+      <c r="D207" t="str">
+        <v>929318437</v>
+      </c>
+      <c r="E207" t="str">
+        <v>LÂM VĂN PHỤNG</v>
+      </c>
+      <c r="F207" t="str">
+        <v>HỢP TÁC XÃ DỊCH VỤ NÔNG NGHIỆP BÌNH HIỆP B</v>
+      </c>
+      <c r="J207" t="str">
+        <v>Intensive rice production // Trồng lúa thâm canh</v>
+      </c>
+      <c r="K207" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="L207" t="str">
+        <v>Male // Nam</v>
+      </c>
+      <c r="M207" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="N207" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O207" t="str">
+        <v>0</v>
+      </c>
+      <c r="P207" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q207" t="str">
+        <v>0</v>
+      </c>
+      <c r="R207" t="str">
+        <v>0</v>
+      </c>
+      <c r="S207" t="str">
+        <v>0</v>
+      </c>
+      <c r="T207" t="str">
+        <v>0</v>
+      </c>
+      <c r="U207" t="str">
+        <v>3</v>
+      </c>
+      <c r="V207" t="str">
+        <v>0</v>
+      </c>
+      <c r="W207" t="str">
+        <v>2</v>
+      </c>
+      <c r="X207" t="str">
+        <v>4/10/26</v>
+      </c>
+      <c r="Y207" t="str">
+        <v>7/14/26</v>
+      </c>
+      <c r="Z207" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="AB207" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="AD207" t="str">
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="str">
+        <v>(389)</v>
+      </c>
+      <c r="B208" t="str">
+        <v>(1) Viet Nga Group, (2) Việt Nga Group-HTX DVNN Bình Hiệp B</v>
+      </c>
+      <c r="C208" t="str">
+        <v>74900</v>
+      </c>
+      <c r="D208" t="str">
+        <v>383006807</v>
+      </c>
+      <c r="E208" t="str">
+        <v>PHẠM HỮU LỢI</v>
+      </c>
+      <c r="F208" t="str">
+        <v>HỢP TÁC XÃ DỊCH VỤ NÔNG NGHIỆP BÌNH HIỆP B</v>
+      </c>
+      <c r="J208" t="str">
+        <v>Intensive rice production // Trồng lúa thâm canh</v>
+      </c>
+      <c r="K208" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="L208" t="str">
+        <v>Male // Nam</v>
+      </c>
+      <c r="M208" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="N208" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O208" t="str">
+        <v>0</v>
+      </c>
+      <c r="P208" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q208" t="str">
+        <v>0</v>
+      </c>
+      <c r="R208" t="str">
+        <v>0</v>
+      </c>
+      <c r="S208" t="str">
+        <v>0</v>
+      </c>
+      <c r="T208" t="str">
+        <v>0</v>
+      </c>
+      <c r="U208" t="str">
+        <v>3</v>
+      </c>
+      <c r="V208" t="str">
+        <v>0</v>
+      </c>
+      <c r="W208" t="str">
+        <v>2</v>
+      </c>
+      <c r="X208" t="str">
+        <v>4/10/26</v>
+      </c>
+      <c r="Y208" t="str">
+        <v>7/14/26</v>
+      </c>
+      <c r="Z208" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="AB208" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="AD208" t="str">
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="str">
+        <v>(393)</v>
+      </c>
+      <c r="B209" t="str">
+        <v>(1) Viet Nga Group, (2) Việt Nga Group-HTX DVNN Bình Hiệp B</v>
+      </c>
+      <c r="C209" t="str">
+        <v>74905</v>
+      </c>
+      <c r="D209" t="str">
+        <v>337961917</v>
+      </c>
+      <c r="E209" t="str">
+        <v>PHẠM THANH NHÂN</v>
+      </c>
+      <c r="F209" t="str">
+        <v>HỢP TÁC XÃ DỊCH VỤ NÔNG NGHIỆP BÌNH HIỆP B</v>
+      </c>
+      <c r="J209" t="str">
+        <v>Intensive rice production // Trồng lúa thâm canh</v>
+      </c>
+      <c r="K209" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="L209" t="str">
+        <v>Male // Nam</v>
+      </c>
+      <c r="M209" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="N209" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O209" t="str">
+        <v>0</v>
+      </c>
+      <c r="P209" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q209" t="str">
+        <v>0</v>
+      </c>
+      <c r="R209" t="str">
+        <v>0</v>
+      </c>
+      <c r="S209" t="str">
+        <v>0</v>
+      </c>
+      <c r="T209" t="str">
+        <v>0</v>
+      </c>
+      <c r="U209" t="str">
+        <v>4</v>
+      </c>
+      <c r="V209" t="str">
+        <v>0</v>
+      </c>
+      <c r="W209" t="str">
+        <v>3</v>
+      </c>
+      <c r="X209" t="str">
+        <v>4/10/26</v>
+      </c>
+      <c r="Y209" t="str">
+        <v>7/14/26</v>
+      </c>
+      <c r="Z209" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="AB209" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="AD209" t="str">
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="str">
+        <v>(401)</v>
+      </c>
+      <c r="B210" t="str">
+        <v>(1) Viet Nga Group, (2) Việt Nga Group-HTX DVNN Bình Hiệp B</v>
+      </c>
+      <c r="C210" t="str">
+        <v>74913</v>
+      </c>
+      <c r="D210" t="str">
+        <v>825525367</v>
+      </c>
+      <c r="E210" t="str">
+        <v>NGUYỄN VĂN KHỠI</v>
+      </c>
+      <c r="F210" t="str">
+        <v>HỢP TÁC XÃ DỊCH VỤ NÔNG NGHIỆP BÌNH HIỆP B</v>
+      </c>
+      <c r="J210" t="str">
+        <v>Intensive rice production // Trồng lúa thâm canh</v>
+      </c>
+      <c r="K210" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="L210" t="str">
+        <v>Male // Nam</v>
+      </c>
+      <c r="M210" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="N210" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O210" t="str">
+        <v>0</v>
+      </c>
+      <c r="P210" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q210" t="str">
+        <v>0</v>
+      </c>
+      <c r="R210" t="str">
+        <v>0</v>
+      </c>
+      <c r="S210" t="str">
+        <v>0</v>
+      </c>
+      <c r="T210" t="str">
+        <v>0</v>
+      </c>
+      <c r="U210" t="str">
+        <v>5</v>
+      </c>
+      <c r="V210" t="str">
+        <v>0</v>
+      </c>
+      <c r="W210" t="str">
+        <v>4</v>
+      </c>
+      <c r="X210" t="str">
+        <v>4/10/26</v>
+      </c>
+      <c r="Y210" t="str">
+        <v>7/14/26</v>
+      </c>
+      <c r="Z210" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="AB210" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="AD210" t="str">
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="str">
+        <v>(402)</v>
+      </c>
+      <c r="B211" t="str">
+        <v>(1) Viet Nga Group, (2) Việt Nga Group-HTX DVNN Bình Hiệp B</v>
+      </c>
+      <c r="C211" t="str">
+        <v>74914</v>
+      </c>
+      <c r="D211" t="str">
+        <v>983848841</v>
+      </c>
+      <c r="E211" t="str">
+        <v>HUỲNH NGỌC DŨNG</v>
+      </c>
+      <c r="F211" t="str">
+        <v>HỢP TÁC XÃ DỊCH VỤ NÔNG NGHIỆP BÌNH HIỆP B</v>
+      </c>
+      <c r="J211" t="str">
+        <v>Intensive rice production // Trồng lúa thâm canh</v>
+      </c>
+      <c r="K211" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="L211" t="str">
+        <v>Male // Nam</v>
+      </c>
+      <c r="M211" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="N211" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O211" t="str">
+        <v>0</v>
+      </c>
+      <c r="P211" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q211" t="str">
+        <v>0</v>
+      </c>
+      <c r="R211" t="str">
+        <v>0</v>
+      </c>
+      <c r="S211" t="str">
+        <v>0</v>
+      </c>
+      <c r="T211" t="str">
+        <v>0</v>
+      </c>
+      <c r="U211" t="str">
+        <v>6</v>
+      </c>
+      <c r="V211" t="str">
+        <v>0</v>
+      </c>
+      <c r="W211" t="str">
+        <v>5</v>
+      </c>
+      <c r="X211" t="str">
+        <v>4/10/26</v>
+      </c>
+      <c r="Y211" t="str">
+        <v>7/14/26</v>
+      </c>
+      <c r="Z211" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="AB211" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="AD211" t="str">
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="str">
+        <v>(410)</v>
+      </c>
+      <c r="B212" t="str">
+        <v>(1) Viet Nga Group, (2) Việt Nga Group-HTX DVNN Bình Hiệp B</v>
+      </c>
+      <c r="C212" t="str">
+        <v>74922</v>
+      </c>
+      <c r="D212" t="str">
+        <v>345567224</v>
+      </c>
+      <c r="E212" t="str">
+        <v>HUỲNH NGỌC ẪN</v>
+      </c>
+      <c r="F212" t="str">
+        <v>HỢP TÁC XÃ DỊCH VỤ NÔNG NGHIỆP BÌNH HIỆP B</v>
+      </c>
+      <c r="J212" t="str">
+        <v>Intensive rice production // Trồng lúa thâm canh</v>
+      </c>
+      <c r="K212" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="L212" t="str">
+        <v>Male // Nam</v>
+      </c>
+      <c r="M212" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="N212" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O212" t="str">
+        <v>0</v>
+      </c>
+      <c r="P212" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q212" t="str">
+        <v>0</v>
+      </c>
+      <c r="R212" t="str">
+        <v>0</v>
+      </c>
+      <c r="S212" t="str">
+        <v>0</v>
+      </c>
+      <c r="T212" t="str">
+        <v>0</v>
+      </c>
+      <c r="U212" t="str">
+        <v>5</v>
+      </c>
+      <c r="V212" t="str">
+        <v>0</v>
+      </c>
+      <c r="W212" t="str">
+        <v>3</v>
+      </c>
+      <c r="X212" t="str">
+        <v>4/10/26</v>
+      </c>
+      <c r="Y212" t="str">
+        <v>7/14/26</v>
+      </c>
+      <c r="Z212" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="AB212" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="AD212" t="str">
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="str">
+        <v>(413)</v>
+      </c>
+      <c r="B213" t="str">
+        <v>(1) Viet Nga Group, (2) Việt Nga Group-HTX DVNN Bình Hiệp B</v>
+      </c>
+      <c r="C213" t="str">
+        <v>74925</v>
+      </c>
+      <c r="D213" t="str">
+        <v>366520832</v>
+      </c>
+      <c r="E213" t="str">
+        <v>LÊ VĂN HỚN</v>
+      </c>
+      <c r="F213" t="str">
+        <v>HỢP TÁC XÃ DỊCH VỤ NÔNG NGHIỆP BÌNH HIỆP B</v>
+      </c>
+      <c r="J213" t="str">
+        <v>Intensive rice production // Trồng lúa thâm canh</v>
+      </c>
+      <c r="K213" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="L213" t="str">
+        <v>Male // Nam</v>
+      </c>
+      <c r="M213" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="N213" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O213" t="str">
+        <v>0</v>
+      </c>
+      <c r="P213" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q213" t="str">
+        <v>0</v>
+      </c>
+      <c r="R213" t="str">
+        <v>0</v>
+      </c>
+      <c r="S213" t="str">
+        <v>0</v>
+      </c>
+      <c r="T213" t="str">
+        <v>0</v>
+      </c>
+      <c r="U213" t="str">
+        <v>3</v>
+      </c>
+      <c r="V213" t="str">
+        <v>0</v>
+      </c>
+      <c r="W213" t="str">
+        <v>2</v>
+      </c>
+      <c r="X213" t="str">
+        <v>4/10/26</v>
+      </c>
+      <c r="Y213" t="str">
+        <v>7/14/26</v>
+      </c>
+      <c r="Z213" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="AB213" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="AD213" t="str">
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="str">
+        <v>(414)</v>
+      </c>
+      <c r="B214" t="str">
+        <v>(1) Viet Nga Group, (2) Việt Nga Group-HTX DVNN Bình Hiệp B</v>
+      </c>
+      <c r="C214" t="str">
+        <v>74926</v>
+      </c>
+      <c r="D214" t="str">
+        <v>366495218</v>
+      </c>
+      <c r="E214" t="str">
+        <v>HUỲNH VĂN VUI</v>
+      </c>
+      <c r="F214" t="str">
+        <v>HỢP TÁC XÃ DỊCH VỤ NÔNG NGHIỆP BÌNH HIỆP B</v>
+      </c>
+      <c r="J214" t="str">
+        <v>Intensive rice production // Trồng lúa thâm canh</v>
+      </c>
+      <c r="K214" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="L214" t="str">
+        <v>Male // Nam</v>
+      </c>
+      <c r="M214" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="N214" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O214" t="str">
+        <v>0</v>
+      </c>
+      <c r="P214" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q214" t="str">
+        <v>0</v>
+      </c>
+      <c r="R214" t="str">
+        <v>0</v>
+      </c>
+      <c r="S214" t="str">
+        <v>0</v>
+      </c>
+      <c r="T214" t="str">
+        <v>0</v>
+      </c>
+      <c r="U214" t="str">
+        <v>3</v>
+      </c>
+      <c r="V214" t="str">
+        <v>0</v>
+      </c>
+      <c r="W214" t="str">
+        <v>2</v>
+      </c>
+      <c r="X214" t="str">
+        <v>4/10/26</v>
+      </c>
+      <c r="Y214" t="str">
+        <v>7/14/26</v>
+      </c>
+      <c r="Z214" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="AB214" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="AD214" t="str">
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="str">
+        <v>(415)</v>
+      </c>
+      <c r="B215" t="str">
+        <v>(1) Viet Nga Group, (2) Việt Nga Group-HTX DVNN Bình Hiệp B</v>
+      </c>
+      <c r="C215" t="str">
+        <v>74927</v>
+      </c>
+      <c r="D215" t="str">
+        <v>965981959</v>
+      </c>
+      <c r="E215" t="str">
+        <v>NGUYỄN VĂN XÃ</v>
+      </c>
+      <c r="F215" t="str">
+        <v>HỢP TÁC XÃ DỊCH VỤ NÔNG NGHIỆP BÌNH HIỆP B</v>
+      </c>
+      <c r="J215" t="str">
+        <v>Intensive rice production // Trồng lúa thâm canh</v>
+      </c>
+      <c r="K215" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="L215" t="str">
+        <v>Male // Nam</v>
+      </c>
+      <c r="M215" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="N215" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O215" t="str">
+        <v>0</v>
+      </c>
+      <c r="P215" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q215" t="str">
+        <v>0</v>
+      </c>
+      <c r="R215" t="str">
+        <v>0</v>
+      </c>
+      <c r="S215" t="str">
+        <v>0</v>
+      </c>
+      <c r="T215" t="str">
+        <v>0</v>
+      </c>
+      <c r="U215" t="str">
+        <v>5</v>
+      </c>
+      <c r="V215" t="str">
+        <v>0</v>
+      </c>
+      <c r="W215" t="str">
+        <v>4</v>
+      </c>
+      <c r="X215" t="str">
+        <v>4/10/26</v>
+      </c>
+      <c r="Y215" t="str">
+        <v>7/14/26</v>
+      </c>
+      <c r="Z215" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="AB215" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="AD215" t="str">
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="str">
+        <v>(416)</v>
+      </c>
+      <c r="B216" t="str">
+        <v>(1) Viet Nga Group, (2) Việt Nga Group-HTX DVNN Bình Hiệp B</v>
+      </c>
+      <c r="C216" t="str">
+        <v>74928</v>
+      </c>
+      <c r="D216" t="str">
+        <v>939063664</v>
+      </c>
+      <c r="E216" t="str">
+        <v>LÊ HỮU TIỀN</v>
+      </c>
+      <c r="F216" t="str">
+        <v>HỢP TÁC XÃ DỊCH VỤ NÔNG NGHIỆP BÌNH HIỆP B</v>
+      </c>
+      <c r="J216" t="str">
+        <v>Intensive rice production // Trồng lúa thâm canh</v>
+      </c>
+      <c r="K216" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="L216" t="str">
+        <v>Male // Nam</v>
+      </c>
+      <c r="M216" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="N216" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O216" t="str">
+        <v>0</v>
+      </c>
+      <c r="P216" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q216" t="str">
+        <v>0</v>
+      </c>
+      <c r="R216" t="str">
+        <v>0</v>
+      </c>
+      <c r="S216" t="str">
+        <v>0</v>
+      </c>
+      <c r="T216" t="str">
+        <v>0</v>
+      </c>
+      <c r="U216" t="str">
+        <v>6</v>
+      </c>
+      <c r="V216" t="str">
+        <v>0</v>
+      </c>
+      <c r="W216" t="str">
+        <v>5</v>
+      </c>
+      <c r="X216" t="str">
+        <v>4/10/26</v>
+      </c>
+      <c r="Y216" t="str">
+        <v>7/14/26</v>
+      </c>
+      <c r="Z216" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="AB216" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="AD216" t="str">
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="str">
+        <v>(417)</v>
+      </c>
+      <c r="B217" t="str">
+        <v>(1) Viet Nga Group, (2) Việt Nga Group-HTX DVNN Bình Hiệp B</v>
+      </c>
+      <c r="C217" t="str">
+        <v>74929</v>
+      </c>
+      <c r="D217" t="str">
+        <v>397912231</v>
+      </c>
+      <c r="E217" t="str">
+        <v>NGUYỄN VĂN TÈO</v>
+      </c>
+      <c r="F217" t="str">
+        <v>HỢP TÁC XÃ DỊCH VỤ NÔNG NGHIỆP BÌNH HIỆP B</v>
+      </c>
+      <c r="J217" t="str">
+        <v>Intensive rice production // Trồng lúa thâm canh</v>
+      </c>
+      <c r="K217" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="L217" t="str">
+        <v>Male // Nam</v>
+      </c>
+      <c r="M217" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="N217" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O217" t="str">
+        <v>0</v>
+      </c>
+      <c r="P217" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q217" t="str">
+        <v>0</v>
+      </c>
+      <c r="R217" t="str">
+        <v>0</v>
+      </c>
+      <c r="S217" t="str">
+        <v>0</v>
+      </c>
+      <c r="T217" t="str">
+        <v>0</v>
+      </c>
+      <c r="U217" t="str">
+        <v>5</v>
+      </c>
+      <c r="V217" t="str">
+        <v>0</v>
+      </c>
+      <c r="W217" t="str">
+        <v>4</v>
+      </c>
+      <c r="X217" t="str">
+        <v>4/10/26</v>
+      </c>
+      <c r="Y217" t="str">
+        <v>7/14/26</v>
+      </c>
+      <c r="Z217" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="AB217" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="AD217" t="str">
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="str">
+        <v>(418)</v>
+      </c>
+      <c r="B218" t="str">
+        <v>(1) Viet Nga Group, (2) Việt Nga Group-HTX DVNN Bình Hiệp B</v>
+      </c>
+      <c r="C218" t="str">
+        <v>74930</v>
+      </c>
+      <c r="D218" t="str">
+        <v>369183344</v>
+      </c>
+      <c r="E218" t="str">
+        <v>NGUYỄN THỊ ĐÀO</v>
+      </c>
+      <c r="F218" t="str">
+        <v>HỢP TÁC XÃ DỊCH VỤ NÔNG NGHIỆP BÌNH HIỆP B</v>
+      </c>
+      <c r="J218" t="str">
+        <v>Intensive rice production // Trồng lúa thâm canh</v>
+      </c>
+      <c r="K218" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="L218" t="str">
+        <v>Female // Nữ</v>
+      </c>
+      <c r="M218" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="N218" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O218" t="str">
+        <v>1</v>
+      </c>
+      <c r="P218" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q218" t="str">
+        <v>0</v>
+      </c>
+      <c r="R218" t="str">
+        <v>0</v>
+      </c>
+      <c r="S218" t="str">
+        <v>0</v>
+      </c>
+      <c r="T218" t="str">
+        <v>0</v>
+      </c>
+      <c r="U218" t="str">
+        <v>4</v>
+      </c>
+      <c r="V218" t="str">
+        <v>0</v>
+      </c>
+      <c r="W218" t="str">
+        <v>3</v>
+      </c>
+      <c r="X218" t="str">
+        <v>4/10/26</v>
+      </c>
+      <c r="Y218" t="str">
+        <v>7/14/26</v>
+      </c>
+      <c r="Z218" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="AB218" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="AD218" t="str">
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="str">
+        <v>(420)</v>
+      </c>
+      <c r="B219" t="str">
+        <v>(1) Viet Nga Group, (2) Việt Nga Group-HTX DVNN Bình Hiệp B</v>
+      </c>
+      <c r="C219" t="str">
+        <v>74932</v>
+      </c>
+      <c r="D219" t="str">
+        <v>984202438</v>
+      </c>
+      <c r="E219" t="str">
+        <v>BÙI VĂN XƯỜNG</v>
+      </c>
+      <c r="F219" t="str">
+        <v>HỢP TÁC XÃ DỊCH VỤ NÔNG NGHIỆP BÌNH HIỆP B</v>
+      </c>
+      <c r="J219" t="str">
+        <v>Intensive rice production // Trồng lúa thâm canh</v>
+      </c>
+      <c r="K219" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="L219" t="str">
+        <v>Male // Nam</v>
+      </c>
+      <c r="M219" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="N219" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O219" t="str">
+        <v>0</v>
+      </c>
+      <c r="P219" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q219" t="str">
+        <v>0</v>
+      </c>
+      <c r="R219" t="str">
+        <v>0</v>
+      </c>
+      <c r="S219" t="str">
+        <v>0</v>
+      </c>
+      <c r="T219" t="str">
+        <v>0</v>
+      </c>
+      <c r="U219" t="str">
+        <v>3</v>
+      </c>
+      <c r="V219" t="str">
+        <v>0</v>
+      </c>
+      <c r="W219" t="str">
+        <v>2</v>
+      </c>
+      <c r="X219" t="str">
+        <v>4/10/26</v>
+      </c>
+      <c r="Y219" t="str">
+        <v>7/14/26</v>
+      </c>
+      <c r="Z219" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="AB219" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="AD219" t="str">
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="str">
+        <v>(421)</v>
+      </c>
+      <c r="B220" t="str">
+        <v>(1) Viet Nga Group, (2) Việt Nga Group-HTX DVNN Bình Hiệp B</v>
+      </c>
+      <c r="C220" t="str">
+        <v>74933</v>
+      </c>
+      <c r="D220" t="str">
+        <v>397378799</v>
+      </c>
+      <c r="E220" t="str">
+        <v>NGUYỄN TRUNG TẤN</v>
+      </c>
+      <c r="F220" t="str">
+        <v>HỢP TÁC XÃ DỊCH VỤ NÔNG NGHIỆP BÌNH HIỆP B</v>
+      </c>
+      <c r="J220" t="str">
+        <v>Intensive rice production // Trồng lúa thâm canh</v>
+      </c>
+      <c r="K220" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="L220" t="str">
+        <v>Male // Nam</v>
+      </c>
+      <c r="M220" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="N220" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O220" t="str">
+        <v>0</v>
+      </c>
+      <c r="P220" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q220" t="str">
+        <v>0</v>
+      </c>
+      <c r="R220" t="str">
+        <v>0</v>
+      </c>
+      <c r="S220" t="str">
+        <v>0</v>
+      </c>
+      <c r="T220" t="str">
+        <v>0</v>
+      </c>
+      <c r="U220" t="str">
+        <v>3</v>
+      </c>
+      <c r="V220" t="str">
+        <v>0</v>
+      </c>
+      <c r="W220" t="str">
+        <v>2</v>
+      </c>
+      <c r="X220" t="str">
+        <v>4/10/26</v>
+      </c>
+      <c r="Y220" t="str">
+        <v>7/14/26</v>
+      </c>
+      <c r="Z220" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="AB220" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="AD220" t="str">
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="str">
+        <v>(423)</v>
+      </c>
+      <c r="B221" t="str">
+        <v>(1) Viet Nga Group, (2) Việt Nga Group-HTX DVNN Bình Hiệp B</v>
+      </c>
+      <c r="C221" t="str">
+        <v>74935</v>
+      </c>
+      <c r="D221" t="str">
+        <v>363328365</v>
+      </c>
+      <c r="E221" t="str">
+        <v>BÙI VĂN PHỤ</v>
+      </c>
+      <c r="F221" t="str">
+        <v>HỢP TÁC XÃ DỊCH VỤ NÔNG NGHIỆP BÌNH HIỆP B</v>
+      </c>
+      <c r="J221" t="str">
+        <v>Intensive rice production // Trồng lúa thâm canh</v>
+      </c>
+      <c r="K221" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="L221" t="str">
+        <v>Male // Nam</v>
+      </c>
+      <c r="M221" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="N221" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O221" t="str">
+        <v>0</v>
+      </c>
+      <c r="P221" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q221" t="str">
+        <v>0</v>
+      </c>
+      <c r="R221" t="str">
+        <v>0</v>
+      </c>
+      <c r="S221" t="str">
+        <v>0</v>
+      </c>
+      <c r="T221" t="str">
+        <v>0</v>
+      </c>
+      <c r="U221" t="str">
+        <v>6</v>
+      </c>
+      <c r="V221" t="str">
+        <v>0</v>
+      </c>
+      <c r="W221" t="str">
+        <v>5</v>
+      </c>
+      <c r="X221" t="str">
+        <v>4/10/26</v>
+      </c>
+      <c r="Y221" t="str">
+        <v>7/14/26</v>
+      </c>
+      <c r="Z221" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="AB221" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="AD221" t="str">
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="str">
+        <v>(424)</v>
+      </c>
+      <c r="B222" t="str">
+        <v>(1) Viet Nga Group, (2) Việt Nga Group-HTX DVNN Bình Hiệp B</v>
+      </c>
+      <c r="C222" t="str">
+        <v>74936</v>
+      </c>
+      <c r="D222" t="str">
+        <v>783926392</v>
+      </c>
+      <c r="E222" t="str">
+        <v>PHẠM VĂN ĐIỀU</v>
+      </c>
+      <c r="F222" t="str">
+        <v>HỢP TÁC XÃ DỊCH VỤ NÔNG NGHIỆP BÌNH HIỆP B</v>
+      </c>
+      <c r="J222" t="str">
+        <v>Intensive rice production // Trồng lúa thâm canh</v>
+      </c>
+      <c r="K222" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="L222" t="str">
+        <v>Male // Nam</v>
+      </c>
+      <c r="M222" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="N222" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O222" t="str">
+        <v>0</v>
+      </c>
+      <c r="P222" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q222" t="str">
+        <v>0</v>
+      </c>
+      <c r="R222" t="str">
+        <v>0</v>
+      </c>
+      <c r="S222" t="str">
+        <v>0</v>
+      </c>
+      <c r="T222" t="str">
+        <v>0</v>
+      </c>
+      <c r="U222" t="str">
+        <v>5</v>
+      </c>
+      <c r="V222" t="str">
+        <v>0</v>
+      </c>
+      <c r="W222" t="str">
+        <v>4</v>
+      </c>
+      <c r="X222" t="str">
+        <v>4/10/26</v>
+      </c>
+      <c r="Y222" t="str">
+        <v>7/14/26</v>
+      </c>
+      <c r="Z222" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="AB222" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="AD222" t="str">
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="str">
+        <v>(425)</v>
+      </c>
+      <c r="B223" t="str">
+        <v>(1) Viet Nga Group, (2) Việt Nga Group-HTX DVNN Bình Hiệp B</v>
+      </c>
+      <c r="C223" t="str">
+        <v>74937</v>
+      </c>
+      <c r="D223" t="str">
+        <v>384629899</v>
+      </c>
+      <c r="E223" t="str">
+        <v>VÕ LỤC THỌ</v>
+      </c>
+      <c r="F223" t="str">
+        <v>HỢP TÁC XÃ DỊCH VỤ NÔNG NGHIỆP BÌNH HIỆP B</v>
+      </c>
+      <c r="J223" t="str">
+        <v>Intensive rice production // Trồng lúa thâm canh</v>
+      </c>
+      <c r="K223" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="L223" t="str">
+        <v>Male // Nam</v>
+      </c>
+      <c r="M223" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="N223" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O223" t="str">
+        <v>0</v>
+      </c>
+      <c r="P223" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q223" t="str">
+        <v>0</v>
+      </c>
+      <c r="R223" t="str">
+        <v>0</v>
+      </c>
+      <c r="S223" t="str">
+        <v>0</v>
+      </c>
+      <c r="T223" t="str">
+        <v>0</v>
+      </c>
+      <c r="U223" t="str">
+        <v>5</v>
+      </c>
+      <c r="V223" t="str">
+        <v>0</v>
+      </c>
+      <c r="W223" t="str">
+        <v>4</v>
+      </c>
+      <c r="X223" t="str">
+        <v>4/10/26</v>
+      </c>
+      <c r="Y223" t="str">
+        <v>7/14/26</v>
+      </c>
+      <c r="Z223" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="AB223" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="AD223" t="str">
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="str">
+        <v>(426)</v>
+      </c>
+      <c r="B224" t="str">
+        <v>(1) Viet Nga Group, (2) Việt Nga Group-HTX DVNN Bình Hiệp B</v>
+      </c>
+      <c r="C224" t="str">
+        <v>74938</v>
+      </c>
+      <c r="D224" t="str">
+        <v>382708583</v>
+      </c>
+      <c r="E224" t="str">
+        <v>LÊ VĂN THOẠI</v>
+      </c>
+      <c r="F224" t="str">
+        <v>HỢP TÁC XÃ DỊCH VỤ NÔNG NGHIỆP BÌNH HIỆP B</v>
+      </c>
+      <c r="J224" t="str">
+        <v>Intensive rice production // Trồng lúa thâm canh</v>
+      </c>
+      <c r="K224" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="L224" t="str">
+        <v>Male // Nam</v>
+      </c>
+      <c r="M224" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="N224" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O224" t="str">
+        <v>0</v>
+      </c>
+      <c r="P224" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q224" t="str">
+        <v>0</v>
+      </c>
+      <c r="R224" t="str">
+        <v>0</v>
+      </c>
+      <c r="S224" t="str">
+        <v>0</v>
+      </c>
+      <c r="T224" t="str">
+        <v>0</v>
+      </c>
+      <c r="U224" t="str">
+        <v>3</v>
+      </c>
+      <c r="V224" t="str">
+        <v>0</v>
+      </c>
+      <c r="W224" t="str">
+        <v>2</v>
+      </c>
+      <c r="X224" t="str">
+        <v>4/10/26</v>
+      </c>
+      <c r="Y224" t="str">
+        <v>7/14/26</v>
+      </c>
+      <c r="Z224" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="AB224" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="AD224" t="str">
+        <v>Yes</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:AD187"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:AD224"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/cypress/fixtures/run-log.xlsx
+++ b/cypress/fixtures/run-log.xlsx
@@ -404,7 +404,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AE87"/>
+  <dimension ref="A1:AE177"/>
   <sheetData>
     <row r="1" xml:space="preserve">
       <c r="A1" t="str" xml:space="preserve">
@@ -7393,9 +7393,7479 @@
         <v/>
       </c>
     </row>
+    <row r="88">
+      <c r="A88" t="str">
+        <v>(9)</v>
+      </c>
+      <c r="B88" t="str">
+        <v>(1) Viet Nga Group, (2) Việt Nga Group - VTNN Dương Phi</v>
+      </c>
+      <c r="C88" t="str">
+        <v>74811</v>
+      </c>
+      <c r="D88" t="str">
+        <v>987281309</v>
+      </c>
+      <c r="E88" t="str">
+        <v>BÙI VĂN PHƯỚC</v>
+      </c>
+      <c r="F88" t="str">
+        <v>CỬA HÀNG VẬT TƯ NÔNG NGHIỆP DƯƠNG PHI</v>
+      </c>
+      <c r="J88" t="str">
+        <v>Intensive rice production // Trồng lúa thâm canh</v>
+      </c>
+      <c r="K88" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="L88" t="str">
+        <v>Male // Nam</v>
+      </c>
+      <c r="M88" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="N88" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O88" t="str">
+        <v>0</v>
+      </c>
+      <c r="P88" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q88" t="str">
+        <v>0</v>
+      </c>
+      <c r="R88" t="str">
+        <v>0</v>
+      </c>
+      <c r="S88" t="str">
+        <v>0</v>
+      </c>
+      <c r="T88" t="str">
+        <v>0</v>
+      </c>
+      <c r="U88" t="str">
+        <v>2</v>
+      </c>
+      <c r="V88" t="str">
+        <v>0</v>
+      </c>
+      <c r="W88" t="str">
+        <v>1</v>
+      </c>
+      <c r="X88" t="str">
+        <v>4/19/26</v>
+      </c>
+      <c r="Y88" t="str">
+        <v>7/23/26</v>
+      </c>
+      <c r="Z88" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="AA88" t="str">
+        <v>NGÂN</v>
+      </c>
+      <c r="AB88" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="AD88" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="AE88" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="str">
+        <v>(9)</v>
+      </c>
+      <c r="B89" t="str">
+        <v>(1) Viet Nga Group, (2) Việt Nga Group - VTNN Dương Phi</v>
+      </c>
+      <c r="C89" t="str">
+        <v>74811</v>
+      </c>
+      <c r="D89" t="str">
+        <v>987281309</v>
+      </c>
+      <c r="E89" t="str">
+        <v>BÙI VĂN PHƯỚC</v>
+      </c>
+      <c r="F89" t="str">
+        <v>CỬA HÀNG VẬT TƯ NÔNG NGHIỆP DƯƠNG PHI</v>
+      </c>
+      <c r="J89" t="str">
+        <v>Intensive rice production // Trồng lúa thâm canh</v>
+      </c>
+      <c r="K89" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="L89" t="str">
+        <v>Male // Nam</v>
+      </c>
+      <c r="M89" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="N89" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O89" t="str">
+        <v>0</v>
+      </c>
+      <c r="P89" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q89" t="str">
+        <v>0</v>
+      </c>
+      <c r="R89" t="str">
+        <v>0</v>
+      </c>
+      <c r="S89" t="str">
+        <v>0</v>
+      </c>
+      <c r="T89" t="str">
+        <v>0</v>
+      </c>
+      <c r="U89" t="str">
+        <v>2</v>
+      </c>
+      <c r="V89" t="str">
+        <v>0</v>
+      </c>
+      <c r="W89" t="str">
+        <v>1</v>
+      </c>
+      <c r="X89" t="str">
+        <v>4/19/26</v>
+      </c>
+      <c r="Y89" t="str">
+        <v>7/23/26</v>
+      </c>
+      <c r="Z89" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="AA89" t="str">
+        <v>NGÂN</v>
+      </c>
+      <c r="AB89" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="AD89" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="AE89" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="str">
+        <v>(138)</v>
+      </c>
+      <c r="B90" t="str">
+        <v>(1) Viet Nga Group, (2) Việt Nga Group-THT HKD Hoàng Núp</v>
+      </c>
+      <c r="C90" t="str">
+        <v>73374</v>
+      </c>
+      <c r="D90" t="str">
+        <v>384365552</v>
+      </c>
+      <c r="E90" t="str">
+        <v>NGUYỄN VĂN CÔNG</v>
+      </c>
+      <c r="F90" t="str">
+        <v>HỘ KINH DOANH HOÀNG NÚP</v>
+      </c>
+      <c r="J90" t="str">
+        <v>Intensive rice production // Trồng lúa thâm canh</v>
+      </c>
+      <c r="K90" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="L90" t="str">
+        <v>Male // Nam</v>
+      </c>
+      <c r="M90" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="N90" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O90" t="str">
+        <v>0</v>
+      </c>
+      <c r="P90" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q90" t="str">
+        <v>0</v>
+      </c>
+      <c r="R90" t="str">
+        <v>0</v>
+      </c>
+      <c r="S90" t="str">
+        <v>0</v>
+      </c>
+      <c r="T90" t="str">
+        <v>0</v>
+      </c>
+      <c r="U90" t="str">
+        <v>2</v>
+      </c>
+      <c r="V90" t="str">
+        <v>0</v>
+      </c>
+      <c r="W90" t="str">
+        <v>1</v>
+      </c>
+      <c r="X90" t="str">
+        <v>4/15/26</v>
+      </c>
+      <c r="Y90" t="str">
+        <v>7/29/26</v>
+      </c>
+      <c r="Z90" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="AA90" t="str">
+        <v>NGÂN</v>
+      </c>
+      <c r="AB90" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="AD90" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="AE90" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="str">
+        <v>(154)</v>
+      </c>
+      <c r="B91" t="str">
+        <v>(1) Viet Nga Group, (2) Việt Nga Group-THT HKD Hoàng Núp</v>
+      </c>
+      <c r="C91" t="str">
+        <v>73390</v>
+      </c>
+      <c r="D91" t="str">
+        <v>345095461</v>
+      </c>
+      <c r="E91" t="str">
+        <v>TRẦN VĂN PHẾT</v>
+      </c>
+      <c r="F91" t="str">
+        <v>HỘ KINH DOANH HOÀNG NÚP</v>
+      </c>
+      <c r="J91" t="str">
+        <v>Intensive rice production // Trồng lúa thâm canh</v>
+      </c>
+      <c r="K91" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="L91" t="str">
+        <v>Male // Nam</v>
+      </c>
+      <c r="M91" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="N91" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O91" t="str">
+        <v>0</v>
+      </c>
+      <c r="P91" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q91" t="str">
+        <v>0</v>
+      </c>
+      <c r="R91" t="str">
+        <v>0</v>
+      </c>
+      <c r="S91" t="str">
+        <v>0</v>
+      </c>
+      <c r="T91" t="str">
+        <v>0</v>
+      </c>
+      <c r="U91" t="str">
+        <v>2</v>
+      </c>
+      <c r="V91" t="str">
+        <v>0</v>
+      </c>
+      <c r="W91" t="str">
+        <v>1</v>
+      </c>
+      <c r="X91" t="str">
+        <v>4/15/26</v>
+      </c>
+      <c r="Y91" t="str">
+        <v>7/29/26</v>
+      </c>
+      <c r="Z91" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="AA91" t="str">
+        <v>NGÂN</v>
+      </c>
+      <c r="AB91" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="AD91" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="AE91" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="str">
+        <v>(155)</v>
+      </c>
+      <c r="B92" t="str">
+        <v>(1) Viet Nga Group, (2) Việt Nga Group - HKD Đoàn Minh Chiến</v>
+      </c>
+      <c r="C92" t="str">
+        <v>75866</v>
+      </c>
+      <c r="D92" t="str">
+        <v>833661510</v>
+      </c>
+      <c r="E92" t="str">
+        <v>BÙI THỊ VÊ</v>
+      </c>
+      <c r="F92" t="str">
+        <v>HỘ KINH DOANH MINH CHIÊN</v>
+      </c>
+      <c r="J92" t="str">
+        <v>Intensive rice production // Trồng lúa thâm canh</v>
+      </c>
+      <c r="K92" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="L92" t="str">
+        <v>Female // Nữ</v>
+      </c>
+      <c r="M92" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="N92" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O92" t="str">
+        <v>1</v>
+      </c>
+      <c r="P92" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q92" t="str">
+        <v>0</v>
+      </c>
+      <c r="R92" t="str">
+        <v>0</v>
+      </c>
+      <c r="S92" t="str">
+        <v>0</v>
+      </c>
+      <c r="T92" t="str">
+        <v>0</v>
+      </c>
+      <c r="U92" t="str">
+        <v>4</v>
+      </c>
+      <c r="V92" t="str">
+        <v>0</v>
+      </c>
+      <c r="W92" t="str">
+        <v>3</v>
+      </c>
+      <c r="X92" t="str">
+        <v>5/19/26</v>
+      </c>
+      <c r="Y92" t="str">
+        <v>9/6/26</v>
+      </c>
+      <c r="Z92" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="AA92" t="str">
+        <v>NGÂN</v>
+      </c>
+      <c r="AB92" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="AD92" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="AE92" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="str">
+        <v>(158)</v>
+      </c>
+      <c r="B93" t="str">
+        <v>(1) Viet Nga Group, (2) Việt Nga Group - HKD Đoàn Minh Chiến</v>
+      </c>
+      <c r="C93" t="str">
+        <v>75869</v>
+      </c>
+      <c r="D93" t="str">
+        <v>939546018</v>
+      </c>
+      <c r="E93" t="str">
+        <v>DANH LÀNH</v>
+      </c>
+      <c r="F93" t="str">
+        <v>HỘ KINH DOANH MINH CHIÊN</v>
+      </c>
+      <c r="J93" t="str">
+        <v>Intensive rice production // Trồng lúa thâm canh</v>
+      </c>
+      <c r="K93" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="L93" t="str">
+        <v>Female // Nữ</v>
+      </c>
+      <c r="M93" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="N93" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O93" t="str">
+        <v>1</v>
+      </c>
+      <c r="P93" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q93" t="str">
+        <v>0</v>
+      </c>
+      <c r="R93" t="str">
+        <v>0</v>
+      </c>
+      <c r="S93" t="str">
+        <v>0</v>
+      </c>
+      <c r="T93" t="str">
+        <v>0</v>
+      </c>
+      <c r="U93" t="str">
+        <v>2</v>
+      </c>
+      <c r="V93" t="str">
+        <v>0</v>
+      </c>
+      <c r="W93" t="str">
+        <v>1</v>
+      </c>
+      <c r="X93" t="str">
+        <v>5/19/26</v>
+      </c>
+      <c r="Y93" t="str">
+        <v>9/6/26</v>
+      </c>
+      <c r="Z93" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="AA93" t="str">
+        <v>NGÂN</v>
+      </c>
+      <c r="AB93" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="AD93" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="AE93" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="str">
+        <v>(159)</v>
+      </c>
+      <c r="B94" t="str">
+        <v>(1) Viet Nga Group, (2) Việt Nga Group - HKD Đoàn Minh Chiến</v>
+      </c>
+      <c r="C94" t="str">
+        <v>75870</v>
+      </c>
+      <c r="D94" t="str">
+        <v>918887694</v>
+      </c>
+      <c r="E94" t="str">
+        <v>TRẦN VĂN BỀN</v>
+      </c>
+      <c r="F94" t="str">
+        <v>HỘ KINH DOANH MINH CHIÊN</v>
+      </c>
+      <c r="J94" t="str">
+        <v>Intensive rice production // Trồng lúa thâm canh</v>
+      </c>
+      <c r="K94" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="L94" t="str">
+        <v>Male // Nam</v>
+      </c>
+      <c r="M94" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="N94" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O94" t="str">
+        <v>1</v>
+      </c>
+      <c r="P94" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q94" t="str">
+        <v>0</v>
+      </c>
+      <c r="R94" t="str">
+        <v>0</v>
+      </c>
+      <c r="S94" t="str">
+        <v>0</v>
+      </c>
+      <c r="T94" t="str">
+        <v>0</v>
+      </c>
+      <c r="U94" t="str">
+        <v>3</v>
+      </c>
+      <c r="V94" t="str">
+        <v>0</v>
+      </c>
+      <c r="W94" t="str">
+        <v>2</v>
+      </c>
+      <c r="X94" t="str">
+        <v>5/19/26</v>
+      </c>
+      <c r="Y94" t="str">
+        <v>9/6/26</v>
+      </c>
+      <c r="Z94" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="AA94" t="str">
+        <v>NGÂN</v>
+      </c>
+      <c r="AB94" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="AD94" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="AE94" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="str">
+        <v>(160)</v>
+      </c>
+      <c r="B95" t="str">
+        <v>(1) Viet Nga Group, (2) Việt Nga Group - HKD Đoàn Minh Chiến</v>
+      </c>
+      <c r="C95" t="str">
+        <v>75871</v>
+      </c>
+      <c r="D95" t="str">
+        <v>983975858</v>
+      </c>
+      <c r="E95" t="str">
+        <v>NGUYỄN ĐÌNH LÂM</v>
+      </c>
+      <c r="F95" t="str">
+        <v>HỘ KINH DOANH MINH CHIÊN</v>
+      </c>
+      <c r="J95" t="str">
+        <v>Intensive rice production // Trồng lúa thâm canh</v>
+      </c>
+      <c r="K95" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="L95" t="str">
+        <v>Male // Nam</v>
+      </c>
+      <c r="M95" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="N95" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O95" t="str">
+        <v>1</v>
+      </c>
+      <c r="P95" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q95" t="str">
+        <v>0</v>
+      </c>
+      <c r="R95" t="str">
+        <v>0</v>
+      </c>
+      <c r="S95" t="str">
+        <v>0</v>
+      </c>
+      <c r="T95" t="str">
+        <v>0</v>
+      </c>
+      <c r="U95" t="str">
+        <v>3</v>
+      </c>
+      <c r="V95" t="str">
+        <v>0</v>
+      </c>
+      <c r="W95" t="str">
+        <v>2</v>
+      </c>
+      <c r="X95" t="str">
+        <v>5/19/26</v>
+      </c>
+      <c r="Y95" t="str">
+        <v>9/6/26</v>
+      </c>
+      <c r="Z95" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="AA95" t="str">
+        <v>NGÂN</v>
+      </c>
+      <c r="AB95" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="AD95" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="AE95" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="str">
+        <v>(161)</v>
+      </c>
+      <c r="B96" t="str">
+        <v>(1) Viet Nga Group, (2) Việt Nga Group - HKD Đoàn Minh Chiến</v>
+      </c>
+      <c r="C96" t="str">
+        <v>75872</v>
+      </c>
+      <c r="D96" t="str">
+        <v>368038680</v>
+      </c>
+      <c r="E96" t="str">
+        <v>PHẠM VĂN MÁO</v>
+      </c>
+      <c r="F96" t="str">
+        <v>HỘ KINH DOANH MINH CHIÊN</v>
+      </c>
+      <c r="J96" t="str">
+        <v>Intensive rice production // Trồng lúa thâm canh</v>
+      </c>
+      <c r="K96" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="L96" t="str">
+        <v>Male // Nam</v>
+      </c>
+      <c r="M96" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="N96" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O96" t="str">
+        <v>1</v>
+      </c>
+      <c r="P96" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q96" t="str">
+        <v>0</v>
+      </c>
+      <c r="R96" t="str">
+        <v>0</v>
+      </c>
+      <c r="S96" t="str">
+        <v>0</v>
+      </c>
+      <c r="T96" t="str">
+        <v>0</v>
+      </c>
+      <c r="U96" t="str">
+        <v>3</v>
+      </c>
+      <c r="V96" t="str">
+        <v>0</v>
+      </c>
+      <c r="W96" t="str">
+        <v>2</v>
+      </c>
+      <c r="X96" t="str">
+        <v>5/19/26</v>
+      </c>
+      <c r="Y96" t="str">
+        <v>9/6/26</v>
+      </c>
+      <c r="Z96" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="AA96" t="str">
+        <v>NGÂN</v>
+      </c>
+      <c r="AB96" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="AD96" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="AE96" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="str">
+        <v>(162)</v>
+      </c>
+      <c r="B97" t="str">
+        <v>(1) Viet Nga Group, (2) Việt Nga Group - HKD Đoàn Minh Chiến</v>
+      </c>
+      <c r="C97" t="str">
+        <v>75873</v>
+      </c>
+      <c r="D97" t="str">
+        <v>387673811</v>
+      </c>
+      <c r="E97" t="str">
+        <v>PHẠM VĂN CHÚC</v>
+      </c>
+      <c r="F97" t="str">
+        <v>HỘ KINH DOANH MINH CHIÊN</v>
+      </c>
+      <c r="J97" t="str">
+        <v>Intensive rice production // Trồng lúa thâm canh</v>
+      </c>
+      <c r="K97" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="L97" t="str">
+        <v>Male // Nam</v>
+      </c>
+      <c r="M97" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="N97" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O97" t="str">
+        <v>1</v>
+      </c>
+      <c r="P97" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q97" t="str">
+        <v>0</v>
+      </c>
+      <c r="R97" t="str">
+        <v>0</v>
+      </c>
+      <c r="S97" t="str">
+        <v>0</v>
+      </c>
+      <c r="T97" t="str">
+        <v>0</v>
+      </c>
+      <c r="U97" t="str">
+        <v>2</v>
+      </c>
+      <c r="V97" t="str">
+        <v>0</v>
+      </c>
+      <c r="W97" t="str">
+        <v>1</v>
+      </c>
+      <c r="X97" t="str">
+        <v>5/19/26</v>
+      </c>
+      <c r="Y97" t="str">
+        <v>9/6/26</v>
+      </c>
+      <c r="Z97" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="AA97" t="str">
+        <v>NGÂN</v>
+      </c>
+      <c r="AB97" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="AD97" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="AE97" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="str">
+        <v>(165)</v>
+      </c>
+      <c r="B98" t="str">
+        <v>(1) Viet Nga Group, (2) Việt Nga Group - HKD Đoàn Minh Chiến</v>
+      </c>
+      <c r="C98" t="str">
+        <v>75876</v>
+      </c>
+      <c r="D98" t="str">
+        <v>326605700</v>
+      </c>
+      <c r="E98" t="str">
+        <v>NGUYỄN VĂN PHƯƠNG</v>
+      </c>
+      <c r="F98" t="str">
+        <v>HỘ KINH DOANH MINH CHIÊN</v>
+      </c>
+      <c r="J98" t="str">
+        <v>Intensive rice production // Trồng lúa thâm canh</v>
+      </c>
+      <c r="K98" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="L98" t="str">
+        <v>Male // Nam</v>
+      </c>
+      <c r="M98" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="N98" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O98" t="str">
+        <v>1</v>
+      </c>
+      <c r="P98" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q98" t="str">
+        <v>0</v>
+      </c>
+      <c r="R98" t="str">
+        <v>0</v>
+      </c>
+      <c r="S98" t="str">
+        <v>0</v>
+      </c>
+      <c r="T98" t="str">
+        <v>0</v>
+      </c>
+      <c r="U98" t="str">
+        <v>4</v>
+      </c>
+      <c r="V98" t="str">
+        <v>0</v>
+      </c>
+      <c r="W98" t="str">
+        <v>3</v>
+      </c>
+      <c r="X98" t="str">
+        <v>5/19/26</v>
+      </c>
+      <c r="Y98" t="str">
+        <v>9/6/26</v>
+      </c>
+      <c r="Z98" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="AA98" t="str">
+        <v>NGÂN</v>
+      </c>
+      <c r="AB98" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="AD98" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="AE98" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="str">
+        <v>(166)</v>
+      </c>
+      <c r="B99" t="str">
+        <v>(1) Viet Nga Group, (2) Việt Nga Group - HKD Đoàn Minh Chiến</v>
+      </c>
+      <c r="C99" t="str">
+        <v>75877</v>
+      </c>
+      <c r="D99" t="str">
+        <v>394234220</v>
+      </c>
+      <c r="E99" t="str">
+        <v>HUỲNH BÁ DUY</v>
+      </c>
+      <c r="F99" t="str">
+        <v>HỘ KINH DOANH MINH CHIÊN</v>
+      </c>
+      <c r="J99" t="str">
+        <v>Intensive rice production // Trồng lúa thâm canh</v>
+      </c>
+      <c r="K99" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="L99" t="str">
+        <v>Male // Nam</v>
+      </c>
+      <c r="M99" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="N99" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O99" t="str">
+        <v>1</v>
+      </c>
+      <c r="P99" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q99" t="str">
+        <v>0</v>
+      </c>
+      <c r="R99" t="str">
+        <v>0</v>
+      </c>
+      <c r="S99" t="str">
+        <v>0</v>
+      </c>
+      <c r="T99" t="str">
+        <v>0</v>
+      </c>
+      <c r="U99" t="str">
+        <v>2</v>
+      </c>
+      <c r="V99" t="str">
+        <v>0</v>
+      </c>
+      <c r="W99" t="str">
+        <v>1</v>
+      </c>
+      <c r="X99" t="str">
+        <v>5/19/26</v>
+      </c>
+      <c r="Y99" t="str">
+        <v>9/6/26</v>
+      </c>
+      <c r="Z99" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="AA99" t="str">
+        <v>NGÂN</v>
+      </c>
+      <c r="AB99" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="AD99" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="AE99" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="str">
+        <v>(173)</v>
+      </c>
+      <c r="B100" t="str">
+        <v>(1) Viet Nga Group, (2) Việt Nga Group - HKD Đoàn Minh Chiến</v>
+      </c>
+      <c r="C100" t="str">
+        <v>75884</v>
+      </c>
+      <c r="D100" t="str">
+        <v>817977017</v>
+      </c>
+      <c r="E100" t="str">
+        <v>PHẠM VĂN NHÂN</v>
+      </c>
+      <c r="F100" t="str">
+        <v>HỘ KINH DOANH MINH CHIÊN</v>
+      </c>
+      <c r="J100" t="str">
+        <v>Intensive rice production // Trồng lúa thâm canh</v>
+      </c>
+      <c r="K100" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="L100" t="str">
+        <v>Male // Nam</v>
+      </c>
+      <c r="M100" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="N100" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O100" t="str">
+        <v>0</v>
+      </c>
+      <c r="P100" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q100" t="str">
+        <v>0</v>
+      </c>
+      <c r="R100" t="str">
+        <v>0</v>
+      </c>
+      <c r="S100" t="str">
+        <v>0</v>
+      </c>
+      <c r="T100" t="str">
+        <v>0</v>
+      </c>
+      <c r="U100" t="str">
+        <v>5</v>
+      </c>
+      <c r="V100" t="str">
+        <v>0</v>
+      </c>
+      <c r="W100" t="str">
+        <v>4</v>
+      </c>
+      <c r="X100" t="str">
+        <v>5/19/26</v>
+      </c>
+      <c r="Y100" t="str">
+        <v>9/6/26</v>
+      </c>
+      <c r="Z100" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="AA100" t="str">
+        <v>NGÂN</v>
+      </c>
+      <c r="AB100" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="AD100" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="AE100" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="str">
+        <v>(175)</v>
+      </c>
+      <c r="B101" t="str">
+        <v>(1) Viet Nga Group, (2) Việt Nga Group - HKD Đoàn Minh Chiến</v>
+      </c>
+      <c r="C101" t="str">
+        <v>75886</v>
+      </c>
+      <c r="D101" t="str">
+        <v>987190004</v>
+      </c>
+      <c r="E101" t="str">
+        <v>NGUYỄN THANH SANG</v>
+      </c>
+      <c r="F101" t="str">
+        <v>HỘ KINH DOANH MINH CHIÊN</v>
+      </c>
+      <c r="J101" t="str">
+        <v>Intensive rice production // Trồng lúa thâm canh</v>
+      </c>
+      <c r="K101" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="L101" t="str">
+        <v>Male // Nam</v>
+      </c>
+      <c r="M101" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="N101" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O101" t="str">
+        <v>0</v>
+      </c>
+      <c r="P101" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q101" t="str">
+        <v>0</v>
+      </c>
+      <c r="R101" t="str">
+        <v>0</v>
+      </c>
+      <c r="S101" t="str">
+        <v>0</v>
+      </c>
+      <c r="T101" t="str">
+        <v>0</v>
+      </c>
+      <c r="U101" t="str">
+        <v>5</v>
+      </c>
+      <c r="V101" t="str">
+        <v>0</v>
+      </c>
+      <c r="W101" t="str">
+        <v>4</v>
+      </c>
+      <c r="X101" t="str">
+        <v>5/19/26</v>
+      </c>
+      <c r="Y101" t="str">
+        <v>9/6/26</v>
+      </c>
+      <c r="Z101" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="AA101" t="str">
+        <v>NGÂN</v>
+      </c>
+      <c r="AB101" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="AD101" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="AE101" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="str">
+        <v>(178)</v>
+      </c>
+      <c r="B102" t="str">
+        <v>(1) Viet Nga Group, (2) Việt Nga Group - HKD Đoàn Minh Chiến</v>
+      </c>
+      <c r="C102" t="str">
+        <v>75889</v>
+      </c>
+      <c r="D102" t="str">
+        <v>889363552</v>
+      </c>
+      <c r="E102" t="str">
+        <v>NGUYỄN VĂN HỶ</v>
+      </c>
+      <c r="F102" t="str">
+        <v>HỘ KINH DOANH MINH CHIÊN</v>
+      </c>
+      <c r="J102" t="str">
+        <v>Intensive rice production // Trồng lúa thâm canh</v>
+      </c>
+      <c r="K102" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="L102" t="str">
+        <v>Male // Nam</v>
+      </c>
+      <c r="M102" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="N102" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O102" t="str">
+        <v>1</v>
+      </c>
+      <c r="P102" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q102" t="str">
+        <v>0</v>
+      </c>
+      <c r="R102" t="str">
+        <v>0</v>
+      </c>
+      <c r="S102" t="str">
+        <v>0</v>
+      </c>
+      <c r="T102" t="str">
+        <v>0</v>
+      </c>
+      <c r="U102" t="str">
+        <v>2</v>
+      </c>
+      <c r="V102" t="str">
+        <v>0</v>
+      </c>
+      <c r="W102" t="str">
+        <v>1</v>
+      </c>
+      <c r="X102" t="str">
+        <v>5/19/26</v>
+      </c>
+      <c r="Y102" t="str">
+        <v>9/6/26</v>
+      </c>
+      <c r="Z102" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="AA102" t="str">
+        <v>NGÂN</v>
+      </c>
+      <c r="AB102" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="AD102" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="AE102" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="str">
+        <v>(181)</v>
+      </c>
+      <c r="B103" t="str">
+        <v>(1) Viet Nga Group, (2) Việt Nga Group - HKD Đoàn Minh Chiến</v>
+      </c>
+      <c r="C103" t="str">
+        <v>75892</v>
+      </c>
+      <c r="D103" t="str">
+        <v>778208780</v>
+      </c>
+      <c r="E103" t="str">
+        <v>HUỲNH THỊ CẨM EM</v>
+      </c>
+      <c r="F103" t="str">
+        <v>HỘ KINH DOANH MINH CHIÊN</v>
+      </c>
+      <c r="J103" t="str">
+        <v>Intensive rice production // Trồng lúa thâm canh</v>
+      </c>
+      <c r="K103" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="L103" t="str">
+        <v>Female // Nữ</v>
+      </c>
+      <c r="M103" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="N103" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O103" t="str">
+        <v>1</v>
+      </c>
+      <c r="P103" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q103" t="str">
+        <v>0</v>
+      </c>
+      <c r="R103" t="str">
+        <v>0</v>
+      </c>
+      <c r="S103" t="str">
+        <v>0</v>
+      </c>
+      <c r="T103" t="str">
+        <v>0</v>
+      </c>
+      <c r="U103" t="str">
+        <v>2</v>
+      </c>
+      <c r="V103" t="str">
+        <v>0</v>
+      </c>
+      <c r="W103" t="str">
+        <v>1</v>
+      </c>
+      <c r="X103" t="str">
+        <v>5/19/26</v>
+      </c>
+      <c r="Y103" t="str">
+        <v>9/6/26</v>
+      </c>
+      <c r="Z103" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="AA103" t="str">
+        <v>NGÂN</v>
+      </c>
+      <c r="AB103" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="AD103" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="AE103" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="str">
+        <v>(183)</v>
+      </c>
+      <c r="B104" t="str">
+        <v>(1) Viet Nga Group, (2) Việt Nga Group - HKD Đoàn Minh Chiến</v>
+      </c>
+      <c r="C104" t="str">
+        <v>75894</v>
+      </c>
+      <c r="D104" t="str">
+        <v>392521700</v>
+      </c>
+      <c r="E104" t="str">
+        <v>THẠCH TỚI</v>
+      </c>
+      <c r="F104" t="str">
+        <v>HỘ KINH DOANH MINH CHIÊN</v>
+      </c>
+      <c r="J104" t="str">
+        <v>Intensive rice production // Trồng lúa thâm canh</v>
+      </c>
+      <c r="K104" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="L104" t="str">
+        <v>Male // Nam</v>
+      </c>
+      <c r="M104" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="N104" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O104" t="str">
+        <v>1</v>
+      </c>
+      <c r="P104" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q104" t="str">
+        <v>0</v>
+      </c>
+      <c r="R104" t="str">
+        <v>0</v>
+      </c>
+      <c r="S104" t="str">
+        <v>0</v>
+      </c>
+      <c r="T104" t="str">
+        <v>0</v>
+      </c>
+      <c r="U104" t="str">
+        <v>4</v>
+      </c>
+      <c r="V104" t="str">
+        <v>0</v>
+      </c>
+      <c r="W104" t="str">
+        <v>3</v>
+      </c>
+      <c r="X104" t="str">
+        <v>5/19/26</v>
+      </c>
+      <c r="Y104" t="str">
+        <v>9/6/26</v>
+      </c>
+      <c r="Z104" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="AA104" t="str">
+        <v>NGÂN</v>
+      </c>
+      <c r="AB104" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="AD104" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="AE104" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="str">
+        <v>(185)</v>
+      </c>
+      <c r="B105" t="str">
+        <v>(1) Viet Nga Group, (2) Việt Nga Group - HKD Đoàn Minh Chiến</v>
+      </c>
+      <c r="C105" t="str">
+        <v>75896</v>
+      </c>
+      <c r="D105" t="str">
+        <v>773442113</v>
+      </c>
+      <c r="E105" t="str">
+        <v>NGUYỄN VĂN HAI</v>
+      </c>
+      <c r="F105" t="str">
+        <v>HỘ KINH DOANH MINH CHIÊN</v>
+      </c>
+      <c r="J105" t="str">
+        <v>Intensive rice production // Trồng lúa thâm canh</v>
+      </c>
+      <c r="K105" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="L105" t="str">
+        <v>Male // Nam</v>
+      </c>
+      <c r="M105" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="N105" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O105" t="str">
+        <v>0</v>
+      </c>
+      <c r="P105" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q105" t="str">
+        <v>0</v>
+      </c>
+      <c r="R105" t="str">
+        <v>0</v>
+      </c>
+      <c r="S105" t="str">
+        <v>0</v>
+      </c>
+      <c r="T105" t="str">
+        <v>0</v>
+      </c>
+      <c r="U105" t="str">
+        <v>3</v>
+      </c>
+      <c r="V105" t="str">
+        <v>0</v>
+      </c>
+      <c r="W105" t="str">
+        <v>2</v>
+      </c>
+      <c r="X105" t="str">
+        <v>5/19/26</v>
+      </c>
+      <c r="Y105" t="str">
+        <v>9/6/26</v>
+      </c>
+      <c r="Z105" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="AA105" t="str">
+        <v>NGÂN</v>
+      </c>
+      <c r="AB105" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="AD105" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="AE105" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="str">
+        <v>(189)</v>
+      </c>
+      <c r="B106" t="str">
+        <v>(1) Viet Nga Group, (2) Viet Nga Group - HKD Sáu Lang</v>
+      </c>
+      <c r="C106" t="str">
+        <v>77027</v>
+      </c>
+      <c r="D106" t="str">
+        <v>393465141</v>
+      </c>
+      <c r="E106" t="str">
+        <v>PHẠM AN RI</v>
+      </c>
+      <c r="F106" t="str">
+        <v>HỘ KINH DOANH SÁU LANG</v>
+      </c>
+      <c r="J106" t="str">
+        <v>Intensive rice production // Trồng lúa thâm canh</v>
+      </c>
+      <c r="K106" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="L106" t="str">
+        <v>Male // Nam</v>
+      </c>
+      <c r="M106" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="N106" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O106" t="str">
+        <v>0</v>
+      </c>
+      <c r="P106" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q106" t="str">
+        <v>0</v>
+      </c>
+      <c r="R106" t="str">
+        <v>0</v>
+      </c>
+      <c r="S106" t="str">
+        <v>0</v>
+      </c>
+      <c r="T106" t="str">
+        <v>0</v>
+      </c>
+      <c r="U106" t="str">
+        <v>3</v>
+      </c>
+      <c r="V106" t="str">
+        <v>0</v>
+      </c>
+      <c r="W106" t="str">
+        <v>2</v>
+      </c>
+      <c r="X106" t="str">
+        <v>4/27/26</v>
+      </c>
+      <c r="Y106" t="str">
+        <v>8/10/26</v>
+      </c>
+      <c r="Z106" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="AA106" t="str">
+        <v>NGÂN</v>
+      </c>
+      <c r="AB106" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="AD106" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="AE106" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="str">
+        <v>(190)</v>
+      </c>
+      <c r="B107" t="str">
+        <v>(1) Viet Nga Group, (2) Viet Nga Group - HKD Sáu Lang</v>
+      </c>
+      <c r="C107" t="str">
+        <v>77028</v>
+      </c>
+      <c r="D107" t="str">
+        <v>335187379</v>
+      </c>
+      <c r="E107" t="str">
+        <v>NGÔ VĂN CƯỜNG</v>
+      </c>
+      <c r="F107" t="str">
+        <v>HỘ KINH DOANH SÁU LANG</v>
+      </c>
+      <c r="J107" t="str">
+        <v>Intensive rice production // Trồng lúa thâm canh</v>
+      </c>
+      <c r="K107" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="L107" t="str">
+        <v>Male // Nam</v>
+      </c>
+      <c r="M107" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="N107" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O107" t="str">
+        <v>0</v>
+      </c>
+      <c r="P107" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q107" t="str">
+        <v>0</v>
+      </c>
+      <c r="R107" t="str">
+        <v>0</v>
+      </c>
+      <c r="S107" t="str">
+        <v>0</v>
+      </c>
+      <c r="T107" t="str">
+        <v>0</v>
+      </c>
+      <c r="U107" t="str">
+        <v>2</v>
+      </c>
+      <c r="V107" t="str">
+        <v>0</v>
+      </c>
+      <c r="W107" t="str">
+        <v>1</v>
+      </c>
+      <c r="X107" t="str">
+        <v>4/27/26</v>
+      </c>
+      <c r="Y107" t="str">
+        <v>8/10/26</v>
+      </c>
+      <c r="Z107" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="AA107" t="str">
+        <v>NGÂN</v>
+      </c>
+      <c r="AB107" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="AD107" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="AE107" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="str">
+        <v>(193)</v>
+      </c>
+      <c r="B108" t="str">
+        <v>(1) Viet Nga Group, (2) Viet Nga Group - HKD Sáu Lang</v>
+      </c>
+      <c r="C108" t="str">
+        <v>77031</v>
+      </c>
+      <c r="D108" t="str">
+        <v>398281775</v>
+      </c>
+      <c r="E108" t="str">
+        <v>NGUYỄN VĂN DŨNG</v>
+      </c>
+      <c r="F108" t="str">
+        <v>HỘ KINH DOANH SÁU LANG</v>
+      </c>
+      <c r="J108" t="str">
+        <v>Intensive rice production // Trồng lúa thâm canh</v>
+      </c>
+      <c r="K108" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="L108" t="str">
+        <v>Male // Nam</v>
+      </c>
+      <c r="M108" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="N108" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O108" t="str">
+        <v>0</v>
+      </c>
+      <c r="P108" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q108" t="str">
+        <v>0</v>
+      </c>
+      <c r="R108" t="str">
+        <v>0</v>
+      </c>
+      <c r="S108" t="str">
+        <v>0</v>
+      </c>
+      <c r="T108" t="str">
+        <v>0</v>
+      </c>
+      <c r="U108" t="str">
+        <v>2</v>
+      </c>
+      <c r="V108" t="str">
+        <v>0</v>
+      </c>
+      <c r="W108" t="str">
+        <v>1</v>
+      </c>
+      <c r="X108" t="str">
+        <v>4/27/26</v>
+      </c>
+      <c r="Y108" t="str">
+        <v>8/10/26</v>
+      </c>
+      <c r="Z108" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="AA108" t="str">
+        <v>NGÂN</v>
+      </c>
+      <c r="AB108" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="AD108" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="AE108" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="str">
+        <v>(195)</v>
+      </c>
+      <c r="B109" t="str">
+        <v>(1) Viet Nga Group, (2) Viet Nga Group - HKD Sáu Lang</v>
+      </c>
+      <c r="C109" t="str">
+        <v>77033</v>
+      </c>
+      <c r="D109" t="str">
+        <v>907206690</v>
+      </c>
+      <c r="E109" t="str">
+        <v>NGUYỄN VĂN MÃNH</v>
+      </c>
+      <c r="F109" t="str">
+        <v>HỘ KINH DOANH SÁU LANG</v>
+      </c>
+      <c r="J109" t="str">
+        <v>Intensive rice production // Trồng lúa thâm canh</v>
+      </c>
+      <c r="K109" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="L109" t="str">
+        <v>Male // Nam</v>
+      </c>
+      <c r="M109" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="N109" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O109" t="str">
+        <v>0</v>
+      </c>
+      <c r="P109" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q109" t="str">
+        <v>0</v>
+      </c>
+      <c r="R109" t="str">
+        <v>0</v>
+      </c>
+      <c r="S109" t="str">
+        <v>0</v>
+      </c>
+      <c r="T109" t="str">
+        <v>0</v>
+      </c>
+      <c r="U109" t="str">
+        <v>2</v>
+      </c>
+      <c r="V109" t="str">
+        <v>0</v>
+      </c>
+      <c r="W109" t="str">
+        <v>1</v>
+      </c>
+      <c r="X109" t="str">
+        <v>4/27/26</v>
+      </c>
+      <c r="Y109" t="str">
+        <v>8/10/26</v>
+      </c>
+      <c r="Z109" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="AA109" t="str">
+        <v>NGÂN</v>
+      </c>
+      <c r="AB109" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="AD109" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="AE109" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="str">
+        <v>(196)</v>
+      </c>
+      <c r="B110" t="str">
+        <v>(1) Viet Nga Group, (2) Viet Nga Group - HKD Sáu Lang</v>
+      </c>
+      <c r="C110" t="str">
+        <v>77034</v>
+      </c>
+      <c r="D110" t="str">
+        <v>961421448</v>
+      </c>
+      <c r="E110" t="str">
+        <v>LÊ HIỀN LƯƠNG</v>
+      </c>
+      <c r="F110" t="str">
+        <v>HỘ KINH DOANH SÁU LANG</v>
+      </c>
+      <c r="J110" t="str">
+        <v>Intensive rice production // Trồng lúa thâm canh</v>
+      </c>
+      <c r="K110" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="L110" t="str">
+        <v>Female // Nữ</v>
+      </c>
+      <c r="M110" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="N110" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O110" t="str">
+        <v>1</v>
+      </c>
+      <c r="P110" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q110" t="str">
+        <v>0</v>
+      </c>
+      <c r="R110" t="str">
+        <v>0</v>
+      </c>
+      <c r="S110" t="str">
+        <v>0</v>
+      </c>
+      <c r="T110" t="str">
+        <v>0</v>
+      </c>
+      <c r="U110" t="str">
+        <v>2</v>
+      </c>
+      <c r="V110" t="str">
+        <v>0</v>
+      </c>
+      <c r="W110" t="str">
+        <v>1</v>
+      </c>
+      <c r="X110" t="str">
+        <v>4/27/26</v>
+      </c>
+      <c r="Y110" t="str">
+        <v>8/10/26</v>
+      </c>
+      <c r="Z110" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="AA110" t="str">
+        <v>NGÂN</v>
+      </c>
+      <c r="AB110" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="AD110" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="AE110" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="str">
+        <v>(197)</v>
+      </c>
+      <c r="B111" t="str">
+        <v>(1) Viet Nga Group, (2) Viet Nga Group - HKD Sáu Lang</v>
+      </c>
+      <c r="C111" t="str">
+        <v>77035</v>
+      </c>
+      <c r="D111" t="str">
+        <v>914835726</v>
+      </c>
+      <c r="E111" t="str">
+        <v>TRẦN VĂN LÃM</v>
+      </c>
+      <c r="F111" t="str">
+        <v>HỘ KINH DOANH SÁU LANG</v>
+      </c>
+      <c r="J111" t="str">
+        <v>Intensive rice production // Trồng lúa thâm canh</v>
+      </c>
+      <c r="K111" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="L111" t="str">
+        <v>Male // Nam</v>
+      </c>
+      <c r="M111" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="N111" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O111" t="str">
+        <v>0</v>
+      </c>
+      <c r="P111" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q111" t="str">
+        <v>0</v>
+      </c>
+      <c r="R111" t="str">
+        <v>0</v>
+      </c>
+      <c r="S111" t="str">
+        <v>0</v>
+      </c>
+      <c r="T111" t="str">
+        <v>0</v>
+      </c>
+      <c r="U111" t="str">
+        <v>3</v>
+      </c>
+      <c r="V111" t="str">
+        <v>0</v>
+      </c>
+      <c r="W111" t="str">
+        <v>2</v>
+      </c>
+      <c r="X111" t="str">
+        <v>4/27/26</v>
+      </c>
+      <c r="Y111" t="str">
+        <v>8/10/26</v>
+      </c>
+      <c r="Z111" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="AA111" t="str">
+        <v>NGÂN</v>
+      </c>
+      <c r="AB111" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="AD111" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="AE111" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="str">
+        <v>(198)</v>
+      </c>
+      <c r="B112" t="str">
+        <v>(1) Viet Nga Group, (2) Viet Nga Group - HKD Sáu Lang</v>
+      </c>
+      <c r="C112" t="str">
+        <v>77036</v>
+      </c>
+      <c r="D112" t="str">
+        <v>852957659</v>
+      </c>
+      <c r="E112" t="str">
+        <v>LÊ VĂN HỪNG</v>
+      </c>
+      <c r="F112" t="str">
+        <v>HỘ KINH DOANH SÁU LANG</v>
+      </c>
+      <c r="J112" t="str">
+        <v>Intensive rice production // Trồng lúa thâm canh</v>
+      </c>
+      <c r="K112" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="L112" t="str">
+        <v>Male // Nam</v>
+      </c>
+      <c r="M112" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="N112" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O112" t="str">
+        <v>0</v>
+      </c>
+      <c r="P112" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q112" t="str">
+        <v>0</v>
+      </c>
+      <c r="R112" t="str">
+        <v>0</v>
+      </c>
+      <c r="S112" t="str">
+        <v>0</v>
+      </c>
+      <c r="T112" t="str">
+        <v>0</v>
+      </c>
+      <c r="U112" t="str">
+        <v>2</v>
+      </c>
+      <c r="V112" t="str">
+        <v>0</v>
+      </c>
+      <c r="W112" t="str">
+        <v>1</v>
+      </c>
+      <c r="X112" t="str">
+        <v>4/27/26</v>
+      </c>
+      <c r="Y112" t="str">
+        <v>8/10/26</v>
+      </c>
+      <c r="Z112" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="AA112" t="str">
+        <v>NGÂN</v>
+      </c>
+      <c r="AB112" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="AD112" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="AE112" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="str">
+        <v>(199)</v>
+      </c>
+      <c r="B113" t="str">
+        <v>(1) Viet Nga Group, (2) Viet Nga Group - HKD Sáu Lang</v>
+      </c>
+      <c r="C113" t="str">
+        <v>77037</v>
+      </c>
+      <c r="D113" t="str">
+        <v>988898257</v>
+      </c>
+      <c r="E113" t="str">
+        <v>LÊ VĂN AN</v>
+      </c>
+      <c r="F113" t="str">
+        <v>HỘ KINH DOANH SÁU LANG</v>
+      </c>
+      <c r="J113" t="str">
+        <v>Intensive rice production // Trồng lúa thâm canh</v>
+      </c>
+      <c r="K113" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="L113" t="str">
+        <v>Male // Nam</v>
+      </c>
+      <c r="M113" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="N113" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O113" t="str">
+        <v>0</v>
+      </c>
+      <c r="P113" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q113" t="str">
+        <v>0</v>
+      </c>
+      <c r="R113" t="str">
+        <v>0</v>
+      </c>
+      <c r="S113" t="str">
+        <v>0</v>
+      </c>
+      <c r="T113" t="str">
+        <v>0</v>
+      </c>
+      <c r="U113" t="str">
+        <v>2</v>
+      </c>
+      <c r="V113" t="str">
+        <v>0</v>
+      </c>
+      <c r="W113" t="str">
+        <v>1</v>
+      </c>
+      <c r="X113" t="str">
+        <v>4/27/26</v>
+      </c>
+      <c r="Y113" t="str">
+        <v>8/10/26</v>
+      </c>
+      <c r="Z113" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="AA113" t="str">
+        <v>NGÂN</v>
+      </c>
+      <c r="AB113" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="AD113" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="AE113" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="str">
+        <v>(200)</v>
+      </c>
+      <c r="B114" t="str">
+        <v>(1) Viet Nga Group, (2) Viet Nga Group - HKD Sáu Lang</v>
+      </c>
+      <c r="C114" t="str">
+        <v>77038</v>
+      </c>
+      <c r="D114" t="str">
+        <v>916727301</v>
+      </c>
+      <c r="E114" t="str">
+        <v>LÊ VĂN BỈ</v>
+      </c>
+      <c r="F114" t="str">
+        <v>HỘ KINH DOANH SÁU LANG</v>
+      </c>
+      <c r="J114" t="str">
+        <v>Intensive rice production // Trồng lúa thâm canh</v>
+      </c>
+      <c r="K114" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="L114" t="str">
+        <v>Male // Nam</v>
+      </c>
+      <c r="M114" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="N114" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O114" t="str">
+        <v>0</v>
+      </c>
+      <c r="P114" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q114" t="str">
+        <v>0</v>
+      </c>
+      <c r="R114" t="str">
+        <v>0</v>
+      </c>
+      <c r="S114" t="str">
+        <v>0</v>
+      </c>
+      <c r="T114" t="str">
+        <v>0</v>
+      </c>
+      <c r="U114" t="str">
+        <v>3</v>
+      </c>
+      <c r="V114" t="str">
+        <v>0</v>
+      </c>
+      <c r="W114" t="str">
+        <v>2</v>
+      </c>
+      <c r="X114" t="str">
+        <v>4/27/26</v>
+      </c>
+      <c r="Y114" t="str">
+        <v>8/10/26</v>
+      </c>
+      <c r="Z114" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="AA114" t="str">
+        <v>NGÂN</v>
+      </c>
+      <c r="AB114" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="AD114" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="AE114" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="str">
+        <v>(201)</v>
+      </c>
+      <c r="B115" t="str">
+        <v>(1) Viet Nga Group, (2) Viet Nga Group - HKD Sáu Lang</v>
+      </c>
+      <c r="C115" t="str">
+        <v>77039</v>
+      </c>
+      <c r="D115" t="str">
+        <v>399978902</v>
+      </c>
+      <c r="E115" t="str">
+        <v>NGUYỄN VĂN TÙNG</v>
+      </c>
+      <c r="F115" t="str">
+        <v>HỘ KINH DOANH SÁU LANG</v>
+      </c>
+      <c r="J115" t="str">
+        <v>Intensive rice production // Trồng lúa thâm canh</v>
+      </c>
+      <c r="K115" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="L115" t="str">
+        <v>Male // Nam</v>
+      </c>
+      <c r="M115" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="N115" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O115" t="str">
+        <v>0</v>
+      </c>
+      <c r="P115" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q115" t="str">
+        <v>0</v>
+      </c>
+      <c r="R115" t="str">
+        <v>0</v>
+      </c>
+      <c r="S115" t="str">
+        <v>0</v>
+      </c>
+      <c r="T115" t="str">
+        <v>0</v>
+      </c>
+      <c r="U115" t="str">
+        <v>2</v>
+      </c>
+      <c r="V115" t="str">
+        <v>0</v>
+      </c>
+      <c r="W115" t="str">
+        <v>1</v>
+      </c>
+      <c r="X115" t="str">
+        <v>4/27/26</v>
+      </c>
+      <c r="Y115" t="str">
+        <v>8/10/26</v>
+      </c>
+      <c r="Z115" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="AA115" t="str">
+        <v>NGÂN</v>
+      </c>
+      <c r="AB115" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="AD115" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="AE115" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="str">
+        <v>(204)</v>
+      </c>
+      <c r="B116" t="str">
+        <v>(1) Viet Nga Group, (2) Viet Nga Group - HKD Sáu Lang</v>
+      </c>
+      <c r="C116" t="str">
+        <v>77042</v>
+      </c>
+      <c r="D116" t="str">
+        <v>343048455</v>
+      </c>
+      <c r="E116" t="str">
+        <v>CHÂU VĂN HIẾU</v>
+      </c>
+      <c r="F116" t="str">
+        <v>HỘ KINH DOANH SÁU LANG</v>
+      </c>
+      <c r="J116" t="str">
+        <v>Intensive rice production // Trồng lúa thâm canh</v>
+      </c>
+      <c r="K116" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="L116" t="str">
+        <v>Male // Nam</v>
+      </c>
+      <c r="M116" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="N116" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O116" t="str">
+        <v>0</v>
+      </c>
+      <c r="P116" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q116" t="str">
+        <v>0</v>
+      </c>
+      <c r="R116" t="str">
+        <v>0</v>
+      </c>
+      <c r="S116" t="str">
+        <v>0</v>
+      </c>
+      <c r="T116" t="str">
+        <v>0</v>
+      </c>
+      <c r="U116" t="str">
+        <v>2</v>
+      </c>
+      <c r="V116" t="str">
+        <v>0</v>
+      </c>
+      <c r="W116" t="str">
+        <v>1</v>
+      </c>
+      <c r="X116" t="str">
+        <v>4/27/26</v>
+      </c>
+      <c r="Y116" t="str">
+        <v>8/10/26</v>
+      </c>
+      <c r="Z116" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="AA116" t="str">
+        <v>NGÂN</v>
+      </c>
+      <c r="AB116" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="AD116" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="AE116" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="str">
+        <v>(206)</v>
+      </c>
+      <c r="B117" t="str">
+        <v>(1) Viet Nga Group, (2) Viet Nga Group - HKD Sáu Lang</v>
+      </c>
+      <c r="C117" t="str">
+        <v>77044</v>
+      </c>
+      <c r="D117" t="str">
+        <v>987071627</v>
+      </c>
+      <c r="E117" t="str">
+        <v>PHẠM VĂN SƠN</v>
+      </c>
+      <c r="F117" t="str">
+        <v>HỘ KINH DOANH SÁU LANG</v>
+      </c>
+      <c r="J117" t="str">
+        <v>Intensive rice production // Trồng lúa thâm canh</v>
+      </c>
+      <c r="K117" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="L117" t="str">
+        <v>Male // Nam</v>
+      </c>
+      <c r="M117" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="N117" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O117" t="str">
+        <v>0</v>
+      </c>
+      <c r="P117" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q117" t="str">
+        <v>0</v>
+      </c>
+      <c r="R117" t="str">
+        <v>0</v>
+      </c>
+      <c r="S117" t="str">
+        <v>0</v>
+      </c>
+      <c r="T117" t="str">
+        <v>0</v>
+      </c>
+      <c r="U117" t="str">
+        <v>3</v>
+      </c>
+      <c r="V117" t="str">
+        <v>0</v>
+      </c>
+      <c r="W117" t="str">
+        <v>2</v>
+      </c>
+      <c r="X117" t="str">
+        <v>4/27/26</v>
+      </c>
+      <c r="Y117" t="str">
+        <v>8/10/26</v>
+      </c>
+      <c r="Z117" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="AA117" t="str">
+        <v>NGÂN</v>
+      </c>
+      <c r="AB117" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="AD117" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="AE117" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="str">
+        <v>(207)</v>
+      </c>
+      <c r="B118" t="str">
+        <v>(1) Viet Nga Group, (2) Viet Nga Group - HKD Sáu Lang</v>
+      </c>
+      <c r="C118" t="str">
+        <v>77045</v>
+      </c>
+      <c r="D118" t="str">
+        <v>388658432</v>
+      </c>
+      <c r="E118" t="str">
+        <v>TRẦN MINH PHỤNG</v>
+      </c>
+      <c r="F118" t="str">
+        <v>HỘ KINH DOANH SÁU LANG</v>
+      </c>
+      <c r="J118" t="str">
+        <v>Intensive rice production // Trồng lúa thâm canh</v>
+      </c>
+      <c r="K118" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="L118" t="str">
+        <v>Male // Nam</v>
+      </c>
+      <c r="M118" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="N118" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O118" t="str">
+        <v>0</v>
+      </c>
+      <c r="P118" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q118" t="str">
+        <v>0</v>
+      </c>
+      <c r="R118" t="str">
+        <v>0</v>
+      </c>
+      <c r="S118" t="str">
+        <v>0</v>
+      </c>
+      <c r="T118" t="str">
+        <v>0</v>
+      </c>
+      <c r="U118" t="str">
+        <v>3</v>
+      </c>
+      <c r="V118" t="str">
+        <v>0</v>
+      </c>
+      <c r="W118" t="str">
+        <v>2</v>
+      </c>
+      <c r="X118" t="str">
+        <v>4/27/26</v>
+      </c>
+      <c r="Y118" t="str">
+        <v>8/10/26</v>
+      </c>
+      <c r="Z118" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="AA118" t="str">
+        <v>NGÂN</v>
+      </c>
+      <c r="AB118" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="AD118" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="AE118" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="str">
+        <v>(209)</v>
+      </c>
+      <c r="B119" t="str">
+        <v>(1) Viet Nga Group, (2) Viet Nga Group - HKD Sáu Lang</v>
+      </c>
+      <c r="C119" t="str">
+        <v>77047</v>
+      </c>
+      <c r="D119" t="str">
+        <v>916797603</v>
+      </c>
+      <c r="E119" t="str">
+        <v>TRẦN VĂN BẦU</v>
+      </c>
+      <c r="F119" t="str">
+        <v>HỘ KINH DOANH SÁU LANG</v>
+      </c>
+      <c r="J119" t="str">
+        <v>Intensive rice production // Trồng lúa thâm canh</v>
+      </c>
+      <c r="K119" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="L119" t="str">
+        <v>Male // Nam</v>
+      </c>
+      <c r="M119" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="N119" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O119" t="str">
+        <v>0</v>
+      </c>
+      <c r="P119" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q119" t="str">
+        <v>0</v>
+      </c>
+      <c r="R119" t="str">
+        <v>0</v>
+      </c>
+      <c r="S119" t="str">
+        <v>0</v>
+      </c>
+      <c r="T119" t="str">
+        <v>0</v>
+      </c>
+      <c r="U119" t="str">
+        <v>3</v>
+      </c>
+      <c r="V119" t="str">
+        <v>0</v>
+      </c>
+      <c r="W119" t="str">
+        <v>2</v>
+      </c>
+      <c r="X119" t="str">
+        <v>4/27/26</v>
+      </c>
+      <c r="Y119" t="str">
+        <v>8/10/26</v>
+      </c>
+      <c r="Z119" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="AA119" t="str">
+        <v>NGÂN</v>
+      </c>
+      <c r="AB119" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="AD119" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="AE119" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="str">
+        <v>(210)</v>
+      </c>
+      <c r="B120" t="str">
+        <v>(1) Viet Nga Group, (2) Viet Nga Group - HKD Sáu Lang</v>
+      </c>
+      <c r="C120" t="str">
+        <v>77048</v>
+      </c>
+      <c r="D120" t="str">
+        <v>916797063</v>
+      </c>
+      <c r="E120" t="str">
+        <v>NGUYỄN VĂN HOAI</v>
+      </c>
+      <c r="F120" t="str">
+        <v>HỘ KINH DOANH SÁU LANG</v>
+      </c>
+      <c r="J120" t="str">
+        <v>Intensive rice production // Trồng lúa thâm canh</v>
+      </c>
+      <c r="K120" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="L120" t="str">
+        <v>Male // Nam</v>
+      </c>
+      <c r="M120" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="N120" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O120" t="str">
+        <v>0</v>
+      </c>
+      <c r="P120" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q120" t="str">
+        <v>0</v>
+      </c>
+      <c r="R120" t="str">
+        <v>0</v>
+      </c>
+      <c r="S120" t="str">
+        <v>0</v>
+      </c>
+      <c r="T120" t="str">
+        <v>0</v>
+      </c>
+      <c r="U120" t="str">
+        <v>3</v>
+      </c>
+      <c r="V120" t="str">
+        <v>0</v>
+      </c>
+      <c r="W120" t="str">
+        <v>2</v>
+      </c>
+      <c r="X120" t="str">
+        <v>4/27/26</v>
+      </c>
+      <c r="Y120" t="str">
+        <v>8/10/26</v>
+      </c>
+      <c r="Z120" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="AA120" t="str">
+        <v>NGÂN</v>
+      </c>
+      <c r="AB120" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="AD120" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="AE120" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="str">
+        <v>(211)</v>
+      </c>
+      <c r="B121" t="str">
+        <v>(1) Viet Nga Group, (2) Viet Nga Group - HKD Sáu Lang</v>
+      </c>
+      <c r="C121" t="str">
+        <v>77049</v>
+      </c>
+      <c r="D121" t="str">
+        <v>978918819</v>
+      </c>
+      <c r="E121" t="str">
+        <v>NGUYỄN VĂN DẪU</v>
+      </c>
+      <c r="F121" t="str">
+        <v>HỘ KINH DOANH SÁU LANG</v>
+      </c>
+      <c r="J121" t="str">
+        <v>Intensive rice production // Trồng lúa thâm canh</v>
+      </c>
+      <c r="K121" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="L121" t="str">
+        <v>Male // Nam</v>
+      </c>
+      <c r="M121" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="N121" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O121" t="str">
+        <v>0</v>
+      </c>
+      <c r="P121" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q121" t="str">
+        <v>0</v>
+      </c>
+      <c r="R121" t="str">
+        <v>0</v>
+      </c>
+      <c r="S121" t="str">
+        <v>0</v>
+      </c>
+      <c r="T121" t="str">
+        <v>0</v>
+      </c>
+      <c r="U121" t="str">
+        <v>2</v>
+      </c>
+      <c r="V121" t="str">
+        <v>0</v>
+      </c>
+      <c r="W121" t="str">
+        <v>1</v>
+      </c>
+      <c r="X121" t="str">
+        <v>4/27/26</v>
+      </c>
+      <c r="Y121" t="str">
+        <v>8/10/26</v>
+      </c>
+      <c r="Z121" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="AA121" t="str">
+        <v>NGÂN</v>
+      </c>
+      <c r="AB121" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="AD121" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="AE121" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="str">
+        <v>(212)</v>
+      </c>
+      <c r="B122" t="str">
+        <v>(1) Viet Nga Group, (2) Viet Nga Group - HKD Sáu Lang</v>
+      </c>
+      <c r="C122" t="str">
+        <v>77050</v>
+      </c>
+      <c r="D122" t="str">
+        <v>333222162</v>
+      </c>
+      <c r="E122" t="str">
+        <v>ĐẶNG VĂN BÌNH</v>
+      </c>
+      <c r="F122" t="str">
+        <v>HỘ KINH DOANH SÁU LANG</v>
+      </c>
+      <c r="J122" t="str">
+        <v>Intensive rice production // Trồng lúa thâm canh</v>
+      </c>
+      <c r="K122" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="L122" t="str">
+        <v>Male // Nam</v>
+      </c>
+      <c r="M122" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="N122" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O122" t="str">
+        <v>0</v>
+      </c>
+      <c r="P122" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q122" t="str">
+        <v>0</v>
+      </c>
+      <c r="R122" t="str">
+        <v>0</v>
+      </c>
+      <c r="S122" t="str">
+        <v>0</v>
+      </c>
+      <c r="T122" t="str">
+        <v>0</v>
+      </c>
+      <c r="U122" t="str">
+        <v>2</v>
+      </c>
+      <c r="V122" t="str">
+        <v>0</v>
+      </c>
+      <c r="W122" t="str">
+        <v>1</v>
+      </c>
+      <c r="X122" t="str">
+        <v>4/27/26</v>
+      </c>
+      <c r="Y122" t="str">
+        <v>8/10/26</v>
+      </c>
+      <c r="Z122" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="AA122" t="str">
+        <v>NGÂN</v>
+      </c>
+      <c r="AB122" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="AD122" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="AE122" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="str">
+        <v>(214)</v>
+      </c>
+      <c r="B123" t="str">
+        <v>(1) Viet Nga Group, (2) Viet Nga Group - HKD Sáu Lang</v>
+      </c>
+      <c r="C123" t="str">
+        <v>77052</v>
+      </c>
+      <c r="D123" t="str">
+        <v>909621146</v>
+      </c>
+      <c r="E123" t="str">
+        <v>NGUYỄN THÀNH QUÝ</v>
+      </c>
+      <c r="F123" t="str">
+        <v>HỘ KINH DOANH SÁU LANG</v>
+      </c>
+      <c r="J123" t="str">
+        <v>Intensive rice production // Trồng lúa thâm canh</v>
+      </c>
+      <c r="K123" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="L123" t="str">
+        <v>Male // Nam</v>
+      </c>
+      <c r="M123" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="N123" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O123" t="str">
+        <v>0</v>
+      </c>
+      <c r="P123" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q123" t="str">
+        <v>0</v>
+      </c>
+      <c r="R123" t="str">
+        <v>0</v>
+      </c>
+      <c r="S123" t="str">
+        <v>0</v>
+      </c>
+      <c r="T123" t="str">
+        <v>0</v>
+      </c>
+      <c r="U123" t="str">
+        <v>2</v>
+      </c>
+      <c r="V123" t="str">
+        <v>0</v>
+      </c>
+      <c r="W123" t="str">
+        <v>1</v>
+      </c>
+      <c r="X123" t="str">
+        <v>4/27/26</v>
+      </c>
+      <c r="Y123" t="str">
+        <v>8/10/26</v>
+      </c>
+      <c r="Z123" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="AA123" t="str">
+        <v>NGÂN</v>
+      </c>
+      <c r="AB123" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="AD123" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="AE123" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="str">
+        <v>(215)</v>
+      </c>
+      <c r="B124" t="str">
+        <v>(1) Viet Nga Group, (2) Viet Nga Group - HKD Sáu Lang</v>
+      </c>
+      <c r="C124" t="str">
+        <v>77053</v>
+      </c>
+      <c r="D124" t="str">
+        <v>395129755</v>
+      </c>
+      <c r="E124" t="str">
+        <v>LÊ VĂN BÌNH</v>
+      </c>
+      <c r="F124" t="str">
+        <v>HỘ KINH DOANH SÁU LANG</v>
+      </c>
+      <c r="J124" t="str">
+        <v>Intensive rice production // Trồng lúa thâm canh</v>
+      </c>
+      <c r="K124" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="L124" t="str">
+        <v>Male // Nam</v>
+      </c>
+      <c r="M124" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="N124" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O124" t="str">
+        <v>0</v>
+      </c>
+      <c r="P124" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q124" t="str">
+        <v>0</v>
+      </c>
+      <c r="R124" t="str">
+        <v>0</v>
+      </c>
+      <c r="S124" t="str">
+        <v>0</v>
+      </c>
+      <c r="T124" t="str">
+        <v>0</v>
+      </c>
+      <c r="U124" t="str">
+        <v>2</v>
+      </c>
+      <c r="V124" t="str">
+        <v>0</v>
+      </c>
+      <c r="W124" t="str">
+        <v>1</v>
+      </c>
+      <c r="X124" t="str">
+        <v>4/27/26</v>
+      </c>
+      <c r="Y124" t="str">
+        <v>8/10/26</v>
+      </c>
+      <c r="Z124" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="AA124" t="str">
+        <v>NGÂN</v>
+      </c>
+      <c r="AB124" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="AD124" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="AE124" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="str">
+        <v>(216)</v>
+      </c>
+      <c r="B125" t="str">
+        <v>(1) Viet Nga Group, (2) Viet Nga Group - HKD Sáu Lang</v>
+      </c>
+      <c r="C125" t="str">
+        <v>77054</v>
+      </c>
+      <c r="D125" t="str">
+        <v>917422363</v>
+      </c>
+      <c r="E125" t="str">
+        <v>LÊ VĂN MÃI</v>
+      </c>
+      <c r="F125" t="str">
+        <v>HỘ KINH DOANH SÁU LANG</v>
+      </c>
+      <c r="J125" t="str">
+        <v>Intensive rice production // Trồng lúa thâm canh</v>
+      </c>
+      <c r="K125" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="L125" t="str">
+        <v>Male // Nam</v>
+      </c>
+      <c r="M125" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="N125" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O125" t="str">
+        <v>0</v>
+      </c>
+      <c r="P125" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q125" t="str">
+        <v>0</v>
+      </c>
+      <c r="R125" t="str">
+        <v>0</v>
+      </c>
+      <c r="S125" t="str">
+        <v>0</v>
+      </c>
+      <c r="T125" t="str">
+        <v>0</v>
+      </c>
+      <c r="U125" t="str">
+        <v>3</v>
+      </c>
+      <c r="V125" t="str">
+        <v>0</v>
+      </c>
+      <c r="W125" t="str">
+        <v>2</v>
+      </c>
+      <c r="X125" t="str">
+        <v>4/27/26</v>
+      </c>
+      <c r="Y125" t="str">
+        <v>8/10/26</v>
+      </c>
+      <c r="Z125" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="AA125" t="str">
+        <v>NGÂN</v>
+      </c>
+      <c r="AB125" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="AD125" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="AE125" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="str">
+        <v>(217)</v>
+      </c>
+      <c r="B126" t="str">
+        <v>(1) Viet Nga Group, (2) Việt Nga Group - HKD Tấn Phúc</v>
+      </c>
+      <c r="C126" t="str">
+        <v>74821</v>
+      </c>
+      <c r="D126" t="str">
+        <v>382033697</v>
+      </c>
+      <c r="E126" t="str">
+        <v>HUỲNH CÔNG TRIỆU</v>
+      </c>
+      <c r="F126" t="str">
+        <v>HỘ KINH DOANH TẤN PHÚC</v>
+      </c>
+      <c r="J126" t="str">
+        <v>Intensive rice production // Trồng lúa thâm canh</v>
+      </c>
+      <c r="K126" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="L126" t="str">
+        <v>Male // Nam</v>
+      </c>
+      <c r="M126" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="N126" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O126" t="str">
+        <v>0</v>
+      </c>
+      <c r="P126" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q126" t="str">
+        <v>0</v>
+      </c>
+      <c r="R126" t="str">
+        <v>0</v>
+      </c>
+      <c r="S126" t="str">
+        <v>0</v>
+      </c>
+      <c r="T126" t="str">
+        <v>0</v>
+      </c>
+      <c r="U126" t="str">
+        <v>3</v>
+      </c>
+      <c r="V126" t="str">
+        <v>0</v>
+      </c>
+      <c r="W126" t="str">
+        <v>2</v>
+      </c>
+      <c r="X126" t="str">
+        <v>4/23/26</v>
+      </c>
+      <c r="Y126" t="str">
+        <v>8/2/26</v>
+      </c>
+      <c r="Z126" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="AA126" t="str">
+        <v>NGÂN</v>
+      </c>
+      <c r="AB126" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="AD126" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="AE126" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="str">
+        <v>(220)</v>
+      </c>
+      <c r="B127" t="str">
+        <v>(1) Viet Nga Group, (2) Việt Nga Group - HKD Tấn Phúc</v>
+      </c>
+      <c r="C127" t="str">
+        <v>74824</v>
+      </c>
+      <c r="D127" t="str">
+        <v>338204050</v>
+      </c>
+      <c r="E127" t="str">
+        <v>PHAN VĂN TO</v>
+      </c>
+      <c r="F127" t="str">
+        <v>HỘ KINH DOANH TẤN PHÚC</v>
+      </c>
+      <c r="J127" t="str">
+        <v>Intensive rice production // Trồng lúa thâm canh</v>
+      </c>
+      <c r="K127" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="L127" t="str">
+        <v>Male // Nam</v>
+      </c>
+      <c r="M127" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="N127" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O127" t="str">
+        <v>0</v>
+      </c>
+      <c r="P127" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q127" t="str">
+        <v>0</v>
+      </c>
+      <c r="R127" t="str">
+        <v>0</v>
+      </c>
+      <c r="S127" t="str">
+        <v>0</v>
+      </c>
+      <c r="T127" t="str">
+        <v>0</v>
+      </c>
+      <c r="U127" t="str">
+        <v>3</v>
+      </c>
+      <c r="V127" t="str">
+        <v>0</v>
+      </c>
+      <c r="W127" t="str">
+        <v>2</v>
+      </c>
+      <c r="X127" t="str">
+        <v>4/23/26</v>
+      </c>
+      <c r="Y127" t="str">
+        <v>8/2/26</v>
+      </c>
+      <c r="Z127" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="AA127" t="str">
+        <v>NGÂN</v>
+      </c>
+      <c r="AB127" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="AD127" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="AE127" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="str">
+        <v>(221)</v>
+      </c>
+      <c r="B128" t="str">
+        <v>(1) Viet Nga Group, (2) Việt Nga Group - HKD Tấn Phúc</v>
+      </c>
+      <c r="C128" t="str">
+        <v>74825</v>
+      </c>
+      <c r="D128" t="str">
+        <v>812828128</v>
+      </c>
+      <c r="E128" t="str">
+        <v>NGUYỄN ANH TÚ</v>
+      </c>
+      <c r="F128" t="str">
+        <v>HỘ KINH DOANH TẤN PHÚC</v>
+      </c>
+      <c r="J128" t="str">
+        <v>Intensive rice production // Trồng lúa thâm canh</v>
+      </c>
+      <c r="K128" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="L128" t="str">
+        <v>Male // Nam</v>
+      </c>
+      <c r="M128" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="N128" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O128" t="str">
+        <v>0</v>
+      </c>
+      <c r="P128" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q128" t="str">
+        <v>0</v>
+      </c>
+      <c r="R128" t="str">
+        <v>0</v>
+      </c>
+      <c r="S128" t="str">
+        <v>0</v>
+      </c>
+      <c r="T128" t="str">
+        <v>0</v>
+      </c>
+      <c r="U128" t="str">
+        <v>3</v>
+      </c>
+      <c r="V128" t="str">
+        <v>0</v>
+      </c>
+      <c r="W128" t="str">
+        <v>2</v>
+      </c>
+      <c r="X128" t="str">
+        <v>4/23/26</v>
+      </c>
+      <c r="Y128" t="str">
+        <v>8/2/26</v>
+      </c>
+      <c r="Z128" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="AA128" t="str">
+        <v>NGÂN</v>
+      </c>
+      <c r="AB128" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="AD128" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="AE128" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="str">
+        <v>(224)</v>
+      </c>
+      <c r="B129" t="str">
+        <v>(1) Viet Nga Group, (2) Việt Nga Group - HKD Tấn Phúc</v>
+      </c>
+      <c r="C129" t="str">
+        <v>74828</v>
+      </c>
+      <c r="D129" t="str">
+        <v>707351340</v>
+      </c>
+      <c r="E129" t="str">
+        <v>LƯU THIÊN HUYỀN</v>
+      </c>
+      <c r="F129" t="str">
+        <v>HỘ KINH DOANH TẤN PHÚC</v>
+      </c>
+      <c r="J129" t="str">
+        <v>Intensive rice production // Trồng lúa thâm canh</v>
+      </c>
+      <c r="K129" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="L129" t="str">
+        <v>Female // Nữ</v>
+      </c>
+      <c r="M129" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="N129" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O129" t="str">
+        <v>1</v>
+      </c>
+      <c r="P129" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q129" t="str">
+        <v>0</v>
+      </c>
+      <c r="R129" t="str">
+        <v>0</v>
+      </c>
+      <c r="S129" t="str">
+        <v>0</v>
+      </c>
+      <c r="T129" t="str">
+        <v>0</v>
+      </c>
+      <c r="U129" t="str">
+        <v>3</v>
+      </c>
+      <c r="V129" t="str">
+        <v>0</v>
+      </c>
+      <c r="W129" t="str">
+        <v>2</v>
+      </c>
+      <c r="X129" t="str">
+        <v>4/23/26</v>
+      </c>
+      <c r="Y129" t="str">
+        <v>8/2/26</v>
+      </c>
+      <c r="Z129" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="AA129" t="str">
+        <v>NGÂN</v>
+      </c>
+      <c r="AB129" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="AD129" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="AE129" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="str">
+        <v>(225)</v>
+      </c>
+      <c r="B130" t="str">
+        <v>(1) Viet Nga Group, (2) Việt Nga Group - HKD Tấn Phúc</v>
+      </c>
+      <c r="C130" t="str">
+        <v>74829</v>
+      </c>
+      <c r="D130" t="str">
+        <v>944248381</v>
+      </c>
+      <c r="E130" t="str">
+        <v>ĐINH HỮU CẢNH</v>
+      </c>
+      <c r="F130" t="str">
+        <v>HỘ KINH DOANH TẤN PHÚC</v>
+      </c>
+      <c r="J130" t="str">
+        <v>Intensive rice production // Trồng lúa thâm canh</v>
+      </c>
+      <c r="K130" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="L130" t="str">
+        <v>Male // Nam</v>
+      </c>
+      <c r="M130" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="N130" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O130" t="str">
+        <v>0</v>
+      </c>
+      <c r="P130" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q130" t="str">
+        <v>0</v>
+      </c>
+      <c r="R130" t="str">
+        <v>0</v>
+      </c>
+      <c r="S130" t="str">
+        <v>0</v>
+      </c>
+      <c r="T130" t="str">
+        <v>0</v>
+      </c>
+      <c r="U130" t="str">
+        <v>3</v>
+      </c>
+      <c r="V130" t="str">
+        <v>0</v>
+      </c>
+      <c r="W130" t="str">
+        <v>2</v>
+      </c>
+      <c r="X130" t="str">
+        <v>4/23/26</v>
+      </c>
+      <c r="Y130" t="str">
+        <v>8/2/26</v>
+      </c>
+      <c r="Z130" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="AA130" t="str">
+        <v>NGÂN</v>
+      </c>
+      <c r="AB130" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="AD130" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="AE130" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="str">
+        <v>(227)</v>
+      </c>
+      <c r="B131" t="str">
+        <v>(1) Viet Nga Group, (2) Việt Nga Group - HKD Tấn Phúc</v>
+      </c>
+      <c r="C131" t="str">
+        <v>74831</v>
+      </c>
+      <c r="D131" t="str">
+        <v>385234164</v>
+      </c>
+      <c r="E131" t="str">
+        <v>NGUYỄN VĂN THIỆT</v>
+      </c>
+      <c r="F131" t="str">
+        <v>HỘ KINH DOANH TẤN PHÚC</v>
+      </c>
+      <c r="J131" t="str">
+        <v>Intensive rice production // Trồng lúa thâm canh</v>
+      </c>
+      <c r="K131" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="L131" t="str">
+        <v>Male // Nam</v>
+      </c>
+      <c r="M131" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="N131" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O131" t="str">
+        <v>0</v>
+      </c>
+      <c r="P131" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q131" t="str">
+        <v>0</v>
+      </c>
+      <c r="R131" t="str">
+        <v>0</v>
+      </c>
+      <c r="S131" t="str">
+        <v>0</v>
+      </c>
+      <c r="T131" t="str">
+        <v>0</v>
+      </c>
+      <c r="U131" t="str">
+        <v>3</v>
+      </c>
+      <c r="V131" t="str">
+        <v>0</v>
+      </c>
+      <c r="W131" t="str">
+        <v>2</v>
+      </c>
+      <c r="X131" t="str">
+        <v>4/23/26</v>
+      </c>
+      <c r="Y131" t="str">
+        <v>8/2/26</v>
+      </c>
+      <c r="Z131" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="AA131" t="str">
+        <v>NGÂN</v>
+      </c>
+      <c r="AB131" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="AD131" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="AE131" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="str">
+        <v>(233)</v>
+      </c>
+      <c r="B132" t="str">
+        <v>(1) Viet Nga Group, (2) Việt Nga Group - HKD Tấn Phúc</v>
+      </c>
+      <c r="C132" t="str">
+        <v>74837</v>
+      </c>
+      <c r="D132" t="str">
+        <v>333113844</v>
+      </c>
+      <c r="E132" t="str">
+        <v>NGUYỄN VĂN THUẬN</v>
+      </c>
+      <c r="F132" t="str">
+        <v>HỘ KINH DOANH TẤN PHÚC</v>
+      </c>
+      <c r="J132" t="str">
+        <v>Intensive rice production // Trồng lúa thâm canh</v>
+      </c>
+      <c r="K132" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="L132" t="str">
+        <v>Male // Nam</v>
+      </c>
+      <c r="M132" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="N132" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O132" t="str">
+        <v>0</v>
+      </c>
+      <c r="P132" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q132" t="str">
+        <v>0</v>
+      </c>
+      <c r="R132" t="str">
+        <v>0</v>
+      </c>
+      <c r="S132" t="str">
+        <v>0</v>
+      </c>
+      <c r="T132" t="str">
+        <v>0</v>
+      </c>
+      <c r="U132" t="str">
+        <v>3</v>
+      </c>
+      <c r="V132" t="str">
+        <v>0</v>
+      </c>
+      <c r="W132" t="str">
+        <v>2</v>
+      </c>
+      <c r="X132" t="str">
+        <v>4/23/26</v>
+      </c>
+      <c r="Y132" t="str">
+        <v>8/2/26</v>
+      </c>
+      <c r="Z132" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="AA132" t="str">
+        <v>NGÂN</v>
+      </c>
+      <c r="AB132" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="AD132" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="AE132" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="str">
+        <v>(238)</v>
+      </c>
+      <c r="B133" t="str">
+        <v>(1) Viet Nga Group, (2) Việt Nga Group-THT HKD Thanh Mai</v>
+      </c>
+      <c r="C133" t="str">
+        <v>73393</v>
+      </c>
+      <c r="D133" t="str">
+        <v>989203032</v>
+      </c>
+      <c r="E133" t="str">
+        <v>BÙI THỊ NGUYỆT</v>
+      </c>
+      <c r="F133" t="str">
+        <v>HỘ KINH DOANH THANH MAI</v>
+      </c>
+      <c r="J133" t="str">
+        <v>Intensive rice production // Trồng lúa thâm canh</v>
+      </c>
+      <c r="K133" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="L133" t="str">
+        <v>Female // Nữ</v>
+      </c>
+      <c r="M133" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="N133" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O133" t="str">
+        <v>1</v>
+      </c>
+      <c r="P133" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q133" t="str">
+        <v>0</v>
+      </c>
+      <c r="R133" t="str">
+        <v>0</v>
+      </c>
+      <c r="S133" t="str">
+        <v>0</v>
+      </c>
+      <c r="T133" t="str">
+        <v>0</v>
+      </c>
+      <c r="U133" t="str">
+        <v>3</v>
+      </c>
+      <c r="V133" t="str">
+        <v>0</v>
+      </c>
+      <c r="W133" t="str">
+        <v>2</v>
+      </c>
+      <c r="X133" t="str">
+        <v>4/6/26</v>
+      </c>
+      <c r="Y133" t="str">
+        <v>7/10/26</v>
+      </c>
+      <c r="Z133" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="AA133" t="str">
+        <v>NGÂN</v>
+      </c>
+      <c r="AB133" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="AD133" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="AE133" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="str">
+        <v>(240)</v>
+      </c>
+      <c r="B134" t="str">
+        <v>(1) Viet Nga Group, (2) Việt Nga Group-THT HKD Thanh Mai</v>
+      </c>
+      <c r="C134" t="str">
+        <v>73395</v>
+      </c>
+      <c r="D134" t="str">
+        <v>352472602</v>
+      </c>
+      <c r="E134" t="str">
+        <v>TRẦN TẤN YẾN</v>
+      </c>
+      <c r="F134" t="str">
+        <v>HỘ KINH DOANH THANH MAI</v>
+      </c>
+      <c r="J134" t="str">
+        <v>Intensive rice production // Trồng lúa thâm canh</v>
+      </c>
+      <c r="K134" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="L134" t="str">
+        <v>Male // Nam</v>
+      </c>
+      <c r="M134" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="N134" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O134" t="str">
+        <v>0</v>
+      </c>
+      <c r="P134" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q134" t="str">
+        <v>0</v>
+      </c>
+      <c r="R134" t="str">
+        <v>0</v>
+      </c>
+      <c r="S134" t="str">
+        <v>0</v>
+      </c>
+      <c r="T134" t="str">
+        <v>0</v>
+      </c>
+      <c r="U134" t="str">
+        <v>4</v>
+      </c>
+      <c r="V134" t="str">
+        <v>0</v>
+      </c>
+      <c r="W134" t="str">
+        <v>3</v>
+      </c>
+      <c r="X134" t="str">
+        <v>4/6/26</v>
+      </c>
+      <c r="Y134" t="str">
+        <v>7/10/26</v>
+      </c>
+      <c r="Z134" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="AA134" t="str">
+        <v>NGÂN</v>
+      </c>
+      <c r="AB134" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="AD134" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="AE134" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="str">
+        <v>(243)</v>
+      </c>
+      <c r="B135" t="str">
+        <v>(1) Viet Nga Group, (2) Việt Nga Group-THT HKD Thanh Mai</v>
+      </c>
+      <c r="C135" t="str">
+        <v>73398</v>
+      </c>
+      <c r="D135" t="str">
+        <v>377310428</v>
+      </c>
+      <c r="E135" t="str">
+        <v>DƯƠNG HOÀNG GIANG</v>
+      </c>
+      <c r="F135" t="str">
+        <v>HỘ KINH DOANH THANH MAI</v>
+      </c>
+      <c r="J135" t="str">
+        <v>Intensive rice production // Trồng lúa thâm canh</v>
+      </c>
+      <c r="K135" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="L135" t="str">
+        <v>Female // Nữ</v>
+      </c>
+      <c r="M135" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="N135" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O135" t="str">
+        <v>1</v>
+      </c>
+      <c r="P135" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q135" t="str">
+        <v>0</v>
+      </c>
+      <c r="R135" t="str">
+        <v>0</v>
+      </c>
+      <c r="S135" t="str">
+        <v>0</v>
+      </c>
+      <c r="T135" t="str">
+        <v>0</v>
+      </c>
+      <c r="U135" t="str">
+        <v>2</v>
+      </c>
+      <c r="V135" t="str">
+        <v>0</v>
+      </c>
+      <c r="W135" t="str">
+        <v>1</v>
+      </c>
+      <c r="X135" t="str">
+        <v>4/6/26</v>
+      </c>
+      <c r="Y135" t="str">
+        <v>7/10/26</v>
+      </c>
+      <c r="Z135" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="AA135" t="str">
+        <v>NGÂN</v>
+      </c>
+      <c r="AB135" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="AD135" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="AE135" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="str">
+        <v>(244)</v>
+      </c>
+      <c r="B136" t="str">
+        <v>(1) Viet Nga Group, (2) Việt Nga Group-THT HKD Thanh Mai</v>
+      </c>
+      <c r="C136" t="str">
+        <v>73399</v>
+      </c>
+      <c r="D136" t="str">
+        <v>388673145</v>
+      </c>
+      <c r="E136" t="str">
+        <v>NGUYỄN VĂN DƯỜNG</v>
+      </c>
+      <c r="F136" t="str">
+        <v>HỘ KINH DOANH THANH MAI</v>
+      </c>
+      <c r="J136" t="str">
+        <v>Intensive rice production // Trồng lúa thâm canh</v>
+      </c>
+      <c r="K136" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="L136" t="str">
+        <v>Male // Nam</v>
+      </c>
+      <c r="M136" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="N136" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O136" t="str">
+        <v>0</v>
+      </c>
+      <c r="P136" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q136" t="str">
+        <v>0</v>
+      </c>
+      <c r="R136" t="str">
+        <v>0</v>
+      </c>
+      <c r="S136" t="str">
+        <v>0</v>
+      </c>
+      <c r="T136" t="str">
+        <v>0</v>
+      </c>
+      <c r="U136" t="str">
+        <v>4</v>
+      </c>
+      <c r="V136" t="str">
+        <v>0</v>
+      </c>
+      <c r="W136" t="str">
+        <v>3</v>
+      </c>
+      <c r="X136" t="str">
+        <v>4/6/26</v>
+      </c>
+      <c r="Y136" t="str">
+        <v>7/10/26</v>
+      </c>
+      <c r="Z136" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="AA136" t="str">
+        <v>NGÂN</v>
+      </c>
+      <c r="AB136" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="AD136" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="AE136" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="str">
+        <v>(246)</v>
+      </c>
+      <c r="B137" t="str">
+        <v>(1) Viet Nga Group, (2) Việt Nga Group-THT HKD Thanh Mai</v>
+      </c>
+      <c r="C137" t="str">
+        <v>73401</v>
+      </c>
+      <c r="D137" t="str">
+        <v>359757527</v>
+      </c>
+      <c r="E137" t="str">
+        <v>NGUYỄN THANH NHÀN</v>
+      </c>
+      <c r="F137" t="str">
+        <v>HỘ KINH DOANH THANH MAI</v>
+      </c>
+      <c r="J137" t="str">
+        <v>Intensive rice production // Trồng lúa thâm canh</v>
+      </c>
+      <c r="K137" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="L137" t="str">
+        <v>Female // Nữ</v>
+      </c>
+      <c r="M137" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="N137" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O137" t="str">
+        <v>1</v>
+      </c>
+      <c r="P137" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q137" t="str">
+        <v>0</v>
+      </c>
+      <c r="R137" t="str">
+        <v>0</v>
+      </c>
+      <c r="S137" t="str">
+        <v>0</v>
+      </c>
+      <c r="T137" t="str">
+        <v>0</v>
+      </c>
+      <c r="U137" t="str">
+        <v>4</v>
+      </c>
+      <c r="V137" t="str">
+        <v>0</v>
+      </c>
+      <c r="W137" t="str">
+        <v>3</v>
+      </c>
+      <c r="X137" t="str">
+        <v>4/6/26</v>
+      </c>
+      <c r="Y137" t="str">
+        <v>7/10/26</v>
+      </c>
+      <c r="Z137" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="AA137" t="str">
+        <v>NGÂN</v>
+      </c>
+      <c r="AB137" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="AD137" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="AE137" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="str">
+        <v>(247)</v>
+      </c>
+      <c r="B138" t="str">
+        <v>(1) Viet Nga Group, (2) Việt Nga Group-THT HKD Thanh Mai</v>
+      </c>
+      <c r="C138" t="str">
+        <v>73402</v>
+      </c>
+      <c r="D138" t="str">
+        <v>382211425</v>
+      </c>
+      <c r="E138" t="str">
+        <v>HUỲNH HOÀNG DŨNG</v>
+      </c>
+      <c r="F138" t="str">
+        <v>HỘ KINH DOANH THANH MAI</v>
+      </c>
+      <c r="J138" t="str">
+        <v>Intensive rice production // Trồng lúa thâm canh</v>
+      </c>
+      <c r="K138" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="L138" t="str">
+        <v>Male // Nam</v>
+      </c>
+      <c r="M138" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="N138" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O138" t="str">
+        <v>1</v>
+      </c>
+      <c r="P138" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q138" t="str">
+        <v>0</v>
+      </c>
+      <c r="R138" t="str">
+        <v>0</v>
+      </c>
+      <c r="S138" t="str">
+        <v>0</v>
+      </c>
+      <c r="T138" t="str">
+        <v>0</v>
+      </c>
+      <c r="U138" t="str">
+        <v>3</v>
+      </c>
+      <c r="V138" t="str">
+        <v>0</v>
+      </c>
+      <c r="W138" t="str">
+        <v>2</v>
+      </c>
+      <c r="X138" t="str">
+        <v>4/6/26</v>
+      </c>
+      <c r="Y138" t="str">
+        <v>7/10/26</v>
+      </c>
+      <c r="Z138" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="AA138" t="str">
+        <v>NGÂN</v>
+      </c>
+      <c r="AB138" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="AD138" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="AE138" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="str">
+        <v>(248)</v>
+      </c>
+      <c r="B139" t="str">
+        <v>(1) Viet Nga Group, (2) Việt Nga Group-THT HKD Thanh Mai</v>
+      </c>
+      <c r="C139" t="str">
+        <v>73403</v>
+      </c>
+      <c r="D139" t="str">
+        <v>913613458</v>
+      </c>
+      <c r="E139" t="str">
+        <v>ĐINH THÀNH NGUYÊN</v>
+      </c>
+      <c r="F139" t="str">
+        <v>HỘ KINH DOANH THANH MAI</v>
+      </c>
+      <c r="J139" t="str">
+        <v>Intensive rice production // Trồng lúa thâm canh</v>
+      </c>
+      <c r="K139" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="L139" t="str">
+        <v>Male // Nam</v>
+      </c>
+      <c r="M139" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="N139" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O139" t="str">
+        <v>0</v>
+      </c>
+      <c r="P139" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q139" t="str">
+        <v>0</v>
+      </c>
+      <c r="R139" t="str">
+        <v>0</v>
+      </c>
+      <c r="S139" t="str">
+        <v>0</v>
+      </c>
+      <c r="T139" t="str">
+        <v>0</v>
+      </c>
+      <c r="U139" t="str">
+        <v>2</v>
+      </c>
+      <c r="V139" t="str">
+        <v>0</v>
+      </c>
+      <c r="W139" t="str">
+        <v>1</v>
+      </c>
+      <c r="X139" t="str">
+        <v>4/6/26</v>
+      </c>
+      <c r="Y139" t="str">
+        <v>7/10/26</v>
+      </c>
+      <c r="Z139" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="AA139" t="str">
+        <v>NGÂN</v>
+      </c>
+      <c r="AB139" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="AD139" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="AE139" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="str">
+        <v>(250)</v>
+      </c>
+      <c r="B140" t="str">
+        <v>(1) Viet Nga Group, (2) Việt Nga Group-THT HKD Thanh Mai</v>
+      </c>
+      <c r="C140" t="str">
+        <v>73405</v>
+      </c>
+      <c r="D140" t="str">
+        <v>834994432</v>
+      </c>
+      <c r="E140" t="str">
+        <v>NGUYỄN VĂN NHÁNH</v>
+      </c>
+      <c r="F140" t="str">
+        <v>HỘ KINH DOANH THANH MAI</v>
+      </c>
+      <c r="J140" t="str">
+        <v>Intensive rice production // Trồng lúa thâm canh</v>
+      </c>
+      <c r="K140" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="L140" t="str">
+        <v>Male // Nam</v>
+      </c>
+      <c r="M140" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="N140" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O140" t="str">
+        <v>0</v>
+      </c>
+      <c r="P140" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q140" t="str">
+        <v>0</v>
+      </c>
+      <c r="R140" t="str">
+        <v>0</v>
+      </c>
+      <c r="S140" t="str">
+        <v>0</v>
+      </c>
+      <c r="T140" t="str">
+        <v>0</v>
+      </c>
+      <c r="U140" t="str">
+        <v>4</v>
+      </c>
+      <c r="V140" t="str">
+        <v>0</v>
+      </c>
+      <c r="W140" t="str">
+        <v>3</v>
+      </c>
+      <c r="X140" t="str">
+        <v>4/6/26</v>
+      </c>
+      <c r="Y140" t="str">
+        <v>7/10/26</v>
+      </c>
+      <c r="Z140" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="AA140" t="str">
+        <v>NGÂN</v>
+      </c>
+      <c r="AB140" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="AD140" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="AE140" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="str">
+        <v>(251)</v>
+      </c>
+      <c r="B141" t="str">
+        <v>(1) Viet Nga Group, (2) Việt Nga Group-THT HKD Thanh Mai</v>
+      </c>
+      <c r="C141" t="str">
+        <v>73406</v>
+      </c>
+      <c r="D141" t="str">
+        <v>936735077</v>
+      </c>
+      <c r="E141" t="str">
+        <v>NGUYỄN MINH TRƯỜNG</v>
+      </c>
+      <c r="F141" t="str">
+        <v>HỘ KINH DOANH THANH MAI</v>
+      </c>
+      <c r="J141" t="str">
+        <v>Intensive rice production // Trồng lúa thâm canh</v>
+      </c>
+      <c r="K141" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="L141" t="str">
+        <v>Male // Nam</v>
+      </c>
+      <c r="M141" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="N141" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O141" t="str">
+        <v>1</v>
+      </c>
+      <c r="P141" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q141" t="str">
+        <v>0</v>
+      </c>
+      <c r="R141" t="str">
+        <v>0</v>
+      </c>
+      <c r="S141" t="str">
+        <v>0</v>
+      </c>
+      <c r="T141" t="str">
+        <v>0</v>
+      </c>
+      <c r="U141" t="str">
+        <v>3</v>
+      </c>
+      <c r="V141" t="str">
+        <v>0</v>
+      </c>
+      <c r="W141" t="str">
+        <v>2</v>
+      </c>
+      <c r="X141" t="str">
+        <v>4/6/26</v>
+      </c>
+      <c r="Y141" t="str">
+        <v>7/10/26</v>
+      </c>
+      <c r="Z141" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="AA141" t="str">
+        <v>NGÂN</v>
+      </c>
+      <c r="AB141" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="AD141" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="AE141" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="str">
+        <v>(252)</v>
+      </c>
+      <c r="B142" t="str">
+        <v>(1) Viet Nga Group, (2) Việt Nga Group-THT HKD Thanh Mai</v>
+      </c>
+      <c r="C142" t="str">
+        <v>73407</v>
+      </c>
+      <c r="D142" t="str">
+        <v>356309142</v>
+      </c>
+      <c r="E142" t="str">
+        <v>TRẦN VĂN VĨNH</v>
+      </c>
+      <c r="F142" t="str">
+        <v>HỘ KINH DOANH THANH MAI</v>
+      </c>
+      <c r="J142" t="str">
+        <v>Intensive rice production // Trồng lúa thâm canh</v>
+      </c>
+      <c r="K142" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="L142" t="str">
+        <v>Male // Nam</v>
+      </c>
+      <c r="M142" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="N142" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O142" t="str">
+        <v>0</v>
+      </c>
+      <c r="P142" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q142" t="str">
+        <v>0</v>
+      </c>
+      <c r="R142" t="str">
+        <v>0</v>
+      </c>
+      <c r="S142" t="str">
+        <v>0</v>
+      </c>
+      <c r="T142" t="str">
+        <v>0</v>
+      </c>
+      <c r="U142" t="str">
+        <v>2</v>
+      </c>
+      <c r="V142" t="str">
+        <v>0</v>
+      </c>
+      <c r="W142" t="str">
+        <v>1</v>
+      </c>
+      <c r="X142" t="str">
+        <v>4/6/26</v>
+      </c>
+      <c r="Y142" t="str">
+        <v>7/10/26</v>
+      </c>
+      <c r="Z142" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="AA142" t="str">
+        <v>NGÂN</v>
+      </c>
+      <c r="AB142" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="AD142" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="AE142" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="str">
+        <v>(257)</v>
+      </c>
+      <c r="B143" t="str">
+        <v>(1) Viet Nga Group, (2) Việt Nga Group-THT HKD Thanh Mai</v>
+      </c>
+      <c r="C143" t="str">
+        <v>73412</v>
+      </c>
+      <c r="D143" t="str">
+        <v>388443780</v>
+      </c>
+      <c r="E143" t="str">
+        <v>PHAN VĂN BE</v>
+      </c>
+      <c r="F143" t="str">
+        <v>HỘ KINH DOANH THANH MAI</v>
+      </c>
+      <c r="J143" t="str">
+        <v>Intensive rice production // Trồng lúa thâm canh</v>
+      </c>
+      <c r="K143" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="L143" t="str">
+        <v>Male // Nam</v>
+      </c>
+      <c r="M143" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="N143" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O143" t="str">
+        <v>0</v>
+      </c>
+      <c r="P143" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q143" t="str">
+        <v>0</v>
+      </c>
+      <c r="R143" t="str">
+        <v>0</v>
+      </c>
+      <c r="S143" t="str">
+        <v>0</v>
+      </c>
+      <c r="T143" t="str">
+        <v>0</v>
+      </c>
+      <c r="U143" t="str">
+        <v>4</v>
+      </c>
+      <c r="V143" t="str">
+        <v>0</v>
+      </c>
+      <c r="W143" t="str">
+        <v>3</v>
+      </c>
+      <c r="X143" t="str">
+        <v>4/6/26</v>
+      </c>
+      <c r="Y143" t="str">
+        <v>7/10/26</v>
+      </c>
+      <c r="Z143" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="AA143" t="str">
+        <v>NGÂN</v>
+      </c>
+      <c r="AB143" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="AD143" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="AE143" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="str">
+        <v>(259)</v>
+      </c>
+      <c r="B144" t="str">
+        <v>(1) Viet Nga Group, (2) Việt Nga Group-THT HKD Thanh Mai</v>
+      </c>
+      <c r="C144" t="str">
+        <v>73414</v>
+      </c>
+      <c r="D144" t="str">
+        <v>339640487</v>
+      </c>
+      <c r="E144" t="str">
+        <v>NGUYỄN VĂN SƠN</v>
+      </c>
+      <c r="F144" t="str">
+        <v>HỘ KINH DOANH THANH MAI</v>
+      </c>
+      <c r="J144" t="str">
+        <v>Intensive rice production // Trồng lúa thâm canh</v>
+      </c>
+      <c r="K144" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="L144" t="str">
+        <v>Male // Nam</v>
+      </c>
+      <c r="M144" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="N144" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O144" t="str">
+        <v>1</v>
+      </c>
+      <c r="P144" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q144" t="str">
+        <v>0</v>
+      </c>
+      <c r="R144" t="str">
+        <v>0</v>
+      </c>
+      <c r="S144" t="str">
+        <v>0</v>
+      </c>
+      <c r="T144" t="str">
+        <v>0</v>
+      </c>
+      <c r="U144" t="str">
+        <v>2</v>
+      </c>
+      <c r="V144" t="str">
+        <v>0</v>
+      </c>
+      <c r="W144" t="str">
+        <v>1</v>
+      </c>
+      <c r="X144" t="str">
+        <v>4/6/26</v>
+      </c>
+      <c r="Y144" t="str">
+        <v>7/10/26</v>
+      </c>
+      <c r="Z144" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="AA144" t="str">
+        <v>NGÂN</v>
+      </c>
+      <c r="AB144" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="AD144" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="AE144" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="str">
+        <v>(260)</v>
+      </c>
+      <c r="B145" t="str">
+        <v>(1) Viet Nga Group, (2) Việt Nga Group-THT HKD Thanh Mai</v>
+      </c>
+      <c r="C145" t="str">
+        <v>73415</v>
+      </c>
+      <c r="D145" t="str">
+        <v>374465404</v>
+      </c>
+      <c r="E145" t="str">
+        <v>NGÔ THANH TUẤN</v>
+      </c>
+      <c r="F145" t="str">
+        <v>HỘ KINH DOANH THANH MAI</v>
+      </c>
+      <c r="J145" t="str">
+        <v>Intensive rice production // Trồng lúa thâm canh</v>
+      </c>
+      <c r="K145" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="L145" t="str">
+        <v>Male // Nam</v>
+      </c>
+      <c r="M145" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="N145" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O145" t="str">
+        <v>0</v>
+      </c>
+      <c r="P145" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q145" t="str">
+        <v>0</v>
+      </c>
+      <c r="R145" t="str">
+        <v>0</v>
+      </c>
+      <c r="S145" t="str">
+        <v>0</v>
+      </c>
+      <c r="T145" t="str">
+        <v>0</v>
+      </c>
+      <c r="U145" t="str">
+        <v>2</v>
+      </c>
+      <c r="V145" t="str">
+        <v>0</v>
+      </c>
+      <c r="W145" t="str">
+        <v>1</v>
+      </c>
+      <c r="X145" t="str">
+        <v>4/6/26</v>
+      </c>
+      <c r="Y145" t="str">
+        <v>7/10/26</v>
+      </c>
+      <c r="Z145" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="AA145" t="str">
+        <v>NGÂN</v>
+      </c>
+      <c r="AB145" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="AD145" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="AE145" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="str">
+        <v>(262)</v>
+      </c>
+      <c r="B146" t="str">
+        <v>(1) Viet Nga Group, (2) Việt Nga Group-THT HKD Thanh Mai</v>
+      </c>
+      <c r="C146" t="str">
+        <v>73417</v>
+      </c>
+      <c r="D146" t="str">
+        <v>977098292</v>
+      </c>
+      <c r="E146" t="str">
+        <v>NGUYỄN THANH SANG</v>
+      </c>
+      <c r="F146" t="str">
+        <v>HỘ KINH DOANH THANH MAI</v>
+      </c>
+      <c r="J146" t="str">
+        <v>Intensive rice production // Trồng lúa thâm canh</v>
+      </c>
+      <c r="K146" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="L146" t="str">
+        <v>Female // Nữ</v>
+      </c>
+      <c r="M146" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="N146" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O146" t="str">
+        <v>1</v>
+      </c>
+      <c r="P146" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q146" t="str">
+        <v>0</v>
+      </c>
+      <c r="R146" t="str">
+        <v>0</v>
+      </c>
+      <c r="S146" t="str">
+        <v>0</v>
+      </c>
+      <c r="T146" t="str">
+        <v>0</v>
+      </c>
+      <c r="U146" t="str">
+        <v>4</v>
+      </c>
+      <c r="V146" t="str">
+        <v>0</v>
+      </c>
+      <c r="W146" t="str">
+        <v>3</v>
+      </c>
+      <c r="X146" t="str">
+        <v>4/6/26</v>
+      </c>
+      <c r="Y146" t="str">
+        <v>7/10/26</v>
+      </c>
+      <c r="Z146" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="AA146" t="str">
+        <v>NGÂN</v>
+      </c>
+      <c r="AB146" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="AD146" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="AE146" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="str">
+        <v>(270)</v>
+      </c>
+      <c r="B147" t="str">
+        <v>(1) Viet Nga Group, (2) Việt Nga Group-THT HKD Thanh Mai</v>
+      </c>
+      <c r="C147" t="str">
+        <v>73425</v>
+      </c>
+      <c r="D147" t="str">
+        <v>772199108</v>
+      </c>
+      <c r="E147" t="str">
+        <v>TRẦN VĂN TRUNG</v>
+      </c>
+      <c r="F147" t="str">
+        <v>HỘ KINH DOANH THANH MAI</v>
+      </c>
+      <c r="J147" t="str">
+        <v>Intensive rice production // Trồng lúa thâm canh</v>
+      </c>
+      <c r="K147" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="L147" t="str">
+        <v>Male // Nam</v>
+      </c>
+      <c r="M147" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="N147" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O147" t="str">
+        <v>0</v>
+      </c>
+      <c r="P147" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q147" t="str">
+        <v>0</v>
+      </c>
+      <c r="R147" t="str">
+        <v>0</v>
+      </c>
+      <c r="S147" t="str">
+        <v>0</v>
+      </c>
+      <c r="T147" t="str">
+        <v>0</v>
+      </c>
+      <c r="U147" t="str">
+        <v>2</v>
+      </c>
+      <c r="V147" t="str">
+        <v>0</v>
+      </c>
+      <c r="W147" t="str">
+        <v>1</v>
+      </c>
+      <c r="X147" t="str">
+        <v>4/6/26</v>
+      </c>
+      <c r="Y147" t="str">
+        <v>7/10/26</v>
+      </c>
+      <c r="Z147" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="AA147" t="str">
+        <v>NGÂN</v>
+      </c>
+      <c r="AB147" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="AD147" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="AE147" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="str">
+        <v>(273)</v>
+      </c>
+      <c r="B148" t="str">
+        <v>(1) Viet Nga Group, (2) Việt Nga Group-THT HKD Thanh Mai</v>
+      </c>
+      <c r="C148" t="str">
+        <v>73428</v>
+      </c>
+      <c r="D148" t="str">
+        <v>372930755</v>
+      </c>
+      <c r="E148" t="str">
+        <v>NGUYỄN VĂN TRÁNG</v>
+      </c>
+      <c r="F148" t="str">
+        <v>HỘ KINH DOANH THANH MAI</v>
+      </c>
+      <c r="J148" t="str">
+        <v>Intensive rice production // Trồng lúa thâm canh</v>
+      </c>
+      <c r="K148" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="L148" t="str">
+        <v>Male // Nam</v>
+      </c>
+      <c r="M148" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="N148" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O148" t="str">
+        <v>0</v>
+      </c>
+      <c r="P148" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q148" t="str">
+        <v>0</v>
+      </c>
+      <c r="R148" t="str">
+        <v>0</v>
+      </c>
+      <c r="S148" t="str">
+        <v>0</v>
+      </c>
+      <c r="T148" t="str">
+        <v>0</v>
+      </c>
+      <c r="U148" t="str">
+        <v>4</v>
+      </c>
+      <c r="V148" t="str">
+        <v>0</v>
+      </c>
+      <c r="W148" t="str">
+        <v>3</v>
+      </c>
+      <c r="X148" t="str">
+        <v>4/6/26</v>
+      </c>
+      <c r="Y148" t="str">
+        <v>7/10/26</v>
+      </c>
+      <c r="Z148" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="AA148" t="str">
+        <v>NGÂN</v>
+      </c>
+      <c r="AB148" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="AD148" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="AE148" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="str">
+        <v>(279)</v>
+      </c>
+      <c r="B149" t="str">
+        <v>(1) Viet Nga Group, (2) Việt Nga Group-THT HKD Thanh Mai</v>
+      </c>
+      <c r="C149" t="str">
+        <v>73434</v>
+      </c>
+      <c r="D149" t="str">
+        <v>988223465</v>
+      </c>
+      <c r="E149" t="str">
+        <v>PHẠM KIM BÌNH</v>
+      </c>
+      <c r="F149" t="str">
+        <v>HỘ KINH DOANH THANH MAI</v>
+      </c>
+      <c r="J149" t="str">
+        <v>Intensive rice production // Trồng lúa thâm canh</v>
+      </c>
+      <c r="K149" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="L149" t="str">
+        <v>Female // Nữ</v>
+      </c>
+      <c r="M149" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="N149" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O149" t="str">
+        <v>1</v>
+      </c>
+      <c r="P149" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q149" t="str">
+        <v>0</v>
+      </c>
+      <c r="R149" t="str">
+        <v>0</v>
+      </c>
+      <c r="S149" t="str">
+        <v>0</v>
+      </c>
+      <c r="T149" t="str">
+        <v>0</v>
+      </c>
+      <c r="U149" t="str">
+        <v>3</v>
+      </c>
+      <c r="V149" t="str">
+        <v>0</v>
+      </c>
+      <c r="W149" t="str">
+        <v>2</v>
+      </c>
+      <c r="X149" t="str">
+        <v>4/6/26</v>
+      </c>
+      <c r="Y149" t="str">
+        <v>7/10/26</v>
+      </c>
+      <c r="Z149" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="AA149" t="str">
+        <v>NGÂN</v>
+      </c>
+      <c r="AB149" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="AD149" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="AE149" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="str">
+        <v>(294)</v>
+      </c>
+      <c r="B150" t="str">
+        <v>(1) Viet Nga Group, (2) Việt Nga Group-THT HKD Tư Lực</v>
+      </c>
+      <c r="C150" t="str">
+        <v>73352</v>
+      </c>
+      <c r="D150" t="str">
+        <v>948884453</v>
+      </c>
+      <c r="E150" t="str">
+        <v>HUỲNH DUY LINH</v>
+      </c>
+      <c r="F150" t="str">
+        <v>HỘ KINH DOANH TƯ LỰC</v>
+      </c>
+      <c r="J150" t="str">
+        <v>Intensive rice production // Trồng lúa thâm canh</v>
+      </c>
+      <c r="K150" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="L150" t="str">
+        <v>Female // Nữ</v>
+      </c>
+      <c r="M150" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="N150" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O150" t="str">
+        <v>0</v>
+      </c>
+      <c r="P150" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q150" t="str">
+        <v>0</v>
+      </c>
+      <c r="R150" t="str">
+        <v>0</v>
+      </c>
+      <c r="S150" t="str">
+        <v>0</v>
+      </c>
+      <c r="T150" t="str">
+        <v>0</v>
+      </c>
+      <c r="U150" t="str">
+        <v>3</v>
+      </c>
+      <c r="V150" t="str">
+        <v>0</v>
+      </c>
+      <c r="W150" t="str">
+        <v>2</v>
+      </c>
+      <c r="X150" t="str">
+        <v>4/16/26</v>
+      </c>
+      <c r="Y150" t="str">
+        <v>7/30/26</v>
+      </c>
+      <c r="Z150" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="AA150" t="str">
+        <v>NGÂN</v>
+      </c>
+      <c r="AB150" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="AD150" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="AE150" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="str">
+        <v>(296)</v>
+      </c>
+      <c r="B151" t="str">
+        <v>(1) Viet Nga Group, (2) Việt Nga Group-THT HKD Tư Lực</v>
+      </c>
+      <c r="C151" t="str">
+        <v>73354</v>
+      </c>
+      <c r="D151" t="str">
+        <v>837335967</v>
+      </c>
+      <c r="E151" t="str">
+        <v>LÂM THỊ TUA</v>
+      </c>
+      <c r="F151" t="str">
+        <v>HỘ KINH DOANH TƯ LỰC</v>
+      </c>
+      <c r="J151" t="str">
+        <v>Intensive rice production // Trồng lúa thâm canh</v>
+      </c>
+      <c r="K151" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="L151" t="str">
+        <v>Female // Nữ</v>
+      </c>
+      <c r="M151" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="N151" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O151" t="str">
+        <v>1</v>
+      </c>
+      <c r="P151" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q151" t="str">
+        <v>0</v>
+      </c>
+      <c r="R151" t="str">
+        <v>0</v>
+      </c>
+      <c r="S151" t="str">
+        <v>0</v>
+      </c>
+      <c r="T151" t="str">
+        <v>0</v>
+      </c>
+      <c r="U151" t="str">
+        <v>3</v>
+      </c>
+      <c r="V151" t="str">
+        <v>0</v>
+      </c>
+      <c r="W151" t="str">
+        <v>2</v>
+      </c>
+      <c r="X151" t="str">
+        <v>4/16/26</v>
+      </c>
+      <c r="Y151" t="str">
+        <v>7/30/26</v>
+      </c>
+      <c r="Z151" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="AA151" t="str">
+        <v>NGÂN</v>
+      </c>
+      <c r="AB151" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="AD151" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="AE151" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="str">
+        <v>(309)</v>
+      </c>
+      <c r="B152" t="str">
+        <v>(1) Viet Nga Group, (2) Việt Nga Group-HTX DVNN Bình Hiệp B</v>
+      </c>
+      <c r="C152" t="str">
+        <v>73798</v>
+      </c>
+      <c r="D152" t="str">
+        <v>375625234</v>
+      </c>
+      <c r="E152" t="str">
+        <v>LÊ VĂN SON</v>
+      </c>
+      <c r="F152" t="str">
+        <v>HỢP TÁC XÃ DỊCH VỤ NÔNG NGHIỆP BÌNH HIỆP B</v>
+      </c>
+      <c r="J152" t="str">
+        <v>Intensive rice production // Trồng lúa thâm canh</v>
+      </c>
+      <c r="K152" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="L152" t="str">
+        <v>Male // Nam</v>
+      </c>
+      <c r="M152" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="N152" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O152" t="str">
+        <v>0</v>
+      </c>
+      <c r="P152" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q152" t="str">
+        <v>0</v>
+      </c>
+      <c r="R152" t="str">
+        <v>0</v>
+      </c>
+      <c r="S152" t="str">
+        <v>0</v>
+      </c>
+      <c r="T152" t="str">
+        <v>0</v>
+      </c>
+      <c r="U152" t="str">
+        <v>3</v>
+      </c>
+      <c r="V152" t="str">
+        <v>0</v>
+      </c>
+      <c r="W152" t="str">
+        <v>2</v>
+      </c>
+      <c r="X152" t="str">
+        <v>4/10/26</v>
+      </c>
+      <c r="Y152" t="str">
+        <v>7/14/26</v>
+      </c>
+      <c r="Z152" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="AA152" t="str">
+        <v>NGÂN</v>
+      </c>
+      <c r="AB152" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="AD152" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="AE152" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="str">
+        <v>(310)</v>
+      </c>
+      <c r="B153" t="str">
+        <v>(1) Viet Nga Group, (2) Việt Nga Group-HTX DVNN Bình Hiệp B</v>
+      </c>
+      <c r="C153" t="str">
+        <v>73799</v>
+      </c>
+      <c r="D153" t="str">
+        <v>862256519</v>
+      </c>
+      <c r="E153" t="str">
+        <v>NGUYỄN VĂN VŨ</v>
+      </c>
+      <c r="F153" t="str">
+        <v>HỢP TÁC XÃ DỊCH VỤ NÔNG NGHIỆP BÌNH HIỆP B</v>
+      </c>
+      <c r="J153" t="str">
+        <v>Intensive rice production // Trồng lúa thâm canh</v>
+      </c>
+      <c r="K153" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="L153" t="str">
+        <v>Male // Nam</v>
+      </c>
+      <c r="M153" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="N153" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O153" t="str">
+        <v>0</v>
+      </c>
+      <c r="P153" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q153" t="str">
+        <v>0</v>
+      </c>
+      <c r="R153" t="str">
+        <v>0</v>
+      </c>
+      <c r="S153" t="str">
+        <v>0</v>
+      </c>
+      <c r="T153" t="str">
+        <v>0</v>
+      </c>
+      <c r="U153" t="str">
+        <v>3</v>
+      </c>
+      <c r="V153" t="str">
+        <v>0</v>
+      </c>
+      <c r="W153" t="str">
+        <v>2</v>
+      </c>
+      <c r="X153" t="str">
+        <v>4/10/26</v>
+      </c>
+      <c r="Y153" t="str">
+        <v>7/14/26</v>
+      </c>
+      <c r="Z153" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="AA153" t="str">
+        <v>NGÂN</v>
+      </c>
+      <c r="AB153" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="AD153" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="AE153" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="str">
+        <v>(311)</v>
+      </c>
+      <c r="B154" t="str">
+        <v>(1) Viet Nga Group, (2) Việt Nga Group-HTX DVNN Bình Hiệp B</v>
+      </c>
+      <c r="C154" t="str">
+        <v>73800</v>
+      </c>
+      <c r="D154" t="str">
+        <v>973345487</v>
+      </c>
+      <c r="E154" t="str">
+        <v>NGUYỄN VĂN SÁU</v>
+      </c>
+      <c r="F154" t="str">
+        <v>HỢP TÁC XÃ DỊCH VỤ NÔNG NGHIỆP BÌNH HIỆP B</v>
+      </c>
+      <c r="J154" t="str">
+        <v>Intensive rice production // Trồng lúa thâm canh</v>
+      </c>
+      <c r="K154" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="L154" t="str">
+        <v>Male // Nam</v>
+      </c>
+      <c r="M154" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="N154" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O154" t="str">
+        <v>0</v>
+      </c>
+      <c r="P154" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q154" t="str">
+        <v>0</v>
+      </c>
+      <c r="R154" t="str">
+        <v>0</v>
+      </c>
+      <c r="S154" t="str">
+        <v>0</v>
+      </c>
+      <c r="T154" t="str">
+        <v>0</v>
+      </c>
+      <c r="U154" t="str">
+        <v>4</v>
+      </c>
+      <c r="V154" t="str">
+        <v>0</v>
+      </c>
+      <c r="W154" t="str">
+        <v>2</v>
+      </c>
+      <c r="X154" t="str">
+        <v>4/10/26</v>
+      </c>
+      <c r="Y154" t="str">
+        <v>7/14/26</v>
+      </c>
+      <c r="Z154" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="AA154" t="str">
+        <v>NGÂN</v>
+      </c>
+      <c r="AB154" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="AD154" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="AE154" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="str">
+        <v>(312)</v>
+      </c>
+      <c r="B155" t="str">
+        <v>(1) Viet Nga Group, (2) Việt Nga Group-HTX DVNN Bình Hiệp B</v>
+      </c>
+      <c r="C155" t="str">
+        <v>73801</v>
+      </c>
+      <c r="D155" t="str">
+        <v>949611220</v>
+      </c>
+      <c r="E155" t="str">
+        <v>PHẠM VĂN LUÔNG</v>
+      </c>
+      <c r="F155" t="str">
+        <v>HỢP TÁC XÃ DỊCH VỤ NÔNG NGHIỆP BÌNH HIỆP B</v>
+      </c>
+      <c r="J155" t="str">
+        <v>Intensive rice production // Trồng lúa thâm canh</v>
+      </c>
+      <c r="K155" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="L155" t="str">
+        <v>Male // Nam</v>
+      </c>
+      <c r="M155" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="N155" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O155" t="str">
+        <v>0</v>
+      </c>
+      <c r="P155" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q155" t="str">
+        <v>0</v>
+      </c>
+      <c r="R155" t="str">
+        <v>0</v>
+      </c>
+      <c r="S155" t="str">
+        <v>0</v>
+      </c>
+      <c r="T155" t="str">
+        <v>0</v>
+      </c>
+      <c r="U155" t="str">
+        <v>5</v>
+      </c>
+      <c r="V155" t="str">
+        <v>0</v>
+      </c>
+      <c r="W155" t="str">
+        <v>2</v>
+      </c>
+      <c r="X155" t="str">
+        <v>4/10/26</v>
+      </c>
+      <c r="Y155" t="str">
+        <v>7/14/26</v>
+      </c>
+      <c r="Z155" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="AA155" t="str">
+        <v>NGÂN</v>
+      </c>
+      <c r="AB155" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="AD155" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="AE155" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="str">
+        <v>(313)</v>
+      </c>
+      <c r="B156" t="str">
+        <v>(1) Viet Nga Group, (2) Việt Nga Group-HTX DVNN Bình Hiệp B</v>
+      </c>
+      <c r="C156" t="str">
+        <v>73802</v>
+      </c>
+      <c r="D156" t="str">
+        <v>939354864</v>
+      </c>
+      <c r="E156" t="str">
+        <v>PHẠM VĂN MỘNG</v>
+      </c>
+      <c r="F156" t="str">
+        <v>HỢP TÁC XÃ DỊCH VỤ NÔNG NGHIỆP BÌNH HIỆP B</v>
+      </c>
+      <c r="J156" t="str">
+        <v>Intensive rice production // Trồng lúa thâm canh</v>
+      </c>
+      <c r="K156" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="L156" t="str">
+        <v>Male // Nam</v>
+      </c>
+      <c r="M156" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="N156" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O156" t="str">
+        <v>0</v>
+      </c>
+      <c r="P156" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q156" t="str">
+        <v>0</v>
+      </c>
+      <c r="R156" t="str">
+        <v>0</v>
+      </c>
+      <c r="S156" t="str">
+        <v>0</v>
+      </c>
+      <c r="T156" t="str">
+        <v>0</v>
+      </c>
+      <c r="U156" t="str">
+        <v>4</v>
+      </c>
+      <c r="V156" t="str">
+        <v>0</v>
+      </c>
+      <c r="W156" t="str">
+        <v>3</v>
+      </c>
+      <c r="X156" t="str">
+        <v>4/10/26</v>
+      </c>
+      <c r="Y156" t="str">
+        <v>7/14/26</v>
+      </c>
+      <c r="Z156" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="AA156" t="str">
+        <v>NGÂN</v>
+      </c>
+      <c r="AB156" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="AD156" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="AE156" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="str">
+        <v>(315)</v>
+      </c>
+      <c r="B157" t="str">
+        <v>(1) Viet Nga Group, (2) Việt Nga Group-HTX DVNN Bình Hiệp B</v>
+      </c>
+      <c r="C157" t="str">
+        <v>73804</v>
+      </c>
+      <c r="D157" t="str">
+        <v>386363522</v>
+      </c>
+      <c r="E157" t="str">
+        <v>NGUYỄN VĂN NGON</v>
+      </c>
+      <c r="F157" t="str">
+        <v>HỢP TÁC XÃ DỊCH VỤ NÔNG NGHIỆP BÌNH HIỆP B</v>
+      </c>
+      <c r="J157" t="str">
+        <v>Intensive rice production // Trồng lúa thâm canh</v>
+      </c>
+      <c r="K157" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="L157" t="str">
+        <v>Male // Nam</v>
+      </c>
+      <c r="M157" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="N157" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O157" t="str">
+        <v>0</v>
+      </c>
+      <c r="P157" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q157" t="str">
+        <v>0</v>
+      </c>
+      <c r="R157" t="str">
+        <v>0</v>
+      </c>
+      <c r="S157" t="str">
+        <v>0</v>
+      </c>
+      <c r="T157" t="str">
+        <v>0</v>
+      </c>
+      <c r="U157" t="str">
+        <v>4</v>
+      </c>
+      <c r="V157" t="str">
+        <v>0</v>
+      </c>
+      <c r="W157" t="str">
+        <v>3</v>
+      </c>
+      <c r="X157" t="str">
+        <v>4/10/26</v>
+      </c>
+      <c r="Y157" t="str">
+        <v>7/14/26</v>
+      </c>
+      <c r="Z157" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="AA157" t="str">
+        <v>NGÂN</v>
+      </c>
+      <c r="AB157" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="AD157" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="AE157" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="str">
+        <v>(320)</v>
+      </c>
+      <c r="B158" t="str">
+        <v>(1) Viet Nga Group, (2) Việt Nga Group-HTX DVNN Bình Hiệp B</v>
+      </c>
+      <c r="C158" t="str">
+        <v>73809</v>
+      </c>
+      <c r="D158" t="str">
+        <v>388744749</v>
+      </c>
+      <c r="E158" t="str">
+        <v>HUỲNH TẤN KIỆT</v>
+      </c>
+      <c r="F158" t="str">
+        <v>HỢP TÁC XÃ DỊCH VỤ NÔNG NGHIỆP BÌNH HIỆP B</v>
+      </c>
+      <c r="J158" t="str">
+        <v>Intensive rice production // Trồng lúa thâm canh</v>
+      </c>
+      <c r="K158" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="L158" t="str">
+        <v>Male // Nam</v>
+      </c>
+      <c r="M158" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="N158" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O158" t="str">
+        <v>0</v>
+      </c>
+      <c r="P158" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q158" t="str">
+        <v>0</v>
+      </c>
+      <c r="R158" t="str">
+        <v>0</v>
+      </c>
+      <c r="S158" t="str">
+        <v>0</v>
+      </c>
+      <c r="T158" t="str">
+        <v>0</v>
+      </c>
+      <c r="U158" t="str">
+        <v>4</v>
+      </c>
+      <c r="V158" t="str">
+        <v>0</v>
+      </c>
+      <c r="W158" t="str">
+        <v>3</v>
+      </c>
+      <c r="X158" t="str">
+        <v>4/10/26</v>
+      </c>
+      <c r="Y158" t="str">
+        <v>7/14/26</v>
+      </c>
+      <c r="Z158" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="AA158" t="str">
+        <v>NGÂN</v>
+      </c>
+      <c r="AB158" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="AD158" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="AE158" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="str">
+        <v>(321)</v>
+      </c>
+      <c r="B159" t="str">
+        <v>(1) Viet Nga Group, (2) Việt Nga Group-HTX DVNN Bình Hiệp B</v>
+      </c>
+      <c r="C159" t="str">
+        <v>73810</v>
+      </c>
+      <c r="D159" t="str">
+        <v>834367845</v>
+      </c>
+      <c r="E159" t="str">
+        <v>HỒ VĂN CÒN</v>
+      </c>
+      <c r="F159" t="str">
+        <v>HỢP TÁC XÃ DỊCH VỤ NÔNG NGHIỆP BÌNH HIỆP B</v>
+      </c>
+      <c r="J159" t="str">
+        <v>Intensive rice production // Trồng lúa thâm canh</v>
+      </c>
+      <c r="K159" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="L159" t="str">
+        <v>Male // Nam</v>
+      </c>
+      <c r="M159" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="N159" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O159" t="str">
+        <v>0</v>
+      </c>
+      <c r="P159" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q159" t="str">
+        <v>0</v>
+      </c>
+      <c r="R159" t="str">
+        <v>0</v>
+      </c>
+      <c r="S159" t="str">
+        <v>0</v>
+      </c>
+      <c r="T159" t="str">
+        <v>0</v>
+      </c>
+      <c r="U159" t="str">
+        <v>5</v>
+      </c>
+      <c r="V159" t="str">
+        <v>0</v>
+      </c>
+      <c r="W159" t="str">
+        <v>4</v>
+      </c>
+      <c r="X159" t="str">
+        <v>4/10/26</v>
+      </c>
+      <c r="Y159" t="str">
+        <v>7/14/26</v>
+      </c>
+      <c r="Z159" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="AA159" t="str">
+        <v>NGÂN</v>
+      </c>
+      <c r="AB159" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="AD159" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="AE159" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="str">
+        <v>(323)</v>
+      </c>
+      <c r="B160" t="str">
+        <v>(1) Viet Nga Group, (2) Việt Nga Group-HTX DVNN Bình Hiệp B</v>
+      </c>
+      <c r="C160" t="str">
+        <v>73812</v>
+      </c>
+      <c r="D160" t="str">
+        <v>374515291</v>
+      </c>
+      <c r="E160" t="str">
+        <v>PHẠM VĂN TIỂNG</v>
+      </c>
+      <c r="F160" t="str">
+        <v>HỢP TÁC XÃ DỊCH VỤ NÔNG NGHIỆP BÌNH HIỆP B</v>
+      </c>
+      <c r="J160" t="str">
+        <v>Intensive rice production // Trồng lúa thâm canh</v>
+      </c>
+      <c r="K160" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="L160" t="str">
+        <v>Male // Nam</v>
+      </c>
+      <c r="M160" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="N160" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O160" t="str">
+        <v>0</v>
+      </c>
+      <c r="P160" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q160" t="str">
+        <v>0</v>
+      </c>
+      <c r="R160" t="str">
+        <v>0</v>
+      </c>
+      <c r="S160" t="str">
+        <v>0</v>
+      </c>
+      <c r="T160" t="str">
+        <v>0</v>
+      </c>
+      <c r="U160" t="str">
+        <v>4</v>
+      </c>
+      <c r="V160" t="str">
+        <v>0</v>
+      </c>
+      <c r="W160" t="str">
+        <v>3</v>
+      </c>
+      <c r="X160" t="str">
+        <v>4/10/26</v>
+      </c>
+      <c r="Y160" t="str">
+        <v>7/14/26</v>
+      </c>
+      <c r="Z160" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="AA160" t="str">
+        <v>NGÂN</v>
+      </c>
+      <c r="AB160" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="AD160" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="AE160" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="str">
+        <v>(325)</v>
+      </c>
+      <c r="B161" t="str">
+        <v>(1) Viet Nga Group, (2) Việt Nga Group-HTX DVNN Bình Hiệp B</v>
+      </c>
+      <c r="C161" t="str">
+        <v>73814</v>
+      </c>
+      <c r="D161" t="str">
+        <v>384965513</v>
+      </c>
+      <c r="E161" t="str">
+        <v>NGUYỄN VĂN BỰC</v>
+      </c>
+      <c r="F161" t="str">
+        <v>HỢP TÁC XÃ DỊCH VỤ NÔNG NGHIỆP BÌNH HIỆP B</v>
+      </c>
+      <c r="J161" t="str">
+        <v>Intensive rice production // Trồng lúa thâm canh</v>
+      </c>
+      <c r="K161" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="L161" t="str">
+        <v>Male // Nam</v>
+      </c>
+      <c r="M161" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="N161" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O161" t="str">
+        <v>0</v>
+      </c>
+      <c r="P161" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q161" t="str">
+        <v>0</v>
+      </c>
+      <c r="R161" t="str">
+        <v>0</v>
+      </c>
+      <c r="S161" t="str">
+        <v>0</v>
+      </c>
+      <c r="T161" t="str">
+        <v>0</v>
+      </c>
+      <c r="U161" t="str">
+        <v>3</v>
+      </c>
+      <c r="V161" t="str">
+        <v>0</v>
+      </c>
+      <c r="W161" t="str">
+        <v>2</v>
+      </c>
+      <c r="X161" t="str">
+        <v>4/10/26</v>
+      </c>
+      <c r="Y161" t="str">
+        <v>7/14/26</v>
+      </c>
+      <c r="Z161" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="AA161" t="str">
+        <v>NGÂN</v>
+      </c>
+      <c r="AB161" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="AD161" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="AE161" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="str">
+        <v>(326)</v>
+      </c>
+      <c r="B162" t="str">
+        <v>(1) Viet Nga Group, (2) Việt Nga Group-HTX DVNN Bình Hiệp B</v>
+      </c>
+      <c r="C162" t="str">
+        <v>73815</v>
+      </c>
+      <c r="D162" t="str">
+        <v>984622189</v>
+      </c>
+      <c r="E162" t="str">
+        <v>NGUYỄN VĂN TÍCH</v>
+      </c>
+      <c r="F162" t="str">
+        <v>HỢP TÁC XÃ DỊCH VỤ NÔNG NGHIỆP BÌNH HIỆP B</v>
+      </c>
+      <c r="J162" t="str">
+        <v>Intensive rice production // Trồng lúa thâm canh</v>
+      </c>
+      <c r="K162" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="L162" t="str">
+        <v>Male // Nam</v>
+      </c>
+      <c r="M162" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="N162" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O162" t="str">
+        <v>0</v>
+      </c>
+      <c r="P162" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q162" t="str">
+        <v>0</v>
+      </c>
+      <c r="R162" t="str">
+        <v>0</v>
+      </c>
+      <c r="S162" t="str">
+        <v>0</v>
+      </c>
+      <c r="T162" t="str">
+        <v>0</v>
+      </c>
+      <c r="U162" t="str">
+        <v>3</v>
+      </c>
+      <c r="V162" t="str">
+        <v>0</v>
+      </c>
+      <c r="W162" t="str">
+        <v>2</v>
+      </c>
+      <c r="X162" t="str">
+        <v>4/10/26</v>
+      </c>
+      <c r="Y162" t="str">
+        <v>7/14/26</v>
+      </c>
+      <c r="Z162" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="AA162" t="str">
+        <v>NGÂN</v>
+      </c>
+      <c r="AB162" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="AD162" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="AE162" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="str">
+        <v>(328)</v>
+      </c>
+      <c r="B163" t="str">
+        <v>(1) Viet Nga Group, (2) Việt Nga Group-HTX DVNN Bình Hiệp B</v>
+      </c>
+      <c r="C163" t="str">
+        <v>73817</v>
+      </c>
+      <c r="D163" t="str">
+        <v>386049296</v>
+      </c>
+      <c r="E163" t="str">
+        <v>NGUYỄN VĂN GÚP</v>
+      </c>
+      <c r="F163" t="str">
+        <v>HỢP TÁC XÃ DỊCH VỤ NÔNG NGHIỆP BÌNH HIỆP B</v>
+      </c>
+      <c r="J163" t="str">
+        <v>Intensive rice production // Trồng lúa thâm canh</v>
+      </c>
+      <c r="K163" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="L163" t="str">
+        <v>Male // Nam</v>
+      </c>
+      <c r="M163" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="N163" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O163" t="str">
+        <v>0</v>
+      </c>
+      <c r="P163" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q163" t="str">
+        <v>0</v>
+      </c>
+      <c r="R163" t="str">
+        <v>0</v>
+      </c>
+      <c r="S163" t="str">
+        <v>0</v>
+      </c>
+      <c r="T163" t="str">
+        <v>0</v>
+      </c>
+      <c r="U163" t="str">
+        <v>5</v>
+      </c>
+      <c r="V163" t="str">
+        <v>0</v>
+      </c>
+      <c r="W163" t="str">
+        <v>4</v>
+      </c>
+      <c r="X163" t="str">
+        <v>4/10/26</v>
+      </c>
+      <c r="Y163" t="str">
+        <v>7/14/26</v>
+      </c>
+      <c r="Z163" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="AA163" t="str">
+        <v>NGÂN</v>
+      </c>
+      <c r="AB163" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="AD163" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="AE163" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="str">
+        <v>(329)</v>
+      </c>
+      <c r="B164" t="str">
+        <v>(1) Viet Nga Group, (2) Việt Nga Group-HTX DVNN Bình Hiệp B</v>
+      </c>
+      <c r="C164" t="str">
+        <v>73818</v>
+      </c>
+      <c r="D164" t="str">
+        <v>939250405</v>
+      </c>
+      <c r="E164" t="str">
+        <v>NGUYỄN THANH TUẤN</v>
+      </c>
+      <c r="F164" t="str">
+        <v>HỢP TÁC XÃ DỊCH VỤ NÔNG NGHIỆP BÌNH HIỆP B</v>
+      </c>
+      <c r="J164" t="str">
+        <v>Intensive rice production // Trồng lúa thâm canh</v>
+      </c>
+      <c r="K164" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="L164" t="str">
+        <v>Male // Nam</v>
+      </c>
+      <c r="M164" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="N164" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O164" t="str">
+        <v>0</v>
+      </c>
+      <c r="P164" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q164" t="str">
+        <v>0</v>
+      </c>
+      <c r="R164" t="str">
+        <v>0</v>
+      </c>
+      <c r="S164" t="str">
+        <v>0</v>
+      </c>
+      <c r="T164" t="str">
+        <v>0</v>
+      </c>
+      <c r="U164" t="str">
+        <v>4</v>
+      </c>
+      <c r="V164" t="str">
+        <v>0</v>
+      </c>
+      <c r="W164" t="str">
+        <v>3</v>
+      </c>
+      <c r="X164" t="str">
+        <v>4/10/26</v>
+      </c>
+      <c r="Y164" t="str">
+        <v>7/14/26</v>
+      </c>
+      <c r="Z164" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="AA164" t="str">
+        <v>NGÂN</v>
+      </c>
+      <c r="AB164" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="AD164" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="AE164" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="str">
+        <v>(332)</v>
+      </c>
+      <c r="B165" t="str">
+        <v>(1) Viet Nga Group, (2) Việt Nga Group-HTX DVNN Bình Hiệp B</v>
+      </c>
+      <c r="C165" t="str">
+        <v>73821</v>
+      </c>
+      <c r="D165" t="str">
+        <v>386658846</v>
+      </c>
+      <c r="E165" t="str">
+        <v>LƯƠNG TẤN XUÂN</v>
+      </c>
+      <c r="F165" t="str">
+        <v>HỢP TÁC XÃ DỊCH VỤ NÔNG NGHIỆP BÌNH HIỆP B</v>
+      </c>
+      <c r="J165" t="str">
+        <v>Intensive rice production // Trồng lúa thâm canh</v>
+      </c>
+      <c r="K165" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="L165" t="str">
+        <v>Male // Nam</v>
+      </c>
+      <c r="M165" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="N165" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O165" t="str">
+        <v>0</v>
+      </c>
+      <c r="P165" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q165" t="str">
+        <v>0</v>
+      </c>
+      <c r="R165" t="str">
+        <v>0</v>
+      </c>
+      <c r="S165" t="str">
+        <v>0</v>
+      </c>
+      <c r="T165" t="str">
+        <v>0</v>
+      </c>
+      <c r="U165" t="str">
+        <v>3</v>
+      </c>
+      <c r="V165" t="str">
+        <v>0</v>
+      </c>
+      <c r="W165" t="str">
+        <v>2</v>
+      </c>
+      <c r="X165" t="str">
+        <v>4/10/26</v>
+      </c>
+      <c r="Y165" t="str">
+        <v>7/14/26</v>
+      </c>
+      <c r="Z165" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="AA165" t="str">
+        <v>NGÂN</v>
+      </c>
+      <c r="AB165" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="AD165" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="AE165" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="str">
+        <v>(334)</v>
+      </c>
+      <c r="B166" t="str">
+        <v>(1) Viet Nga Group, (2) Việt Nga Group-HTX DVNN Bình Hiệp B</v>
+      </c>
+      <c r="C166" t="str">
+        <v>73823</v>
+      </c>
+      <c r="D166" t="str">
+        <v>336348881</v>
+      </c>
+      <c r="E166" t="str">
+        <v>ĐOÀN VĂN HAI</v>
+      </c>
+      <c r="F166" t="str">
+        <v>HỢP TÁC XÃ DỊCH VỤ NÔNG NGHIỆP BÌNH HIỆP B</v>
+      </c>
+      <c r="J166" t="str">
+        <v>Intensive rice production // Trồng lúa thâm canh</v>
+      </c>
+      <c r="K166" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="L166" t="str">
+        <v>Male // Nam</v>
+      </c>
+      <c r="M166" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="N166" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O166" t="str">
+        <v>0</v>
+      </c>
+      <c r="P166" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q166" t="str">
+        <v>0</v>
+      </c>
+      <c r="R166" t="str">
+        <v>0</v>
+      </c>
+      <c r="S166" t="str">
+        <v>0</v>
+      </c>
+      <c r="T166" t="str">
+        <v>0</v>
+      </c>
+      <c r="U166" t="str">
+        <v>3</v>
+      </c>
+      <c r="V166" t="str">
+        <v>0</v>
+      </c>
+      <c r="W166" t="str">
+        <v>2</v>
+      </c>
+      <c r="X166" t="str">
+        <v>4/10/26</v>
+      </c>
+      <c r="Y166" t="str">
+        <v>7/14/26</v>
+      </c>
+      <c r="Z166" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="AA166" t="str">
+        <v>NGÂN</v>
+      </c>
+      <c r="AB166" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="AD166" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="AE166" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="str">
+        <v>(335)</v>
+      </c>
+      <c r="B167" t="str">
+        <v>(1) Viet Nga Group, (2) Việt Nga Group-HTX DVNN Bình Hiệp B</v>
+      </c>
+      <c r="C167" t="str">
+        <v>73824</v>
+      </c>
+      <c r="D167" t="str">
+        <v>388218751</v>
+      </c>
+      <c r="E167" t="str">
+        <v>NGUYỄN VĂN LẮM</v>
+      </c>
+      <c r="F167" t="str">
+        <v>HỢP TÁC XÃ DỊCH VỤ NÔNG NGHIỆP BÌNH HIỆP B</v>
+      </c>
+      <c r="J167" t="str">
+        <v>Intensive rice production // Trồng lúa thâm canh</v>
+      </c>
+      <c r="K167" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="L167" t="str">
+        <v>Male // Nam</v>
+      </c>
+      <c r="M167" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="N167" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O167" t="str">
+        <v>0</v>
+      </c>
+      <c r="P167" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q167" t="str">
+        <v>0</v>
+      </c>
+      <c r="R167" t="str">
+        <v>0</v>
+      </c>
+      <c r="S167" t="str">
+        <v>0</v>
+      </c>
+      <c r="T167" t="str">
+        <v>0</v>
+      </c>
+      <c r="U167" t="str">
+        <v>4</v>
+      </c>
+      <c r="V167" t="str">
+        <v>0</v>
+      </c>
+      <c r="W167" t="str">
+        <v>2</v>
+      </c>
+      <c r="X167" t="str">
+        <v>4/10/26</v>
+      </c>
+      <c r="Y167" t="str">
+        <v>7/14/26</v>
+      </c>
+      <c r="Z167" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="AA167" t="str">
+        <v>NGÂN</v>
+      </c>
+      <c r="AB167" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="AD167" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="AE167" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="str">
+        <v>(336)</v>
+      </c>
+      <c r="B168" t="str">
+        <v>(1) Viet Nga Group, (2) Việt Nga Group-HTX DVNN Bình Hiệp B</v>
+      </c>
+      <c r="C168" t="str">
+        <v>73825</v>
+      </c>
+      <c r="D168" t="str">
+        <v>919320157</v>
+      </c>
+      <c r="E168" t="str">
+        <v>NGUYỄN HỮU ĐỨC</v>
+      </c>
+      <c r="F168" t="str">
+        <v>HỢP TÁC XÃ DỊCH VỤ NÔNG NGHIỆP BÌNH HIỆP B</v>
+      </c>
+      <c r="J168" t="str">
+        <v>Intensive rice production // Trồng lúa thâm canh</v>
+      </c>
+      <c r="K168" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="L168" t="str">
+        <v>Male // Nam</v>
+      </c>
+      <c r="M168" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="N168" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O168" t="str">
+        <v>0</v>
+      </c>
+      <c r="P168" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q168" t="str">
+        <v>0</v>
+      </c>
+      <c r="R168" t="str">
+        <v>0</v>
+      </c>
+      <c r="S168" t="str">
+        <v>0</v>
+      </c>
+      <c r="T168" t="str">
+        <v>0</v>
+      </c>
+      <c r="U168" t="str">
+        <v>4</v>
+      </c>
+      <c r="V168" t="str">
+        <v>0</v>
+      </c>
+      <c r="W168" t="str">
+        <v>3</v>
+      </c>
+      <c r="X168" t="str">
+        <v>4/10/26</v>
+      </c>
+      <c r="Y168" t="str">
+        <v>7/14/26</v>
+      </c>
+      <c r="Z168" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="AA168" t="str">
+        <v>NGÂN</v>
+      </c>
+      <c r="AB168" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="AD168" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="AE168" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="str">
+        <v>(337)</v>
+      </c>
+      <c r="B169" t="str">
+        <v>(1) Viet Nga Group, (2) Việt Nga Group-HTX DVNN Bình Hiệp B</v>
+      </c>
+      <c r="C169" t="str">
+        <v>73826</v>
+      </c>
+      <c r="D169" t="str">
+        <v>919705659</v>
+      </c>
+      <c r="E169" t="str">
+        <v>LÊ VĂN ÚT</v>
+      </c>
+      <c r="F169" t="str">
+        <v>HỢP TÁC XÃ DỊCH VỤ NÔNG NGHIỆP BÌNH HIỆP B</v>
+      </c>
+      <c r="J169" t="str">
+        <v>Intensive rice production // Trồng lúa thâm canh</v>
+      </c>
+      <c r="K169" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="L169" t="str">
+        <v>Male // Nam</v>
+      </c>
+      <c r="M169" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="N169" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O169" t="str">
+        <v>0</v>
+      </c>
+      <c r="P169" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q169" t="str">
+        <v>0</v>
+      </c>
+      <c r="R169" t="str">
+        <v>0</v>
+      </c>
+      <c r="S169" t="str">
+        <v>0</v>
+      </c>
+      <c r="T169" t="str">
+        <v>0</v>
+      </c>
+      <c r="U169" t="str">
+        <v>4</v>
+      </c>
+      <c r="V169" t="str">
+        <v>0</v>
+      </c>
+      <c r="W169" t="str">
+        <v>3</v>
+      </c>
+      <c r="X169" t="str">
+        <v>4/10/26</v>
+      </c>
+      <c r="Y169" t="str">
+        <v>7/14/26</v>
+      </c>
+      <c r="Z169" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="AA169" t="str">
+        <v>NGÂN</v>
+      </c>
+      <c r="AB169" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="AD169" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="AE169" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="str">
+        <v>(338)</v>
+      </c>
+      <c r="B170" t="str">
+        <v>(1) Viet Nga Group, (2) Việt Nga Group-HTX DVNN Bình Hiệp B</v>
+      </c>
+      <c r="C170" t="str">
+        <v>73827</v>
+      </c>
+      <c r="D170" t="str">
+        <v>372108598</v>
+      </c>
+      <c r="E170" t="str">
+        <v>NGUYỄN VĂN ÚT</v>
+      </c>
+      <c r="F170" t="str">
+        <v>HỢP TÁC XÃ DỊCH VỤ NÔNG NGHIỆP BÌNH HIỆP B</v>
+      </c>
+      <c r="J170" t="str">
+        <v>Intensive rice production // Trồng lúa thâm canh</v>
+      </c>
+      <c r="K170" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="L170" t="str">
+        <v>Male // Nam</v>
+      </c>
+      <c r="M170" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="N170" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O170" t="str">
+        <v>0</v>
+      </c>
+      <c r="P170" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q170" t="str">
+        <v>0</v>
+      </c>
+      <c r="R170" t="str">
+        <v>0</v>
+      </c>
+      <c r="S170" t="str">
+        <v>0</v>
+      </c>
+      <c r="T170" t="str">
+        <v>0</v>
+      </c>
+      <c r="U170" t="str">
+        <v>4</v>
+      </c>
+      <c r="V170" t="str">
+        <v>0</v>
+      </c>
+      <c r="W170" t="str">
+        <v>3</v>
+      </c>
+      <c r="X170" t="str">
+        <v>4/10/26</v>
+      </c>
+      <c r="Y170" t="str">
+        <v>7/14/26</v>
+      </c>
+      <c r="Z170" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="AA170" t="str">
+        <v>NGÂN</v>
+      </c>
+      <c r="AB170" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="AD170" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="AE170" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="str">
+        <v>(339)</v>
+      </c>
+      <c r="B171" t="str">
+        <v>(1) Viet Nga Group, (2) Việt Nga Group-HTX DVNN Bình Hiệp B</v>
+      </c>
+      <c r="C171" t="str">
+        <v>73828</v>
+      </c>
+      <c r="D171" t="str">
+        <v>783858306</v>
+      </c>
+      <c r="E171" t="str">
+        <v>HOÀNG HOA THÁM</v>
+      </c>
+      <c r="F171" t="str">
+        <v>HỢP TÁC XÃ DỊCH VỤ NÔNG NGHIỆP BÌNH HIỆP B</v>
+      </c>
+      <c r="J171" t="str">
+        <v>Intensive rice production // Trồng lúa thâm canh</v>
+      </c>
+      <c r="K171" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="L171" t="str">
+        <v>Male // Nam</v>
+      </c>
+      <c r="M171" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="N171" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O171" t="str">
+        <v>0</v>
+      </c>
+      <c r="P171" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q171" t="str">
+        <v>0</v>
+      </c>
+      <c r="R171" t="str">
+        <v>0</v>
+      </c>
+      <c r="S171" t="str">
+        <v>0</v>
+      </c>
+      <c r="T171" t="str">
+        <v>0</v>
+      </c>
+      <c r="U171" t="str">
+        <v>4</v>
+      </c>
+      <c r="V171" t="str">
+        <v>0</v>
+      </c>
+      <c r="W171" t="str">
+        <v>3</v>
+      </c>
+      <c r="X171" t="str">
+        <v>4/10/26</v>
+      </c>
+      <c r="Y171" t="str">
+        <v>7/14/26</v>
+      </c>
+      <c r="Z171" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="AA171" t="str">
+        <v>NGÂN</v>
+      </c>
+      <c r="AB171" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="AD171" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="AE171" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="str">
+        <v>(340)</v>
+      </c>
+      <c r="B172" t="str">
+        <v>(1) Viet Nga Group, (2) Việt Nga Group-HTX DVNN Bình Hiệp B</v>
+      </c>
+      <c r="C172" t="str">
+        <v>73829</v>
+      </c>
+      <c r="D172" t="str">
+        <v>329301571</v>
+      </c>
+      <c r="E172" t="str">
+        <v>ĐOÀN TẤN VÂN</v>
+      </c>
+      <c r="F172" t="str">
+        <v>HỢP TÁC XÃ DỊCH VỤ NÔNG NGHIỆP BÌNH HIỆP B</v>
+      </c>
+      <c r="J172" t="str">
+        <v>Intensive rice production // Trồng lúa thâm canh</v>
+      </c>
+      <c r="K172" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="L172" t="str">
+        <v>Male // Nam</v>
+      </c>
+      <c r="M172" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="N172" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O172" t="str">
+        <v>0</v>
+      </c>
+      <c r="P172" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q172" t="str">
+        <v>0</v>
+      </c>
+      <c r="R172" t="str">
+        <v>0</v>
+      </c>
+      <c r="S172" t="str">
+        <v>0</v>
+      </c>
+      <c r="T172" t="str">
+        <v>0</v>
+      </c>
+      <c r="U172" t="str">
+        <v>5</v>
+      </c>
+      <c r="V172" t="str">
+        <v>0</v>
+      </c>
+      <c r="W172" t="str">
+        <v>4</v>
+      </c>
+      <c r="X172" t="str">
+        <v>4/10/26</v>
+      </c>
+      <c r="Y172" t="str">
+        <v>7/14/26</v>
+      </c>
+      <c r="Z172" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="AA172" t="str">
+        <v>NGÂN</v>
+      </c>
+      <c r="AB172" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="AD172" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="AE172" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="str">
+        <v>(341)</v>
+      </c>
+      <c r="B173" t="str">
+        <v>(1) Viet Nga Group, (2) Việt Nga Group-HTX DVNN Bình Hiệp B</v>
+      </c>
+      <c r="C173" t="str">
+        <v>74852</v>
+      </c>
+      <c r="D173" t="str">
+        <v>784448070</v>
+      </c>
+      <c r="E173" t="str">
+        <v>LÊ THANH TÙNG</v>
+      </c>
+      <c r="F173" t="str">
+        <v>HỢP TÁC XÃ DỊCH VỤ NÔNG NGHIỆP BÌNH HIỆP B</v>
+      </c>
+      <c r="J173" t="str">
+        <v>Intensive rice production // Trồng lúa thâm canh</v>
+      </c>
+      <c r="K173" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="L173" t="str">
+        <v>Male // Nam</v>
+      </c>
+      <c r="M173" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="N173" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O173" t="str">
+        <v>0</v>
+      </c>
+      <c r="P173" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q173" t="str">
+        <v>0</v>
+      </c>
+      <c r="R173" t="str">
+        <v>0</v>
+      </c>
+      <c r="S173" t="str">
+        <v>0</v>
+      </c>
+      <c r="T173" t="str">
+        <v>0</v>
+      </c>
+      <c r="U173" t="str">
+        <v>3</v>
+      </c>
+      <c r="V173" t="str">
+        <v>0</v>
+      </c>
+      <c r="W173" t="str">
+        <v>2</v>
+      </c>
+      <c r="X173" t="str">
+        <v>4/10/26</v>
+      </c>
+      <c r="Y173" t="str">
+        <v>7/14/26</v>
+      </c>
+      <c r="Z173" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="AA173" t="str">
+        <v>NGÂN</v>
+      </c>
+      <c r="AB173" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="AD173" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="AE173" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="str">
+        <v>(342)</v>
+      </c>
+      <c r="B174" t="str">
+        <v>(1) Viet Nga Group, (2) Việt Nga Group-HTX DVNN Bình Hiệp B</v>
+      </c>
+      <c r="C174" t="str">
+        <v>74853</v>
+      </c>
+      <c r="D174" t="str">
+        <v>939269691</v>
+      </c>
+      <c r="E174" t="str">
+        <v>MAI VĂN SUÔL</v>
+      </c>
+      <c r="F174" t="str">
+        <v>HỢP TÁC XÃ DỊCH VỤ NÔNG NGHIỆP BÌNH HIỆP B</v>
+      </c>
+      <c r="J174" t="str">
+        <v>Intensive rice production // Trồng lúa thâm canh</v>
+      </c>
+      <c r="K174" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="L174" t="str">
+        <v>Male // Nam</v>
+      </c>
+      <c r="M174" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="N174" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O174" t="str">
+        <v>0</v>
+      </c>
+      <c r="P174" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q174" t="str">
+        <v>0</v>
+      </c>
+      <c r="R174" t="str">
+        <v>0</v>
+      </c>
+      <c r="S174" t="str">
+        <v>0</v>
+      </c>
+      <c r="T174" t="str">
+        <v>0</v>
+      </c>
+      <c r="U174" t="str">
+        <v>4</v>
+      </c>
+      <c r="V174" t="str">
+        <v>0</v>
+      </c>
+      <c r="W174" t="str">
+        <v>3</v>
+      </c>
+      <c r="X174" t="str">
+        <v>4/10/26</v>
+      </c>
+      <c r="Y174" t="str">
+        <v>7/14/26</v>
+      </c>
+      <c r="Z174" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="AA174" t="str">
+        <v>NGÂN</v>
+      </c>
+      <c r="AB174" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="AD174" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="AE174" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="str">
+        <v>(343)</v>
+      </c>
+      <c r="B175" t="str">
+        <v>(1) Viet Nga Group, (2) Việt Nga Group-HTX DVNN Bình Hiệp B</v>
+      </c>
+      <c r="C175" t="str">
+        <v>74854</v>
+      </c>
+      <c r="D175" t="str">
+        <v>326466713</v>
+      </c>
+      <c r="E175" t="str">
+        <v>HUỲNH VĂN DỰA</v>
+      </c>
+      <c r="F175" t="str">
+        <v>HỢP TÁC XÃ DỊCH VỤ NÔNG NGHIỆP BÌNH HIỆP B</v>
+      </c>
+      <c r="J175" t="str">
+        <v>Intensive rice production // Trồng lúa thâm canh</v>
+      </c>
+      <c r="K175" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="L175" t="str">
+        <v>Male // Nam</v>
+      </c>
+      <c r="M175" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="N175" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O175" t="str">
+        <v>0</v>
+      </c>
+      <c r="P175" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q175" t="str">
+        <v>0</v>
+      </c>
+      <c r="R175" t="str">
+        <v>0</v>
+      </c>
+      <c r="S175" t="str">
+        <v>0</v>
+      </c>
+      <c r="T175" t="str">
+        <v>0</v>
+      </c>
+      <c r="U175" t="str">
+        <v>3</v>
+      </c>
+      <c r="V175" t="str">
+        <v>0</v>
+      </c>
+      <c r="W175" t="str">
+        <v>2</v>
+      </c>
+      <c r="X175" t="str">
+        <v>4/10/26</v>
+      </c>
+      <c r="Y175" t="str">
+        <v>7/14/26</v>
+      </c>
+      <c r="Z175" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="AA175" t="str">
+        <v>NGÂN</v>
+      </c>
+      <c r="AB175" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="AD175" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="AE175" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="str">
+        <v>(345)</v>
+      </c>
+      <c r="B176" t="str">
+        <v>(1) Viet Nga Group, (2) Việt Nga Group-HTX DVNN Bình Hiệp B</v>
+      </c>
+      <c r="C176" t="str">
+        <v>74856</v>
+      </c>
+      <c r="D176" t="str">
+        <v>939308990</v>
+      </c>
+      <c r="E176" t="str">
+        <v>LÊ THANH DƯƠNG</v>
+      </c>
+      <c r="F176" t="str">
+        <v>HỢP TÁC XÃ DỊCH VỤ NÔNG NGHIỆP BÌNH HIỆP B</v>
+      </c>
+      <c r="J176" t="str">
+        <v>Intensive rice production // Trồng lúa thâm canh</v>
+      </c>
+      <c r="K176" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="L176" t="str">
+        <v>Male // Nam</v>
+      </c>
+      <c r="M176" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="N176" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O176" t="str">
+        <v>0</v>
+      </c>
+      <c r="P176" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q176" t="str">
+        <v>0</v>
+      </c>
+      <c r="R176" t="str">
+        <v>0</v>
+      </c>
+      <c r="S176" t="str">
+        <v>0</v>
+      </c>
+      <c r="T176" t="str">
+        <v>0</v>
+      </c>
+      <c r="U176" t="str">
+        <v>4</v>
+      </c>
+      <c r="V176" t="str">
+        <v>0</v>
+      </c>
+      <c r="W176" t="str">
+        <v>3</v>
+      </c>
+      <c r="X176" t="str">
+        <v>4/10/26</v>
+      </c>
+      <c r="Y176" t="str">
+        <v>7/14/26</v>
+      </c>
+      <c r="Z176" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="AA176" t="str">
+        <v>NGÂN</v>
+      </c>
+      <c r="AB176" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="AD176" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="AE176" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="str">
+        <v>(346)</v>
+      </c>
+      <c r="B177" t="str">
+        <v>(1) Viet Nga Group, (2) Việt Nga Group-HTX DVNN Bình Hiệp B</v>
+      </c>
+      <c r="C177" t="str">
+        <v>74857</v>
+      </c>
+      <c r="D177" t="str">
+        <v>398161268</v>
+      </c>
+      <c r="E177" t="str">
+        <v>NGÔ VĂN NGHIÊM</v>
+      </c>
+      <c r="F177" t="str">
+        <v>HỢP TÁC XÃ DỊCH VỤ NÔNG NGHIỆP BÌNH HIỆP B</v>
+      </c>
+      <c r="J177" t="str">
+        <v>Intensive rice production // Trồng lúa thâm canh</v>
+      </c>
+      <c r="K177" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="L177" t="str">
+        <v>Male // Nam</v>
+      </c>
+      <c r="M177" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="N177" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O177" t="str">
+        <v>0</v>
+      </c>
+      <c r="P177" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q177" t="str">
+        <v>0</v>
+      </c>
+      <c r="R177" t="str">
+        <v>0</v>
+      </c>
+      <c r="S177" t="str">
+        <v>0</v>
+      </c>
+      <c r="T177" t="str">
+        <v>0</v>
+      </c>
+      <c r="U177" t="str">
+        <v>3</v>
+      </c>
+      <c r="V177" t="str">
+        <v>0</v>
+      </c>
+      <c r="W177" t="str">
+        <v>2</v>
+      </c>
+      <c r="X177" t="str">
+        <v>4/10/26</v>
+      </c>
+      <c r="Y177" t="str">
+        <v>7/14/26</v>
+      </c>
+      <c r="Z177" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="AA177" t="str">
+        <v>NGÂN</v>
+      </c>
+      <c r="AB177" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="AD177" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="AE177" t="str">
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:AE87"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:AE177"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/cypress/fixtures/run-log.xlsx
+++ b/cypress/fixtures/run-log.xlsx
@@ -404,7 +404,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AE177"/>
+  <dimension ref="A1:AE193"/>
   <sheetData>
     <row r="1" xml:space="preserve">
       <c r="A1" t="str" xml:space="preserve">
@@ -14863,9 +14863,1337 @@
         <v/>
       </c>
     </row>
+    <row r="178" xml:space="preserve">
+      <c r="A178" t="str">
+        <v>(1175)</v>
+      </c>
+      <c r="B178" t="str">
+        <v>(1) Viet Nga Group, (2) Việt Nga Group-HTX Hoà Thuận</v>
+      </c>
+      <c r="C178" t="str">
+        <v>73970</v>
+      </c>
+      <c r="D178" t="str">
+        <v>919813394</v>
+      </c>
+      <c r="E178" t="str">
+        <v>TRƯƠNG THỊ TIẾN</v>
+      </c>
+      <c r="F178" t="str">
+        <v>HỢP TÁC XÃ DỊCH VỤ TỔNG HỢP HÒA THUẬN</v>
+      </c>
+      <c r="J178" t="str" xml:space="preserve">
+        <v xml:space="preserve">✅ Residue removal // Thu gom rơm rạ_x000d_
+✅ Rate reduction // Giảm lượng phân bón_x000d_
+✅ Reduced planting density // Giảm mật độ trồng_x000d_
+✅ Irrigation Management // Quản lý tưới tiêu</v>
+      </c>
+      <c r="K178" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="L178" t="str">
+        <v>Female // Nữ</v>
+      </c>
+      <c r="M178" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="N178" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O178" t="str">
+        <v>1</v>
+      </c>
+      <c r="P178" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q178" t="str">
+        <v>0</v>
+      </c>
+      <c r="R178" t="str">
+        <v>0</v>
+      </c>
+      <c r="S178" t="str">
+        <v>0</v>
+      </c>
+      <c r="T178" t="str">
+        <v>0</v>
+      </c>
+      <c r="U178" t="str">
+        <v>4</v>
+      </c>
+      <c r="V178" t="str">
+        <v>0</v>
+      </c>
+      <c r="W178" t="str">
+        <v>2</v>
+      </c>
+      <c r="X178" t="str">
+        <v>4/20/26</v>
+      </c>
+      <c r="Y178" t="str">
+        <v>7/24/26</v>
+      </c>
+      <c r="Z178" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="AB178" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="AD178" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="AE178" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="179" xml:space="preserve">
+      <c r="A179" t="str">
+        <v>(1175)</v>
+      </c>
+      <c r="B179" t="str">
+        <v>(1) Viet Nga Group, (2) Việt Nga Group-HTX Hoà Thuận</v>
+      </c>
+      <c r="C179" t="str">
+        <v>73970</v>
+      </c>
+      <c r="D179" t="str">
+        <v>919813394</v>
+      </c>
+      <c r="E179" t="str">
+        <v>TRƯƠNG THỊ TIẾN</v>
+      </c>
+      <c r="F179" t="str">
+        <v>HỢP TÁC XÃ DỊCH VỤ TỔNG HỢP HÒA THUẬN</v>
+      </c>
+      <c r="J179" t="str" xml:space="preserve">
+        <v xml:space="preserve">✅ Residue removal // Thu gom rơm rạ_x000d_
+✅ Rate reduction // Giảm lượng phân bón_x000d_
+✅ Reduced planting density // Giảm mật độ trồng_x000d_
+✅ Irrigation Management // Quản lý tưới tiêu</v>
+      </c>
+      <c r="K179" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="L179" t="str">
+        <v>Female // Nữ</v>
+      </c>
+      <c r="M179" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="N179" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O179" t="str">
+        <v>1</v>
+      </c>
+      <c r="P179" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q179" t="str">
+        <v>0</v>
+      </c>
+      <c r="R179" t="str">
+        <v>0</v>
+      </c>
+      <c r="S179" t="str">
+        <v>0</v>
+      </c>
+      <c r="T179" t="str">
+        <v>0</v>
+      </c>
+      <c r="U179" t="str">
+        <v>4</v>
+      </c>
+      <c r="V179" t="str">
+        <v>0</v>
+      </c>
+      <c r="W179" t="str">
+        <v>2</v>
+      </c>
+      <c r="X179" t="str">
+        <v>4/20/26</v>
+      </c>
+      <c r="Y179" t="str">
+        <v>7/24/26</v>
+      </c>
+      <c r="Z179" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="AB179" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="AD179" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="AE179" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="180" xml:space="preserve">
+      <c r="A180" t="str">
+        <v>(1175)</v>
+      </c>
+      <c r="B180" t="str">
+        <v>(1) Viet Nga Group, (2) Việt Nga Group-HTX Hoà Thuận</v>
+      </c>
+      <c r="C180" t="str">
+        <v>73970</v>
+      </c>
+      <c r="D180" t="str">
+        <v>919813394</v>
+      </c>
+      <c r="E180" t="str">
+        <v>TRƯƠNG THỊ TIẾN</v>
+      </c>
+      <c r="F180" t="str">
+        <v>HỢP TÁC XÃ DỊCH VỤ TỔNG HỢP HÒA THUẬN</v>
+      </c>
+      <c r="J180" t="str" xml:space="preserve">
+        <v xml:space="preserve">✅ Residue removal // Thu gom rơm rạ_x000d_
+✅ Rate reduction // Giảm lượng phân bón_x000d_
+✅ Reduced planting density // Giảm mật độ trồng_x000d_
+✅ Irrigation Management // Quản lý tưới tiêu</v>
+      </c>
+      <c r="K180" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="L180" t="str">
+        <v>Female // Nữ</v>
+      </c>
+      <c r="M180" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="N180" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O180" t="str">
+        <v>1</v>
+      </c>
+      <c r="P180" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q180" t="str">
+        <v>0</v>
+      </c>
+      <c r="R180" t="str">
+        <v>0</v>
+      </c>
+      <c r="S180" t="str">
+        <v>0</v>
+      </c>
+      <c r="T180" t="str">
+        <v>0</v>
+      </c>
+      <c r="U180" t="str">
+        <v>4</v>
+      </c>
+      <c r="V180" t="str">
+        <v>0</v>
+      </c>
+      <c r="W180" t="str">
+        <v>2</v>
+      </c>
+      <c r="X180" t="str">
+        <v>4/20/26</v>
+      </c>
+      <c r="Y180" t="str">
+        <v>7/24/26</v>
+      </c>
+      <c r="Z180" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="AB180" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="AD180" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="AE180" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="181" xml:space="preserve">
+      <c r="A181" t="str">
+        <v>(1175)</v>
+      </c>
+      <c r="B181" t="str">
+        <v>(1) Viet Nga Group, (2) Việt Nga Group-HTX Hoà Thuận</v>
+      </c>
+      <c r="C181" t="str">
+        <v>73970</v>
+      </c>
+      <c r="D181" t="str">
+        <v>919813394</v>
+      </c>
+      <c r="E181" t="str">
+        <v>TRƯƠNG THỊ TIẾN</v>
+      </c>
+      <c r="F181" t="str">
+        <v>HỢP TÁC XÃ DỊCH VỤ TỔNG HỢP HÒA THUẬN</v>
+      </c>
+      <c r="J181" t="str" xml:space="preserve">
+        <v xml:space="preserve">✅ Residue removal // Thu gom rơm rạ_x000d_
+✅ Rate reduction // Giảm lượng phân bón_x000d_
+✅ Reduced planting density // Giảm mật độ trồng_x000d_
+✅ Irrigation Management // Quản lý tưới tiêu</v>
+      </c>
+      <c r="K181" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="L181" t="str">
+        <v>Female // Nữ</v>
+      </c>
+      <c r="M181" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="N181" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O181" t="str">
+        <v>1</v>
+      </c>
+      <c r="P181" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q181" t="str">
+        <v>0</v>
+      </c>
+      <c r="R181" t="str">
+        <v>0</v>
+      </c>
+      <c r="S181" t="str">
+        <v>0</v>
+      </c>
+      <c r="T181" t="str">
+        <v>0</v>
+      </c>
+      <c r="U181" t="str">
+        <v>4</v>
+      </c>
+      <c r="V181" t="str">
+        <v>0</v>
+      </c>
+      <c r="W181" t="str">
+        <v>2</v>
+      </c>
+      <c r="X181" t="str">
+        <v>4/20/26</v>
+      </c>
+      <c r="Y181" t="str">
+        <v>7/24/26</v>
+      </c>
+      <c r="Z181" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="AB181" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="AD181" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="AE181" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="182" xml:space="preserve">
+      <c r="A182" t="str">
+        <v>(1175)</v>
+      </c>
+      <c r="B182" t="str">
+        <v>(1) Viet Nga Group, (2) Việt Nga Group-HTX Hoà Thuận</v>
+      </c>
+      <c r="C182" t="str">
+        <v>73970</v>
+      </c>
+      <c r="D182" t="str">
+        <v>919813394</v>
+      </c>
+      <c r="E182" t="str">
+        <v>TRƯƠNG THỊ TIẾN</v>
+      </c>
+      <c r="F182" t="str">
+        <v>HỢP TÁC XÃ DỊCH VỤ TỔNG HỢP HÒA THUẬN</v>
+      </c>
+      <c r="J182" t="str" xml:space="preserve">
+        <v xml:space="preserve">✅ Residue removal // Thu gom rơm rạ_x000d_
+✅ Rate reduction // Giảm lượng phân bón_x000d_
+✅ Reduced planting density // Giảm mật độ trồng_x000d_
+✅ Irrigation Management // Quản lý tưới tiêu</v>
+      </c>
+      <c r="K182" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="L182" t="str">
+        <v>Female // Nữ</v>
+      </c>
+      <c r="M182" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="N182" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O182" t="str">
+        <v>1</v>
+      </c>
+      <c r="P182" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q182" t="str">
+        <v>0</v>
+      </c>
+      <c r="R182" t="str">
+        <v>0</v>
+      </c>
+      <c r="S182" t="str">
+        <v>0</v>
+      </c>
+      <c r="T182" t="str">
+        <v>0</v>
+      </c>
+      <c r="U182" t="str">
+        <v>4</v>
+      </c>
+      <c r="V182" t="str">
+        <v>0</v>
+      </c>
+      <c r="W182" t="str">
+        <v>2</v>
+      </c>
+      <c r="X182" t="str">
+        <v>4/20/26</v>
+      </c>
+      <c r="Y182" t="str">
+        <v>7/24/26</v>
+      </c>
+      <c r="Z182" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="AB182" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="AD182" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="AE182" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="183" xml:space="preserve">
+      <c r="A183" t="str">
+        <v>(1175)</v>
+      </c>
+      <c r="B183" t="str">
+        <v>(1) Viet Nga Group, (2) Việt Nga Group-HTX Hoà Thuận</v>
+      </c>
+      <c r="C183" t="str">
+        <v>73970</v>
+      </c>
+      <c r="D183" t="str">
+        <v>919813394</v>
+      </c>
+      <c r="E183" t="str">
+        <v>TRƯƠNG THỊ TIẾN</v>
+      </c>
+      <c r="F183" t="str">
+        <v>HỢP TÁC XÃ DỊCH VỤ TỔNG HỢP HÒA THUẬN</v>
+      </c>
+      <c r="J183" t="str" xml:space="preserve">
+        <v xml:space="preserve">✅ Residue removal // Thu gom rơm rạ_x000d_
+✅ Rate reduction // Giảm lượng phân bón_x000d_
+✅ Reduced planting density // Giảm mật độ trồng_x000d_
+✅ Irrigation Management // Quản lý tưới tiêu</v>
+      </c>
+      <c r="K183" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="L183" t="str">
+        <v>Female // Nữ</v>
+      </c>
+      <c r="M183" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="N183" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O183" t="str">
+        <v>1</v>
+      </c>
+      <c r="P183" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q183" t="str">
+        <v>0</v>
+      </c>
+      <c r="R183" t="str">
+        <v>0</v>
+      </c>
+      <c r="S183" t="str">
+        <v>0</v>
+      </c>
+      <c r="T183" t="str">
+        <v>0</v>
+      </c>
+      <c r="U183" t="str">
+        <v>4</v>
+      </c>
+      <c r="V183" t="str">
+        <v>0</v>
+      </c>
+      <c r="W183" t="str">
+        <v>2</v>
+      </c>
+      <c r="X183" t="str">
+        <v>4/20/26</v>
+      </c>
+      <c r="Y183" t="str">
+        <v>7/24/26</v>
+      </c>
+      <c r="Z183" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="AB183" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="AD183" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="AE183" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="184" xml:space="preserve">
+      <c r="A184" t="str">
+        <v>(1175)</v>
+      </c>
+      <c r="B184" t="str">
+        <v>(1) Viet Nga Group, (2) Việt Nga Group-HTX Hoà Thuận</v>
+      </c>
+      <c r="C184" t="str">
+        <v>73970</v>
+      </c>
+      <c r="D184" t="str">
+        <v>919813394</v>
+      </c>
+      <c r="E184" t="str">
+        <v>TRƯƠNG THỊ TIẾN</v>
+      </c>
+      <c r="F184" t="str">
+        <v>HỢP TÁC XÃ DỊCH VỤ TỔNG HỢP HÒA THUẬN</v>
+      </c>
+      <c r="J184" t="str" xml:space="preserve">
+        <v xml:space="preserve">✅ Residue removal // Thu gom rơm rạ_x000d_
+✅ Rate reduction // Giảm lượng phân bón_x000d_
+✅ Reduced planting density // Giảm mật độ trồng_x000d_
+✅ Irrigation Management // Quản lý tưới tiêu</v>
+      </c>
+      <c r="K184" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="L184" t="str">
+        <v>Female // Nữ</v>
+      </c>
+      <c r="M184" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="N184" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O184" t="str">
+        <v>1</v>
+      </c>
+      <c r="P184" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q184" t="str">
+        <v>0</v>
+      </c>
+      <c r="R184" t="str">
+        <v>0</v>
+      </c>
+      <c r="S184" t="str">
+        <v>0</v>
+      </c>
+      <c r="T184" t="str">
+        <v>0</v>
+      </c>
+      <c r="U184" t="str">
+        <v>4</v>
+      </c>
+      <c r="V184" t="str">
+        <v>0</v>
+      </c>
+      <c r="W184" t="str">
+        <v>2</v>
+      </c>
+      <c r="X184" t="str">
+        <v>4/20/26</v>
+      </c>
+      <c r="Y184" t="str">
+        <v>7/24/26</v>
+      </c>
+      <c r="Z184" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="AB184" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="AD184" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="AE184" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="185" xml:space="preserve">
+      <c r="A185" t="str">
+        <v>(1175)</v>
+      </c>
+      <c r="B185" t="str">
+        <v>(1) Viet Nga Group, (2) Việt Nga Group-HTX Hoà Thuận</v>
+      </c>
+      <c r="C185" t="str">
+        <v>73970</v>
+      </c>
+      <c r="D185" t="str">
+        <v>919813394</v>
+      </c>
+      <c r="E185" t="str">
+        <v>TRƯƠNG THỊ TIẾN</v>
+      </c>
+      <c r="F185" t="str">
+        <v>HỢP TÁC XÃ DỊCH VỤ TỔNG HỢP HÒA THUẬN</v>
+      </c>
+      <c r="J185" t="str" xml:space="preserve">
+        <v xml:space="preserve">✅ Residue removal // Thu gom rơm rạ_x000d_
+✅ Rate reduction // Giảm lượng phân bón_x000d_
+✅ Reduced planting density // Giảm mật độ trồng_x000d_
+✅ Irrigation Management // Quản lý tưới tiêu</v>
+      </c>
+      <c r="K185" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="L185" t="str">
+        <v>Female // Nữ</v>
+      </c>
+      <c r="M185" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="N185" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O185" t="str">
+        <v>1</v>
+      </c>
+      <c r="P185" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q185" t="str">
+        <v>0</v>
+      </c>
+      <c r="R185" t="str">
+        <v>0</v>
+      </c>
+      <c r="S185" t="str">
+        <v>0</v>
+      </c>
+      <c r="T185" t="str">
+        <v>0</v>
+      </c>
+      <c r="U185" t="str">
+        <v>4</v>
+      </c>
+      <c r="V185" t="str">
+        <v>0</v>
+      </c>
+      <c r="W185" t="str">
+        <v>2</v>
+      </c>
+      <c r="X185" t="str">
+        <v>4/20/26</v>
+      </c>
+      <c r="Y185" t="str">
+        <v>7/24/26</v>
+      </c>
+      <c r="Z185" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="AB185" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="AD185" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="AE185" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="186" xml:space="preserve">
+      <c r="A186" t="str">
+        <v>(1175)</v>
+      </c>
+      <c r="B186" t="str">
+        <v>(1) Viet Nga Group, (2) Việt Nga Group-HTX Hoà Thuận</v>
+      </c>
+      <c r="C186" t="str">
+        <v>73970</v>
+      </c>
+      <c r="D186" t="str">
+        <v>919813394</v>
+      </c>
+      <c r="E186" t="str">
+        <v>TRƯƠNG THỊ TIẾN</v>
+      </c>
+      <c r="F186" t="str">
+        <v>HỢP TÁC XÃ DỊCH VỤ TỔNG HỢP HÒA THUẬN</v>
+      </c>
+      <c r="J186" t="str" xml:space="preserve">
+        <v xml:space="preserve">✅ Residue removal // Thu gom rơm rạ_x000d_
+✅ Rate reduction // Giảm lượng phân bón_x000d_
+✅ Reduced planting density // Giảm mật độ trồng_x000d_
+✅ Irrigation Management // Quản lý tưới tiêu</v>
+      </c>
+      <c r="K186" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="L186" t="str">
+        <v>Female // Nữ</v>
+      </c>
+      <c r="M186" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="N186" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O186" t="str">
+        <v>1</v>
+      </c>
+      <c r="P186" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q186" t="str">
+        <v>0</v>
+      </c>
+      <c r="R186" t="str">
+        <v>0</v>
+      </c>
+      <c r="S186" t="str">
+        <v>0</v>
+      </c>
+      <c r="T186" t="str">
+        <v>0</v>
+      </c>
+      <c r="U186" t="str">
+        <v>4</v>
+      </c>
+      <c r="V186" t="str">
+        <v>0</v>
+      </c>
+      <c r="W186" t="str">
+        <v>2</v>
+      </c>
+      <c r="X186" t="str">
+        <v>4/20/26</v>
+      </c>
+      <c r="Y186" t="str">
+        <v>7/24/26</v>
+      </c>
+      <c r="Z186" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="AB186" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="AD186" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="AE186" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="187" xml:space="preserve">
+      <c r="A187" t="str">
+        <v>(1252)</v>
+      </c>
+      <c r="B187" t="str">
+        <v>(1) Viet Nga Group, (2) Việt Nga Group - HTX An Hoà</v>
+      </c>
+      <c r="C187" t="str">
+        <v>74110</v>
+      </c>
+      <c r="D187" t="str">
+        <v>946756347</v>
+      </c>
+      <c r="E187" t="str">
+        <v>TRẦN VĂN KHÁNH</v>
+      </c>
+      <c r="F187" t="str">
+        <v>HỢP TÁC XÃ NÔNG NGHIỆP AN HÒA</v>
+      </c>
+      <c r="J187" t="str" xml:space="preserve">
+        <v xml:space="preserve">✅ Residue removal // Thu gom rơm rạ_x000d_
+✅ Rate reduction // Giảm lượng phân bón_x000d_
+✅ Reduced planting density // Giảm mật độ trồng_x000d_
+✅ Irrigation Management // Quản lý tưới tiêu</v>
+      </c>
+      <c r="K187" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="L187" t="str">
+        <v>Male // Nam</v>
+      </c>
+      <c r="M187" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="N187" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O187" t="str">
+        <v>0</v>
+      </c>
+      <c r="P187" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q187" t="str">
+        <v>0</v>
+      </c>
+      <c r="R187" t="str">
+        <v>0</v>
+      </c>
+      <c r="S187" t="str">
+        <v>0</v>
+      </c>
+      <c r="T187" t="str">
+        <v>0</v>
+      </c>
+      <c r="U187" t="str">
+        <v>2</v>
+      </c>
+      <c r="V187" t="str">
+        <v>0</v>
+      </c>
+      <c r="W187" t="str">
+        <v>1</v>
+      </c>
+      <c r="X187" t="str">
+        <v>5/17/26</v>
+      </c>
+      <c r="Y187" t="str">
+        <v>8/20/26</v>
+      </c>
+      <c r="Z187" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="AB187" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="AD187" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="AE187" t="str">
+        <v>Skipped: Intended practices disabled (program stage)</v>
+      </c>
+    </row>
+    <row r="188" xml:space="preserve">
+      <c r="A188" t="str">
+        <v>(1175)</v>
+      </c>
+      <c r="B188" t="str">
+        <v>(1) Viet Nga Group, (2) Việt Nga Group-HTX Hoà Thuận</v>
+      </c>
+      <c r="C188" t="str">
+        <v>73970</v>
+      </c>
+      <c r="D188" t="str">
+        <v>919813394</v>
+      </c>
+      <c r="E188" t="str">
+        <v>TRƯƠNG THỊ TIẾN</v>
+      </c>
+      <c r="F188" t="str">
+        <v>HỢP TÁC XÃ DỊCH VỤ TỔNG HỢP HÒA THUẬN</v>
+      </c>
+      <c r="J188" t="str" xml:space="preserve">
+        <v xml:space="preserve">✅ Residue removal // Thu gom rơm rạ_x000d_
+✅ Rate reduction // Giảm lượng phân bón_x000d_
+✅ Reduced planting density // Giảm mật độ trồng_x000d_
+✅ Irrigation Management // Quản lý tưới tiêu</v>
+      </c>
+      <c r="K188" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="L188" t="str">
+        <v>Female // Nữ</v>
+      </c>
+      <c r="M188" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="N188" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O188" t="str">
+        <v>1</v>
+      </c>
+      <c r="P188" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q188" t="str">
+        <v>0</v>
+      </c>
+      <c r="R188" t="str">
+        <v>0</v>
+      </c>
+      <c r="S188" t="str">
+        <v>0</v>
+      </c>
+      <c r="T188" t="str">
+        <v>0</v>
+      </c>
+      <c r="U188" t="str">
+        <v>4</v>
+      </c>
+      <c r="V188" t="str">
+        <v>0</v>
+      </c>
+      <c r="W188" t="str">
+        <v>2</v>
+      </c>
+      <c r="X188" t="str">
+        <v>4/20/26</v>
+      </c>
+      <c r="Y188" t="str">
+        <v>7/24/26</v>
+      </c>
+      <c r="Z188" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="AB188" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="AD188" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="AE188" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="189" xml:space="preserve">
+      <c r="A189" t="str">
+        <v>(1252)</v>
+      </c>
+      <c r="B189" t="str">
+        <v>(1) Viet Nga Group, (2) Việt Nga Group - HTX An Hoà</v>
+      </c>
+      <c r="C189" t="str">
+        <v>74110</v>
+      </c>
+      <c r="D189" t="str">
+        <v>946756347</v>
+      </c>
+      <c r="E189" t="str">
+        <v>TRẦN VĂN KHÁNH</v>
+      </c>
+      <c r="F189" t="str">
+        <v>HỢP TÁC XÃ NÔNG NGHIỆP AN HÒA</v>
+      </c>
+      <c r="J189" t="str" xml:space="preserve">
+        <v xml:space="preserve">✅ Residue removal // Thu gom rơm rạ_x000d_
+✅ Rate reduction // Giảm lượng phân bón_x000d_
+✅ Reduced planting density // Giảm mật độ trồng_x000d_
+✅ Irrigation Management // Quản lý tưới tiêu</v>
+      </c>
+      <c r="K189" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="L189" t="str">
+        <v>Male // Nam</v>
+      </c>
+      <c r="M189" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="N189" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O189" t="str">
+        <v>0</v>
+      </c>
+      <c r="P189" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q189" t="str">
+        <v>0</v>
+      </c>
+      <c r="R189" t="str">
+        <v>0</v>
+      </c>
+      <c r="S189" t="str">
+        <v>0</v>
+      </c>
+      <c r="T189" t="str">
+        <v>0</v>
+      </c>
+      <c r="U189" t="str">
+        <v>2</v>
+      </c>
+      <c r="V189" t="str">
+        <v>0</v>
+      </c>
+      <c r="W189" t="str">
+        <v>1</v>
+      </c>
+      <c r="X189" t="str">
+        <v>5/17/26</v>
+      </c>
+      <c r="Y189" t="str">
+        <v>8/20/26</v>
+      </c>
+      <c r="Z189" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="AB189" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="AD189" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="AE189" t="str">
+        <v>Skipped: Intended practices disabled (program stage)</v>
+      </c>
+    </row>
+    <row r="190" xml:space="preserve">
+      <c r="A190" t="str">
+        <v>(1175)</v>
+      </c>
+      <c r="B190" t="str">
+        <v>(1) Viet Nga Group, (2) Việt Nga Group-HTX Hoà Thuận</v>
+      </c>
+      <c r="C190" t="str">
+        <v>73970</v>
+      </c>
+      <c r="D190" t="str">
+        <v>919813394</v>
+      </c>
+      <c r="E190" t="str">
+        <v>TRƯƠNG THỊ TIẾN</v>
+      </c>
+      <c r="F190" t="str">
+        <v>HỢP TÁC XÃ DỊCH VỤ TỔNG HỢP HÒA THUẬN</v>
+      </c>
+      <c r="J190" t="str" xml:space="preserve">
+        <v xml:space="preserve">✅ Residue removal // Thu gom rơm rạ_x000d_
+✅ Rate reduction // Giảm lượng phân bón_x000d_
+✅ Reduced planting density // Giảm mật độ trồng_x000d_
+✅ Irrigation Management // Quản lý tưới tiêu</v>
+      </c>
+      <c r="K190" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="L190" t="str">
+        <v>Female // Nữ</v>
+      </c>
+      <c r="M190" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="N190" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O190" t="str">
+        <v>1</v>
+      </c>
+      <c r="P190" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q190" t="str">
+        <v>0</v>
+      </c>
+      <c r="R190" t="str">
+        <v>0</v>
+      </c>
+      <c r="S190" t="str">
+        <v>0</v>
+      </c>
+      <c r="T190" t="str">
+        <v>0</v>
+      </c>
+      <c r="U190" t="str">
+        <v>4</v>
+      </c>
+      <c r="V190" t="str">
+        <v>0</v>
+      </c>
+      <c r="W190" t="str">
+        <v>2</v>
+      </c>
+      <c r="X190" t="str">
+        <v>4/20/26</v>
+      </c>
+      <c r="Y190" t="str">
+        <v>7/24/26</v>
+      </c>
+      <c r="Z190" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="AB190" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="AD190" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="AE190" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="191" xml:space="preserve">
+      <c r="A191" t="str">
+        <v>(1252)</v>
+      </c>
+      <c r="B191" t="str">
+        <v>(1) Viet Nga Group, (2) Việt Nga Group - HTX An Hoà</v>
+      </c>
+      <c r="C191" t="str">
+        <v>74110</v>
+      </c>
+      <c r="D191" t="str">
+        <v>946756347</v>
+      </c>
+      <c r="E191" t="str">
+        <v>TRẦN VĂN KHÁNH</v>
+      </c>
+      <c r="F191" t="str">
+        <v>HỢP TÁC XÃ NÔNG NGHIỆP AN HÒA</v>
+      </c>
+      <c r="J191" t="str" xml:space="preserve">
+        <v xml:space="preserve">✅ Residue removal // Thu gom rơm rạ_x000d_
+✅ Rate reduction // Giảm lượng phân bón_x000d_
+✅ Reduced planting density // Giảm mật độ trồng_x000d_
+✅ Irrigation Management // Quản lý tưới tiêu</v>
+      </c>
+      <c r="K191" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="L191" t="str">
+        <v>Male // Nam</v>
+      </c>
+      <c r="M191" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="N191" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O191" t="str">
+        <v>0</v>
+      </c>
+      <c r="P191" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q191" t="str">
+        <v>0</v>
+      </c>
+      <c r="R191" t="str">
+        <v>0</v>
+      </c>
+      <c r="S191" t="str">
+        <v>0</v>
+      </c>
+      <c r="T191" t="str">
+        <v>0</v>
+      </c>
+      <c r="U191" t="str">
+        <v>2</v>
+      </c>
+      <c r="V191" t="str">
+        <v>0</v>
+      </c>
+      <c r="W191" t="str">
+        <v>1</v>
+      </c>
+      <c r="X191" t="str">
+        <v>5/17/26</v>
+      </c>
+      <c r="Y191" t="str">
+        <v>8/20/26</v>
+      </c>
+      <c r="Z191" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="AB191" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="AD191" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="AE191" t="str">
+        <v>Skipped: Intended practices disabled (program stage)</v>
+      </c>
+    </row>
+    <row r="192" xml:space="preserve">
+      <c r="A192" t="str">
+        <v>(1175)</v>
+      </c>
+      <c r="B192" t="str">
+        <v>(1) Viet Nga Group, (2) Việt Nga Group-HTX Hoà Thuận</v>
+      </c>
+      <c r="C192" t="str">
+        <v>73970</v>
+      </c>
+      <c r="D192" t="str">
+        <v>919813394</v>
+      </c>
+      <c r="E192" t="str">
+        <v>TRƯƠNG THỊ TIẾN</v>
+      </c>
+      <c r="F192" t="str">
+        <v>HỢP TÁC XÃ DỊCH VỤ TỔNG HỢP HÒA THUẬN</v>
+      </c>
+      <c r="J192" t="str" xml:space="preserve">
+        <v xml:space="preserve">✅ Residue removal // Thu gom rơm rạ_x000d_
+✅ Rate reduction // Giảm lượng phân bón_x000d_
+✅ Reduced planting density // Giảm mật độ trồng_x000d_
+✅ Irrigation Management // Quản lý tưới tiêu</v>
+      </c>
+      <c r="K192" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="L192" t="str">
+        <v>Female // Nữ</v>
+      </c>
+      <c r="M192" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="N192" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O192" t="str">
+        <v>1</v>
+      </c>
+      <c r="P192" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q192" t="str">
+        <v>0</v>
+      </c>
+      <c r="R192" t="str">
+        <v>0</v>
+      </c>
+      <c r="S192" t="str">
+        <v>0</v>
+      </c>
+      <c r="T192" t="str">
+        <v>0</v>
+      </c>
+      <c r="U192" t="str">
+        <v>4</v>
+      </c>
+      <c r="V192" t="str">
+        <v>0</v>
+      </c>
+      <c r="W192" t="str">
+        <v>2</v>
+      </c>
+      <c r="X192" t="str">
+        <v>4/20/26</v>
+      </c>
+      <c r="Y192" t="str">
+        <v>7/24/26</v>
+      </c>
+      <c r="Z192" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="AB192" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="AD192" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="AE192" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="193" xml:space="preserve">
+      <c r="A193" t="str">
+        <v>(1252)</v>
+      </c>
+      <c r="B193" t="str">
+        <v>(1) Viet Nga Group, (2) Việt Nga Group - HTX An Hoà</v>
+      </c>
+      <c r="C193" t="str">
+        <v>74110</v>
+      </c>
+      <c r="D193" t="str">
+        <v>946756347</v>
+      </c>
+      <c r="E193" t="str">
+        <v>TRẦN VĂN KHÁNH</v>
+      </c>
+      <c r="F193" t="str">
+        <v>HỢP TÁC XÃ NÔNG NGHIỆP AN HÒA</v>
+      </c>
+      <c r="J193" t="str" xml:space="preserve">
+        <v xml:space="preserve">✅ Residue removal // Thu gom rơm rạ_x000d_
+✅ Rate reduction // Giảm lượng phân bón_x000d_
+✅ Reduced planting density // Giảm mật độ trồng_x000d_
+✅ Irrigation Management // Quản lý tưới tiêu</v>
+      </c>
+      <c r="K193" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="L193" t="str">
+        <v>Male // Nam</v>
+      </c>
+      <c r="M193" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="N193" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O193" t="str">
+        <v>0</v>
+      </c>
+      <c r="P193" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q193" t="str">
+        <v>0</v>
+      </c>
+      <c r="R193" t="str">
+        <v>0</v>
+      </c>
+      <c r="S193" t="str">
+        <v>0</v>
+      </c>
+      <c r="T193" t="str">
+        <v>0</v>
+      </c>
+      <c r="U193" t="str">
+        <v>2</v>
+      </c>
+      <c r="V193" t="str">
+        <v>0</v>
+      </c>
+      <c r="W193" t="str">
+        <v>1</v>
+      </c>
+      <c r="X193" t="str">
+        <v>5/17/26</v>
+      </c>
+      <c r="Y193" t="str">
+        <v>8/20/26</v>
+      </c>
+      <c r="Z193" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="AB193" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="AD193" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="AE193" t="str">
+        <v>Skipped: Intended practices disabled (program stage)</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:AE177"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:AE193"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/cypress/fixtures/run-log.xlsx
+++ b/cypress/fixtures/run-log.xlsx
@@ -404,7 +404,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AE193"/>
+  <dimension ref="A1:AE274"/>
   <sheetData>
     <row r="1" xml:space="preserve">
       <c r="A1" t="str" xml:space="preserve">
@@ -16191,9 +16191,6732 @@
         <v>Skipped: Intended practices disabled (program stage)</v>
       </c>
     </row>
+    <row r="194" xml:space="preserve">
+      <c r="A194" t="str">
+        <v>(1175)</v>
+      </c>
+      <c r="B194" t="str">
+        <v>(1) Viet Nga Group, (2) Việt Nga Group-HTX Hoà Thuận</v>
+      </c>
+      <c r="C194" t="str">
+        <v>73970</v>
+      </c>
+      <c r="D194" t="str">
+        <v>919813394</v>
+      </c>
+      <c r="E194" t="str">
+        <v>TRƯƠNG THỊ TIẾN</v>
+      </c>
+      <c r="F194" t="str">
+        <v>HỢP TÁC XÃ DỊCH VỤ TỔNG HỢP HÒA THUẬN</v>
+      </c>
+      <c r="J194" t="str" xml:space="preserve">
+        <v xml:space="preserve">✅ Residue removal // Thu gom rơm rạ_x000d_
+✅ Rate reduction // Giảm lượng phân bón_x000d_
+✅ Reduced planting density // Giảm mật độ trồng_x000d_
+✅ Irrigation Management // Quản lý tưới tiêu</v>
+      </c>
+      <c r="K194" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="L194" t="str">
+        <v>Female // Nữ</v>
+      </c>
+      <c r="M194" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="N194" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O194" t="str">
+        <v>1</v>
+      </c>
+      <c r="P194" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q194" t="str">
+        <v>0</v>
+      </c>
+      <c r="R194" t="str">
+        <v>0</v>
+      </c>
+      <c r="S194" t="str">
+        <v>0</v>
+      </c>
+      <c r="T194" t="str">
+        <v>0</v>
+      </c>
+      <c r="U194" t="str">
+        <v>4</v>
+      </c>
+      <c r="V194" t="str">
+        <v>0</v>
+      </c>
+      <c r="W194" t="str">
+        <v>2</v>
+      </c>
+      <c r="X194" t="str">
+        <v>4/20/26</v>
+      </c>
+      <c r="Y194" t="str">
+        <v>7/24/26</v>
+      </c>
+      <c r="Z194" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="AB194" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="AD194" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="AE194" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="195" xml:space="preserve">
+      <c r="A195" t="str">
+        <v>(1252)</v>
+      </c>
+      <c r="B195" t="str">
+        <v>(1) Viet Nga Group, (2) Việt Nga Group - HTX An Hoà</v>
+      </c>
+      <c r="C195" t="str">
+        <v>74110</v>
+      </c>
+      <c r="D195" t="str">
+        <v>946756347</v>
+      </c>
+      <c r="E195" t="str">
+        <v>TRẦN VĂN KHÁNH</v>
+      </c>
+      <c r="F195" t="str">
+        <v>HỢP TÁC XÃ NÔNG NGHIỆP AN HÒA</v>
+      </c>
+      <c r="J195" t="str" xml:space="preserve">
+        <v xml:space="preserve">✅ Residue removal // Thu gom rơm rạ_x000d_
+✅ Rate reduction // Giảm lượng phân bón_x000d_
+✅ Reduced planting density // Giảm mật độ trồng_x000d_
+✅ Irrigation Management // Quản lý tưới tiêu</v>
+      </c>
+      <c r="K195" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="L195" t="str">
+        <v>Male // Nam</v>
+      </c>
+      <c r="M195" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="N195" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O195" t="str">
+        <v>0</v>
+      </c>
+      <c r="P195" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q195" t="str">
+        <v>0</v>
+      </c>
+      <c r="R195" t="str">
+        <v>0</v>
+      </c>
+      <c r="S195" t="str">
+        <v>0</v>
+      </c>
+      <c r="T195" t="str">
+        <v>0</v>
+      </c>
+      <c r="U195" t="str">
+        <v>2</v>
+      </c>
+      <c r="V195" t="str">
+        <v>0</v>
+      </c>
+      <c r="W195" t="str">
+        <v>1</v>
+      </c>
+      <c r="X195" t="str">
+        <v>5/17/26</v>
+      </c>
+      <c r="Y195" t="str">
+        <v>8/20/26</v>
+      </c>
+      <c r="Z195" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="AB195" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="AD195" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="AE195" t="str">
+        <v>Skipped: Intended practices disabled (program stage)</v>
+      </c>
+    </row>
+    <row r="196" xml:space="preserve">
+      <c r="A196" t="str">
+        <v>(1253)</v>
+      </c>
+      <c r="B196" t="str">
+        <v>(1) Viet Nga Group, (2) Việt Nga Group - HTX An Hoà</v>
+      </c>
+      <c r="C196" t="str">
+        <v>74111</v>
+      </c>
+      <c r="D196" t="str">
+        <v>902441863</v>
+      </c>
+      <c r="E196" t="str">
+        <v>ĐÀO VĂN CHŨNG</v>
+      </c>
+      <c r="F196" t="str">
+        <v>HỢP TÁC XÃ NÔNG NGHIỆP AN HÒA</v>
+      </c>
+      <c r="J196" t="str" xml:space="preserve">
+        <v xml:space="preserve">✅ Residue removal // Thu gom rơm rạ_x000d_
+✅ Rate reduction // Giảm lượng phân bón_x000d_
+✅ Reduced planting density // Giảm mật độ trồng_x000d_
+✅ Irrigation Management // Quản lý tưới tiêu</v>
+      </c>
+      <c r="K196" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="L196" t="str">
+        <v>Male // Nam</v>
+      </c>
+      <c r="M196" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="N196" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O196" t="str">
+        <v>0</v>
+      </c>
+      <c r="P196" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q196" t="str">
+        <v>0</v>
+      </c>
+      <c r="R196" t="str">
+        <v>0</v>
+      </c>
+      <c r="S196" t="str">
+        <v>0</v>
+      </c>
+      <c r="T196" t="str">
+        <v>0</v>
+      </c>
+      <c r="U196" t="str">
+        <v>3</v>
+      </c>
+      <c r="V196" t="str">
+        <v>0</v>
+      </c>
+      <c r="W196" t="str">
+        <v>2</v>
+      </c>
+      <c r="X196" t="str">
+        <v>5/17/26</v>
+      </c>
+      <c r="Y196" t="str">
+        <v>8/20/26</v>
+      </c>
+      <c r="Z196" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="AB196" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="AD196" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="AE196" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="197" xml:space="preserve">
+      <c r="A197" t="str">
+        <v>(1254)</v>
+      </c>
+      <c r="B197" t="str">
+        <v>(1) Viet Nga Group, (2) Việt Nga Group - HTX An Hoà</v>
+      </c>
+      <c r="C197" t="str">
+        <v>74112</v>
+      </c>
+      <c r="D197" t="str">
+        <v>353740919</v>
+      </c>
+      <c r="E197" t="str">
+        <v>NGUYỄN VĂN ĐÚNG</v>
+      </c>
+      <c r="F197" t="str">
+        <v>HỢP TÁC XÃ NÔNG NGHIỆP AN HÒA</v>
+      </c>
+      <c r="J197" t="str" xml:space="preserve">
+        <v xml:space="preserve">✅ Residue removal // Thu gom rơm rạ_x000d_
+✅ Rate reduction // Giảm lượng phân bón_x000d_
+✅ Reduced planting density // Giảm mật độ trồng_x000d_
+✅ Irrigation Management // Quản lý tưới tiêu</v>
+      </c>
+      <c r="K197" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="L197" t="str">
+        <v>Male // Nam</v>
+      </c>
+      <c r="M197" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="N197" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O197" t="str">
+        <v>0</v>
+      </c>
+      <c r="P197" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q197" t="str">
+        <v>0</v>
+      </c>
+      <c r="R197" t="str">
+        <v>0</v>
+      </c>
+      <c r="S197" t="str">
+        <v>0</v>
+      </c>
+      <c r="T197" t="str">
+        <v>0</v>
+      </c>
+      <c r="U197" t="str">
+        <v>2</v>
+      </c>
+      <c r="V197" t="str">
+        <v>0</v>
+      </c>
+      <c r="W197" t="str">
+        <v>1</v>
+      </c>
+      <c r="X197" t="str">
+        <v>5/17/26</v>
+      </c>
+      <c r="Y197" t="str">
+        <v>8/20/26</v>
+      </c>
+      <c r="Z197" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="AB197" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="AD197" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="AE197" t="str">
+        <v>Skipped: Intended practices disabled (program stage)</v>
+      </c>
+    </row>
+    <row r="198" xml:space="preserve">
+      <c r="A198" t="str">
+        <v>(1255)</v>
+      </c>
+      <c r="B198" t="str">
+        <v>(1) Viet Nga Group, (2) Việt Nga Group - HTX An Hoà</v>
+      </c>
+      <c r="C198" t="str">
+        <v>74113</v>
+      </c>
+      <c r="D198" t="str">
+        <v>918215404</v>
+      </c>
+      <c r="E198" t="str">
+        <v>ĐẶNG VĂN NE</v>
+      </c>
+      <c r="F198" t="str">
+        <v>HỢP TÁC XÃ NÔNG NGHIỆP AN HÒA</v>
+      </c>
+      <c r="J198" t="str" xml:space="preserve">
+        <v xml:space="preserve">✅ Residue removal // Thu gom rơm rạ_x000d_
+✅ Rate reduction // Giảm lượng phân bón_x000d_
+✅ Reduced planting density // Giảm mật độ trồng_x000d_
+✅ Irrigation Management // Quản lý tưới tiêu</v>
+      </c>
+      <c r="K198" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="L198" t="str">
+        <v>Male // Nam</v>
+      </c>
+      <c r="M198" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="N198" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O198" t="str">
+        <v>0</v>
+      </c>
+      <c r="P198" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q198" t="str">
+        <v>0</v>
+      </c>
+      <c r="R198" t="str">
+        <v>0</v>
+      </c>
+      <c r="S198" t="str">
+        <v>0</v>
+      </c>
+      <c r="T198" t="str">
+        <v>0</v>
+      </c>
+      <c r="U198" t="str">
+        <v>2</v>
+      </c>
+      <c r="V198" t="str">
+        <v>0</v>
+      </c>
+      <c r="W198" t="str">
+        <v>1</v>
+      </c>
+      <c r="X198" t="str">
+        <v>5/17/26</v>
+      </c>
+      <c r="Y198" t="str">
+        <v>8/20/26</v>
+      </c>
+      <c r="Z198" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="AB198" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="AD198" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="AE198" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="199" xml:space="preserve">
+      <c r="A199" t="str">
+        <v>(1256)</v>
+      </c>
+      <c r="B199" t="str">
+        <v>(1) Viet Nga Group, (2) Việt Nga Group - HTX An Hoà</v>
+      </c>
+      <c r="C199" t="str">
+        <v>74114</v>
+      </c>
+      <c r="D199" t="str">
+        <v>394201779</v>
+      </c>
+      <c r="E199" t="str">
+        <v>NGUYỄN VĂN TÂM</v>
+      </c>
+      <c r="F199" t="str">
+        <v>HỢP TÁC XÃ NÔNG NGHIỆP AN HÒA</v>
+      </c>
+      <c r="J199" t="str" xml:space="preserve">
+        <v xml:space="preserve">✅ Residue removal // Thu gom rơm rạ_x000d_
+✅ Rate reduction // Giảm lượng phân bón_x000d_
+✅ Reduced planting density // Giảm mật độ trồng_x000d_
+✅ Irrigation Management // Quản lý tưới tiêu</v>
+      </c>
+      <c r="K199" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="L199" t="str">
+        <v>Male // Nam</v>
+      </c>
+      <c r="M199" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="N199" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O199" t="str">
+        <v>0</v>
+      </c>
+      <c r="P199" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q199" t="str">
+        <v>0</v>
+      </c>
+      <c r="R199" t="str">
+        <v>0</v>
+      </c>
+      <c r="S199" t="str">
+        <v>0</v>
+      </c>
+      <c r="T199" t="str">
+        <v>0</v>
+      </c>
+      <c r="U199" t="str">
+        <v>3</v>
+      </c>
+      <c r="V199" t="str">
+        <v>0</v>
+      </c>
+      <c r="W199" t="str">
+        <v>2</v>
+      </c>
+      <c r="X199" t="str">
+        <v>5/17/26</v>
+      </c>
+      <c r="Y199" t="str">
+        <v>8/20/26</v>
+      </c>
+      <c r="Z199" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="AB199" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="AD199" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="AE199" t="str">
+        <v>Skipped: Intended practices disabled (program stage)</v>
+      </c>
+    </row>
+    <row r="200" xml:space="preserve">
+      <c r="A200" t="str">
+        <v>(1257)</v>
+      </c>
+      <c r="B200" t="str">
+        <v>(1) Viet Nga Group, (2) Việt Nga Group - HTX An Hoà</v>
+      </c>
+      <c r="C200" t="str">
+        <v>74115</v>
+      </c>
+      <c r="D200" t="str">
+        <v>776858954</v>
+      </c>
+      <c r="E200" t="str">
+        <v>VÕ KIM DUNG</v>
+      </c>
+      <c r="F200" t="str">
+        <v>HỢP TÁC XÃ NÔNG NGHIỆP AN HÒA</v>
+      </c>
+      <c r="J200" t="str" xml:space="preserve">
+        <v xml:space="preserve">✅ Residue removal // Thu gom rơm rạ_x000d_
+✅ Rate reduction // Giảm lượng phân bón_x000d_
+✅ Reduced planting density // Giảm mật độ trồng_x000d_
+✅ Irrigation Management // Quản lý tưới tiêu</v>
+      </c>
+      <c r="K200" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="L200" t="str">
+        <v>Female // Nữ</v>
+      </c>
+      <c r="M200" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="N200" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O200" t="str">
+        <v>1</v>
+      </c>
+      <c r="P200" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q200" t="str">
+        <v>0</v>
+      </c>
+      <c r="R200" t="str">
+        <v>0</v>
+      </c>
+      <c r="S200" t="str">
+        <v>0</v>
+      </c>
+      <c r="T200" t="str">
+        <v>0</v>
+      </c>
+      <c r="U200" t="str">
+        <v>2</v>
+      </c>
+      <c r="V200" t="str">
+        <v>0</v>
+      </c>
+      <c r="W200" t="str">
+        <v>1</v>
+      </c>
+      <c r="X200" t="str">
+        <v>5/17/26</v>
+      </c>
+      <c r="Y200" t="str">
+        <v>8/20/26</v>
+      </c>
+      <c r="Z200" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="AB200" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="AD200" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="AE200" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="201" xml:space="preserve">
+      <c r="A201" t="str">
+        <v>(1258)</v>
+      </c>
+      <c r="B201" t="str">
+        <v>(1) Viet Nga Group, (2) Việt Nga Group - HTX An Hoà</v>
+      </c>
+      <c r="C201" t="str">
+        <v>74116</v>
+      </c>
+      <c r="D201" t="str">
+        <v>772819670</v>
+      </c>
+      <c r="E201" t="str">
+        <v>QUÁCH VĂN HỦNG</v>
+      </c>
+      <c r="F201" t="str">
+        <v>HỢP TÁC XÃ NÔNG NGHIỆP AN HÒA</v>
+      </c>
+      <c r="J201" t="str" xml:space="preserve">
+        <v xml:space="preserve">✅ Residue removal // Thu gom rơm rạ_x000d_
+✅ Rate reduction // Giảm lượng phân bón_x000d_
+✅ Reduced planting density // Giảm mật độ trồng_x000d_
+✅ Irrigation Management // Quản lý tưới tiêu</v>
+      </c>
+      <c r="K201" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="L201" t="str">
+        <v>Male // Nam</v>
+      </c>
+      <c r="M201" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="N201" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O201" t="str">
+        <v>0</v>
+      </c>
+      <c r="P201" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q201" t="str">
+        <v>0</v>
+      </c>
+      <c r="R201" t="str">
+        <v>0</v>
+      </c>
+      <c r="S201" t="str">
+        <v>0</v>
+      </c>
+      <c r="T201" t="str">
+        <v>0</v>
+      </c>
+      <c r="U201" t="str">
+        <v>3</v>
+      </c>
+      <c r="V201" t="str">
+        <v>0</v>
+      </c>
+      <c r="W201" t="str">
+        <v>2</v>
+      </c>
+      <c r="X201" t="str">
+        <v>5/17/26</v>
+      </c>
+      <c r="Y201" t="str">
+        <v>8/20/26</v>
+      </c>
+      <c r="Z201" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="AB201" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="AD201" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="AE201" t="str">
+        <v>Skipped: Intended practices disabled (program stage)</v>
+      </c>
+    </row>
+    <row r="202" xml:space="preserve">
+      <c r="A202" t="str">
+        <v>(1259)</v>
+      </c>
+      <c r="B202" t="str">
+        <v>(1) Viet Nga Group, (2) Việt Nga Group - HTX An Hoà</v>
+      </c>
+      <c r="C202" t="str">
+        <v>74117</v>
+      </c>
+      <c r="D202" t="str">
+        <v>984227916</v>
+      </c>
+      <c r="E202" t="str">
+        <v>ĐỖ THỊ ẤM</v>
+      </c>
+      <c r="F202" t="str">
+        <v>HỢP TÁC XÃ NÔNG NGHIỆP AN HÒA</v>
+      </c>
+      <c r="J202" t="str" xml:space="preserve">
+        <v xml:space="preserve">✅ Residue removal // Thu gom rơm rạ_x000d_
+✅ Rate reduction // Giảm lượng phân bón_x000d_
+✅ Reduced planting density // Giảm mật độ trồng_x000d_
+✅ Irrigation Management // Quản lý tưới tiêu</v>
+      </c>
+      <c r="K202" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="L202" t="str">
+        <v>Female // Nữ</v>
+      </c>
+      <c r="M202" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="N202" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O202" t="str">
+        <v>1</v>
+      </c>
+      <c r="P202" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q202" t="str">
+        <v>0</v>
+      </c>
+      <c r="R202" t="str">
+        <v>0</v>
+      </c>
+      <c r="S202" t="str">
+        <v>0</v>
+      </c>
+      <c r="T202" t="str">
+        <v>0</v>
+      </c>
+      <c r="U202" t="str">
+        <v>3</v>
+      </c>
+      <c r="V202" t="str">
+        <v>0</v>
+      </c>
+      <c r="W202" t="str">
+        <v>2</v>
+      </c>
+      <c r="X202" t="str">
+        <v>5/17/26</v>
+      </c>
+      <c r="Y202" t="str">
+        <v>8/20/26</v>
+      </c>
+      <c r="Z202" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="AB202" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="AD202" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="AE202" t="str">
+        <v>Skipped: Intended practices disabled (program stage)</v>
+      </c>
+    </row>
+    <row r="203" xml:space="preserve">
+      <c r="A203" t="str">
+        <v>(1260)</v>
+      </c>
+      <c r="B203" t="str">
+        <v>(1) Viet Nga Group, (2) Việt Nga Group - HTX An Hoà</v>
+      </c>
+      <c r="C203" t="str">
+        <v>74118</v>
+      </c>
+      <c r="D203" t="str">
+        <v>917609986</v>
+      </c>
+      <c r="E203" t="str">
+        <v>NGUYỄN HÙNG SƠN</v>
+      </c>
+      <c r="F203" t="str">
+        <v>HỢP TÁC XÃ NÔNG NGHIỆP AN HÒA</v>
+      </c>
+      <c r="J203" t="str" xml:space="preserve">
+        <v xml:space="preserve">✅ Residue removal // Thu gom rơm rạ_x000d_
+✅ Rate reduction // Giảm lượng phân bón_x000d_
+✅ Reduced planting density // Giảm mật độ trồng_x000d_
+✅ Irrigation Management // Quản lý tưới tiêu</v>
+      </c>
+      <c r="K203" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="L203" t="str">
+        <v>Male // Nam</v>
+      </c>
+      <c r="M203" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="N203" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O203" t="str">
+        <v>0</v>
+      </c>
+      <c r="P203" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q203" t="str">
+        <v>0</v>
+      </c>
+      <c r="R203" t="str">
+        <v>0</v>
+      </c>
+      <c r="S203" t="str">
+        <v>0</v>
+      </c>
+      <c r="T203" t="str">
+        <v>0</v>
+      </c>
+      <c r="U203" t="str">
+        <v>3</v>
+      </c>
+      <c r="V203" t="str">
+        <v>0</v>
+      </c>
+      <c r="W203" t="str">
+        <v>2</v>
+      </c>
+      <c r="X203" t="str">
+        <v>5/17/26</v>
+      </c>
+      <c r="Y203" t="str">
+        <v>8/20/26</v>
+      </c>
+      <c r="Z203" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="AB203" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="AD203" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="AE203" t="str">
+        <v>Skipped: Intended practices disabled (program stage)</v>
+      </c>
+    </row>
+    <row r="204" xml:space="preserve">
+      <c r="A204" t="str">
+        <v>(1261)</v>
+      </c>
+      <c r="B204" t="str">
+        <v>(1) Viet Nga Group, (2) Việt Nga Group - HTX An Hoà</v>
+      </c>
+      <c r="C204" t="str">
+        <v>74119</v>
+      </c>
+      <c r="D204" t="str">
+        <v>977442419</v>
+      </c>
+      <c r="E204" t="str">
+        <v>LÊ VĂN NU</v>
+      </c>
+      <c r="F204" t="str">
+        <v>HỢP TÁC XÃ NÔNG NGHIỆP AN HÒA</v>
+      </c>
+      <c r="J204" t="str" xml:space="preserve">
+        <v xml:space="preserve">✅ Residue removal // Thu gom rơm rạ_x000d_
+✅ Rate reduction // Giảm lượng phân bón_x000d_
+✅ Reduced planting density // Giảm mật độ trồng_x000d_
+✅ Irrigation Management // Quản lý tưới tiêu</v>
+      </c>
+      <c r="K204" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="L204" t="str">
+        <v>Male // Nam</v>
+      </c>
+      <c r="M204" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="N204" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O204" t="str">
+        <v>0</v>
+      </c>
+      <c r="P204" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q204" t="str">
+        <v>0</v>
+      </c>
+      <c r="R204" t="str">
+        <v>0</v>
+      </c>
+      <c r="S204" t="str">
+        <v>0</v>
+      </c>
+      <c r="T204" t="str">
+        <v>0</v>
+      </c>
+      <c r="U204" t="str">
+        <v>3</v>
+      </c>
+      <c r="V204" t="str">
+        <v>0</v>
+      </c>
+      <c r="W204" t="str">
+        <v>2</v>
+      </c>
+      <c r="X204" t="str">
+        <v>5/17/26</v>
+      </c>
+      <c r="Y204" t="str">
+        <v>8/20/26</v>
+      </c>
+      <c r="Z204" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="AB204" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="AD204" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="AE204" t="str">
+        <v>Skipped: Intended practices disabled (program stage)</v>
+      </c>
+    </row>
+    <row r="205" xml:space="preserve">
+      <c r="A205" t="str">
+        <v>(1262)</v>
+      </c>
+      <c r="B205" t="str">
+        <v>(1) Viet Nga Group, (2) Việt Nga Group - HTX An Hoà</v>
+      </c>
+      <c r="C205" t="str">
+        <v>74120</v>
+      </c>
+      <c r="D205" t="str">
+        <v>385188053</v>
+      </c>
+      <c r="E205" t="str">
+        <v>LÊ VĂN DŨNG</v>
+      </c>
+      <c r="F205" t="str">
+        <v>HỢP TÁC XÃ NÔNG NGHIỆP AN HÒA</v>
+      </c>
+      <c r="J205" t="str" xml:space="preserve">
+        <v xml:space="preserve">✅ Residue removal // Thu gom rơm rạ_x000d_
+✅ Rate reduction // Giảm lượng phân bón_x000d_
+✅ Reduced planting density // Giảm mật độ trồng_x000d_
+✅ Irrigation Management // Quản lý tưới tiêu</v>
+      </c>
+      <c r="K205" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="L205" t="str">
+        <v>Male // Nam</v>
+      </c>
+      <c r="M205" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="N205" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O205" t="str">
+        <v>0</v>
+      </c>
+      <c r="P205" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q205" t="str">
+        <v>0</v>
+      </c>
+      <c r="R205" t="str">
+        <v>0</v>
+      </c>
+      <c r="S205" t="str">
+        <v>0</v>
+      </c>
+      <c r="T205" t="str">
+        <v>0</v>
+      </c>
+      <c r="U205" t="str">
+        <v>2</v>
+      </c>
+      <c r="V205" t="str">
+        <v>0</v>
+      </c>
+      <c r="W205" t="str">
+        <v>1</v>
+      </c>
+      <c r="X205" t="str">
+        <v>5/17/26</v>
+      </c>
+      <c r="Y205" t="str">
+        <v>8/20/26</v>
+      </c>
+      <c r="Z205" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="AB205" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="AD205" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="AE205" t="str">
+        <v>Skipped: Intended practices disabled (program stage)</v>
+      </c>
+    </row>
+    <row r="206" xml:space="preserve">
+      <c r="A206" t="str">
+        <v>(1263)</v>
+      </c>
+      <c r="B206" t="str">
+        <v>(1) Viet Nga Group, (2) Việt Nga Group - HTX An Hoà</v>
+      </c>
+      <c r="C206" t="str">
+        <v>74121</v>
+      </c>
+      <c r="D206" t="str">
+        <v>949463815</v>
+      </c>
+      <c r="E206" t="str">
+        <v>PHẠM VĂN BÌNH</v>
+      </c>
+      <c r="F206" t="str">
+        <v>HỢP TÁC XÃ NÔNG NGHIỆP AN HÒA</v>
+      </c>
+      <c r="J206" t="str" xml:space="preserve">
+        <v xml:space="preserve">✅ Residue removal // Thu gom rơm rạ_x000d_
+✅ Rate reduction // Giảm lượng phân bón_x000d_
+✅ Reduced planting density // Giảm mật độ trồng_x000d_
+✅ Irrigation Management // Quản lý tưới tiêu</v>
+      </c>
+      <c r="K206" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="L206" t="str">
+        <v>Male // Nam</v>
+      </c>
+      <c r="M206" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="N206" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O206" t="str">
+        <v>0</v>
+      </c>
+      <c r="P206" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q206" t="str">
+        <v>0</v>
+      </c>
+      <c r="R206" t="str">
+        <v>0</v>
+      </c>
+      <c r="S206" t="str">
+        <v>0</v>
+      </c>
+      <c r="T206" t="str">
+        <v>0</v>
+      </c>
+      <c r="U206" t="str">
+        <v>3</v>
+      </c>
+      <c r="V206" t="str">
+        <v>0</v>
+      </c>
+      <c r="W206" t="str">
+        <v>2</v>
+      </c>
+      <c r="X206" t="str">
+        <v>5/17/26</v>
+      </c>
+      <c r="Y206" t="str">
+        <v>8/20/26</v>
+      </c>
+      <c r="Z206" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="AB206" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="AD206" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="AE206" t="str">
+        <v>Skipped: Intended practices disabled (program stage)</v>
+      </c>
+    </row>
+    <row r="207" xml:space="preserve">
+      <c r="A207" t="str">
+        <v>(1264)</v>
+      </c>
+      <c r="B207" t="str">
+        <v>(1) Viet Nga Group, (2) Việt Nga Group - HTX An Hoà</v>
+      </c>
+      <c r="C207" t="str">
+        <v>74122</v>
+      </c>
+      <c r="D207" t="str">
+        <v>355206824</v>
+      </c>
+      <c r="E207" t="str">
+        <v>ĐẶNG THỊ SANG</v>
+      </c>
+      <c r="F207" t="str">
+        <v>HỢP TÁC XÃ NÔNG NGHIỆP AN HÒA</v>
+      </c>
+      <c r="J207" t="str" xml:space="preserve">
+        <v xml:space="preserve">✅ Residue removal // Thu gom rơm rạ_x000d_
+✅ Rate reduction // Giảm lượng phân bón_x000d_
+✅ Reduced planting density // Giảm mật độ trồng_x000d_
+✅ Irrigation Management // Quản lý tưới tiêu</v>
+      </c>
+      <c r="K207" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="L207" t="str">
+        <v>Female // Nữ</v>
+      </c>
+      <c r="M207" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="N207" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O207" t="str">
+        <v>1</v>
+      </c>
+      <c r="P207" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q207" t="str">
+        <v>0</v>
+      </c>
+      <c r="R207" t="str">
+        <v>0</v>
+      </c>
+      <c r="S207" t="str">
+        <v>0</v>
+      </c>
+      <c r="T207" t="str">
+        <v>0</v>
+      </c>
+      <c r="U207" t="str">
+        <v>2</v>
+      </c>
+      <c r="V207" t="str">
+        <v>0</v>
+      </c>
+      <c r="W207" t="str">
+        <v>1</v>
+      </c>
+      <c r="X207" t="str">
+        <v>5/17/26</v>
+      </c>
+      <c r="Y207" t="str">
+        <v>8/20/26</v>
+      </c>
+      <c r="Z207" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="AB207" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="AD207" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="AE207" t="str">
+        <v>Skipped: Intended practices disabled (program stage)</v>
+      </c>
+    </row>
+    <row r="208" xml:space="preserve">
+      <c r="A208" t="str">
+        <v>(1265)</v>
+      </c>
+      <c r="B208" t="str">
+        <v>(1) Viet Nga Group, (2) Việt Nga Group - HTX An Hoà</v>
+      </c>
+      <c r="C208" t="str">
+        <v>74123</v>
+      </c>
+      <c r="D208" t="str">
+        <v>874848090</v>
+      </c>
+      <c r="E208" t="str">
+        <v>NGUYỄN THỊ TÚ ANH</v>
+      </c>
+      <c r="F208" t="str">
+        <v>HỢP TÁC XÃ NÔNG NGHIỆP AN HÒA</v>
+      </c>
+      <c r="J208" t="str" xml:space="preserve">
+        <v xml:space="preserve">✅ Residue removal // Thu gom rơm rạ_x000d_
+✅ Rate reduction // Giảm lượng phân bón_x000d_
+✅ Reduced planting density // Giảm mật độ trồng_x000d_
+✅ Irrigation Management // Quản lý tưới tiêu</v>
+      </c>
+      <c r="K208" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="L208" t="str">
+        <v>Female // Nữ</v>
+      </c>
+      <c r="M208" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="N208" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O208" t="str">
+        <v>1</v>
+      </c>
+      <c r="P208" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q208" t="str">
+        <v>0</v>
+      </c>
+      <c r="R208" t="str">
+        <v>0</v>
+      </c>
+      <c r="S208" t="str">
+        <v>0</v>
+      </c>
+      <c r="T208" t="str">
+        <v>0</v>
+      </c>
+      <c r="U208" t="str">
+        <v>3</v>
+      </c>
+      <c r="V208" t="str">
+        <v>0</v>
+      </c>
+      <c r="W208" t="str">
+        <v>2</v>
+      </c>
+      <c r="X208" t="str">
+        <v>5/17/26</v>
+      </c>
+      <c r="Y208" t="str">
+        <v>8/20/26</v>
+      </c>
+      <c r="Z208" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="AB208" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="AD208" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="AE208" t="str">
+        <v>Skipped: Intended practices disabled (program stage)</v>
+      </c>
+    </row>
+    <row r="209" xml:space="preserve">
+      <c r="A209" t="str">
+        <v>(1266)</v>
+      </c>
+      <c r="B209" t="str">
+        <v>(1) Viet Nga Group, (2) Việt Nga Group - HTX An Hoà</v>
+      </c>
+      <c r="C209" t="str">
+        <v>74124</v>
+      </c>
+      <c r="D209" t="str">
+        <v>333505481</v>
+      </c>
+      <c r="E209" t="str">
+        <v>NGUYỄN VĂN TRÀ</v>
+      </c>
+      <c r="F209" t="str">
+        <v>HỢP TÁC XÃ NÔNG NGHIỆP AN HÒA</v>
+      </c>
+      <c r="J209" t="str" xml:space="preserve">
+        <v xml:space="preserve">✅ Residue removal // Thu gom rơm rạ_x000d_
+✅ Rate reduction // Giảm lượng phân bón_x000d_
+✅ Reduced planting density // Giảm mật độ trồng_x000d_
+✅ Irrigation Management // Quản lý tưới tiêu</v>
+      </c>
+      <c r="K209" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="L209" t="str">
+        <v>Male // Nam</v>
+      </c>
+      <c r="M209" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="N209" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O209" t="str">
+        <v>0</v>
+      </c>
+      <c r="P209" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q209" t="str">
+        <v>0</v>
+      </c>
+      <c r="R209" t="str">
+        <v>0</v>
+      </c>
+      <c r="S209" t="str">
+        <v>0</v>
+      </c>
+      <c r="T209" t="str">
+        <v>0</v>
+      </c>
+      <c r="U209" t="str">
+        <v>2</v>
+      </c>
+      <c r="V209" t="str">
+        <v>0</v>
+      </c>
+      <c r="W209" t="str">
+        <v>1</v>
+      </c>
+      <c r="X209" t="str">
+        <v>5/17/26</v>
+      </c>
+      <c r="Y209" t="str">
+        <v>8/20/26</v>
+      </c>
+      <c r="Z209" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="AB209" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="AD209" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="AE209" t="str">
+        <v>Skipped: Intended practices disabled (program stage)</v>
+      </c>
+    </row>
+    <row r="210" xml:space="preserve">
+      <c r="A210" t="str">
+        <v>(1267)</v>
+      </c>
+      <c r="B210" t="str">
+        <v>(1) Viet Nga Group, (2) Việt Nga Group - HTX An Hoà</v>
+      </c>
+      <c r="C210" t="str">
+        <v>74125</v>
+      </c>
+      <c r="D210" t="str">
+        <v>387550079</v>
+      </c>
+      <c r="E210" t="str">
+        <v>TRẦN MINH TRÍ</v>
+      </c>
+      <c r="F210" t="str">
+        <v>HỢP TÁC XÃ NÔNG NGHIỆP AN HÒA</v>
+      </c>
+      <c r="J210" t="str" xml:space="preserve">
+        <v xml:space="preserve">✅ Residue removal // Thu gom rơm rạ_x000d_
+✅ Rate reduction // Giảm lượng phân bón_x000d_
+✅ Reduced planting density // Giảm mật độ trồng_x000d_
+✅ Irrigation Management // Quản lý tưới tiêu</v>
+      </c>
+      <c r="K210" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="L210" t="str">
+        <v>Male // Nam</v>
+      </c>
+      <c r="M210" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="N210" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O210" t="str">
+        <v>0</v>
+      </c>
+      <c r="P210" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q210" t="str">
+        <v>0</v>
+      </c>
+      <c r="R210" t="str">
+        <v>0</v>
+      </c>
+      <c r="S210" t="str">
+        <v>0</v>
+      </c>
+      <c r="T210" t="str">
+        <v>0</v>
+      </c>
+      <c r="U210" t="str">
+        <v>3</v>
+      </c>
+      <c r="V210" t="str">
+        <v>0</v>
+      </c>
+      <c r="W210" t="str">
+        <v>2</v>
+      </c>
+      <c r="X210" t="str">
+        <v>5/17/26</v>
+      </c>
+      <c r="Y210" t="str">
+        <v>8/20/26</v>
+      </c>
+      <c r="Z210" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="AB210" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="AD210" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="AE210" t="str">
+        <v>Skipped: Intended practices disabled (program stage)</v>
+      </c>
+    </row>
+    <row r="211" xml:space="preserve">
+      <c r="A211" t="str">
+        <v>(1268)</v>
+      </c>
+      <c r="B211" t="str">
+        <v>(1) Viet Nga Group, (2) Việt Nga Group - HTX An Hoà</v>
+      </c>
+      <c r="C211" t="str">
+        <v>74126</v>
+      </c>
+      <c r="D211" t="str">
+        <v>916433534</v>
+      </c>
+      <c r="E211" t="str">
+        <v>NGUYỄN VĂN MÈO</v>
+      </c>
+      <c r="F211" t="str">
+        <v>HỢP TÁC XÃ NÔNG NGHIỆP AN HÒA</v>
+      </c>
+      <c r="J211" t="str" xml:space="preserve">
+        <v xml:space="preserve">✅ Residue removal // Thu gom rơm rạ_x000d_
+✅ Rate reduction // Giảm lượng phân bón_x000d_
+✅ Reduced planting density // Giảm mật độ trồng_x000d_
+✅ Irrigation Management // Quản lý tưới tiêu</v>
+      </c>
+      <c r="K211" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="L211" t="str">
+        <v>Male // Nam</v>
+      </c>
+      <c r="M211" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="N211" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O211" t="str">
+        <v>0</v>
+      </c>
+      <c r="P211" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q211" t="str">
+        <v>0</v>
+      </c>
+      <c r="R211" t="str">
+        <v>0</v>
+      </c>
+      <c r="S211" t="str">
+        <v>0</v>
+      </c>
+      <c r="T211" t="str">
+        <v>0</v>
+      </c>
+      <c r="U211" t="str">
+        <v>2</v>
+      </c>
+      <c r="V211" t="str">
+        <v>0</v>
+      </c>
+      <c r="W211" t="str">
+        <v>1</v>
+      </c>
+      <c r="X211" t="str">
+        <v>5/17/26</v>
+      </c>
+      <c r="Y211" t="str">
+        <v>8/20/26</v>
+      </c>
+      <c r="Z211" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="AB211" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="AD211" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="AE211" t="str">
+        <v>Skipped: Intended practices disabled (program stage)</v>
+      </c>
+    </row>
+    <row r="212" xml:space="preserve">
+      <c r="A212" t="str">
+        <v>(1269)</v>
+      </c>
+      <c r="B212" t="str">
+        <v>(1) Viet Nga Group, (2) Việt Nga Group - HTX An Hoà</v>
+      </c>
+      <c r="C212" t="str">
+        <v>74127</v>
+      </c>
+      <c r="D212" t="str">
+        <v>366155507</v>
+      </c>
+      <c r="E212" t="str">
+        <v>LÊ VĂN THẠT</v>
+      </c>
+      <c r="F212" t="str">
+        <v>HỢP TÁC XÃ NÔNG NGHIỆP AN HÒA</v>
+      </c>
+      <c r="J212" t="str" xml:space="preserve">
+        <v xml:space="preserve">✅ Residue removal // Thu gom rơm rạ_x000d_
+✅ Rate reduction // Giảm lượng phân bón_x000d_
+✅ Reduced planting density // Giảm mật độ trồng_x000d_
+✅ Irrigation Management // Quản lý tưới tiêu</v>
+      </c>
+      <c r="K212" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="L212" t="str">
+        <v>Male // Nam</v>
+      </c>
+      <c r="M212" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="N212" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O212" t="str">
+        <v>0</v>
+      </c>
+      <c r="P212" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q212" t="str">
+        <v>0</v>
+      </c>
+      <c r="R212" t="str">
+        <v>0</v>
+      </c>
+      <c r="S212" t="str">
+        <v>0</v>
+      </c>
+      <c r="T212" t="str">
+        <v>0</v>
+      </c>
+      <c r="U212" t="str">
+        <v>3</v>
+      </c>
+      <c r="V212" t="str">
+        <v>0</v>
+      </c>
+      <c r="W212" t="str">
+        <v>2</v>
+      </c>
+      <c r="X212" t="str">
+        <v>5/17/26</v>
+      </c>
+      <c r="Y212" t="str">
+        <v>8/20/26</v>
+      </c>
+      <c r="Z212" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="AB212" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="AD212" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="AE212" t="str">
+        <v>Skipped: Intended practices disabled (program stage)</v>
+      </c>
+    </row>
+    <row r="213" xml:space="preserve">
+      <c r="A213" t="str">
+        <v>(1270)</v>
+      </c>
+      <c r="B213" t="str">
+        <v>(1) Viet Nga Group, (2) Việt Nga Group - HTX An Hoà</v>
+      </c>
+      <c r="C213" t="str">
+        <v>74128</v>
+      </c>
+      <c r="D213" t="str">
+        <v>396861101</v>
+      </c>
+      <c r="E213" t="str">
+        <v>NGUYỄN VĂN NGHE</v>
+      </c>
+      <c r="F213" t="str">
+        <v>HỢP TÁC XÃ NÔNG NGHIỆP AN HÒA</v>
+      </c>
+      <c r="J213" t="str" xml:space="preserve">
+        <v xml:space="preserve">✅ Residue removal // Thu gom rơm rạ_x000d_
+✅ Rate reduction // Giảm lượng phân bón_x000d_
+✅ Reduced planting density // Giảm mật độ trồng_x000d_
+✅ Irrigation Management // Quản lý tưới tiêu</v>
+      </c>
+      <c r="K213" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="L213" t="str">
+        <v>Male // Nam</v>
+      </c>
+      <c r="M213" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="N213" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O213" t="str">
+        <v>0</v>
+      </c>
+      <c r="P213" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q213" t="str">
+        <v>0</v>
+      </c>
+      <c r="R213" t="str">
+        <v>0</v>
+      </c>
+      <c r="S213" t="str">
+        <v>0</v>
+      </c>
+      <c r="T213" t="str">
+        <v>0</v>
+      </c>
+      <c r="U213" t="str">
+        <v>2</v>
+      </c>
+      <c r="V213" t="str">
+        <v>0</v>
+      </c>
+      <c r="W213" t="str">
+        <v>1</v>
+      </c>
+      <c r="X213" t="str">
+        <v>5/17/26</v>
+      </c>
+      <c r="Y213" t="str">
+        <v>8/20/26</v>
+      </c>
+      <c r="Z213" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="AB213" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="AD213" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="AE213" t="str">
+        <v>Skipped: Intended practices disabled (program stage)</v>
+      </c>
+    </row>
+    <row r="214" xml:space="preserve">
+      <c r="A214" t="str">
+        <v>(1271)</v>
+      </c>
+      <c r="B214" t="str">
+        <v>(1) Viet Nga Group, (2) Việt Nga Group - HTX An Hoà</v>
+      </c>
+      <c r="C214" t="str">
+        <v>74129</v>
+      </c>
+      <c r="D214" t="str">
+        <v>378777418</v>
+      </c>
+      <c r="E214" t="str">
+        <v>DƯƠNG VĂN PHƯƠNG</v>
+      </c>
+      <c r="F214" t="str">
+        <v>HỢP TÁC XÃ NÔNG NGHIỆP AN HÒA</v>
+      </c>
+      <c r="J214" t="str" xml:space="preserve">
+        <v xml:space="preserve">✅ Residue removal // Thu gom rơm rạ_x000d_
+✅ Rate reduction // Giảm lượng phân bón_x000d_
+✅ Reduced planting density // Giảm mật độ trồng_x000d_
+✅ Irrigation Management // Quản lý tưới tiêu</v>
+      </c>
+      <c r="K214" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="L214" t="str">
+        <v>Male // Nam</v>
+      </c>
+      <c r="M214" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="N214" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O214" t="str">
+        <v>0</v>
+      </c>
+      <c r="P214" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q214" t="str">
+        <v>0</v>
+      </c>
+      <c r="R214" t="str">
+        <v>0</v>
+      </c>
+      <c r="S214" t="str">
+        <v>0</v>
+      </c>
+      <c r="T214" t="str">
+        <v>0</v>
+      </c>
+      <c r="U214" t="str">
+        <v>2</v>
+      </c>
+      <c r="V214" t="str">
+        <v>0</v>
+      </c>
+      <c r="W214" t="str">
+        <v>1</v>
+      </c>
+      <c r="X214" t="str">
+        <v>5/17/26</v>
+      </c>
+      <c r="Y214" t="str">
+        <v>8/20/26</v>
+      </c>
+      <c r="Z214" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="AB214" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="AD214" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="AE214" t="str">
+        <v>Skipped: Intended practices disabled (program stage)</v>
+      </c>
+    </row>
+    <row r="215" xml:space="preserve">
+      <c r="A215" t="str">
+        <v>(1272)</v>
+      </c>
+      <c r="B215" t="str">
+        <v>(1) Viet Nga Group, (2) Việt Nga Group - HTX An Hoà</v>
+      </c>
+      <c r="C215" t="str">
+        <v>74130</v>
+      </c>
+      <c r="D215" t="str">
+        <v>819966006</v>
+      </c>
+      <c r="E215" t="str">
+        <v>NGUYỄN VĂN BI</v>
+      </c>
+      <c r="F215" t="str">
+        <v>HỢP TÁC XÃ NÔNG NGHIỆP AN HÒA</v>
+      </c>
+      <c r="J215" t="str" xml:space="preserve">
+        <v xml:space="preserve">✅ Residue removal // Thu gom rơm rạ_x000d_
+✅ Rate reduction // Giảm lượng phân bón_x000d_
+✅ Reduced planting density // Giảm mật độ trồng_x000d_
+✅ Irrigation Management // Quản lý tưới tiêu</v>
+      </c>
+      <c r="K215" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="L215" t="str">
+        <v>Male // Nam</v>
+      </c>
+      <c r="M215" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="N215" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O215" t="str">
+        <v>0</v>
+      </c>
+      <c r="P215" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q215" t="str">
+        <v>0</v>
+      </c>
+      <c r="R215" t="str">
+        <v>0</v>
+      </c>
+      <c r="S215" t="str">
+        <v>0</v>
+      </c>
+      <c r="T215" t="str">
+        <v>0</v>
+      </c>
+      <c r="U215" t="str">
+        <v>2</v>
+      </c>
+      <c r="V215" t="str">
+        <v>0</v>
+      </c>
+      <c r="W215" t="str">
+        <v>1</v>
+      </c>
+      <c r="X215" t="str">
+        <v>5/17/26</v>
+      </c>
+      <c r="Y215" t="str">
+        <v>8/20/26</v>
+      </c>
+      <c r="Z215" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="AB215" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="AD215" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="AE215" t="str">
+        <v>Skipped: Intended practices disabled (program stage)</v>
+      </c>
+    </row>
+    <row r="216" xml:space="preserve">
+      <c r="A216" t="str">
+        <v>(1273)</v>
+      </c>
+      <c r="B216" t="str">
+        <v>(1) Viet Nga Group, (2) Việt Nga Group - HTX An Hoà</v>
+      </c>
+      <c r="C216" t="str">
+        <v>74131</v>
+      </c>
+      <c r="D216" t="str">
+        <v>795488022</v>
+      </c>
+      <c r="E216" t="str">
+        <v>ĐỖ VĂN NGƯNG</v>
+      </c>
+      <c r="F216" t="str">
+        <v>HỢP TÁC XÃ NÔNG NGHIỆP AN HÒA</v>
+      </c>
+      <c r="J216" t="str" xml:space="preserve">
+        <v xml:space="preserve">✅ Residue removal // Thu gom rơm rạ_x000d_
+✅ Rate reduction // Giảm lượng phân bón_x000d_
+✅ Reduced planting density // Giảm mật độ trồng_x000d_
+✅ Irrigation Management // Quản lý tưới tiêu</v>
+      </c>
+      <c r="K216" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="L216" t="str">
+        <v>Male // Nam</v>
+      </c>
+      <c r="M216" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="N216" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O216" t="str">
+        <v>0</v>
+      </c>
+      <c r="P216" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q216" t="str">
+        <v>0</v>
+      </c>
+      <c r="R216" t="str">
+        <v>0</v>
+      </c>
+      <c r="S216" t="str">
+        <v>0</v>
+      </c>
+      <c r="T216" t="str">
+        <v>0</v>
+      </c>
+      <c r="U216" t="str">
+        <v>2</v>
+      </c>
+      <c r="V216" t="str">
+        <v>0</v>
+      </c>
+      <c r="W216" t="str">
+        <v>1</v>
+      </c>
+      <c r="X216" t="str">
+        <v>5/17/26</v>
+      </c>
+      <c r="Y216" t="str">
+        <v>8/20/26</v>
+      </c>
+      <c r="Z216" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="AB216" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="AD216" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="AE216" t="str">
+        <v>Skipped: Intended practices disabled (program stage)</v>
+      </c>
+    </row>
+    <row r="217" xml:space="preserve">
+      <c r="A217" t="str">
+        <v>(1274)</v>
+      </c>
+      <c r="B217" t="str">
+        <v>(1) Viet Nga Group, (2) Việt Nga Group - HTX An Hoà</v>
+      </c>
+      <c r="C217" t="str">
+        <v>74132</v>
+      </c>
+      <c r="D217" t="str">
+        <v>348671494</v>
+      </c>
+      <c r="E217" t="str">
+        <v>THÁI NGỌC HÙNG BÉ</v>
+      </c>
+      <c r="F217" t="str">
+        <v>HỢP TÁC XÃ NÔNG NGHIỆP AN HÒA</v>
+      </c>
+      <c r="J217" t="str" xml:space="preserve">
+        <v xml:space="preserve">✅ Residue removal // Thu gom rơm rạ_x000d_
+✅ Rate reduction // Giảm lượng phân bón_x000d_
+✅ Reduced planting density // Giảm mật độ trồng_x000d_
+✅ Irrigation Management // Quản lý tưới tiêu</v>
+      </c>
+      <c r="K217" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="L217" t="str">
+        <v>Male // Nam</v>
+      </c>
+      <c r="M217" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="N217" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O217" t="str">
+        <v>0</v>
+      </c>
+      <c r="P217" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q217" t="str">
+        <v>0</v>
+      </c>
+      <c r="R217" t="str">
+        <v>0</v>
+      </c>
+      <c r="S217" t="str">
+        <v>0</v>
+      </c>
+      <c r="T217" t="str">
+        <v>0</v>
+      </c>
+      <c r="U217" t="str">
+        <v>2</v>
+      </c>
+      <c r="V217" t="str">
+        <v>0</v>
+      </c>
+      <c r="W217" t="str">
+        <v>1</v>
+      </c>
+      <c r="X217" t="str">
+        <v>5/17/26</v>
+      </c>
+      <c r="Y217" t="str">
+        <v>8/20/26</v>
+      </c>
+      <c r="Z217" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="AB217" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="AD217" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="AE217" t="str">
+        <v>Skipped: Intended practices disabled (program stage)</v>
+      </c>
+    </row>
+    <row r="218" xml:space="preserve">
+      <c r="A218" t="str">
+        <v>(1275)</v>
+      </c>
+      <c r="B218" t="str">
+        <v>(1) Viet Nga Group, (2) Việt Nga Group - HTX An Hoà</v>
+      </c>
+      <c r="C218" t="str">
+        <v>74133</v>
+      </c>
+      <c r="D218" t="str">
+        <v>774098618</v>
+      </c>
+      <c r="E218" t="str">
+        <v>NGUYỄN THANH LONG</v>
+      </c>
+      <c r="F218" t="str">
+        <v>HỢP TÁC XÃ NÔNG NGHIỆP AN HÒA</v>
+      </c>
+      <c r="J218" t="str" xml:space="preserve">
+        <v xml:space="preserve">✅ Residue removal // Thu gom rơm rạ_x000d_
+✅ Rate reduction // Giảm lượng phân bón_x000d_
+✅ Reduced planting density // Giảm mật độ trồng_x000d_
+✅ Irrigation Management // Quản lý tưới tiêu</v>
+      </c>
+      <c r="K218" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="L218" t="str">
+        <v>Male // Nam</v>
+      </c>
+      <c r="M218" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="N218" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O218" t="str">
+        <v>0</v>
+      </c>
+      <c r="P218" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q218" t="str">
+        <v>0</v>
+      </c>
+      <c r="R218" t="str">
+        <v>0</v>
+      </c>
+      <c r="S218" t="str">
+        <v>0</v>
+      </c>
+      <c r="T218" t="str">
+        <v>0</v>
+      </c>
+      <c r="U218" t="str">
+        <v>2</v>
+      </c>
+      <c r="V218" t="str">
+        <v>0</v>
+      </c>
+      <c r="W218" t="str">
+        <v>1</v>
+      </c>
+      <c r="X218" t="str">
+        <v>5/17/26</v>
+      </c>
+      <c r="Y218" t="str">
+        <v>8/20/26</v>
+      </c>
+      <c r="Z218" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="AB218" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="AD218" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="AE218" t="str">
+        <v>Skipped: Intended practices disabled (program stage)</v>
+      </c>
+    </row>
+    <row r="219" xml:space="preserve">
+      <c r="A219" t="str">
+        <v>(1276)</v>
+      </c>
+      <c r="B219" t="str">
+        <v>(1) Viet Nga Group, (2) Việt Nga Group - HTX An Hoà</v>
+      </c>
+      <c r="C219" t="str">
+        <v>74134</v>
+      </c>
+      <c r="D219" t="str">
+        <v>377522513</v>
+      </c>
+      <c r="E219" t="str">
+        <v>NGUYỄN VĂN LÀNH</v>
+      </c>
+      <c r="F219" t="str">
+        <v>HỢP TÁC XÃ NÔNG NGHIỆP AN HÒA</v>
+      </c>
+      <c r="J219" t="str" xml:space="preserve">
+        <v xml:space="preserve">✅ Residue removal // Thu gom rơm rạ_x000d_
+✅ Rate reduction // Giảm lượng phân bón_x000d_
+✅ Reduced planting density // Giảm mật độ trồng_x000d_
+✅ Irrigation Management // Quản lý tưới tiêu</v>
+      </c>
+      <c r="K219" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="L219" t="str">
+        <v>Male // Nam</v>
+      </c>
+      <c r="M219" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="N219" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O219" t="str">
+        <v>0</v>
+      </c>
+      <c r="P219" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q219" t="str">
+        <v>0</v>
+      </c>
+      <c r="R219" t="str">
+        <v>0</v>
+      </c>
+      <c r="S219" t="str">
+        <v>0</v>
+      </c>
+      <c r="T219" t="str">
+        <v>0</v>
+      </c>
+      <c r="U219" t="str">
+        <v>3</v>
+      </c>
+      <c r="V219" t="str">
+        <v>0</v>
+      </c>
+      <c r="W219" t="str">
+        <v>2</v>
+      </c>
+      <c r="X219" t="str">
+        <v>5/17/26</v>
+      </c>
+      <c r="Y219" t="str">
+        <v>8/20/26</v>
+      </c>
+      <c r="Z219" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="AB219" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="AD219" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="AE219" t="str">
+        <v>Skipped: Intended practices disabled (program stage)</v>
+      </c>
+    </row>
+    <row r="220" xml:space="preserve">
+      <c r="A220" t="str">
+        <v>(1277)</v>
+      </c>
+      <c r="B220" t="str">
+        <v>(1) Viet Nga Group, (2) Việt Nga Group - HTX An Hoà</v>
+      </c>
+      <c r="C220" t="str">
+        <v>74135</v>
+      </c>
+      <c r="D220" t="str">
+        <v>372968599</v>
+      </c>
+      <c r="E220" t="str">
+        <v>LÊ VĂN MÊN</v>
+      </c>
+      <c r="F220" t="str">
+        <v>HỢP TÁC XÃ NÔNG NGHIỆP AN HÒA</v>
+      </c>
+      <c r="J220" t="str" xml:space="preserve">
+        <v xml:space="preserve">✅ Residue removal // Thu gom rơm rạ_x000d_
+✅ Rate reduction // Giảm lượng phân bón_x000d_
+✅ Reduced planting density // Giảm mật độ trồng_x000d_
+✅ Irrigation Management // Quản lý tưới tiêu</v>
+      </c>
+      <c r="K220" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="L220" t="str">
+        <v>Male // Nam</v>
+      </c>
+      <c r="M220" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="N220" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O220" t="str">
+        <v>0</v>
+      </c>
+      <c r="P220" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q220" t="str">
+        <v>0</v>
+      </c>
+      <c r="R220" t="str">
+        <v>0</v>
+      </c>
+      <c r="S220" t="str">
+        <v>0</v>
+      </c>
+      <c r="T220" t="str">
+        <v>0</v>
+      </c>
+      <c r="U220" t="str">
+        <v>3</v>
+      </c>
+      <c r="V220" t="str">
+        <v>0</v>
+      </c>
+      <c r="W220" t="str">
+        <v>2</v>
+      </c>
+      <c r="X220" t="str">
+        <v>5/17/26</v>
+      </c>
+      <c r="Y220" t="str">
+        <v>8/20/26</v>
+      </c>
+      <c r="Z220" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="AB220" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="AD220" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="AE220" t="str">
+        <v>Skipped: Intended practices disabled (program stage)</v>
+      </c>
+    </row>
+    <row r="221" xml:space="preserve">
+      <c r="A221" t="str">
+        <v>(1278)</v>
+      </c>
+      <c r="B221" t="str">
+        <v>(1) Viet Nga Group, (2) Việt Nga Group - HTX An Hoà</v>
+      </c>
+      <c r="C221" t="str">
+        <v>74136</v>
+      </c>
+      <c r="D221" t="str">
+        <v>782815288</v>
+      </c>
+      <c r="E221" t="str">
+        <v>ĐỖ THỊ DẸN</v>
+      </c>
+      <c r="F221" t="str">
+        <v>HỢP TÁC XÃ NÔNG NGHIỆP AN HÒA</v>
+      </c>
+      <c r="J221" t="str" xml:space="preserve">
+        <v xml:space="preserve">✅ Residue removal // Thu gom rơm rạ_x000d_
+✅ Rate reduction // Giảm lượng phân bón_x000d_
+✅ Reduced planting density // Giảm mật độ trồng_x000d_
+✅ Irrigation Management // Quản lý tưới tiêu</v>
+      </c>
+      <c r="K221" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="L221" t="str">
+        <v>Female // Nữ</v>
+      </c>
+      <c r="M221" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="N221" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O221" t="str">
+        <v>1</v>
+      </c>
+      <c r="P221" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q221" t="str">
+        <v>0</v>
+      </c>
+      <c r="R221" t="str">
+        <v>0</v>
+      </c>
+      <c r="S221" t="str">
+        <v>0</v>
+      </c>
+      <c r="T221" t="str">
+        <v>0</v>
+      </c>
+      <c r="U221" t="str">
+        <v>2</v>
+      </c>
+      <c r="V221" t="str">
+        <v>0</v>
+      </c>
+      <c r="W221" t="str">
+        <v>1</v>
+      </c>
+      <c r="X221" t="str">
+        <v>5/17/26</v>
+      </c>
+      <c r="Y221" t="str">
+        <v>8/20/26</v>
+      </c>
+      <c r="Z221" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="AB221" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="AD221" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="AE221" t="str">
+        <v>Skipped: Intended practices disabled (program stage)</v>
+      </c>
+    </row>
+    <row r="222" xml:space="preserve">
+      <c r="A222" t="str">
+        <v>(1279)</v>
+      </c>
+      <c r="B222" t="str">
+        <v>(1) Viet Nga Group, (2) Việt Nga Group - HTX An Hoà</v>
+      </c>
+      <c r="C222" t="str">
+        <v>74137</v>
+      </c>
+      <c r="D222" t="str">
+        <v>832804033</v>
+      </c>
+      <c r="E222" t="str">
+        <v>ĐỖ VĂN THUM</v>
+      </c>
+      <c r="F222" t="str">
+        <v>HỢP TÁC XÃ NÔNG NGHIỆP AN HÒA</v>
+      </c>
+      <c r="J222" t="str" xml:space="preserve">
+        <v xml:space="preserve">✅ Residue removal // Thu gom rơm rạ_x000d_
+✅ Rate reduction // Giảm lượng phân bón_x000d_
+✅ Reduced planting density // Giảm mật độ trồng_x000d_
+✅ Irrigation Management // Quản lý tưới tiêu</v>
+      </c>
+      <c r="K222" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="L222" t="str">
+        <v>Male // Nam</v>
+      </c>
+      <c r="M222" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="N222" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O222" t="str">
+        <v>0</v>
+      </c>
+      <c r="P222" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q222" t="str">
+        <v>0</v>
+      </c>
+      <c r="R222" t="str">
+        <v>0</v>
+      </c>
+      <c r="S222" t="str">
+        <v>0</v>
+      </c>
+      <c r="T222" t="str">
+        <v>0</v>
+      </c>
+      <c r="U222" t="str">
+        <v>2</v>
+      </c>
+      <c r="V222" t="str">
+        <v>0</v>
+      </c>
+      <c r="W222" t="str">
+        <v>1</v>
+      </c>
+      <c r="X222" t="str">
+        <v>5/17/26</v>
+      </c>
+      <c r="Y222" t="str">
+        <v>8/20/26</v>
+      </c>
+      <c r="Z222" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="AB222" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="AD222" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="AE222" t="str">
+        <v>Skipped: Intended practices disabled (program stage)</v>
+      </c>
+    </row>
+    <row r="223" xml:space="preserve">
+      <c r="A223" t="str">
+        <v>(1280)</v>
+      </c>
+      <c r="B223" t="str">
+        <v>(1) Viet Nga Group, (2) Việt Nga Group - HTX An Hoà</v>
+      </c>
+      <c r="C223" t="str">
+        <v>74138</v>
+      </c>
+      <c r="D223" t="str">
+        <v>987650747</v>
+      </c>
+      <c r="E223" t="str">
+        <v>NGUYỄN VĂN TÀU</v>
+      </c>
+      <c r="F223" t="str">
+        <v>HỢP TÁC XÃ NÔNG NGHIỆP AN HÒA</v>
+      </c>
+      <c r="J223" t="str" xml:space="preserve">
+        <v xml:space="preserve">✅ Residue removal // Thu gom rơm rạ_x000d_
+✅ Rate reduction // Giảm lượng phân bón_x000d_
+✅ Reduced planting density // Giảm mật độ trồng_x000d_
+✅ Irrigation Management // Quản lý tưới tiêu</v>
+      </c>
+      <c r="K223" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="L223" t="str">
+        <v>Male // Nam</v>
+      </c>
+      <c r="M223" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="N223" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O223" t="str">
+        <v>0</v>
+      </c>
+      <c r="P223" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q223" t="str">
+        <v>0</v>
+      </c>
+      <c r="R223" t="str">
+        <v>0</v>
+      </c>
+      <c r="S223" t="str">
+        <v>0</v>
+      </c>
+      <c r="T223" t="str">
+        <v>0</v>
+      </c>
+      <c r="U223" t="str">
+        <v>2</v>
+      </c>
+      <c r="V223" t="str">
+        <v>0</v>
+      </c>
+      <c r="W223" t="str">
+        <v>1</v>
+      </c>
+      <c r="X223" t="str">
+        <v>5/17/26</v>
+      </c>
+      <c r="Y223" t="str">
+        <v>8/20/26</v>
+      </c>
+      <c r="Z223" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="AB223" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="AD223" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="AE223" t="str">
+        <v>Skipped: Intended practices disabled (program stage)</v>
+      </c>
+    </row>
+    <row r="224" xml:space="preserve">
+      <c r="A224" t="str">
+        <v>(1260)</v>
+      </c>
+      <c r="B224" t="str">
+        <v>(1) Viet Nga Group, (2) Việt Nga Group - HTX An Hoà</v>
+      </c>
+      <c r="C224" t="str">
+        <v>74118</v>
+      </c>
+      <c r="D224" t="str">
+        <v>917609986</v>
+      </c>
+      <c r="E224" t="str">
+        <v>NGUYỄN HÙNG SƠN</v>
+      </c>
+      <c r="F224" t="str">
+        <v>HỢP TÁC XÃ NÔNG NGHIỆP AN HÒA</v>
+      </c>
+      <c r="J224" t="str" xml:space="preserve">
+        <v xml:space="preserve">✅ Residue removal // Thu gom rơm rạ_x000d_
+✅ Rate reduction // Giảm lượng phân bón_x000d_
+✅ Reduced planting density // Giảm mật độ trồng_x000d_
+✅ Irrigation Management // Quản lý tưới tiêu</v>
+      </c>
+      <c r="K224" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="L224" t="str">
+        <v>Male // Nam</v>
+      </c>
+      <c r="M224" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="N224" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O224" t="str">
+        <v>0</v>
+      </c>
+      <c r="P224" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q224" t="str">
+        <v>0</v>
+      </c>
+      <c r="R224" t="str">
+        <v>0</v>
+      </c>
+      <c r="S224" t="str">
+        <v>0</v>
+      </c>
+      <c r="T224" t="str">
+        <v>0</v>
+      </c>
+      <c r="U224" t="str">
+        <v>3</v>
+      </c>
+      <c r="V224" t="str">
+        <v>0</v>
+      </c>
+      <c r="W224" t="str">
+        <v>2</v>
+      </c>
+      <c r="X224" t="str">
+        <v>5/17/26</v>
+      </c>
+      <c r="Y224" t="str">
+        <v>8/20/26</v>
+      </c>
+      <c r="Z224" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="AB224" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="AD224" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="AE224" t="str">
+        <v>Skipped: Intended practices disabled (program stage)</v>
+      </c>
+    </row>
+    <row r="225" xml:space="preserve">
+      <c r="A225" t="str">
+        <v>(1261)</v>
+      </c>
+      <c r="B225" t="str">
+        <v>(1) Viet Nga Group, (2) Việt Nga Group - HTX An Hoà</v>
+      </c>
+      <c r="C225" t="str">
+        <v>74119</v>
+      </c>
+      <c r="D225" t="str">
+        <v>977442419</v>
+      </c>
+      <c r="E225" t="str">
+        <v>LÊ VĂN NU</v>
+      </c>
+      <c r="F225" t="str">
+        <v>HỢP TÁC XÃ NÔNG NGHIỆP AN HÒA</v>
+      </c>
+      <c r="J225" t="str" xml:space="preserve">
+        <v xml:space="preserve">✅ Residue removal // Thu gom rơm rạ_x000d_
+✅ Rate reduction // Giảm lượng phân bón_x000d_
+✅ Reduced planting density // Giảm mật độ trồng_x000d_
+✅ Irrigation Management // Quản lý tưới tiêu</v>
+      </c>
+      <c r="K225" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="L225" t="str">
+        <v>Male // Nam</v>
+      </c>
+      <c r="M225" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="N225" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O225" t="str">
+        <v>0</v>
+      </c>
+      <c r="P225" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q225" t="str">
+        <v>0</v>
+      </c>
+      <c r="R225" t="str">
+        <v>0</v>
+      </c>
+      <c r="S225" t="str">
+        <v>0</v>
+      </c>
+      <c r="T225" t="str">
+        <v>0</v>
+      </c>
+      <c r="U225" t="str">
+        <v>3</v>
+      </c>
+      <c r="V225" t="str">
+        <v>0</v>
+      </c>
+      <c r="W225" t="str">
+        <v>2</v>
+      </c>
+      <c r="X225" t="str">
+        <v>5/17/26</v>
+      </c>
+      <c r="Y225" t="str">
+        <v>8/20/26</v>
+      </c>
+      <c r="Z225" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="AB225" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="AD225" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="AE225" t="str">
+        <v>Skipped: Intended practices disabled (program stage)</v>
+      </c>
+    </row>
+    <row r="226" xml:space="preserve">
+      <c r="A226" t="str">
+        <v>(1262)</v>
+      </c>
+      <c r="B226" t="str">
+        <v>(1) Viet Nga Group, (2) Việt Nga Group - HTX An Hoà</v>
+      </c>
+      <c r="C226" t="str">
+        <v>74120</v>
+      </c>
+      <c r="D226" t="str">
+        <v>385188053</v>
+      </c>
+      <c r="E226" t="str">
+        <v>LÊ VĂN DŨNG</v>
+      </c>
+      <c r="F226" t="str">
+        <v>HỢP TÁC XÃ NÔNG NGHIỆP AN HÒA</v>
+      </c>
+      <c r="J226" t="str" xml:space="preserve">
+        <v xml:space="preserve">✅ Residue removal // Thu gom rơm rạ_x000d_
+✅ Rate reduction // Giảm lượng phân bón_x000d_
+✅ Reduced planting density // Giảm mật độ trồng_x000d_
+✅ Irrigation Management // Quản lý tưới tiêu</v>
+      </c>
+      <c r="K226" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="L226" t="str">
+        <v>Male // Nam</v>
+      </c>
+      <c r="M226" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="N226" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O226" t="str">
+        <v>0</v>
+      </c>
+      <c r="P226" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q226" t="str">
+        <v>0</v>
+      </c>
+      <c r="R226" t="str">
+        <v>0</v>
+      </c>
+      <c r="S226" t="str">
+        <v>0</v>
+      </c>
+      <c r="T226" t="str">
+        <v>0</v>
+      </c>
+      <c r="U226" t="str">
+        <v>2</v>
+      </c>
+      <c r="V226" t="str">
+        <v>0</v>
+      </c>
+      <c r="W226" t="str">
+        <v>1</v>
+      </c>
+      <c r="X226" t="str">
+        <v>5/17/26</v>
+      </c>
+      <c r="Y226" t="str">
+        <v>8/20/26</v>
+      </c>
+      <c r="Z226" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="AB226" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="AD226" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="AE226" t="str">
+        <v>Skipped: Intended practices disabled (program stage)</v>
+      </c>
+    </row>
+    <row r="227" xml:space="preserve">
+      <c r="A227" t="str">
+        <v>(1263)</v>
+      </c>
+      <c r="B227" t="str">
+        <v>(1) Viet Nga Group, (2) Việt Nga Group - HTX An Hoà</v>
+      </c>
+      <c r="C227" t="str">
+        <v>74121</v>
+      </c>
+      <c r="D227" t="str">
+        <v>949463815</v>
+      </c>
+      <c r="E227" t="str">
+        <v>PHẠM VĂN BÌNH</v>
+      </c>
+      <c r="F227" t="str">
+        <v>HỢP TÁC XÃ NÔNG NGHIỆP AN HÒA</v>
+      </c>
+      <c r="J227" t="str" xml:space="preserve">
+        <v xml:space="preserve">✅ Residue removal // Thu gom rơm rạ_x000d_
+✅ Rate reduction // Giảm lượng phân bón_x000d_
+✅ Reduced planting density // Giảm mật độ trồng_x000d_
+✅ Irrigation Management // Quản lý tưới tiêu</v>
+      </c>
+      <c r="K227" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="L227" t="str">
+        <v>Male // Nam</v>
+      </c>
+      <c r="M227" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="N227" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O227" t="str">
+        <v>0</v>
+      </c>
+      <c r="P227" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q227" t="str">
+        <v>0</v>
+      </c>
+      <c r="R227" t="str">
+        <v>0</v>
+      </c>
+      <c r="S227" t="str">
+        <v>0</v>
+      </c>
+      <c r="T227" t="str">
+        <v>0</v>
+      </c>
+      <c r="U227" t="str">
+        <v>3</v>
+      </c>
+      <c r="V227" t="str">
+        <v>0</v>
+      </c>
+      <c r="W227" t="str">
+        <v>2</v>
+      </c>
+      <c r="X227" t="str">
+        <v>5/17/26</v>
+      </c>
+      <c r="Y227" t="str">
+        <v>8/20/26</v>
+      </c>
+      <c r="Z227" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="AB227" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="AD227" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="AE227" t="str">
+        <v>Skipped: Intended practices disabled (program stage)</v>
+      </c>
+    </row>
+    <row r="228" xml:space="preserve">
+      <c r="A228" t="str">
+        <v>(1264)</v>
+      </c>
+      <c r="B228" t="str">
+        <v>(1) Viet Nga Group, (2) Việt Nga Group - HTX An Hoà</v>
+      </c>
+      <c r="C228" t="str">
+        <v>74122</v>
+      </c>
+      <c r="D228" t="str">
+        <v>355206824</v>
+      </c>
+      <c r="E228" t="str">
+        <v>ĐẶNG THỊ SANG</v>
+      </c>
+      <c r="F228" t="str">
+        <v>HỢP TÁC XÃ NÔNG NGHIỆP AN HÒA</v>
+      </c>
+      <c r="J228" t="str" xml:space="preserve">
+        <v xml:space="preserve">✅ Residue removal // Thu gom rơm rạ_x000d_
+✅ Rate reduction // Giảm lượng phân bón_x000d_
+✅ Reduced planting density // Giảm mật độ trồng_x000d_
+✅ Irrigation Management // Quản lý tưới tiêu</v>
+      </c>
+      <c r="K228" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="L228" t="str">
+        <v>Female // Nữ</v>
+      </c>
+      <c r="M228" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="N228" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O228" t="str">
+        <v>1</v>
+      </c>
+      <c r="P228" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q228" t="str">
+        <v>0</v>
+      </c>
+      <c r="R228" t="str">
+        <v>0</v>
+      </c>
+      <c r="S228" t="str">
+        <v>0</v>
+      </c>
+      <c r="T228" t="str">
+        <v>0</v>
+      </c>
+      <c r="U228" t="str">
+        <v>2</v>
+      </c>
+      <c r="V228" t="str">
+        <v>0</v>
+      </c>
+      <c r="W228" t="str">
+        <v>1</v>
+      </c>
+      <c r="X228" t="str">
+        <v>5/17/26</v>
+      </c>
+      <c r="Y228" t="str">
+        <v>8/20/26</v>
+      </c>
+      <c r="Z228" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="AB228" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="AD228" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="AE228" t="str">
+        <v>Skipped: Intended practices disabled (program stage)</v>
+      </c>
+    </row>
+    <row r="229" xml:space="preserve">
+      <c r="A229" t="str">
+        <v>(1265)</v>
+      </c>
+      <c r="B229" t="str">
+        <v>(1) Viet Nga Group, (2) Việt Nga Group - HTX An Hoà</v>
+      </c>
+      <c r="C229" t="str">
+        <v>74123</v>
+      </c>
+      <c r="D229" t="str">
+        <v>874848090</v>
+      </c>
+      <c r="E229" t="str">
+        <v>NGUYỄN THỊ TÚ ANH</v>
+      </c>
+      <c r="F229" t="str">
+        <v>HỢP TÁC XÃ NÔNG NGHIỆP AN HÒA</v>
+      </c>
+      <c r="J229" t="str" xml:space="preserve">
+        <v xml:space="preserve">✅ Residue removal // Thu gom rơm rạ_x000d_
+✅ Rate reduction // Giảm lượng phân bón_x000d_
+✅ Reduced planting density // Giảm mật độ trồng_x000d_
+✅ Irrigation Management // Quản lý tưới tiêu</v>
+      </c>
+      <c r="K229" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="L229" t="str">
+        <v>Female // Nữ</v>
+      </c>
+      <c r="M229" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="N229" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O229" t="str">
+        <v>1</v>
+      </c>
+      <c r="P229" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q229" t="str">
+        <v>0</v>
+      </c>
+      <c r="R229" t="str">
+        <v>0</v>
+      </c>
+      <c r="S229" t="str">
+        <v>0</v>
+      </c>
+      <c r="T229" t="str">
+        <v>0</v>
+      </c>
+      <c r="U229" t="str">
+        <v>3</v>
+      </c>
+      <c r="V229" t="str">
+        <v>0</v>
+      </c>
+      <c r="W229" t="str">
+        <v>2</v>
+      </c>
+      <c r="X229" t="str">
+        <v>5/17/26</v>
+      </c>
+      <c r="Y229" t="str">
+        <v>8/20/26</v>
+      </c>
+      <c r="Z229" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="AB229" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="AD229" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="AE229" t="str">
+        <v>Skipped: Intended practices disabled (program stage)</v>
+      </c>
+    </row>
+    <row r="230" xml:space="preserve">
+      <c r="A230" t="str">
+        <v>(1266)</v>
+      </c>
+      <c r="B230" t="str">
+        <v>(1) Viet Nga Group, (2) Việt Nga Group - HTX An Hoà</v>
+      </c>
+      <c r="C230" t="str">
+        <v>74124</v>
+      </c>
+      <c r="D230" t="str">
+        <v>333505481</v>
+      </c>
+      <c r="E230" t="str">
+        <v>NGUYỄN VĂN TRÀ</v>
+      </c>
+      <c r="F230" t="str">
+        <v>HỢP TÁC XÃ NÔNG NGHIỆP AN HÒA</v>
+      </c>
+      <c r="J230" t="str" xml:space="preserve">
+        <v xml:space="preserve">✅ Residue removal // Thu gom rơm rạ_x000d_
+✅ Rate reduction // Giảm lượng phân bón_x000d_
+✅ Reduced planting density // Giảm mật độ trồng_x000d_
+✅ Irrigation Management // Quản lý tưới tiêu</v>
+      </c>
+      <c r="K230" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="L230" t="str">
+        <v>Male // Nam</v>
+      </c>
+      <c r="M230" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="N230" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O230" t="str">
+        <v>0</v>
+      </c>
+      <c r="P230" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q230" t="str">
+        <v>0</v>
+      </c>
+      <c r="R230" t="str">
+        <v>0</v>
+      </c>
+      <c r="S230" t="str">
+        <v>0</v>
+      </c>
+      <c r="T230" t="str">
+        <v>0</v>
+      </c>
+      <c r="U230" t="str">
+        <v>2</v>
+      </c>
+      <c r="V230" t="str">
+        <v>0</v>
+      </c>
+      <c r="W230" t="str">
+        <v>1</v>
+      </c>
+      <c r="X230" t="str">
+        <v>5/17/26</v>
+      </c>
+      <c r="Y230" t="str">
+        <v>8/20/26</v>
+      </c>
+      <c r="Z230" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="AB230" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="AD230" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="AE230" t="str">
+        <v>Skipped: Intended practices disabled (program stage)</v>
+      </c>
+    </row>
+    <row r="231" xml:space="preserve">
+      <c r="A231" t="str">
+        <v>(1267)</v>
+      </c>
+      <c r="B231" t="str">
+        <v>(1) Viet Nga Group, (2) Việt Nga Group - HTX An Hoà</v>
+      </c>
+      <c r="C231" t="str">
+        <v>74125</v>
+      </c>
+      <c r="D231" t="str">
+        <v>387550079</v>
+      </c>
+      <c r="E231" t="str">
+        <v>TRẦN MINH TRÍ</v>
+      </c>
+      <c r="F231" t="str">
+        <v>HỢP TÁC XÃ NÔNG NGHIỆP AN HÒA</v>
+      </c>
+      <c r="J231" t="str" xml:space="preserve">
+        <v xml:space="preserve">✅ Residue removal // Thu gom rơm rạ_x000d_
+✅ Rate reduction // Giảm lượng phân bón_x000d_
+✅ Reduced planting density // Giảm mật độ trồng_x000d_
+✅ Irrigation Management // Quản lý tưới tiêu</v>
+      </c>
+      <c r="K231" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="L231" t="str">
+        <v>Male // Nam</v>
+      </c>
+      <c r="M231" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="N231" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O231" t="str">
+        <v>0</v>
+      </c>
+      <c r="P231" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q231" t="str">
+        <v>0</v>
+      </c>
+      <c r="R231" t="str">
+        <v>0</v>
+      </c>
+      <c r="S231" t="str">
+        <v>0</v>
+      </c>
+      <c r="T231" t="str">
+        <v>0</v>
+      </c>
+      <c r="U231" t="str">
+        <v>3</v>
+      </c>
+      <c r="V231" t="str">
+        <v>0</v>
+      </c>
+      <c r="W231" t="str">
+        <v>2</v>
+      </c>
+      <c r="X231" t="str">
+        <v>5/17/26</v>
+      </c>
+      <c r="Y231" t="str">
+        <v>8/20/26</v>
+      </c>
+      <c r="Z231" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="AB231" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="AD231" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="AE231" t="str">
+        <v>Skipped: Intended practices disabled (program stage)</v>
+      </c>
+    </row>
+    <row r="232" xml:space="preserve">
+      <c r="A232" t="str">
+        <v>(1268)</v>
+      </c>
+      <c r="B232" t="str">
+        <v>(1) Viet Nga Group, (2) Việt Nga Group - HTX An Hoà</v>
+      </c>
+      <c r="C232" t="str">
+        <v>74126</v>
+      </c>
+      <c r="D232" t="str">
+        <v>916433534</v>
+      </c>
+      <c r="E232" t="str">
+        <v>NGUYỄN VĂN MÈO</v>
+      </c>
+      <c r="F232" t="str">
+        <v>HỢP TÁC XÃ NÔNG NGHIỆP AN HÒA</v>
+      </c>
+      <c r="J232" t="str" xml:space="preserve">
+        <v xml:space="preserve">✅ Residue removal // Thu gom rơm rạ_x000d_
+✅ Rate reduction // Giảm lượng phân bón_x000d_
+✅ Reduced planting density // Giảm mật độ trồng_x000d_
+✅ Irrigation Management // Quản lý tưới tiêu</v>
+      </c>
+      <c r="K232" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="L232" t="str">
+        <v>Male // Nam</v>
+      </c>
+      <c r="M232" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="N232" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O232" t="str">
+        <v>0</v>
+      </c>
+      <c r="P232" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q232" t="str">
+        <v>0</v>
+      </c>
+      <c r="R232" t="str">
+        <v>0</v>
+      </c>
+      <c r="S232" t="str">
+        <v>0</v>
+      </c>
+      <c r="T232" t="str">
+        <v>0</v>
+      </c>
+      <c r="U232" t="str">
+        <v>2</v>
+      </c>
+      <c r="V232" t="str">
+        <v>0</v>
+      </c>
+      <c r="W232" t="str">
+        <v>1</v>
+      </c>
+      <c r="X232" t="str">
+        <v>5/17/26</v>
+      </c>
+      <c r="Y232" t="str">
+        <v>8/20/26</v>
+      </c>
+      <c r="Z232" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="AB232" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="AD232" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="AE232" t="str">
+        <v>Skipped: Intended practices disabled (program stage)</v>
+      </c>
+    </row>
+    <row r="233" xml:space="preserve">
+      <c r="A233" t="str">
+        <v>(1269)</v>
+      </c>
+      <c r="B233" t="str">
+        <v>(1) Viet Nga Group, (2) Việt Nga Group - HTX An Hoà</v>
+      </c>
+      <c r="C233" t="str">
+        <v>74127</v>
+      </c>
+      <c r="D233" t="str">
+        <v>366155507</v>
+      </c>
+      <c r="E233" t="str">
+        <v>LÊ VĂN THẠT</v>
+      </c>
+      <c r="F233" t="str">
+        <v>HỢP TÁC XÃ NÔNG NGHIỆP AN HÒA</v>
+      </c>
+      <c r="J233" t="str" xml:space="preserve">
+        <v xml:space="preserve">✅ Residue removal // Thu gom rơm rạ_x000d_
+✅ Rate reduction // Giảm lượng phân bón_x000d_
+✅ Reduced planting density // Giảm mật độ trồng_x000d_
+✅ Irrigation Management // Quản lý tưới tiêu</v>
+      </c>
+      <c r="K233" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="L233" t="str">
+        <v>Male // Nam</v>
+      </c>
+      <c r="M233" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="N233" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O233" t="str">
+        <v>0</v>
+      </c>
+      <c r="P233" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q233" t="str">
+        <v>0</v>
+      </c>
+      <c r="R233" t="str">
+        <v>0</v>
+      </c>
+      <c r="S233" t="str">
+        <v>0</v>
+      </c>
+      <c r="T233" t="str">
+        <v>0</v>
+      </c>
+      <c r="U233" t="str">
+        <v>3</v>
+      </c>
+      <c r="V233" t="str">
+        <v>0</v>
+      </c>
+      <c r="W233" t="str">
+        <v>2</v>
+      </c>
+      <c r="X233" t="str">
+        <v>5/17/26</v>
+      </c>
+      <c r="Y233" t="str">
+        <v>8/20/26</v>
+      </c>
+      <c r="Z233" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="AB233" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="AD233" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="AE233" t="str">
+        <v>Skipped: Intended practices disabled (program stage)</v>
+      </c>
+    </row>
+    <row r="234" xml:space="preserve">
+      <c r="A234" t="str">
+        <v>(1270)</v>
+      </c>
+      <c r="B234" t="str">
+        <v>(1) Viet Nga Group, (2) Việt Nga Group - HTX An Hoà</v>
+      </c>
+      <c r="C234" t="str">
+        <v>74128</v>
+      </c>
+      <c r="D234" t="str">
+        <v>396861101</v>
+      </c>
+      <c r="E234" t="str">
+        <v>NGUYỄN VĂN NGHE</v>
+      </c>
+      <c r="F234" t="str">
+        <v>HỢP TÁC XÃ NÔNG NGHIỆP AN HÒA</v>
+      </c>
+      <c r="J234" t="str" xml:space="preserve">
+        <v xml:space="preserve">✅ Residue removal // Thu gom rơm rạ_x000d_
+✅ Rate reduction // Giảm lượng phân bón_x000d_
+✅ Reduced planting density // Giảm mật độ trồng_x000d_
+✅ Irrigation Management // Quản lý tưới tiêu</v>
+      </c>
+      <c r="K234" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="L234" t="str">
+        <v>Male // Nam</v>
+      </c>
+      <c r="M234" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="N234" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O234" t="str">
+        <v>0</v>
+      </c>
+      <c r="P234" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q234" t="str">
+        <v>0</v>
+      </c>
+      <c r="R234" t="str">
+        <v>0</v>
+      </c>
+      <c r="S234" t="str">
+        <v>0</v>
+      </c>
+      <c r="T234" t="str">
+        <v>0</v>
+      </c>
+      <c r="U234" t="str">
+        <v>2</v>
+      </c>
+      <c r="V234" t="str">
+        <v>0</v>
+      </c>
+      <c r="W234" t="str">
+        <v>1</v>
+      </c>
+      <c r="X234" t="str">
+        <v>5/17/26</v>
+      </c>
+      <c r="Y234" t="str">
+        <v>8/20/26</v>
+      </c>
+      <c r="Z234" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="AB234" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="AD234" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="AE234" t="str">
+        <v>Skipped: Intended practices disabled (program stage)</v>
+      </c>
+    </row>
+    <row r="235" xml:space="preserve">
+      <c r="A235" t="str">
+        <v>(1271)</v>
+      </c>
+      <c r="B235" t="str">
+        <v>(1) Viet Nga Group, (2) Việt Nga Group - HTX An Hoà</v>
+      </c>
+      <c r="C235" t="str">
+        <v>74129</v>
+      </c>
+      <c r="D235" t="str">
+        <v>378777418</v>
+      </c>
+      <c r="E235" t="str">
+        <v>DƯƠNG VĂN PHƯƠNG</v>
+      </c>
+      <c r="F235" t="str">
+        <v>HỢP TÁC XÃ NÔNG NGHIỆP AN HÒA</v>
+      </c>
+      <c r="J235" t="str" xml:space="preserve">
+        <v xml:space="preserve">✅ Residue removal // Thu gom rơm rạ_x000d_
+✅ Rate reduction // Giảm lượng phân bón_x000d_
+✅ Reduced planting density // Giảm mật độ trồng_x000d_
+✅ Irrigation Management // Quản lý tưới tiêu</v>
+      </c>
+      <c r="K235" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="L235" t="str">
+        <v>Male // Nam</v>
+      </c>
+      <c r="M235" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="N235" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O235" t="str">
+        <v>0</v>
+      </c>
+      <c r="P235" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q235" t="str">
+        <v>0</v>
+      </c>
+      <c r="R235" t="str">
+        <v>0</v>
+      </c>
+      <c r="S235" t="str">
+        <v>0</v>
+      </c>
+      <c r="T235" t="str">
+        <v>0</v>
+      </c>
+      <c r="U235" t="str">
+        <v>2</v>
+      </c>
+      <c r="V235" t="str">
+        <v>0</v>
+      </c>
+      <c r="W235" t="str">
+        <v>1</v>
+      </c>
+      <c r="X235" t="str">
+        <v>5/17/26</v>
+      </c>
+      <c r="Y235" t="str">
+        <v>8/20/26</v>
+      </c>
+      <c r="Z235" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="AB235" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="AD235" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="AE235" t="str">
+        <v>Skipped: Intended practices disabled (program stage)</v>
+      </c>
+    </row>
+    <row r="236" xml:space="preserve">
+      <c r="A236" t="str">
+        <v>(1272)</v>
+      </c>
+      <c r="B236" t="str">
+        <v>(1) Viet Nga Group, (2) Việt Nga Group - HTX An Hoà</v>
+      </c>
+      <c r="C236" t="str">
+        <v>74130</v>
+      </c>
+      <c r="D236" t="str">
+        <v>819966006</v>
+      </c>
+      <c r="E236" t="str">
+        <v>NGUYỄN VĂN BI</v>
+      </c>
+      <c r="F236" t="str">
+        <v>HỢP TÁC XÃ NÔNG NGHIỆP AN HÒA</v>
+      </c>
+      <c r="J236" t="str" xml:space="preserve">
+        <v xml:space="preserve">✅ Residue removal // Thu gom rơm rạ_x000d_
+✅ Rate reduction // Giảm lượng phân bón_x000d_
+✅ Reduced planting density // Giảm mật độ trồng_x000d_
+✅ Irrigation Management // Quản lý tưới tiêu</v>
+      </c>
+      <c r="K236" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="L236" t="str">
+        <v>Male // Nam</v>
+      </c>
+      <c r="M236" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="N236" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O236" t="str">
+        <v>0</v>
+      </c>
+      <c r="P236" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q236" t="str">
+        <v>0</v>
+      </c>
+      <c r="R236" t="str">
+        <v>0</v>
+      </c>
+      <c r="S236" t="str">
+        <v>0</v>
+      </c>
+      <c r="T236" t="str">
+        <v>0</v>
+      </c>
+      <c r="U236" t="str">
+        <v>2</v>
+      </c>
+      <c r="V236" t="str">
+        <v>0</v>
+      </c>
+      <c r="W236" t="str">
+        <v>1</v>
+      </c>
+      <c r="X236" t="str">
+        <v>5/17/26</v>
+      </c>
+      <c r="Y236" t="str">
+        <v>8/20/26</v>
+      </c>
+      <c r="Z236" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="AB236" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="AD236" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="AE236" t="str">
+        <v>Skipped: Intended practices disabled (program stage)</v>
+      </c>
+    </row>
+    <row r="237" xml:space="preserve">
+      <c r="A237" t="str">
+        <v>(1273)</v>
+      </c>
+      <c r="B237" t="str">
+        <v>(1) Viet Nga Group, (2) Việt Nga Group - HTX An Hoà</v>
+      </c>
+      <c r="C237" t="str">
+        <v>74131</v>
+      </c>
+      <c r="D237" t="str">
+        <v>795488022</v>
+      </c>
+      <c r="E237" t="str">
+        <v>ĐỖ VĂN NGƯNG</v>
+      </c>
+      <c r="F237" t="str">
+        <v>HỢP TÁC XÃ NÔNG NGHIỆP AN HÒA</v>
+      </c>
+      <c r="J237" t="str" xml:space="preserve">
+        <v xml:space="preserve">✅ Residue removal // Thu gom rơm rạ_x000d_
+✅ Rate reduction // Giảm lượng phân bón_x000d_
+✅ Reduced planting density // Giảm mật độ trồng_x000d_
+✅ Irrigation Management // Quản lý tưới tiêu</v>
+      </c>
+      <c r="K237" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="L237" t="str">
+        <v>Male // Nam</v>
+      </c>
+      <c r="M237" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="N237" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O237" t="str">
+        <v>0</v>
+      </c>
+      <c r="P237" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q237" t="str">
+        <v>0</v>
+      </c>
+      <c r="R237" t="str">
+        <v>0</v>
+      </c>
+      <c r="S237" t="str">
+        <v>0</v>
+      </c>
+      <c r="T237" t="str">
+        <v>0</v>
+      </c>
+      <c r="U237" t="str">
+        <v>2</v>
+      </c>
+      <c r="V237" t="str">
+        <v>0</v>
+      </c>
+      <c r="W237" t="str">
+        <v>1</v>
+      </c>
+      <c r="X237" t="str">
+        <v>5/17/26</v>
+      </c>
+      <c r="Y237" t="str">
+        <v>8/20/26</v>
+      </c>
+      <c r="Z237" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="AB237" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="AD237" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="AE237" t="str">
+        <v>Skipped: Intended practices disabled (program stage)</v>
+      </c>
+    </row>
+    <row r="238" xml:space="preserve">
+      <c r="A238" t="str">
+        <v>(1274)</v>
+      </c>
+      <c r="B238" t="str">
+        <v>(1) Viet Nga Group, (2) Việt Nga Group - HTX An Hoà</v>
+      </c>
+      <c r="C238" t="str">
+        <v>74132</v>
+      </c>
+      <c r="D238" t="str">
+        <v>348671494</v>
+      </c>
+      <c r="E238" t="str">
+        <v>THÁI NGỌC HÙNG BÉ</v>
+      </c>
+      <c r="F238" t="str">
+        <v>HỢP TÁC XÃ NÔNG NGHIỆP AN HÒA</v>
+      </c>
+      <c r="J238" t="str" xml:space="preserve">
+        <v xml:space="preserve">✅ Residue removal // Thu gom rơm rạ_x000d_
+✅ Rate reduction // Giảm lượng phân bón_x000d_
+✅ Reduced planting density // Giảm mật độ trồng_x000d_
+✅ Irrigation Management // Quản lý tưới tiêu</v>
+      </c>
+      <c r="K238" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="L238" t="str">
+        <v>Male // Nam</v>
+      </c>
+      <c r="M238" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="N238" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O238" t="str">
+        <v>0</v>
+      </c>
+      <c r="P238" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q238" t="str">
+        <v>0</v>
+      </c>
+      <c r="R238" t="str">
+        <v>0</v>
+      </c>
+      <c r="S238" t="str">
+        <v>0</v>
+      </c>
+      <c r="T238" t="str">
+        <v>0</v>
+      </c>
+      <c r="U238" t="str">
+        <v>2</v>
+      </c>
+      <c r="V238" t="str">
+        <v>0</v>
+      </c>
+      <c r="W238" t="str">
+        <v>1</v>
+      </c>
+      <c r="X238" t="str">
+        <v>5/17/26</v>
+      </c>
+      <c r="Y238" t="str">
+        <v>8/20/26</v>
+      </c>
+      <c r="Z238" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="AB238" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="AD238" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="AE238" t="str">
+        <v>Skipped: Intended practices disabled (program stage)</v>
+      </c>
+    </row>
+    <row r="239" xml:space="preserve">
+      <c r="A239" t="str">
+        <v>(1275)</v>
+      </c>
+      <c r="B239" t="str">
+        <v>(1) Viet Nga Group, (2) Việt Nga Group - HTX An Hoà</v>
+      </c>
+      <c r="C239" t="str">
+        <v>74133</v>
+      </c>
+      <c r="D239" t="str">
+        <v>774098618</v>
+      </c>
+      <c r="E239" t="str">
+        <v>NGUYỄN THANH LONG</v>
+      </c>
+      <c r="F239" t="str">
+        <v>HỢP TÁC XÃ NÔNG NGHIỆP AN HÒA</v>
+      </c>
+      <c r="J239" t="str" xml:space="preserve">
+        <v xml:space="preserve">✅ Residue removal // Thu gom rơm rạ_x000d_
+✅ Rate reduction // Giảm lượng phân bón_x000d_
+✅ Reduced planting density // Giảm mật độ trồng_x000d_
+✅ Irrigation Management // Quản lý tưới tiêu</v>
+      </c>
+      <c r="K239" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="L239" t="str">
+        <v>Male // Nam</v>
+      </c>
+      <c r="M239" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="N239" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O239" t="str">
+        <v>0</v>
+      </c>
+      <c r="P239" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q239" t="str">
+        <v>0</v>
+      </c>
+      <c r="R239" t="str">
+        <v>0</v>
+      </c>
+      <c r="S239" t="str">
+        <v>0</v>
+      </c>
+      <c r="T239" t="str">
+        <v>0</v>
+      </c>
+      <c r="U239" t="str">
+        <v>2</v>
+      </c>
+      <c r="V239" t="str">
+        <v>0</v>
+      </c>
+      <c r="W239" t="str">
+        <v>1</v>
+      </c>
+      <c r="X239" t="str">
+        <v>5/17/26</v>
+      </c>
+      <c r="Y239" t="str">
+        <v>8/20/26</v>
+      </c>
+      <c r="Z239" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="AB239" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="AD239" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="AE239" t="str">
+        <v>Skipped: Intended practices disabled (program stage)</v>
+      </c>
+    </row>
+    <row r="240" xml:space="preserve">
+      <c r="A240" t="str">
+        <v>(1276)</v>
+      </c>
+      <c r="B240" t="str">
+        <v>(1) Viet Nga Group, (2) Việt Nga Group - HTX An Hoà</v>
+      </c>
+      <c r="C240" t="str">
+        <v>74134</v>
+      </c>
+      <c r="D240" t="str">
+        <v>377522513</v>
+      </c>
+      <c r="E240" t="str">
+        <v>NGUYỄN VĂN LÀNH</v>
+      </c>
+      <c r="F240" t="str">
+        <v>HỢP TÁC XÃ NÔNG NGHIỆP AN HÒA</v>
+      </c>
+      <c r="J240" t="str" xml:space="preserve">
+        <v xml:space="preserve">✅ Residue removal // Thu gom rơm rạ_x000d_
+✅ Rate reduction // Giảm lượng phân bón_x000d_
+✅ Reduced planting density // Giảm mật độ trồng_x000d_
+✅ Irrigation Management // Quản lý tưới tiêu</v>
+      </c>
+      <c r="K240" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="L240" t="str">
+        <v>Male // Nam</v>
+      </c>
+      <c r="M240" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="N240" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O240" t="str">
+        <v>0</v>
+      </c>
+      <c r="P240" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q240" t="str">
+        <v>0</v>
+      </c>
+      <c r="R240" t="str">
+        <v>0</v>
+      </c>
+      <c r="S240" t="str">
+        <v>0</v>
+      </c>
+      <c r="T240" t="str">
+        <v>0</v>
+      </c>
+      <c r="U240" t="str">
+        <v>3</v>
+      </c>
+      <c r="V240" t="str">
+        <v>0</v>
+      </c>
+      <c r="W240" t="str">
+        <v>2</v>
+      </c>
+      <c r="X240" t="str">
+        <v>5/17/26</v>
+      </c>
+      <c r="Y240" t="str">
+        <v>8/20/26</v>
+      </c>
+      <c r="Z240" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="AB240" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="AD240" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="AE240" t="str">
+        <v>Skipped: Intended practices disabled (program stage)</v>
+      </c>
+    </row>
+    <row r="241" xml:space="preserve">
+      <c r="A241" t="str">
+        <v>(1277)</v>
+      </c>
+      <c r="B241" t="str">
+        <v>(1) Viet Nga Group, (2) Việt Nga Group - HTX An Hoà</v>
+      </c>
+      <c r="C241" t="str">
+        <v>74135</v>
+      </c>
+      <c r="D241" t="str">
+        <v>372968599</v>
+      </c>
+      <c r="E241" t="str">
+        <v>LÊ VĂN MÊN</v>
+      </c>
+      <c r="F241" t="str">
+        <v>HỢP TÁC XÃ NÔNG NGHIỆP AN HÒA</v>
+      </c>
+      <c r="J241" t="str" xml:space="preserve">
+        <v xml:space="preserve">✅ Residue removal // Thu gom rơm rạ_x000d_
+✅ Rate reduction // Giảm lượng phân bón_x000d_
+✅ Reduced planting density // Giảm mật độ trồng_x000d_
+✅ Irrigation Management // Quản lý tưới tiêu</v>
+      </c>
+      <c r="K241" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="L241" t="str">
+        <v>Male // Nam</v>
+      </c>
+      <c r="M241" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="N241" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O241" t="str">
+        <v>0</v>
+      </c>
+      <c r="P241" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q241" t="str">
+        <v>0</v>
+      </c>
+      <c r="R241" t="str">
+        <v>0</v>
+      </c>
+      <c r="S241" t="str">
+        <v>0</v>
+      </c>
+      <c r="T241" t="str">
+        <v>0</v>
+      </c>
+      <c r="U241" t="str">
+        <v>3</v>
+      </c>
+      <c r="V241" t="str">
+        <v>0</v>
+      </c>
+      <c r="W241" t="str">
+        <v>2</v>
+      </c>
+      <c r="X241" t="str">
+        <v>5/17/26</v>
+      </c>
+      <c r="Y241" t="str">
+        <v>8/20/26</v>
+      </c>
+      <c r="Z241" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="AB241" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="AD241" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="AE241" t="str">
+        <v>Skipped: Intended practices disabled (program stage)</v>
+      </c>
+    </row>
+    <row r="242" xml:space="preserve">
+      <c r="A242" t="str">
+        <v>(1278)</v>
+      </c>
+      <c r="B242" t="str">
+        <v>(1) Viet Nga Group, (2) Việt Nga Group - HTX An Hoà</v>
+      </c>
+      <c r="C242" t="str">
+        <v>74136</v>
+      </c>
+      <c r="D242" t="str">
+        <v>782815288</v>
+      </c>
+      <c r="E242" t="str">
+        <v>ĐỖ THỊ DẸN</v>
+      </c>
+      <c r="F242" t="str">
+        <v>HỢP TÁC XÃ NÔNG NGHIỆP AN HÒA</v>
+      </c>
+      <c r="J242" t="str" xml:space="preserve">
+        <v xml:space="preserve">✅ Residue removal // Thu gom rơm rạ_x000d_
+✅ Rate reduction // Giảm lượng phân bón_x000d_
+✅ Reduced planting density // Giảm mật độ trồng_x000d_
+✅ Irrigation Management // Quản lý tưới tiêu</v>
+      </c>
+      <c r="K242" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="L242" t="str">
+        <v>Female // Nữ</v>
+      </c>
+      <c r="M242" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="N242" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O242" t="str">
+        <v>1</v>
+      </c>
+      <c r="P242" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q242" t="str">
+        <v>0</v>
+      </c>
+      <c r="R242" t="str">
+        <v>0</v>
+      </c>
+      <c r="S242" t="str">
+        <v>0</v>
+      </c>
+      <c r="T242" t="str">
+        <v>0</v>
+      </c>
+      <c r="U242" t="str">
+        <v>2</v>
+      </c>
+      <c r="V242" t="str">
+        <v>0</v>
+      </c>
+      <c r="W242" t="str">
+        <v>1</v>
+      </c>
+      <c r="X242" t="str">
+        <v>5/17/26</v>
+      </c>
+      <c r="Y242" t="str">
+        <v>8/20/26</v>
+      </c>
+      <c r="Z242" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="AB242" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="AD242" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="AE242" t="str">
+        <v>Skipped: Intended practices disabled (program stage)</v>
+      </c>
+    </row>
+    <row r="243" xml:space="preserve">
+      <c r="A243" t="str">
+        <v>(1279)</v>
+      </c>
+      <c r="B243" t="str">
+        <v>(1) Viet Nga Group, (2) Việt Nga Group - HTX An Hoà</v>
+      </c>
+      <c r="C243" t="str">
+        <v>74137</v>
+      </c>
+      <c r="D243" t="str">
+        <v>832804033</v>
+      </c>
+      <c r="E243" t="str">
+        <v>ĐỖ VĂN THUM</v>
+      </c>
+      <c r="F243" t="str">
+        <v>HỢP TÁC XÃ NÔNG NGHIỆP AN HÒA</v>
+      </c>
+      <c r="J243" t="str" xml:space="preserve">
+        <v xml:space="preserve">✅ Residue removal // Thu gom rơm rạ_x000d_
+✅ Rate reduction // Giảm lượng phân bón_x000d_
+✅ Reduced planting density // Giảm mật độ trồng_x000d_
+✅ Irrigation Management // Quản lý tưới tiêu</v>
+      </c>
+      <c r="K243" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="L243" t="str">
+        <v>Male // Nam</v>
+      </c>
+      <c r="M243" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="N243" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O243" t="str">
+        <v>0</v>
+      </c>
+      <c r="P243" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q243" t="str">
+        <v>0</v>
+      </c>
+      <c r="R243" t="str">
+        <v>0</v>
+      </c>
+      <c r="S243" t="str">
+        <v>0</v>
+      </c>
+      <c r="T243" t="str">
+        <v>0</v>
+      </c>
+      <c r="U243" t="str">
+        <v>2</v>
+      </c>
+      <c r="V243" t="str">
+        <v>0</v>
+      </c>
+      <c r="W243" t="str">
+        <v>1</v>
+      </c>
+      <c r="X243" t="str">
+        <v>5/17/26</v>
+      </c>
+      <c r="Y243" t="str">
+        <v>8/20/26</v>
+      </c>
+      <c r="Z243" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="AB243" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="AD243" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="AE243" t="str">
+        <v>Skipped: Intended practices disabled (program stage)</v>
+      </c>
+    </row>
+    <row r="244" xml:space="preserve">
+      <c r="A244" t="str">
+        <v>(1280)</v>
+      </c>
+      <c r="B244" t="str">
+        <v>(1) Viet Nga Group, (2) Việt Nga Group - HTX An Hoà</v>
+      </c>
+      <c r="C244" t="str">
+        <v>74138</v>
+      </c>
+      <c r="D244" t="str">
+        <v>987650747</v>
+      </c>
+      <c r="E244" t="str">
+        <v>NGUYỄN VĂN TÀU</v>
+      </c>
+      <c r="F244" t="str">
+        <v>HỢP TÁC XÃ NÔNG NGHIỆP AN HÒA</v>
+      </c>
+      <c r="J244" t="str" xml:space="preserve">
+        <v xml:space="preserve">✅ Residue removal // Thu gom rơm rạ_x000d_
+✅ Rate reduction // Giảm lượng phân bón_x000d_
+✅ Reduced planting density // Giảm mật độ trồng_x000d_
+✅ Irrigation Management // Quản lý tưới tiêu</v>
+      </c>
+      <c r="K244" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="L244" t="str">
+        <v>Male // Nam</v>
+      </c>
+      <c r="M244" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="N244" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O244" t="str">
+        <v>0</v>
+      </c>
+      <c r="P244" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q244" t="str">
+        <v>0</v>
+      </c>
+      <c r="R244" t="str">
+        <v>0</v>
+      </c>
+      <c r="S244" t="str">
+        <v>0</v>
+      </c>
+      <c r="T244" t="str">
+        <v>0</v>
+      </c>
+      <c r="U244" t="str">
+        <v>2</v>
+      </c>
+      <c r="V244" t="str">
+        <v>0</v>
+      </c>
+      <c r="W244" t="str">
+        <v>1</v>
+      </c>
+      <c r="X244" t="str">
+        <v>5/17/26</v>
+      </c>
+      <c r="Y244" t="str">
+        <v>8/20/26</v>
+      </c>
+      <c r="Z244" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="AB244" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="AD244" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="AE244" t="str">
+        <v>Skipped: Intended practices disabled (program stage)</v>
+      </c>
+    </row>
+    <row r="245" xml:space="preserve">
+      <c r="A245" t="str">
+        <v>(1260)</v>
+      </c>
+      <c r="B245" t="str">
+        <v>(1) Viet Nga Group, (2) Việt Nga Group - HTX An Hoà</v>
+      </c>
+      <c r="C245" t="str">
+        <v>74118</v>
+      </c>
+      <c r="D245" t="str">
+        <v>917609986</v>
+      </c>
+      <c r="E245" t="str">
+        <v>NGUYỄN HÙNG SƠN</v>
+      </c>
+      <c r="F245" t="str">
+        <v>HỢP TÁC XÃ NÔNG NGHIỆP AN HÒA</v>
+      </c>
+      <c r="J245" t="str" xml:space="preserve">
+        <v xml:space="preserve">✅ Residue removal // Thu gom rơm rạ_x000d_
+✅ Rate reduction // Giảm lượng phân bón_x000d_
+✅ Reduced planting density // Giảm mật độ trồng_x000d_
+✅ Irrigation Management // Quản lý tưới tiêu</v>
+      </c>
+      <c r="K245" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="L245" t="str">
+        <v>Male // Nam</v>
+      </c>
+      <c r="M245" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="N245" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O245" t="str">
+        <v>0</v>
+      </c>
+      <c r="P245" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q245" t="str">
+        <v>0</v>
+      </c>
+      <c r="R245" t="str">
+        <v>0</v>
+      </c>
+      <c r="S245" t="str">
+        <v>0</v>
+      </c>
+      <c r="T245" t="str">
+        <v>0</v>
+      </c>
+      <c r="U245" t="str">
+        <v>3</v>
+      </c>
+      <c r="V245" t="str">
+        <v>0</v>
+      </c>
+      <c r="W245" t="str">
+        <v>2</v>
+      </c>
+      <c r="X245" t="str">
+        <v>5/17/26</v>
+      </c>
+      <c r="Y245" t="str">
+        <v>8/20/26</v>
+      </c>
+      <c r="Z245" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="AB245" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="AD245" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="AE245" t="str">
+        <v>Skipped: Intended practices disabled (program stage)</v>
+      </c>
+    </row>
+    <row r="246" xml:space="preserve">
+      <c r="A246" t="str">
+        <v>(1261)</v>
+      </c>
+      <c r="B246" t="str">
+        <v>(1) Viet Nga Group, (2) Việt Nga Group - HTX An Hoà</v>
+      </c>
+      <c r="C246" t="str">
+        <v>74119</v>
+      </c>
+      <c r="D246" t="str">
+        <v>977442419</v>
+      </c>
+      <c r="E246" t="str">
+        <v>LÊ VĂN NU</v>
+      </c>
+      <c r="F246" t="str">
+        <v>HỢP TÁC XÃ NÔNG NGHIỆP AN HÒA</v>
+      </c>
+      <c r="J246" t="str" xml:space="preserve">
+        <v xml:space="preserve">✅ Residue removal // Thu gom rơm rạ_x000d_
+✅ Rate reduction // Giảm lượng phân bón_x000d_
+✅ Reduced planting density // Giảm mật độ trồng_x000d_
+✅ Irrigation Management // Quản lý tưới tiêu</v>
+      </c>
+      <c r="K246" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="L246" t="str">
+        <v>Male // Nam</v>
+      </c>
+      <c r="M246" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="N246" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O246" t="str">
+        <v>0</v>
+      </c>
+      <c r="P246" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q246" t="str">
+        <v>0</v>
+      </c>
+      <c r="R246" t="str">
+        <v>0</v>
+      </c>
+      <c r="S246" t="str">
+        <v>0</v>
+      </c>
+      <c r="T246" t="str">
+        <v>0</v>
+      </c>
+      <c r="U246" t="str">
+        <v>3</v>
+      </c>
+      <c r="V246" t="str">
+        <v>0</v>
+      </c>
+      <c r="W246" t="str">
+        <v>2</v>
+      </c>
+      <c r="X246" t="str">
+        <v>5/17/26</v>
+      </c>
+      <c r="Y246" t="str">
+        <v>8/20/26</v>
+      </c>
+      <c r="Z246" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="AB246" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="AD246" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="AE246" t="str">
+        <v>Skipped: Intended practices disabled (program stage)</v>
+      </c>
+    </row>
+    <row r="247" xml:space="preserve">
+      <c r="A247" t="str">
+        <v>(1262)</v>
+      </c>
+      <c r="B247" t="str">
+        <v>(1) Viet Nga Group, (2) Việt Nga Group - HTX An Hoà</v>
+      </c>
+      <c r="C247" t="str">
+        <v>74120</v>
+      </c>
+      <c r="D247" t="str">
+        <v>385188053</v>
+      </c>
+      <c r="E247" t="str">
+        <v>LÊ VĂN DŨNG</v>
+      </c>
+      <c r="F247" t="str">
+        <v>HỢP TÁC XÃ NÔNG NGHIỆP AN HÒA</v>
+      </c>
+      <c r="J247" t="str" xml:space="preserve">
+        <v xml:space="preserve">✅ Residue removal // Thu gom rơm rạ_x000d_
+✅ Rate reduction // Giảm lượng phân bón_x000d_
+✅ Reduced planting density // Giảm mật độ trồng_x000d_
+✅ Irrigation Management // Quản lý tưới tiêu</v>
+      </c>
+      <c r="K247" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="L247" t="str">
+        <v>Male // Nam</v>
+      </c>
+      <c r="M247" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="N247" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O247" t="str">
+        <v>0</v>
+      </c>
+      <c r="P247" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q247" t="str">
+        <v>0</v>
+      </c>
+      <c r="R247" t="str">
+        <v>0</v>
+      </c>
+      <c r="S247" t="str">
+        <v>0</v>
+      </c>
+      <c r="T247" t="str">
+        <v>0</v>
+      </c>
+      <c r="U247" t="str">
+        <v>2</v>
+      </c>
+      <c r="V247" t="str">
+        <v>0</v>
+      </c>
+      <c r="W247" t="str">
+        <v>1</v>
+      </c>
+      <c r="X247" t="str">
+        <v>5/17/26</v>
+      </c>
+      <c r="Y247" t="str">
+        <v>8/20/26</v>
+      </c>
+      <c r="Z247" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="AB247" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="AD247" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="AE247" t="str">
+        <v>Skipped: Intended practices disabled (program stage)</v>
+      </c>
+    </row>
+    <row r="248" xml:space="preserve">
+      <c r="A248" t="str">
+        <v>(1263)</v>
+      </c>
+      <c r="B248" t="str">
+        <v>(1) Viet Nga Group, (2) Việt Nga Group - HTX An Hoà</v>
+      </c>
+      <c r="C248" t="str">
+        <v>74121</v>
+      </c>
+      <c r="D248" t="str">
+        <v>949463815</v>
+      </c>
+      <c r="E248" t="str">
+        <v>PHẠM VĂN BÌNH</v>
+      </c>
+      <c r="F248" t="str">
+        <v>HỢP TÁC XÃ NÔNG NGHIỆP AN HÒA</v>
+      </c>
+      <c r="J248" t="str" xml:space="preserve">
+        <v xml:space="preserve">✅ Residue removal // Thu gom rơm rạ_x000d_
+✅ Rate reduction // Giảm lượng phân bón_x000d_
+✅ Reduced planting density // Giảm mật độ trồng_x000d_
+✅ Irrigation Management // Quản lý tưới tiêu</v>
+      </c>
+      <c r="K248" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="L248" t="str">
+        <v>Male // Nam</v>
+      </c>
+      <c r="M248" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="N248" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O248" t="str">
+        <v>0</v>
+      </c>
+      <c r="P248" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q248" t="str">
+        <v>0</v>
+      </c>
+      <c r="R248" t="str">
+        <v>0</v>
+      </c>
+      <c r="S248" t="str">
+        <v>0</v>
+      </c>
+      <c r="T248" t="str">
+        <v>0</v>
+      </c>
+      <c r="U248" t="str">
+        <v>3</v>
+      </c>
+      <c r="V248" t="str">
+        <v>0</v>
+      </c>
+      <c r="W248" t="str">
+        <v>2</v>
+      </c>
+      <c r="X248" t="str">
+        <v>5/17/26</v>
+      </c>
+      <c r="Y248" t="str">
+        <v>8/20/26</v>
+      </c>
+      <c r="Z248" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="AB248" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="AD248" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="AE248" t="str">
+        <v>Skipped: Intended practices disabled (program stage)</v>
+      </c>
+    </row>
+    <row r="249" xml:space="preserve">
+      <c r="A249" t="str">
+        <v>(1264)</v>
+      </c>
+      <c r="B249" t="str">
+        <v>(1) Viet Nga Group, (2) Việt Nga Group - HTX An Hoà</v>
+      </c>
+      <c r="C249" t="str">
+        <v>74122</v>
+      </c>
+      <c r="D249" t="str">
+        <v>355206824</v>
+      </c>
+      <c r="E249" t="str">
+        <v>ĐẶNG THỊ SANG</v>
+      </c>
+      <c r="F249" t="str">
+        <v>HỢP TÁC XÃ NÔNG NGHIỆP AN HÒA</v>
+      </c>
+      <c r="J249" t="str" xml:space="preserve">
+        <v xml:space="preserve">✅ Residue removal // Thu gom rơm rạ_x000d_
+✅ Rate reduction // Giảm lượng phân bón_x000d_
+✅ Reduced planting density // Giảm mật độ trồng_x000d_
+✅ Irrigation Management // Quản lý tưới tiêu</v>
+      </c>
+      <c r="K249" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="L249" t="str">
+        <v>Female // Nữ</v>
+      </c>
+      <c r="M249" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="N249" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O249" t="str">
+        <v>1</v>
+      </c>
+      <c r="P249" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q249" t="str">
+        <v>0</v>
+      </c>
+      <c r="R249" t="str">
+        <v>0</v>
+      </c>
+      <c r="S249" t="str">
+        <v>0</v>
+      </c>
+      <c r="T249" t="str">
+        <v>0</v>
+      </c>
+      <c r="U249" t="str">
+        <v>2</v>
+      </c>
+      <c r="V249" t="str">
+        <v>0</v>
+      </c>
+      <c r="W249" t="str">
+        <v>1</v>
+      </c>
+      <c r="X249" t="str">
+        <v>5/17/26</v>
+      </c>
+      <c r="Y249" t="str">
+        <v>8/20/26</v>
+      </c>
+      <c r="Z249" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="AB249" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="AD249" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="AE249" t="str">
+        <v>Skipped: Intended practices disabled (program stage)</v>
+      </c>
+    </row>
+    <row r="250" xml:space="preserve">
+      <c r="A250" t="str">
+        <v>(1265)</v>
+      </c>
+      <c r="B250" t="str">
+        <v>(1) Viet Nga Group, (2) Việt Nga Group - HTX An Hoà</v>
+      </c>
+      <c r="C250" t="str">
+        <v>74123</v>
+      </c>
+      <c r="D250" t="str">
+        <v>874848090</v>
+      </c>
+      <c r="E250" t="str">
+        <v>NGUYỄN THỊ TÚ ANH</v>
+      </c>
+      <c r="F250" t="str">
+        <v>HỢP TÁC XÃ NÔNG NGHIỆP AN HÒA</v>
+      </c>
+      <c r="J250" t="str" xml:space="preserve">
+        <v xml:space="preserve">✅ Residue removal // Thu gom rơm rạ_x000d_
+✅ Rate reduction // Giảm lượng phân bón_x000d_
+✅ Reduced planting density // Giảm mật độ trồng_x000d_
+✅ Irrigation Management // Quản lý tưới tiêu</v>
+      </c>
+      <c r="K250" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="L250" t="str">
+        <v>Female // Nữ</v>
+      </c>
+      <c r="M250" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="N250" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O250" t="str">
+        <v>1</v>
+      </c>
+      <c r="P250" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q250" t="str">
+        <v>0</v>
+      </c>
+      <c r="R250" t="str">
+        <v>0</v>
+      </c>
+      <c r="S250" t="str">
+        <v>0</v>
+      </c>
+      <c r="T250" t="str">
+        <v>0</v>
+      </c>
+      <c r="U250" t="str">
+        <v>3</v>
+      </c>
+      <c r="V250" t="str">
+        <v>0</v>
+      </c>
+      <c r="W250" t="str">
+        <v>2</v>
+      </c>
+      <c r="X250" t="str">
+        <v>5/17/26</v>
+      </c>
+      <c r="Y250" t="str">
+        <v>8/20/26</v>
+      </c>
+      <c r="Z250" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="AB250" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="AD250" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="AE250" t="str">
+        <v>Skipped: Intended practices disabled (program stage)</v>
+      </c>
+    </row>
+    <row r="251" xml:space="preserve">
+      <c r="A251" t="str">
+        <v>(1266)</v>
+      </c>
+      <c r="B251" t="str">
+        <v>(1) Viet Nga Group, (2) Việt Nga Group - HTX An Hoà</v>
+      </c>
+      <c r="C251" t="str">
+        <v>74124</v>
+      </c>
+      <c r="D251" t="str">
+        <v>333505481</v>
+      </c>
+      <c r="E251" t="str">
+        <v>NGUYỄN VĂN TRÀ</v>
+      </c>
+      <c r="F251" t="str">
+        <v>HỢP TÁC XÃ NÔNG NGHIỆP AN HÒA</v>
+      </c>
+      <c r="J251" t="str" xml:space="preserve">
+        <v xml:space="preserve">✅ Residue removal // Thu gom rơm rạ_x000d_
+✅ Rate reduction // Giảm lượng phân bón_x000d_
+✅ Reduced planting density // Giảm mật độ trồng_x000d_
+✅ Irrigation Management // Quản lý tưới tiêu</v>
+      </c>
+      <c r="K251" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="L251" t="str">
+        <v>Male // Nam</v>
+      </c>
+      <c r="M251" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="N251" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O251" t="str">
+        <v>0</v>
+      </c>
+      <c r="P251" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q251" t="str">
+        <v>0</v>
+      </c>
+      <c r="R251" t="str">
+        <v>0</v>
+      </c>
+      <c r="S251" t="str">
+        <v>0</v>
+      </c>
+      <c r="T251" t="str">
+        <v>0</v>
+      </c>
+      <c r="U251" t="str">
+        <v>2</v>
+      </c>
+      <c r="V251" t="str">
+        <v>0</v>
+      </c>
+      <c r="W251" t="str">
+        <v>1</v>
+      </c>
+      <c r="X251" t="str">
+        <v>5/17/26</v>
+      </c>
+      <c r="Y251" t="str">
+        <v>8/20/26</v>
+      </c>
+      <c r="Z251" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="AB251" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="AD251" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="AE251" t="str">
+        <v>Skipped: Intended practices disabled (program stage)</v>
+      </c>
+    </row>
+    <row r="252" xml:space="preserve">
+      <c r="A252" t="str">
+        <v>(1267)</v>
+      </c>
+      <c r="B252" t="str">
+        <v>(1) Viet Nga Group, (2) Việt Nga Group - HTX An Hoà</v>
+      </c>
+      <c r="C252" t="str">
+        <v>74125</v>
+      </c>
+      <c r="D252" t="str">
+        <v>387550079</v>
+      </c>
+      <c r="E252" t="str">
+        <v>TRẦN MINH TRÍ</v>
+      </c>
+      <c r="F252" t="str">
+        <v>HỢP TÁC XÃ NÔNG NGHIỆP AN HÒA</v>
+      </c>
+      <c r="J252" t="str" xml:space="preserve">
+        <v xml:space="preserve">✅ Residue removal // Thu gom rơm rạ_x000d_
+✅ Rate reduction // Giảm lượng phân bón_x000d_
+✅ Reduced planting density // Giảm mật độ trồng_x000d_
+✅ Irrigation Management // Quản lý tưới tiêu</v>
+      </c>
+      <c r="K252" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="L252" t="str">
+        <v>Male // Nam</v>
+      </c>
+      <c r="M252" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="N252" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O252" t="str">
+        <v>0</v>
+      </c>
+      <c r="P252" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q252" t="str">
+        <v>0</v>
+      </c>
+      <c r="R252" t="str">
+        <v>0</v>
+      </c>
+      <c r="S252" t="str">
+        <v>0</v>
+      </c>
+      <c r="T252" t="str">
+        <v>0</v>
+      </c>
+      <c r="U252" t="str">
+        <v>3</v>
+      </c>
+      <c r="V252" t="str">
+        <v>0</v>
+      </c>
+      <c r="W252" t="str">
+        <v>2</v>
+      </c>
+      <c r="X252" t="str">
+        <v>5/17/26</v>
+      </c>
+      <c r="Y252" t="str">
+        <v>8/20/26</v>
+      </c>
+      <c r="Z252" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="AB252" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="AD252" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="AE252" t="str">
+        <v>Skipped: Intended practices disabled (program stage)</v>
+      </c>
+    </row>
+    <row r="253" xml:space="preserve">
+      <c r="A253" t="str">
+        <v>(1268)</v>
+      </c>
+      <c r="B253" t="str">
+        <v>(1) Viet Nga Group, (2) Việt Nga Group - HTX An Hoà</v>
+      </c>
+      <c r="C253" t="str">
+        <v>74126</v>
+      </c>
+      <c r="D253" t="str">
+        <v>916433534</v>
+      </c>
+      <c r="E253" t="str">
+        <v>NGUYỄN VĂN MÈO</v>
+      </c>
+      <c r="F253" t="str">
+        <v>HỢP TÁC XÃ NÔNG NGHIỆP AN HÒA</v>
+      </c>
+      <c r="J253" t="str" xml:space="preserve">
+        <v xml:space="preserve">✅ Residue removal // Thu gom rơm rạ_x000d_
+✅ Rate reduction // Giảm lượng phân bón_x000d_
+✅ Reduced planting density // Giảm mật độ trồng_x000d_
+✅ Irrigation Management // Quản lý tưới tiêu</v>
+      </c>
+      <c r="K253" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="L253" t="str">
+        <v>Male // Nam</v>
+      </c>
+      <c r="M253" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="N253" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O253" t="str">
+        <v>0</v>
+      </c>
+      <c r="P253" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q253" t="str">
+        <v>0</v>
+      </c>
+      <c r="R253" t="str">
+        <v>0</v>
+      </c>
+      <c r="S253" t="str">
+        <v>0</v>
+      </c>
+      <c r="T253" t="str">
+        <v>0</v>
+      </c>
+      <c r="U253" t="str">
+        <v>2</v>
+      </c>
+      <c r="V253" t="str">
+        <v>0</v>
+      </c>
+      <c r="W253" t="str">
+        <v>1</v>
+      </c>
+      <c r="X253" t="str">
+        <v>5/17/26</v>
+      </c>
+      <c r="Y253" t="str">
+        <v>8/20/26</v>
+      </c>
+      <c r="Z253" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="AB253" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="AD253" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="AE253" t="str">
+        <v>Skipped: Intended practices disabled (program stage)</v>
+      </c>
+    </row>
+    <row r="254" xml:space="preserve">
+      <c r="A254" t="str">
+        <v>(1269)</v>
+      </c>
+      <c r="B254" t="str">
+        <v>(1) Viet Nga Group, (2) Việt Nga Group - HTX An Hoà</v>
+      </c>
+      <c r="C254" t="str">
+        <v>74127</v>
+      </c>
+      <c r="D254" t="str">
+        <v>366155507</v>
+      </c>
+      <c r="E254" t="str">
+        <v>LÊ VĂN THẠT</v>
+      </c>
+      <c r="F254" t="str">
+        <v>HỢP TÁC XÃ NÔNG NGHIỆP AN HÒA</v>
+      </c>
+      <c r="J254" t="str" xml:space="preserve">
+        <v xml:space="preserve">✅ Residue removal // Thu gom rơm rạ_x000d_
+✅ Rate reduction // Giảm lượng phân bón_x000d_
+✅ Reduced planting density // Giảm mật độ trồng_x000d_
+✅ Irrigation Management // Quản lý tưới tiêu</v>
+      </c>
+      <c r="K254" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="L254" t="str">
+        <v>Male // Nam</v>
+      </c>
+      <c r="M254" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="N254" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O254" t="str">
+        <v>0</v>
+      </c>
+      <c r="P254" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q254" t="str">
+        <v>0</v>
+      </c>
+      <c r="R254" t="str">
+        <v>0</v>
+      </c>
+      <c r="S254" t="str">
+        <v>0</v>
+      </c>
+      <c r="T254" t="str">
+        <v>0</v>
+      </c>
+      <c r="U254" t="str">
+        <v>3</v>
+      </c>
+      <c r="V254" t="str">
+        <v>0</v>
+      </c>
+      <c r="W254" t="str">
+        <v>2</v>
+      </c>
+      <c r="X254" t="str">
+        <v>5/17/26</v>
+      </c>
+      <c r="Y254" t="str">
+        <v>8/20/26</v>
+      </c>
+      <c r="Z254" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="AB254" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="AD254" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="AE254" t="str">
+        <v>Skipped: Intended practices disabled (program stage)</v>
+      </c>
+    </row>
+    <row r="255" xml:space="preserve">
+      <c r="A255" t="str">
+        <v>(1270)</v>
+      </c>
+      <c r="B255" t="str">
+        <v>(1) Viet Nga Group, (2) Việt Nga Group - HTX An Hoà</v>
+      </c>
+      <c r="C255" t="str">
+        <v>74128</v>
+      </c>
+      <c r="D255" t="str">
+        <v>396861101</v>
+      </c>
+      <c r="E255" t="str">
+        <v>NGUYỄN VĂN NGHE</v>
+      </c>
+      <c r="F255" t="str">
+        <v>HỢP TÁC XÃ NÔNG NGHIỆP AN HÒA</v>
+      </c>
+      <c r="J255" t="str" xml:space="preserve">
+        <v xml:space="preserve">✅ Residue removal // Thu gom rơm rạ_x000d_
+✅ Rate reduction // Giảm lượng phân bón_x000d_
+✅ Reduced planting density // Giảm mật độ trồng_x000d_
+✅ Irrigation Management // Quản lý tưới tiêu</v>
+      </c>
+      <c r="K255" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="L255" t="str">
+        <v>Male // Nam</v>
+      </c>
+      <c r="M255" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="N255" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O255" t="str">
+        <v>0</v>
+      </c>
+      <c r="P255" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q255" t="str">
+        <v>0</v>
+      </c>
+      <c r="R255" t="str">
+        <v>0</v>
+      </c>
+      <c r="S255" t="str">
+        <v>0</v>
+      </c>
+      <c r="T255" t="str">
+        <v>0</v>
+      </c>
+      <c r="U255" t="str">
+        <v>2</v>
+      </c>
+      <c r="V255" t="str">
+        <v>0</v>
+      </c>
+      <c r="W255" t="str">
+        <v>1</v>
+      </c>
+      <c r="X255" t="str">
+        <v>5/17/26</v>
+      </c>
+      <c r="Y255" t="str">
+        <v>8/20/26</v>
+      </c>
+      <c r="Z255" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="AB255" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="AD255" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="AE255" t="str">
+        <v>Skipped: Intended practices disabled (program stage)</v>
+      </c>
+    </row>
+    <row r="256" xml:space="preserve">
+      <c r="A256" t="str">
+        <v>(1271)</v>
+      </c>
+      <c r="B256" t="str">
+        <v>(1) Viet Nga Group, (2) Việt Nga Group - HTX An Hoà</v>
+      </c>
+      <c r="C256" t="str">
+        <v>74129</v>
+      </c>
+      <c r="D256" t="str">
+        <v>378777418</v>
+      </c>
+      <c r="E256" t="str">
+        <v>DƯƠNG VĂN PHƯƠNG</v>
+      </c>
+      <c r="F256" t="str">
+        <v>HỢP TÁC XÃ NÔNG NGHIỆP AN HÒA</v>
+      </c>
+      <c r="J256" t="str" xml:space="preserve">
+        <v xml:space="preserve">✅ Residue removal // Thu gom rơm rạ_x000d_
+✅ Rate reduction // Giảm lượng phân bón_x000d_
+✅ Reduced planting density // Giảm mật độ trồng_x000d_
+✅ Irrigation Management // Quản lý tưới tiêu</v>
+      </c>
+      <c r="K256" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="L256" t="str">
+        <v>Male // Nam</v>
+      </c>
+      <c r="M256" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="N256" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O256" t="str">
+        <v>0</v>
+      </c>
+      <c r="P256" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q256" t="str">
+        <v>0</v>
+      </c>
+      <c r="R256" t="str">
+        <v>0</v>
+      </c>
+      <c r="S256" t="str">
+        <v>0</v>
+      </c>
+      <c r="T256" t="str">
+        <v>0</v>
+      </c>
+      <c r="U256" t="str">
+        <v>2</v>
+      </c>
+      <c r="V256" t="str">
+        <v>0</v>
+      </c>
+      <c r="W256" t="str">
+        <v>1</v>
+      </c>
+      <c r="X256" t="str">
+        <v>5/17/26</v>
+      </c>
+      <c r="Y256" t="str">
+        <v>8/20/26</v>
+      </c>
+      <c r="Z256" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="AB256" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="AD256" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="AE256" t="str">
+        <v>Skipped: Intended practices disabled (program stage)</v>
+      </c>
+    </row>
+    <row r="257" xml:space="preserve">
+      <c r="A257" t="str">
+        <v>(1272)</v>
+      </c>
+      <c r="B257" t="str">
+        <v>(1) Viet Nga Group, (2) Việt Nga Group - HTX An Hoà</v>
+      </c>
+      <c r="C257" t="str">
+        <v>74130</v>
+      </c>
+      <c r="D257" t="str">
+        <v>819966006</v>
+      </c>
+      <c r="E257" t="str">
+        <v>NGUYỄN VĂN BI</v>
+      </c>
+      <c r="F257" t="str">
+        <v>HỢP TÁC XÃ NÔNG NGHIỆP AN HÒA</v>
+      </c>
+      <c r="J257" t="str" xml:space="preserve">
+        <v xml:space="preserve">✅ Residue removal // Thu gom rơm rạ_x000d_
+✅ Rate reduction // Giảm lượng phân bón_x000d_
+✅ Reduced planting density // Giảm mật độ trồng_x000d_
+✅ Irrigation Management // Quản lý tưới tiêu</v>
+      </c>
+      <c r="K257" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="L257" t="str">
+        <v>Male // Nam</v>
+      </c>
+      <c r="M257" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="N257" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O257" t="str">
+        <v>0</v>
+      </c>
+      <c r="P257" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q257" t="str">
+        <v>0</v>
+      </c>
+      <c r="R257" t="str">
+        <v>0</v>
+      </c>
+      <c r="S257" t="str">
+        <v>0</v>
+      </c>
+      <c r="T257" t="str">
+        <v>0</v>
+      </c>
+      <c r="U257" t="str">
+        <v>2</v>
+      </c>
+      <c r="V257" t="str">
+        <v>0</v>
+      </c>
+      <c r="W257" t="str">
+        <v>1</v>
+      </c>
+      <c r="X257" t="str">
+        <v>5/17/26</v>
+      </c>
+      <c r="Y257" t="str">
+        <v>8/20/26</v>
+      </c>
+      <c r="Z257" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="AB257" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="AD257" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="AE257" t="str">
+        <v>Skipped: Intended practices disabled (program stage)</v>
+      </c>
+    </row>
+    <row r="258" xml:space="preserve">
+      <c r="A258" t="str">
+        <v>(1273)</v>
+      </c>
+      <c r="B258" t="str">
+        <v>(1) Viet Nga Group, (2) Việt Nga Group - HTX An Hoà</v>
+      </c>
+      <c r="C258" t="str">
+        <v>74131</v>
+      </c>
+      <c r="D258" t="str">
+        <v>795488022</v>
+      </c>
+      <c r="E258" t="str">
+        <v>ĐỖ VĂN NGƯNG</v>
+      </c>
+      <c r="F258" t="str">
+        <v>HỢP TÁC XÃ NÔNG NGHIỆP AN HÒA</v>
+      </c>
+      <c r="J258" t="str" xml:space="preserve">
+        <v xml:space="preserve">✅ Residue removal // Thu gom rơm rạ_x000d_
+✅ Rate reduction // Giảm lượng phân bón_x000d_
+✅ Reduced planting density // Giảm mật độ trồng_x000d_
+✅ Irrigation Management // Quản lý tưới tiêu</v>
+      </c>
+      <c r="K258" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="L258" t="str">
+        <v>Male // Nam</v>
+      </c>
+      <c r="M258" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="N258" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O258" t="str">
+        <v>0</v>
+      </c>
+      <c r="P258" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q258" t="str">
+        <v>0</v>
+      </c>
+      <c r="R258" t="str">
+        <v>0</v>
+      </c>
+      <c r="S258" t="str">
+        <v>0</v>
+      </c>
+      <c r="T258" t="str">
+        <v>0</v>
+      </c>
+      <c r="U258" t="str">
+        <v>2</v>
+      </c>
+      <c r="V258" t="str">
+        <v>0</v>
+      </c>
+      <c r="W258" t="str">
+        <v>1</v>
+      </c>
+      <c r="X258" t="str">
+        <v>5/17/26</v>
+      </c>
+      <c r="Y258" t="str">
+        <v>8/20/26</v>
+      </c>
+      <c r="Z258" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="AB258" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="AD258" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="AE258" t="str">
+        <v>Skipped: Intended practices disabled (program stage)</v>
+      </c>
+    </row>
+    <row r="259" xml:space="preserve">
+      <c r="A259" t="str">
+        <v>(1274)</v>
+      </c>
+      <c r="B259" t="str">
+        <v>(1) Viet Nga Group, (2) Việt Nga Group - HTX An Hoà</v>
+      </c>
+      <c r="C259" t="str">
+        <v>74132</v>
+      </c>
+      <c r="D259" t="str">
+        <v>348671494</v>
+      </c>
+      <c r="E259" t="str">
+        <v>THÁI NGỌC HÙNG BÉ</v>
+      </c>
+      <c r="F259" t="str">
+        <v>HỢP TÁC XÃ NÔNG NGHIỆP AN HÒA</v>
+      </c>
+      <c r="J259" t="str" xml:space="preserve">
+        <v xml:space="preserve">✅ Residue removal // Thu gom rơm rạ_x000d_
+✅ Rate reduction // Giảm lượng phân bón_x000d_
+✅ Reduced planting density // Giảm mật độ trồng_x000d_
+✅ Irrigation Management // Quản lý tưới tiêu</v>
+      </c>
+      <c r="K259" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="L259" t="str">
+        <v>Male // Nam</v>
+      </c>
+      <c r="M259" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="N259" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O259" t="str">
+        <v>0</v>
+      </c>
+      <c r="P259" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q259" t="str">
+        <v>0</v>
+      </c>
+      <c r="R259" t="str">
+        <v>0</v>
+      </c>
+      <c r="S259" t="str">
+        <v>0</v>
+      </c>
+      <c r="T259" t="str">
+        <v>0</v>
+      </c>
+      <c r="U259" t="str">
+        <v>2</v>
+      </c>
+      <c r="V259" t="str">
+        <v>0</v>
+      </c>
+      <c r="W259" t="str">
+        <v>1</v>
+      </c>
+      <c r="X259" t="str">
+        <v>5/17/26</v>
+      </c>
+      <c r="Y259" t="str">
+        <v>8/20/26</v>
+      </c>
+      <c r="Z259" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="AB259" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="AD259" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="AE259" t="str">
+        <v>Skipped: Intended practices disabled (program stage)</v>
+      </c>
+    </row>
+    <row r="260" xml:space="preserve">
+      <c r="A260" t="str">
+        <v>(1275)</v>
+      </c>
+      <c r="B260" t="str">
+        <v>(1) Viet Nga Group, (2) Việt Nga Group - HTX An Hoà</v>
+      </c>
+      <c r="C260" t="str">
+        <v>74133</v>
+      </c>
+      <c r="D260" t="str">
+        <v>774098618</v>
+      </c>
+      <c r="E260" t="str">
+        <v>NGUYỄN THANH LONG</v>
+      </c>
+      <c r="F260" t="str">
+        <v>HỢP TÁC XÃ NÔNG NGHIỆP AN HÒA</v>
+      </c>
+      <c r="J260" t="str" xml:space="preserve">
+        <v xml:space="preserve">✅ Residue removal // Thu gom rơm rạ_x000d_
+✅ Rate reduction // Giảm lượng phân bón_x000d_
+✅ Reduced planting density // Giảm mật độ trồng_x000d_
+✅ Irrigation Management // Quản lý tưới tiêu</v>
+      </c>
+      <c r="K260" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="L260" t="str">
+        <v>Male // Nam</v>
+      </c>
+      <c r="M260" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="N260" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O260" t="str">
+        <v>0</v>
+      </c>
+      <c r="P260" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q260" t="str">
+        <v>0</v>
+      </c>
+      <c r="R260" t="str">
+        <v>0</v>
+      </c>
+      <c r="S260" t="str">
+        <v>0</v>
+      </c>
+      <c r="T260" t="str">
+        <v>0</v>
+      </c>
+      <c r="U260" t="str">
+        <v>2</v>
+      </c>
+      <c r="V260" t="str">
+        <v>0</v>
+      </c>
+      <c r="W260" t="str">
+        <v>1</v>
+      </c>
+      <c r="X260" t="str">
+        <v>5/17/26</v>
+      </c>
+      <c r="Y260" t="str">
+        <v>8/20/26</v>
+      </c>
+      <c r="Z260" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="AB260" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="AD260" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="AE260" t="str">
+        <v>Skipped: Intended practices disabled (program stage)</v>
+      </c>
+    </row>
+    <row r="261" xml:space="preserve">
+      <c r="A261" t="str">
+        <v>(1276)</v>
+      </c>
+      <c r="B261" t="str">
+        <v>(1) Viet Nga Group, (2) Việt Nga Group - HTX An Hoà</v>
+      </c>
+      <c r="C261" t="str">
+        <v>74134</v>
+      </c>
+      <c r="D261" t="str">
+        <v>377522513</v>
+      </c>
+      <c r="E261" t="str">
+        <v>NGUYỄN VĂN LÀNH</v>
+      </c>
+      <c r="F261" t="str">
+        <v>HỢP TÁC XÃ NÔNG NGHIỆP AN HÒA</v>
+      </c>
+      <c r="J261" t="str" xml:space="preserve">
+        <v xml:space="preserve">✅ Residue removal // Thu gom rơm rạ_x000d_
+✅ Rate reduction // Giảm lượng phân bón_x000d_
+✅ Reduced planting density // Giảm mật độ trồng_x000d_
+✅ Irrigation Management // Quản lý tưới tiêu</v>
+      </c>
+      <c r="K261" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="L261" t="str">
+        <v>Male // Nam</v>
+      </c>
+      <c r="M261" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="N261" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O261" t="str">
+        <v>0</v>
+      </c>
+      <c r="P261" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q261" t="str">
+        <v>0</v>
+      </c>
+      <c r="R261" t="str">
+        <v>0</v>
+      </c>
+      <c r="S261" t="str">
+        <v>0</v>
+      </c>
+      <c r="T261" t="str">
+        <v>0</v>
+      </c>
+      <c r="U261" t="str">
+        <v>3</v>
+      </c>
+      <c r="V261" t="str">
+        <v>0</v>
+      </c>
+      <c r="W261" t="str">
+        <v>2</v>
+      </c>
+      <c r="X261" t="str">
+        <v>5/17/26</v>
+      </c>
+      <c r="Y261" t="str">
+        <v>8/20/26</v>
+      </c>
+      <c r="Z261" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="AB261" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="AD261" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="AE261" t="str">
+        <v>Skipped: Intended practices disabled (program stage)</v>
+      </c>
+    </row>
+    <row r="262" xml:space="preserve">
+      <c r="A262" t="str">
+        <v>(1277)</v>
+      </c>
+      <c r="B262" t="str">
+        <v>(1) Viet Nga Group, (2) Việt Nga Group - HTX An Hoà</v>
+      </c>
+      <c r="C262" t="str">
+        <v>74135</v>
+      </c>
+      <c r="D262" t="str">
+        <v>372968599</v>
+      </c>
+      <c r="E262" t="str">
+        <v>LÊ VĂN MÊN</v>
+      </c>
+      <c r="F262" t="str">
+        <v>HỢP TÁC XÃ NÔNG NGHIỆP AN HÒA</v>
+      </c>
+      <c r="J262" t="str" xml:space="preserve">
+        <v xml:space="preserve">✅ Residue removal // Thu gom rơm rạ_x000d_
+✅ Rate reduction // Giảm lượng phân bón_x000d_
+✅ Reduced planting density // Giảm mật độ trồng_x000d_
+✅ Irrigation Management // Quản lý tưới tiêu</v>
+      </c>
+      <c r="K262" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="L262" t="str">
+        <v>Male // Nam</v>
+      </c>
+      <c r="M262" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="N262" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O262" t="str">
+        <v>0</v>
+      </c>
+      <c r="P262" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q262" t="str">
+        <v>0</v>
+      </c>
+      <c r="R262" t="str">
+        <v>0</v>
+      </c>
+      <c r="S262" t="str">
+        <v>0</v>
+      </c>
+      <c r="T262" t="str">
+        <v>0</v>
+      </c>
+      <c r="U262" t="str">
+        <v>3</v>
+      </c>
+      <c r="V262" t="str">
+        <v>0</v>
+      </c>
+      <c r="W262" t="str">
+        <v>2</v>
+      </c>
+      <c r="X262" t="str">
+        <v>5/17/26</v>
+      </c>
+      <c r="Y262" t="str">
+        <v>8/20/26</v>
+      </c>
+      <c r="Z262" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="AB262" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="AD262" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="AE262" t="str">
+        <v>Skipped: Intended practices disabled (program stage)</v>
+      </c>
+    </row>
+    <row r="263" xml:space="preserve">
+      <c r="A263" t="str">
+        <v>(1278)</v>
+      </c>
+      <c r="B263" t="str">
+        <v>(1) Viet Nga Group, (2) Việt Nga Group - HTX An Hoà</v>
+      </c>
+      <c r="C263" t="str">
+        <v>74136</v>
+      </c>
+      <c r="D263" t="str">
+        <v>782815288</v>
+      </c>
+      <c r="E263" t="str">
+        <v>ĐỖ THỊ DẸN</v>
+      </c>
+      <c r="F263" t="str">
+        <v>HỢP TÁC XÃ NÔNG NGHIỆP AN HÒA</v>
+      </c>
+      <c r="J263" t="str" xml:space="preserve">
+        <v xml:space="preserve">✅ Residue removal // Thu gom rơm rạ_x000d_
+✅ Rate reduction // Giảm lượng phân bón_x000d_
+✅ Reduced planting density // Giảm mật độ trồng_x000d_
+✅ Irrigation Management // Quản lý tưới tiêu</v>
+      </c>
+      <c r="K263" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="L263" t="str">
+        <v>Female // Nữ</v>
+      </c>
+      <c r="M263" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="N263" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O263" t="str">
+        <v>1</v>
+      </c>
+      <c r="P263" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q263" t="str">
+        <v>0</v>
+      </c>
+      <c r="R263" t="str">
+        <v>0</v>
+      </c>
+      <c r="S263" t="str">
+        <v>0</v>
+      </c>
+      <c r="T263" t="str">
+        <v>0</v>
+      </c>
+      <c r="U263" t="str">
+        <v>2</v>
+      </c>
+      <c r="V263" t="str">
+        <v>0</v>
+      </c>
+      <c r="W263" t="str">
+        <v>1</v>
+      </c>
+      <c r="X263" t="str">
+        <v>5/17/26</v>
+      </c>
+      <c r="Y263" t="str">
+        <v>8/20/26</v>
+      </c>
+      <c r="Z263" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="AB263" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="AD263" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="AE263" t="str">
+        <v>Skipped: Intended practices disabled (program stage)</v>
+      </c>
+    </row>
+    <row r="264" xml:space="preserve">
+      <c r="A264" t="str">
+        <v>(1279)</v>
+      </c>
+      <c r="B264" t="str">
+        <v>(1) Viet Nga Group, (2) Việt Nga Group - HTX An Hoà</v>
+      </c>
+      <c r="C264" t="str">
+        <v>74137</v>
+      </c>
+      <c r="D264" t="str">
+        <v>832804033</v>
+      </c>
+      <c r="E264" t="str">
+        <v>ĐỖ VĂN THUM</v>
+      </c>
+      <c r="F264" t="str">
+        <v>HỢP TÁC XÃ NÔNG NGHIỆP AN HÒA</v>
+      </c>
+      <c r="J264" t="str" xml:space="preserve">
+        <v xml:space="preserve">✅ Residue removal // Thu gom rơm rạ_x000d_
+✅ Rate reduction // Giảm lượng phân bón_x000d_
+✅ Reduced planting density // Giảm mật độ trồng_x000d_
+✅ Irrigation Management // Quản lý tưới tiêu</v>
+      </c>
+      <c r="K264" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="L264" t="str">
+        <v>Male // Nam</v>
+      </c>
+      <c r="M264" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="N264" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O264" t="str">
+        <v>0</v>
+      </c>
+      <c r="P264" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q264" t="str">
+        <v>0</v>
+      </c>
+      <c r="R264" t="str">
+        <v>0</v>
+      </c>
+      <c r="S264" t="str">
+        <v>0</v>
+      </c>
+      <c r="T264" t="str">
+        <v>0</v>
+      </c>
+      <c r="U264" t="str">
+        <v>2</v>
+      </c>
+      <c r="V264" t="str">
+        <v>0</v>
+      </c>
+      <c r="W264" t="str">
+        <v>1</v>
+      </c>
+      <c r="X264" t="str">
+        <v>5/17/26</v>
+      </c>
+      <c r="Y264" t="str">
+        <v>8/20/26</v>
+      </c>
+      <c r="Z264" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="AB264" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="AD264" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="AE264" t="str">
+        <v>Skipped: Intended practices disabled (program stage)</v>
+      </c>
+    </row>
+    <row r="265" xml:space="preserve">
+      <c r="A265" t="str">
+        <v>(1280)</v>
+      </c>
+      <c r="B265" t="str">
+        <v>(1) Viet Nga Group, (2) Việt Nga Group - HTX An Hoà</v>
+      </c>
+      <c r="C265" t="str">
+        <v>74138</v>
+      </c>
+      <c r="D265" t="str">
+        <v>987650747</v>
+      </c>
+      <c r="E265" t="str">
+        <v>NGUYỄN VĂN TÀU</v>
+      </c>
+      <c r="F265" t="str">
+        <v>HỢP TÁC XÃ NÔNG NGHIỆP AN HÒA</v>
+      </c>
+      <c r="J265" t="str" xml:space="preserve">
+        <v xml:space="preserve">✅ Residue removal // Thu gom rơm rạ_x000d_
+✅ Rate reduction // Giảm lượng phân bón_x000d_
+✅ Reduced planting density // Giảm mật độ trồng_x000d_
+✅ Irrigation Management // Quản lý tưới tiêu</v>
+      </c>
+      <c r="K265" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="L265" t="str">
+        <v>Male // Nam</v>
+      </c>
+      <c r="M265" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="N265" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O265" t="str">
+        <v>0</v>
+      </c>
+      <c r="P265" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q265" t="str">
+        <v>0</v>
+      </c>
+      <c r="R265" t="str">
+        <v>0</v>
+      </c>
+      <c r="S265" t="str">
+        <v>0</v>
+      </c>
+      <c r="T265" t="str">
+        <v>0</v>
+      </c>
+      <c r="U265" t="str">
+        <v>2</v>
+      </c>
+      <c r="V265" t="str">
+        <v>0</v>
+      </c>
+      <c r="W265" t="str">
+        <v>1</v>
+      </c>
+      <c r="X265" t="str">
+        <v>5/17/26</v>
+      </c>
+      <c r="Y265" t="str">
+        <v>8/20/26</v>
+      </c>
+      <c r="Z265" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="AB265" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="AD265" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="AE265" t="str">
+        <v>Skipped: Intended practices disabled (program stage)</v>
+      </c>
+    </row>
+    <row r="266" xml:space="preserve">
+      <c r="A266" t="str">
+        <v>(1260)</v>
+      </c>
+      <c r="B266" t="str">
+        <v>(1) Viet Nga Group, (2) Việt Nga Group - HTX An Hoà</v>
+      </c>
+      <c r="C266" t="str">
+        <v>74118</v>
+      </c>
+      <c r="D266" t="str">
+        <v>917609986</v>
+      </c>
+      <c r="E266" t="str">
+        <v>NGUYỄN HÙNG SƠN</v>
+      </c>
+      <c r="F266" t="str">
+        <v>HỢP TÁC XÃ NÔNG NGHIỆP AN HÒA</v>
+      </c>
+      <c r="J266" t="str" xml:space="preserve">
+        <v xml:space="preserve">✅ Residue removal // Thu gom rơm rạ_x000d_
+✅ Rate reduction // Giảm lượng phân bón_x000d_
+✅ Reduced planting density // Giảm mật độ trồng_x000d_
+✅ Irrigation Management // Quản lý tưới tiêu</v>
+      </c>
+      <c r="K266" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="L266" t="str">
+        <v>Male // Nam</v>
+      </c>
+      <c r="M266" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="N266" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O266" t="str">
+        <v>0</v>
+      </c>
+      <c r="P266" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q266" t="str">
+        <v>0</v>
+      </c>
+      <c r="R266" t="str">
+        <v>0</v>
+      </c>
+      <c r="S266" t="str">
+        <v>0</v>
+      </c>
+      <c r="T266" t="str">
+        <v>0</v>
+      </c>
+      <c r="U266" t="str">
+        <v>3</v>
+      </c>
+      <c r="V266" t="str">
+        <v>0</v>
+      </c>
+      <c r="W266" t="str">
+        <v>2</v>
+      </c>
+      <c r="X266" t="str">
+        <v>5/17/26</v>
+      </c>
+      <c r="Y266" t="str">
+        <v>8/20/26</v>
+      </c>
+      <c r="Z266" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="AB266" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="AD266" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="AE266" t="str">
+        <v>Skipped: Intended practices disabled (program stage)</v>
+      </c>
+    </row>
+    <row r="267" xml:space="preserve">
+      <c r="A267" t="str">
+        <v>(1261)</v>
+      </c>
+      <c r="B267" t="str">
+        <v>(1) Viet Nga Group, (2) Việt Nga Group - HTX An Hoà</v>
+      </c>
+      <c r="C267" t="str">
+        <v>74119</v>
+      </c>
+      <c r="D267" t="str">
+        <v>977442419</v>
+      </c>
+      <c r="E267" t="str">
+        <v>LÊ VĂN NU</v>
+      </c>
+      <c r="F267" t="str">
+        <v>HỢP TÁC XÃ NÔNG NGHIỆP AN HÒA</v>
+      </c>
+      <c r="J267" t="str" xml:space="preserve">
+        <v xml:space="preserve">✅ Residue removal // Thu gom rơm rạ_x000d_
+✅ Rate reduction // Giảm lượng phân bón_x000d_
+✅ Reduced planting density // Giảm mật độ trồng_x000d_
+✅ Irrigation Management // Quản lý tưới tiêu</v>
+      </c>
+      <c r="K267" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="L267" t="str">
+        <v>Male // Nam</v>
+      </c>
+      <c r="M267" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="N267" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O267" t="str">
+        <v>0</v>
+      </c>
+      <c r="P267" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q267" t="str">
+        <v>0</v>
+      </c>
+      <c r="R267" t="str">
+        <v>0</v>
+      </c>
+      <c r="S267" t="str">
+        <v>0</v>
+      </c>
+      <c r="T267" t="str">
+        <v>0</v>
+      </c>
+      <c r="U267" t="str">
+        <v>3</v>
+      </c>
+      <c r="V267" t="str">
+        <v>0</v>
+      </c>
+      <c r="W267" t="str">
+        <v>2</v>
+      </c>
+      <c r="X267" t="str">
+        <v>5/17/26</v>
+      </c>
+      <c r="Y267" t="str">
+        <v>8/20/26</v>
+      </c>
+      <c r="Z267" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="AB267" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="AD267" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="AE267" t="str">
+        <v>Skipped: Intended practices disabled (program stage)</v>
+      </c>
+    </row>
+    <row r="268" xml:space="preserve">
+      <c r="A268" t="str">
+        <v>(1262)</v>
+      </c>
+      <c r="B268" t="str">
+        <v>(1) Viet Nga Group, (2) Việt Nga Group - HTX An Hoà</v>
+      </c>
+      <c r="C268" t="str">
+        <v>74120</v>
+      </c>
+      <c r="D268" t="str">
+        <v>385188053</v>
+      </c>
+      <c r="E268" t="str">
+        <v>LÊ VĂN DŨNG</v>
+      </c>
+      <c r="F268" t="str">
+        <v>HỢP TÁC XÃ NÔNG NGHIỆP AN HÒA</v>
+      </c>
+      <c r="J268" t="str" xml:space="preserve">
+        <v xml:space="preserve">✅ Residue removal // Thu gom rơm rạ_x000d_
+✅ Rate reduction // Giảm lượng phân bón_x000d_
+✅ Reduced planting density // Giảm mật độ trồng_x000d_
+✅ Irrigation Management // Quản lý tưới tiêu</v>
+      </c>
+      <c r="K268" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="L268" t="str">
+        <v>Male // Nam</v>
+      </c>
+      <c r="M268" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="N268" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O268" t="str">
+        <v>0</v>
+      </c>
+      <c r="P268" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q268" t="str">
+        <v>0</v>
+      </c>
+      <c r="R268" t="str">
+        <v>0</v>
+      </c>
+      <c r="S268" t="str">
+        <v>0</v>
+      </c>
+      <c r="T268" t="str">
+        <v>0</v>
+      </c>
+      <c r="U268" t="str">
+        <v>2</v>
+      </c>
+      <c r="V268" t="str">
+        <v>0</v>
+      </c>
+      <c r="W268" t="str">
+        <v>1</v>
+      </c>
+      <c r="X268" t="str">
+        <v>5/17/26</v>
+      </c>
+      <c r="Y268" t="str">
+        <v>8/20/26</v>
+      </c>
+      <c r="Z268" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="AB268" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="AD268" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="AE268" t="str">
+        <v>Skipped: Intended practices disabled (program stage)</v>
+      </c>
+    </row>
+    <row r="269" xml:space="preserve">
+      <c r="A269" t="str">
+        <v>(1263)</v>
+      </c>
+      <c r="B269" t="str">
+        <v>(1) Viet Nga Group, (2) Việt Nga Group - HTX An Hoà</v>
+      </c>
+      <c r="C269" t="str">
+        <v>74121</v>
+      </c>
+      <c r="D269" t="str">
+        <v>949463815</v>
+      </c>
+      <c r="E269" t="str">
+        <v>PHẠM VĂN BÌNH</v>
+      </c>
+      <c r="F269" t="str">
+        <v>HỢP TÁC XÃ NÔNG NGHIỆP AN HÒA</v>
+      </c>
+      <c r="J269" t="str" xml:space="preserve">
+        <v xml:space="preserve">✅ Residue removal // Thu gom rơm rạ_x000d_
+✅ Rate reduction // Giảm lượng phân bón_x000d_
+✅ Reduced planting density // Giảm mật độ trồng_x000d_
+✅ Irrigation Management // Quản lý tưới tiêu</v>
+      </c>
+      <c r="K269" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="L269" t="str">
+        <v>Male // Nam</v>
+      </c>
+      <c r="M269" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="N269" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O269" t="str">
+        <v>0</v>
+      </c>
+      <c r="P269" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q269" t="str">
+        <v>0</v>
+      </c>
+      <c r="R269" t="str">
+        <v>0</v>
+      </c>
+      <c r="S269" t="str">
+        <v>0</v>
+      </c>
+      <c r="T269" t="str">
+        <v>0</v>
+      </c>
+      <c r="U269" t="str">
+        <v>3</v>
+      </c>
+      <c r="V269" t="str">
+        <v>0</v>
+      </c>
+      <c r="W269" t="str">
+        <v>2</v>
+      </c>
+      <c r="X269" t="str">
+        <v>5/17/26</v>
+      </c>
+      <c r="Y269" t="str">
+        <v>8/20/26</v>
+      </c>
+      <c r="Z269" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="AB269" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="AD269" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="AE269" t="str">
+        <v>Skipped: Intended practices disabled (program stage)</v>
+      </c>
+    </row>
+    <row r="270" xml:space="preserve">
+      <c r="A270" t="str">
+        <v>(1260)</v>
+      </c>
+      <c r="B270" t="str">
+        <v>(1) Viet Nga Group, (2) Việt Nga Group - HTX An Hoà</v>
+      </c>
+      <c r="C270" t="str">
+        <v>74118</v>
+      </c>
+      <c r="D270" t="str">
+        <v>917609986</v>
+      </c>
+      <c r="E270" t="str">
+        <v>NGUYỄN HÙNG SƠN</v>
+      </c>
+      <c r="F270" t="str">
+        <v>HỢP TÁC XÃ NÔNG NGHIỆP AN HÒA</v>
+      </c>
+      <c r="J270" t="str" xml:space="preserve">
+        <v xml:space="preserve">✅ Residue removal // Thu gom rơm rạ_x000d_
+✅ Rate reduction // Giảm lượng phân bón_x000d_
+✅ Reduced planting density // Giảm mật độ trồng_x000d_
+✅ Irrigation Management // Quản lý tưới tiêu</v>
+      </c>
+      <c r="K270" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="L270" t="str">
+        <v>Male // Nam</v>
+      </c>
+      <c r="M270" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="N270" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O270" t="str">
+        <v>0</v>
+      </c>
+      <c r="P270" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q270" t="str">
+        <v>0</v>
+      </c>
+      <c r="R270" t="str">
+        <v>0</v>
+      </c>
+      <c r="S270" t="str">
+        <v>0</v>
+      </c>
+      <c r="T270" t="str">
+        <v>0</v>
+      </c>
+      <c r="U270" t="str">
+        <v>3</v>
+      </c>
+      <c r="V270" t="str">
+        <v>0</v>
+      </c>
+      <c r="W270" t="str">
+        <v>2</v>
+      </c>
+      <c r="X270" t="str">
+        <v>5/17/26</v>
+      </c>
+      <c r="Y270" t="str">
+        <v>8/20/26</v>
+      </c>
+      <c r="Z270" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="AB270" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="AD270" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="AE270" t="str">
+        <v>Skipped: Intended practices disabled (program stage)</v>
+      </c>
+    </row>
+    <row r="271" xml:space="preserve">
+      <c r="A271" t="str">
+        <v>(1261)</v>
+      </c>
+      <c r="B271" t="str">
+        <v>(1) Viet Nga Group, (2) Việt Nga Group - HTX An Hoà</v>
+      </c>
+      <c r="C271" t="str">
+        <v>74119</v>
+      </c>
+      <c r="D271" t="str">
+        <v>977442419</v>
+      </c>
+      <c r="E271" t="str">
+        <v>LÊ VĂN NU</v>
+      </c>
+      <c r="F271" t="str">
+        <v>HỢP TÁC XÃ NÔNG NGHIỆP AN HÒA</v>
+      </c>
+      <c r="J271" t="str" xml:space="preserve">
+        <v xml:space="preserve">✅ Residue removal // Thu gom rơm rạ_x000d_
+✅ Rate reduction // Giảm lượng phân bón_x000d_
+✅ Reduced planting density // Giảm mật độ trồng_x000d_
+✅ Irrigation Management // Quản lý tưới tiêu</v>
+      </c>
+      <c r="K271" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="L271" t="str">
+        <v>Male // Nam</v>
+      </c>
+      <c r="M271" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="N271" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O271" t="str">
+        <v>0</v>
+      </c>
+      <c r="P271" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q271" t="str">
+        <v>0</v>
+      </c>
+      <c r="R271" t="str">
+        <v>0</v>
+      </c>
+      <c r="S271" t="str">
+        <v>0</v>
+      </c>
+      <c r="T271" t="str">
+        <v>0</v>
+      </c>
+      <c r="U271" t="str">
+        <v>3</v>
+      </c>
+      <c r="V271" t="str">
+        <v>0</v>
+      </c>
+      <c r="W271" t="str">
+        <v>2</v>
+      </c>
+      <c r="X271" t="str">
+        <v>5/17/26</v>
+      </c>
+      <c r="Y271" t="str">
+        <v>8/20/26</v>
+      </c>
+      <c r="Z271" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="AB271" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="AD271" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="AE271" t="str">
+        <v>Skipped: Intended practices disabled (program stage)</v>
+      </c>
+    </row>
+    <row r="272" xml:space="preserve">
+      <c r="A272" t="str">
+        <v>(1262)</v>
+      </c>
+      <c r="B272" t="str">
+        <v>(1) Viet Nga Group, (2) Việt Nga Group - HTX An Hoà</v>
+      </c>
+      <c r="C272" t="str">
+        <v>74120</v>
+      </c>
+      <c r="D272" t="str">
+        <v>385188053</v>
+      </c>
+      <c r="E272" t="str">
+        <v>LÊ VĂN DŨNG</v>
+      </c>
+      <c r="F272" t="str">
+        <v>HỢP TÁC XÃ NÔNG NGHIỆP AN HÒA</v>
+      </c>
+      <c r="J272" t="str" xml:space="preserve">
+        <v xml:space="preserve">✅ Residue removal // Thu gom rơm rạ_x000d_
+✅ Rate reduction // Giảm lượng phân bón_x000d_
+✅ Reduced planting density // Giảm mật độ trồng_x000d_
+✅ Irrigation Management // Quản lý tưới tiêu</v>
+      </c>
+      <c r="K272" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="L272" t="str">
+        <v>Male // Nam</v>
+      </c>
+      <c r="M272" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="N272" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O272" t="str">
+        <v>0</v>
+      </c>
+      <c r="P272" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q272" t="str">
+        <v>0</v>
+      </c>
+      <c r="R272" t="str">
+        <v>0</v>
+      </c>
+      <c r="S272" t="str">
+        <v>0</v>
+      </c>
+      <c r="T272" t="str">
+        <v>0</v>
+      </c>
+      <c r="U272" t="str">
+        <v>2</v>
+      </c>
+      <c r="V272" t="str">
+        <v>0</v>
+      </c>
+      <c r="W272" t="str">
+        <v>1</v>
+      </c>
+      <c r="X272" t="str">
+        <v>5/17/26</v>
+      </c>
+      <c r="Y272" t="str">
+        <v>8/20/26</v>
+      </c>
+      <c r="Z272" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="AB272" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="AD272" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="AE272" t="str">
+        <v>Skipped: Intended practices disabled (program stage)</v>
+      </c>
+    </row>
+    <row r="273" xml:space="preserve">
+      <c r="A273" t="str">
+        <v>(1263)</v>
+      </c>
+      <c r="B273" t="str">
+        <v>(1) Viet Nga Group, (2) Việt Nga Group - HTX An Hoà</v>
+      </c>
+      <c r="C273" t="str">
+        <v>74121</v>
+      </c>
+      <c r="D273" t="str">
+        <v>949463815</v>
+      </c>
+      <c r="E273" t="str">
+        <v>PHẠM VĂN BÌNH</v>
+      </c>
+      <c r="F273" t="str">
+        <v>HỢP TÁC XÃ NÔNG NGHIỆP AN HÒA</v>
+      </c>
+      <c r="J273" t="str" xml:space="preserve">
+        <v xml:space="preserve">✅ Residue removal // Thu gom rơm rạ_x000d_
+✅ Rate reduction // Giảm lượng phân bón_x000d_
+✅ Reduced planting density // Giảm mật độ trồng_x000d_
+✅ Irrigation Management // Quản lý tưới tiêu</v>
+      </c>
+      <c r="K273" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="L273" t="str">
+        <v>Male // Nam</v>
+      </c>
+      <c r="M273" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="N273" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O273" t="str">
+        <v>0</v>
+      </c>
+      <c r="P273" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q273" t="str">
+        <v>0</v>
+      </c>
+      <c r="R273" t="str">
+        <v>0</v>
+      </c>
+      <c r="S273" t="str">
+        <v>0</v>
+      </c>
+      <c r="T273" t="str">
+        <v>0</v>
+      </c>
+      <c r="U273" t="str">
+        <v>3</v>
+      </c>
+      <c r="V273" t="str">
+        <v>0</v>
+      </c>
+      <c r="W273" t="str">
+        <v>2</v>
+      </c>
+      <c r="X273" t="str">
+        <v>5/17/26</v>
+      </c>
+      <c r="Y273" t="str">
+        <v>8/20/26</v>
+      </c>
+      <c r="Z273" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="AB273" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="AD273" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="AE273" t="str">
+        <v>Skipped: Intended practices disabled (program stage)</v>
+      </c>
+    </row>
+    <row r="274" xml:space="preserve">
+      <c r="A274" t="str">
+        <v>(1264)</v>
+      </c>
+      <c r="B274" t="str">
+        <v>(1) Viet Nga Group, (2) Việt Nga Group - HTX An Hoà</v>
+      </c>
+      <c r="C274" t="str">
+        <v>74122</v>
+      </c>
+      <c r="D274" t="str">
+        <v>355206824</v>
+      </c>
+      <c r="E274" t="str">
+        <v>ĐẶNG THỊ SANG</v>
+      </c>
+      <c r="F274" t="str">
+        <v>HỢP TÁC XÃ NÔNG NGHIỆP AN HÒA</v>
+      </c>
+      <c r="J274" t="str" xml:space="preserve">
+        <v xml:space="preserve">✅ Residue removal // Thu gom rơm rạ_x000d_
+✅ Rate reduction // Giảm lượng phân bón_x000d_
+✅ Reduced planting density // Giảm mật độ trồng_x000d_
+✅ Irrigation Management // Quản lý tưới tiêu</v>
+      </c>
+      <c r="K274" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="L274" t="str">
+        <v>Female // Nữ</v>
+      </c>
+      <c r="M274" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="N274" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O274" t="str">
+        <v>1</v>
+      </c>
+      <c r="P274" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q274" t="str">
+        <v>0</v>
+      </c>
+      <c r="R274" t="str">
+        <v>0</v>
+      </c>
+      <c r="S274" t="str">
+        <v>0</v>
+      </c>
+      <c r="T274" t="str">
+        <v>0</v>
+      </c>
+      <c r="U274" t="str">
+        <v>2</v>
+      </c>
+      <c r="V274" t="str">
+        <v>0</v>
+      </c>
+      <c r="W274" t="str">
+        <v>1</v>
+      </c>
+      <c r="X274" t="str">
+        <v>5/17/26</v>
+      </c>
+      <c r="Y274" t="str">
+        <v>8/20/26</v>
+      </c>
+      <c r="Z274" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="AB274" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="AD274" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="AE274" t="str">
+        <v>Skipped: Intended practices disabled (program stage)</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:AE193"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:AE274"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/cypress/fixtures/run-log.xlsx
+++ b/cypress/fixtures/run-log.xlsx
@@ -404,7 +404,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AE599"/>
+  <dimension ref="A1:AE603"/>
   <sheetData>
     <row r="1" xml:space="preserve">
       <c r="A1" t="str" xml:space="preserve">
@@ -49493,9 +49493,317 @@
         <v/>
       </c>
     </row>
+    <row r="600">
+      <c r="A600" t="str">
+        <v>(2058)</v>
+      </c>
+      <c r="B600" t="str">
+        <v>(1) Viet Nga Group, (2) Viet Nga Group - NN số 2</v>
+      </c>
+      <c r="C600" t="str">
+        <v>65803</v>
+      </c>
+      <c r="D600" t="str">
+        <v>349539663</v>
+      </c>
+      <c r="E600" t="str">
+        <v>HUỲNH THỊ DUNG</v>
+      </c>
+      <c r="F600" t="str">
+        <v>HỢP TÁC XÃ NÔNG NGHIỆP SỐ 2</v>
+      </c>
+      <c r="K600" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="L600" t="str">
+        <v>Female // Nữ</v>
+      </c>
+      <c r="M600" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="N600" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O600" t="str">
+        <v>1</v>
+      </c>
+      <c r="P600" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q600" t="str">
+        <v>0</v>
+      </c>
+      <c r="R600" t="str">
+        <v>0</v>
+      </c>
+      <c r="S600" t="str">
+        <v>0</v>
+      </c>
+      <c r="T600" t="str">
+        <v>0</v>
+      </c>
+      <c r="U600" t="str">
+        <v>3</v>
+      </c>
+      <c r="V600" t="str">
+        <v>0</v>
+      </c>
+      <c r="W600" t="str">
+        <v>2</v>
+      </c>
+      <c r="X600" t="str">
+        <v>4/28/26</v>
+      </c>
+      <c r="Y600" t="str">
+        <v>8/1/26</v>
+      </c>
+      <c r="Z600" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="AB600" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="AD600" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="AE600" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="601">
+      <c r="A601" t="str">
+        <v>(2059)</v>
+      </c>
+      <c r="B601" t="str">
+        <v>(1) Viet Nga Group, (2) Viet Nga Group - NN số 2</v>
+      </c>
+      <c r="C601" t="str">
+        <v>65804</v>
+      </c>
+      <c r="D601" t="str">
+        <v>975405539</v>
+      </c>
+      <c r="E601" t="str">
+        <v>TRẦN THỊ BÉ</v>
+      </c>
+      <c r="F601" t="str">
+        <v>HỢP TÁC XÃ NÔNG NGHIỆP SỐ 2</v>
+      </c>
+      <c r="K601" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="L601" t="str">
+        <v>Female // Nữ</v>
+      </c>
+      <c r="M601" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="N601" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O601" t="str">
+        <v>1</v>
+      </c>
+      <c r="P601" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q601" t="str">
+        <v>0</v>
+      </c>
+      <c r="R601" t="str">
+        <v>0</v>
+      </c>
+      <c r="S601" t="str">
+        <v>0</v>
+      </c>
+      <c r="T601" t="str">
+        <v>0</v>
+      </c>
+      <c r="U601" t="str">
+        <v>4</v>
+      </c>
+      <c r="V601" t="str">
+        <v>0</v>
+      </c>
+      <c r="W601" t="str">
+        <v>3</v>
+      </c>
+      <c r="X601" t="str">
+        <v>4/28/26</v>
+      </c>
+      <c r="Y601" t="str">
+        <v>8/1/26</v>
+      </c>
+      <c r="Z601" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="AB601" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="AD601" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="AE601" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="602">
+      <c r="A602" t="str">
+        <v>(2060)</v>
+      </c>
+      <c r="B602" t="str">
+        <v>(1) Viet Nga Group, (2) Viet Nga Group - NN số 2</v>
+      </c>
+      <c r="C602" t="str">
+        <v>65812</v>
+      </c>
+      <c r="D602" t="str">
+        <v>326318151</v>
+      </c>
+      <c r="E602" t="str">
+        <v>NGUYỄN VĂN TRẠNG</v>
+      </c>
+      <c r="F602" t="str">
+        <v>HỢP TÁC XÃ NÔNG NGHIỆP SỐ 2</v>
+      </c>
+      <c r="K602" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="L602" t="str">
+        <v>Male // Nam</v>
+      </c>
+      <c r="M602" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="N602" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O602" t="str">
+        <v>0</v>
+      </c>
+      <c r="P602" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q602" t="str">
+        <v>0</v>
+      </c>
+      <c r="R602" t="str">
+        <v>0</v>
+      </c>
+      <c r="S602" t="str">
+        <v>0</v>
+      </c>
+      <c r="T602" t="str">
+        <v>0</v>
+      </c>
+      <c r="U602" t="str">
+        <v>3</v>
+      </c>
+      <c r="V602" t="str">
+        <v>0</v>
+      </c>
+      <c r="W602" t="str">
+        <v>2</v>
+      </c>
+      <c r="X602" t="str">
+        <v>4/28/26</v>
+      </c>
+      <c r="Y602" t="str">
+        <v>8/1/26</v>
+      </c>
+      <c r="Z602" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="AB602" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="AD602" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="AE602" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="603">
+      <c r="A603" t="str">
+        <v>(2063)</v>
+      </c>
+      <c r="B603" t="str">
+        <v>(1) Viet Nga Group, (2) Viet Nga Group - NN số 2</v>
+      </c>
+      <c r="C603" t="str">
+        <v>65815</v>
+      </c>
+      <c r="D603" t="str">
+        <v>975112490</v>
+      </c>
+      <c r="E603" t="str">
+        <v>LÊ THỊ CẢNH</v>
+      </c>
+      <c r="F603" t="str">
+        <v>HỢP TÁC XÃ NÔNG NGHIỆP SỐ 2</v>
+      </c>
+      <c r="K603" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="L603" t="str">
+        <v>Female // Nữ</v>
+      </c>
+      <c r="M603" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="N603" t="str">
+        <v>NO</v>
+      </c>
+      <c r="O603" t="str">
+        <v>1</v>
+      </c>
+      <c r="P603" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q603" t="str">
+        <v>0</v>
+      </c>
+      <c r="R603" t="str">
+        <v>0</v>
+      </c>
+      <c r="S603" t="str">
+        <v>0</v>
+      </c>
+      <c r="T603" t="str">
+        <v>0</v>
+      </c>
+      <c r="U603" t="str">
+        <v>3</v>
+      </c>
+      <c r="V603" t="str">
+        <v>0</v>
+      </c>
+      <c r="W603" t="str">
+        <v>2</v>
+      </c>
+      <c r="X603" t="str">
+        <v>4/28/26</v>
+      </c>
+      <c r="Y603" t="str">
+        <v>8/1/26</v>
+      </c>
+      <c r="Z603" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="AB603" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="AD603" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="AE603" t="str">
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:AE599"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:AE603"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/cypress/fixtures/run-log.xlsx
+++ b/cypress/fixtures/run-log.xlsx
@@ -404,7 +404,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AE603"/>
+  <dimension ref="A1:AE610"/>
   <sheetData>
     <row r="1" xml:space="preserve">
       <c r="A1" t="str" xml:space="preserve">
@@ -49801,9 +49801,563 @@
         <v/>
       </c>
     </row>
+    <row r="604">
+      <c r="A604" t="str">
+        <v>(2083)</v>
+      </c>
+      <c r="B604" t="str">
+        <v>(1) Viet Nga Group, (2) Viet Nga Group - NN số 2</v>
+      </c>
+      <c r="C604" t="str">
+        <v>65868</v>
+      </c>
+      <c r="D604" t="str">
+        <v>346700178</v>
+      </c>
+      <c r="E604" t="str">
+        <v>VÕ THỊ MẠNH</v>
+      </c>
+      <c r="F604" t="str">
+        <v>Intensive rice production // Trồng lúa thâm canh</v>
+      </c>
+      <c r="G604" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="H604" t="str">
+        <v>Female // Nữ</v>
+      </c>
+      <c r="I604" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="J604" t="str">
+        <v>NO</v>
+      </c>
+      <c r="K604" t="str">
+        <v>1</v>
+      </c>
+      <c r="L604" t="str">
+        <v>0</v>
+      </c>
+      <c r="M604" t="str">
+        <v>0</v>
+      </c>
+      <c r="N604" t="str">
+        <v>0</v>
+      </c>
+      <c r="O604" t="str">
+        <v>0</v>
+      </c>
+      <c r="P604" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q604" t="str">
+        <v>3</v>
+      </c>
+      <c r="R604" t="str">
+        <v>0</v>
+      </c>
+      <c r="S604" t="str">
+        <v>2</v>
+      </c>
+      <c r="T604" t="str">
+        <v>4/28/26</v>
+      </c>
+      <c r="U604" t="str">
+        <v>8/1/26</v>
+      </c>
+      <c r="V604" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="W604" t="str">
+        <v>NGÂN</v>
+      </c>
+      <c r="X604" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="Z604" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="AA604" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="605">
+      <c r="A605" t="str">
+        <v>(2086)</v>
+      </c>
+      <c r="B605" t="str">
+        <v>(1) Viet Nga Group, (2) Viet Nga Group - NN số 2</v>
+      </c>
+      <c r="C605" t="str">
+        <v>65871</v>
+      </c>
+      <c r="D605" t="str">
+        <v>326167990</v>
+      </c>
+      <c r="E605" t="str">
+        <v>LÊ THỊ OANH</v>
+      </c>
+      <c r="F605" t="str">
+        <v>Intensive rice production // Trồng lúa thâm canh</v>
+      </c>
+      <c r="G605" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="H605" t="str">
+        <v>Female // Nữ</v>
+      </c>
+      <c r="I605" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="J605" t="str">
+        <v>NO</v>
+      </c>
+      <c r="K605" t="str">
+        <v>1</v>
+      </c>
+      <c r="L605" t="str">
+        <v>0</v>
+      </c>
+      <c r="M605" t="str">
+        <v>0</v>
+      </c>
+      <c r="N605" t="str">
+        <v>0</v>
+      </c>
+      <c r="O605" t="str">
+        <v>0</v>
+      </c>
+      <c r="P605" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q605" t="str">
+        <v>3</v>
+      </c>
+      <c r="R605" t="str">
+        <v>0</v>
+      </c>
+      <c r="S605" t="str">
+        <v>2</v>
+      </c>
+      <c r="T605" t="str">
+        <v>4/28/26</v>
+      </c>
+      <c r="U605" t="str">
+        <v>8/1/26</v>
+      </c>
+      <c r="V605" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="W605" t="str">
+        <v>NGÂN</v>
+      </c>
+      <c r="X605" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="Z605" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="AA605" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="606">
+      <c r="A606" t="str">
+        <v>(2088)</v>
+      </c>
+      <c r="B606" t="str">
+        <v>(1) Viet Nga Group, (2) Viet Nga Group - NN số 2</v>
+      </c>
+      <c r="C606" t="str">
+        <v>65873</v>
+      </c>
+      <c r="D606" t="str">
+        <v>333342462</v>
+      </c>
+      <c r="E606" t="str">
+        <v>LÊ TẤN TÀI</v>
+      </c>
+      <c r="F606" t="str">
+        <v>Intensive rice production // Trồng lúa thâm canh</v>
+      </c>
+      <c r="G606" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="H606" t="str">
+        <v>Male // Nam</v>
+      </c>
+      <c r="I606" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="J606" t="str">
+        <v>NO</v>
+      </c>
+      <c r="K606" t="str">
+        <v>0</v>
+      </c>
+      <c r="L606" t="str">
+        <v>0</v>
+      </c>
+      <c r="M606" t="str">
+        <v>0</v>
+      </c>
+      <c r="N606" t="str">
+        <v>0</v>
+      </c>
+      <c r="O606" t="str">
+        <v>0</v>
+      </c>
+      <c r="P606" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q606" t="str">
+        <v>2</v>
+      </c>
+      <c r="R606" t="str">
+        <v>0</v>
+      </c>
+      <c r="S606" t="str">
+        <v>1</v>
+      </c>
+      <c r="T606" t="str">
+        <v>4/28/26</v>
+      </c>
+      <c r="U606" t="str">
+        <v>8/1/26</v>
+      </c>
+      <c r="V606" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="W606" t="str">
+        <v>NGÂN</v>
+      </c>
+      <c r="X606" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="Z606" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="AA606" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="607">
+      <c r="A607" t="str">
+        <v>(2108)</v>
+      </c>
+      <c r="B607" t="str">
+        <v>(1) Viet Nga Group, (2) Viet Nga Group - NN số 2</v>
+      </c>
+      <c r="C607" t="str">
+        <v>65922</v>
+      </c>
+      <c r="D607" t="str">
+        <v>354342105</v>
+      </c>
+      <c r="E607" t="str">
+        <v>GIANG VĂN HỌT</v>
+      </c>
+      <c r="F607" t="str">
+        <v>Intensive rice production // Trồng lúa thâm canh</v>
+      </c>
+      <c r="G607" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="H607" t="str">
+        <v>Male // Nam</v>
+      </c>
+      <c r="I607" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="J607" t="str">
+        <v>NO</v>
+      </c>
+      <c r="K607" t="str">
+        <v>0</v>
+      </c>
+      <c r="L607" t="str">
+        <v>0</v>
+      </c>
+      <c r="M607" t="str">
+        <v>0</v>
+      </c>
+      <c r="N607" t="str">
+        <v>0</v>
+      </c>
+      <c r="O607" t="str">
+        <v>0</v>
+      </c>
+      <c r="P607" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q607" t="str">
+        <v>4</v>
+      </c>
+      <c r="R607" t="str">
+        <v>0</v>
+      </c>
+      <c r="S607" t="str">
+        <v>3</v>
+      </c>
+      <c r="T607" t="str">
+        <v>4/28/26</v>
+      </c>
+      <c r="U607" t="str">
+        <v>8/1/26</v>
+      </c>
+      <c r="V607" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="W607" t="str">
+        <v>NGÂN</v>
+      </c>
+      <c r="X607" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="Z607" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="AA607" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="608">
+      <c r="A608" t="str">
+        <v>(2109)</v>
+      </c>
+      <c r="B608" t="str">
+        <v>(1) Viet Nga Group, (2) Viet Nga Group - NN số 2</v>
+      </c>
+      <c r="C608" t="str">
+        <v>65923</v>
+      </c>
+      <c r="D608" t="str">
+        <v>748939500</v>
+      </c>
+      <c r="E608" t="str">
+        <v>HỒ VĂN LONG</v>
+      </c>
+      <c r="F608" t="str">
+        <v>Intensive rice production // Trồng lúa thâm canh</v>
+      </c>
+      <c r="G608" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="H608" t="str">
+        <v>Male // Nam</v>
+      </c>
+      <c r="I608" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="J608" t="str">
+        <v>NO</v>
+      </c>
+      <c r="K608" t="str">
+        <v>0</v>
+      </c>
+      <c r="L608" t="str">
+        <v>0</v>
+      </c>
+      <c r="M608" t="str">
+        <v>0</v>
+      </c>
+      <c r="N608" t="str">
+        <v>0</v>
+      </c>
+      <c r="O608" t="str">
+        <v>0</v>
+      </c>
+      <c r="P608" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q608" t="str">
+        <v>4</v>
+      </c>
+      <c r="R608" t="str">
+        <v>0</v>
+      </c>
+      <c r="S608" t="str">
+        <v>3</v>
+      </c>
+      <c r="T608" t="str">
+        <v>4/28/26</v>
+      </c>
+      <c r="U608" t="str">
+        <v>8/1/26</v>
+      </c>
+      <c r="V608" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="W608" t="str">
+        <v>NGÂN</v>
+      </c>
+      <c r="X608" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="Z608" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="AA608" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="609">
+      <c r="A609" t="str">
+        <v>(3376)</v>
+      </c>
+      <c r="B609" t="str">
+        <v>(1) Viet Nga Group, (2) Viet Nga Group - HTX Tân Hà B</v>
+      </c>
+      <c r="C609" t="str">
+        <v>79855</v>
+      </c>
+      <c r="D609" t="str">
+        <v>974252489</v>
+      </c>
+      <c r="E609" t="str">
+        <v>TRƯƠNG THỊ TUYẾT NHUNG</v>
+      </c>
+      <c r="F609" t="str">
+        <v>Intensive rice production // Trồng lúa thâm canh</v>
+      </c>
+      <c r="G609" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="H609" t="str">
+        <v>Female // Nữ</v>
+      </c>
+      <c r="I609" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="J609" t="str">
+        <v>NO</v>
+      </c>
+      <c r="K609" t="str">
+        <v>1</v>
+      </c>
+      <c r="L609" t="str">
+        <v>0</v>
+      </c>
+      <c r="M609" t="str">
+        <v>0</v>
+      </c>
+      <c r="N609" t="str">
+        <v>0</v>
+      </c>
+      <c r="O609" t="str">
+        <v>0</v>
+      </c>
+      <c r="P609" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q609" t="str">
+        <v>2</v>
+      </c>
+      <c r="R609" t="str">
+        <v>0</v>
+      </c>
+      <c r="S609" t="str">
+        <v>1</v>
+      </c>
+      <c r="T609" t="str">
+        <v>5/10/26</v>
+      </c>
+      <c r="U609" t="str">
+        <v>8/15/26</v>
+      </c>
+      <c r="V609" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="X609" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="Z609" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="AA609" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="610">
+      <c r="A610" t="str">
+        <v>(3376)</v>
+      </c>
+      <c r="B610" t="str">
+        <v>(1) Viet Nga Group, (2) Viet Nga Group - HTX Tân Hà B</v>
+      </c>
+      <c r="C610" t="str">
+        <v>79855</v>
+      </c>
+      <c r="D610" t="str">
+        <v>974252489</v>
+      </c>
+      <c r="E610" t="str">
+        <v>TRƯƠNG THỊ TUYẾT NHUNG</v>
+      </c>
+      <c r="F610" t="str">
+        <v>Intensive rice production // Trồng lúa thâm canh</v>
+      </c>
+      <c r="G610" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="H610" t="str">
+        <v>Female // Nữ</v>
+      </c>
+      <c r="I610" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="J610" t="str">
+        <v>NO</v>
+      </c>
+      <c r="K610" t="str">
+        <v>1</v>
+      </c>
+      <c r="L610" t="str">
+        <v>0</v>
+      </c>
+      <c r="M610" t="str">
+        <v>0</v>
+      </c>
+      <c r="N610" t="str">
+        <v>0</v>
+      </c>
+      <c r="O610" t="str">
+        <v>0</v>
+      </c>
+      <c r="P610" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q610" t="str">
+        <v>2</v>
+      </c>
+      <c r="R610" t="str">
+        <v>0</v>
+      </c>
+      <c r="S610" t="str">
+        <v>1</v>
+      </c>
+      <c r="T610" t="str">
+        <v>5/10/26</v>
+      </c>
+      <c r="U610" t="str">
+        <v>8/15/26</v>
+      </c>
+      <c r="V610" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="X610" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="Z610" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="AA610" t="str">
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:AE603"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:AE610"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/cypress/fixtures/run-log.xlsx
+++ b/cypress/fixtures/run-log.xlsx
@@ -404,7 +404,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AE610"/>
+  <dimension ref="A1:AE611"/>
   <sheetData>
     <row r="1" xml:space="preserve">
       <c r="A1" t="str" xml:space="preserve">
@@ -50355,9 +50355,86 @@
         <v/>
       </c>
     </row>
+    <row r="611">
+      <c r="A611" t="str">
+        <v>(1516)</v>
+      </c>
+      <c r="B611" t="str">
+        <v>(1) Viet Nga Group, (2) Viet Nga Group - HTX NN 285</v>
+      </c>
+      <c r="C611" t="str">
+        <v>80016</v>
+      </c>
+      <c r="D611" t="str">
+        <v>393822588</v>
+      </c>
+      <c r="E611" t="str">
+        <v>NGUYỄN NGỌC NAM</v>
+      </c>
+      <c r="F611" t="str">
+        <v>Intensive rice production // Trồng lúa thâm canh</v>
+      </c>
+      <c r="G611" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="H611" t="str">
+        <v>Male // Nam</v>
+      </c>
+      <c r="I611" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="J611" t="str">
+        <v>NO</v>
+      </c>
+      <c r="K611" t="str">
+        <v>0</v>
+      </c>
+      <c r="L611" t="str">
+        <v>0</v>
+      </c>
+      <c r="M611" t="str">
+        <v>0</v>
+      </c>
+      <c r="N611" t="str">
+        <v>0</v>
+      </c>
+      <c r="O611" t="str">
+        <v>0</v>
+      </c>
+      <c r="P611" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q611" t="str">
+        <v>2</v>
+      </c>
+      <c r="R611" t="str">
+        <v>0</v>
+      </c>
+      <c r="S611" t="str">
+        <v>1</v>
+      </c>
+      <c r="T611" t="str">
+        <v>5/31/26</v>
+      </c>
+      <c r="U611" t="str">
+        <v>9/25/26</v>
+      </c>
+      <c r="V611" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="X611" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="Z611" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="AA611" t="str">
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:AE610"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:AE611"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/cypress/fixtures/run-log.xlsx
+++ b/cypress/fixtures/run-log.xlsx
@@ -404,7 +404,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AE611"/>
+  <dimension ref="A1:AE670"/>
   <sheetData>
     <row r="1" xml:space="preserve">
       <c r="A1" t="str" xml:space="preserve">
@@ -50432,9 +50432,4726 @@
         <v/>
       </c>
     </row>
+    <row r="612">
+      <c r="A612" t="str">
+        <v>(2083)</v>
+      </c>
+      <c r="B612" t="str">
+        <v>(1) Viet Nga Group, (2) Viet Nga Group - NN số 2</v>
+      </c>
+      <c r="C612" t="str">
+        <v>65868</v>
+      </c>
+      <c r="D612" t="str">
+        <v>346700178</v>
+      </c>
+      <c r="E612" t="str">
+        <v>VÕ THỊ MẠNH</v>
+      </c>
+      <c r="F612" t="str">
+        <v>Intensive rice production // Trồng lúa thâm canh</v>
+      </c>
+      <c r="G612" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="H612" t="str">
+        <v>Female // Nữ</v>
+      </c>
+      <c r="I612" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="J612" t="str">
+        <v>NO</v>
+      </c>
+      <c r="K612" t="str">
+        <v>1</v>
+      </c>
+      <c r="L612" t="str">
+        <v>0</v>
+      </c>
+      <c r="M612" t="str">
+        <v>0</v>
+      </c>
+      <c r="N612" t="str">
+        <v>0</v>
+      </c>
+      <c r="O612" t="str">
+        <v>0</v>
+      </c>
+      <c r="P612" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q612" t="str">
+        <v>3</v>
+      </c>
+      <c r="R612" t="str">
+        <v>0</v>
+      </c>
+      <c r="S612" t="str">
+        <v>2</v>
+      </c>
+      <c r="T612" t="str">
+        <v>4/28/26</v>
+      </c>
+      <c r="U612" t="str">
+        <v>8/1/26</v>
+      </c>
+      <c r="V612" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="W612" t="str">
+        <v>NGÂN</v>
+      </c>
+      <c r="X612" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="Z612" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="AA612" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="613">
+      <c r="A613" t="str">
+        <v>(2086)</v>
+      </c>
+      <c r="B613" t="str">
+        <v>(1) Viet Nga Group, (2) Viet Nga Group - NN số 2</v>
+      </c>
+      <c r="C613" t="str">
+        <v>65871</v>
+      </c>
+      <c r="D613" t="str">
+        <v>326167990</v>
+      </c>
+      <c r="E613" t="str">
+        <v>LÊ THỊ OANH</v>
+      </c>
+      <c r="F613" t="str">
+        <v>Intensive rice production // Trồng lúa thâm canh</v>
+      </c>
+      <c r="G613" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="H613" t="str">
+        <v>Female // Nữ</v>
+      </c>
+      <c r="I613" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="J613" t="str">
+        <v>NO</v>
+      </c>
+      <c r="K613" t="str">
+        <v>1</v>
+      </c>
+      <c r="L613" t="str">
+        <v>0</v>
+      </c>
+      <c r="M613" t="str">
+        <v>0</v>
+      </c>
+      <c r="N613" t="str">
+        <v>0</v>
+      </c>
+      <c r="O613" t="str">
+        <v>0</v>
+      </c>
+      <c r="P613" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q613" t="str">
+        <v>3</v>
+      </c>
+      <c r="R613" t="str">
+        <v>0</v>
+      </c>
+      <c r="S613" t="str">
+        <v>2</v>
+      </c>
+      <c r="T613" t="str">
+        <v>4/28/26</v>
+      </c>
+      <c r="U613" t="str">
+        <v>8/1/26</v>
+      </c>
+      <c r="V613" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="W613" t="str">
+        <v>NGÂN</v>
+      </c>
+      <c r="X613" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="Z613" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="AA613" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="614">
+      <c r="A614" t="str">
+        <v>(2088)</v>
+      </c>
+      <c r="B614" t="str">
+        <v>(1) Viet Nga Group, (2) Viet Nga Group - NN số 2</v>
+      </c>
+      <c r="C614" t="str">
+        <v>65873</v>
+      </c>
+      <c r="D614" t="str">
+        <v>333342462</v>
+      </c>
+      <c r="E614" t="str">
+        <v>LÊ TẤN TÀI</v>
+      </c>
+      <c r="F614" t="str">
+        <v>Intensive rice production // Trồng lúa thâm canh</v>
+      </c>
+      <c r="G614" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="H614" t="str">
+        <v>Male // Nam</v>
+      </c>
+      <c r="I614" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="J614" t="str">
+        <v>NO</v>
+      </c>
+      <c r="K614" t="str">
+        <v>0</v>
+      </c>
+      <c r="L614" t="str">
+        <v>0</v>
+      </c>
+      <c r="M614" t="str">
+        <v>0</v>
+      </c>
+      <c r="N614" t="str">
+        <v>0</v>
+      </c>
+      <c r="O614" t="str">
+        <v>0</v>
+      </c>
+      <c r="P614" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q614" t="str">
+        <v>2</v>
+      </c>
+      <c r="R614" t="str">
+        <v>0</v>
+      </c>
+      <c r="S614" t="str">
+        <v>1</v>
+      </c>
+      <c r="T614" t="str">
+        <v>4/28/26</v>
+      </c>
+      <c r="U614" t="str">
+        <v>8/1/26</v>
+      </c>
+      <c r="V614" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="W614" t="str">
+        <v>NGÂN</v>
+      </c>
+      <c r="X614" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="Z614" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="AA614" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="615">
+      <c r="A615" t="str">
+        <v>(2108)</v>
+      </c>
+      <c r="B615" t="str">
+        <v>(1) Viet Nga Group, (2) Viet Nga Group - NN số 2</v>
+      </c>
+      <c r="C615" t="str">
+        <v>65922</v>
+      </c>
+      <c r="D615" t="str">
+        <v>354342105</v>
+      </c>
+      <c r="E615" t="str">
+        <v>GIANG VĂN HỌT</v>
+      </c>
+      <c r="F615" t="str">
+        <v>Intensive rice production // Trồng lúa thâm canh</v>
+      </c>
+      <c r="G615" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="H615" t="str">
+        <v>Male // Nam</v>
+      </c>
+      <c r="I615" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="J615" t="str">
+        <v>NO</v>
+      </c>
+      <c r="K615" t="str">
+        <v>0</v>
+      </c>
+      <c r="L615" t="str">
+        <v>0</v>
+      </c>
+      <c r="M615" t="str">
+        <v>0</v>
+      </c>
+      <c r="N615" t="str">
+        <v>0</v>
+      </c>
+      <c r="O615" t="str">
+        <v>0</v>
+      </c>
+      <c r="P615" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q615" t="str">
+        <v>4</v>
+      </c>
+      <c r="R615" t="str">
+        <v>0</v>
+      </c>
+      <c r="S615" t="str">
+        <v>3</v>
+      </c>
+      <c r="T615" t="str">
+        <v>4/28/26</v>
+      </c>
+      <c r="U615" t="str">
+        <v>8/1/26</v>
+      </c>
+      <c r="V615" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="W615" t="str">
+        <v>NGÂN</v>
+      </c>
+      <c r="X615" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="Z615" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="AA615" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="616">
+      <c r="A616" t="str">
+        <v>(2109)</v>
+      </c>
+      <c r="B616" t="str">
+        <v>(1) Viet Nga Group, (2) Viet Nga Group - NN số 2</v>
+      </c>
+      <c r="C616" t="str">
+        <v>65923</v>
+      </c>
+      <c r="D616" t="str">
+        <v>748939500</v>
+      </c>
+      <c r="E616" t="str">
+        <v>HỒ VĂN LONG</v>
+      </c>
+      <c r="F616" t="str">
+        <v>Intensive rice production // Trồng lúa thâm canh</v>
+      </c>
+      <c r="G616" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="H616" t="str">
+        <v>Male // Nam</v>
+      </c>
+      <c r="I616" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="J616" t="str">
+        <v>NO</v>
+      </c>
+      <c r="K616" t="str">
+        <v>0</v>
+      </c>
+      <c r="L616" t="str">
+        <v>0</v>
+      </c>
+      <c r="M616" t="str">
+        <v>0</v>
+      </c>
+      <c r="N616" t="str">
+        <v>0</v>
+      </c>
+      <c r="O616" t="str">
+        <v>0</v>
+      </c>
+      <c r="P616" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q616" t="str">
+        <v>4</v>
+      </c>
+      <c r="R616" t="str">
+        <v>0</v>
+      </c>
+      <c r="S616" t="str">
+        <v>3</v>
+      </c>
+      <c r="T616" t="str">
+        <v>4/28/26</v>
+      </c>
+      <c r="U616" t="str">
+        <v>8/1/26</v>
+      </c>
+      <c r="V616" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="W616" t="str">
+        <v>NGÂN</v>
+      </c>
+      <c r="X616" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="Z616" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="AA616" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="617">
+      <c r="A617" t="str">
+        <v>(2110)</v>
+      </c>
+      <c r="B617" t="str">
+        <v>(1) Viet Nga Group, (2) Viet Nga Group - NN số 2</v>
+      </c>
+      <c r="C617" t="str">
+        <v>65924</v>
+      </c>
+      <c r="D617" t="str">
+        <v>388445205</v>
+      </c>
+      <c r="E617" t="str">
+        <v>LÊ THỊ BÍA</v>
+      </c>
+      <c r="F617" t="str">
+        <v>Intensive rice production // Trồng lúa thâm canh</v>
+      </c>
+      <c r="G617" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="H617" t="str">
+        <v>Female // Nữ</v>
+      </c>
+      <c r="I617" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="J617" t="str">
+        <v>NO</v>
+      </c>
+      <c r="K617" t="str">
+        <v>1</v>
+      </c>
+      <c r="L617" t="str">
+        <v>0</v>
+      </c>
+      <c r="M617" t="str">
+        <v>0</v>
+      </c>
+      <c r="N617" t="str">
+        <v>0</v>
+      </c>
+      <c r="O617" t="str">
+        <v>0</v>
+      </c>
+      <c r="P617" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q617" t="str">
+        <v>2</v>
+      </c>
+      <c r="R617" t="str">
+        <v>0</v>
+      </c>
+      <c r="S617" t="str">
+        <v>1</v>
+      </c>
+      <c r="T617" t="str">
+        <v>4/28/26</v>
+      </c>
+      <c r="U617" t="str">
+        <v>8/1/26</v>
+      </c>
+      <c r="V617" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="W617" t="str">
+        <v>NGÂN</v>
+      </c>
+      <c r="X617" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="Z617" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="AA617" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="618">
+      <c r="A618" t="str">
+        <v>(2111)</v>
+      </c>
+      <c r="B618" t="str">
+        <v>(1) Viet Nga Group, (2) Viet Nga Group - NN số 2</v>
+      </c>
+      <c r="C618" t="str">
+        <v>65925</v>
+      </c>
+      <c r="D618" t="str">
+        <v>377105512</v>
+      </c>
+      <c r="E618" t="str">
+        <v>LÊ THỊ LOAN</v>
+      </c>
+      <c r="F618" t="str">
+        <v>Intensive rice production // Trồng lúa thâm canh</v>
+      </c>
+      <c r="G618" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="H618" t="str">
+        <v>Female // Nữ</v>
+      </c>
+      <c r="I618" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="J618" t="str">
+        <v>NO</v>
+      </c>
+      <c r="K618" t="str">
+        <v>1</v>
+      </c>
+      <c r="L618" t="str">
+        <v>0</v>
+      </c>
+      <c r="M618" t="str">
+        <v>0</v>
+      </c>
+      <c r="N618" t="str">
+        <v>0</v>
+      </c>
+      <c r="O618" t="str">
+        <v>0</v>
+      </c>
+      <c r="P618" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q618" t="str">
+        <v>3</v>
+      </c>
+      <c r="R618" t="str">
+        <v>0</v>
+      </c>
+      <c r="S618" t="str">
+        <v>2</v>
+      </c>
+      <c r="T618" t="str">
+        <v>4/28/26</v>
+      </c>
+      <c r="U618" t="str">
+        <v>8/1/26</v>
+      </c>
+      <c r="V618" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="W618" t="str">
+        <v>NGÂN</v>
+      </c>
+      <c r="X618" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="Z618" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="AA618" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="619">
+      <c r="A619" t="str">
+        <v>(2114)</v>
+      </c>
+      <c r="B619" t="str">
+        <v>(1) Viet Nga Group, (2) Viet Nga Group - NN số 2</v>
+      </c>
+      <c r="C619" t="str">
+        <v>65928</v>
+      </c>
+      <c r="D619" t="str">
+        <v>939078660</v>
+      </c>
+      <c r="E619" t="str">
+        <v>VÕ VĂN LÊN</v>
+      </c>
+      <c r="F619" t="str">
+        <v>Intensive rice production // Trồng lúa thâm canh</v>
+      </c>
+      <c r="G619" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="H619" t="str">
+        <v>Male // Nam</v>
+      </c>
+      <c r="I619" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="J619" t="str">
+        <v>NO</v>
+      </c>
+      <c r="K619" t="str">
+        <v>0</v>
+      </c>
+      <c r="L619" t="str">
+        <v>0</v>
+      </c>
+      <c r="M619" t="str">
+        <v>0</v>
+      </c>
+      <c r="N619" t="str">
+        <v>0</v>
+      </c>
+      <c r="O619" t="str">
+        <v>0</v>
+      </c>
+      <c r="P619" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q619" t="str">
+        <v>4</v>
+      </c>
+      <c r="R619" t="str">
+        <v>0</v>
+      </c>
+      <c r="S619" t="str">
+        <v>3</v>
+      </c>
+      <c r="T619" t="str">
+        <v>4/28/26</v>
+      </c>
+      <c r="U619" t="str">
+        <v>8/1/26</v>
+      </c>
+      <c r="V619" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="W619" t="str">
+        <v>NGÂN</v>
+      </c>
+      <c r="X619" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="Z619" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="AA619" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="620">
+      <c r="A620" t="str">
+        <v>(2116)</v>
+      </c>
+      <c r="B620" t="str">
+        <v>(1) Viet Nga Group, (2) Viet Nga Group - NN số 2</v>
+      </c>
+      <c r="C620" t="str">
+        <v>65931</v>
+      </c>
+      <c r="D620" t="str">
+        <v>894526922</v>
+      </c>
+      <c r="E620" t="str">
+        <v>LÊ VĂN TOÁN</v>
+      </c>
+      <c r="F620" t="str">
+        <v>Intensive rice production // Trồng lúa thâm canh</v>
+      </c>
+      <c r="G620" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="H620" t="str">
+        <v>Male // Nam</v>
+      </c>
+      <c r="I620" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="J620" t="str">
+        <v>NO</v>
+      </c>
+      <c r="K620" t="str">
+        <v>0</v>
+      </c>
+      <c r="L620" t="str">
+        <v>0</v>
+      </c>
+      <c r="M620" t="str">
+        <v>0</v>
+      </c>
+      <c r="N620" t="str">
+        <v>0</v>
+      </c>
+      <c r="O620" t="str">
+        <v>0</v>
+      </c>
+      <c r="P620" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q620" t="str">
+        <v>4</v>
+      </c>
+      <c r="R620" t="str">
+        <v>0</v>
+      </c>
+      <c r="S620" t="str">
+        <v>3</v>
+      </c>
+      <c r="T620" t="str">
+        <v>4/28/26</v>
+      </c>
+      <c r="U620" t="str">
+        <v>8/1/26</v>
+      </c>
+      <c r="V620" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="W620" t="str">
+        <v>NGÂN</v>
+      </c>
+      <c r="X620" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="Z620" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="AA620" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="621">
+      <c r="A621" t="str">
+        <v>(2117)</v>
+      </c>
+      <c r="B621" t="str">
+        <v>(1) Viet Nga Group, (2) Viet Nga Group - NN số 2</v>
+      </c>
+      <c r="C621" t="str">
+        <v>65932</v>
+      </c>
+      <c r="D621" t="str">
+        <v>738961332</v>
+      </c>
+      <c r="E621" t="str">
+        <v>PHAN VĂN PHƯỚC EM</v>
+      </c>
+      <c r="F621" t="str">
+        <v>Intensive rice production // Trồng lúa thâm canh</v>
+      </c>
+      <c r="G621" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="H621" t="str">
+        <v>Male // Nam</v>
+      </c>
+      <c r="I621" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="J621" t="str">
+        <v>NO</v>
+      </c>
+      <c r="K621" t="str">
+        <v>0</v>
+      </c>
+      <c r="L621" t="str">
+        <v>0</v>
+      </c>
+      <c r="M621" t="str">
+        <v>0</v>
+      </c>
+      <c r="N621" t="str">
+        <v>0</v>
+      </c>
+      <c r="O621" t="str">
+        <v>0</v>
+      </c>
+      <c r="P621" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q621" t="str">
+        <v>3</v>
+      </c>
+      <c r="R621" t="str">
+        <v>0</v>
+      </c>
+      <c r="S621" t="str">
+        <v>2</v>
+      </c>
+      <c r="T621" t="str">
+        <v>4/28/26</v>
+      </c>
+      <c r="U621" t="str">
+        <v>8/1/26</v>
+      </c>
+      <c r="V621" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="W621" t="str">
+        <v>NGÂN</v>
+      </c>
+      <c r="X621" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="Z621" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="AA621" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="622">
+      <c r="A622" t="str">
+        <v>(2118)</v>
+      </c>
+      <c r="B622" t="str">
+        <v>(1) Viet Nga Group, (2) Viet Nga Group - NN số 2</v>
+      </c>
+      <c r="C622" t="str">
+        <v>66882</v>
+      </c>
+      <c r="D622" t="str">
+        <v>969227829</v>
+      </c>
+      <c r="E622" t="str">
+        <v>NGÔ VĂN KHẾN</v>
+      </c>
+      <c r="F622" t="str">
+        <v>Intensive rice production // Trồng lúa thâm canh</v>
+      </c>
+      <c r="G622" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="H622" t="str">
+        <v>Male // Nam</v>
+      </c>
+      <c r="I622" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="J622" t="str">
+        <v>NO</v>
+      </c>
+      <c r="K622" t="str">
+        <v>0</v>
+      </c>
+      <c r="L622" t="str">
+        <v>0</v>
+      </c>
+      <c r="M622" t="str">
+        <v>0</v>
+      </c>
+      <c r="N622" t="str">
+        <v>0</v>
+      </c>
+      <c r="O622" t="str">
+        <v>0</v>
+      </c>
+      <c r="P622" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q622" t="str">
+        <v>2</v>
+      </c>
+      <c r="R622" t="str">
+        <v>0</v>
+      </c>
+      <c r="S622" t="str">
+        <v>1</v>
+      </c>
+      <c r="T622" t="str">
+        <v>4/28/26</v>
+      </c>
+      <c r="U622" t="str">
+        <v>8/1/26</v>
+      </c>
+      <c r="V622" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="W622" t="str">
+        <v>NGÂN</v>
+      </c>
+      <c r="X622" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="Z622" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="AA622" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="623">
+      <c r="A623" t="str">
+        <v>(2119)</v>
+      </c>
+      <c r="B623" t="str">
+        <v>(1) Viet Nga Group, (2) Viet Nga Group - NN số 2</v>
+      </c>
+      <c r="C623" t="str">
+        <v>66883</v>
+      </c>
+      <c r="D623" t="str">
+        <v>919667814</v>
+      </c>
+      <c r="E623" t="str">
+        <v>NGUYỄN THANH TÙNG</v>
+      </c>
+      <c r="F623" t="str">
+        <v>Intensive rice production // Trồng lúa thâm canh</v>
+      </c>
+      <c r="G623" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="H623" t="str">
+        <v>Male // Nam</v>
+      </c>
+      <c r="I623" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="J623" t="str">
+        <v>NO</v>
+      </c>
+      <c r="K623" t="str">
+        <v>0</v>
+      </c>
+      <c r="L623" t="str">
+        <v>0</v>
+      </c>
+      <c r="M623" t="str">
+        <v>0</v>
+      </c>
+      <c r="N623" t="str">
+        <v>0</v>
+      </c>
+      <c r="O623" t="str">
+        <v>0</v>
+      </c>
+      <c r="P623" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q623" t="str">
+        <v>2</v>
+      </c>
+      <c r="R623" t="str">
+        <v>0</v>
+      </c>
+      <c r="S623" t="str">
+        <v>1</v>
+      </c>
+      <c r="T623" t="str">
+        <v>4/28/26</v>
+      </c>
+      <c r="U623" t="str">
+        <v>8/1/26</v>
+      </c>
+      <c r="V623" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="W623" t="str">
+        <v>NGÂN</v>
+      </c>
+      <c r="X623" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="Z623" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="AA623" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="624">
+      <c r="A624" t="str">
+        <v>(2120)</v>
+      </c>
+      <c r="B624" t="str">
+        <v>(1) Viet Nga Group, (2) Viet Nga Group - NN số 2</v>
+      </c>
+      <c r="C624" t="str">
+        <v>66884</v>
+      </c>
+      <c r="D624" t="str">
+        <v>944370700</v>
+      </c>
+      <c r="E624" t="str">
+        <v>NGUYỄN THỊ BƯƠNG</v>
+      </c>
+      <c r="F624" t="str">
+        <v>Intensive rice production // Trồng lúa thâm canh</v>
+      </c>
+      <c r="G624" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="H624" t="str">
+        <v>Female // Nữ</v>
+      </c>
+      <c r="I624" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="J624" t="str">
+        <v>NO</v>
+      </c>
+      <c r="K624" t="str">
+        <v>1</v>
+      </c>
+      <c r="L624" t="str">
+        <v>0</v>
+      </c>
+      <c r="M624" t="str">
+        <v>0</v>
+      </c>
+      <c r="N624" t="str">
+        <v>0</v>
+      </c>
+      <c r="O624" t="str">
+        <v>0</v>
+      </c>
+      <c r="P624" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q624" t="str">
+        <v>3</v>
+      </c>
+      <c r="R624" t="str">
+        <v>0</v>
+      </c>
+      <c r="S624" t="str">
+        <v>2</v>
+      </c>
+      <c r="T624" t="str">
+        <v>4/28/26</v>
+      </c>
+      <c r="U624" t="str">
+        <v>8/1/26</v>
+      </c>
+      <c r="V624" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="W624" t="str">
+        <v>NGÂN</v>
+      </c>
+      <c r="X624" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="Z624" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="AA624" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="625">
+      <c r="A625" t="str">
+        <v>(2121)</v>
+      </c>
+      <c r="B625" t="str">
+        <v>(1) Viet Nga Group, (2) Viet Nga Group - NN số 2</v>
+      </c>
+      <c r="C625" t="str">
+        <v>66885</v>
+      </c>
+      <c r="D625" t="str">
+        <v>933747600</v>
+      </c>
+      <c r="E625" t="str">
+        <v>NGUYỄN THỊ HUYỀN HOA</v>
+      </c>
+      <c r="F625" t="str">
+        <v>Intensive rice production // Trồng lúa thâm canh</v>
+      </c>
+      <c r="G625" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="H625" t="str">
+        <v>Female // Nữ</v>
+      </c>
+      <c r="I625" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="J625" t="str">
+        <v>NO</v>
+      </c>
+      <c r="K625" t="str">
+        <v>1</v>
+      </c>
+      <c r="L625" t="str">
+        <v>0</v>
+      </c>
+      <c r="M625" t="str">
+        <v>0</v>
+      </c>
+      <c r="N625" t="str">
+        <v>0</v>
+      </c>
+      <c r="O625" t="str">
+        <v>0</v>
+      </c>
+      <c r="P625" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q625" t="str">
+        <v>2</v>
+      </c>
+      <c r="R625" t="str">
+        <v>0</v>
+      </c>
+      <c r="S625" t="str">
+        <v>1</v>
+      </c>
+      <c r="T625" t="str">
+        <v>4/28/26</v>
+      </c>
+      <c r="U625" t="str">
+        <v>8/1/26</v>
+      </c>
+      <c r="V625" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="W625" t="str">
+        <v>NGÂN</v>
+      </c>
+      <c r="X625" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="Z625" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="AA625" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="626">
+      <c r="A626" t="str">
+        <v>(2122)</v>
+      </c>
+      <c r="B626" t="str">
+        <v>(1) Viet Nga Group, (2) Viet Nga Group - NN số 2</v>
+      </c>
+      <c r="C626" t="str">
+        <v>66886</v>
+      </c>
+      <c r="D626" t="str">
+        <v>939082024</v>
+      </c>
+      <c r="E626" t="str">
+        <v>NGUYỄN THỊ NGỢI</v>
+      </c>
+      <c r="F626" t="str">
+        <v>Intensive rice production // Trồng lúa thâm canh</v>
+      </c>
+      <c r="G626" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="H626" t="str">
+        <v>Female // Nữ</v>
+      </c>
+      <c r="I626" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="J626" t="str">
+        <v>NO</v>
+      </c>
+      <c r="K626" t="str">
+        <v>1</v>
+      </c>
+      <c r="L626" t="str">
+        <v>0</v>
+      </c>
+      <c r="M626" t="str">
+        <v>0</v>
+      </c>
+      <c r="N626" t="str">
+        <v>0</v>
+      </c>
+      <c r="O626" t="str">
+        <v>0</v>
+      </c>
+      <c r="P626" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q626" t="str">
+        <v>3</v>
+      </c>
+      <c r="R626" t="str">
+        <v>0</v>
+      </c>
+      <c r="S626" t="str">
+        <v>2</v>
+      </c>
+      <c r="T626" t="str">
+        <v>4/28/26</v>
+      </c>
+      <c r="U626" t="str">
+        <v>8/1/26</v>
+      </c>
+      <c r="V626" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="W626" t="str">
+        <v>NGÂN</v>
+      </c>
+      <c r="X626" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="Z626" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="AA626" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="627">
+      <c r="A627" t="str">
+        <v>(2123)</v>
+      </c>
+      <c r="B627" t="str">
+        <v>(1) Viet Nga Group, (2) Viet Nga Group - NN số 2</v>
+      </c>
+      <c r="C627" t="str">
+        <v>66887</v>
+      </c>
+      <c r="D627" t="str">
+        <v>968221043</v>
+      </c>
+      <c r="E627" t="str">
+        <v>NGUYỄN THỊ NHU</v>
+      </c>
+      <c r="F627" t="str">
+        <v>Intensive rice production // Trồng lúa thâm canh</v>
+      </c>
+      <c r="G627" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="H627" t="str">
+        <v>Female // Nữ</v>
+      </c>
+      <c r="I627" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="J627" t="str">
+        <v>NO</v>
+      </c>
+      <c r="K627" t="str">
+        <v>1</v>
+      </c>
+      <c r="L627" t="str">
+        <v>0</v>
+      </c>
+      <c r="M627" t="str">
+        <v>0</v>
+      </c>
+      <c r="N627" t="str">
+        <v>0</v>
+      </c>
+      <c r="O627" t="str">
+        <v>0</v>
+      </c>
+      <c r="P627" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q627" t="str">
+        <v>4</v>
+      </c>
+      <c r="R627" t="str">
+        <v>0</v>
+      </c>
+      <c r="S627" t="str">
+        <v>3</v>
+      </c>
+      <c r="T627" t="str">
+        <v>4/28/26</v>
+      </c>
+      <c r="U627" t="str">
+        <v>8/1/26</v>
+      </c>
+      <c r="V627" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="W627" t="str">
+        <v>NGÂN</v>
+      </c>
+      <c r="X627" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="Z627" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="AA627" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="628">
+      <c r="A628" t="str">
+        <v>(2124)</v>
+      </c>
+      <c r="B628" t="str">
+        <v>(1) Viet Nga Group, (2) Viet Nga Group - NN số 2</v>
+      </c>
+      <c r="C628" t="str">
+        <v>66888</v>
+      </c>
+      <c r="D628" t="str">
+        <v>338771600</v>
+      </c>
+      <c r="E628" t="str">
+        <v>NGUYỄN THỊ PHẤN</v>
+      </c>
+      <c r="F628" t="str">
+        <v>Intensive rice production // Trồng lúa thâm canh</v>
+      </c>
+      <c r="G628" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="H628" t="str">
+        <v>Female // Nữ</v>
+      </c>
+      <c r="I628" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="J628" t="str">
+        <v>NO</v>
+      </c>
+      <c r="K628" t="str">
+        <v>1</v>
+      </c>
+      <c r="L628" t="str">
+        <v>0</v>
+      </c>
+      <c r="M628" t="str">
+        <v>0</v>
+      </c>
+      <c r="N628" t="str">
+        <v>0</v>
+      </c>
+      <c r="O628" t="str">
+        <v>0</v>
+      </c>
+      <c r="P628" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q628" t="str">
+        <v>3</v>
+      </c>
+      <c r="R628" t="str">
+        <v>0</v>
+      </c>
+      <c r="S628" t="str">
+        <v>2</v>
+      </c>
+      <c r="T628" t="str">
+        <v>4/28/26</v>
+      </c>
+      <c r="U628" t="str">
+        <v>8/1/26</v>
+      </c>
+      <c r="V628" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="W628" t="str">
+        <v>NGÂN</v>
+      </c>
+      <c r="X628" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="Z628" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="AA628" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="629">
+      <c r="A629" t="str">
+        <v>(2125)</v>
+      </c>
+      <c r="B629" t="str">
+        <v>(1) Viet Nga Group, (2) Viet Nga Group - NN số 2</v>
+      </c>
+      <c r="C629" t="str">
+        <v>66889</v>
+      </c>
+      <c r="D629" t="str">
+        <v>919869190</v>
+      </c>
+      <c r="E629" t="str">
+        <v>NGUYỄN THỊ THA</v>
+      </c>
+      <c r="F629" t="str">
+        <v>Intensive rice production // Trồng lúa thâm canh</v>
+      </c>
+      <c r="G629" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="H629" t="str">
+        <v>Female // Nữ</v>
+      </c>
+      <c r="I629" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="J629" t="str">
+        <v>NO</v>
+      </c>
+      <c r="K629" t="str">
+        <v>1</v>
+      </c>
+      <c r="L629" t="str">
+        <v>0</v>
+      </c>
+      <c r="M629" t="str">
+        <v>0</v>
+      </c>
+      <c r="N629" t="str">
+        <v>0</v>
+      </c>
+      <c r="O629" t="str">
+        <v>0</v>
+      </c>
+      <c r="P629" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q629" t="str">
+        <v>4</v>
+      </c>
+      <c r="R629" t="str">
+        <v>0</v>
+      </c>
+      <c r="S629" t="str">
+        <v>3</v>
+      </c>
+      <c r="T629" t="str">
+        <v>4/28/26</v>
+      </c>
+      <c r="U629" t="str">
+        <v>8/1/26</v>
+      </c>
+      <c r="V629" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="W629" t="str">
+        <v>NGÂN</v>
+      </c>
+      <c r="X629" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="Z629" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="AA629" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="630">
+      <c r="A630" t="str">
+        <v>(2126)</v>
+      </c>
+      <c r="B630" t="str">
+        <v>(1) Viet Nga Group, (2) Viet Nga Group - NN số 2</v>
+      </c>
+      <c r="C630" t="str">
+        <v>66890</v>
+      </c>
+      <c r="D630" t="str">
+        <v>339968565</v>
+      </c>
+      <c r="E630" t="str">
+        <v>NGUYỄN VĂN CÔNG</v>
+      </c>
+      <c r="F630" t="str">
+        <v>Intensive rice production // Trồng lúa thâm canh</v>
+      </c>
+      <c r="G630" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="H630" t="str">
+        <v>Male // Nam</v>
+      </c>
+      <c r="I630" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="J630" t="str">
+        <v>NO</v>
+      </c>
+      <c r="K630" t="str">
+        <v>0</v>
+      </c>
+      <c r="L630" t="str">
+        <v>0</v>
+      </c>
+      <c r="M630" t="str">
+        <v>0</v>
+      </c>
+      <c r="N630" t="str">
+        <v>0</v>
+      </c>
+      <c r="O630" t="str">
+        <v>0</v>
+      </c>
+      <c r="P630" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q630" t="str">
+        <v>2</v>
+      </c>
+      <c r="R630" t="str">
+        <v>0</v>
+      </c>
+      <c r="S630" t="str">
+        <v>1</v>
+      </c>
+      <c r="T630" t="str">
+        <v>4/28/26</v>
+      </c>
+      <c r="U630" t="str">
+        <v>8/1/26</v>
+      </c>
+      <c r="V630" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="W630" t="str">
+        <v>NGÂN</v>
+      </c>
+      <c r="X630" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="Z630" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="AA630" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="631">
+      <c r="A631" t="str">
+        <v>(2127)</v>
+      </c>
+      <c r="B631" t="str">
+        <v>(1) Viet Nga Group, (2) Viet Nga Group - NN số 2</v>
+      </c>
+      <c r="C631" t="str">
+        <v>66892</v>
+      </c>
+      <c r="D631" t="str">
+        <v>911137806</v>
+      </c>
+      <c r="E631" t="str">
+        <v>NGUYỄN VĂN DƯƠNG</v>
+      </c>
+      <c r="F631" t="str">
+        <v>Intensive rice production // Trồng lúa thâm canh</v>
+      </c>
+      <c r="G631" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="H631" t="str">
+        <v>Male // Nam</v>
+      </c>
+      <c r="I631" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="J631" t="str">
+        <v>NO</v>
+      </c>
+      <c r="K631" t="str">
+        <v>0</v>
+      </c>
+      <c r="L631" t="str">
+        <v>0</v>
+      </c>
+      <c r="M631" t="str">
+        <v>0</v>
+      </c>
+      <c r="N631" t="str">
+        <v>0</v>
+      </c>
+      <c r="O631" t="str">
+        <v>0</v>
+      </c>
+      <c r="P631" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q631" t="str">
+        <v>4</v>
+      </c>
+      <c r="R631" t="str">
+        <v>0</v>
+      </c>
+      <c r="S631" t="str">
+        <v>3</v>
+      </c>
+      <c r="T631" t="str">
+        <v>4/28/26</v>
+      </c>
+      <c r="U631" t="str">
+        <v>8/1/26</v>
+      </c>
+      <c r="V631" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="W631" t="str">
+        <v>NGÂN</v>
+      </c>
+      <c r="X631" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="Z631" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="AA631" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="632">
+      <c r="A632" t="str">
+        <v>(2128)</v>
+      </c>
+      <c r="B632" t="str">
+        <v>(1) Viet Nga Group, (2) Viet Nga Group - NN số 2</v>
+      </c>
+      <c r="C632" t="str">
+        <v>66893</v>
+      </c>
+      <c r="D632" t="str">
+        <v>904252449</v>
+      </c>
+      <c r="E632" t="str">
+        <v>NGUYỄN VĂN CẢNH</v>
+      </c>
+      <c r="F632" t="str">
+        <v>Intensive rice production // Trồng lúa thâm canh</v>
+      </c>
+      <c r="G632" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="H632" t="str">
+        <v>Male // Nam</v>
+      </c>
+      <c r="I632" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="J632" t="str">
+        <v>NO</v>
+      </c>
+      <c r="K632" t="str">
+        <v>0</v>
+      </c>
+      <c r="L632" t="str">
+        <v>0</v>
+      </c>
+      <c r="M632" t="str">
+        <v>0</v>
+      </c>
+      <c r="N632" t="str">
+        <v>0</v>
+      </c>
+      <c r="O632" t="str">
+        <v>0</v>
+      </c>
+      <c r="P632" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q632" t="str">
+        <v>2</v>
+      </c>
+      <c r="R632" t="str">
+        <v>0</v>
+      </c>
+      <c r="S632" t="str">
+        <v>1</v>
+      </c>
+      <c r="T632" t="str">
+        <v>4/28/26</v>
+      </c>
+      <c r="U632" t="str">
+        <v>8/1/26</v>
+      </c>
+      <c r="V632" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="W632" t="str">
+        <v>NGÂN</v>
+      </c>
+      <c r="X632" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="Z632" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="AA632" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="633">
+      <c r="A633" t="str">
+        <v>(2133)</v>
+      </c>
+      <c r="B633" t="str">
+        <v>(1) Viet Nga Group, (2) Viet Nga Group - NN số 2</v>
+      </c>
+      <c r="C633" t="str">
+        <v>66896</v>
+      </c>
+      <c r="D633" t="str">
+        <v>978623803</v>
+      </c>
+      <c r="E633" t="str">
+        <v>NGUYỄN VĂN TĂNG</v>
+      </c>
+      <c r="F633" t="str">
+        <v>Intensive rice production // Trồng lúa thâm canh</v>
+      </c>
+      <c r="G633" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="H633" t="str">
+        <v>Male // Nam</v>
+      </c>
+      <c r="I633" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="J633" t="str">
+        <v>NO</v>
+      </c>
+      <c r="K633" t="str">
+        <v>0</v>
+      </c>
+      <c r="L633" t="str">
+        <v>0</v>
+      </c>
+      <c r="M633" t="str">
+        <v>0</v>
+      </c>
+      <c r="N633" t="str">
+        <v>0</v>
+      </c>
+      <c r="O633" t="str">
+        <v>0</v>
+      </c>
+      <c r="P633" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q633" t="str">
+        <v>4</v>
+      </c>
+      <c r="R633" t="str">
+        <v>0</v>
+      </c>
+      <c r="S633" t="str">
+        <v>3</v>
+      </c>
+      <c r="T633" t="str">
+        <v>4/28/26</v>
+      </c>
+      <c r="U633" t="str">
+        <v>8/1/26</v>
+      </c>
+      <c r="V633" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="W633" t="str">
+        <v>NGÂN</v>
+      </c>
+      <c r="X633" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="Z633" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="AA633" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="634">
+      <c r="A634" t="str">
+        <v>(2137)</v>
+      </c>
+      <c r="B634" t="str">
+        <v>(1) Viet Nga Group, (2) Viet Nga Group - NN số 2</v>
+      </c>
+      <c r="C634" t="str">
+        <v>66900</v>
+      </c>
+      <c r="D634" t="str">
+        <v>358402817</v>
+      </c>
+      <c r="E634" t="str">
+        <v>PHẠM THỊ MÃI</v>
+      </c>
+      <c r="F634" t="str">
+        <v>Intensive rice production // Trồng lúa thâm canh</v>
+      </c>
+      <c r="G634" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="H634" t="str">
+        <v>Female // Nữ</v>
+      </c>
+      <c r="I634" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="J634" t="str">
+        <v>NO</v>
+      </c>
+      <c r="K634" t="str">
+        <v>1</v>
+      </c>
+      <c r="L634" t="str">
+        <v>0</v>
+      </c>
+      <c r="M634" t="str">
+        <v>0</v>
+      </c>
+      <c r="N634" t="str">
+        <v>0</v>
+      </c>
+      <c r="O634" t="str">
+        <v>0</v>
+      </c>
+      <c r="P634" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q634" t="str">
+        <v>3</v>
+      </c>
+      <c r="R634" t="str">
+        <v>0</v>
+      </c>
+      <c r="S634" t="str">
+        <v>2</v>
+      </c>
+      <c r="T634" t="str">
+        <v>4/28/26</v>
+      </c>
+      <c r="U634" t="str">
+        <v>8/1/26</v>
+      </c>
+      <c r="V634" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="W634" t="str">
+        <v>NGÂN</v>
+      </c>
+      <c r="X634" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="Z634" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="AA634" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="635">
+      <c r="A635" t="str">
+        <v>(2142)</v>
+      </c>
+      <c r="B635" t="str">
+        <v>(1) Viet Nga Group, (2) Viet Nga Group - NN số 2</v>
+      </c>
+      <c r="C635" t="str">
+        <v>66903</v>
+      </c>
+      <c r="D635" t="str">
+        <v>398392735</v>
+      </c>
+      <c r="E635" t="str">
+        <v>TRẦN MINH THUẬN</v>
+      </c>
+      <c r="F635" t="str">
+        <v>Intensive rice production // Trồng lúa thâm canh</v>
+      </c>
+      <c r="G635" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="H635" t="str">
+        <v>Male // Nam</v>
+      </c>
+      <c r="I635" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="J635" t="str">
+        <v>NO</v>
+      </c>
+      <c r="K635" t="str">
+        <v>0</v>
+      </c>
+      <c r="L635" t="str">
+        <v>0</v>
+      </c>
+      <c r="M635" t="str">
+        <v>0</v>
+      </c>
+      <c r="N635" t="str">
+        <v>0</v>
+      </c>
+      <c r="O635" t="str">
+        <v>0</v>
+      </c>
+      <c r="P635" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q635" t="str">
+        <v>2</v>
+      </c>
+      <c r="R635" t="str">
+        <v>0</v>
+      </c>
+      <c r="S635" t="str">
+        <v>1</v>
+      </c>
+      <c r="T635" t="str">
+        <v>4/28/26</v>
+      </c>
+      <c r="U635" t="str">
+        <v>8/1/26</v>
+      </c>
+      <c r="V635" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="W635" t="str">
+        <v>NGÂN</v>
+      </c>
+      <c r="X635" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="Z635" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="AA635" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="636">
+      <c r="A636" t="str">
+        <v>(2149)</v>
+      </c>
+      <c r="B636" t="str">
+        <v>(1) Viet Nga Group, (2) Viet Nga Group - NN số 2</v>
+      </c>
+      <c r="C636" t="str">
+        <v>66907</v>
+      </c>
+      <c r="D636" t="str">
+        <v>914696967</v>
+      </c>
+      <c r="E636" t="str">
+        <v>LÊ THỊ THU VÂN</v>
+      </c>
+      <c r="F636" t="str">
+        <v>Intensive rice production // Trồng lúa thâm canh</v>
+      </c>
+      <c r="G636" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="H636" t="str">
+        <v>Female // Nữ</v>
+      </c>
+      <c r="I636" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="J636" t="str">
+        <v>NO</v>
+      </c>
+      <c r="K636" t="str">
+        <v>1</v>
+      </c>
+      <c r="L636" t="str">
+        <v>0</v>
+      </c>
+      <c r="M636" t="str">
+        <v>0</v>
+      </c>
+      <c r="N636" t="str">
+        <v>0</v>
+      </c>
+      <c r="O636" t="str">
+        <v>0</v>
+      </c>
+      <c r="P636" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q636" t="str">
+        <v>3</v>
+      </c>
+      <c r="R636" t="str">
+        <v>0</v>
+      </c>
+      <c r="S636" t="str">
+        <v>2</v>
+      </c>
+      <c r="T636" t="str">
+        <v>4/28/26</v>
+      </c>
+      <c r="U636" t="str">
+        <v>8/1/26</v>
+      </c>
+      <c r="V636" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="W636" t="str">
+        <v>NGÂN</v>
+      </c>
+      <c r="X636" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="Z636" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="AA636" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="637">
+      <c r="A637" t="str">
+        <v>(2152)</v>
+      </c>
+      <c r="B637" t="str">
+        <v>(1) Viet Nga Group, (2) Viet Nga Group - NN số 2</v>
+      </c>
+      <c r="C637" t="str">
+        <v>66909</v>
+      </c>
+      <c r="D637" t="str">
+        <v>343396665</v>
+      </c>
+      <c r="E637" t="str">
+        <v>VÕ THỊ XUÂN HƯỜNG</v>
+      </c>
+      <c r="F637" t="str">
+        <v>Intensive rice production // Trồng lúa thâm canh</v>
+      </c>
+      <c r="G637" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="H637" t="str">
+        <v>Female // Nữ</v>
+      </c>
+      <c r="I637" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="J637" t="str">
+        <v>NO</v>
+      </c>
+      <c r="K637" t="str">
+        <v>1</v>
+      </c>
+      <c r="L637" t="str">
+        <v>0</v>
+      </c>
+      <c r="M637" t="str">
+        <v>0</v>
+      </c>
+      <c r="N637" t="str">
+        <v>0</v>
+      </c>
+      <c r="O637" t="str">
+        <v>0</v>
+      </c>
+      <c r="P637" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q637" t="str">
+        <v>3</v>
+      </c>
+      <c r="R637" t="str">
+        <v>0</v>
+      </c>
+      <c r="S637" t="str">
+        <v>2</v>
+      </c>
+      <c r="T637" t="str">
+        <v>4/28/26</v>
+      </c>
+      <c r="U637" t="str">
+        <v>8/1/26</v>
+      </c>
+      <c r="V637" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="W637" t="str">
+        <v>NGÂN</v>
+      </c>
+      <c r="X637" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="Z637" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="AA637" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="638">
+      <c r="A638" t="str">
+        <v>(2157)</v>
+      </c>
+      <c r="B638" t="str">
+        <v>(1) Viet Nga Group, (2) Viet Nga Group - NN số 2</v>
+      </c>
+      <c r="C638" t="str">
+        <v>66912</v>
+      </c>
+      <c r="D638" t="str">
+        <v>708613247</v>
+      </c>
+      <c r="E638" t="str">
+        <v>HỒ MINH QUANG</v>
+      </c>
+      <c r="F638" t="str">
+        <v>Intensive rice production // Trồng lúa thâm canh</v>
+      </c>
+      <c r="G638" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="H638" t="str">
+        <v>Male // Nam</v>
+      </c>
+      <c r="I638" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="J638" t="str">
+        <v>NO</v>
+      </c>
+      <c r="K638" t="str">
+        <v>0</v>
+      </c>
+      <c r="L638" t="str">
+        <v>0</v>
+      </c>
+      <c r="M638" t="str">
+        <v>0</v>
+      </c>
+      <c r="N638" t="str">
+        <v>0</v>
+      </c>
+      <c r="O638" t="str">
+        <v>0</v>
+      </c>
+      <c r="P638" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q638" t="str">
+        <v>2</v>
+      </c>
+      <c r="R638" t="str">
+        <v>0</v>
+      </c>
+      <c r="S638" t="str">
+        <v>1</v>
+      </c>
+      <c r="T638" t="str">
+        <v>4/28/26</v>
+      </c>
+      <c r="U638" t="str">
+        <v>8/1/26</v>
+      </c>
+      <c r="V638" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="W638" t="str">
+        <v>NGÂN</v>
+      </c>
+      <c r="X638" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="Z638" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="AA638" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="639">
+      <c r="A639" t="str">
+        <v>(2158)</v>
+      </c>
+      <c r="B639" t="str">
+        <v>(1) Viet Nga Group, (2) Viet Nga Group - NN số 2</v>
+      </c>
+      <c r="C639" t="str">
+        <v>66914</v>
+      </c>
+      <c r="D639" t="str">
+        <v>366624702</v>
+      </c>
+      <c r="E639" t="str">
+        <v>PHAN THANH CƯỜNG</v>
+      </c>
+      <c r="F639" t="str">
+        <v>Intensive rice production // Trồng lúa thâm canh</v>
+      </c>
+      <c r="G639" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="H639" t="str">
+        <v>Male // Nam</v>
+      </c>
+      <c r="I639" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="J639" t="str">
+        <v>NO</v>
+      </c>
+      <c r="K639" t="str">
+        <v>0</v>
+      </c>
+      <c r="L639" t="str">
+        <v>0</v>
+      </c>
+      <c r="M639" t="str">
+        <v>0</v>
+      </c>
+      <c r="N639" t="str">
+        <v>0</v>
+      </c>
+      <c r="O639" t="str">
+        <v>0</v>
+      </c>
+      <c r="P639" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q639" t="str">
+        <v>4</v>
+      </c>
+      <c r="R639" t="str">
+        <v>0</v>
+      </c>
+      <c r="S639" t="str">
+        <v>3</v>
+      </c>
+      <c r="T639" t="str">
+        <v>4/28/26</v>
+      </c>
+      <c r="U639" t="str">
+        <v>8/1/26</v>
+      </c>
+      <c r="V639" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="W639" t="str">
+        <v>NGÂN</v>
+      </c>
+      <c r="X639" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="Z639" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="AA639" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="640">
+      <c r="A640" t="str">
+        <v>(2164)</v>
+      </c>
+      <c r="B640" t="str">
+        <v>(1) Viet Nga Group, (2) Viet Nga Group - NN số 2</v>
+      </c>
+      <c r="C640" t="str">
+        <v>66918</v>
+      </c>
+      <c r="D640" t="str">
+        <v>986097330</v>
+      </c>
+      <c r="E640" t="str">
+        <v>TRẦN VĂN DẪU</v>
+      </c>
+      <c r="F640" t="str">
+        <v>Intensive rice production // Trồng lúa thâm canh</v>
+      </c>
+      <c r="G640" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="H640" t="str">
+        <v>Male // Nam</v>
+      </c>
+      <c r="I640" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="J640" t="str">
+        <v>NO</v>
+      </c>
+      <c r="K640" t="str">
+        <v>0</v>
+      </c>
+      <c r="L640" t="str">
+        <v>0</v>
+      </c>
+      <c r="M640" t="str">
+        <v>0</v>
+      </c>
+      <c r="N640" t="str">
+        <v>0</v>
+      </c>
+      <c r="O640" t="str">
+        <v>0</v>
+      </c>
+      <c r="P640" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q640" t="str">
+        <v>3</v>
+      </c>
+      <c r="R640" t="str">
+        <v>0</v>
+      </c>
+      <c r="S640" t="str">
+        <v>2</v>
+      </c>
+      <c r="T640" t="str">
+        <v>4/28/26</v>
+      </c>
+      <c r="U640" t="str">
+        <v>8/1/26</v>
+      </c>
+      <c r="V640" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="W640" t="str">
+        <v>NGÂN</v>
+      </c>
+      <c r="X640" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="Z640" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="AA640" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="641">
+      <c r="A641" t="str">
+        <v>(2083)</v>
+      </c>
+      <c r="B641" t="str">
+        <v>(1) Viet Nga Group, (2) Viet Nga Group - NN số 2</v>
+      </c>
+      <c r="C641" t="str">
+        <v>65868</v>
+      </c>
+      <c r="D641" t="str">
+        <v>346700178</v>
+      </c>
+      <c r="E641" t="str">
+        <v>VÕ THỊ MẠNH</v>
+      </c>
+      <c r="F641" t="str">
+        <v>Intensive rice production // Trồng lúa thâm canh</v>
+      </c>
+      <c r="G641" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="H641" t="str">
+        <v>Female // Nữ</v>
+      </c>
+      <c r="I641" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="J641" t="str">
+        <v>NO</v>
+      </c>
+      <c r="K641" t="str">
+        <v>1</v>
+      </c>
+      <c r="L641" t="str">
+        <v>0</v>
+      </c>
+      <c r="M641" t="str">
+        <v>0</v>
+      </c>
+      <c r="N641" t="str">
+        <v>0</v>
+      </c>
+      <c r="O641" t="str">
+        <v>0</v>
+      </c>
+      <c r="P641" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q641" t="str">
+        <v>3</v>
+      </c>
+      <c r="R641" t="str">
+        <v>0</v>
+      </c>
+      <c r="S641" t="str">
+        <v>2</v>
+      </c>
+      <c r="T641" t="str">
+        <v>4/28/26</v>
+      </c>
+      <c r="U641" t="str">
+        <v>8/1/26</v>
+      </c>
+      <c r="V641" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="W641" t="str">
+        <v>NGÂN</v>
+      </c>
+      <c r="X641" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="Z641" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="AA641" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="642">
+      <c r="A642" t="str">
+        <v>(2086)</v>
+      </c>
+      <c r="B642" t="str">
+        <v>(1) Viet Nga Group, (2) Viet Nga Group - NN số 2</v>
+      </c>
+      <c r="C642" t="str">
+        <v>65871</v>
+      </c>
+      <c r="D642" t="str">
+        <v>326167990</v>
+      </c>
+      <c r="E642" t="str">
+        <v>LÊ THỊ OANH</v>
+      </c>
+      <c r="F642" t="str">
+        <v>Intensive rice production // Trồng lúa thâm canh</v>
+      </c>
+      <c r="G642" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="H642" t="str">
+        <v>Female // Nữ</v>
+      </c>
+      <c r="I642" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="J642" t="str">
+        <v>NO</v>
+      </c>
+      <c r="K642" t="str">
+        <v>1</v>
+      </c>
+      <c r="L642" t="str">
+        <v>0</v>
+      </c>
+      <c r="M642" t="str">
+        <v>0</v>
+      </c>
+      <c r="N642" t="str">
+        <v>0</v>
+      </c>
+      <c r="O642" t="str">
+        <v>0</v>
+      </c>
+      <c r="P642" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q642" t="str">
+        <v>3</v>
+      </c>
+      <c r="R642" t="str">
+        <v>0</v>
+      </c>
+      <c r="S642" t="str">
+        <v>2</v>
+      </c>
+      <c r="T642" t="str">
+        <v>4/28/26</v>
+      </c>
+      <c r="U642" t="str">
+        <v>8/1/26</v>
+      </c>
+      <c r="V642" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="W642" t="str">
+        <v>NGÂN</v>
+      </c>
+      <c r="X642" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="Z642" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="AA642" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="643">
+      <c r="A643" t="str">
+        <v>(2088)</v>
+      </c>
+      <c r="B643" t="str">
+        <v>(1) Viet Nga Group, (2) Viet Nga Group - NN số 2</v>
+      </c>
+      <c r="C643" t="str">
+        <v>65873</v>
+      </c>
+      <c r="D643" t="str">
+        <v>333342462</v>
+      </c>
+      <c r="E643" t="str">
+        <v>LÊ TẤN TÀI</v>
+      </c>
+      <c r="F643" t="str">
+        <v>Intensive rice production // Trồng lúa thâm canh</v>
+      </c>
+      <c r="G643" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="H643" t="str">
+        <v>Male // Nam</v>
+      </c>
+      <c r="I643" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="J643" t="str">
+        <v>NO</v>
+      </c>
+      <c r="K643" t="str">
+        <v>0</v>
+      </c>
+      <c r="L643" t="str">
+        <v>0</v>
+      </c>
+      <c r="M643" t="str">
+        <v>0</v>
+      </c>
+      <c r="N643" t="str">
+        <v>0</v>
+      </c>
+      <c r="O643" t="str">
+        <v>0</v>
+      </c>
+      <c r="P643" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q643" t="str">
+        <v>2</v>
+      </c>
+      <c r="R643" t="str">
+        <v>0</v>
+      </c>
+      <c r="S643" t="str">
+        <v>1</v>
+      </c>
+      <c r="T643" t="str">
+        <v>4/28/26</v>
+      </c>
+      <c r="U643" t="str">
+        <v>8/1/26</v>
+      </c>
+      <c r="V643" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="W643" t="str">
+        <v>NGÂN</v>
+      </c>
+      <c r="X643" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="Z643" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="AA643" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="644">
+      <c r="A644" t="str">
+        <v>(2108)</v>
+      </c>
+      <c r="B644" t="str">
+        <v>(1) Viet Nga Group, (2) Viet Nga Group - NN số 2</v>
+      </c>
+      <c r="C644" t="str">
+        <v>65922</v>
+      </c>
+      <c r="D644" t="str">
+        <v>354342105</v>
+      </c>
+      <c r="E644" t="str">
+        <v>GIANG VĂN HỌT</v>
+      </c>
+      <c r="F644" t="str">
+        <v>Intensive rice production // Trồng lúa thâm canh</v>
+      </c>
+      <c r="G644" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="H644" t="str">
+        <v>Male // Nam</v>
+      </c>
+      <c r="I644" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="J644" t="str">
+        <v>NO</v>
+      </c>
+      <c r="K644" t="str">
+        <v>0</v>
+      </c>
+      <c r="L644" t="str">
+        <v>0</v>
+      </c>
+      <c r="M644" t="str">
+        <v>0</v>
+      </c>
+      <c r="N644" t="str">
+        <v>0</v>
+      </c>
+      <c r="O644" t="str">
+        <v>0</v>
+      </c>
+      <c r="P644" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q644" t="str">
+        <v>4</v>
+      </c>
+      <c r="R644" t="str">
+        <v>0</v>
+      </c>
+      <c r="S644" t="str">
+        <v>3</v>
+      </c>
+      <c r="T644" t="str">
+        <v>4/28/26</v>
+      </c>
+      <c r="U644" t="str">
+        <v>8/1/26</v>
+      </c>
+      <c r="V644" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="W644" t="str">
+        <v>NGÂN</v>
+      </c>
+      <c r="X644" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="Z644" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="AA644" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="645">
+      <c r="A645" t="str">
+        <v>(2109)</v>
+      </c>
+      <c r="B645" t="str">
+        <v>(1) Viet Nga Group, (2) Viet Nga Group - NN số 2</v>
+      </c>
+      <c r="C645" t="str">
+        <v>65923</v>
+      </c>
+      <c r="D645" t="str">
+        <v>748939500</v>
+      </c>
+      <c r="E645" t="str">
+        <v>HỒ VĂN LONG</v>
+      </c>
+      <c r="F645" t="str">
+        <v>Intensive rice production // Trồng lúa thâm canh</v>
+      </c>
+      <c r="G645" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="H645" t="str">
+        <v>Male // Nam</v>
+      </c>
+      <c r="I645" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="J645" t="str">
+        <v>NO</v>
+      </c>
+      <c r="K645" t="str">
+        <v>0</v>
+      </c>
+      <c r="L645" t="str">
+        <v>0</v>
+      </c>
+      <c r="M645" t="str">
+        <v>0</v>
+      </c>
+      <c r="N645" t="str">
+        <v>0</v>
+      </c>
+      <c r="O645" t="str">
+        <v>0</v>
+      </c>
+      <c r="P645" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q645" t="str">
+        <v>4</v>
+      </c>
+      <c r="R645" t="str">
+        <v>0</v>
+      </c>
+      <c r="S645" t="str">
+        <v>3</v>
+      </c>
+      <c r="T645" t="str">
+        <v>4/28/26</v>
+      </c>
+      <c r="U645" t="str">
+        <v>8/1/26</v>
+      </c>
+      <c r="V645" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="W645" t="str">
+        <v>NGÂN</v>
+      </c>
+      <c r="X645" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="Z645" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="AA645" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="646">
+      <c r="A646" t="str">
+        <v>(2110)</v>
+      </c>
+      <c r="B646" t="str">
+        <v>(1) Viet Nga Group, (2) Viet Nga Group - NN số 2</v>
+      </c>
+      <c r="C646" t="str">
+        <v>65924</v>
+      </c>
+      <c r="D646" t="str">
+        <v>388445205</v>
+      </c>
+      <c r="E646" t="str">
+        <v>LÊ THỊ BÍA</v>
+      </c>
+      <c r="F646" t="str">
+        <v>Intensive rice production // Trồng lúa thâm canh</v>
+      </c>
+      <c r="G646" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="H646" t="str">
+        <v>Female // Nữ</v>
+      </c>
+      <c r="I646" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="J646" t="str">
+        <v>NO</v>
+      </c>
+      <c r="K646" t="str">
+        <v>1</v>
+      </c>
+      <c r="L646" t="str">
+        <v>0</v>
+      </c>
+      <c r="M646" t="str">
+        <v>0</v>
+      </c>
+      <c r="N646" t="str">
+        <v>0</v>
+      </c>
+      <c r="O646" t="str">
+        <v>0</v>
+      </c>
+      <c r="P646" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q646" t="str">
+        <v>2</v>
+      </c>
+      <c r="R646" t="str">
+        <v>0</v>
+      </c>
+      <c r="S646" t="str">
+        <v>1</v>
+      </c>
+      <c r="T646" t="str">
+        <v>4/28/26</v>
+      </c>
+      <c r="U646" t="str">
+        <v>8/1/26</v>
+      </c>
+      <c r="V646" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="W646" t="str">
+        <v>NGÂN</v>
+      </c>
+      <c r="X646" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="Z646" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="AA646" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="647">
+      <c r="A647" t="str">
+        <v>(2111)</v>
+      </c>
+      <c r="B647" t="str">
+        <v>(1) Viet Nga Group, (2) Viet Nga Group - NN số 2</v>
+      </c>
+      <c r="C647" t="str">
+        <v>65925</v>
+      </c>
+      <c r="D647" t="str">
+        <v>377105512</v>
+      </c>
+      <c r="E647" t="str">
+        <v>LÊ THỊ LOAN</v>
+      </c>
+      <c r="F647" t="str">
+        <v>Intensive rice production // Trồng lúa thâm canh</v>
+      </c>
+      <c r="G647" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="H647" t="str">
+        <v>Female // Nữ</v>
+      </c>
+      <c r="I647" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="J647" t="str">
+        <v>NO</v>
+      </c>
+      <c r="K647" t="str">
+        <v>1</v>
+      </c>
+      <c r="L647" t="str">
+        <v>0</v>
+      </c>
+      <c r="M647" t="str">
+        <v>0</v>
+      </c>
+      <c r="N647" t="str">
+        <v>0</v>
+      </c>
+      <c r="O647" t="str">
+        <v>0</v>
+      </c>
+      <c r="P647" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q647" t="str">
+        <v>3</v>
+      </c>
+      <c r="R647" t="str">
+        <v>0</v>
+      </c>
+      <c r="S647" t="str">
+        <v>2</v>
+      </c>
+      <c r="T647" t="str">
+        <v>4/28/26</v>
+      </c>
+      <c r="U647" t="str">
+        <v>8/1/26</v>
+      </c>
+      <c r="V647" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="W647" t="str">
+        <v>NGÂN</v>
+      </c>
+      <c r="X647" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="Z647" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="AA647" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="648">
+      <c r="A648" t="str">
+        <v>(2114)</v>
+      </c>
+      <c r="B648" t="str">
+        <v>(1) Viet Nga Group, (2) Viet Nga Group - NN số 2</v>
+      </c>
+      <c r="C648" t="str">
+        <v>65928</v>
+      </c>
+      <c r="D648" t="str">
+        <v>939078660</v>
+      </c>
+      <c r="E648" t="str">
+        <v>VÕ VĂN LÊN</v>
+      </c>
+      <c r="F648" t="str">
+        <v>Intensive rice production // Trồng lúa thâm canh</v>
+      </c>
+      <c r="G648" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="H648" t="str">
+        <v>Male // Nam</v>
+      </c>
+      <c r="I648" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="J648" t="str">
+        <v>NO</v>
+      </c>
+      <c r="K648" t="str">
+        <v>0</v>
+      </c>
+      <c r="L648" t="str">
+        <v>0</v>
+      </c>
+      <c r="M648" t="str">
+        <v>0</v>
+      </c>
+      <c r="N648" t="str">
+        <v>0</v>
+      </c>
+      <c r="O648" t="str">
+        <v>0</v>
+      </c>
+      <c r="P648" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q648" t="str">
+        <v>4</v>
+      </c>
+      <c r="R648" t="str">
+        <v>0</v>
+      </c>
+      <c r="S648" t="str">
+        <v>3</v>
+      </c>
+      <c r="T648" t="str">
+        <v>4/28/26</v>
+      </c>
+      <c r="U648" t="str">
+        <v>8/1/26</v>
+      </c>
+      <c r="V648" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="W648" t="str">
+        <v>NGÂN</v>
+      </c>
+      <c r="X648" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="Z648" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="AA648" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="649">
+      <c r="A649" t="str">
+        <v>(2116)</v>
+      </c>
+      <c r="B649" t="str">
+        <v>(1) Viet Nga Group, (2) Viet Nga Group - NN số 2</v>
+      </c>
+      <c r="C649" t="str">
+        <v>65931</v>
+      </c>
+      <c r="D649" t="str">
+        <v>894526922</v>
+      </c>
+      <c r="E649" t="str">
+        <v>LÊ VĂN TOÁN</v>
+      </c>
+      <c r="F649" t="str">
+        <v>Intensive rice production // Trồng lúa thâm canh</v>
+      </c>
+      <c r="G649" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="H649" t="str">
+        <v>Male // Nam</v>
+      </c>
+      <c r="I649" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="J649" t="str">
+        <v>NO</v>
+      </c>
+      <c r="K649" t="str">
+        <v>0</v>
+      </c>
+      <c r="L649" t="str">
+        <v>0</v>
+      </c>
+      <c r="M649" t="str">
+        <v>0</v>
+      </c>
+      <c r="N649" t="str">
+        <v>0</v>
+      </c>
+      <c r="O649" t="str">
+        <v>0</v>
+      </c>
+      <c r="P649" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q649" t="str">
+        <v>4</v>
+      </c>
+      <c r="R649" t="str">
+        <v>0</v>
+      </c>
+      <c r="S649" t="str">
+        <v>3</v>
+      </c>
+      <c r="T649" t="str">
+        <v>4/28/26</v>
+      </c>
+      <c r="U649" t="str">
+        <v>8/1/26</v>
+      </c>
+      <c r="V649" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="W649" t="str">
+        <v>NGÂN</v>
+      </c>
+      <c r="X649" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="Z649" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="AA649" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="650">
+      <c r="A650" t="str">
+        <v>(2117)</v>
+      </c>
+      <c r="B650" t="str">
+        <v>(1) Viet Nga Group, (2) Viet Nga Group - NN số 2</v>
+      </c>
+      <c r="C650" t="str">
+        <v>65932</v>
+      </c>
+      <c r="D650" t="str">
+        <v>738961332</v>
+      </c>
+      <c r="E650" t="str">
+        <v>PHAN VĂN PHƯỚC EM</v>
+      </c>
+      <c r="F650" t="str">
+        <v>Intensive rice production // Trồng lúa thâm canh</v>
+      </c>
+      <c r="G650" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="H650" t="str">
+        <v>Male // Nam</v>
+      </c>
+      <c r="I650" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="J650" t="str">
+        <v>NO</v>
+      </c>
+      <c r="K650" t="str">
+        <v>0</v>
+      </c>
+      <c r="L650" t="str">
+        <v>0</v>
+      </c>
+      <c r="M650" t="str">
+        <v>0</v>
+      </c>
+      <c r="N650" t="str">
+        <v>0</v>
+      </c>
+      <c r="O650" t="str">
+        <v>0</v>
+      </c>
+      <c r="P650" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q650" t="str">
+        <v>3</v>
+      </c>
+      <c r="R650" t="str">
+        <v>0</v>
+      </c>
+      <c r="S650" t="str">
+        <v>2</v>
+      </c>
+      <c r="T650" t="str">
+        <v>4/28/26</v>
+      </c>
+      <c r="U650" t="str">
+        <v>8/1/26</v>
+      </c>
+      <c r="V650" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="W650" t="str">
+        <v>NGÂN</v>
+      </c>
+      <c r="X650" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="Z650" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="AA650" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="651">
+      <c r="A651" t="str">
+        <v>(2118)</v>
+      </c>
+      <c r="B651" t="str">
+        <v>(1) Viet Nga Group, (2) Viet Nga Group - NN số 2</v>
+      </c>
+      <c r="C651" t="str">
+        <v>66882</v>
+      </c>
+      <c r="D651" t="str">
+        <v>969227829</v>
+      </c>
+      <c r="E651" t="str">
+        <v>NGÔ VĂN KHẾN</v>
+      </c>
+      <c r="F651" t="str">
+        <v>Intensive rice production // Trồng lúa thâm canh</v>
+      </c>
+      <c r="G651" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="H651" t="str">
+        <v>Male // Nam</v>
+      </c>
+      <c r="I651" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="J651" t="str">
+        <v>NO</v>
+      </c>
+      <c r="K651" t="str">
+        <v>0</v>
+      </c>
+      <c r="L651" t="str">
+        <v>0</v>
+      </c>
+      <c r="M651" t="str">
+        <v>0</v>
+      </c>
+      <c r="N651" t="str">
+        <v>0</v>
+      </c>
+      <c r="O651" t="str">
+        <v>0</v>
+      </c>
+      <c r="P651" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q651" t="str">
+        <v>2</v>
+      </c>
+      <c r="R651" t="str">
+        <v>0</v>
+      </c>
+      <c r="S651" t="str">
+        <v>1</v>
+      </c>
+      <c r="T651" t="str">
+        <v>4/28/26</v>
+      </c>
+      <c r="U651" t="str">
+        <v>8/1/26</v>
+      </c>
+      <c r="V651" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="W651" t="str">
+        <v>NGÂN</v>
+      </c>
+      <c r="X651" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="Z651" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="AA651" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="652">
+      <c r="A652" t="str">
+        <v>(2119)</v>
+      </c>
+      <c r="B652" t="str">
+        <v>(1) Viet Nga Group, (2) Viet Nga Group - NN số 2</v>
+      </c>
+      <c r="C652" t="str">
+        <v>66883</v>
+      </c>
+      <c r="D652" t="str">
+        <v>919667814</v>
+      </c>
+      <c r="E652" t="str">
+        <v>NGUYỄN THANH TÙNG</v>
+      </c>
+      <c r="F652" t="str">
+        <v>Intensive rice production // Trồng lúa thâm canh</v>
+      </c>
+      <c r="G652" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="H652" t="str">
+        <v>Male // Nam</v>
+      </c>
+      <c r="I652" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="J652" t="str">
+        <v>NO</v>
+      </c>
+      <c r="K652" t="str">
+        <v>0</v>
+      </c>
+      <c r="L652" t="str">
+        <v>0</v>
+      </c>
+      <c r="M652" t="str">
+        <v>0</v>
+      </c>
+      <c r="N652" t="str">
+        <v>0</v>
+      </c>
+      <c r="O652" t="str">
+        <v>0</v>
+      </c>
+      <c r="P652" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q652" t="str">
+        <v>2</v>
+      </c>
+      <c r="R652" t="str">
+        <v>0</v>
+      </c>
+      <c r="S652" t="str">
+        <v>1</v>
+      </c>
+      <c r="T652" t="str">
+        <v>4/28/26</v>
+      </c>
+      <c r="U652" t="str">
+        <v>8/1/26</v>
+      </c>
+      <c r="V652" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="W652" t="str">
+        <v>NGÂN</v>
+      </c>
+      <c r="X652" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="Z652" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="AA652" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="653">
+      <c r="A653" t="str">
+        <v>(2120)</v>
+      </c>
+      <c r="B653" t="str">
+        <v>(1) Viet Nga Group, (2) Viet Nga Group - NN số 2</v>
+      </c>
+      <c r="C653" t="str">
+        <v>66884</v>
+      </c>
+      <c r="D653" t="str">
+        <v>944370700</v>
+      </c>
+      <c r="E653" t="str">
+        <v>NGUYỄN THỊ BƯƠNG</v>
+      </c>
+      <c r="F653" t="str">
+        <v>Intensive rice production // Trồng lúa thâm canh</v>
+      </c>
+      <c r="G653" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="H653" t="str">
+        <v>Female // Nữ</v>
+      </c>
+      <c r="I653" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="J653" t="str">
+        <v>NO</v>
+      </c>
+      <c r="K653" t="str">
+        <v>1</v>
+      </c>
+      <c r="L653" t="str">
+        <v>0</v>
+      </c>
+      <c r="M653" t="str">
+        <v>0</v>
+      </c>
+      <c r="N653" t="str">
+        <v>0</v>
+      </c>
+      <c r="O653" t="str">
+        <v>0</v>
+      </c>
+      <c r="P653" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q653" t="str">
+        <v>3</v>
+      </c>
+      <c r="R653" t="str">
+        <v>0</v>
+      </c>
+      <c r="S653" t="str">
+        <v>2</v>
+      </c>
+      <c r="T653" t="str">
+        <v>4/28/26</v>
+      </c>
+      <c r="U653" t="str">
+        <v>8/1/26</v>
+      </c>
+      <c r="V653" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="W653" t="str">
+        <v>NGÂN</v>
+      </c>
+      <c r="X653" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="Z653" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="AA653" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="654">
+      <c r="A654" t="str">
+        <v>(2121)</v>
+      </c>
+      <c r="B654" t="str">
+        <v>(1) Viet Nga Group, (2) Viet Nga Group - NN số 2</v>
+      </c>
+      <c r="C654" t="str">
+        <v>66885</v>
+      </c>
+      <c r="D654" t="str">
+        <v>933747600</v>
+      </c>
+      <c r="E654" t="str">
+        <v>NGUYỄN THỊ HUYỀN HOA</v>
+      </c>
+      <c r="F654" t="str">
+        <v>Intensive rice production // Trồng lúa thâm canh</v>
+      </c>
+      <c r="G654" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="H654" t="str">
+        <v>Female // Nữ</v>
+      </c>
+      <c r="I654" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="J654" t="str">
+        <v>NO</v>
+      </c>
+      <c r="K654" t="str">
+        <v>1</v>
+      </c>
+      <c r="L654" t="str">
+        <v>0</v>
+      </c>
+      <c r="M654" t="str">
+        <v>0</v>
+      </c>
+      <c r="N654" t="str">
+        <v>0</v>
+      </c>
+      <c r="O654" t="str">
+        <v>0</v>
+      </c>
+      <c r="P654" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q654" t="str">
+        <v>2</v>
+      </c>
+      <c r="R654" t="str">
+        <v>0</v>
+      </c>
+      <c r="S654" t="str">
+        <v>1</v>
+      </c>
+      <c r="T654" t="str">
+        <v>4/28/26</v>
+      </c>
+      <c r="U654" t="str">
+        <v>8/1/26</v>
+      </c>
+      <c r="V654" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="W654" t="str">
+        <v>NGÂN</v>
+      </c>
+      <c r="X654" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="Z654" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="AA654" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="655">
+      <c r="A655" t="str">
+        <v>(2122)</v>
+      </c>
+      <c r="B655" t="str">
+        <v>(1) Viet Nga Group, (2) Viet Nga Group - NN số 2</v>
+      </c>
+      <c r="C655" t="str">
+        <v>66886</v>
+      </c>
+      <c r="D655" t="str">
+        <v>939082024</v>
+      </c>
+      <c r="E655" t="str">
+        <v>NGUYỄN THỊ NGỢI</v>
+      </c>
+      <c r="F655" t="str">
+        <v>Intensive rice production // Trồng lúa thâm canh</v>
+      </c>
+      <c r="G655" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="H655" t="str">
+        <v>Female // Nữ</v>
+      </c>
+      <c r="I655" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="J655" t="str">
+        <v>NO</v>
+      </c>
+      <c r="K655" t="str">
+        <v>1</v>
+      </c>
+      <c r="L655" t="str">
+        <v>0</v>
+      </c>
+      <c r="M655" t="str">
+        <v>0</v>
+      </c>
+      <c r="N655" t="str">
+        <v>0</v>
+      </c>
+      <c r="O655" t="str">
+        <v>0</v>
+      </c>
+      <c r="P655" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q655" t="str">
+        <v>3</v>
+      </c>
+      <c r="R655" t="str">
+        <v>0</v>
+      </c>
+      <c r="S655" t="str">
+        <v>2</v>
+      </c>
+      <c r="T655" t="str">
+        <v>4/28/26</v>
+      </c>
+      <c r="U655" t="str">
+        <v>8/1/26</v>
+      </c>
+      <c r="V655" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="W655" t="str">
+        <v>NGÂN</v>
+      </c>
+      <c r="X655" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="Z655" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="AA655" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="656">
+      <c r="A656" t="str">
+        <v>(2123)</v>
+      </c>
+      <c r="B656" t="str">
+        <v>(1) Viet Nga Group, (2) Viet Nga Group - NN số 2</v>
+      </c>
+      <c r="C656" t="str">
+        <v>66887</v>
+      </c>
+      <c r="D656" t="str">
+        <v>968221043</v>
+      </c>
+      <c r="E656" t="str">
+        <v>NGUYỄN THỊ NHU</v>
+      </c>
+      <c r="F656" t="str">
+        <v>Intensive rice production // Trồng lúa thâm canh</v>
+      </c>
+      <c r="G656" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="H656" t="str">
+        <v>Female // Nữ</v>
+      </c>
+      <c r="I656" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="J656" t="str">
+        <v>NO</v>
+      </c>
+      <c r="K656" t="str">
+        <v>1</v>
+      </c>
+      <c r="L656" t="str">
+        <v>0</v>
+      </c>
+      <c r="M656" t="str">
+        <v>0</v>
+      </c>
+      <c r="N656" t="str">
+        <v>0</v>
+      </c>
+      <c r="O656" t="str">
+        <v>0</v>
+      </c>
+      <c r="P656" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q656" t="str">
+        <v>4</v>
+      </c>
+      <c r="R656" t="str">
+        <v>0</v>
+      </c>
+      <c r="S656" t="str">
+        <v>3</v>
+      </c>
+      <c r="T656" t="str">
+        <v>4/28/26</v>
+      </c>
+      <c r="U656" t="str">
+        <v>8/1/26</v>
+      </c>
+      <c r="V656" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="W656" t="str">
+        <v>NGÂN</v>
+      </c>
+      <c r="X656" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="Z656" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="AA656" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="657">
+      <c r="A657" t="str">
+        <v>(2124)</v>
+      </c>
+      <c r="B657" t="str">
+        <v>(1) Viet Nga Group, (2) Viet Nga Group - NN số 2</v>
+      </c>
+      <c r="C657" t="str">
+        <v>66888</v>
+      </c>
+      <c r="D657" t="str">
+        <v>338771600</v>
+      </c>
+      <c r="E657" t="str">
+        <v>NGUYỄN THỊ PHẤN</v>
+      </c>
+      <c r="F657" t="str">
+        <v>Intensive rice production // Trồng lúa thâm canh</v>
+      </c>
+      <c r="G657" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="H657" t="str">
+        <v>Female // Nữ</v>
+      </c>
+      <c r="I657" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="J657" t="str">
+        <v>NO</v>
+      </c>
+      <c r="K657" t="str">
+        <v>1</v>
+      </c>
+      <c r="L657" t="str">
+        <v>0</v>
+      </c>
+      <c r="M657" t="str">
+        <v>0</v>
+      </c>
+      <c r="N657" t="str">
+        <v>0</v>
+      </c>
+      <c r="O657" t="str">
+        <v>0</v>
+      </c>
+      <c r="P657" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q657" t="str">
+        <v>3</v>
+      </c>
+      <c r="R657" t="str">
+        <v>0</v>
+      </c>
+      <c r="S657" t="str">
+        <v>2</v>
+      </c>
+      <c r="T657" t="str">
+        <v>4/28/26</v>
+      </c>
+      <c r="U657" t="str">
+        <v>8/1/26</v>
+      </c>
+      <c r="V657" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="W657" t="str">
+        <v>NGÂN</v>
+      </c>
+      <c r="X657" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="Z657" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="AA657" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="658">
+      <c r="A658" t="str">
+        <v>(2125)</v>
+      </c>
+      <c r="B658" t="str">
+        <v>(1) Viet Nga Group, (2) Viet Nga Group - NN số 2</v>
+      </c>
+      <c r="C658" t="str">
+        <v>66889</v>
+      </c>
+      <c r="D658" t="str">
+        <v>919869190</v>
+      </c>
+      <c r="E658" t="str">
+        <v>NGUYỄN THỊ THA</v>
+      </c>
+      <c r="F658" t="str">
+        <v>Intensive rice production // Trồng lúa thâm canh</v>
+      </c>
+      <c r="G658" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="H658" t="str">
+        <v>Female // Nữ</v>
+      </c>
+      <c r="I658" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="J658" t="str">
+        <v>NO</v>
+      </c>
+      <c r="K658" t="str">
+        <v>1</v>
+      </c>
+      <c r="L658" t="str">
+        <v>0</v>
+      </c>
+      <c r="M658" t="str">
+        <v>0</v>
+      </c>
+      <c r="N658" t="str">
+        <v>0</v>
+      </c>
+      <c r="O658" t="str">
+        <v>0</v>
+      </c>
+      <c r="P658" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q658" t="str">
+        <v>4</v>
+      </c>
+      <c r="R658" t="str">
+        <v>0</v>
+      </c>
+      <c r="S658" t="str">
+        <v>3</v>
+      </c>
+      <c r="T658" t="str">
+        <v>4/28/26</v>
+      </c>
+      <c r="U658" t="str">
+        <v>8/1/26</v>
+      </c>
+      <c r="V658" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="W658" t="str">
+        <v>NGÂN</v>
+      </c>
+      <c r="X658" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="Z658" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="AA658" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="659">
+      <c r="A659" t="str">
+        <v>(2126)</v>
+      </c>
+      <c r="B659" t="str">
+        <v>(1) Viet Nga Group, (2) Viet Nga Group - NN số 2</v>
+      </c>
+      <c r="C659" t="str">
+        <v>66890</v>
+      </c>
+      <c r="D659" t="str">
+        <v>339968565</v>
+      </c>
+      <c r="E659" t="str">
+        <v>NGUYỄN VĂN CÔNG</v>
+      </c>
+      <c r="F659" t="str">
+        <v>Intensive rice production // Trồng lúa thâm canh</v>
+      </c>
+      <c r="G659" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="H659" t="str">
+        <v>Male // Nam</v>
+      </c>
+      <c r="I659" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="J659" t="str">
+        <v>NO</v>
+      </c>
+      <c r="K659" t="str">
+        <v>0</v>
+      </c>
+      <c r="L659" t="str">
+        <v>0</v>
+      </c>
+      <c r="M659" t="str">
+        <v>0</v>
+      </c>
+      <c r="N659" t="str">
+        <v>0</v>
+      </c>
+      <c r="O659" t="str">
+        <v>0</v>
+      </c>
+      <c r="P659" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q659" t="str">
+        <v>2</v>
+      </c>
+      <c r="R659" t="str">
+        <v>0</v>
+      </c>
+      <c r="S659" t="str">
+        <v>1</v>
+      </c>
+      <c r="T659" t="str">
+        <v>4/28/26</v>
+      </c>
+      <c r="U659" t="str">
+        <v>8/1/26</v>
+      </c>
+      <c r="V659" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="W659" t="str">
+        <v>NGÂN</v>
+      </c>
+      <c r="X659" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="Z659" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="AA659" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="660">
+      <c r="A660" t="str">
+        <v>(2127)</v>
+      </c>
+      <c r="B660" t="str">
+        <v>(1) Viet Nga Group, (2) Viet Nga Group - NN số 2</v>
+      </c>
+      <c r="C660" t="str">
+        <v>66892</v>
+      </c>
+      <c r="D660" t="str">
+        <v>911137806</v>
+      </c>
+      <c r="E660" t="str">
+        <v>NGUYỄN VĂN DƯƠNG</v>
+      </c>
+      <c r="F660" t="str">
+        <v>Intensive rice production // Trồng lúa thâm canh</v>
+      </c>
+      <c r="G660" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="H660" t="str">
+        <v>Male // Nam</v>
+      </c>
+      <c r="I660" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="J660" t="str">
+        <v>NO</v>
+      </c>
+      <c r="K660" t="str">
+        <v>0</v>
+      </c>
+      <c r="L660" t="str">
+        <v>0</v>
+      </c>
+      <c r="M660" t="str">
+        <v>0</v>
+      </c>
+      <c r="N660" t="str">
+        <v>0</v>
+      </c>
+      <c r="O660" t="str">
+        <v>0</v>
+      </c>
+      <c r="P660" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q660" t="str">
+        <v>4</v>
+      </c>
+      <c r="R660" t="str">
+        <v>0</v>
+      </c>
+      <c r="S660" t="str">
+        <v>3</v>
+      </c>
+      <c r="T660" t="str">
+        <v>4/28/26</v>
+      </c>
+      <c r="U660" t="str">
+        <v>8/1/26</v>
+      </c>
+      <c r="V660" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="W660" t="str">
+        <v>NGÂN</v>
+      </c>
+      <c r="X660" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="Z660" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="AA660" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="661">
+      <c r="A661" t="str">
+        <v>(2128)</v>
+      </c>
+      <c r="B661" t="str">
+        <v>(1) Viet Nga Group, (2) Viet Nga Group - NN số 2</v>
+      </c>
+      <c r="C661" t="str">
+        <v>66893</v>
+      </c>
+      <c r="D661" t="str">
+        <v>904252449</v>
+      </c>
+      <c r="E661" t="str">
+        <v>NGUYỄN VĂN CẢNH</v>
+      </c>
+      <c r="F661" t="str">
+        <v>Intensive rice production // Trồng lúa thâm canh</v>
+      </c>
+      <c r="G661" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="H661" t="str">
+        <v>Male // Nam</v>
+      </c>
+      <c r="I661" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="J661" t="str">
+        <v>NO</v>
+      </c>
+      <c r="K661" t="str">
+        <v>0</v>
+      </c>
+      <c r="L661" t="str">
+        <v>0</v>
+      </c>
+      <c r="M661" t="str">
+        <v>0</v>
+      </c>
+      <c r="N661" t="str">
+        <v>0</v>
+      </c>
+      <c r="O661" t="str">
+        <v>0</v>
+      </c>
+      <c r="P661" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q661" t="str">
+        <v>2</v>
+      </c>
+      <c r="R661" t="str">
+        <v>0</v>
+      </c>
+      <c r="S661" t="str">
+        <v>1</v>
+      </c>
+      <c r="T661" t="str">
+        <v>4/28/26</v>
+      </c>
+      <c r="U661" t="str">
+        <v>8/1/26</v>
+      </c>
+      <c r="V661" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="W661" t="str">
+        <v>NGÂN</v>
+      </c>
+      <c r="X661" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="Z661" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="AA661" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="662">
+      <c r="A662" t="str">
+        <v>(2133)</v>
+      </c>
+      <c r="B662" t="str">
+        <v>(1) Viet Nga Group, (2) Viet Nga Group - NN số 2</v>
+      </c>
+      <c r="C662" t="str">
+        <v>66896</v>
+      </c>
+      <c r="D662" t="str">
+        <v>978623803</v>
+      </c>
+      <c r="E662" t="str">
+        <v>NGUYỄN VĂN TĂNG</v>
+      </c>
+      <c r="F662" t="str">
+        <v>Intensive rice production // Trồng lúa thâm canh</v>
+      </c>
+      <c r="G662" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="H662" t="str">
+        <v>Male // Nam</v>
+      </c>
+      <c r="I662" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="J662" t="str">
+        <v>NO</v>
+      </c>
+      <c r="K662" t="str">
+        <v>0</v>
+      </c>
+      <c r="L662" t="str">
+        <v>0</v>
+      </c>
+      <c r="M662" t="str">
+        <v>0</v>
+      </c>
+      <c r="N662" t="str">
+        <v>0</v>
+      </c>
+      <c r="O662" t="str">
+        <v>0</v>
+      </c>
+      <c r="P662" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q662" t="str">
+        <v>4</v>
+      </c>
+      <c r="R662" t="str">
+        <v>0</v>
+      </c>
+      <c r="S662" t="str">
+        <v>3</v>
+      </c>
+      <c r="T662" t="str">
+        <v>4/28/26</v>
+      </c>
+      <c r="U662" t="str">
+        <v>8/1/26</v>
+      </c>
+      <c r="V662" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="W662" t="str">
+        <v>NGÂN</v>
+      </c>
+      <c r="X662" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="Z662" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="AA662" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="663">
+      <c r="A663" t="str">
+        <v>(2137)</v>
+      </c>
+      <c r="B663" t="str">
+        <v>(1) Viet Nga Group, (2) Viet Nga Group - NN số 2</v>
+      </c>
+      <c r="C663" t="str">
+        <v>66900</v>
+      </c>
+      <c r="D663" t="str">
+        <v>358402817</v>
+      </c>
+      <c r="E663" t="str">
+        <v>PHẠM THỊ MÃI</v>
+      </c>
+      <c r="F663" t="str">
+        <v>Intensive rice production // Trồng lúa thâm canh</v>
+      </c>
+      <c r="G663" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="H663" t="str">
+        <v>Female // Nữ</v>
+      </c>
+      <c r="I663" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="J663" t="str">
+        <v>NO</v>
+      </c>
+      <c r="K663" t="str">
+        <v>1</v>
+      </c>
+      <c r="L663" t="str">
+        <v>0</v>
+      </c>
+      <c r="M663" t="str">
+        <v>0</v>
+      </c>
+      <c r="N663" t="str">
+        <v>0</v>
+      </c>
+      <c r="O663" t="str">
+        <v>0</v>
+      </c>
+      <c r="P663" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q663" t="str">
+        <v>3</v>
+      </c>
+      <c r="R663" t="str">
+        <v>0</v>
+      </c>
+      <c r="S663" t="str">
+        <v>2</v>
+      </c>
+      <c r="T663" t="str">
+        <v>4/28/26</v>
+      </c>
+      <c r="U663" t="str">
+        <v>8/1/26</v>
+      </c>
+      <c r="V663" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="W663" t="str">
+        <v>NGÂN</v>
+      </c>
+      <c r="X663" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="Z663" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="AA663" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="664">
+      <c r="A664" t="str">
+        <v>(2142)</v>
+      </c>
+      <c r="B664" t="str">
+        <v>(1) Viet Nga Group, (2) Viet Nga Group - NN số 2</v>
+      </c>
+      <c r="C664" t="str">
+        <v>66903</v>
+      </c>
+      <c r="D664" t="str">
+        <v>398392735</v>
+      </c>
+      <c r="E664" t="str">
+        <v>TRẦN MINH THUẬN</v>
+      </c>
+      <c r="F664" t="str">
+        <v>Intensive rice production // Trồng lúa thâm canh</v>
+      </c>
+      <c r="G664" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="H664" t="str">
+        <v>Male // Nam</v>
+      </c>
+      <c r="I664" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="J664" t="str">
+        <v>NO</v>
+      </c>
+      <c r="K664" t="str">
+        <v>0</v>
+      </c>
+      <c r="L664" t="str">
+        <v>0</v>
+      </c>
+      <c r="M664" t="str">
+        <v>0</v>
+      </c>
+      <c r="N664" t="str">
+        <v>0</v>
+      </c>
+      <c r="O664" t="str">
+        <v>0</v>
+      </c>
+      <c r="P664" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q664" t="str">
+        <v>2</v>
+      </c>
+      <c r="R664" t="str">
+        <v>0</v>
+      </c>
+      <c r="S664" t="str">
+        <v>1</v>
+      </c>
+      <c r="T664" t="str">
+        <v>4/28/26</v>
+      </c>
+      <c r="U664" t="str">
+        <v>8/1/26</v>
+      </c>
+      <c r="V664" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="W664" t="str">
+        <v>NGÂN</v>
+      </c>
+      <c r="X664" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="Z664" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="AA664" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="665">
+      <c r="A665" t="str">
+        <v>(2149)</v>
+      </c>
+      <c r="B665" t="str">
+        <v>(1) Viet Nga Group, (2) Viet Nga Group - NN số 2</v>
+      </c>
+      <c r="C665" t="str">
+        <v>66907</v>
+      </c>
+      <c r="D665" t="str">
+        <v>914696967</v>
+      </c>
+      <c r="E665" t="str">
+        <v>LÊ THỊ THU VÂN</v>
+      </c>
+      <c r="F665" t="str">
+        <v>Intensive rice production // Trồng lúa thâm canh</v>
+      </c>
+      <c r="G665" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="H665" t="str">
+        <v>Female // Nữ</v>
+      </c>
+      <c r="I665" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="J665" t="str">
+        <v>NO</v>
+      </c>
+      <c r="K665" t="str">
+        <v>1</v>
+      </c>
+      <c r="L665" t="str">
+        <v>0</v>
+      </c>
+      <c r="M665" t="str">
+        <v>0</v>
+      </c>
+      <c r="N665" t="str">
+        <v>0</v>
+      </c>
+      <c r="O665" t="str">
+        <v>0</v>
+      </c>
+      <c r="P665" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q665" t="str">
+        <v>3</v>
+      </c>
+      <c r="R665" t="str">
+        <v>0</v>
+      </c>
+      <c r="S665" t="str">
+        <v>2</v>
+      </c>
+      <c r="T665" t="str">
+        <v>4/28/26</v>
+      </c>
+      <c r="U665" t="str">
+        <v>8/1/26</v>
+      </c>
+      <c r="V665" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="W665" t="str">
+        <v>NGÂN</v>
+      </c>
+      <c r="X665" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="Z665" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="AA665" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="666">
+      <c r="A666" t="str">
+        <v>(2152)</v>
+      </c>
+      <c r="B666" t="str">
+        <v>(1) Viet Nga Group, (2) Viet Nga Group - NN số 2</v>
+      </c>
+      <c r="C666" t="str">
+        <v>66909</v>
+      </c>
+      <c r="D666" t="str">
+        <v>343396665</v>
+      </c>
+      <c r="E666" t="str">
+        <v>VÕ THỊ XUÂN HƯỜNG</v>
+      </c>
+      <c r="F666" t="str">
+        <v>Intensive rice production // Trồng lúa thâm canh</v>
+      </c>
+      <c r="G666" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="H666" t="str">
+        <v>Female // Nữ</v>
+      </c>
+      <c r="I666" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="J666" t="str">
+        <v>NO</v>
+      </c>
+      <c r="K666" t="str">
+        <v>1</v>
+      </c>
+      <c r="L666" t="str">
+        <v>0</v>
+      </c>
+      <c r="M666" t="str">
+        <v>0</v>
+      </c>
+      <c r="N666" t="str">
+        <v>0</v>
+      </c>
+      <c r="O666" t="str">
+        <v>0</v>
+      </c>
+      <c r="P666" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q666" t="str">
+        <v>3</v>
+      </c>
+      <c r="R666" t="str">
+        <v>0</v>
+      </c>
+      <c r="S666" t="str">
+        <v>2</v>
+      </c>
+      <c r="T666" t="str">
+        <v>4/28/26</v>
+      </c>
+      <c r="U666" t="str">
+        <v>8/1/26</v>
+      </c>
+      <c r="V666" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="W666" t="str">
+        <v>NGÂN</v>
+      </c>
+      <c r="X666" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="Z666" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="AA666" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="667">
+      <c r="A667" t="str">
+        <v>(2157)</v>
+      </c>
+      <c r="B667" t="str">
+        <v>(1) Viet Nga Group, (2) Viet Nga Group - NN số 2</v>
+      </c>
+      <c r="C667" t="str">
+        <v>66912</v>
+      </c>
+      <c r="D667" t="str">
+        <v>708613247</v>
+      </c>
+      <c r="E667" t="str">
+        <v>HỒ MINH QUANG</v>
+      </c>
+      <c r="F667" t="str">
+        <v>Intensive rice production // Trồng lúa thâm canh</v>
+      </c>
+      <c r="G667" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="H667" t="str">
+        <v>Male // Nam</v>
+      </c>
+      <c r="I667" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="J667" t="str">
+        <v>NO</v>
+      </c>
+      <c r="K667" t="str">
+        <v>0</v>
+      </c>
+      <c r="L667" t="str">
+        <v>0</v>
+      </c>
+      <c r="M667" t="str">
+        <v>0</v>
+      </c>
+      <c r="N667" t="str">
+        <v>0</v>
+      </c>
+      <c r="O667" t="str">
+        <v>0</v>
+      </c>
+      <c r="P667" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q667" t="str">
+        <v>2</v>
+      </c>
+      <c r="R667" t="str">
+        <v>0</v>
+      </c>
+      <c r="S667" t="str">
+        <v>1</v>
+      </c>
+      <c r="T667" t="str">
+        <v>4/28/26</v>
+      </c>
+      <c r="U667" t="str">
+        <v>8/1/26</v>
+      </c>
+      <c r="V667" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="W667" t="str">
+        <v>NGÂN</v>
+      </c>
+      <c r="X667" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="Z667" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="AA667" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="668">
+      <c r="A668" t="str">
+        <v>(2158)</v>
+      </c>
+      <c r="B668" t="str">
+        <v>(1) Viet Nga Group, (2) Viet Nga Group - NN số 2</v>
+      </c>
+      <c r="C668" t="str">
+        <v>66914</v>
+      </c>
+      <c r="D668" t="str">
+        <v>366624702</v>
+      </c>
+      <c r="E668" t="str">
+        <v>PHAN THANH CƯỜNG</v>
+      </c>
+      <c r="F668" t="str">
+        <v>Intensive rice production // Trồng lúa thâm canh</v>
+      </c>
+      <c r="G668" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="H668" t="str">
+        <v>Male // Nam</v>
+      </c>
+      <c r="I668" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="J668" t="str">
+        <v>NO</v>
+      </c>
+      <c r="K668" t="str">
+        <v>0</v>
+      </c>
+      <c r="L668" t="str">
+        <v>0</v>
+      </c>
+      <c r="M668" t="str">
+        <v>0</v>
+      </c>
+      <c r="N668" t="str">
+        <v>0</v>
+      </c>
+      <c r="O668" t="str">
+        <v>0</v>
+      </c>
+      <c r="P668" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q668" t="str">
+        <v>4</v>
+      </c>
+      <c r="R668" t="str">
+        <v>0</v>
+      </c>
+      <c r="S668" t="str">
+        <v>3</v>
+      </c>
+      <c r="T668" t="str">
+        <v>4/28/26</v>
+      </c>
+      <c r="U668" t="str">
+        <v>8/1/26</v>
+      </c>
+      <c r="V668" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="W668" t="str">
+        <v>NGÂN</v>
+      </c>
+      <c r="X668" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="Z668" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="AA668" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="669">
+      <c r="A669" t="str">
+        <v>(2164)</v>
+      </c>
+      <c r="B669" t="str">
+        <v>(1) Viet Nga Group, (2) Viet Nga Group - NN số 2</v>
+      </c>
+      <c r="C669" t="str">
+        <v>66918</v>
+      </c>
+      <c r="D669" t="str">
+        <v>986097330</v>
+      </c>
+      <c r="E669" t="str">
+        <v>TRẦN VĂN DẪU</v>
+      </c>
+      <c r="F669" t="str">
+        <v>Intensive rice production // Trồng lúa thâm canh</v>
+      </c>
+      <c r="G669" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="H669" t="str">
+        <v>Male // Nam</v>
+      </c>
+      <c r="I669" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="J669" t="str">
+        <v>NO</v>
+      </c>
+      <c r="K669" t="str">
+        <v>0</v>
+      </c>
+      <c r="L669" t="str">
+        <v>0</v>
+      </c>
+      <c r="M669" t="str">
+        <v>0</v>
+      </c>
+      <c r="N669" t="str">
+        <v>0</v>
+      </c>
+      <c r="O669" t="str">
+        <v>0</v>
+      </c>
+      <c r="P669" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q669" t="str">
+        <v>3</v>
+      </c>
+      <c r="R669" t="str">
+        <v>0</v>
+      </c>
+      <c r="S669" t="str">
+        <v>2</v>
+      </c>
+      <c r="T669" t="str">
+        <v>4/28/26</v>
+      </c>
+      <c r="U669" t="str">
+        <v>8/1/26</v>
+      </c>
+      <c r="V669" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="W669" t="str">
+        <v>NGÂN</v>
+      </c>
+      <c r="X669" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="Z669" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="AA669" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="670">
+      <c r="A670" t="str">
+        <v>(3972)</v>
+      </c>
+      <c r="B670" t="str">
+        <v>(1) Viet Nga Group, (2) Việt Nga Group-HTX DVNN Bình Hiệp B</v>
+      </c>
+      <c r="C670" t="str">
+        <v>81372</v>
+      </c>
+      <c r="D670" t="str">
+        <v>706598599</v>
+      </c>
+      <c r="E670" t="str">
+        <v>BÙI VĂN TRỰC</v>
+      </c>
+      <c r="F670" t="str">
+        <v>Intensive rice production // Trồng lúa thâm canh</v>
+      </c>
+      <c r="G670" t="str">
+        <v>Residue removal; Rate reduction; Reduced planting density; Irrigation Management;</v>
+      </c>
+      <c r="H670" t="str">
+        <v>Male // Nam</v>
+      </c>
+      <c r="I670" t="str">
+        <v>KINH</v>
+      </c>
+      <c r="J670" t="str">
+        <v>NO</v>
+      </c>
+      <c r="K670" t="str">
+        <v>0</v>
+      </c>
+      <c r="L670" t="str">
+        <v>0</v>
+      </c>
+      <c r="M670" t="str">
+        <v>0</v>
+      </c>
+      <c r="N670" t="str">
+        <v>0</v>
+      </c>
+      <c r="O670" t="str">
+        <v>0</v>
+      </c>
+      <c r="P670" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q670" t="str">
+        <v>2</v>
+      </c>
+      <c r="R670" t="str">
+        <v>0</v>
+      </c>
+      <c r="S670" t="str">
+        <v>1</v>
+      </c>
+      <c r="T670" t="str">
+        <v>4/10/26</v>
+      </c>
+      <c r="U670" t="str">
+        <v>7/14/26</v>
+      </c>
+      <c r="V670" t="str">
+        <v>Có thể nhập MRV</v>
+      </c>
+      <c r="X670" t="str">
+        <v>Ngân</v>
+      </c>
+      <c r="Z670" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="AA670" t="str">
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:AE611"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:AE670"/>
   </ignoredErrors>
 </worksheet>
 </file>